--- a/npi_dashboard.xlsx
+++ b/npi_dashboard.xlsx
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Prestige N16 Flip AI+</t>
+          <t>Prestige N16 Spark</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Prestige N16 AI+</t>
+          <t>Prestige N16 Flip Spark</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">

--- a/npi_dashboard.xlsx
+++ b/npi_dashboard.xlsx
@@ -148,10 +148,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -901,13 +901,12 @@
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>MLG(魔龍姬)ID，因盤點,排6/15 CR工單重工及測試，6/19入庫</t>
+          <t>MLG(魔龍姬)ID，CR工單已重工完成待入庫</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>1)Schedule：因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，MP時間受影響由6/9 delay至6/19
-2)備料: A/B件及rear cover重新備料，6/11首批交料500pcs，至6/30陸續可齊套交料共3.8K，與6月份出貨6.2K有2.4K gap</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1124,8 +1123,7 @@
       <c r="P8" s="6" t="inlineStr">
         <is>
           <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；
-2) Packing: WW版本設計確認中;
-3)Schedule: ID更換噴漆廠商,導致機構件缺料，ATS 由6/26更新為7/1，MP@7/8</t>
+2) Packing: WW版本設計確認中;</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1493,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>24VL</t>
+          <t>26VL</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Modern A14 LE J1M</t>
+          <t>Modern A16 LE J1M</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -1556,15 +1554,14 @@
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>MVT測試中，DQA 測試Issue 需微步協助盡快釐清&amp;導入對策，滿足ATS 6/E上線排程</t>
+          <t>MVT測試中，DQA 測試Issue 需微步協助盡快釐清&amp;導入對策,</t>
         </is>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步
-2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復）
-3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA，
-4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+          <t>1)物料： adapter：目標6K， 已到料2.8K ,其它7/B 陸續進料 B&amp;S物料： 6/18已寄送微步 ，預計6/22到料，
+2)認證 a))TUV 認證预计7/E b)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 c) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復）
+3）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，目前TTM時間預計從7/8 延後到7/10</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1571,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>24VL</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
+          <t>Modern A14 LE J1M</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -1625,25 +1622,24 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/07/01</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>MVT測試中，DQA 測試Issue 需微步協助盡快釐清&amp;導入對策,滿足ATS 6/E 規劃</t>
+          <t>MVT測試中，DQA 測試Issue 需微步協助盡快釐清&amp;導入對策，</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 2.8K ETA @ 6/15,其它7/B 陸續進料 B&amp;S物料：6/9 釋放PO給微步，需要微步6/12協助下單備料，目前規劃ATS 6/20 SMT，物料需在6/18前寄送到微步
-2)認證   a)CE：預計6/12認證ready  b)CB：24VL 6/2通知啟動認證，預計6/E ready  C)TUV 認證预计7/E  d)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 e) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG  ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復）
-3)TYPEC+USB4接口 SI测试Fail，需主板升级，6/8已安排SMT驗證，需微步加快SI驗證，已協調微步6/13到昆山更換PCBA，
-4）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，deadline 6/19</t>
+          <t>1)物料： adapter：目標6K， 已到料2.8K ,其它7/B 陸續進料 B&amp;S物料： 6/18已寄送微步 ，預計6/22到料，
+2)認證 a))TUV 認證预计7/E b)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 c) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復）
+3）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，目前TTM時間預計從7/8 延後到7/10</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1887,7 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>1) 台北RD已取得主板,需麻煩各RD加速相關驗證</t>
+          <t>1) 10 gerberout@6/25,需麻煩各RD加速相關驗證</t>
         </is>
       </c>
     </row>
@@ -2544,13 +2540,13 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>2026/06/21</t>
+          <t>2026/06/29</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr"/>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>2026/07/21</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -2560,7 +2556,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>2026/08/09</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2570,12 +2566,12 @@
       </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
-          <t>新料備料中, Weibu plan 6/21 DVT SMT</t>
+          <t>Weibu plan 6/29 DVT SMT, 7/1 ASSY--熱管&amp;D件重新開模, 交期7/1</t>
         </is>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>1)備料for 6/21: a. 熱管6/29交期還在pull in b. D件開模, 交期還在確認中
+          <t>1)Schedule: 考量新料備料時程, 調整試產和ATS時間@8/17 start
 2)認證: 參考Weibu認證Schedule, 有四個國家無法同步於8/E TTM, 持續追蹤中 MX: 11/28 ready；AR:10/3 ready；CO: 9/5 ready；RU: 9/12 ready</t>
         </is>
       </c>
@@ -2621,13 +2617,13 @@
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>2026/06/21</t>
+          <t>2026/06/29</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr"/>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>2026/07/21</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -2637,7 +2633,7 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>2026/08/09</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -2647,12 +2643,12 @@
       </c>
       <c r="O28" s="6" t="inlineStr">
         <is>
-          <t>新料備料中, Weibu plan 6/21 DVT SMT</t>
+          <t>Weibu plan 6/29 DVT SMT, 7/1 ASSY --熱管重新開模, 交期6/30</t>
         </is>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>1)備料for 6/21: a. 熱管6/29交期還在pull in b. D件開模, 交期還在確認中
+          <t>1)Schedule: 考量新料備料時程, 調整試產和ATS時間@8/17 start
 2)認證: 參考Weibu認證Schedule, 有四個國家無法同步於8/E TTM, 持續追蹤中 MX: 11/28 ready；AR:10/3 ready；CO: 9/5 ready；RU: 9/12 ready</t>
         </is>
       </c>
@@ -2663,151 +2659,143 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>14T3</t>
+          <t>15TK</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Prestige N14 Spark D1M</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>EVT</t>
+          <t>Cyborg A15 Max C1PWE</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>N1 35W</t>
+          <t>HWK 45W</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>倪嬌嬌</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>2025/04/30</t>
+          <t>2026/05/28</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>2025/09/01</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/15</t>
-        </is>
-      </c>
+          <t>2026/07/03</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>2026/07/20</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>2026/09/01</t>
+          <t>2026/09/07</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>2026/09/14</t>
+          <t>2026/09/17</t>
         </is>
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>EVT DQA更新BSP6.1.2 驗證中,  0C gerber out@6/17</t>
-        </is>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>1) 備料： 2.8K panel的驗證 follow leading customer, 交料plan:a. 1st MP lot: 2K 數量, 型號HQ15, 九月份交料(同步Leading customers量產交料時間 具體九月份ETD日期還在追蹤中. b. Others order: 需轉型號至HQxx, 十一月份交料</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
+          <t>AMD預計ww25寄出R9 180/R7 165, RD會先進行重工做開機驗證</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30" hidden="1" outlineLevel="1">
+      <c r="A30" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>15TK</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Cyborg A15 Max C1PWE</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Cyborg A15 Max C1PWF</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>HWK 45W</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H30" s="9" t="inlineStr">
         <is>
           <t>2026/05/28</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="I30" s="9" t="inlineStr">
         <is>
           <t>2026/07/03</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr"/>
-      <c r="K30" s="4" t="inlineStr">
+      <c r="J30" s="9" t="inlineStr"/>
+      <c r="K30" s="9" t="inlineStr">
         <is>
           <t>2026/08/06</t>
         </is>
       </c>
-      <c r="L30" s="4" t="inlineStr">
+      <c r="L30" s="9" t="inlineStr">
         <is>
           <t>2026/08/17</t>
         </is>
       </c>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="M30" s="9" t="inlineStr">
         <is>
           <t>2026/09/07</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="N30" s="9" t="inlineStr">
         <is>
           <t>2026/09/17</t>
         </is>
       </c>
-      <c r="O30" s="6" t="inlineStr">
+      <c r="O30" s="11" t="inlineStr">
         <is>
           <t>AMD預計ww25寄出R9 180/R7 165, RD會先進行重工做開機驗證</t>
         </is>
       </c>
-      <c r="P30" s="6" t="inlineStr"/>
+      <c r="P30" s="11" t="inlineStr"/>
     </row>
     <row r="31" hidden="1" outlineLevel="1">
       <c r="A31" s="7" t="n">
@@ -2820,10 +2808,10 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Cyborg A15 Max C1PWF</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
+          <t>Cyborg A15 Max C1PWG</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -2835,7 +2823,7 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
@@ -2892,10 +2880,10 @@
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Cyborg A15 Max C1PWG</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
+          <t>Cyborg A15 C1PWE</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -2907,7 +2895,7 @@
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -2922,108 +2910,117 @@
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>2026/07/03</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr"/>
       <c r="K32" s="9" t="inlineStr">
         <is>
-          <t>2026/08/06</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr">
         <is>
-          <t>2026/08/17</t>
+          <t>2026/08/27</t>
         </is>
       </c>
       <c r="M32" s="9" t="inlineStr">
         <is>
-          <t>2026/09/07</t>
+          <t>2026/09/19</t>
         </is>
       </c>
       <c r="N32" s="9" t="inlineStr">
         <is>
-          <t>2026/09/17</t>
+          <t>2026/09/29</t>
         </is>
       </c>
       <c r="O32" s="11" t="inlineStr">
         <is>
-          <t>AMD預計ww25寄出R9 180/R7 165, RD會先進行重工做開機驗證</t>
+          <t>AMD預計ww27寄出R7 155/ R5 125, RD會先進行重工做開機驗證</t>
         </is>
       </c>
       <c r="P32" s="11" t="inlineStr"/>
     </row>
-    <row r="33" hidden="1" outlineLevel="1">
-      <c r="A33" s="7" t="n">
+    <row r="33">
+      <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>15TK</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Cyborg A15 C1PWE</t>
-        </is>
-      </c>
-      <c r="D33" s="18" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>HWK 45W</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/17</t>
-        </is>
-      </c>
-      <c r="J33" s="9" t="inlineStr"/>
-      <c r="K33" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/19</t>
-        </is>
-      </c>
-      <c r="L33" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/27</t>
-        </is>
-      </c>
-      <c r="M33" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/19</t>
-        </is>
-      </c>
-      <c r="N33" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="O33" s="11" t="inlineStr">
-        <is>
-          <t>AMD預計ww27寄出R7 155/ R5 125, RD會先進行重工做開機驗證</t>
-        </is>
-      </c>
-      <c r="P33" s="11" t="inlineStr"/>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>14T3</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Prestige N14 Spark D1M</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>N1 35W</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>倪嬌嬌</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/30</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>2025/09/01</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/13</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/26</t>
+        </is>
+      </c>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>MVT SMT@7/20--depend on 0C PCB ETA</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>1) Schedule: NV update BSP時間Factory drop final ETA@10/6, 更新ATS start@10/13
+2)備料： 2.8K panel的驗證 follow leading customer, 交料plan:a. 1st MP lot: 1K 數量, 型號HQ15, 九月份交料(同步Leading customers量產交料時間 具體九月份ETD日期還在追蹤中. b. Others order: 需轉型號至HQxx, 十一月份交料</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -3039,7 +3036,7 @@
           <t>Prestige N16 Spark C1M</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="D34" s="18" t="inlineStr">
         <is>
           <t>EVT</t>
         </is>
@@ -3177,7 +3174,7 @@
       </c>
       <c r="O35" s="6" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: NV approved @ 6/11, DVT SMT @ 6/18</t>
+          <t>RPL-HX R + DDR5: DVT SMT @ 6/18 VBIOS先用2653的替用，待1861申請到後請HW重刷測試</t>
         </is>
       </c>
       <c r="P35" s="6" t="inlineStr">
@@ -3257,7 +3254,7 @@
       </c>
       <c r="O36" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: NV approved @ 6/11, DVT SMT @ 6/18</t>
+          <t>RPL-HX R + DDR5: DVT SMT @ 6/18 VBIOS先用2653的替用，待1861申請到後請HW重刷測試</t>
         </is>
       </c>
       <c r="P36" s="11" t="inlineStr">
@@ -3337,7 +3334,7 @@
       </c>
       <c r="O37" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: NV approved @ 6/11, DVT SMT @ 6/18</t>
+          <t>RPL-HX R + DDR5: DVT SMT @ 6/18 VBIOS先用2653的替用，待1861申請到後請HW重刷測試</t>
         </is>
       </c>
       <c r="P37" s="11" t="inlineStr">
@@ -3413,7 +3410,7 @@
       </c>
       <c r="O38" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: 3.0 G/O @ 6/12, 預計DVT SMT @ 6/27</t>
+          <t>RPL-HX R + DDR4: 預計DVT SMT @ 6/29</t>
         </is>
       </c>
       <c r="P38" s="11" t="inlineStr">
@@ -3489,7 +3486,7 @@
       </c>
       <c r="O39" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: 3.0 G/O @ 6/12, 預計DVT SMT @ 6/27</t>
+          <t>RPL-HX R + DDR4: 預計DVT SMT @ 6/29</t>
         </is>
       </c>
       <c r="P39" s="11" t="inlineStr">
@@ -3565,7 +3562,7 @@
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: 3.0 G/O @ 6/12, 預計DVT SMT @ 6/27</t>
+          <t>RPL-HX R + DDR4: 預計DVT SMT @ 6/29</t>
         </is>
       </c>
       <c r="P40" s="11" t="inlineStr">
@@ -3645,7 +3642,7 @@
       </c>
       <c r="O41" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: NV approved @ 6/11, DVT SMT @ 6/18</t>
+          <t>RPL-HX R + DDR5: DVT SMT @ 6/18 VBIOS先用2653的替用，待1861申請到後請HW重刷測試</t>
         </is>
       </c>
       <c r="P41" s="11" t="inlineStr">
@@ -3721,7 +3718,7 @@
       </c>
       <c r="O42" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: 3.0 G/O @ 6/12, 預計DVT SMT @ 6/27</t>
+          <t>RPL-HX R + DDR4: 預計DVT SMT @ 6/29</t>
         </is>
       </c>
       <c r="P42" s="11" t="inlineStr">
@@ -3801,7 +3798,7 @@
       </c>
       <c r="O43" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: NV approved @ 6/11, DVT SMT @ 6/18</t>
+          <t>RPL-HX R + DDR5: DVT SMT @ 6/18 VBIOS先用2653的替用，待1861申請到後請HW重刷測試</t>
         </is>
       </c>
       <c r="P43" s="11" t="inlineStr">
@@ -3877,7 +3874,7 @@
       </c>
       <c r="O44" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: 3.0 G/O @ 6/12, 預計DVT SMT @ 6/27</t>
+          <t>RPL-HX R + DDR4: 預計DVT SMT @ 6/29</t>
         </is>
       </c>
       <c r="P44" s="11" t="inlineStr">
@@ -3957,7 +3954,7 @@
       </c>
       <c r="O45" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: NV approved @ 6/11, DVT SMT @ 6/18</t>
+          <t>RPL-HX R + DDR5: DVT SMT @ 6/18 VBIOS先用2653的替用，待1861申請到後請HW重刷測試</t>
         </is>
       </c>
       <c r="P45" s="11" t="inlineStr">
@@ -4033,7 +4030,7 @@
       </c>
       <c r="O46" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: 3.0 G/O @ 6/12, 預計DVT SMT @ 6/27</t>
+          <t>RPL-HX R + DDR4: 預計DVT SMT @ 6/29</t>
         </is>
       </c>
       <c r="P46" s="11" t="inlineStr">
@@ -4113,7 +4110,7 @@
       </c>
       <c r="O47" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: NV approved @ 6/11, DVT SMT @ 6/18</t>
+          <t>RPL-HX R + DDR5: DVT SMT @ 6/18 VBIOS先用2653的替用，待1861申請到後請HW重刷測試</t>
         </is>
       </c>
       <c r="P47" s="11" t="inlineStr">
@@ -4189,7 +4186,7 @@
       </c>
       <c r="O48" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: 3.0 G/O @ 6/12, 預計DVT SMT @ 6/27</t>
+          <t>RPL-HX R + DDR4: 預計DVT SMT @ 6/29</t>
         </is>
       </c>
       <c r="P48" s="11" t="inlineStr">
@@ -4212,7 +4209,7 @@
           <t>Crosshair 18 Max HX B2WE</t>
         </is>
       </c>
-      <c r="D49" s="18" t="inlineStr">
+      <c r="D49" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4284,7 +4281,7 @@
           <t>Crosshair 18 Max HX B2WEO</t>
         </is>
       </c>
-      <c r="D50" s="18" t="inlineStr">
+      <c r="D50" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4356,7 +4353,7 @@
           <t>Crosshair 18 Max HX B2WF</t>
         </is>
       </c>
-      <c r="D51" s="18" t="inlineStr">
+      <c r="D51" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4428,7 +4425,7 @@
           <t>Crosshair 18 Max HX B2WFO</t>
         </is>
       </c>
-      <c r="D52" s="18" t="inlineStr">
+      <c r="D52" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4500,7 +4497,7 @@
           <t>Crosshair 18 Max HX B2WG</t>
         </is>
       </c>
-      <c r="D53" s="18" t="inlineStr">
+      <c r="D53" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4572,7 +4569,7 @@
           <t>Crosshair 18 Max HX B2WGO</t>
         </is>
       </c>
-      <c r="D54" s="18" t="inlineStr">
+      <c r="D54" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4644,7 +4641,7 @@
           <t>Crosshair 18 Max HX B2WGX</t>
         </is>
       </c>
-      <c r="D55" s="18" t="inlineStr">
+      <c r="D55" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4716,7 +4713,7 @@
           <t>Crosshair 18 Max HX B2WGXO</t>
         </is>
       </c>
-      <c r="D56" s="18" t="inlineStr">
+      <c r="D56" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4788,7 +4785,7 @@
           <t>Katana 18 HX A2WEK</t>
         </is>
       </c>
-      <c r="D57" s="18" t="inlineStr">
+      <c r="D57" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4860,7 +4857,7 @@
           <t>Katana 18 HX A2WEOK</t>
         </is>
       </c>
-      <c r="D58" s="18" t="inlineStr">
+      <c r="D58" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4936,7 +4933,7 @@
           <t>Katana 18 HX A2WFK</t>
         </is>
       </c>
-      <c r="D59" s="18" t="inlineStr">
+      <c r="D59" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5008,7 +5005,7 @@
           <t>Katana 18 HX A2WFOK</t>
         </is>
       </c>
-      <c r="D60" s="18" t="inlineStr">
+      <c r="D60" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5084,7 +5081,7 @@
           <t>Katana 18 HX A2WGK</t>
         </is>
       </c>
-      <c r="D61" s="18" t="inlineStr">
+      <c r="D61" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5156,7 +5153,7 @@
           <t>Katana 18 HX A2WGOK</t>
         </is>
       </c>
-      <c r="D62" s="18" t="inlineStr">
+      <c r="D62" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5312,7 +5309,7 @@
           <t>Prestige 14 AI+ Flip</t>
         </is>
       </c>
-      <c r="D64" s="18" t="inlineStr">
+      <c r="D64" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5468,7 +5465,7 @@
           <t>Prestige 16 Flip AI+</t>
         </is>
       </c>
-      <c r="D66" s="18" t="inlineStr">
+      <c r="D66" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5624,7 +5621,7 @@
           <t>Stealth 16 AI+ B4WH</t>
         </is>
       </c>
-      <c r="D68" s="18" t="inlineStr">
+      <c r="D68" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5704,7 +5701,7 @@
           <t>Stealth 16 AI+ B4WJ</t>
         </is>
       </c>
-      <c r="D69" s="18" t="inlineStr">
+      <c r="D69" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5865,7 +5862,7 @@
           <t>Stealth 16 AI+ B4WF</t>
         </is>
       </c>
-      <c r="D71" s="18" t="inlineStr">
+      <c r="D71" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5946,7 +5943,7 @@
           <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
         </is>
       </c>
-      <c r="D72" s="18" t="inlineStr">
+      <c r="D72" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6027,7 +6024,7 @@
           <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
         </is>
       </c>
-      <c r="D73" s="18" t="inlineStr">
+      <c r="D73" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6188,7 +6185,7 @@
           <t>Raider 16 Max HX B4WI</t>
         </is>
       </c>
-      <c r="D75" s="18" t="inlineStr">
+      <c r="D75" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6268,7 +6265,7 @@
           <t>Raider 16 Max HX B4WJ</t>
         </is>
       </c>
-      <c r="D76" s="18" t="inlineStr">
+      <c r="D76" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6348,7 +6345,7 @@
           <t>Raider 16  HX B4WH</t>
         </is>
       </c>
-      <c r="D77" s="18" t="inlineStr">
+      <c r="D77" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6428,7 +6425,7 @@
           <t>Raider 16  HX B4WI</t>
         </is>
       </c>
-      <c r="D78" s="18" t="inlineStr">
+      <c r="D78" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6588,7 +6585,7 @@
           <t>Crosshair 16 Max HX E4WFK</t>
         </is>
       </c>
-      <c r="D80" s="18" t="inlineStr">
+      <c r="D80" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6668,7 +6665,7 @@
           <t>Crosshair 16 Max HX E4WGK</t>
         </is>
       </c>
-      <c r="D81" s="18" t="inlineStr">
+      <c r="D81" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6748,7 +6745,7 @@
           <t>Crosshair 16 Max HX E4WGXK</t>
         </is>
       </c>
-      <c r="D82" s="18" t="inlineStr">
+      <c r="D82" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>

--- a/npi_dashboard.xlsx
+++ b/npi_dashboard.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPI Dashboard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -148,10 +148,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -519,7 +519,7 @@
     <outlinePr summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P82"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -772,12 +772,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>15T1</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Cyborg 15 Toy Story Edition C13WE</t>
+          <t>Crosshair 16 HX MLG Edition E14WFK</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -787,39 +787,39 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>RPL-H 45W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>蔡東宏</t>
+          <t>劉芬</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>2026/04/08</t>
+          <t>2026/03/27</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr"/>
       <c r="J4" s="4" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2026/05/15</t>
+          <t>2026/05/21</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/04/30</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>2026/06/05</t>
+          <t>2026/05/30</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>Disney ID, 預計6/15 C/R Assy 26PN049119C*200, 6/18入庫</t>
+          <t>MLG(魔龍姬)ID，+9</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>Process:出口備案申請,預計6/22完成</t>
+          <t>1.因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，重新備料+驗證以致MP 6/9 delay至6/18</t>
         </is>
       </c>
     </row>
@@ -844,286 +844,286 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>14T2</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Crosshair 16 HX MLG Edition E14WFK</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>ATS</t>
+          <t>Prestige 14 Flip AI+ Rhône</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>MVT</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>PTL-H 30W</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>劉芬</t>
+          <t>朱芳芳</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>2026/03/27</t>
+          <t>2026/04/13</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2026/05/21</t>
+          <t>2026/05/10</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>2026/05/30</t>
+          <t>2026/06/23</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>2026/06/19</t>
+          <t>2026/06/30</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>MLG(魔龍姬)ID，CR工單已重工完成待入庫</t>
+          <t>梵谷特仕版 物料持續追踪，6/23 ATS CR，6/E出貨</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+          <t>ATS CR 6/22齊料 ，2nd MP 請ID&amp;Buyer持續pull in。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" hidden="1" outlineLevel="1">
+      <c r="A6" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>14T2</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Prestige 14 Flip AI+ Rhône</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Prestige 14 Flip AI+ Starry Night</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>PTL-H 30W</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>朱芳芳</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>2026/04/13</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr"/>
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>2026/05/10</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/22</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/23</t>
+        </is>
+      </c>
+      <c r="N6" s="9" t="inlineStr">
         <is>
           <t>2026/06/30</t>
         </is>
       </c>
-      <c r="O6" s="6" t="inlineStr">
-        <is>
-          <t>梵谷特仕版 物料持續追踪，規劃6/22 ATS CR，6/E出貨</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>C/D件陽極QUV測試NG ，改善阳极药水染料樣品測試中，6/14 提供測試結果，請ID&amp;Buyer持續pull in。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" hidden="1" outlineLevel="1">
-      <c r="A7" s="7" t="n">
+      <c r="O6" s="11" t="inlineStr">
+        <is>
+          <t>梵谷特仕版 物料持續追踪，規劃6/23 ATS CR，6/E出貨</t>
+        </is>
+      </c>
+      <c r="P6" s="11" t="inlineStr">
+        <is>
+          <t>ATS CR 6/22齊料 ，2nd MP 請ID&amp;Buyer持續pull in。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>14T2</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Prestige 14 Flip AI+ Starry Night</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>265L</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>PTL-H 30W</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>Intel® Arc™ Graphics</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>朱芳芳</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>2026/04/13</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr"/>
-      <c r="J7" s="9" t="inlineStr"/>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/10</t>
-        </is>
-      </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/22</t>
-        </is>
-      </c>
-      <c r="N7" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/30</t>
-        </is>
-      </c>
-      <c r="O7" s="11" t="inlineStr">
-        <is>
-          <t>梵谷特仕版 物料持續追踪，規劃6/22 ATS CR，6/E出貨</t>
-        </is>
-      </c>
-      <c r="P7" s="11" t="inlineStr">
-        <is>
-          <t>C/D件陽極QUV測試NG ，改善阳极药水染料樣品測試中，6/14 提供測試結果，請ID&amp;Buyer持續pull in。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>265L</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>DRG-HX 55W</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>RTX 5060</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>朱欣怡</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>2026/06/02</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>2026/05/26</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>2026/07/01</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>2026/07/08</t>
         </is>
       </c>
-      <c r="O8" s="6" t="inlineStr">
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>MLG(魔龍姬)ID: DQA 測試中</t>
         </is>
       </c>
-      <c r="P8" s="6" t="inlineStr">
+      <c r="P7" s="6" t="inlineStr">
         <is>
           <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；
 2) Packing: WW版本設計確認中;</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" hidden="1" outlineLevel="1">
+      <c r="A8" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>265L</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>DRG-HX 55W</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr"/>
+      <c r="J8" s="9" t="inlineStr"/>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/01</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="O8" s="11" t="inlineStr">
+        <is>
+          <t>MLG(魔龍姬)ID: DQA 測試中</t>
+        </is>
+      </c>
+      <c r="P8" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="O9" s="11" t="inlineStr">
         <is>
-          <t>MLG(魔龍姬)ID: DQA 測試中</t>
+          <t>MLG(魔龍姬)ID:  DQA 測試中</t>
         </is>
       </c>
       <c r="P9" s="11" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
@@ -1235,34 +1235,34 @@
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2025/10/22</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr"/>
       <c r="J10" s="9" t="inlineStr"/>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>2026/06/02</t>
+          <t>2026/05/18</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>2026/05/26</t>
+          <t>2026/06/16</t>
         </is>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>2026/07/01</t>
+          <t>2026/07/16</t>
         </is>
       </c>
       <c r="N10" s="9" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="O10" s="11" t="inlineStr">
         <is>
-          <t>MLG(魔龍姬)ID:  DQA 測試中</t>
+          <t>FRG (5/4通知resume）: DQA 測試中</t>
         </is>
       </c>
       <c r="P10" s="11" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WFK</t>
+          <t>Crosshair A16 HX E9WGXK</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
@@ -1364,12 +1364,12 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -1415,75 +1415,81 @@
         </is>
       </c>
     </row>
-    <row r="13" hidden="1" outlineLevel="1">
-      <c r="A13" s="7" t="n">
+    <row r="13">
+      <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>265L</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Crosshair A16 HX E9WGXK</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>26VL</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>FRG-HX3D 55W</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="I13" s="9" t="inlineStr"/>
-      <c r="J13" s="9" t="inlineStr"/>
-      <c r="K13" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/18</t>
-        </is>
-      </c>
-      <c r="L13" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/16</t>
-        </is>
-      </c>
-      <c r="M13" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/16</t>
-        </is>
-      </c>
-      <c r="N13" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
-      <c r="O13" s="11" t="inlineStr">
-        <is>
-          <t>FRG (5/4通知resume）: DQA 測試中</t>
-        </is>
-      </c>
-      <c r="P13" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>RMB 100 35W</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>2026/03/30</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/17</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/15</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>MVT測試中，DQA 測試Issue 需微步協助盡快釐清&amp;導入對策,</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>1)物料： adapter：目標6K， 已到料2.8K ,其它7/B 陸續進料 B&amp;S物料： 6/18已寄送微步 ，預計6/22到料，
+2)認證 a))TUV 認證预计7/E b)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 c) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG ,SG 無需認證，TH 認證已ready
+3）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，目前TTM時間預計從7/8 延後到7/10，</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1499,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>24VL</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
+          <t>Modern A14 LE J1M</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -1544,24 +1550,25 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/07/01</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>MVT測試中，DQA 測試Issue 需微步協助盡快釐清&amp;導入對策,</t>
+          <t>MVT測試中，DQA 測試Issue 需微步協助盡快釐清&amp;導入對策，</t>
         </is>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
           <t>1)物料： adapter：目標6K， 已到料2.8K ,其它7/B 陸續進料 B&amp;S物料： 6/18已寄送微步 ，預計6/22到料，
-2)認證 a))TUV 認證预计7/E b)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 c) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復）
-3）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，目前TTM時間預計從7/8 延後到7/10</t>
+2)認證 a))TUV 認證预计7/E b)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 c) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG ,SG 無需認證，TH 認證已ready
+3）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，目前TTM時間預計從7/8 延後到7/10，
+4）6/18 微步通知24VL Panel ESD 測試Fail，需更換替代料，需微步安排相關測試項目，以及評估是否對Schedule 有影響，</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1578,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>24VL</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Modern A14 LE J1M</t>
+          <t>Prestige N16 Spark</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -1586,7 +1593,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>N1x 80W</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1596,222 +1603,214 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>林晉弘</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>2026/01/05</t>
+          <t>2024/11/25</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>2026/03/30</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr"/>
+          <t>2025/01/20</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>2025/06/25</t>
+        </is>
+      </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/03/12</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>2026/05/15</t>
+          <t>2026/06/30</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>2026/07/01</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026/07/10</t>
+          <t>2026/08/14</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>MVT測試中，DQA 測試Issue 需微步協助盡快釐清&amp;導入對策，</t>
+          <t>MVT測試中</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 已到料2.8K ,其它7/B 陸續進料 B&amp;S物料： 6/18已寄送微步 ，預計6/22到料，
-2)認證 a))TUV 認證预计7/E b)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 c) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG ,SG 無需認證，TH 已通知業務安排申請認證流程（待業務回復）
-3）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，目前TTM時間預計從7/8 延後到7/10</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
+          <t>1)MSFT CER/HWE主要如下P0問題，與MSFT確認以BIOS 048+ image 2.17複驗，6/18寄送3台更換2.8K panel樣品for HWV/CER P0問題驗證
+2)6/15 NV通知進版 BSP FD Rev.B，BIOS release 6/18 BIOS 049因應，MSFT release WIR 6B請preload重新製作image中for Rev.B測試 。
+3)3.8K panel 需更新FW，NV VK key 6/16已提供，三星6/17提供FW，已更新給DQA與RD for 現行樣品驗證。
+4)6/10 通知A-side需增加龍盾+小標，備料需4週，ME評估6/E前須完成打樣讓老闆確認，才能趕上7/31 ATS start。ID已提供proposal，Ronald請行銷須於6/18請老闆確認，以免影響後續ATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" hidden="1" outlineLevel="1">
+      <c r="A16" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Prestige N16 Spark</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Prestige N16 Flip Spark</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>N1x 80W</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>林晉弘</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>2024/11/25</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I16" s="9" t="inlineStr">
         <is>
           <t>2025/01/20</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>2025/06/25</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="K16" s="9" t="inlineStr">
         <is>
           <t>2026/03/12</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="L16" s="9" t="inlineStr">
         <is>
           <t>2026/06/30</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="M16" s="9" t="inlineStr">
         <is>
           <t>2026/07/31</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="N16" s="9" t="inlineStr">
         <is>
           <t>2026/08/14</t>
         </is>
       </c>
-      <c r="O16" s="6" t="inlineStr">
+      <c r="O16" s="11" t="inlineStr">
         <is>
           <t>MVT測試中</t>
         </is>
       </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>1)modern standby battery life: DQA測試新BSP FD 1.0 preview2 + MCU FW+EC+2.8K panel，結果達14.28 days，已符合微軟標準。因BSP FD office 1.0關panel ALPM，會影響耗電，DQA複驗中，預計6/11再確認一次結果。
-2)BSP FD1.0 official + OS WIR5D，廠內已更新BIOS 047+ image 2.15驗證中。本周release BSP FD rev.A預計6/11 release BIOS 048 + image 2.16後進行切換。
-3)Long run issue a)abnormal shutdown: NV提供新driver，RD驗證確定有效，待NV確認導入哪一版BSP。 b)3Dmark hang: 新版3DMark v2.32.8871 (released 06/03/
-2026)已解
-3)6/10 通知A-side需增加龍盾+小標，因備料需4週，ME評估6/E前須完成打樣讓老闆確認，才能趕上7/31 ATS start，目前正push ID提供color plan。
-4)3.8K panel 需更新FW，三星預計6/12提供LDAT report，新樣品6/10已收到，會安排RD先跑eDP CTS report for NV VK key申請，已請採購協助push三星提供FW for廠內現行樣品更新與RD驗證。
-5) PCB 1.0 6/10已出圖。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" hidden="1" outlineLevel="1">
-      <c r="A17" s="7" t="n">
+      <c r="P16" s="11" t="inlineStr">
+        <is>
+          <t>1)MSFT CER/HWE主要如下P0問題，與MSFT確認以BIOS 048+ image 2.17複驗，6/18寄送3台更換2.8K panel樣品for HWV/CER P0問題驗證
+2)6/15 NV通知進版 BSP FD Rev.B，BIOS release 6/18 BIOS 049因應，MSFT release WIR 6B請preload重新製作image中for Rev.B測試 。
+3)3.8K panel 需更新FW，NV VK key 6/16已提供，三星6/17提供FW，已更新給DQA與RD for 現行樣品驗證。
+4)6/10 通知A-side需增加龍盾+小標，備料需4週，ME評估6/E前須完成打樣讓老闆確認，才能趕上7/31 ATS start。ID已提供proposal，Ronald請行銷須於6/18請老闆確認，以免影響後續ATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>2621</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Prestige N16 Flip Spark</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>N1x 80W</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>林晉弘</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>2024/11/25</t>
-        </is>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>2025/01/20</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/25</t>
-        </is>
-      </c>
-      <c r="K17" s="9" t="inlineStr">
-        <is>
-          <t>2026/03/12</t>
-        </is>
-      </c>
-      <c r="L17" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/30</t>
-        </is>
-      </c>
-      <c r="M17" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/31</t>
-        </is>
-      </c>
-      <c r="N17" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/14</t>
-        </is>
-      </c>
-      <c r="O17" s="11" t="inlineStr">
-        <is>
-          <t>MVT測試中</t>
-        </is>
-      </c>
-      <c r="P17" s="11" t="inlineStr">
-        <is>
-          <t>1)modern standby battery life: DQA測試新BSP FD 1.0 preview2 + MCU FW+EC+2.8K panel，結果達14.28 days，已符合微軟標準。因BSP FD office 1.0關panel ALPM，會影響耗電，DQA複驗中，預計6/11再確認一次結果。
-2)BSP FD1.0 official + OS WIR5D，廠內已更新BIOS 047+ image 2.15驗證中。本周release BSP FD rev.A預計6/11 release BIOS 048 + image 2.16後進行切換。
-3)Long run issue a)abnormal shutdown: NV提供新driver，RD驗證確定有效，待NV確認導入哪一版BSP。 b)3Dmark hang: 新版3DMark v2.32.8871 (released 06/03/
-2026)已解
-3)6/10 通知A-side需增加龍盾+小標，因備料需4週，ME評估6/E前須完成打樣讓老闆確認，才能趕上7/31 ATS start，目前正push ID提供color plan。
-4)3.8K panel 需更新FW，三星預計6/12提供LDAT report，新樣品6/10已收到，會安排RD先跑eDP CTS report for NV VK key申請，已請採購協助push三星提供FW for廠內現行樣品更新與RD驗證。
-5) PCB 1.0 6/10已出圖。</t>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>15T2</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Venture 15 AI+ B3M</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>PTL-H 80W</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>李文欽</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/20</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="O17" s="6" t="inlineStr">
+        <is>
+          <t>DVT Debug &amp; 測試中</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>1) 10 gerberout@6/25,需麻煩各RD加速相關驗證</t>
         </is>
       </c>
     </row>
@@ -1821,12 +1820,12 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>15T2</t>
+          <t>15T3</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Venture 15 AI+ B3M</t>
+          <t>Katana 15 HX C14WEK</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
@@ -1836,17 +1835,17 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>PTL-H 80W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Intel® Arc™ Graphics</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>李文欽</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1856,114 +1855,114 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>2026/05/26</t>
+          <t>2026/06/01</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr"/>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>2026/07/20</t>
+          <t>2026/07/30</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>2026/08/17</t>
+          <t>2026/08/20</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>2026/08/27</t>
+          <t>2026/08/30</t>
         </is>
       </c>
       <c r="O18" s="6" t="inlineStr">
         <is>
-          <t>DVT Debug &amp; 測試中</t>
+          <t>DDR5 sku, DVT測試中</t>
         </is>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>1) 10 gerberout@6/25,需麻煩各RD加速相關驗證</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
+          <t>SA測項:USB3.2 Gen1 SSC fail,請RD儘速提供solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" hidden="1" outlineLevel="1">
+      <c r="A19" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>15T3</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Katana 15 HX C14WEK</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Katana 15 HX C14WFK</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>2026/04/20</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>2026/06/01</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr"/>
+      <c r="K19" s="9" t="inlineStr">
         <is>
           <t>2026/07/14</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L19" s="9" t="inlineStr">
         <is>
           <t>2026/07/30</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M19" s="9" t="inlineStr">
         <is>
           <t>2026/08/20</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="N19" s="9" t="inlineStr">
         <is>
           <t>2026/08/30</t>
         </is>
       </c>
-      <c r="O19" s="6" t="inlineStr">
+      <c r="O19" s="11" t="inlineStr">
         <is>
           <t>DDR5 sku, DVT測試中</t>
         </is>
       </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="P19" s="11" t="inlineStr">
+        <is>
+          <t>SA測項:USB3.2 Gen1 SSC fail,請RD儘速提供solution</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1977,7 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WFK</t>
+          <t>Katana 15 HX C14WGK</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
@@ -1993,7 +1992,7 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
@@ -2039,7 +2038,7 @@
       </c>
       <c r="P20" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>SA測項:USB3.2 Gen1 SSC fail,請RD儘速提供solution</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2053,7 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WGK</t>
+          <t>Katana 15 HX C14WGXK</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
@@ -2115,7 +2114,7 @@
       </c>
       <c r="P21" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>SA測項:USB3.2 Gen1 SSC fail,請RD儘速提供solution</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2129,7 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WGXK</t>
+          <t>Katana 15 HX C14WEOK</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
@@ -2145,7 +2144,7 @@
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -2155,38 +2154,38 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/05/15</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>2026/06/01</t>
+          <t>2026/06/15</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr"/>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>2026/07/14</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>2026/07/30</t>
+          <t>2026/08/07</t>
         </is>
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
-          <t>2026/08/20</t>
+          <t>2026/08/21</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
         <is>
-          <t>2026/08/30</t>
+          <t>2026/08/31</t>
         </is>
       </c>
       <c r="O22" s="11" t="inlineStr">
         <is>
-          <t>DDR5 sku, DVT測試中</t>
+          <t>DDR4 sku, DVT測試中</t>
         </is>
       </c>
       <c r="P22" s="11" t="inlineStr">
@@ -2206,7 +2205,7 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WEOK</t>
+          <t>Katana 15 HX C14WFOK</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
@@ -2221,7 +2220,7 @@
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
@@ -2262,7 +2261,7 @@
       </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
-          <t>DDR4 sku,預計6/15 DVT SMT</t>
+          <t>DDR4 sku, DVT測試中</t>
         </is>
       </c>
       <c r="P23" s="11" t="inlineStr">
@@ -2282,7 +2281,7 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WFOK</t>
+          <t>Katana 15 HX C14WGOK</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
@@ -2297,7 +2296,7 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
@@ -2338,7 +2337,7 @@
       </c>
       <c r="O24" s="11" t="inlineStr">
         <is>
-          <t>DDR4 sku,預計6/15 DVT SMT</t>
+          <t>DDR4 sku, DVT測試中</t>
         </is>
       </c>
       <c r="P24" s="11" t="inlineStr">
@@ -2358,7 +2357,7 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WGOK</t>
+          <t>Katana 15 HX C14WGXOK</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
@@ -2414,7 +2413,7 @@
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>DDR4 sku,預計6/15 DVT SMT</t>
+          <t>DDR4 sku, DVT測試中</t>
         </is>
       </c>
       <c r="P25" s="11" t="inlineStr">
@@ -2423,523 +2422,548 @@
         </is>
       </c>
     </row>
-    <row r="26" hidden="1" outlineLevel="1">
-      <c r="A26" s="7" t="n">
+    <row r="26">
+      <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>15T3</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Katana 15 HX C14WGXOK</t>
-        </is>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>15TK</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Cyborg A15 Max C1PWE</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>HWK 45W</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>蔡東宏</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/17</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/31</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>APU預計8月中供貨(from AMD),業務目標8月底MP,為達成量產時程目標,整體開發與驗證需pull in至8月底MP,與team member討論後,預計DVT@6/26,MVT@7/17,ATS start@8/21,MP@8/31</t>
+        </is>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>1).Schedule:R7-155優先進行ATS,以 8 月底 MP 為目標,其餘APU sku在9月進行ATS C/R
+2). Material:Thermal module將依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS,若實測驗證結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" hidden="1" outlineLevel="1">
+      <c r="A27" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>15TK</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Cyborg A15 Max C1PWF</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>HWK 45W</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>蔡東宏</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="inlineStr"/>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/17</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/31</t>
+        </is>
+      </c>
+      <c r="M27" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="N27" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="O27" s="11" t="inlineStr">
+        <is>
+          <t>APU預計8月中供貨(from AMD),業務目標8月底MP,為達成量產時程目標,整體開發與驗證需pull in至8月底MP,與team member討論後,預計DVT@6/26,MVT@7/17,ATS start@8/21,MP@8/31</t>
+        </is>
+      </c>
+      <c r="P27" s="11" t="inlineStr">
+        <is>
+          <t>1).Schedule:R7-155優先進行ATS,以 8 月底 MP 為目標,其餘APU sku在9月進行ATS C/R
+2). Material:Thermal module將依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS,若實測驗證結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" hidden="1" outlineLevel="1">
+      <c r="A28" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>15TK</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Cyborg A15 Max C1PWG</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>HWK 45W</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G28" s="9" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/15</t>
-        </is>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J26" s="9" t="inlineStr"/>
-      <c r="K26" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/24</t>
-        </is>
-      </c>
-      <c r="L26" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="M26" s="9" t="inlineStr">
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr"/>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/17</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/31</t>
+        </is>
+      </c>
+      <c r="M28" s="9" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="N26" s="9" t="inlineStr">
+      <c r="N28" s="9" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O26" s="11" t="inlineStr">
-        <is>
-          <t>DDR4 sku,預計6/15 DVT SMT</t>
-        </is>
-      </c>
-      <c r="P26" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="O28" s="11" t="inlineStr">
+        <is>
+          <t>APU預計8月中供貨(from AMD),業務目標8月底MP,為達成量產時程目標,整體開發與驗證需pull in至8月底MP,與team member討論後,預計DVT@6/26,MVT@7/17,ATS start@8/21,MP@8/31</t>
+        </is>
+      </c>
+      <c r="P28" s="11" t="inlineStr">
+        <is>
+          <t>1).Schedule:R7-155優先進行ATS,以 8 月底 MP 為目標,其餘APU sku在9月進行ATS C/R
+2). Material:Thermal module將依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS,若實測驗證結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" hidden="1" outlineLevel="1">
+      <c r="A29" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>15TK</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Cyborg A15 C1PWE</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>HWK 45W</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>蔡東宏</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr"/>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/17</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/31</t>
+        </is>
+      </c>
+      <c r="M29" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="N29" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="O29" s="11" t="inlineStr">
+        <is>
+          <t>APU預計8月中供貨(from AMD),業務目標8月底MP,為達成量產時程目標,整體開發與驗證需pull in至8月底MP,與team member討論後,預計DVT@6/26,MVT@7/17,ATS start@8/21,MP@8/31</t>
+        </is>
+      </c>
+      <c r="P29" s="11" t="inlineStr">
+        <is>
+          <t>1).Schedule:R7-155優先進行ATS,以 8 月底 MP 為目標,其餘APU sku在9月進行ATS C/R
+2). Material:Thermal module將依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS,若實測驗證結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>24V1</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Modern 14 LE J3M</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>WCL 25W</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>Intel® graphics</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>倪嬌嬌</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>2026/06/02</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>2026/06/29</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr"/>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr">
         <is>
           <t>2026/07/29</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="L30" s="4" t="inlineStr">
         <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="M30" s="4" t="inlineStr">
         <is>
           <t>2026/08/17</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="N30" s="4" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O27" s="6" t="inlineStr">
+      <c r="O30" s="6" t="inlineStr">
         <is>
           <t>Weibu plan 6/29 DVT SMT, 7/1 ASSY--熱管&amp;D件重新開模, 交期7/1</t>
         </is>
       </c>
-      <c r="P27" s="6" t="inlineStr">
+      <c r="P30" s="6" t="inlineStr">
         <is>
           <t>1)Schedule: 考量新料備料時程, 調整試產和ATS時間@8/17 start
 2)認證: 參考Weibu認證Schedule, 有四個國家無法同步於8/E TTM, 持續追蹤中 MX: 11/28 ready；AR:10/3 ready；CO: 9/5 ready；RU: 9/12 ready</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>26V1</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Modern 16 LE J3M</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>WCL 25W</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>Intel® graphics</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>倪嬌嬌</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>2026/06/02</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>2026/06/29</t>
         </is>
       </c>
-      <c r="J28" s="4" t="inlineStr"/>
-      <c r="K28" s="4" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>2026/07/29</t>
         </is>
       </c>
-      <c r="L28" s="4" t="inlineStr">
+      <c r="L31" s="4" t="inlineStr">
         <is>
           <t>2026/07/06</t>
         </is>
       </c>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>2026/08/17</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O28" s="6" t="inlineStr">
+      <c r="O31" s="6" t="inlineStr">
         <is>
           <t>Weibu plan 6/29 DVT SMT, 7/1 ASSY --熱管重新開模, 交期6/30</t>
         </is>
       </c>
-      <c r="P28" s="6" t="inlineStr">
+      <c r="P31" s="6" t="inlineStr">
         <is>
           <t>1)Schedule: 考量新料備料時程, 調整試產和ATS時間@8/17 start
 2)認證: 參考Weibu認證Schedule, 有四個國家無法同步於8/E TTM, 持續追蹤中 MX: 11/28 ready；AR:10/3 ready；CO: 9/5 ready；RU: 9/12 ready</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>15TK</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Cyborg A15 Max C1PWE</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>HWK 45W</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/03</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr"/>
-      <c r="K29" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/06</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/17</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/07</t>
-        </is>
-      </c>
-      <c r="N29" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/17</t>
-        </is>
-      </c>
-      <c r="O29" s="6" t="inlineStr">
-        <is>
-          <t>AMD預計ww25寄出R9 180/R7 165, RD會先進行重工做開機驗證</t>
-        </is>
-      </c>
-      <c r="P29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30" hidden="1" outlineLevel="1">
-      <c r="A30" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>15TK</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Cyborg A15 Max C1PWF</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>HWK 45W</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/03</t>
-        </is>
-      </c>
-      <c r="J30" s="9" t="inlineStr"/>
-      <c r="K30" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/06</t>
-        </is>
-      </c>
-      <c r="L30" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/17</t>
-        </is>
-      </c>
-      <c r="M30" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/07</t>
-        </is>
-      </c>
-      <c r="N30" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/17</t>
-        </is>
-      </c>
-      <c r="O30" s="11" t="inlineStr">
-        <is>
-          <t>AMD預計ww25寄出R9 180/R7 165, RD會先進行重工做開機驗證</t>
-        </is>
-      </c>
-      <c r="P30" s="11" t="inlineStr"/>
-    </row>
-    <row r="31" hidden="1" outlineLevel="1">
-      <c r="A31" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>15TK</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Cyborg A15 Max C1PWG</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>HWK 45W</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H31" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/03</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="inlineStr"/>
-      <c r="K31" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/06</t>
-        </is>
-      </c>
-      <c r="L31" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/17</t>
-        </is>
-      </c>
-      <c r="M31" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/07</t>
-        </is>
-      </c>
-      <c r="N31" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/17</t>
-        </is>
-      </c>
-      <c r="O31" s="11" t="inlineStr">
-        <is>
-          <t>AMD預計ww25寄出R9 180/R7 165, RD會先進行重工做開機驗證</t>
-        </is>
-      </c>
-      <c r="P31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32" hidden="1" outlineLevel="1">
-      <c r="A32" s="7" t="n">
+    <row r="32">
+      <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>15TK</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Cyborg A15 C1PWE</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>HWK 45W</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/17</t>
-        </is>
-      </c>
-      <c r="J32" s="9" t="inlineStr"/>
-      <c r="K32" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/19</t>
-        </is>
-      </c>
-      <c r="L32" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/27</t>
-        </is>
-      </c>
-      <c r="M32" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/19</t>
-        </is>
-      </c>
-      <c r="N32" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="O32" s="11" t="inlineStr">
-        <is>
-          <t>AMD預計ww27寄出R7 155/ R5 125, RD會先進行重工做開機驗證</t>
-        </is>
-      </c>
-      <c r="P32" s="11" t="inlineStr"/>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>14T3</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Prestige N14 Spark D1M</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>N1 35W</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>倪嬌嬌</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/30</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>2025/09/01</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/13</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/26</t>
+        </is>
+      </c>
+      <c r="O32" s="6" t="inlineStr">
+        <is>
+          <t>MVT SMT@7/20--depend on 0C PCB ETA</t>
+        </is>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>1) Schedule: NV update BSP時間Factory drop final ETA@10/6, 更新ATS start@10/13
+2)備料： 2.8K panel的驗證 follow leading customer, 交料plan:a. 1st MP lot: 1K 數量, 型號HQ15, 九月份交料(同步Leading customers量產交料時間 具體九月份ETD日期還在追蹤中. b. Others order: 需轉型號至HQxx, 十一月份交料</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -2947,22 +2971,22 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>14T3</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Prestige N14 Spark D1M</t>
-        </is>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>MVT</t>
+          <t>Prestige N16 Spark C1M</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>EVT</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>N1 35W</t>
+          <t>N1 45W</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -2972,7 +2996,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>倪嬌嬌</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -3012,13 +3036,13 @@
       </c>
       <c r="O33" s="6" t="inlineStr">
         <is>
-          <t>MVT SMT@7/20--depend on 0C PCB ETA</t>
+          <t>1)EVT 更新BSP6.1.2  持續驗證中, 對應NV schedule 更新 MVT延到7/20.
+2) NV 更新BSP 時間 Factory Drop Final ETA 10/6 ,需要1周時間完成 HDI+BIOS 更新ATS strat 10/13</t>
         </is>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>1) Schedule: NV update BSP時間Factory drop final ETA@10/6, 更新ATS start@10/13
-2)備料： 2.8K panel的驗證 follow leading customer, 交料plan:a. 1st MP lot: 1K 數量, 型號HQ15, 九月份交料(同步Leading customers量產交料時間 具體九月份ETD日期還在追蹤中. b. Others order: 需轉型號至HQxx, 十一月份交料</t>
+          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
         </is>
       </c>
     </row>
@@ -3028,158 +3052,157 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Prestige N16 Spark C1M</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>EVT</t>
+          <t>Katana 18 HX A14WEK</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>N1 45W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>顧曉琴</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>2025/04/30</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>2025/09/01</t>
+          <t>2026/06/15</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>2026/04/15</t>
+          <t>2026/08/24</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026/07/20</t>
+          <t>2026/10/12</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>2026/09/14</t>
+          <t>2026/11/02</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>2026/10/13</t>
+          <t>2026/11/21</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/11/30</t>
         </is>
       </c>
       <c r="O34" s="6" t="inlineStr">
         <is>
-          <t>1)EVT 更新BSP6.1.2  持續驗證中, 對應NV schedule 更新 MVT延到7/20.
-2) NV 更新BSP 時間 Factory Drop Final ETA 10/6 ,需要1周時間完成 HDI+BIOS 更新ATS strat 10/13</t>
+          <t>RPL-HX R + DDR5: DVT SMT @ 6/18 VBIOS先用2653的替用，待1861申請到後請HW重刷測試</t>
         </is>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
+          <t>1）schedule：因ID變動，可能會整體順延2W，請RD繼續努力，盡量keep目前schedule，實際影響待後續再做更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" hidden="1" outlineLevel="1">
+      <c r="A35" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Katana 18 HX A14WEK</t>
-        </is>
-      </c>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Katana 18 HX A14WFK</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="H35" s="9" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="J35" s="4" t="inlineStr">
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>2026/08/24</t>
         </is>
       </c>
-      <c r="K35" s="4" t="inlineStr">
+      <c r="K35" s="9" t="inlineStr">
         <is>
           <t>2026/10/12</t>
         </is>
       </c>
-      <c r="L35" s="4" t="inlineStr">
+      <c r="L35" s="9" t="inlineStr">
         <is>
           <t>2026/11/02</t>
         </is>
       </c>
-      <c r="M35" s="4" t="inlineStr">
+      <c r="M35" s="9" t="inlineStr">
         <is>
           <t>2026/11/21</t>
         </is>
       </c>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="N35" s="9" t="inlineStr">
         <is>
           <t>2026/11/30</t>
         </is>
       </c>
-      <c r="O35" s="6" t="inlineStr">
+      <c r="O35" s="11" t="inlineStr">
         <is>
           <t>RPL-HX R + DDR5: DVT SMT @ 6/18 VBIOS先用2653的替用，待1861申請到後請HW重刷測試</t>
         </is>
       </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="P35" s="11" t="inlineStr">
+        <is>
+          <t>1）schedule：因ID變動，可能會整體順延2W，請RD繼續努力，盡量keep目前schedule，實際影響待後續再做更新</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3217,7 @@
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WFK</t>
+          <t>Katana 18 HX A14WGK</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
@@ -3209,7 +3232,7 @@
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -3259,7 +3282,7 @@
       </c>
       <c r="P36" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1）schedule：因ID變動，可能會整體順延2W，請RD繼續努力，盡量keep目前schedule，實際影響待後續再做更新</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3297,7 @@
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGK</t>
+          <t>Katana 18 HX A14WEOK</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
@@ -3289,7 +3312,7 @@
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -3299,22 +3322,18 @@
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="inlineStr"/>
       <c r="K37" s="9" t="inlineStr">
         <is>
-          <t>2026/10/12</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
@@ -3324,17 +3343,17 @@
       </c>
       <c r="M37" s="9" t="inlineStr">
         <is>
-          <t>2026/11/21</t>
+          <t>2026/11/23</t>
         </is>
       </c>
       <c r="N37" s="9" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2026/12/02</t>
         </is>
       </c>
       <c r="O37" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT SMT @ 6/18 VBIOS先用2653的替用，待1861申請到後請HW重刷測試</t>
+          <t>RPL-HX R + DDR4: 預計DVT SMT @ 6/29</t>
         </is>
       </c>
       <c r="P37" s="11" t="inlineStr">
@@ -3354,7 +3373,7 @@
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WEOK</t>
+          <t>Katana 18 HX A14WFOK</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
@@ -3369,7 +3388,7 @@
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -3430,7 +3449,7 @@
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WFOK</t>
+          <t>Katana 18 HX A14WGOK</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
@@ -3445,7 +3464,7 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
@@ -3506,7 +3525,7 @@
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGOK</t>
+          <t>Crosshair 18 Max HX B14WE</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
@@ -3521,7 +3540,7 @@
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
@@ -3531,15 +3550,19 @@
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J40" s="9" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3552,22 +3575,22 @@
       </c>
       <c r="M40" s="9" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2026/11/28</t>
         </is>
       </c>
       <c r="N40" s="9" t="inlineStr">
         <is>
-          <t>2026/12/02</t>
+          <t>2026/12/07</t>
         </is>
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: 預計DVT SMT @ 6/29</t>
+          <t>RPL-HX R + DDR5: DVT SMT @ 6/18 VBIOS先用2653的替用，待1861申請到後請HW重刷測試</t>
         </is>
       </c>
       <c r="P40" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1）schedule：因ID變動，可能會整體順延2W，請RD繼續努力，盡量keep目前schedule，實際影響待後續再做更新</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3605,7 @@
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WE</t>
+          <t>Crosshair 18 Max HX B14WF</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
@@ -3597,7 +3620,7 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -3647,7 +3670,7 @@
       </c>
       <c r="P41" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1）schedule：因ID變動，可能會整體順延2W，請RD繼續努力，盡量keep目前schedule，實際影響待後續再做更新</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3685,7 @@
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WEO</t>
+          <t>Crosshair 18 Max HX B14WG</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
@@ -3677,7 +3700,7 @@
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -3687,15 +3710,19 @@
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J42" s="9" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
       <c r="K42" s="9" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3718,12 +3745,12 @@
       </c>
       <c r="O42" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: 預計DVT SMT @ 6/29</t>
+          <t>RPL-HX R + DDR5: DVT SMT @ 6/18 VBIOS先用2653的替用，待1861申請到後請HW重刷測試</t>
         </is>
       </c>
       <c r="P42" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1）schedule：因ID變動，可能會整體順延2W，請RD繼續努力，盡量keep目前schedule，實際影響待後續再做更新</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3765,7 @@
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WF</t>
+          <t>Crosshair 18 Max HX B14WGX</t>
         </is>
       </c>
       <c r="D43" s="15" t="inlineStr">
@@ -3753,7 +3780,7 @@
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -3803,7 +3830,7 @@
       </c>
       <c r="P43" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1）schedule：因ID變動，可能會整體順延2W，請RD繼續努力，盡量keep目前schedule，實際影響待後續再做更新</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3845,7 @@
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WFO</t>
+          <t>Crosshair 18 Max HX B14WEO</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
@@ -3833,7 +3860,7 @@
       </c>
       <c r="F44" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
@@ -3894,7 +3921,7 @@
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WG</t>
+          <t>Crosshair 18 Max HX B14WFO</t>
         </is>
       </c>
       <c r="D45" s="15" t="inlineStr">
@@ -3909,7 +3936,7 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
@@ -3919,19 +3946,15 @@
       </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J45" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="inlineStr"/>
       <c r="K45" s="9" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3954,7 +3977,7 @@
       </c>
       <c r="O45" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT SMT @ 6/18 VBIOS先用2653的替用，待1861申請到後請HW重刷測試</t>
+          <t>RPL-HX R + DDR4: 預計DVT SMT @ 6/29</t>
         </is>
       </c>
       <c r="P45" s="11" t="inlineStr">
@@ -4050,7 +4073,7 @@
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WGX</t>
+          <t>Crosshair 18 Max HX B14WGXO</t>
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
@@ -4075,19 +4098,15 @@
       </c>
       <c r="H47" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J47" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="inlineStr"/>
       <c r="K47" s="9" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -4110,7 +4129,7 @@
       </c>
       <c r="O47" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT SMT @ 6/18 VBIOS先用2653的替用，待1861申請到後請HW重刷測試</t>
+          <t>RPL-HX R + DDR4: 預計DVT SMT @ 6/29</t>
         </is>
       </c>
       <c r="P47" s="11" t="inlineStr">
@@ -4130,22 +4149,22 @@
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WGXO</t>
-        </is>
-      </c>
-      <c r="D48" s="15" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Crosshair 18 Max HX B2WE</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>RPL-HX Next 55W</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
@@ -4155,38 +4174,34 @@
       </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="inlineStr"/>
       <c r="J48" s="9" t="inlineStr"/>
       <c r="K48" s="9" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/12/08</t>
         </is>
       </c>
       <c r="L48" s="9" t="inlineStr">
         <is>
-          <t>2026/11/02</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="M48" s="9" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2027/01/19</t>
         </is>
       </c>
       <c r="N48" s="9" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="O48" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: 預計DVT SMT @ 6/29</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P48" s="11" t="inlineStr">
@@ -4206,10 +4221,10 @@
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WE</t>
-        </is>
-      </c>
-      <c r="D49" s="17" t="inlineStr">
+          <t>Crosshair 18 Max HX B2WEO</t>
+        </is>
+      </c>
+      <c r="D49" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4231,7 +4246,7 @@
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I49" s="9" t="inlineStr"/>
@@ -4258,7 +4273,7 @@
       </c>
       <c r="O49" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P49" s="11" t="inlineStr">
@@ -4278,10 +4293,10 @@
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WEO</t>
-        </is>
-      </c>
-      <c r="D50" s="17" t="inlineStr">
+          <t>Crosshair 18 Max HX B2WF</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4293,7 +4308,7 @@
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
@@ -4303,7 +4318,7 @@
       </c>
       <c r="H50" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I50" s="9" t="inlineStr"/>
@@ -4330,7 +4345,7 @@
       </c>
       <c r="O50" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P50" s="11" t="inlineStr">
@@ -4350,10 +4365,10 @@
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WF</t>
-        </is>
-      </c>
-      <c r="D51" s="17" t="inlineStr">
+          <t>Crosshair 18 Max HX B2WFO</t>
+        </is>
+      </c>
+      <c r="D51" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4375,7 +4390,7 @@
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I51" s="9" t="inlineStr"/>
@@ -4402,7 +4417,7 @@
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
@@ -4422,10 +4437,10 @@
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WFO</t>
-        </is>
-      </c>
-      <c r="D52" s="17" t="inlineStr">
+          <t>Crosshair 18 Max HX B2WG</t>
+        </is>
+      </c>
+      <c r="D52" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4437,7 +4452,7 @@
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -4447,7 +4462,7 @@
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I52" s="9" t="inlineStr"/>
@@ -4474,7 +4489,7 @@
       </c>
       <c r="O52" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P52" s="11" t="inlineStr">
@@ -4494,10 +4509,10 @@
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WG</t>
-        </is>
-      </c>
-      <c r="D53" s="17" t="inlineStr">
+          <t>Crosshair 18 Max HX B2WGO</t>
+        </is>
+      </c>
+      <c r="D53" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4519,7 +4534,7 @@
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I53" s="9" t="inlineStr"/>
@@ -4546,7 +4561,7 @@
       </c>
       <c r="O53" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P53" s="11" t="inlineStr">
@@ -4566,10 +4581,10 @@
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WGO</t>
-        </is>
-      </c>
-      <c r="D54" s="17" t="inlineStr">
+          <t>Crosshair 18 Max HX B2WGX</t>
+        </is>
+      </c>
+      <c r="D54" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4591,7 +4606,7 @@
       </c>
       <c r="H54" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I54" s="9" t="inlineStr"/>
@@ -4618,7 +4633,7 @@
       </c>
       <c r="O54" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P54" s="11" t="inlineStr">
@@ -4638,10 +4653,10 @@
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WGX</t>
-        </is>
-      </c>
-      <c r="D55" s="17" t="inlineStr">
+          <t>Crosshair 18 Max HX B2WGXO</t>
+        </is>
+      </c>
+      <c r="D55" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4663,7 +4678,7 @@
       </c>
       <c r="H55" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I55" s="9" t="inlineStr"/>
@@ -4690,7 +4705,7 @@
       </c>
       <c r="O55" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P55" s="11" t="inlineStr">
@@ -4710,10 +4725,10 @@
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WGXO</t>
-        </is>
-      </c>
-      <c r="D56" s="17" t="inlineStr">
+          <t>Katana 18 HX A2WEK</t>
+        </is>
+      </c>
+      <c r="D56" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4725,7 +4740,7 @@
       </c>
       <c r="F56" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr">
@@ -4735,7 +4750,7 @@
       </c>
       <c r="H56" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I56" s="9" t="inlineStr"/>
@@ -4762,7 +4777,7 @@
       </c>
       <c r="O56" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P56" s="11" t="inlineStr">
@@ -4782,10 +4797,10 @@
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WEK</t>
-        </is>
-      </c>
-      <c r="D57" s="17" t="inlineStr">
+          <t>Katana 18 HX A2WEOK</t>
+        </is>
+      </c>
+      <c r="D57" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4807,10 +4822,14 @@
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I57" s="9" t="inlineStr"/>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
       <c r="J57" s="9" t="inlineStr"/>
       <c r="K57" s="9" t="inlineStr">
         <is>
@@ -4834,7 +4853,7 @@
       </c>
       <c r="O57" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P57" s="11" t="inlineStr">
@@ -4854,10 +4873,10 @@
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WEOK</t>
-        </is>
-      </c>
-      <c r="D58" s="17" t="inlineStr">
+          <t>Katana 18 HX A2WFK</t>
+        </is>
+      </c>
+      <c r="D58" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4869,7 +4888,7 @@
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr">
@@ -4879,14 +4898,10 @@
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I58" s="9" t="inlineStr"/>
       <c r="J58" s="9" t="inlineStr"/>
       <c r="K58" s="9" t="inlineStr">
         <is>
@@ -4910,7 +4925,7 @@
       </c>
       <c r="O58" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P58" s="11" t="inlineStr">
@@ -4930,10 +4945,10 @@
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WFK</t>
-        </is>
-      </c>
-      <c r="D59" s="17" t="inlineStr">
+          <t>Katana 18 HX A2WFOK</t>
+        </is>
+      </c>
+      <c r="D59" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4955,10 +4970,14 @@
       </c>
       <c r="H59" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I59" s="9" t="inlineStr"/>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
       <c r="J59" s="9" t="inlineStr"/>
       <c r="K59" s="9" t="inlineStr">
         <is>
@@ -4982,7 +5001,7 @@
       </c>
       <c r="O59" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P59" s="11" t="inlineStr">
@@ -5002,10 +5021,10 @@
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WFOK</t>
-        </is>
-      </c>
-      <c r="D60" s="17" t="inlineStr">
+          <t>Katana 18 HX A2WGK</t>
+        </is>
+      </c>
+      <c r="D60" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5017,7 +5036,7 @@
       </c>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr">
@@ -5027,14 +5046,10 @@
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I60" s="9" t="inlineStr"/>
       <c r="J60" s="9" t="inlineStr"/>
       <c r="K60" s="9" t="inlineStr">
         <is>
@@ -5058,7 +5073,7 @@
       </c>
       <c r="O60" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P60" s="11" t="inlineStr">
@@ -5078,10 +5093,10 @@
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WGK</t>
-        </is>
-      </c>
-      <c r="D61" s="17" t="inlineStr">
+          <t>Katana 18 HX A2WGOK</t>
+        </is>
+      </c>
+      <c r="D61" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5103,10 +5118,14 @@
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I61" s="9" t="inlineStr"/>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
       <c r="J61" s="9" t="inlineStr"/>
       <c r="K61" s="9" t="inlineStr">
         <is>
@@ -5130,7 +5149,7 @@
       </c>
       <c r="O61" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P61" s="11" t="inlineStr">
@@ -5139,471 +5158,475 @@
         </is>
       </c>
     </row>
-    <row r="62" hidden="1" outlineLevel="1">
-      <c r="A62" s="7" t="n">
+    <row r="62">
+      <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="C62" s="9" t="inlineStr">
-        <is>
-          <t>Katana 18 HX A2WGOK</t>
-        </is>
-      </c>
-      <c r="D62" s="17" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>14T4</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Prestige 14 AI</t>
+        </is>
+      </c>
+      <c r="D62" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E62" s="9" t="inlineStr">
-        <is>
-          <t>RPL-HX Next 55W</t>
-        </is>
-      </c>
-      <c r="F62" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G62" s="9" t="inlineStr">
-        <is>
-          <t>顧曉琴</t>
-        </is>
-      </c>
-      <c r="H62" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J62" s="9" t="inlineStr"/>
-      <c r="K62" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/08</t>
-        </is>
-      </c>
-      <c r="L62" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/30</t>
-        </is>
-      </c>
-      <c r="M62" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/19</t>
-        </is>
-      </c>
-      <c r="N62" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/30</t>
-        </is>
-      </c>
-      <c r="O62" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
-        </is>
-      </c>
-      <c r="P62" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>NVL-H 30W</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>朱芳芳</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/04</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/20</t>
+        </is>
+      </c>
+      <c r="M62" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/15</t>
+        </is>
+      </c>
+      <c r="N62" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/25</t>
+        </is>
+      </c>
+      <c r="O62" s="6" t="inlineStr">
+        <is>
+          <t>0A gerberout ：6/26,DVT SMT@7/22</t>
+        </is>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" hidden="1" outlineLevel="1">
+      <c r="A63" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>14T4</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>Prestige 14 AI</t>
-        </is>
-      </c>
-      <c r="D63" s="16" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>Prestige 14 AI+ Flip</t>
+        </is>
+      </c>
+      <c r="D63" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="E63" s="9" t="inlineStr">
         <is>
           <t>NVL-H 30W</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="F63" s="9" t="inlineStr">
         <is>
           <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="G63" s="9" t="inlineStr">
         <is>
           <t>朱芳芳</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr">
+      <c r="H63" s="9" t="inlineStr">
         <is>
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="I63" s="4" t="inlineStr">
+      <c r="I63" s="9" t="inlineStr">
         <is>
           <t>2026/07/22</t>
         </is>
       </c>
-      <c r="J63" s="4" t="inlineStr">
+      <c r="J63" s="9" t="inlineStr">
         <is>
           <t>2026/09/15</t>
         </is>
       </c>
-      <c r="K63" s="4" t="inlineStr">
+      <c r="K63" s="9" t="inlineStr">
         <is>
           <t>2026/11/04</t>
         </is>
       </c>
-      <c r="L63" s="4" t="inlineStr">
+      <c r="L63" s="9" t="inlineStr">
         <is>
           <t>2026/11/20</t>
         </is>
       </c>
-      <c r="M63" s="4" t="inlineStr">
+      <c r="M63" s="9" t="inlineStr">
         <is>
           <t>2026/12/15</t>
         </is>
       </c>
-      <c r="N63" s="4" t="inlineStr">
+      <c r="N63" s="9" t="inlineStr">
         <is>
           <t>2026/12/25</t>
         </is>
       </c>
-      <c r="O63" s="6" t="inlineStr">
+      <c r="O63" s="11" t="inlineStr">
         <is>
           <t>0A gerberout ：6/26,DVT SMT@7/22</t>
         </is>
       </c>
-      <c r="P63" s="6" t="inlineStr">
+      <c r="P63" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
-    <row r="64" hidden="1" outlineLevel="1">
-      <c r="A64" s="7" t="n">
+    <row r="64">
+      <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>14T4</t>
-        </is>
-      </c>
-      <c r="C64" s="9" t="inlineStr">
-        <is>
-          <t>Prestige 14 AI+ Flip</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>2624</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Prestige 16 AI+</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E64" s="9" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>NVL-H 30W</t>
         </is>
       </c>
-      <c r="F64" s="9" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
-      <c r="G64" s="9" t="inlineStr">
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t>朱芳芳</t>
         </is>
       </c>
-      <c r="H64" s="9" t="inlineStr">
+      <c r="H64" s="4" t="inlineStr">
         <is>
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="I64" s="9" t="inlineStr">
+      <c r="I64" s="4" t="inlineStr"/>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/04</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/20</t>
+        </is>
+      </c>
+      <c r="M64" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/15</t>
+        </is>
+      </c>
+      <c r="N64" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/25</t>
+        </is>
+      </c>
+      <c r="O64" s="6" t="inlineStr">
+        <is>
+          <t>0A gerberout ：6/26,DVT SMT@7/22</t>
+        </is>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" hidden="1" outlineLevel="1">
+      <c r="A65" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>2624</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>Prestige 16 Flip AI+</t>
+        </is>
+      </c>
+      <c r="D65" s="18" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>NVL-H 30W</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>朱芳芳</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="I65" s="9" t="inlineStr"/>
+      <c r="J65" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="K65" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/04</t>
+        </is>
+      </c>
+      <c r="L65" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/20</t>
+        </is>
+      </c>
+      <c r="M65" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/15</t>
+        </is>
+      </c>
+      <c r="N65" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/25</t>
+        </is>
+      </c>
+      <c r="O65" s="11" t="inlineStr">
+        <is>
+          <t>0A gerberout ：6/26,DVT SMT@7/22</t>
+        </is>
+      </c>
+      <c r="P65" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>2633</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WI</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5080</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
         <is>
           <t>2026/07/22</t>
         </is>
       </c>
-      <c r="J64" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/15</t>
-        </is>
-      </c>
-      <c r="K64" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/04</t>
-        </is>
-      </c>
-      <c r="L64" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/20</t>
-        </is>
-      </c>
-      <c r="M64" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/15</t>
-        </is>
-      </c>
-      <c r="N64" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/25</t>
-        </is>
-      </c>
-      <c r="O64" s="11" t="inlineStr">
-        <is>
-          <t>0A gerberout ：6/26,DVT SMT@7/22</t>
-        </is>
-      </c>
-      <c r="P64" s="11" t="inlineStr">
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="M66" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N66" s="4" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="O66" s="6" t="inlineStr">
+        <is>
+          <t>0M layout中，预计6/30 gerber out</t>
+        </is>
+      </c>
+      <c r="P66" s="6" t="inlineStr">
+        <is>
+          <t>1) Schedule:NV VBIOS @1/6, gating 8天,預計12/E 拿到WHQL，可能影響到最終TTM 時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" hidden="1" outlineLevel="1">
+      <c r="A67" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>2633</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WH</t>
+        </is>
+      </c>
+      <c r="D67" s="18" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K67" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L67" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="M67" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N67" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="O67" s="11" t="inlineStr">
+        <is>
+          <t>0M layout中，预计6/30 gerber out</t>
+        </is>
+      </c>
+      <c r="P67" s="11" t="inlineStr">
         <is>
           <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>2624</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>Prestige 16 AI+</t>
-        </is>
-      </c>
-      <c r="D65" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>NVL-H 30W</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>Intel® Arc™ Graphics</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>朱芳芳</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/14</t>
-        </is>
-      </c>
-      <c r="I65" s="4" t="inlineStr"/>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/15</t>
-        </is>
-      </c>
-      <c r="K65" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/04</t>
-        </is>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/20</t>
-        </is>
-      </c>
-      <c r="M65" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/15</t>
-        </is>
-      </c>
-      <c r="N65" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/25</t>
-        </is>
-      </c>
-      <c r="O65" s="6" t="inlineStr">
-        <is>
-          <t>0A gerberout ：6/26,DVT SMT@7/22</t>
-        </is>
-      </c>
-      <c r="P65" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" hidden="1" outlineLevel="1">
-      <c r="A66" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>2624</t>
-        </is>
-      </c>
-      <c r="C66" s="9" t="inlineStr">
-        <is>
-          <t>Prestige 16 Flip AI+</t>
-        </is>
-      </c>
-      <c r="D66" s="17" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E66" s="9" t="inlineStr">
-        <is>
-          <t>NVL-H 30W</t>
-        </is>
-      </c>
-      <c r="F66" s="9" t="inlineStr">
-        <is>
-          <t>Intel® Arc™ Graphics</t>
-        </is>
-      </c>
-      <c r="G66" s="9" t="inlineStr">
-        <is>
-          <t>朱芳芳</t>
-        </is>
-      </c>
-      <c r="H66" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/14</t>
-        </is>
-      </c>
-      <c r="I66" s="9" t="inlineStr"/>
-      <c r="J66" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/15</t>
-        </is>
-      </c>
-      <c r="K66" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/04</t>
-        </is>
-      </c>
-      <c r="L66" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/20</t>
-        </is>
-      </c>
-      <c r="M66" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/15</t>
-        </is>
-      </c>
-      <c r="N66" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/25</t>
-        </is>
-      </c>
-      <c r="O66" s="11" t="inlineStr">
-        <is>
-          <t>0A gerberout ：6/26,DVT SMT@7/22</t>
-        </is>
-      </c>
-      <c r="P66" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WI</t>
-        </is>
-      </c>
-      <c r="D67" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5080</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I67" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/22</t>
-        </is>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K67" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/30</t>
-        </is>
-      </c>
-      <c r="M67" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N67" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="O67" s="6" t="inlineStr">
-        <is>
-          <t>0M layout中，预计6/30 gerber out</t>
-        </is>
-      </c>
-      <c r="P67" s="6" t="inlineStr">
-        <is>
-          <t>1) Schedule:NV VBIOS @1/6, gating 8天,預計12/E 拿到WHQL，可能影響到最終TTM 時間</t>
         </is>
       </c>
     </row>
@@ -5618,10 +5641,10 @@
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WH</t>
-        </is>
-      </c>
-      <c r="D68" s="17" t="inlineStr">
+          <t>Stealth 16 AI+ B4WJ</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5633,7 +5656,7 @@
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="G68" s="9" t="inlineStr">
@@ -5687,161 +5710,162 @@
         </is>
       </c>
     </row>
-    <row r="69" hidden="1" outlineLevel="1">
-      <c r="A69" s="7" t="n">
+    <row r="69">
+      <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="C69" s="9" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WJ</t>
-        </is>
-      </c>
-      <c r="D69" s="17" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WE</t>
+        </is>
+      </c>
+      <c r="D69" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E69" s="9" t="inlineStr">
+      <c r="E69" s="4" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F69" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5090</t>
-        </is>
-      </c>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H69" s="9" t="inlineStr">
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>賴雪鳳</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I69" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/22</t>
-        </is>
-      </c>
-      <c r="J69" s="9" t="inlineStr">
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K69" s="9" t="inlineStr">
+      <c r="K69" s="4" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L69" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/30</t>
-        </is>
-      </c>
-      <c r="M69" s="9" t="inlineStr">
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/27</t>
+        </is>
+      </c>
+      <c r="M69" s="4" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N69" s="9" t="inlineStr">
+      <c r="N69" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O69" s="11" t="inlineStr">
-        <is>
-          <t>0M layout中，预计6/30 gerber out</t>
-        </is>
-      </c>
-      <c r="P69" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="O69" s="6" t="inlineStr">
+        <is>
+          <t>5/22 kick off ,0A layout start 6/8-7/17</t>
+        </is>
+      </c>
+      <c r="P69" s="6" t="inlineStr">
+        <is>
+          <t>1)NV VBIOS 驗證時間6周
+2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" hidden="1" outlineLevel="1">
+      <c r="A70" s="7" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>2634</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WE</t>
-        </is>
-      </c>
-      <c r="D70" s="16" t="inlineStr">
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WF</t>
+        </is>
+      </c>
+      <c r="D70" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="E70" s="9" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G70" s="4" t="inlineStr">
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
         <is>
           <t>賴雪鳳</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
+      <c r="H70" s="9" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I70" s="4" t="inlineStr">
+      <c r="I70" s="9" t="inlineStr">
         <is>
           <t>2026/08/07</t>
         </is>
       </c>
-      <c r="J70" s="4" t="inlineStr">
+      <c r="J70" s="9" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K70" s="4" t="inlineStr">
+      <c r="K70" s="9" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L70" s="4" t="inlineStr">
+      <c r="L70" s="9" t="inlineStr">
         <is>
           <t>2026/11/27</t>
         </is>
       </c>
-      <c r="M70" s="4" t="inlineStr">
+      <c r="M70" s="9" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N70" s="4" t="inlineStr">
+      <c r="N70" s="9" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O70" s="6" t="inlineStr">
+      <c r="O70" s="11" t="inlineStr">
         <is>
           <t>5/22 kick off ,0A layout start 6/8-7/17</t>
         </is>
       </c>
-      <c r="P70" s="6" t="inlineStr">
+      <c r="P70" s="11" t="inlineStr">
         <is>
           <t>1)NV VBIOS 驗證時間6周
 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
@@ -5859,10 +5883,10 @@
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WF</t>
-        </is>
-      </c>
-      <c r="D71" s="17" t="inlineStr">
+          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
+        </is>
+      </c>
+      <c r="D71" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5874,7 +5898,7 @@
       </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G71" s="9" t="inlineStr">
@@ -5940,10 +5964,10 @@
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
-        </is>
-      </c>
-      <c r="D72" s="17" t="inlineStr">
+          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
+        </is>
+      </c>
+      <c r="D72" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6010,162 +6034,161 @@
         </is>
       </c>
     </row>
-    <row r="73" hidden="1" outlineLevel="1">
-      <c r="A73" s="7" t="n">
+    <row r="73">
+      <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="C73" s="9" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
-        </is>
-      </c>
-      <c r="D73" s="17" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>2654</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Raider 16 Max HX B4WH</t>
+        </is>
+      </c>
+      <c r="D73" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F73" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>賴雪鳳</t>
-        </is>
-      </c>
-      <c r="H73" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="J73" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K73" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L73" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/27</t>
-        </is>
-      </c>
-      <c r="M73" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N73" s="9" t="inlineStr">
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>吳美芳</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O73" s="11" t="inlineStr">
-        <is>
-          <t>5/22 kick off ,0A layout start 6/8-7/17</t>
-        </is>
-      </c>
-      <c r="P73" s="11" t="inlineStr">
-        <is>
-          <t>1)NV VBIOS 驗證時間6周
-2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M73" s="4" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O73" s="6" t="inlineStr">
+        <is>
+          <t>0M layout中，预计6/29 gerber out</t>
+        </is>
+      </c>
+      <c r="P73" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" hidden="1" outlineLevel="1">
+      <c r="A74" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>2654</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>Raider 16 Max HX B4WH</t>
-        </is>
-      </c>
-      <c r="D74" s="16" t="inlineStr">
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>Raider 16 Max HX B4WI</t>
+        </is>
+      </c>
+      <c r="D74" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="E74" s="9" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5070Ti</t>
-        </is>
-      </c>
-      <c r="G74" s="4" t="inlineStr">
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5080</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
         <is>
           <t>吳美芳</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
+      <c r="H74" s="9" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I74" s="4" t="inlineStr">
+      <c r="I74" s="9" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J74" s="4" t="inlineStr">
+      <c r="J74" s="9" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K74" s="4" t="inlineStr">
+      <c r="K74" s="9" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L74" s="4" t="inlineStr">
+      <c r="L74" s="9" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M74" s="4" t="inlineStr">
+      <c r="M74" s="9" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N74" s="4" t="inlineStr">
+      <c r="N74" s="9" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O74" s="6" t="inlineStr">
-        <is>
-          <t>0M layout中，预计6/29 gerber out</t>
-        </is>
-      </c>
-      <c r="P74" s="6" t="inlineStr">
+      <c r="O74" s="11" t="inlineStr">
+        <is>
+          <t>0M layout中,预计6/29 gerber out</t>
+        </is>
+      </c>
+      <c r="P74" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -6182,10 +6205,10 @@
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B4WI</t>
-        </is>
-      </c>
-      <c r="D75" s="17" t="inlineStr">
+          <t>Raider 16 Max HX B4WJ</t>
+        </is>
+      </c>
+      <c r="D75" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6197,7 +6220,7 @@
       </c>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="G75" s="9" t="inlineStr">
@@ -6262,10 +6285,10 @@
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B4WJ</t>
-        </is>
-      </c>
-      <c r="D76" s="17" t="inlineStr">
+          <t>Raider 16  HX B4WH</t>
+        </is>
+      </c>
+      <c r="D76" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6277,7 +6300,7 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="G76" s="9" t="inlineStr">
@@ -6322,7 +6345,7 @@
       </c>
       <c r="O76" s="11" t="inlineStr">
         <is>
-          <t>0M layout中,预计6/29 gerber out</t>
+          <t>0M layout中，预计6/29 gerber out</t>
         </is>
       </c>
       <c r="P76" s="11" t="inlineStr">
@@ -6342,10 +6365,10 @@
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WH</t>
-        </is>
-      </c>
-      <c r="D77" s="17" t="inlineStr">
+          <t>Raider 16  HX B4WI</t>
+        </is>
+      </c>
+      <c r="D77" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6357,7 +6380,7 @@
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="G77" s="9" t="inlineStr">
@@ -6411,163 +6434,163 @@
         </is>
       </c>
     </row>
-    <row r="78" hidden="1" outlineLevel="1">
-      <c r="A78" s="7" t="n">
+    <row r="78">
+      <c r="A78" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>2654</t>
-        </is>
-      </c>
-      <c r="C78" s="9" t="inlineStr">
-        <is>
-          <t>Raider 16  HX B4WI</t>
-        </is>
-      </c>
-      <c r="D78" s="17" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>2655</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Crosshair 16 Max HX E4WEK</t>
+        </is>
+      </c>
+      <c r="D78" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E78" s="9" t="inlineStr">
+      <c r="E78" s="4" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F78" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5080</t>
-        </is>
-      </c>
-      <c r="G78" s="9" t="inlineStr">
-        <is>
-          <t>吳美芳</t>
-        </is>
-      </c>
-      <c r="H78" s="9" t="inlineStr">
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>鮑佩佩</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I78" s="9" t="inlineStr">
+      <c r="I78" s="4" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J78" s="9" t="inlineStr">
+      <c r="J78" s="4" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K78" s="9" t="inlineStr">
+      <c r="K78" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L78" s="9" t="inlineStr">
+      <c r="L78" s="4" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M78" s="9" t="inlineStr">
+      <c r="M78" s="4" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N78" s="9" t="inlineStr">
+      <c r="N78" s="4" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O78" s="11" t="inlineStr">
-        <is>
-          <t>0M layout中，预计6/29 gerber out</t>
-        </is>
-      </c>
-      <c r="P78" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="O78" s="6" t="inlineStr">
+        <is>
+          <t>0A layout中，plan 6/29 gerber out</t>
+        </is>
+      </c>
+      <c r="P78" s="6" t="inlineStr">
+        <is>
+          <t>Spec change: I/O  TypeC 由1*TBT4+ 1*alt mode改為2*TBT4,對0A gerber out 影響TBD,對TTM 無影響</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" hidden="1" outlineLevel="1">
+      <c r="A79" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>2655</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WEK</t>
-        </is>
-      </c>
-      <c r="D79" s="16" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>Crosshair 16 Max HX E4WFK</t>
+        </is>
+      </c>
+      <c r="D79" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="E79" s="9" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
         <is>
           <t>鮑佩佩</t>
         </is>
       </c>
-      <c r="H79" s="4" t="inlineStr">
+      <c r="H79" s="9" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I79" s="4" t="inlineStr">
+      <c r="I79" s="9" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J79" s="4" t="inlineStr">
+      <c r="J79" s="9" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K79" s="4" t="inlineStr">
+      <c r="K79" s="9" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L79" s="4" t="inlineStr">
+      <c r="L79" s="9" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M79" s="4" t="inlineStr">
+      <c r="M79" s="9" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N79" s="4" t="inlineStr">
+      <c r="N79" s="9" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O79" s="6" t="inlineStr">
-        <is>
-          <t>GN22-X2 SKU, 0A layout中，预计6/29 gerber out</t>
-        </is>
-      </c>
-      <c r="P79" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="O79" s="11" t="inlineStr">
+        <is>
+          <t>0A layout中，plan 6/29 gerber out</t>
+        </is>
+      </c>
+      <c r="P79" s="11" t="inlineStr">
+        <is>
+          <t>Spec change: I/O  TypeC 由1*TBT4+ 1*alt mode改為2*TBT4,對0A gerber out 影響TBD,對TTM 無影響</t>
         </is>
       </c>
     </row>
@@ -6582,10 +6605,10 @@
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 16 Max HX E4WFK</t>
-        </is>
-      </c>
-      <c r="D80" s="17" t="inlineStr">
+          <t>Crosshair 16 Max HX E4WGK</t>
+        </is>
+      </c>
+      <c r="D80" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6597,7 +6620,7 @@
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G80" s="9" t="inlineStr">
@@ -6642,12 +6665,12 @@
       </c>
       <c r="O80" s="11" t="inlineStr">
         <is>
-          <t>GN22-X4 SKU,0A layout中，预计6/29 gerber out</t>
+          <t>GN22-X6 8GB SKU,0A layout中，plan 6/29 gerber out</t>
         </is>
       </c>
       <c r="P80" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Spec change: I/O  TypeC 由1*TBT4+ 1*alt mode改為2*TBT4,對0A gerber out 影響TBD,對TTM 無影響</t>
         </is>
       </c>
     </row>
@@ -6662,10 +6685,10 @@
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 16 Max HX E4WGK</t>
-        </is>
-      </c>
-      <c r="D81" s="17" t="inlineStr">
+          <t>Crosshair 16 Max HX E4WGXK</t>
+        </is>
+      </c>
+      <c r="D81" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6722,97 +6745,17 @@
       </c>
       <c r="O81" s="11" t="inlineStr">
         <is>
-          <t>GN22-X6 8GB SKU,0A layout中，预计6/29 gerber out</t>
+          <t>GN22-X6 12GB SKU, 0A layout中，plan 6/29 gerber out</t>
         </is>
       </c>
       <c r="P81" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" hidden="1" outlineLevel="1">
-      <c r="A82" s="7" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>2655</t>
-        </is>
-      </c>
-      <c r="C82" s="9" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WGXK</t>
-        </is>
-      </c>
-      <c r="D82" s="17" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E82" s="9" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G82" s="9" t="inlineStr">
-        <is>
-          <t>鮑佩佩</t>
-        </is>
-      </c>
-      <c r="H82" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I82" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K82" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L82" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M82" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N82" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O82" s="11" t="inlineStr">
-        <is>
-          <t>GN22-X6 12GB SKU, 0A layout中，预计6/29 gerber out</t>
-        </is>
-      </c>
-      <c r="P82" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Spec change: I/O  TypeC 由1*TBT4+ 1*alt mode改為2*TBT4,對0A gerber out 影響TBD,對TTM 無影響</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P82"/>
+  <autoFilter ref="A1:P81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/npi_dashboard.xlsx
+++ b/npi_dashboard.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPI Dashboard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -52,12 +52,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="007030A0"/>
+      <color rgb="0000B0F0"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000B0F0"/>
+      <color rgb="007030A0"/>
       <sz val="10"/>
     </font>
     <font>
@@ -142,16 +142,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -519,7 +519,7 @@
     <outlinePr summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P81"/>
+  <dimension ref="A1:P82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -685,7 +685,7 @@
       </c>
       <c r="O2" s="6" t="inlineStr">
         <is>
-          <t>第一波只上線RPL-U  Refresh SKU，RPL-U SKU訂單 待6月排程上線</t>
+          <t>因PCB 最快交期落在6/29,加上微步盤點，預計最快7/10 TTM</t>
         </is>
       </c>
       <c r="P2" s="6" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="O3" s="11" t="inlineStr">
         <is>
-          <t>第一波只上線RPL-U  Refresh SKU，RPL-U SKU訂單 待6月排程上線</t>
+          <t>因PCB 最快交期落在6/29,加上微步盤點，預計最快7/10 TTM</t>
         </is>
       </c>
       <c r="P3" s="11" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>14T2</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Crosshair 16 HX MLG Edition E14WFK</t>
+          <t>Prestige 14 Flip AI+ Rhône</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -787,271 +787,272 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>PTL-H 30W</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>劉芬</t>
+          <t>朱芳芳</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>2026/03/27</t>
+          <t>2026/04/13</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr"/>
       <c r="J4" s="4" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2026/05/21</t>
+          <t>2026/05/10</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>2026/04/30</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>2026/05/30</t>
+          <t>2026/06/23</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>2026/06/18</t>
+          <t>2026/06/30</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>MLG(魔龍姬)ID，+9</t>
+          <t>梵谷特仕版 物料持續追踪，6/23 ATS CR，6/E出貨</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>1.因A/B件及rear cover有發黃issue，ID確認重新更換噴漆廠商，重新備料+驗證以致MP 6/9 delay至6/18</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
+          <t>1. ALS sensor NG  HDI 進版 6/27重工， 1.A件成品LOGO不良較高，交料瓶頸 請ID&amp;Buyer持續pull in。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" hidden="1" outlineLevel="1">
+      <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>14T2</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Prestige 14 Flip AI+ Rhône</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Prestige 14 Flip AI+ Starry Night</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>PTL-H 30W</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>朱芳芳</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>2026/04/13</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr"/>
+      <c r="J5" s="9" t="inlineStr"/>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/10</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/23</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="O5" s="11" t="inlineStr">
+        <is>
+          <t>梵谷特仕版 物料持續追踪，規劃6/23 ATS CR，6/E出貨</t>
+        </is>
+      </c>
+      <c r="P5" s="11" t="inlineStr">
+        <is>
+          <t>1. ALS sensor NG  HDI 進版 6/27重工， 2.A件成品LOGO不良較高，交料瓶頸 請ID&amp;Buyer持續pull in。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>265L</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>PTL-H 30W</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Intel® Arc™ Graphics</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>朱芳芳</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/13</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/10</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/23</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/30</t>
-        </is>
-      </c>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t>梵谷特仕版 物料持續追踪，6/23 ATS CR，6/E出貨</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>ATS CR 6/22齊料 ，2nd MP 請ID&amp;Buyer持續pull in。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" hidden="1" outlineLevel="1">
-      <c r="A6" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>14T2</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Prestige 14 Flip AI+ Starry Night</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>DRG-HX 55W</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/03</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/10</t>
+        </is>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>MLG(魔龍姬)ID: DQA 測試中</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；
+2) Packing: WW版本設計確認中;
+3) Schedule: 生管排程, ATS 由7/1更新為7/3. MP @7/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" hidden="1" outlineLevel="1">
+      <c r="A7" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>265L</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>PTL-H 30W</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>Intel® Arc™ Graphics</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>朱芳芳</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>2026/04/13</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr"/>
-      <c r="J6" s="9" t="inlineStr"/>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/10</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/23</t>
-        </is>
-      </c>
-      <c r="N6" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/30</t>
-        </is>
-      </c>
-      <c r="O6" s="11" t="inlineStr">
-        <is>
-          <t>梵谷特仕版 物料持續追踪，規劃6/23 ATS CR，6/E出貨</t>
-        </is>
-      </c>
-      <c r="P6" s="11" t="inlineStr">
-        <is>
-          <t>ATS CR 6/22齊料 ，2nd MP 請ID&amp;Buyer持續pull in。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>265L</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>DRG-HX 55W</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>朱欣怡</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr"/>
+      <c r="J7" s="9" t="inlineStr"/>
+      <c r="K7" s="9" t="inlineStr">
         <is>
           <t>2026/06/02</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>2026/05/26</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/01</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/08</t>
-        </is>
-      </c>
-      <c r="O7" s="6" t="inlineStr">
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/03</t>
+        </is>
+      </c>
+      <c r="N7" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/10</t>
+        </is>
+      </c>
+      <c r="O7" s="11" t="inlineStr">
         <is>
           <t>MLG(魔龍姬)ID: DQA 測試中</t>
         </is>
       </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；
-2) Packing: WW版本設計確認中;</t>
+      <c r="P7" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1067,7 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
@@ -1081,7 +1082,7 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -1108,17 +1109,17 @@
       </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
-          <t>2026/07/01</t>
+          <t>2026/07/03</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="O8" s="11" t="inlineStr">
         <is>
-          <t>MLG(魔龍姬)ID: DQA 測試中</t>
+          <t>MLG(魔龍姬)ID:  DQA 測試中</t>
         </is>
       </c>
       <c r="P8" s="11" t="inlineStr">
@@ -1138,7 +1139,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+          <t>Crosshair A16 HX MLG Edition E8WGXK</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
@@ -1180,12 +1181,12 @@
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
-          <t>2026/07/01</t>
+          <t>2026/07/03</t>
         </is>
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="O9" s="11" t="inlineStr">
@@ -1421,12 +1422,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>24VL</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
+          <t>Modern A14 LE J1M</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -1472,24 +1473,22 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>2026/06/25</t>
+          <t>2026/07/01</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>MVT測試中，DQA 測試Issue 需微步協助盡快釐清&amp;導入對策,</t>
+          <t>預計7/1 ATS ASSY，DQA 測試Issue 需微步協助在6/29前釐清&amp; 導入對策，</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 已到料2.8K ,其它7/B 陸續進料 B&amp;S物料： 6/18已寄送微步 ，預計6/22到料，
-2)認證 a))TUV 認證预计7/E b)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 c) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG ,SG 無需認證，TH 認證已ready
-3）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，目前TTM時間預計從7/8 延後到7/10，</t>
+          <t>1)	Schedule：MVT Issue，需微步協調人力加速，確保在6/29前釐清Issue及導入對策，AMD  VGA WHQL  driver需在6/26 提供，滿足7/1 ATS start,</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1498,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>24VL</t>
+          <t>26VL</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Modern A14 LE J1M</t>
+          <t>Modern A16 LE J1M</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -1550,25 +1549,22 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>2026/07/01</t>
+          <t>2026/07/04</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>2026/07/10</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>MVT測試中，DQA 測試Issue 需微步協助盡快釐清&amp;導入對策，</t>
+          <t>因26VL 機構物料7/3 ready，預計7/3 ATS ASSY ，</t>
         </is>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>1)物料： adapter：目標6K， 已到料2.8K ,其它7/B 陸續進料 B&amp;S物料： 6/18已寄送微步 ，預計6/22到料，
-2)認證 a))TUV 認證预计7/E b)其他地區認證follow In house 流程，有訂單需求後由業務通知申請 c) 24VL/26VL只有TH&amp;SG下單， Total 2072 Pcs：26VL:1.8K TH+80Pcs SG &amp; 24VL: 192Pcs SG ,SG 無需認證，TH 認證已ready
-3）MVT Issue 微步Debug 進度緩慢，需微步協調人力加速釐清Issue及導入對策，目前TTM時間預計從7/8 延後到7/10，
-4）6/18 微步通知24VL Panel ESD 測試Fail，需更換替代料，需微步安排相關測試項目，以及評估是否對Schedule 有影響，</t>
+          <t>1)	Schedule：MVT Issue，需微步協調人力加速，確保在6/29前釐清Issue及導入對策，AMD  VGA WHQL  driver需在6/26 提供，滿足7/3 ATS start,</t>
         </is>
       </c>
     </row>
@@ -1578,239 +1574,233 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
+          <t>15Q1</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Cyborg 15 B2VE</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>ARL-H 45W</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>RTX 4050 (35W+10W)/ GDDR6 6GB</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>李文欽</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/31</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>（清白光鍵盤庫存）預計下周提供樣機給DQA驗證,測試預計２周時間</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
           <t>2621</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Prestige N16 Spark</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>N1x 80W</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>林晉弘</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>2024/11/25</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>2025/01/20</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>2025/06/25</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>2026/03/12</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>2026/06/30</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>2026/07/31</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>2026/08/14</t>
         </is>
       </c>
-      <c r="O15" s="6" t="inlineStr">
+      <c r="O16" s="6" t="inlineStr">
         <is>
           <t>MVT測試中</t>
         </is>
       </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>1)MSFT CER/HWE主要如下P0問題，與MSFT確認以BIOS 048+ image 2.17複驗，6/18寄送3台更換2.8K panel樣品for HWV/CER P0問題驗證
-2)6/15 NV通知進版 BSP FD Rev.B，BIOS release 6/18 BIOS 049因應，MSFT release WIR 6B請preload重新製作image中for Rev.B測試 。
-3)3.8K panel 需更新FW，NV VK key 6/16已提供，三星6/17提供FW，已更新給DQA與RD for 現行樣品驗證。
-4)6/10 通知A-side需增加龍盾+小標，備料需4週，ME評估6/E前須完成打樣讓老闆確認，才能趕上7/31 ATS start。ID已提供proposal，Ronald請行銷須於6/18請老闆確認，以免影響後續ATS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" hidden="1" outlineLevel="1">
-      <c r="A16" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>1)MSFT 6/24 release power report，report中power consumption數據與battery life跟廠內DQA及RD有落差，待與MSFT比對測試環境差異，釐清測試結果。
+2)DQA/RD/工廠切換到BSP FD Rev.B與BIOS 049測試中。NV 6/23 release BSP FD ver.C，待BIOS與preload更新後，會再切換新版測試。
+3)6/10 通知A-side需增加龍盾+小標，ME評估6/E前須完成打樣讓老闆確認，才能趕上7/31 ATS start。已請Ronald push務必於本周確認完成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" hidden="1" outlineLevel="1">
+      <c r="A17" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>Prestige N16 Flip Spark</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>N1x 80W</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>林晉弘</t>
         </is>
       </c>
-      <c r="H16" s="9" t="inlineStr">
+      <c r="H17" s="9" t="inlineStr">
         <is>
           <t>2024/11/25</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>2025/01/20</t>
         </is>
       </c>
-      <c r="J16" s="9" t="inlineStr">
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>2025/06/25</t>
         </is>
       </c>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="K17" s="9" t="inlineStr">
         <is>
           <t>2026/03/12</t>
         </is>
       </c>
-      <c r="L16" s="9" t="inlineStr">
+      <c r="L17" s="9" t="inlineStr">
         <is>
           <t>2026/06/30</t>
         </is>
       </c>
-      <c r="M16" s="9" t="inlineStr">
+      <c r="M17" s="9" t="inlineStr">
         <is>
           <t>2026/07/31</t>
         </is>
       </c>
-      <c r="N16" s="9" t="inlineStr">
+      <c r="N17" s="9" t="inlineStr">
         <is>
           <t>2026/08/14</t>
         </is>
       </c>
-      <c r="O16" s="11" t="inlineStr">
+      <c r="O17" s="11" t="inlineStr">
         <is>
           <t>MVT測試中</t>
         </is>
       </c>
-      <c r="P16" s="11" t="inlineStr">
-        <is>
-          <t>1)MSFT CER/HWE主要如下P0問題，與MSFT確認以BIOS 048+ image 2.17複驗，6/18寄送3台更換2.8K panel樣品for HWV/CER P0問題驗證
-2)6/15 NV通知進版 BSP FD Rev.B，BIOS release 6/18 BIOS 049因應，MSFT release WIR 6B請preload重新製作image中for Rev.B測試 。
-3)3.8K panel 需更新FW，NV VK key 6/16已提供，三星6/17提供FW，已更新給DQA與RD for 現行樣品驗證。
-4)6/10 通知A-side需增加龍盾+小標，備料需4週，ME評估6/E前須完成打樣讓老闆確認，才能趕上7/31 ATS start。ID已提供proposal，Ronald請行銷須於6/18請老闆確認，以免影響後續ATS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>15T2</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Venture 15 AI+ B3M</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>PTL-H 80W</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Intel® Arc™ Graphics</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>李文欽</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/20</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/26</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr"/>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/08</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/20</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/17</t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/27</t>
-        </is>
-      </c>
-      <c r="O17" s="6" t="inlineStr">
-        <is>
-          <t>DVT Debug &amp; 測試中</t>
-        </is>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>1) 10 gerberout@6/25,需麻煩各RD加速相關驗證</t>
+      <c r="P17" s="11" t="inlineStr">
+        <is>
+          <t>1)MSFT 6/24 release power report，report中power consumption數據與battery life跟廠內DQA及RD有落差，待與MSFT比對測試環境差異，釐清測試結果。
+2)DQA/RD/工廠切換到BSP FD Rev.B與BIOS 049測試中。NV 6/23 release BSP FD ver.C，待BIOS與preload更新後，會再切換新版測試。
+3)6/10 通知A-side需增加龍盾+小標，ME評估6/E前須完成打樣讓老闆確認，才能趕上7/31 ATS start。已請Ronald push務必於本周確認完成。</t>
         </is>
       </c>
     </row>
@@ -1820,32 +1810,32 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>15T3</t>
+          <t>15T2</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WEK</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
+          <t>Venture 15 AI+ B3M</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>PTL-H 80W</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>蔡東宏</t>
+          <t>李文欽</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1855,114 +1845,114 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>2026/06/01</t>
+          <t>2026/05/26</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr"/>
       <c r="K18" s="4" t="inlineStr">
         <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="O18" s="6" t="inlineStr">
+        <is>
+          <t>DVT Debug &amp; 測試中</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>1) 10 gerberout@6/26,schedule暫不影響</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>15T3</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Katana 15 HX C14WEK</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>蔡東宏</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/20</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
           <t>2026/07/14</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>2026/07/30</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>2026/08/20</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>2026/08/30</t>
         </is>
       </c>
-      <c r="O18" s="6" t="inlineStr">
-        <is>
-          <t>DDR5 sku, DVT測試中</t>
-        </is>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>SA測項:USB3.2 Gen1 SSC fail,請RD儘速提供solution</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" hidden="1" outlineLevel="1">
-      <c r="A19" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>15T3</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Katana 15 HX C14WFK</t>
-        </is>
-      </c>
-      <c r="D19" s="15" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>2026/04/20</t>
-        </is>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
-      </c>
-      <c r="J19" s="9" t="inlineStr"/>
-      <c r="K19" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/14</t>
-        </is>
-      </c>
-      <c r="L19" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/30</t>
-        </is>
-      </c>
-      <c r="M19" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/20</t>
-        </is>
-      </c>
-      <c r="N19" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/30</t>
-        </is>
-      </c>
-      <c r="O19" s="11" t="inlineStr">
-        <is>
-          <t>DDR5 sku, DVT測試中</t>
-        </is>
-      </c>
-      <c r="P19" s="11" t="inlineStr">
-        <is>
-          <t>SA測項:USB3.2 Gen1 SSC fail,請RD儘速提供solution</t>
+      <c r="O19" s="6" t="inlineStr">
+        <is>
+          <t>DDR5 sku, DVT測試中,預計7/2 PCB 10 gerberout</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1977,10 +1967,10 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WGK</t>
-        </is>
-      </c>
-      <c r="D20" s="15" t="inlineStr">
+          <t>Katana 15 HX C14WFK</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -1992,7 +1982,7 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
@@ -2033,12 +2023,12 @@
       </c>
       <c r="O20" s="11" t="inlineStr">
         <is>
-          <t>DDR5 sku, DVT測試中</t>
+          <t>DDR5 sku, DVT測試中,預計7/2 PCB 10 gerberout</t>
         </is>
       </c>
       <c r="P20" s="11" t="inlineStr">
         <is>
-          <t>SA測項:USB3.2 Gen1 SSC fail,請RD儘速提供solution</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2053,10 +2043,10 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WGXK</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
+          <t>Katana 15 HX C14WGK</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2109,12 +2099,12 @@
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>DDR5 sku, DVT測試中</t>
+          <t>DDR5 sku, DVT測試中,預計7/2 PCB 10 gerberout</t>
         </is>
       </c>
       <c r="P21" s="11" t="inlineStr">
         <is>
-          <t>SA測項:USB3.2 Gen1 SSC fail,請RD儘速提供solution</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2129,10 +2119,10 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WEOK</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
+          <t>Katana 15 HX C14WGXK</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2144,7 +2134,7 @@
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -2154,38 +2144,38 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>2026/05/15</t>
+          <t>2026/04/20</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
+          <t>2026/06/01</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr"/>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>2026/08/07</t>
+          <t>2026/07/30</t>
         </is>
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
-          <t>2026/08/21</t>
+          <t>2026/08/20</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
         <is>
-          <t>2026/08/31</t>
+          <t>2026/08/30</t>
         </is>
       </c>
       <c r="O22" s="11" t="inlineStr">
         <is>
-          <t>DDR4 sku, DVT測試中</t>
+          <t>DDR5 sku, DVT測試中,預計7/2 PCB 10 gerberout</t>
         </is>
       </c>
       <c r="P22" s="11" t="inlineStr">
@@ -2205,10 +2195,10 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WFOK</t>
-        </is>
-      </c>
-      <c r="D23" s="15" t="inlineStr">
+          <t>Katana 15 HX C14WEOK</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2220,7 +2210,7 @@
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
@@ -2281,10 +2271,10 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WGOK</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
+          <t>Katana 15 HX C14WFOK</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2296,7 +2286,7 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
@@ -2357,10 +2347,10 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WGXOK</t>
-        </is>
-      </c>
-      <c r="D25" s="15" t="inlineStr">
+          <t>Katana 15 HX C14WGOK</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2422,157 +2412,156 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
+    <row r="26" hidden="1" outlineLevel="1">
+      <c r="A26" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>15T3</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Katana 15 HX C14WGXOK</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>蔡東宏</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/15</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr"/>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/24</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="M26" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="N26" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="O26" s="11" t="inlineStr">
+        <is>
+          <t>DDR4 sku, DVT測試中</t>
+        </is>
+      </c>
+      <c r="P26" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>15TK</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Cyborg A15 Max C1PWE</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D27" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>HWK 45W</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>2026/05/28</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>2026/06/26</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr"/>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>2026/07/17</t>
         </is>
       </c>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>2026/07/31</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="N27" s="4" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O26" s="6" t="inlineStr">
-        <is>
-          <t>APU預計8月中供貨(from AMD),業務目標8月底MP,為達成量產時程目標,整體開發與驗證需pull in至8月底MP,與team member討論後,預計DVT@6/26,MVT@7/17,ATS start@8/21,MP@8/31</t>
-        </is>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>1).Schedule:R7-155優先進行ATS,以 8 月底 MP 為目標,其餘APU sku在9月進行ATS C/R
-2). Material:Thermal module將依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS,若實測驗證結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" hidden="1" outlineLevel="1">
-      <c r="A27" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>15TK</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Cyborg A15 Max C1PWF</t>
-        </is>
-      </c>
-      <c r="D27" s="15" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>HWK 45W</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H27" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/26</t>
-        </is>
-      </c>
-      <c r="J27" s="9" t="inlineStr"/>
-      <c r="K27" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/17</t>
-        </is>
-      </c>
-      <c r="L27" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/31</t>
-        </is>
-      </c>
-      <c r="M27" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="N27" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/31</t>
-        </is>
-      </c>
-      <c r="O27" s="11" t="inlineStr">
-        <is>
-          <t>APU預計8月中供貨(from AMD),業務目標8月底MP,為達成量產時程目標,整體開發與驗證需pull in至8月底MP,與team member討論後,預計DVT@6/26,MVT@7/17,ATS start@8/21,MP@8/31</t>
-        </is>
-      </c>
-      <c r="P27" s="11" t="inlineStr">
-        <is>
-          <t>1).Schedule:R7-155優先進行ATS,以 8 月底 MP 為目標,其餘APU sku在9月進行ATS C/R
-2). Material:Thermal module將依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS,若實測驗證結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
+          <t>HPT sku:RD已重工3台成APU 180且刷16RK的BIOS可開機進OS,需AMD/AMI 儘速release PI code 1200i進行測試</t>
+        </is>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>1).Schedule:APU 155優先ATS,採購已下單6.5k,以 8 月底 MP為目標,其餘APU sku在9月進行ATS C/R,但PI code 1200i release延至6/30與APU 155 PR樣品ETD 延至7/11,已影響 MP 時程,待收到PI code與PR樣品後將依實際測試情況確認是否調整MP時程
+2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
     </row>
@@ -2587,10 +2576,10 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Cyborg A15 Max C1PWG</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="inlineStr">
+          <t>Cyborg A15 Max C1PWF</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2602,7 +2591,7 @@
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
@@ -2643,13 +2632,13 @@
       </c>
       <c r="O28" s="11" t="inlineStr">
         <is>
-          <t>APU預計8月中供貨(from AMD),業務目標8月底MP,為達成量產時程目標,整體開發與驗證需pull in至8月底MP,與team member討論後,預計DVT@6/26,MVT@7/17,ATS start@8/21,MP@8/31</t>
+          <t>HPT sku:RD已重工3台成APU 180且刷16RK的BIOS可開機進OS,需AMD/AMI 儘速release PI code 1200i進行測試</t>
         </is>
       </c>
       <c r="P28" s="11" t="inlineStr">
         <is>
-          <t>1).Schedule:R7-155優先進行ATS,以 8 月底 MP 為目標,其餘APU sku在9月進行ATS C/R
-2). Material:Thermal module將依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS,若實測驗證結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
+          <t>1).Schedule:APU 155優先ATS,採購已下單6.5k,以 8 月底 MP為目標,其餘APU sku在9月進行ATS C/R,但PI code 1200i release延至6/30與APU 155 PR樣品ETD 延至7/11,已影響 MP 時程,待收到PI code與PR樣品後將依實際測試情況確認是否調整MP時程
+2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
     </row>
@@ -2664,10 +2653,10 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Cyborg A15 C1PWE</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="inlineStr">
+          <t>Cyborg A15 Max C1PWG</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2679,7 +2668,7 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -2720,90 +2709,90 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>APU預計8月中供貨(from AMD),業務目標8月底MP,為達成量產時程目標,整體開發與驗證需pull in至8月底MP,與team member討論後,預計DVT@6/26,MVT@7/17,ATS start@8/21,MP@8/31</t>
+          <t>HPT sku:RD已重工3台成APU 180且刷16RK的BIOS可開機進OS,需AMD/AMI 儘速release PI code 1200i進行測試</t>
         </is>
       </c>
       <c r="P29" s="11" t="inlineStr">
         <is>
-          <t>1).Schedule:R7-155優先進行ATS,以 8 月底 MP 為目標,其餘APU sku在9月進行ATS C/R
-2). Material:Thermal module將依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS,若實測驗證結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
+          <t>1).Schedule:APU 155優先ATS,採購已下單6.5k,以 8 月底 MP為目標,其餘APU sku在9月進行ATS C/R,但PI code 1200i release延至6/30與APU 155 PR樣品ETD 延至7/11,已影響 MP 時程,待收到PI code與PR樣品後將依實際測試情況確認是否調整MP時程
+2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" hidden="1" outlineLevel="1">
+      <c r="A30" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>24V1</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Modern 14 LE J3M</t>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>15TK</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Cyborg A15 C1PWE</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>WCL 25W</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Intel® graphics</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>倪嬌嬌</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr"/>
-      <c r="K30" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/29</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/06</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/17</t>
-        </is>
-      </c>
-      <c r="N30" s="4" t="inlineStr">
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>HWK 45W</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>蔡東宏</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr"/>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/17</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/31</t>
+        </is>
+      </c>
+      <c r="M30" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="N30" s="9" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O30" s="6" t="inlineStr">
-        <is>
-          <t>Weibu plan 6/29 DVT SMT, 7/1 ASSY--熱管&amp;D件重新開模, 交期7/1</t>
-        </is>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>1)Schedule: 考量新料備料時程, 調整試產和ATS時間@8/17 start
-2)認證: 參考Weibu認證Schedule, 有四個國家無法同步於8/E TTM, 持續追蹤中 MX: 11/28 ready；AR:10/3 ready；CO: 9/5 ready；RU: 9/12 ready</t>
+      <c r="O30" s="11" t="inlineStr">
+        <is>
+          <t>HPT sku:RD已重工3台成APU 180且刷16RK的BIOS可開機進OS,需AMD/AMI 儘速release PI code 1200i進行測試</t>
+        </is>
+      </c>
+      <c r="P30" s="11" t="inlineStr">
+        <is>
+          <t>1).Schedule:APU 155優先ATS,採購已下單6.5k,以 8 月底 MP為目標,其餘APU sku在9月進行ATS C/R,但PI code 1200i release延至6/30與APU 155 PR樣品ETD 延至7/11,已影響 MP 時程,待收到PI code與PR樣品後將依實際測試情況確認是否調整MP時程
+2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
     </row>
@@ -2813,15 +2802,15 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>26V1</t>
+          <t>24V1</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Modern 16 LE J3M</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
+          <t>Modern 14 LE J3M</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -2874,7 +2863,7 @@
       </c>
       <c r="O31" s="6" t="inlineStr">
         <is>
-          <t>Weibu plan 6/29 DVT SMT, 7/1 ASSY --熱管重新開模, 交期6/30</t>
+          <t>Weibu plan 6/29 DVT SMT, 7/1 ASSY--熱管&amp;D件重新開模, 交期7/1</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
@@ -2890,27 +2879,27 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>14T3</t>
+          <t>26V1</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Prestige N14 Spark D1M</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>MVT</t>
+          <t>Modern 16 LE J3M</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>N1 35W</t>
+          <t>WCL 25W</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Intel® graphics</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -2920,48 +2909,44 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>2025/04/30</t>
+          <t>2026/06/02</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>2025/09/01</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/15</t>
-        </is>
-      </c>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr"/>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026/07/20</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>2026/09/14</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>2026/10/13</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/08/31</t>
         </is>
       </c>
       <c r="O32" s="6" t="inlineStr">
         <is>
-          <t>MVT SMT@7/20--depend on 0C PCB ETA</t>
+          <t>Weibu plan 6/29 DVT SMT, 7/1 ASSY --熱管重新開模, 交期6/30</t>
         </is>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>1) Schedule: NV update BSP時間Factory drop final ETA@10/6, 更新ATS start@10/13
-2)備料： 2.8K panel的驗證 follow leading customer, 交料plan:a. 1st MP lot: 1K 數量, 型號HQ15, 九月份交料(同步Leading customers量產交料時間 具體九月份ETD日期還在追蹤中. b. Others order: 需轉型號至HQxx, 十一月份交料</t>
+          <t>1)Schedule: 考量新料備料時程, 調整試產和ATS時間@8/17 start
+2)認證: 參考Weibu認證Schedule, 有四個國家無法同步於8/E TTM, 持續追蹤中 MX: 11/28 ready；AR:10/3 ready；CO: 9/5 ready；RU: 9/12 ready</t>
         </is>
       </c>
     </row>
@@ -3052,157 +3037,157 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
+          <t>14T3</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Prestige N14 Spark D1M</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>N1 35W</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>倪嬌嬌</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/30</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>2025/09/01</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/13</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/26</t>
+        </is>
+      </c>
+      <c r="O34" s="6" t="inlineStr">
+        <is>
+          <t>MVT SMT@7/20--depend on Material ready date</t>
+        </is>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>1)備料：MP focus on 2.8K panel, for MVT@7/M, 待廠商確認中; for MP: a, 1st lot 1K 數量, 型號HQ15, 九月份交料(同步Leading customers量產交料時間 具體九月份ETD日期還在追蹤中. b. Others order: 需轉型號至HQxx, 十一月份交料</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Katana 18 HX A14WEK</t>
         </is>
       </c>
-      <c r="D34" s="14" t="inlineStr">
+      <c r="D35" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>2026/08/24</t>
         </is>
       </c>
-      <c r="K34" s="4" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>2026/10/12</t>
         </is>
       </c>
-      <c r="L34" s="4" t="inlineStr">
+      <c r="L35" s="4" t="inlineStr">
         <is>
           <t>2026/11/02</t>
         </is>
       </c>
-      <c r="M34" s="4" t="inlineStr">
+      <c r="M35" s="4" t="inlineStr">
         <is>
           <t>2026/11/21</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>2026/11/30</t>
         </is>
       </c>
-      <c r="O34" s="6" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR5: DVT SMT @ 6/18 VBIOS先用2653的替用，待1861申請到後請HW重刷測試</t>
-        </is>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>1）schedule：因ID變動，可能會整體順延2W，請RD繼續努力，盡量keep目前schedule，實際影響待後續再做更新</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" hidden="1" outlineLevel="1">
-      <c r="A35" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Katana 18 HX A14WFK</t>
-        </is>
-      </c>
-      <c r="D35" s="15" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>顧曉琴</t>
-        </is>
-      </c>
-      <c r="H35" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J35" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
-      <c r="K35" s="9" t="inlineStr">
-        <is>
-          <t>2026/10/12</t>
-        </is>
-      </c>
-      <c r="L35" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/02</t>
-        </is>
-      </c>
-      <c r="M35" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/21</t>
-        </is>
-      </c>
-      <c r="N35" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/30</t>
-        </is>
-      </c>
-      <c r="O35" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR5: DVT SMT @ 6/18 VBIOS先用2653的替用，待1861申請到後請HW重刷測試</t>
-        </is>
-      </c>
-      <c r="P35" s="11" t="inlineStr">
-        <is>
-          <t>1）schedule：因ID變動，可能會整體順延2W，請RD繼續努力，盡量keep目前schedule，實際影響待後續再做更新</t>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR5: DVT PCBA快遞3pcs 6/24到,目前已開機,調撥部分6/25到料供RD測試</t>
+        </is>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3217,10 +3202,10 @@
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGK</t>
-        </is>
-      </c>
-      <c r="D36" s="15" t="inlineStr">
+          <t>Katana 18 HX A14WFK</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3232,7 +3217,7 @@
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -3277,12 +3262,12 @@
       </c>
       <c r="O36" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT SMT @ 6/18 VBIOS先用2653的替用，待1861申請到後請HW重刷測試</t>
+          <t>RPL-HX R + DDR5: DVT PCBA快遞3pcs 6/24到,目前已開機,調撥部分6/25到料供RD測試</t>
         </is>
       </c>
       <c r="P36" s="11" t="inlineStr">
         <is>
-          <t>1）schedule：因ID變動，可能會整體順延2W，請RD繼續努力，盡量keep目前schedule，實際影響待後續再做更新</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3297,10 +3282,10 @@
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WEOK</t>
-        </is>
-      </c>
-      <c r="D37" s="15" t="inlineStr">
+          <t>Katana 18 HX A14WGK</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3312,7 +3297,7 @@
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -3322,18 +3307,22 @@
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J37" s="9" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
       <c r="K37" s="9" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/10/12</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
@@ -3343,22 +3332,22 @@
       </c>
       <c r="M37" s="9" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2026/11/21</t>
         </is>
       </c>
       <c r="N37" s="9" t="inlineStr">
         <is>
-          <t>2026/12/02</t>
+          <t>2026/11/30</t>
         </is>
       </c>
       <c r="O37" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: 預計DVT SMT @ 6/29</t>
+          <t>RPL-HX R + DDR5: DVT PCBA快遞3pcs 6/24到,目前已開機,調撥部分6/25到料供RD測試</t>
         </is>
       </c>
       <c r="P37" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3373,10 +3362,10 @@
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WFOK</t>
-        </is>
-      </c>
-      <c r="D38" s="15" t="inlineStr">
+          <t>Katana 18 HX A14WEOK</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3388,7 +3377,7 @@
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -3429,7 +3418,7 @@
       </c>
       <c r="O38" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: 預計DVT SMT @ 6/29</t>
+          <t>RPL-HX R + DDR4: DVT SMT @ 6/30</t>
         </is>
       </c>
       <c r="P38" s="11" t="inlineStr">
@@ -3449,10 +3438,10 @@
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGOK</t>
-        </is>
-      </c>
-      <c r="D39" s="15" t="inlineStr">
+          <t>Katana 18 HX A14WFOK</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3464,7 +3453,7 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
@@ -3505,7 +3494,7 @@
       </c>
       <c r="O39" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: 預計DVT SMT @ 6/29</t>
+          <t>RPL-HX R + DDR4: DVT SMT @ 6/30</t>
         </is>
       </c>
       <c r="P39" s="11" t="inlineStr">
@@ -3525,10 +3514,10 @@
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WE</t>
-        </is>
-      </c>
-      <c r="D40" s="15" t="inlineStr">
+          <t>Katana 18 HX A14WGOK</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3540,7 +3529,7 @@
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
@@ -3550,19 +3539,15 @@
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J40" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="inlineStr"/>
       <c r="K40" s="9" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3575,22 +3560,22 @@
       </c>
       <c r="M40" s="9" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2026/11/23</t>
         </is>
       </c>
       <c r="N40" s="9" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2026/12/02</t>
         </is>
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT SMT @ 6/18 VBIOS先用2653的替用，待1861申請到後請HW重刷測試</t>
+          <t>RPL-HX R + DDR4: DVT SMT @ 6/30</t>
         </is>
       </c>
       <c r="P40" s="11" t="inlineStr">
         <is>
-          <t>1）schedule：因ID變動，可能會整體順延2W，請RD繼續努力，盡量keep目前schedule，實際影響待後續再做更新</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3605,10 +3590,10 @@
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WF</t>
-        </is>
-      </c>
-      <c r="D41" s="15" t="inlineStr">
+          <t>Crosshair 18 Max HX B14WEO</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3620,7 +3605,7 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -3630,19 +3615,15 @@
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J41" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="inlineStr"/>
       <c r="K41" s="9" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3665,12 +3646,12 @@
       </c>
       <c r="O41" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT SMT @ 6/18 VBIOS先用2653的替用，待1861申請到後請HW重刷測試</t>
+          <t>RPL-HX R + DDR4: DVT SMT @ 6/30</t>
         </is>
       </c>
       <c r="P41" s="11" t="inlineStr">
         <is>
-          <t>1）schedule：因ID變動，可能會整體順延2W，請RD繼續努力，盡量keep目前schedule，實際影響待後續再做更新</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3685,10 +3666,10 @@
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WG</t>
-        </is>
-      </c>
-      <c r="D42" s="15" t="inlineStr">
+          <t>Crosshair 18 Max HX B14WFO</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3700,7 +3681,7 @@
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -3710,19 +3691,15 @@
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J42" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="inlineStr"/>
       <c r="K42" s="9" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3745,12 +3722,12 @@
       </c>
       <c r="O42" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT SMT @ 6/18 VBIOS先用2653的替用，待1861申請到後請HW重刷測試</t>
+          <t>RPL-HX R + DDR4: DVT SMT @ 6/30</t>
         </is>
       </c>
       <c r="P42" s="11" t="inlineStr">
         <is>
-          <t>1）schedule：因ID變動，可能會整體順延2W，請RD繼續努力，盡量keep目前schedule，實際影響待後續再做更新</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3765,10 +3742,10 @@
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WGX</t>
-        </is>
-      </c>
-      <c r="D43" s="15" t="inlineStr">
+          <t>Crosshair 18 Max HX B14WGO</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3790,19 +3767,15 @@
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J43" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="inlineStr"/>
       <c r="K43" s="9" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3825,12 +3798,12 @@
       </c>
       <c r="O43" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT SMT @ 6/18 VBIOS先用2653的替用，待1861申請到後請HW重刷測試</t>
+          <t>RPL-HX R + DDR4: DVT SMT @ 6/30</t>
         </is>
       </c>
       <c r="P43" s="11" t="inlineStr">
         <is>
-          <t>1）schedule：因ID變動，可能會整體順延2W，請RD繼續努力，盡量keep目前schedule，實際影響待後續再做更新</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3845,10 +3818,10 @@
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WEO</t>
-        </is>
-      </c>
-      <c r="D44" s="15" t="inlineStr">
+          <t>Crosshair 18 Max HX B14WGXO</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3860,7 +3833,7 @@
       </c>
       <c r="F44" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
@@ -3901,7 +3874,7 @@
       </c>
       <c r="O44" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: 預計DVT SMT @ 6/29</t>
+          <t>RPL-HX R + DDR4: DVT SMT @ 6/30</t>
         </is>
       </c>
       <c r="P44" s="11" t="inlineStr">
@@ -3921,10 +3894,10 @@
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WFO</t>
-        </is>
-      </c>
-      <c r="D45" s="15" t="inlineStr">
+          <t>Crosshair 18 Max HX B14WE</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3936,7 +3909,7 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
@@ -3946,15 +3919,19 @@
       </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J45" s="9" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
       <c r="K45" s="9" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3977,12 +3954,12 @@
       </c>
       <c r="O45" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: 預計DVT SMT @ 6/29</t>
+          <t>RPL-HX R + DDR5: DVT PCBA快遞3pcs 6/24到,目前已開機,調撥部分6/25到料供RD測試</t>
         </is>
       </c>
       <c r="P45" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3997,10 +3974,10 @@
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WGO</t>
-        </is>
-      </c>
-      <c r="D46" s="15" t="inlineStr">
+          <t>Crosshair 18 Max HX B14WF</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -4012,7 +3989,7 @@
       </c>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
@@ -4022,15 +3999,19 @@
       </c>
       <c r="H46" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J46" s="9" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
       <c r="K46" s="9" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -4053,12 +4034,12 @@
       </c>
       <c r="O46" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: 預計DVT SMT @ 6/29</t>
+          <t>RPL-HX R + DDR5: DVT PCBA快遞3pcs 6/24到,目前已開機,調撥部分6/25到料供RD測試</t>
         </is>
       </c>
       <c r="P46" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4073,10 +4054,10 @@
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WGXO</t>
-        </is>
-      </c>
-      <c r="D47" s="15" t="inlineStr">
+          <t>Crosshair 18 Max HX B14WG</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -4098,15 +4079,19 @@
       </c>
       <c r="H47" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J47" s="9" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
       <c r="K47" s="9" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -4129,12 +4114,12 @@
       </c>
       <c r="O47" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: 預計DVT SMT @ 6/29</t>
+          <t>RPL-HX R + DDR5: DVT PCBA快遞3pcs 6/24到,目前已開機,調撥部分6/25到料供RD測試</t>
         </is>
       </c>
       <c r="P47" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4149,22 +4134,22 @@
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WE</t>
-        </is>
-      </c>
-      <c r="D48" s="18" t="inlineStr">
-        <is>
-          <t>Design</t>
+          <t>Crosshair 18 Max HX B14WGX</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX Next 55W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
@@ -4177,36 +4162,44 @@
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I48" s="9" t="inlineStr"/>
-      <c r="J48" s="9" t="inlineStr"/>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
       <c r="K48" s="9" t="inlineStr">
         <is>
-          <t>2026/12/08</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="L48" s="9" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/11/02</t>
         </is>
       </c>
       <c r="M48" s="9" t="inlineStr">
         <is>
-          <t>2027/01/19</t>
+          <t>2026/11/28</t>
         </is>
       </c>
       <c r="N48" s="9" t="inlineStr">
         <is>
-          <t>2027/01/30</t>
+          <t>2026/12/07</t>
         </is>
       </c>
       <c r="O48" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX R + DDR5: DVT PCBA快遞3pcs 6/24到,目前已開機,調撥部分6/25到料供RD測試</t>
         </is>
       </c>
       <c r="P48" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4214,7 @@
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WEO</t>
+          <t>Crosshair 18 Max HX B2WE</t>
         </is>
       </c>
       <c r="D49" s="18" t="inlineStr">
@@ -4246,7 +4239,7 @@
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I49" s="9" t="inlineStr"/>
@@ -4273,7 +4266,7 @@
       </c>
       <c r="O49" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P49" s="11" t="inlineStr">
@@ -4293,7 +4286,7 @@
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WF</t>
+          <t>Crosshair 18 Max HX B2WEO</t>
         </is>
       </c>
       <c r="D50" s="18" t="inlineStr">
@@ -4308,7 +4301,7 @@
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
@@ -4318,7 +4311,7 @@
       </c>
       <c r="H50" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I50" s="9" t="inlineStr"/>
@@ -4345,7 +4338,7 @@
       </c>
       <c r="O50" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P50" s="11" t="inlineStr">
@@ -4365,7 +4358,7 @@
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WFO</t>
+          <t>Crosshair 18 Max HX B2WF</t>
         </is>
       </c>
       <c r="D51" s="18" t="inlineStr">
@@ -4390,7 +4383,7 @@
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I51" s="9" t="inlineStr"/>
@@ -4417,7 +4410,7 @@
       </c>
       <c r="O51" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P51" s="11" t="inlineStr">
@@ -4437,7 +4430,7 @@
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WG</t>
+          <t>Crosshair 18 Max HX B2WFO</t>
         </is>
       </c>
       <c r="D52" s="18" t="inlineStr">
@@ -4452,7 +4445,7 @@
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -4462,7 +4455,7 @@
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I52" s="9" t="inlineStr"/>
@@ -4489,7 +4482,7 @@
       </c>
       <c r="O52" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P52" s="11" t="inlineStr">
@@ -4509,7 +4502,7 @@
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WGO</t>
+          <t>Crosshair 18 Max HX B2WG</t>
         </is>
       </c>
       <c r="D53" s="18" t="inlineStr">
@@ -4534,7 +4527,7 @@
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I53" s="9" t="inlineStr"/>
@@ -4561,7 +4554,7 @@
       </c>
       <c r="O53" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P53" s="11" t="inlineStr">
@@ -4581,7 +4574,7 @@
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WGX</t>
+          <t>Crosshair 18 Max HX B2WGO</t>
         </is>
       </c>
       <c r="D54" s="18" t="inlineStr">
@@ -4606,7 +4599,7 @@
       </c>
       <c r="H54" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I54" s="9" t="inlineStr"/>
@@ -4633,7 +4626,7 @@
       </c>
       <c r="O54" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P54" s="11" t="inlineStr">
@@ -4653,7 +4646,7 @@
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WGXO</t>
+          <t>Crosshair 18 Max HX B2WGX</t>
         </is>
       </c>
       <c r="D55" s="18" t="inlineStr">
@@ -4678,7 +4671,7 @@
       </c>
       <c r="H55" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I55" s="9" t="inlineStr"/>
@@ -4705,7 +4698,7 @@
       </c>
       <c r="O55" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P55" s="11" t="inlineStr">
@@ -4725,7 +4718,7 @@
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WEK</t>
+          <t>Crosshair 18 Max HX B2WGXO</t>
         </is>
       </c>
       <c r="D56" s="18" t="inlineStr">
@@ -4740,7 +4733,7 @@
       </c>
       <c r="F56" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr">
@@ -4750,7 +4743,7 @@
       </c>
       <c r="H56" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I56" s="9" t="inlineStr"/>
@@ -4777,7 +4770,7 @@
       </c>
       <c r="O56" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P56" s="11" t="inlineStr">
@@ -4797,7 +4790,7 @@
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WEOK</t>
+          <t>Katana 18 HX A2WEK</t>
         </is>
       </c>
       <c r="D57" s="18" t="inlineStr">
@@ -4822,14 +4815,10 @@
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I57" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I57" s="9" t="inlineStr"/>
       <c r="J57" s="9" t="inlineStr"/>
       <c r="K57" s="9" t="inlineStr">
         <is>
@@ -4853,7 +4842,7 @@
       </c>
       <c r="O57" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P57" s="11" t="inlineStr">
@@ -4873,7 +4862,7 @@
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WFK</t>
+          <t>Katana 18 HX A2WEOK</t>
         </is>
       </c>
       <c r="D58" s="18" t="inlineStr">
@@ -4888,7 +4877,7 @@
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr">
@@ -4898,10 +4887,14 @@
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I58" s="9" t="inlineStr"/>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
       <c r="J58" s="9" t="inlineStr"/>
       <c r="K58" s="9" t="inlineStr">
         <is>
@@ -4925,7 +4918,7 @@
       </c>
       <c r="O58" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P58" s="11" t="inlineStr">
@@ -4945,7 +4938,7 @@
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WFOK</t>
+          <t>Katana 18 HX A2WFK</t>
         </is>
       </c>
       <c r="D59" s="18" t="inlineStr">
@@ -4970,14 +4963,10 @@
       </c>
       <c r="H59" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I59" s="9" t="inlineStr"/>
       <c r="J59" s="9" t="inlineStr"/>
       <c r="K59" s="9" t="inlineStr">
         <is>
@@ -5001,7 +4990,7 @@
       </c>
       <c r="O59" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P59" s="11" t="inlineStr">
@@ -5021,7 +5010,7 @@
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WGK</t>
+          <t>Katana 18 HX A2WFOK</t>
         </is>
       </c>
       <c r="D60" s="18" t="inlineStr">
@@ -5036,7 +5025,7 @@
       </c>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr">
@@ -5046,10 +5035,14 @@
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I60" s="9" t="inlineStr"/>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
       <c r="J60" s="9" t="inlineStr"/>
       <c r="K60" s="9" t="inlineStr">
         <is>
@@ -5073,7 +5066,7 @@
       </c>
       <c r="O60" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P60" s="11" t="inlineStr">
@@ -5093,7 +5086,7 @@
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WGOK</t>
+          <t>Katana 18 HX A2WGK</t>
         </is>
       </c>
       <c r="D61" s="18" t="inlineStr">
@@ -5118,14 +5111,10 @@
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I61" s="9" t="inlineStr"/>
       <c r="J61" s="9" t="inlineStr"/>
       <c r="K61" s="9" t="inlineStr">
         <is>
@@ -5149,484 +5138,480 @@
       </c>
       <c r="O61" s="11" t="inlineStr">
         <is>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+        </is>
+      </c>
+      <c r="P61" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" hidden="1" outlineLevel="1">
+      <c r="A62" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>Katana 18 HX A2WGOK</t>
+        </is>
+      </c>
+      <c r="D62" s="18" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>RPL-HX Next 55W</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>顧曉琴</t>
+        </is>
+      </c>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="inlineStr"/>
+      <c r="K62" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/08</t>
+        </is>
+      </c>
+      <c r="L62" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/30</t>
+        </is>
+      </c>
+      <c r="M62" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/19</t>
+        </is>
+      </c>
+      <c r="N62" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/30</t>
+        </is>
+      </c>
+      <c r="O62" s="11" t="inlineStr">
+        <is>
           <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
-      <c r="P61" s="11" t="inlineStr">
+      <c r="P62" s="11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>14T4</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>Prestige 14 AI</t>
         </is>
       </c>
-      <c r="D62" s="16" t="inlineStr">
+      <c r="D63" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E63" s="4" t="inlineStr">
         <is>
           <t>NVL-H 30W</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="F63" s="4" t="inlineStr">
         <is>
           <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="G63" s="4" t="inlineStr">
         <is>
           <t>朱芳芳</t>
         </is>
       </c>
-      <c r="H62" s="4" t="inlineStr">
+      <c r="H63" s="4" t="inlineStr">
         <is>
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="I62" s="4" t="inlineStr">
+      <c r="I63" s="4" t="inlineStr">
         <is>
           <t>2026/07/22</t>
         </is>
       </c>
-      <c r="J62" s="4" t="inlineStr">
+      <c r="J63" s="4" t="inlineStr">
         <is>
           <t>2026/09/15</t>
         </is>
       </c>
-      <c r="K62" s="4" t="inlineStr">
+      <c r="K63" s="4" t="inlineStr">
         <is>
           <t>2026/11/04</t>
         </is>
       </c>
-      <c r="L62" s="4" t="inlineStr">
+      <c r="L63" s="4" t="inlineStr">
         <is>
           <t>2026/11/20</t>
         </is>
       </c>
-      <c r="M62" s="4" t="inlineStr">
+      <c r="M63" s="4" t="inlineStr">
         <is>
           <t>2026/12/15</t>
         </is>
       </c>
-      <c r="N62" s="4" t="inlineStr">
+      <c r="N63" s="4" t="inlineStr">
         <is>
           <t>2026/12/25</t>
         </is>
       </c>
-      <c r="O62" s="6" t="inlineStr">
+      <c r="O63" s="6" t="inlineStr">
         <is>
           <t>0A gerberout ：6/26,DVT SMT@7/22</t>
         </is>
       </c>
-      <c r="P62" s="6" t="inlineStr">
+      <c r="P63" s="6" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
-    <row r="63" hidden="1" outlineLevel="1">
-      <c r="A63" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
+    <row r="64" hidden="1" outlineLevel="1">
+      <c r="A64" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>14T4</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C64" s="9" t="inlineStr">
         <is>
           <t>Prestige 14 AI+ Flip</t>
         </is>
       </c>
-      <c r="D63" s="18" t="inlineStr">
+      <c r="D64" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E63" s="9" t="inlineStr">
+      <c r="E64" s="9" t="inlineStr">
         <is>
           <t>NVL-H 30W</t>
         </is>
       </c>
-      <c r="F63" s="9" t="inlineStr">
+      <c r="F64" s="9" t="inlineStr">
         <is>
           <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
-      <c r="G63" s="9" t="inlineStr">
+      <c r="G64" s="9" t="inlineStr">
         <is>
           <t>朱芳芳</t>
         </is>
       </c>
-      <c r="H63" s="9" t="inlineStr">
+      <c r="H64" s="9" t="inlineStr">
         <is>
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="I63" s="9" t="inlineStr">
+      <c r="I64" s="9" t="inlineStr">
         <is>
           <t>2026/07/22</t>
         </is>
       </c>
-      <c r="J63" s="9" t="inlineStr">
+      <c r="J64" s="9" t="inlineStr">
         <is>
           <t>2026/09/15</t>
         </is>
       </c>
-      <c r="K63" s="9" t="inlineStr">
+      <c r="K64" s="9" t="inlineStr">
         <is>
           <t>2026/11/04</t>
         </is>
       </c>
-      <c r="L63" s="9" t="inlineStr">
+      <c r="L64" s="9" t="inlineStr">
         <is>
           <t>2026/11/20</t>
         </is>
       </c>
-      <c r="M63" s="9" t="inlineStr">
+      <c r="M64" s="9" t="inlineStr">
         <is>
           <t>2026/12/15</t>
         </is>
       </c>
-      <c r="N63" s="9" t="inlineStr">
+      <c r="N64" s="9" t="inlineStr">
         <is>
           <t>2026/12/25</t>
         </is>
       </c>
-      <c r="O63" s="11" t="inlineStr">
+      <c r="O64" s="11" t="inlineStr">
         <is>
           <t>0A gerberout ：6/26,DVT SMT@7/22</t>
         </is>
       </c>
-      <c r="P63" s="11" t="inlineStr">
+      <c r="P64" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>Prestige 16 AI+</t>
         </is>
       </c>
-      <c r="D64" s="16" t="inlineStr">
+      <c r="D65" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>NVL-H 30W</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
-      <c r="G64" s="4" t="inlineStr">
+      <c r="G65" s="4" t="inlineStr">
         <is>
           <t>朱芳芳</t>
         </is>
       </c>
-      <c r="H64" s="4" t="inlineStr">
+      <c r="H65" s="4" t="inlineStr">
         <is>
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="I64" s="4" t="inlineStr"/>
-      <c r="J64" s="4" t="inlineStr">
+      <c r="I65" s="4" t="inlineStr"/>
+      <c r="J65" s="4" t="inlineStr">
         <is>
           <t>2026/09/15</t>
         </is>
       </c>
-      <c r="K64" s="4" t="inlineStr">
+      <c r="K65" s="4" t="inlineStr">
         <is>
           <t>2026/11/04</t>
         </is>
       </c>
-      <c r="L64" s="4" t="inlineStr">
+      <c r="L65" s="4" t="inlineStr">
         <is>
           <t>2026/11/20</t>
         </is>
       </c>
-      <c r="M64" s="4" t="inlineStr">
+      <c r="M65" s="4" t="inlineStr">
         <is>
           <t>2026/12/15</t>
         </is>
       </c>
-      <c r="N64" s="4" t="inlineStr">
+      <c r="N65" s="4" t="inlineStr">
         <is>
           <t>2026/12/25</t>
         </is>
       </c>
-      <c r="O64" s="6" t="inlineStr">
+      <c r="O65" s="6" t="inlineStr">
         <is>
           <t>0A gerberout ：6/26,DVT SMT@7/22</t>
         </is>
       </c>
-      <c r="P64" s="6" t="inlineStr">
+      <c r="P65" s="6" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
-    <row r="65" hidden="1" outlineLevel="1">
-      <c r="A65" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
+    <row r="66" hidden="1" outlineLevel="1">
+      <c r="A66" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C66" s="9" t="inlineStr">
         <is>
           <t>Prestige 16 Flip AI+</t>
         </is>
       </c>
-      <c r="D65" s="18" t="inlineStr">
+      <c r="D66" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr">
+      <c r="E66" s="9" t="inlineStr">
         <is>
           <t>NVL-H 30W</t>
         </is>
       </c>
-      <c r="F65" s="9" t="inlineStr">
+      <c r="F66" s="9" t="inlineStr">
         <is>
           <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
-      <c r="G65" s="9" t="inlineStr">
+      <c r="G66" s="9" t="inlineStr">
         <is>
           <t>朱芳芳</t>
         </is>
       </c>
-      <c r="H65" s="9" t="inlineStr">
+      <c r="H66" s="9" t="inlineStr">
         <is>
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="I65" s="9" t="inlineStr"/>
-      <c r="J65" s="9" t="inlineStr">
+      <c r="I66" s="9" t="inlineStr"/>
+      <c r="J66" s="9" t="inlineStr">
         <is>
           <t>2026/09/15</t>
         </is>
       </c>
-      <c r="K65" s="9" t="inlineStr">
+      <c r="K66" s="9" t="inlineStr">
         <is>
           <t>2026/11/04</t>
         </is>
       </c>
-      <c r="L65" s="9" t="inlineStr">
+      <c r="L66" s="9" t="inlineStr">
         <is>
           <t>2026/11/20</t>
         </is>
       </c>
-      <c r="M65" s="9" t="inlineStr">
+      <c r="M66" s="9" t="inlineStr">
         <is>
           <t>2026/12/15</t>
         </is>
       </c>
-      <c r="N65" s="9" t="inlineStr">
+      <c r="N66" s="9" t="inlineStr">
         <is>
           <t>2026/12/25</t>
         </is>
       </c>
-      <c r="O65" s="11" t="inlineStr">
+      <c r="O66" s="11" t="inlineStr">
         <is>
           <t>0A gerberout ：6/26,DVT SMT@7/22</t>
         </is>
       </c>
-      <c r="P65" s="11" t="inlineStr">
+      <c r="P66" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>2633</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>Stealth 16 AI+ B4WI</t>
         </is>
       </c>
-      <c r="D66" s="16" t="inlineStr">
+      <c r="D67" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
+      <c r="F67" s="4" t="inlineStr">
         <is>
           <t>RTX 5080</t>
         </is>
       </c>
-      <c r="G66" s="4" t="inlineStr">
+      <c r="G67" s="4" t="inlineStr">
         <is>
           <t>朱欣怡</t>
         </is>
       </c>
-      <c r="H66" s="4" t="inlineStr">
+      <c r="H67" s="4" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I66" s="4" t="inlineStr">
+      <c r="I67" s="4" t="inlineStr">
         <is>
           <t>2026/07/22</t>
         </is>
       </c>
-      <c r="J66" s="4" t="inlineStr">
+      <c r="J67" s="4" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K66" s="4" t="inlineStr">
+      <c r="K67" s="4" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L66" s="4" t="inlineStr">
+      <c r="L67" s="4" t="inlineStr">
         <is>
           <t>2026/11/30</t>
         </is>
       </c>
-      <c r="M66" s="4" t="inlineStr">
+      <c r="M67" s="4" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N66" s="4" t="inlineStr">
+      <c r="N67" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O66" s="6" t="inlineStr">
+      <c r="O67" s="6" t="inlineStr">
         <is>
           <t>0M layout中，预计6/30 gerber out</t>
         </is>
       </c>
-      <c r="P66" s="6" t="inlineStr">
+      <c r="P67" s="6" t="inlineStr">
         <is>
           <t>1) Schedule:NV VBIOS @1/6, gating 8天,預計12/E 拿到WHQL，可能影響到最終TTM 時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" hidden="1" outlineLevel="1">
-      <c r="A67" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="C67" s="9" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WH</t>
-        </is>
-      </c>
-      <c r="D67" s="18" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E67" s="9" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F67" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070Ti</t>
-        </is>
-      </c>
-      <c r="G67" s="9" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H67" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I67" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/22</t>
-        </is>
-      </c>
-      <c r="J67" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K67" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L67" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/30</t>
-        </is>
-      </c>
-      <c r="M67" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N67" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="O67" s="11" t="inlineStr">
-        <is>
-          <t>0M layout中，预计6/30 gerber out</t>
-        </is>
-      </c>
-      <c r="P67" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -5641,231 +5626,230 @@
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
+          <t>Stealth 16 AI+ B4WH</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K68" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L68" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="M68" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N68" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="O68" s="11" t="inlineStr">
+        <is>
+          <t>0M layout中，预计6/30 gerber out</t>
+        </is>
+      </c>
+      <c r="P68" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" hidden="1" outlineLevel="1">
+      <c r="A69" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>2633</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
           <t>Stealth 16 AI+ B4WJ</t>
         </is>
       </c>
-      <c r="D68" s="18" t="inlineStr">
+      <c r="D69" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E68" s="9" t="inlineStr">
+      <c r="E69" s="9" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F68" s="9" t="inlineStr">
+      <c r="F69" s="9" t="inlineStr">
         <is>
           <t>RTX 5090</t>
         </is>
       </c>
-      <c r="G68" s="9" t="inlineStr">
+      <c r="G69" s="9" t="inlineStr">
         <is>
           <t>朱欣怡</t>
         </is>
       </c>
-      <c r="H68" s="9" t="inlineStr">
+      <c r="H69" s="9" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I68" s="9" t="inlineStr">
+      <c r="I69" s="9" t="inlineStr">
         <is>
           <t>2026/07/22</t>
         </is>
       </c>
-      <c r="J68" s="9" t="inlineStr">
+      <c r="J69" s="9" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K68" s="9" t="inlineStr">
+      <c r="K69" s="9" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L68" s="9" t="inlineStr">
+      <c r="L69" s="9" t="inlineStr">
         <is>
           <t>2026/11/30</t>
         </is>
       </c>
-      <c r="M68" s="9" t="inlineStr">
+      <c r="M69" s="9" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N68" s="9" t="inlineStr">
+      <c r="N69" s="9" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O68" s="11" t="inlineStr">
+      <c r="O69" s="11" t="inlineStr">
         <is>
           <t>0M layout中，预计6/30 gerber out</t>
         </is>
       </c>
-      <c r="P68" s="11" t="inlineStr">
+      <c r="P69" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>2634</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>Stealth 16 AI+ B4WE</t>
         </is>
       </c>
-      <c r="D69" s="16" t="inlineStr">
+      <c r="D70" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="F70" s="4" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G69" s="4" t="inlineStr">
+      <c r="G70" s="4" t="inlineStr">
         <is>
           <t>賴雪鳳</t>
         </is>
       </c>
-      <c r="H69" s="4" t="inlineStr">
+      <c r="H70" s="4" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I69" s="4" t="inlineStr">
+      <c r="I70" s="4" t="inlineStr">
         <is>
           <t>2026/08/07</t>
         </is>
       </c>
-      <c r="J69" s="4" t="inlineStr">
+      <c r="J70" s="4" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K69" s="4" t="inlineStr">
+      <c r="K70" s="4" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L69" s="4" t="inlineStr">
+      <c r="L70" s="4" t="inlineStr">
         <is>
           <t>2026/11/27</t>
         </is>
       </c>
-      <c r="M69" s="4" t="inlineStr">
+      <c r="M70" s="4" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N69" s="4" t="inlineStr">
+      <c r="N70" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O69" s="6" t="inlineStr">
-        <is>
-          <t>5/22 kick off ,0A layout start 6/8-7/17</t>
-        </is>
-      </c>
-      <c r="P69" s="6" t="inlineStr">
-        <is>
-          <t>1)NV VBIOS 驗證時間6周
-2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" hidden="1" outlineLevel="1">
-      <c r="A70" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WF</t>
-        </is>
-      </c>
-      <c r="D70" s="18" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E70" s="9" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F70" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G70" s="9" t="inlineStr">
-        <is>
-          <t>賴雪鳳</t>
-        </is>
-      </c>
-      <c r="H70" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I70" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="J70" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K70" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L70" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/27</t>
-        </is>
-      </c>
-      <c r="M70" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N70" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="O70" s="11" t="inlineStr">
-        <is>
-          <t>5/22 kick off ,0A layout start 6/8-7/17</t>
-        </is>
-      </c>
-      <c r="P70" s="11" t="inlineStr">
+      <c r="O70" s="6" t="inlineStr">
+        <is>
+          <t>0A layout start 6/8-7/17</t>
+        </is>
+      </c>
+      <c r="P70" s="6" t="inlineStr">
         <is>
           <t>1)NV VBIOS 驗證時間6周
 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
@@ -5883,7 +5867,7 @@
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
+          <t>Stealth 16 AI+ B4WF</t>
         </is>
       </c>
       <c r="D71" s="18" t="inlineStr">
@@ -5898,7 +5882,7 @@
       </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G71" s="9" t="inlineStr">
@@ -5943,7 +5927,7 @@
       </c>
       <c r="O71" s="11" t="inlineStr">
         <is>
-          <t>5/22 kick off ,0A layout start 6/8-7/17</t>
+          <t>0A layout start 6/8-7/17</t>
         </is>
       </c>
       <c r="P71" s="11" t="inlineStr">
@@ -5964,7 +5948,7 @@
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
+          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
         </is>
       </c>
       <c r="D72" s="18" t="inlineStr">
@@ -6024,7 +6008,7 @@
       </c>
       <c r="O72" s="11" t="inlineStr">
         <is>
-          <t>5/22 kick off ,0A layout start 6/8-7/17</t>
+          <t>0A layout start 6/8-7/17</t>
         </is>
       </c>
       <c r="P72" s="11" t="inlineStr">
@@ -6034,161 +6018,162 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="n">
+    <row r="73" hidden="1" outlineLevel="1">
+      <c r="A73" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
+        </is>
+      </c>
+      <c r="D73" s="18" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>賴雪鳳</t>
+        </is>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K73" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L73" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/27</t>
+        </is>
+      </c>
+      <c r="M73" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N73" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="O73" s="11" t="inlineStr">
+        <is>
+          <t>0A layout start 6/8-7/17</t>
+        </is>
+      </c>
+      <c r="P73" s="11" t="inlineStr">
+        <is>
+          <t>1)NV VBIOS 驗證時間6周
+2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>2654</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>Raider 16 Max HX B4WH</t>
         </is>
       </c>
-      <c r="D73" s="16" t="inlineStr">
+      <c r="D74" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F73" s="4" t="inlineStr">
+      <c r="F74" s="4" t="inlineStr">
         <is>
           <t>RTX 5070Ti</t>
         </is>
       </c>
-      <c r="G73" s="4" t="inlineStr">
+      <c r="G74" s="4" t="inlineStr">
         <is>
           <t>吳美芳</t>
         </is>
       </c>
-      <c r="H73" s="4" t="inlineStr">
+      <c r="H74" s="4" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I73" s="4" t="inlineStr">
+      <c r="I74" s="4" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J73" s="4" t="inlineStr">
+      <c r="J74" s="4" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K73" s="4" t="inlineStr">
+      <c r="K74" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L73" s="4" t="inlineStr">
+      <c r="L74" s="4" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M73" s="4" t="inlineStr">
+      <c r="M74" s="4" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N73" s="4" t="inlineStr">
+      <c r="N74" s="4" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O73" s="6" t="inlineStr">
+      <c r="O74" s="6" t="inlineStr">
         <is>
           <t>0M layout中，预计6/29 gerber out</t>
         </is>
       </c>
-      <c r="P73" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" hidden="1" outlineLevel="1">
-      <c r="A74" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>2654</t>
-        </is>
-      </c>
-      <c r="C74" s="9" t="inlineStr">
-        <is>
-          <t>Raider 16 Max HX B4WI</t>
-        </is>
-      </c>
-      <c r="D74" s="18" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E74" s="9" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F74" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5080</t>
-        </is>
-      </c>
-      <c r="G74" s="9" t="inlineStr">
-        <is>
-          <t>吳美芳</t>
-        </is>
-      </c>
-      <c r="H74" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I74" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J74" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K74" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L74" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M74" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N74" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O74" s="11" t="inlineStr">
-        <is>
-          <t>0M layout中,预计6/29 gerber out</t>
-        </is>
-      </c>
-      <c r="P74" s="11" t="inlineStr">
+      <c r="P74" s="6" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -6205,7 +6190,7 @@
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B4WJ</t>
+          <t>Raider 16 Max HX B4WI</t>
         </is>
       </c>
       <c r="D75" s="18" t="inlineStr">
@@ -6220,7 +6205,7 @@
       </c>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="G75" s="9" t="inlineStr">
@@ -6285,7 +6270,7 @@
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WH</t>
+          <t>Raider 16 Max HX B4WJ</t>
         </is>
       </c>
       <c r="D76" s="18" t="inlineStr">
@@ -6300,7 +6285,7 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="G76" s="9" t="inlineStr">
@@ -6345,7 +6330,7 @@
       </c>
       <c r="O76" s="11" t="inlineStr">
         <is>
-          <t>0M layout中，预计6/29 gerber out</t>
+          <t>0M layout中,预计6/29 gerber out</t>
         </is>
       </c>
       <c r="P76" s="11" t="inlineStr">
@@ -6365,232 +6350,232 @@
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
+          <t>Raider 16  HX B4WH</t>
+        </is>
+      </c>
+      <c r="D77" s="18" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>吳美芳</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K77" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="L77" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M77" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N77" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O77" s="11" t="inlineStr">
+        <is>
+          <t>0M layout中，预计6/29 gerber out</t>
+        </is>
+      </c>
+      <c r="P77" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" hidden="1" outlineLevel="1">
+      <c r="A78" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>2654</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
           <t>Raider 16  HX B4WI</t>
         </is>
       </c>
-      <c r="D77" s="18" t="inlineStr">
+      <c r="D78" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E77" s="9" t="inlineStr">
+      <c r="E78" s="9" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F77" s="9" t="inlineStr">
+      <c r="F78" s="9" t="inlineStr">
         <is>
           <t>RTX 5080</t>
         </is>
       </c>
-      <c r="G77" s="9" t="inlineStr">
+      <c r="G78" s="9" t="inlineStr">
         <is>
           <t>吳美芳</t>
         </is>
       </c>
-      <c r="H77" s="9" t="inlineStr">
+      <c r="H78" s="9" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I77" s="9" t="inlineStr">
+      <c r="I78" s="9" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J77" s="9" t="inlineStr">
+      <c r="J78" s="9" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K77" s="9" t="inlineStr">
+      <c r="K78" s="9" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L77" s="9" t="inlineStr">
+      <c r="L78" s="9" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M77" s="9" t="inlineStr">
+      <c r="M78" s="9" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N77" s="9" t="inlineStr">
+      <c r="N78" s="9" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O77" s="11" t="inlineStr">
+      <c r="O78" s="11" t="inlineStr">
         <is>
           <t>0M layout中，预计6/29 gerber out</t>
         </is>
       </c>
-      <c r="P77" s="11" t="inlineStr">
+      <c r="P78" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>2655</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>Crosshair 16 Max HX E4WEK</t>
         </is>
       </c>
-      <c r="D78" s="16" t="inlineStr">
+      <c r="D79" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G78" s="4" t="inlineStr">
+      <c r="G79" s="4" t="inlineStr">
         <is>
           <t>鮑佩佩</t>
         </is>
       </c>
-      <c r="H78" s="4" t="inlineStr">
+      <c r="H79" s="4" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I78" s="4" t="inlineStr">
+      <c r="I79" s="4" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J78" s="4" t="inlineStr">
+      <c r="J79" s="4" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K78" s="4" t="inlineStr">
+      <c r="K79" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L78" s="4" t="inlineStr">
+      <c r="L79" s="4" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M78" s="4" t="inlineStr">
+      <c r="M79" s="4" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N78" s="4" t="inlineStr">
+      <c r="N79" s="4" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O78" s="6" t="inlineStr">
-        <is>
-          <t>0A layout中，plan 6/29 gerber out</t>
-        </is>
-      </c>
-      <c r="P78" s="6" t="inlineStr">
-        <is>
-          <t>Spec change: I/O  TypeC 由1*TBT4+ 1*alt mode改為2*TBT4,對0A gerber out 影響TBD,對TTM 無影響</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" hidden="1" outlineLevel="1">
-      <c r="A79" s="7" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>2655</t>
-        </is>
-      </c>
-      <c r="C79" s="9" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WFK</t>
-        </is>
-      </c>
-      <c r="D79" s="18" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E79" s="9" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F79" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G79" s="9" t="inlineStr">
-        <is>
-          <t>鮑佩佩</t>
-        </is>
-      </c>
-      <c r="H79" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I79" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J79" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K79" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L79" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M79" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N79" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O79" s="11" t="inlineStr">
-        <is>
-          <t>0A layout中，plan 6/29 gerber out</t>
-        </is>
-      </c>
-      <c r="P79" s="11" t="inlineStr">
-        <is>
-          <t>Spec change: I/O  TypeC 由1*TBT4+ 1*alt mode改為2*TBT4,對0A gerber out 影響TBD,對TTM 無影響</t>
+      <c r="O79" s="6" t="inlineStr">
+        <is>
+          <t>0A layout中</t>
+        </is>
+      </c>
+      <c r="P79" s="6" t="inlineStr">
+        <is>
+          <t>plan 7/3 gerber out，比預期 delay 4d,對後續schedule無影響</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6590,7 @@
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 16 Max HX E4WGK</t>
+          <t>Crosshair 16 Max HX E4WFK</t>
         </is>
       </c>
       <c r="D80" s="18" t="inlineStr">
@@ -6620,7 +6605,7 @@
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G80" s="9" t="inlineStr">
@@ -6665,12 +6650,12 @@
       </c>
       <c r="O80" s="11" t="inlineStr">
         <is>
-          <t>GN22-X6 8GB SKU,0A layout中，plan 6/29 gerber out</t>
+          <t>0A layout中</t>
         </is>
       </c>
       <c r="P80" s="11" t="inlineStr">
         <is>
-          <t>Spec change: I/O  TypeC 由1*TBT4+ 1*alt mode改為2*TBT4,對0A gerber out 影響TBD,對TTM 無影響</t>
+          <t>plan 7/3 gerber out，比預期 delay 4d,對後續schedule無影響</t>
         </is>
       </c>
     </row>
@@ -6685,77 +6670,157 @@
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
+          <t>Crosshair 16 Max HX E4WGK</t>
+        </is>
+      </c>
+      <c r="D81" s="18" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>鮑佩佩</t>
+        </is>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K81" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="L81" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M81" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N81" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O81" s="11" t="inlineStr">
+        <is>
+          <t>GN22-X6 8GB SKU,0A layout中</t>
+        </is>
+      </c>
+      <c r="P81" s="11" t="inlineStr">
+        <is>
+          <t>plan 7/3 gerber out，比預期 delay 4d,對後續schedule無影響</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" hidden="1" outlineLevel="1">
+      <c r="A82" s="7" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>2655</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
           <t>Crosshair 16 Max HX E4WGXK</t>
         </is>
       </c>
-      <c r="D81" s="18" t="inlineStr">
+      <c r="D82" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E81" s="9" t="inlineStr">
+      <c r="E82" s="9" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F81" s="9" t="inlineStr">
+      <c r="F82" s="9" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G81" s="9" t="inlineStr">
+      <c r="G82" s="9" t="inlineStr">
         <is>
           <t>鮑佩佩</t>
         </is>
       </c>
-      <c r="H81" s="9" t="inlineStr">
+      <c r="H82" s="9" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I81" s="9" t="inlineStr">
+      <c r="I82" s="9" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J81" s="9" t="inlineStr">
+      <c r="J82" s="9" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K81" s="9" t="inlineStr">
+      <c r="K82" s="9" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L81" s="9" t="inlineStr">
+      <c r="L82" s="9" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M81" s="9" t="inlineStr">
+      <c r="M82" s="9" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N81" s="9" t="inlineStr">
+      <c r="N82" s="9" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O81" s="11" t="inlineStr">
-        <is>
-          <t>GN22-X6 12GB SKU, 0A layout中，plan 6/29 gerber out</t>
-        </is>
-      </c>
-      <c r="P81" s="11" t="inlineStr">
-        <is>
-          <t>Spec change: I/O  TypeC 由1*TBT4+ 1*alt mode改為2*TBT4,對0A gerber out 影響TBD,對TTM 無影響</t>
+      <c r="O82" s="11" t="inlineStr">
+        <is>
+          <t>GN22-X6 12GB SKU, 0A layout中</t>
+        </is>
+      </c>
+      <c r="P82" s="11" t="inlineStr">
+        <is>
+          <t>plan 7/3 gerber out，比預期 delay 4d,對後續schedule無影響</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P81"/>
+  <autoFilter ref="A1:P82"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/npi_dashboard.xlsx
+++ b/npi_dashboard.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPI Dashboard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,7 +519,7 @@
     <outlinePr summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P82"/>
+  <dimension ref="A1:P83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -628,12 +628,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>14V2</t>
+          <t>14T2</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Commercial 14 C13M</t>
+          <t>Prestige 14 Flip AI+ Rhône</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -643,54 +643,54 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>RPL-U 25W</t>
+          <t>PTL-H 30W</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Intel® graphics</t>
+          <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>朱芳芳</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>2026/01/04</t>
+          <t>2026/04/13</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr"/>
       <c r="J2" s="4" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>2026/02/05</t>
+          <t>2026/05/10</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>2026/03/16</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>2026/05/15</t>
+          <t>2026/06/23</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>2026/05/30</t>
+          <t>2026/06/30</t>
         </is>
       </c>
       <c r="O2" s="6" t="inlineStr">
         <is>
-          <t>因PCB 最快交期落在6/29,加上微步盤點，預計最快7/10 TTM</t>
+          <t>梵谷特仕版 物料持續追踪，6/23 ATS CR，6/E出貨</t>
         </is>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1. ALS sensor NG  HDI 進版 6/27重工， 1.A件成品LOGO不良較高，交料瓶頸 請ID&amp;Buyer持續pull in。</t>
         </is>
       </c>
     </row>
@@ -700,12 +700,12 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>14V2</t>
+          <t>14T2</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Modern 14 H13M</t>
+          <t>Prestige 14 Flip AI+ Starry Night</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -715,54 +715,54 @@
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>RPL-U 25W</t>
+          <t>PTL-H 30W</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>Intel® graphics</t>
+          <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>朱芳芳</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>2025/11/14</t>
+          <t>2026/04/13</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr"/>
       <c r="J3" s="9" t="inlineStr"/>
       <c r="K3" s="9" t="inlineStr">
         <is>
-          <t>2026/01/14</t>
+          <t>2026/05/10</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
         <is>
-          <t>2026/03/16</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>2026/05/15</t>
+          <t>2026/06/23</t>
         </is>
       </c>
       <c r="N3" s="9" t="inlineStr">
         <is>
-          <t>2026/05/30</t>
+          <t>2026/06/30</t>
         </is>
       </c>
       <c r="O3" s="11" t="inlineStr">
         <is>
-          <t>因PCB 最快交期落在6/29,加上微步盤點，預計最快7/10 TTM</t>
+          <t>梵谷特仕版 物料持續追踪，規劃6/23 ATS CR，6/E出貨</t>
         </is>
       </c>
       <c r="P3" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1. ALS sensor NG  HDI 進版 6/27重工， 2.A件成品LOGO不良較高，交料瓶頸 請ID&amp;Buyer持續pull in。</t>
         </is>
       </c>
     </row>
@@ -772,69 +772,71 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>14T2</t>
+          <t>265L</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Prestige 14 Flip AI+ Rhône</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>ATS</t>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>MVT</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>PTL-H 30W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Intel® Arc™ Graphics</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>朱芳芳</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>2026/04/13</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr"/>
       <c r="J4" s="4" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2026/05/10</t>
+          <t>2026/06/02</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/05/26</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>2026/06/23</t>
+          <t>2026/07/03</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>2026/06/30</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>梵谷特仕版 物料持續追踪，6/23 ATS CR，6/E出貨</t>
+          <t>MLG(魔龍姬)ID: DQA 測試中</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>1. ALS sensor NG  HDI 進版 6/27重工， 1.A件成品LOGO不良較高，交料瓶頸 請ID&amp;Buyer持續pull in。</t>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；
+2) Packing: WW版本設計確認中;
+3) Schedule: 生管排程, ATS 由7/1更新為7/3. MP @7/10</t>
         </is>
       </c>
     </row>
@@ -844,143 +846,141 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>14T2</t>
+          <t>265L</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Prestige 14 Flip AI+ Starry Night</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>ATS</t>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>MVT</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>PTL-H 30W</t>
+          <t>DRG-HX 55W</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Intel® Arc™ Graphics</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>朱芳芳</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>2026/04/13</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr"/>
       <c r="J5" s="9" t="inlineStr"/>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>2026/05/10</t>
+          <t>2026/06/02</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/05/26</t>
         </is>
       </c>
       <c r="M5" s="9" t="inlineStr">
         <is>
-          <t>2026/06/23</t>
+          <t>2026/07/03</t>
         </is>
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>2026/06/30</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="O5" s="11" t="inlineStr">
         <is>
-          <t>梵谷特仕版 物料持續追踪，規劃6/23 ATS CR，6/E出貨</t>
+          <t>MLG(魔龍姬)ID: DQA 測試中</t>
         </is>
       </c>
       <c r="P5" s="11" t="inlineStr">
         <is>
-          <t>1. ALS sensor NG  HDI 進版 6/27重工， 2.A件成品LOGO不良較高，交料瓶頸 請ID&amp;Buyer持續pull in。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" hidden="1" outlineLevel="1">
+      <c r="A6" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>265L</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>DRG-HX 55W</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>朱欣怡</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr"/>
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>2026/06/02</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>2026/05/26</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>2026/07/03</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" s="9" t="inlineStr">
         <is>
           <t>2026/07/10</t>
         </is>
       </c>
-      <c r="O6" s="6" t="inlineStr">
-        <is>
-          <t>MLG(魔龍姬)ID: DQA 測試中</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；
-2) Packing: WW版本設計確認中;
-3) Schedule: 生管排程, ATS 由7/1更新為7/3. MP @7/10</t>
+      <c r="O6" s="11" t="inlineStr">
+        <is>
+          <t>MLG(魔龍姬)ID:  DQA 測試中</t>
+        </is>
+      </c>
+      <c r="P6" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+          <t>Crosshair A16 HX MLG Edition E8WGXK</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="O7" s="11" t="inlineStr">
         <is>
-          <t>MLG(魔龍姬)ID: DQA 測試中</t>
+          <t>MLG(魔龍姬)ID:  DQA 測試中</t>
         </is>
       </c>
       <c r="P7" s="11" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
@@ -1077,12 +1077,12 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -1092,34 +1092,34 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2025/10/22</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr"/>
       <c r="J8" s="9" t="inlineStr"/>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>2026/06/02</t>
+          <t>2026/05/18</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>2026/05/26</t>
+          <t>2026/06/16</t>
         </is>
       </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
-          <t>2026/07/03</t>
+          <t>2026/07/16</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
-          <t>2026/07/10</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="O8" s="11" t="inlineStr">
         <is>
-          <t>MLG(魔龍姬)ID:  DQA 測試中</t>
+          <t>FRG (5/4通知resume）: DQA 測試中</t>
         </is>
       </c>
       <c r="P8" s="11" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX MLG Edition E8WGXK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>DRG-HX 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
@@ -1164,34 +1164,34 @@
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2025/10/22</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr"/>
       <c r="J9" s="9" t="inlineStr"/>
       <c r="K9" s="9" t="inlineStr">
         <is>
-          <t>2026/06/02</t>
+          <t>2026/05/18</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>2026/05/26</t>
+          <t>2026/06/16</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
-          <t>2026/07/03</t>
+          <t>2026/07/16</t>
         </is>
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>2026/07/10</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="O9" s="11" t="inlineStr">
         <is>
-          <t>MLG(魔龍姬)ID:  DQA 測試中</t>
+          <t>FRG (5/4通知resume）: DQA 測試中</t>
         </is>
       </c>
       <c r="P9" s="11" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E9WGXK</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
@@ -1272,75 +1272,75 @@
         </is>
       </c>
     </row>
-    <row r="11" hidden="1" outlineLevel="1">
-      <c r="A11" s="7" t="n">
+    <row r="11">
+      <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>265L</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Crosshair A16 HX E9WFK</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>FRG-HX 55W</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="I11" s="9" t="inlineStr"/>
-      <c r="J11" s="9" t="inlineStr"/>
-      <c r="K11" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/18</t>
-        </is>
-      </c>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/16</t>
-        </is>
-      </c>
-      <c r="M11" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/16</t>
-        </is>
-      </c>
-      <c r="N11" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
-      <c r="O11" s="11" t="inlineStr">
-        <is>
-          <t>FRG (5/4通知resume）: DQA 測試中</t>
-        </is>
-      </c>
-      <c r="P11" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>14V2</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Commercial 14 C13M</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>RPL-U 25W</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Intel® graphics</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>2026/01/04</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>2026/02/05</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>2026/03/16</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/10</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t>因首批安排RPL-U Refresh 優先投產，第二波投產因PCB 最快交期落在6/29,加上微步盤點，預計最快7/10 TTM</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1350,69 +1350,69 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>265L</t>
+          <t>14V2</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WGXK</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>MVT</t>
+          <t>Modern 14 H13M</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>ATS</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>RPL-U 25W</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>Intel® graphics</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>杜晨光</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/11/14</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr"/>
       <c r="J12" s="9" t="inlineStr"/>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>2026/05/18</t>
+          <t>2026/01/14</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>2026/06/16</t>
+          <t>2026/03/16</t>
         </is>
       </c>
       <c r="M12" s="9" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/06</t>
         </is>
       </c>
       <c r="N12" s="9" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/07/10</t>
         </is>
       </c>
       <c r="O12" s="11" t="inlineStr">
         <is>
-          <t>FRG (5/4通知resume）: DQA 測試中</t>
+          <t>因首批安排RPL-U Refresh 優先投產，第二波投產因PCB 最快交期落在6/29,加上微步盤點，預計最快7/10 TTM</t>
         </is>
       </c>
       <c r="P12" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
-          <t>HPT sku:RD已重工3台成APU 180且刷16RK的BIOS可開機進OS,需AMD/AMI 儘速release PI code 1200i進行測試</t>
+          <t>HPT sku:RD已重工3台成APU 180,AMI release PI 1200i RC3@6/29,BIOS RD需儘速提供MSI版本BIOSi進行測試</t>
         </is>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>1).Schedule:APU 155優先ATS,採購已下單6.5k,以 8 月底 MP為目標,其餘APU sku在9月進行ATS C/R,但PI code 1200i release延至6/30與APU 155 PR樣品ETD 延至7/11,已影響 MP 時程,待收到PI code與PR樣品後將依實際測試情況確認是否調整MP時程
+          <t>1).Schedule:APU 155優先ATS,採購已下單6.5k,以 8 月底 MP為目標,其餘APU sku在9月進行ATS C/R,但AMD PI 1200i NDA release延至6/30與APU 155 PR樣品ETD 延至7/11,已影響 MP 時程,待收到PI code與PR樣品後將依實際測試情況確認是否調整MP時程
 2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
@@ -2632,12 +2632,12 @@
       </c>
       <c r="O28" s="11" t="inlineStr">
         <is>
-          <t>HPT sku:RD已重工3台成APU 180且刷16RK的BIOS可開機進OS,需AMD/AMI 儘速release PI code 1200i進行測試</t>
+          <t>HPT sku:RD已重工3台成APU 180,AMI release PI 1200i RC3@6/29,BIOS RD需儘速提供MSI版本BIOSi進行測試</t>
         </is>
       </c>
       <c r="P28" s="11" t="inlineStr">
         <is>
-          <t>1).Schedule:APU 155優先ATS,採購已下單6.5k,以 8 月底 MP為目標,其餘APU sku在9月進行ATS C/R,但PI code 1200i release延至6/30與APU 155 PR樣品ETD 延至7/11,已影響 MP 時程,待收到PI code與PR樣品後將依實際測試情況確認是否調整MP時程
+          <t>1).Schedule:APU 155優先ATS,採購已下單6.5k,以 8 月底 MP為目標,其餘APU sku在9月進行ATS C/R,但AMD PI 1200i NDA release延至6/30與APU 155 PR樣品ETD 延至7/11,已影響 MP 時程,待收到PI code與PR樣品後將依實際測試情況確認是否調整MP時程
 2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>HPT sku:RD已重工3台成APU 180且刷16RK的BIOS可開機進OS,需AMD/AMI 儘速release PI code 1200i進行測試</t>
+          <t>HPT sku:RD已重工3台成APU 180,AMI release PI 1200i RC3@6/29,BIOS RD需儘速提供MSI版本BIOSi進行測試</t>
         </is>
       </c>
       <c r="P29" s="11" t="inlineStr">
         <is>
-          <t>1).Schedule:APU 155優先ATS,採購已下單6.5k,以 8 月底 MP為目標,其餘APU sku在9月進行ATS C/R,但PI code 1200i release延至6/30與APU 155 PR樣品ETD 延至7/11,已影響 MP 時程,待收到PI code與PR樣品後將依實際測試情況確認是否調整MP時程
+          <t>1).Schedule:APU 155優先ATS,採購已下單6.5k,以 8 月底 MP為目標,其餘APU sku在9月進行ATS C/R,但AMD PI 1200i NDA release延至6/30與APU 155 PR樣品ETD 延至7/11,已影響 MP 時程,待收到PI code與PR樣品後將依實際測試情況確認是否調整MP時程
 2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
@@ -2786,12 +2786,12 @@
       </c>
       <c r="O30" s="11" t="inlineStr">
         <is>
-          <t>HPT sku:RD已重工3台成APU 180且刷16RK的BIOS可開機進OS,需AMD/AMI 儘速release PI code 1200i進行測試</t>
+          <t>HPT sku:RD已重工3台成APU 180,AMI release PI 1200i RC3@6/29,BIOS RD需儘速提供MSI版本BIOSi進行測試</t>
         </is>
       </c>
       <c r="P30" s="11" t="inlineStr">
         <is>
-          <t>1).Schedule:APU 155優先ATS,採購已下單6.5k,以 8 月底 MP為目標,其餘APU sku在9月進行ATS C/R,但PI code 1200i release延至6/30與APU 155 PR樣品ETD 延至7/11,已影響 MP 時程,待收到PI code與PR樣品後將依實際測試情況確認是否調整MP時程
+          <t>1).Schedule:APU 155優先ATS,採購已下單6.5k,以 8 月底 MP為目標,其餘APU sku在9月進行ATS C/R,但AMD PI 1200i NDA release延至6/30與APU 155 PR樣品ETD 延至7/11,已影響 MP 時程,待收到PI code與PR樣品後將依實際測試情況確認是否調整MP時程
 2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
@@ -5541,157 +5541,149 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
+          <t>13Q5</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Prestige 13 AI+ A4M</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>NVL-H 28W</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>顏春梅</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/08</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/21</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/22</t>
+        </is>
+      </c>
+      <c r="M67" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/22</t>
+        </is>
+      </c>
+      <c r="N67" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/31</t>
+        </is>
+      </c>
+      <c r="O67" s="6" t="inlineStr"/>
+      <c r="P67" s="6" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
           <t>2633</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>Stealth 16 AI+ B4WI</t>
         </is>
       </c>
-      <c r="D67" s="14" t="inlineStr">
+      <c r="D68" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="E68" s="4" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="F68" s="4" t="inlineStr">
         <is>
           <t>RTX 5080</t>
         </is>
       </c>
-      <c r="G67" s="4" t="inlineStr">
+      <c r="G68" s="4" t="inlineStr">
         <is>
           <t>朱欣怡</t>
         </is>
       </c>
-      <c r="H67" s="4" t="inlineStr">
+      <c r="H68" s="4" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I67" s="4" t="inlineStr">
+      <c r="I68" s="4" t="inlineStr">
         <is>
           <t>2026/07/22</t>
         </is>
       </c>
-      <c r="J67" s="4" t="inlineStr">
+      <c r="J68" s="4" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K67" s="4" t="inlineStr">
+      <c r="K68" s="4" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L67" s="4" t="inlineStr">
+      <c r="L68" s="4" t="inlineStr">
         <is>
           <t>2026/11/30</t>
         </is>
       </c>
-      <c r="M67" s="4" t="inlineStr">
+      <c r="M68" s="4" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N67" s="4" t="inlineStr">
+      <c r="N68" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O67" s="6" t="inlineStr">
+      <c r="O68" s="6" t="inlineStr">
         <is>
           <t>0M layout中，预计6/30 gerber out</t>
         </is>
       </c>
-      <c r="P67" s="6" t="inlineStr">
+      <c r="P68" s="6" t="inlineStr">
         <is>
           <t>1) Schedule:NV VBIOS @1/6, gating 8天,預計12/E 拿到WHQL，可能影響到最終TTM 時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" hidden="1" outlineLevel="1">
-      <c r="A68" s="7" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="C68" s="9" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WH</t>
-        </is>
-      </c>
-      <c r="D68" s="18" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E68" s="9" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F68" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070Ti</t>
-        </is>
-      </c>
-      <c r="G68" s="9" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H68" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I68" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/22</t>
-        </is>
-      </c>
-      <c r="J68" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K68" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L68" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/30</t>
-        </is>
-      </c>
-      <c r="M68" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N68" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="O68" s="11" t="inlineStr">
-        <is>
-          <t>0M layout中，预计6/30 gerber out</t>
-        </is>
-      </c>
-      <c r="P68" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -5706,231 +5698,230 @@
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
+          <t>Stealth 16 AI+ B4WH</t>
+        </is>
+      </c>
+      <c r="D69" s="18" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K69" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L69" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="M69" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N69" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="O69" s="11" t="inlineStr">
+        <is>
+          <t>0M layout中，预计6/30 gerber out</t>
+        </is>
+      </c>
+      <c r="P69" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" hidden="1" outlineLevel="1">
+      <c r="A70" s="7" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>2633</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
           <t>Stealth 16 AI+ B4WJ</t>
         </is>
       </c>
-      <c r="D69" s="18" t="inlineStr">
+      <c r="D70" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E69" s="9" t="inlineStr">
+      <c r="E70" s="9" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F69" s="9" t="inlineStr">
+      <c r="F70" s="9" t="inlineStr">
         <is>
           <t>RTX 5090</t>
         </is>
       </c>
-      <c r="G69" s="9" t="inlineStr">
+      <c r="G70" s="9" t="inlineStr">
         <is>
           <t>朱欣怡</t>
         </is>
       </c>
-      <c r="H69" s="9" t="inlineStr">
+      <c r="H70" s="9" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I69" s="9" t="inlineStr">
+      <c r="I70" s="9" t="inlineStr">
         <is>
           <t>2026/07/22</t>
         </is>
       </c>
-      <c r="J69" s="9" t="inlineStr">
+      <c r="J70" s="9" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K69" s="9" t="inlineStr">
+      <c r="K70" s="9" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L69" s="9" t="inlineStr">
+      <c r="L70" s="9" t="inlineStr">
         <is>
           <t>2026/11/30</t>
         </is>
       </c>
-      <c r="M69" s="9" t="inlineStr">
+      <c r="M70" s="9" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N69" s="9" t="inlineStr">
+      <c r="N70" s="9" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O69" s="11" t="inlineStr">
+      <c r="O70" s="11" t="inlineStr">
         <is>
           <t>0M layout中，预计6/30 gerber out</t>
         </is>
       </c>
-      <c r="P69" s="11" t="inlineStr">
+      <c r="P70" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>2634</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>Stealth 16 AI+ B4WE</t>
         </is>
       </c>
-      <c r="D70" s="14" t="inlineStr">
+      <c r="D71" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="E71" s="4" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="F71" s="4" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G70" s="4" t="inlineStr">
+      <c r="G71" s="4" t="inlineStr">
         <is>
           <t>賴雪鳳</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
+      <c r="H71" s="4" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I70" s="4" t="inlineStr">
+      <c r="I71" s="4" t="inlineStr">
         <is>
           <t>2026/08/07</t>
         </is>
       </c>
-      <c r="J70" s="4" t="inlineStr">
+      <c r="J71" s="4" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K70" s="4" t="inlineStr">
+      <c r="K71" s="4" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L70" s="4" t="inlineStr">
+      <c r="L71" s="4" t="inlineStr">
         <is>
           <t>2026/11/27</t>
         </is>
       </c>
-      <c r="M70" s="4" t="inlineStr">
+      <c r="M71" s="4" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N70" s="4" t="inlineStr">
+      <c r="N71" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O70" s="6" t="inlineStr">
+      <c r="O71" s="6" t="inlineStr">
         <is>
           <t>0A layout start 6/8-7/17</t>
         </is>
       </c>
-      <c r="P70" s="6" t="inlineStr">
-        <is>
-          <t>1)NV VBIOS 驗證時間6周
-2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" hidden="1" outlineLevel="1">
-      <c r="A71" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WF</t>
-        </is>
-      </c>
-      <c r="D71" s="18" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F71" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G71" s="9" t="inlineStr">
-        <is>
-          <t>賴雪鳳</t>
-        </is>
-      </c>
-      <c r="H71" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="J71" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K71" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L71" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/27</t>
-        </is>
-      </c>
-      <c r="M71" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N71" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="O71" s="11" t="inlineStr">
-        <is>
-          <t>0A layout start 6/8-7/17</t>
-        </is>
-      </c>
-      <c r="P71" s="11" t="inlineStr">
+      <c r="P71" s="6" t="inlineStr">
         <is>
           <t>1)NV VBIOS 驗證時間6周
 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
@@ -5948,7 +5939,7 @@
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
+          <t>Stealth 16 AI+ B4WF</t>
         </is>
       </c>
       <c r="D72" s="18" t="inlineStr">
@@ -5963,7 +5954,7 @@
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G72" s="9" t="inlineStr">
@@ -6029,7 +6020,7 @@
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
+          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
         </is>
       </c>
       <c r="D73" s="18" t="inlineStr">
@@ -6099,161 +6090,162 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="n">
+    <row r="74" hidden="1" outlineLevel="1">
+      <c r="A74" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
+        </is>
+      </c>
+      <c r="D74" s="18" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>賴雪鳳</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K74" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L74" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/27</t>
+        </is>
+      </c>
+      <c r="M74" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N74" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="O74" s="11" t="inlineStr">
+        <is>
+          <t>0A layout start 6/8-7/17</t>
+        </is>
+      </c>
+      <c r="P74" s="11" t="inlineStr">
+        <is>
+          <t>1)NV VBIOS 驗證時間6周
+2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>2654</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>Raider 16 Max HX B4WH</t>
         </is>
       </c>
-      <c r="D74" s="14" t="inlineStr">
+      <c r="D75" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr">
+      <c r="F75" s="4" t="inlineStr">
         <is>
           <t>RTX 5070Ti</t>
         </is>
       </c>
-      <c r="G74" s="4" t="inlineStr">
+      <c r="G75" s="4" t="inlineStr">
         <is>
           <t>吳美芳</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
+      <c r="H75" s="4" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I74" s="4" t="inlineStr">
+      <c r="I75" s="4" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J74" s="4" t="inlineStr">
+      <c r="J75" s="4" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K74" s="4" t="inlineStr">
+      <c r="K75" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L74" s="4" t="inlineStr">
+      <c r="L75" s="4" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M74" s="4" t="inlineStr">
+      <c r="M75" s="4" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N74" s="4" t="inlineStr">
+      <c r="N75" s="4" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O74" s="6" t="inlineStr">
+      <c r="O75" s="6" t="inlineStr">
         <is>
           <t>0M layout中，预计6/29 gerber out</t>
         </is>
       </c>
-      <c r="P74" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" hidden="1" outlineLevel="1">
-      <c r="A75" s="7" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>2654</t>
-        </is>
-      </c>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>Raider 16 Max HX B4WI</t>
-        </is>
-      </c>
-      <c r="D75" s="18" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F75" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5080</t>
-        </is>
-      </c>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>吳美芳</t>
-        </is>
-      </c>
-      <c r="H75" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J75" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K75" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L75" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M75" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N75" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O75" s="11" t="inlineStr">
-        <is>
-          <t>0M layout中,预计6/29 gerber out</t>
-        </is>
-      </c>
-      <c r="P75" s="11" t="inlineStr">
+      <c r="P75" s="6" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -6270,7 +6262,7 @@
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B4WJ</t>
+          <t>Raider 16 Max HX B4WI</t>
         </is>
       </c>
       <c r="D76" s="18" t="inlineStr">
@@ -6285,7 +6277,7 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="G76" s="9" t="inlineStr">
@@ -6350,7 +6342,7 @@
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WH</t>
+          <t>Raider 16 Max HX B4WJ</t>
         </is>
       </c>
       <c r="D77" s="18" t="inlineStr">
@@ -6365,7 +6357,7 @@
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="G77" s="9" t="inlineStr">
@@ -6410,7 +6402,7 @@
       </c>
       <c r="O77" s="11" t="inlineStr">
         <is>
-          <t>0M layout中，预计6/29 gerber out</t>
+          <t>0M layout中,预计6/29 gerber out</t>
         </is>
       </c>
       <c r="P77" s="11" t="inlineStr">
@@ -6430,230 +6422,230 @@
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
+          <t>Raider 16  HX B4WH</t>
+        </is>
+      </c>
+      <c r="D78" s="18" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>吳美芳</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K78" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="L78" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M78" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N78" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O78" s="11" t="inlineStr">
+        <is>
+          <t>0M layout中，预计6/29 gerber out</t>
+        </is>
+      </c>
+      <c r="P78" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" hidden="1" outlineLevel="1">
+      <c r="A79" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>2654</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
           <t>Raider 16  HX B4WI</t>
         </is>
       </c>
-      <c r="D78" s="18" t="inlineStr">
+      <c r="D79" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E78" s="9" t="inlineStr">
+      <c r="E79" s="9" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F78" s="9" t="inlineStr">
+      <c r="F79" s="9" t="inlineStr">
         <is>
           <t>RTX 5080</t>
         </is>
       </c>
-      <c r="G78" s="9" t="inlineStr">
+      <c r="G79" s="9" t="inlineStr">
         <is>
           <t>吳美芳</t>
         </is>
       </c>
-      <c r="H78" s="9" t="inlineStr">
+      <c r="H79" s="9" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I78" s="9" t="inlineStr">
+      <c r="I79" s="9" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J78" s="9" t="inlineStr">
+      <c r="J79" s="9" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K78" s="9" t="inlineStr">
+      <c r="K79" s="9" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L78" s="9" t="inlineStr">
+      <c r="L79" s="9" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M78" s="9" t="inlineStr">
+      <c r="M79" s="9" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N78" s="9" t="inlineStr">
+      <c r="N79" s="9" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O78" s="11" t="inlineStr">
+      <c r="O79" s="11" t="inlineStr">
         <is>
           <t>0M layout中，预计6/29 gerber out</t>
         </is>
       </c>
-      <c r="P78" s="11" t="inlineStr">
+      <c r="P79" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>2655</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>Crosshair 16 Max HX E4WEK</t>
         </is>
       </c>
-      <c r="D79" s="14" t="inlineStr">
+      <c r="D80" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="E80" s="4" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="F80" s="4" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G79" s="4" t="inlineStr">
+      <c r="G80" s="4" t="inlineStr">
         <is>
           <t>鮑佩佩</t>
         </is>
       </c>
-      <c r="H79" s="4" t="inlineStr">
+      <c r="H80" s="4" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I79" s="4" t="inlineStr">
+      <c r="I80" s="4" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J79" s="4" t="inlineStr">
+      <c r="J80" s="4" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K79" s="4" t="inlineStr">
+      <c r="K80" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L79" s="4" t="inlineStr">
+      <c r="L80" s="4" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M79" s="4" t="inlineStr">
+      <c r="M80" s="4" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N79" s="4" t="inlineStr">
+      <c r="N80" s="4" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O79" s="6" t="inlineStr">
+      <c r="O80" s="6" t="inlineStr">
         <is>
           <t>0A layout中</t>
         </is>
       </c>
-      <c r="P79" s="6" t="inlineStr">
-        <is>
-          <t>plan 7/3 gerber out，比預期 delay 4d,對後續schedule無影響</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" hidden="1" outlineLevel="1">
-      <c r="A80" s="7" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>2655</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WFK</t>
-        </is>
-      </c>
-      <c r="D80" s="18" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E80" s="9" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F80" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G80" s="9" t="inlineStr">
-        <is>
-          <t>鮑佩佩</t>
-        </is>
-      </c>
-      <c r="H80" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I80" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J80" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K80" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L80" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M80" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N80" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O80" s="11" t="inlineStr">
-        <is>
-          <t>0A layout中</t>
-        </is>
-      </c>
-      <c r="P80" s="11" t="inlineStr">
+      <c r="P80" s="6" t="inlineStr">
         <is>
           <t>plan 7/3 gerber out，比預期 delay 4d,對後續schedule無影響</t>
         </is>
@@ -6670,7 +6662,7 @@
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 16 Max HX E4WGK</t>
+          <t>Crosshair 16 Max HX E4WFK</t>
         </is>
       </c>
       <c r="D81" s="18" t="inlineStr">
@@ -6685,7 +6677,7 @@
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G81" s="9" t="inlineStr">
@@ -6730,7 +6722,7 @@
       </c>
       <c r="O81" s="11" t="inlineStr">
         <is>
-          <t>GN22-X6 8GB SKU,0A layout中</t>
+          <t>0A layout中</t>
         </is>
       </c>
       <c r="P81" s="11" t="inlineStr">
@@ -6750,77 +6742,157 @@
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
+          <t>Crosshair 16 Max HX E4WGK</t>
+        </is>
+      </c>
+      <c r="D82" s="18" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G82" s="9" t="inlineStr">
+        <is>
+          <t>鮑佩佩</t>
+        </is>
+      </c>
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K82" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="L82" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M82" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N82" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O82" s="11" t="inlineStr">
+        <is>
+          <t>GN22-X6 8GB SKU,0A layout中</t>
+        </is>
+      </c>
+      <c r="P82" s="11" t="inlineStr">
+        <is>
+          <t>plan 7/3 gerber out，比預期 delay 4d,對後續schedule無影響</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" hidden="1" outlineLevel="1">
+      <c r="A83" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>2655</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
           <t>Crosshair 16 Max HX E4WGXK</t>
         </is>
       </c>
-      <c r="D82" s="18" t="inlineStr">
+      <c r="D83" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E82" s="9" t="inlineStr">
+      <c r="E83" s="9" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F82" s="9" t="inlineStr">
+      <c r="F83" s="9" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G82" s="9" t="inlineStr">
+      <c r="G83" s="9" t="inlineStr">
         <is>
           <t>鮑佩佩</t>
         </is>
       </c>
-      <c r="H82" s="9" t="inlineStr">
+      <c r="H83" s="9" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I82" s="9" t="inlineStr">
+      <c r="I83" s="9" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J82" s="9" t="inlineStr">
+      <c r="J83" s="9" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K82" s="9" t="inlineStr">
+      <c r="K83" s="9" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L82" s="9" t="inlineStr">
+      <c r="L83" s="9" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M82" s="9" t="inlineStr">
+      <c r="M83" s="9" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N82" s="9" t="inlineStr">
+      <c r="N83" s="9" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O82" s="11" t="inlineStr">
+      <c r="O83" s="11" t="inlineStr">
         <is>
           <t>GN22-X6 12GB SKU, 0A layout中</t>
         </is>
       </c>
-      <c r="P82" s="11" t="inlineStr">
+      <c r="P83" s="11" t="inlineStr">
         <is>
           <t>plan 7/3 gerber out，比預期 delay 4d,對後續schedule無影響</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P82"/>
+  <autoFilter ref="A1:P83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/npi_dashboard.xlsx
+++ b/npi_dashboard.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPI Dashboard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -52,12 +52,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000B0F0"/>
+      <color rgb="007030A0"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="007030A0"/>
+      <color rgb="0000B0F0"/>
       <sz val="10"/>
     </font>
     <font>
@@ -142,16 +142,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -519,7 +519,7 @@
     <outlinePr summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P83"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1582,9 +1582,9 @@
           <t>Cyborg 15 B2VE</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>Design</t>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>MVT</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1818,7 +1818,7 @@
           <t>Venture 15 AI+ B3M</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -1894,7 +1894,7 @@
           <t>Katana 15 HX C14WEK</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -1970,7 +1970,7 @@
           <t>Katana 15 HX C14WFK</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2046,7 +2046,7 @@
           <t>Katana 15 HX C14WGK</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2119,10 +2119,10 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WGXK</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
+          <t>Katana 15 HX C14WEOK</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -2144,38 +2144,38 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/05/15</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>2026/06/01</t>
+          <t>2026/06/15</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr"/>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>2026/07/14</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>2026/07/30</t>
+          <t>2026/08/07</t>
         </is>
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
-          <t>2026/08/20</t>
+          <t>2026/08/21</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
         <is>
-          <t>2026/08/30</t>
+          <t>2026/08/31</t>
         </is>
       </c>
       <c r="O22" s="11" t="inlineStr">
         <is>
-          <t>DDR5 sku, DVT測試中,預計7/2 PCB 10 gerberout</t>
+          <t>DDR4 sku, DVT測試中</t>
         </is>
       </c>
       <c r="P22" s="11" t="inlineStr">
@@ -2195,10 +2195,10 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WEOK</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
+          <t>Katana 15 HX C14WFOK</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
@@ -2271,10 +2271,10 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WFOK</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
+          <t>Katana 15 HX C14WGOK</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
@@ -2336,79 +2336,80 @@
         </is>
       </c>
     </row>
-    <row r="25" hidden="1" outlineLevel="1">
-      <c r="A25" s="7" t="n">
+    <row r="25">
+      <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>15T3</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Katana 15 HX C14WGOK</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>15TK</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Cyborg A15 Max C1PWE</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>HWK 45W</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H25" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/15</t>
-        </is>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J25" s="9" t="inlineStr"/>
-      <c r="K25" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/24</t>
-        </is>
-      </c>
-      <c r="L25" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="M25" s="9" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/17</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/31</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="N25" s="9" t="inlineStr">
+      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O25" s="11" t="inlineStr">
-        <is>
-          <t>DDR4 sku, DVT測試中</t>
-        </is>
-      </c>
-      <c r="P25" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>HPT sku:RD已重工3台成APU 180,AMI release PI 1200i RC3@6/29,BIOS RD需儘速提供MSI版本BIOSi進行測試</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>1).Schedule:APU 155優先ATS,採購已下單6.5k,以 8 月底 MP為目標,其餘APU sku在9月進行ATS C/R,但AMD PI 1200i NDA release延至6/30與APU 155 PR樣品ETD 延至7/11,已影響 MP 時程,待收到PI code與PR樣品後將依實際測試情況確認是否調整MP時程
+2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
     </row>
@@ -2418,27 +2419,27 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>15T3</t>
+          <t>15TK</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WGXOK</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
+          <t>Cyborg A15 Max C1PWF</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>HWK 45W</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
@@ -2448,23 +2449,23 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>2026/05/15</t>
+          <t>2026/05/28</t>
         </is>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
+          <t>2026/06/26</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr"/>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>2026/08/07</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="M26" s="9" t="inlineStr">
@@ -2479,27 +2480,28 @@
       </c>
       <c r="O26" s="11" t="inlineStr">
         <is>
-          <t>DDR4 sku, DVT測試中</t>
+          <t>HPT sku:RD已重工3台成APU 180,AMI release PI 1200i RC3@6/29,BIOS RD需儘速提供MSI版本BIOSi進行測試</t>
         </is>
       </c>
       <c r="P26" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
+          <t>1).Schedule:APU 155優先ATS,採購已下單6.5k,以 8 月底 MP為目標,其餘APU sku在9月進行ATS C/R,但AMD PI 1200i NDA release延至6/30與APU 155 PR樣品ETD 延至7/11,已影響 MP 時程,待收到PI code與PR樣品後將依實際測試情況確認是否調整MP時程
+2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" hidden="1" outlineLevel="1">
+      <c r="A27" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>15TK</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Cyborg A15 Max C1PWE</t>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Cyborg A15 Max C1PWG</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
@@ -2507,58 +2509,58 @@
           <t>DVT</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>HWK 45W</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>2026/05/28</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>2026/06/26</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr"/>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr"/>
+      <c r="K27" s="9" t="inlineStr">
         <is>
           <t>2026/07/17</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="L27" s="9" t="inlineStr">
         <is>
           <t>2026/07/31</t>
         </is>
       </c>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="M27" s="9" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="N27" s="9" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O27" s="6" t="inlineStr">
+      <c r="O27" s="11" t="inlineStr">
         <is>
           <t>HPT sku:RD已重工3台成APU 180,AMI release PI 1200i RC3@6/29,BIOS RD需儘速提供MSI版本BIOSi進行測試</t>
         </is>
       </c>
-      <c r="P27" s="6" t="inlineStr">
+      <c r="P27" s="11" t="inlineStr">
         <is>
           <t>1).Schedule:APU 155優先ATS,採購已下單6.5k,以 8 月底 MP為目標,其餘APU sku在9月進行ATS C/R,但AMD PI 1200i NDA release延至6/30與APU 155 PR樣品ETD 延至7/11,已影響 MP 時程,待收到PI code與PR樣品後將依實際測試情況確認是否調整MP時程
 2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
@@ -2576,10 +2578,10 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Cyborg A15 Max C1PWF</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
+          <t>Cyborg A15 C1PWE</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2591,7 +2593,7 @@
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
@@ -2642,157 +2644,157 @@
         </is>
       </c>
     </row>
-    <row r="29" hidden="1" outlineLevel="1">
-      <c r="A29" s="7" t="n">
+    <row r="29">
+      <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>15TK</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Cyborg A15 Max C1PWG</t>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>24V1</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Modern 14 LE J3M</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>HWK 45W</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/26</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="inlineStr"/>
-      <c r="K29" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/17</t>
-        </is>
-      </c>
-      <c r="L29" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/31</t>
-        </is>
-      </c>
-      <c r="M29" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="N29" s="9" t="inlineStr">
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>WCL 25W</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Intel® graphics</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>倪嬌嬌</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/29</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O29" s="11" t="inlineStr">
-        <is>
-          <t>HPT sku:RD已重工3台成APU 180,AMI release PI 1200i RC3@6/29,BIOS RD需儘速提供MSI版本BIOSi進行測試</t>
-        </is>
-      </c>
-      <c r="P29" s="11" t="inlineStr">
-        <is>
-          <t>1).Schedule:APU 155優先ATS,採購已下單6.5k,以 8 月底 MP為目標,其餘APU sku在9月進行ATS C/R,但AMD PI 1200i NDA release延至6/30與APU 155 PR樣品ETD 延至7/11,已影響 MP 時程,待收到PI code與PR樣品後將依實際測試情況確認是否調整MP時程
-2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" hidden="1" outlineLevel="1">
-      <c r="A30" s="7" t="n">
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>Weibu plan 6/29 DVT SMT, 7/1 ASSY--熱管&amp;D件重新開模, 交期7/1</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>1)Schedule: 考量新料備料時程, 調整試產和ATS時間@8/17 start
+2)認證: 參考Weibu認證Schedule, 有四個國家無法同步於8/E TTM, 持續追蹤中 MX: 11/28 ready；AR:10/3 ready；CO: 9/5 ready；RU: 9/12 ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>15TK</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Cyborg A15 C1PWE</t>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>26V1</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Modern 16 LE J3M</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>HWK 45W</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/26</t>
-        </is>
-      </c>
-      <c r="J30" s="9" t="inlineStr"/>
-      <c r="K30" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/17</t>
-        </is>
-      </c>
-      <c r="L30" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/31</t>
-        </is>
-      </c>
-      <c r="M30" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="N30" s="9" t="inlineStr">
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>WCL 25W</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Intel® graphics</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>倪嬌嬌</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/29</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O30" s="11" t="inlineStr">
-        <is>
-          <t>HPT sku:RD已重工3台成APU 180,AMI release PI 1200i RC3@6/29,BIOS RD需儘速提供MSI版本BIOSi進行測試</t>
-        </is>
-      </c>
-      <c r="P30" s="11" t="inlineStr">
-        <is>
-          <t>1).Schedule:APU 155優先ATS,採購已下單6.5k,以 8 月底 MP為目標,其餘APU sku在9月進行ATS C/R,但AMD PI 1200i NDA release延至6/30與APU 155 PR樣品ETD 延至7/11,已影響 MP 時程,待收到PI code與PR樣品後將依實際測試情況確認是否調整MP時程
-2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
+      <c r="O30" s="6" t="inlineStr">
+        <is>
+          <t>Weibu plan 6/29 DVT SMT, 7/1 ASSY --熱管重新開模, 交期6/30</t>
+        </is>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>1)Schedule: 考量新料備料時程, 調整試產和ATS時間@8/17 start
+2)認證: 參考Weibu認證Schedule, 有四個國家無法同步於8/E TTM, 持續追蹤中 MX: 11/28 ready；AR:10/3 ready；CO: 9/5 ready；RU: 9/12 ready</t>
         </is>
       </c>
     </row>
@@ -2802,74 +2804,78 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>24V1</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Modern 14 LE J3M</t>
-        </is>
-      </c>
-      <c r="D31" s="14" t="inlineStr">
-        <is>
-          <t>Design</t>
+          <t>Prestige N16 Spark C1M</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>EVT</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>WCL 25W</t>
+          <t>N1 45W</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Intel® graphics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>倪嬌嬌</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>2026/06/02</t>
+          <t>2025/04/30</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr"/>
+          <t>2025/09/01</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/07/20</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/09/14</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>2026/08/17</t>
+          <t>2026/10/13</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>2026/08/31</t>
+          <t>2026/10/26</t>
         </is>
       </c>
       <c r="O31" s="6" t="inlineStr">
         <is>
-          <t>Weibu plan 6/29 DVT SMT, 7/1 ASSY--熱管&amp;D件重新開模, 交期7/1</t>
+          <t>1)EVT 更新BSP6.1.2  持續驗證中, 對應NV schedule 更新 MVT延到7/20.
+2) NV 更新BSP 時間 Factory Drop Final ETA 10/6 ,需要1周時間完成 HDI+BIOS 更新ATS strat 10/13</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>1)Schedule: 考量新料備料時程, 調整試產和ATS時間@8/17 start
-2)認證: 參考Weibu認證Schedule, 有四個國家無法同步於8/E TTM, 持續追蹤中 MX: 11/28 ready；AR:10/3 ready；CO: 9/5 ready；RU: 9/12 ready</t>
+          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
         </is>
       </c>
     </row>
@@ -2879,27 +2885,27 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>26V1</t>
+          <t>14T3</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Modern 16 LE J3M</t>
-        </is>
-      </c>
-      <c r="D32" s="14" t="inlineStr">
-        <is>
-          <t>Design</t>
+          <t>Prestige N14 Spark D1M</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>MVT</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>WCL 25W</t>
+          <t>N1 35W</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Intel® graphics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -2909,44 +2915,47 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>2026/06/02</t>
+          <t>2025/04/30</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr"/>
+          <t>2025/09/01</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/07/20</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/09/14</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>2026/08/17</t>
+          <t>2026/10/13</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>2026/08/31</t>
+          <t>2026/10/26</t>
         </is>
       </c>
       <c r="O32" s="6" t="inlineStr">
         <is>
-          <t>Weibu plan 6/29 DVT SMT, 7/1 ASSY --熱管重新開模, 交期6/30</t>
+          <t>MVT SMT@7/20--depend on Material ready date</t>
         </is>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>1)Schedule: 考量新料備料時程, 調整試產和ATS時間@8/17 start
-2)認證: 參考Weibu認證Schedule, 有四個國家無法同步於8/E TTM, 持續追蹤中 MX: 11/28 ready；AR:10/3 ready；CO: 9/5 ready；RU: 9/12 ready</t>
+          <t>1)備料：MP focus on 2.8K panel, for MVT@7/M, 待廠商確認中; for MP: a, 1st lot 1K 數量, 型號HQ15, 九月份交料(同步Leading customers量產交料時間 具體九月份ETD日期還在追蹤中. b. Others order: 需轉型號至HQxx, 十一月份交料</t>
         </is>
       </c>
     </row>
@@ -2956,173 +2965,172 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Prestige N16 Spark C1M</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>EVT</t>
+          <t>Katana 18 HX A14WEK</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>N1 45W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>顧曉琴</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>2025/04/30</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>2025/09/01</t>
+          <t>2026/06/15</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>2026/04/15</t>
+          <t>2026/08/24</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>2026/07/20</t>
+          <t>2026/10/12</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>2026/09/14</t>
+          <t>2026/11/02</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>2026/10/13</t>
+          <t>2026/11/21</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/11/30</t>
         </is>
       </c>
       <c r="O33" s="6" t="inlineStr">
         <is>
-          <t>1)EVT 更新BSP6.1.2  持續驗證中, 對應NV schedule 更新 MVT延到7/20.
-2) NV 更新BSP 時間 Factory Drop Final ETA 10/6 ,需要1周時間完成 HDI+BIOS 更新ATS strat 10/13</t>
+          <t>RPL-HX R + DDR5: DVT PCBA快遞3pcs 6/24到,目前已開機,調撥部分6/25到料供RD測試</t>
         </is>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" hidden="1" outlineLevel="1">
+      <c r="A34" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>14T3</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Prestige N14 Spark D1M</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>N1 35W</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>倪嬌嬌</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>2025/04/30</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>2025/09/01</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/15</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/20</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/14</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
-        <is>
-          <t>2026/10/13</t>
-        </is>
-      </c>
-      <c r="N34" s="4" t="inlineStr">
-        <is>
-          <t>2026/10/26</t>
-        </is>
-      </c>
-      <c r="O34" s="6" t="inlineStr">
-        <is>
-          <t>MVT SMT@7/20--depend on Material ready date</t>
-        </is>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>1)備料：MP focus on 2.8K panel, for MVT@7/M, 待廠商確認中; for MP: a, 1st lot 1K 數量, 型號HQ15, 九月份交料(同步Leading customers量產交料時間 具體九月份ETD日期還在追蹤中. b. Others order: 需轉型號至HQxx, 十一月份交料</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Katana 18 HX A14WFK</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>顧曉琴</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/12</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="M34" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/21</t>
+        </is>
+      </c>
+      <c r="N34" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="O34" s="11" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR5: DVT PCBA快遞3pcs 6/24到,目前已開機,調撥部分6/25到料供RD測試</t>
+        </is>
+      </c>
+      <c r="P34" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" hidden="1" outlineLevel="1">
+      <c r="A35" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Katana 18 HX A14WEK</t>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Katana 18 HX A14WGK</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
@@ -3130,62 +3138,62 @@
           <t>DVT</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="H35" s="9" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="J35" s="4" t="inlineStr">
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>2026/08/24</t>
         </is>
       </c>
-      <c r="K35" s="4" t="inlineStr">
+      <c r="K35" s="9" t="inlineStr">
         <is>
           <t>2026/10/12</t>
         </is>
       </c>
-      <c r="L35" s="4" t="inlineStr">
+      <c r="L35" s="9" t="inlineStr">
         <is>
           <t>2026/11/02</t>
         </is>
       </c>
-      <c r="M35" s="4" t="inlineStr">
+      <c r="M35" s="9" t="inlineStr">
         <is>
           <t>2026/11/21</t>
         </is>
       </c>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="N35" s="9" t="inlineStr">
         <is>
           <t>2026/11/30</t>
         </is>
       </c>
-      <c r="O35" s="6" t="inlineStr">
+      <c r="O35" s="11" t="inlineStr">
         <is>
           <t>RPL-HX R + DDR5: DVT PCBA快遞3pcs 6/24到,目前已開機,調撥部分6/25到料供RD測試</t>
         </is>
       </c>
-      <c r="P35" s="6" t="inlineStr">
+      <c r="P35" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -3202,10 +3210,10 @@
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WFK</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
+          <t>Katana 18 HX A14WEOK</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3217,7 +3225,7 @@
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -3227,22 +3235,18 @@
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J36" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr"/>
       <c r="K36" s="9" t="inlineStr">
         <is>
-          <t>2026/10/12</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr">
@@ -3252,22 +3256,22 @@
       </c>
       <c r="M36" s="9" t="inlineStr">
         <is>
-          <t>2026/11/21</t>
+          <t>2026/11/23</t>
         </is>
       </c>
       <c r="N36" s="9" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2026/12/02</t>
         </is>
       </c>
       <c r="O36" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT PCBA快遞3pcs 6/24到,目前已開機,調撥部分6/25到料供RD測試</t>
+          <t>RPL-HX R + DDR4: DVT SMT @ 6/30</t>
         </is>
       </c>
       <c r="P36" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3282,10 +3286,10 @@
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGK</t>
-        </is>
-      </c>
-      <c r="D37" s="16" t="inlineStr">
+          <t>Katana 18 HX A14WFOK</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3297,7 +3301,7 @@
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -3307,22 +3311,18 @@
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="inlineStr"/>
       <c r="K37" s="9" t="inlineStr">
         <is>
-          <t>2026/10/12</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
@@ -3332,22 +3332,22 @@
       </c>
       <c r="M37" s="9" t="inlineStr">
         <is>
-          <t>2026/11/21</t>
+          <t>2026/11/23</t>
         </is>
       </c>
       <c r="N37" s="9" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2026/12/02</t>
         </is>
       </c>
       <c r="O37" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT PCBA快遞3pcs 6/24到,目前已開機,調撥部分6/25到料供RD測試</t>
+          <t>RPL-HX R + DDR4: DVT SMT @ 6/30</t>
         </is>
       </c>
       <c r="P37" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3362,10 +3362,10 @@
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WEOK</t>
-        </is>
-      </c>
-      <c r="D38" s="16" t="inlineStr">
+          <t>Katana 18 HX A14WGOK</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -3438,10 +3438,10 @@
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WFOK</t>
-        </is>
-      </c>
-      <c r="D39" s="16" t="inlineStr">
+          <t>Crosshair 18 Max HX B14WEO</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="M39" s="9" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2026/11/28</t>
         </is>
       </c>
       <c r="N39" s="9" t="inlineStr">
         <is>
-          <t>2026/12/02</t>
+          <t>2026/12/07</t>
         </is>
       </c>
       <c r="O39" s="11" t="inlineStr">
@@ -3514,10 +3514,10 @@
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGOK</t>
-        </is>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
+          <t>Crosshair 18 Max HX B14WFO</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="M40" s="9" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2026/11/28</t>
         </is>
       </c>
       <c r="N40" s="9" t="inlineStr">
         <is>
-          <t>2026/12/02</t>
+          <t>2026/12/07</t>
         </is>
       </c>
       <c r="O40" s="11" t="inlineStr">
@@ -3590,10 +3590,10 @@
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WEO</t>
-        </is>
-      </c>
-      <c r="D41" s="16" t="inlineStr">
+          <t>Crosshair 18 Max HX B14WGO</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -3666,10 +3666,10 @@
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WFO</t>
-        </is>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
+          <t>Crosshair 18 Max HX B14WGXO</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -3742,10 +3742,10 @@
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WGO</t>
-        </is>
-      </c>
-      <c r="D43" s="16" t="inlineStr">
+          <t>Crosshair 18 Max HX B14WE</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -3767,15 +3767,19 @@
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J43" s="9" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
       <c r="K43" s="9" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3798,12 +3802,12 @@
       </c>
       <c r="O43" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT SMT @ 6/30</t>
+          <t>RPL-HX R + DDR5: DVT PCBA快遞3pcs 6/24到,目前已開機,調撥部分6/25到料供RD測試</t>
         </is>
       </c>
       <c r="P43" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3818,10 +3822,10 @@
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WGXO</t>
-        </is>
-      </c>
-      <c r="D44" s="16" t="inlineStr">
+          <t>Crosshair 18 Max HX B14WF</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3833,7 +3837,7 @@
       </c>
       <c r="F44" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
@@ -3843,15 +3847,19 @@
       </c>
       <c r="H44" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J44" s="9" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
       <c r="K44" s="9" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3874,12 +3882,12 @@
       </c>
       <c r="O44" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT SMT @ 6/30</t>
+          <t>RPL-HX R + DDR5: DVT PCBA快遞3pcs 6/24到,目前已開機,調撥部分6/25到料供RD測試</t>
         </is>
       </c>
       <c r="P44" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3894,10 +3902,10 @@
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WE</t>
-        </is>
-      </c>
-      <c r="D45" s="16" t="inlineStr">
+          <t>Crosshair 18 Max HX B14WG</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3909,7 +3917,7 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
@@ -3974,10 +3982,10 @@
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WF</t>
-        </is>
-      </c>
-      <c r="D46" s="16" t="inlineStr">
+          <t>Crosshair 18 Max HX B14WGX</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3989,7 +3997,7 @@
       </c>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
@@ -4054,22 +4062,22 @@
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WG</t>
-        </is>
-      </c>
-      <c r="D47" s="16" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Crosshair 18 Max HX B2WE</t>
+        </is>
+      </c>
+      <c r="D47" s="18" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>RPL-HX Next 55W</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G47" s="9" t="inlineStr">
@@ -4082,44 +4090,36 @@
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J47" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
+      <c r="I47" s="9" t="inlineStr"/>
+      <c r="J47" s="9" t="inlineStr"/>
       <c r="K47" s="9" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/12/08</t>
         </is>
       </c>
       <c r="L47" s="9" t="inlineStr">
         <is>
-          <t>2026/11/02</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="M47" s="9" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2027/01/19</t>
         </is>
       </c>
       <c r="N47" s="9" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="O47" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT PCBA快遞3pcs 6/24到,目前已開機,調撥部分6/25到料供RD測試</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P47" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -4134,22 +4134,22 @@
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WGX</t>
-        </is>
-      </c>
-      <c r="D48" s="16" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Crosshair 18 Max HX B2WEO</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>RPL-HX Next 55W</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
@@ -4159,47 +4159,39 @@
       </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J48" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="inlineStr"/>
+      <c r="J48" s="9" t="inlineStr"/>
       <c r="K48" s="9" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/12/08</t>
         </is>
       </c>
       <c r="L48" s="9" t="inlineStr">
         <is>
-          <t>2026/11/02</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="M48" s="9" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2027/01/19</t>
         </is>
       </c>
       <c r="N48" s="9" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="O48" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT PCBA快遞3pcs 6/24到,目前已開機,調撥部分6/25到料供RD測試</t>
+          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P48" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4206,7 @@
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WE</t>
+          <t>Crosshair 18 Max HX B2WF</t>
         </is>
       </c>
       <c r="D49" s="18" t="inlineStr">
@@ -4229,7 +4221,7 @@
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G49" s="9" t="inlineStr">
@@ -4286,7 +4278,7 @@
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WEO</t>
+          <t>Crosshair 18 Max HX B2WFO</t>
         </is>
       </c>
       <c r="D50" s="18" t="inlineStr">
@@ -4301,7 +4293,7 @@
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
@@ -4358,7 +4350,7 @@
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WF</t>
+          <t>Crosshair 18 Max HX B2WG</t>
         </is>
       </c>
       <c r="D51" s="18" t="inlineStr">
@@ -4373,7 +4365,7 @@
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
@@ -4430,7 +4422,7 @@
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WFO</t>
+          <t>Crosshair 18 Max HX B2WGO</t>
         </is>
       </c>
       <c r="D52" s="18" t="inlineStr">
@@ -4445,7 +4437,7 @@
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -4502,7 +4494,7 @@
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WG</t>
+          <t>Crosshair 18 Max HX B2WGX</t>
         </is>
       </c>
       <c r="D53" s="18" t="inlineStr">
@@ -4574,7 +4566,7 @@
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WGO</t>
+          <t>Crosshair 18 Max HX B2WGXO</t>
         </is>
       </c>
       <c r="D54" s="18" t="inlineStr">
@@ -4646,7 +4638,7 @@
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WGX</t>
+          <t>Katana 18 HX A2WEK</t>
         </is>
       </c>
       <c r="D55" s="18" t="inlineStr">
@@ -4661,7 +4653,7 @@
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G55" s="9" t="inlineStr">
@@ -4718,7 +4710,7 @@
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WGXO</t>
+          <t>Katana 18 HX A2WEOK</t>
         </is>
       </c>
       <c r="D56" s="18" t="inlineStr">
@@ -4733,7 +4725,7 @@
       </c>
       <c r="F56" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr">
@@ -4746,7 +4738,11 @@
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="I56" s="9" t="inlineStr"/>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
       <c r="J56" s="9" t="inlineStr"/>
       <c r="K56" s="9" t="inlineStr">
         <is>
@@ -4770,7 +4766,7 @@
       </c>
       <c r="O56" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P56" s="11" t="inlineStr">
@@ -4790,7 +4786,7 @@
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WEK</t>
+          <t>Katana 18 HX A2WFK</t>
         </is>
       </c>
       <c r="D57" s="18" t="inlineStr">
@@ -4805,7 +4801,7 @@
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G57" s="9" t="inlineStr">
@@ -4862,7 +4858,7 @@
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WEOK</t>
+          <t>Katana 18 HX A2WFOK</t>
         </is>
       </c>
       <c r="D58" s="18" t="inlineStr">
@@ -4877,7 +4873,7 @@
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr">
@@ -4938,7 +4934,7 @@
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WFK</t>
+          <t>Katana 18 HX A2WGK</t>
         </is>
       </c>
       <c r="D59" s="18" t="inlineStr">
@@ -4953,7 +4949,7 @@
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G59" s="9" t="inlineStr">
@@ -5010,7 +5006,7 @@
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WFOK</t>
+          <t>Katana 18 HX A2WGOK</t>
         </is>
       </c>
       <c r="D60" s="18" t="inlineStr">
@@ -5025,7 +5021,7 @@
       </c>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr">
@@ -5075,75 +5071,83 @@
         </is>
       </c>
     </row>
-    <row r="61" hidden="1" outlineLevel="1">
-      <c r="A61" s="7" t="n">
+    <row r="61">
+      <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="C61" s="9" t="inlineStr">
-        <is>
-          <t>Katana 18 HX A2WGK</t>
-        </is>
-      </c>
-      <c r="D61" s="18" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>14T4</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Prestige 14 AI</t>
+        </is>
+      </c>
+      <c r="D61" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E61" s="9" t="inlineStr">
-        <is>
-          <t>RPL-HX Next 55W</t>
-        </is>
-      </c>
-      <c r="F61" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G61" s="9" t="inlineStr">
-        <is>
-          <t>顧曉琴</t>
-        </is>
-      </c>
-      <c r="H61" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I61" s="9" t="inlineStr"/>
-      <c r="J61" s="9" t="inlineStr"/>
-      <c r="K61" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/08</t>
-        </is>
-      </c>
-      <c r="L61" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/30</t>
-        </is>
-      </c>
-      <c r="M61" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/19</t>
-        </is>
-      </c>
-      <c r="N61" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/30</t>
-        </is>
-      </c>
-      <c r="O61" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
-        </is>
-      </c>
-      <c r="P61" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>NVL-H 30W</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>朱芳芳</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/04</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/20</t>
+        </is>
+      </c>
+      <c r="M61" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/15</t>
+        </is>
+      </c>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/25</t>
+        </is>
+      </c>
+      <c r="O61" s="6" t="inlineStr">
+        <is>
+          <t>0A gerberout ：6/26,DVT SMT@7/22</t>
+        </is>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -5153,12 +5157,12 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>14T4</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WGOK</t>
+          <t>Prestige 14 AI+ Flip</t>
         </is>
       </c>
       <c r="D62" s="18" t="inlineStr">
@@ -5168,58 +5172,62 @@
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX Next 55W</t>
+          <t>NVL-H 30W</t>
         </is>
       </c>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>顧曉琴</t>
+          <t>朱芳芳</t>
         </is>
       </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/14</t>
         </is>
       </c>
       <c r="I62" s="9" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J62" s="9" t="inlineStr"/>
+          <t>2026/07/22</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
       <c r="K62" s="9" t="inlineStr">
         <is>
-          <t>2026/12/08</t>
+          <t>2026/11/04</t>
         </is>
       </c>
       <c r="L62" s="9" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/11/20</t>
         </is>
       </c>
       <c r="M62" s="9" t="inlineStr">
         <is>
-          <t>2027/01/19</t>
+          <t>2026/12/15</t>
         </is>
       </c>
       <c r="N62" s="9" t="inlineStr">
         <is>
-          <t>2027/01/30</t>
+          <t>2026/12/25</t>
         </is>
       </c>
       <c r="O62" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>0A gerberout ：6/26,DVT SMT@7/22</t>
         </is>
       </c>
       <c r="P62" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -5229,15 +5237,15 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>14T4</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Prestige 14 AI</t>
-        </is>
-      </c>
-      <c r="D63" s="14" t="inlineStr">
+          <t>Prestige 16 AI+</t>
+        </is>
+      </c>
+      <c r="D63" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5262,11 +5270,7 @@
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="I63" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/22</t>
-        </is>
-      </c>
+      <c r="I63" s="4" t="inlineStr"/>
       <c r="J63" s="4" t="inlineStr">
         <is>
           <t>2026/09/15</t>
@@ -5309,12 +5313,12 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>14T4</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Prestige 14 AI+ Flip</t>
+          <t>Prestige 16 Flip AI+</t>
         </is>
       </c>
       <c r="D64" s="18" t="inlineStr">
@@ -5342,11 +5346,7 @@
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/22</t>
-        </is>
-      </c>
+      <c r="I64" s="9" t="inlineStr"/>
       <c r="J64" s="9" t="inlineStr">
         <is>
           <t>2026/09/15</t>
@@ -5389,22 +5389,22 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>13Q5</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Prestige 16 AI+</t>
-        </is>
-      </c>
-      <c r="D65" s="14" t="inlineStr">
+          <t>Prestige 13 AI+ A4M</t>
+        </is>
+      </c>
+      <c r="D65" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>NVL-H 30W</t>
+          <t>NVL-H 28W</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -5414,356 +5414,365 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>朱芳芳</t>
+          <t>顏春梅</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>2026/05/14</t>
-        </is>
-      </c>
-      <c r="I65" s="4" t="inlineStr"/>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>2026/09/15</t>
+          <t>2026/10/08</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>2026/11/04</t>
+          <t>2026/11/21</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>2026/11/20</t>
+          <t>2026/11/22</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>2026/12/15</t>
+          <t>2026/12/22</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>2026/12/25</t>
-        </is>
-      </c>
-      <c r="O65" s="6" t="inlineStr">
-        <is>
-          <t>0A gerberout ：6/26,DVT SMT@7/22</t>
-        </is>
-      </c>
-      <c r="P65" s="6" t="inlineStr">
+          <t>2026/12/31</t>
+        </is>
+      </c>
+      <c r="O65" s="6" t="inlineStr"/>
+      <c r="P65" s="6" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>2633</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WI</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5080</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="M66" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N66" s="4" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="O66" s="6" t="inlineStr">
+        <is>
+          <t>0M layout中，预计6/30 gerber out</t>
+        </is>
+      </c>
+      <c r="P66" s="6" t="inlineStr">
+        <is>
+          <t>1) Schedule:NV VBIOS @1/6, gating 8天,預計12/E 拿到WHQL，可能影響到最終TTM 時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" hidden="1" outlineLevel="1">
+      <c r="A67" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>2633</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WH</t>
+        </is>
+      </c>
+      <c r="D67" s="18" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K67" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L67" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="M67" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N67" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="O67" s="11" t="inlineStr">
+        <is>
+          <t>0M layout中，预计6/30 gerber out</t>
+        </is>
+      </c>
+      <c r="P67" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
-    <row r="66" hidden="1" outlineLevel="1">
-      <c r="A66" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>2624</t>
-        </is>
-      </c>
-      <c r="C66" s="9" t="inlineStr">
-        <is>
-          <t>Prestige 16 Flip AI+</t>
-        </is>
-      </c>
-      <c r="D66" s="18" t="inlineStr">
+    <row r="68" hidden="1" outlineLevel="1">
+      <c r="A68" s="7" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>2633</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WJ</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E66" s="9" t="inlineStr">
-        <is>
-          <t>NVL-H 30W</t>
-        </is>
-      </c>
-      <c r="F66" s="9" t="inlineStr">
-        <is>
-          <t>Intel® Arc™ Graphics</t>
-        </is>
-      </c>
-      <c r="G66" s="9" t="inlineStr">
-        <is>
-          <t>朱芳芳</t>
-        </is>
-      </c>
-      <c r="H66" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/14</t>
-        </is>
-      </c>
-      <c r="I66" s="9" t="inlineStr"/>
-      <c r="J66" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/15</t>
-        </is>
-      </c>
-      <c r="K66" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/04</t>
-        </is>
-      </c>
-      <c r="L66" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/20</t>
-        </is>
-      </c>
-      <c r="M66" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/15</t>
-        </is>
-      </c>
-      <c r="N66" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/25</t>
-        </is>
-      </c>
-      <c r="O66" s="11" t="inlineStr">
-        <is>
-          <t>0A gerberout ：6/26,DVT SMT@7/22</t>
-        </is>
-      </c>
-      <c r="P66" s="11" t="inlineStr">
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5090</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K68" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L68" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="M68" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N68" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="O68" s="11" t="inlineStr">
+        <is>
+          <t>0M layout中，预计6/30 gerber out</t>
+        </is>
+      </c>
+      <c r="P68" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>13Q5</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>Prestige 13 AI+ A4M</t>
-        </is>
-      </c>
-      <c r="D67" s="14" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WE</t>
+        </is>
+      </c>
+      <c r="D69" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>NVL-H 28W</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>Intel® Arc™ Graphics</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>顏春梅</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="I67" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/18</t>
-        </is>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>2026/10/08</t>
-        </is>
-      </c>
-      <c r="K67" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/21</t>
-        </is>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/22</t>
-        </is>
-      </c>
-      <c r="M67" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/22</t>
-        </is>
-      </c>
-      <c r="N67" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/31</t>
-        </is>
-      </c>
-      <c r="O67" s="6" t="inlineStr"/>
-      <c r="P67" s="6" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WI</t>
-        </is>
-      </c>
-      <c r="D68" s="14" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E69" s="4" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5080</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>賴雪鳳</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I68" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/22</t>
-        </is>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K68" s="4" t="inlineStr">
+      <c r="K69" s="4" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/30</t>
-        </is>
-      </c>
-      <c r="M68" s="4" t="inlineStr">
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/27</t>
+        </is>
+      </c>
+      <c r="M69" s="4" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N68" s="4" t="inlineStr">
+      <c r="N69" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O68" s="6" t="inlineStr">
-        <is>
-          <t>0M layout中，预计6/30 gerber out</t>
-        </is>
-      </c>
-      <c r="P68" s="6" t="inlineStr">
-        <is>
-          <t>1) Schedule:NV VBIOS @1/6, gating 8天,預計12/E 拿到WHQL，可能影響到最終TTM 時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" hidden="1" outlineLevel="1">
-      <c r="A69" s="7" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="C69" s="9" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WH</t>
-        </is>
-      </c>
-      <c r="D69" s="18" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F69" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070Ti</t>
-        </is>
-      </c>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H69" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I69" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/22</t>
-        </is>
-      </c>
-      <c r="J69" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K69" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L69" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/30</t>
-        </is>
-      </c>
-      <c r="M69" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N69" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="O69" s="11" t="inlineStr">
-        <is>
-          <t>0M layout中，预计6/30 gerber out</t>
-        </is>
-      </c>
-      <c r="P69" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="O69" s="6" t="inlineStr">
+        <is>
+          <t>0A layout start 6/8-7/17</t>
+        </is>
+      </c>
+      <c r="P69" s="6" t="inlineStr">
+        <is>
+          <t>1)NV VBIOS 驗證時間6周
+2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
     </row>
@@ -5773,12 +5782,12 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WJ</t>
+          <t>Stealth 16 AI+ B4WF</t>
         </is>
       </c>
       <c r="D70" s="18" t="inlineStr">
@@ -5793,12 +5802,12 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="H70" s="9" t="inlineStr">
@@ -5808,7 +5817,7 @@
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
-          <t>2026/07/22</t>
+          <t>2026/08/07</t>
         </is>
       </c>
       <c r="J70" s="9" t="inlineStr">
@@ -5823,7 +5832,7 @@
       </c>
       <c r="L70" s="9" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2026/11/27</t>
         </is>
       </c>
       <c r="M70" s="9" t="inlineStr">
@@ -5838,90 +5847,91 @@
       </c>
       <c r="O70" s="11" t="inlineStr">
         <is>
-          <t>0M layout中，预计6/30 gerber out</t>
+          <t>0A layout start 6/8-7/17</t>
         </is>
       </c>
       <c r="P70" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="n">
+          <t>1)NV VBIOS 驗證時間6周
+2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" hidden="1" outlineLevel="1">
+      <c r="A71" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>2634</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WE</t>
-        </is>
-      </c>
-      <c r="D71" s="14" t="inlineStr">
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
+        </is>
+      </c>
+      <c r="D71" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
+      <c r="E71" s="9" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G71" s="4" t="inlineStr">
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
         <is>
           <t>賴雪鳳</t>
         </is>
       </c>
-      <c r="H71" s="4" t="inlineStr">
+      <c r="H71" s="9" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I71" s="4" t="inlineStr">
+      <c r="I71" s="9" t="inlineStr">
         <is>
           <t>2026/08/07</t>
         </is>
       </c>
-      <c r="J71" s="4" t="inlineStr">
+      <c r="J71" s="9" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K71" s="4" t="inlineStr">
+      <c r="K71" s="9" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L71" s="4" t="inlineStr">
+      <c r="L71" s="9" t="inlineStr">
         <is>
           <t>2026/11/27</t>
         </is>
       </c>
-      <c r="M71" s="4" t="inlineStr">
+      <c r="M71" s="9" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N71" s="4" t="inlineStr">
+      <c r="N71" s="9" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O71" s="6" t="inlineStr">
+      <c r="O71" s="11" t="inlineStr">
         <is>
           <t>0A layout start 6/8-7/17</t>
         </is>
       </c>
-      <c r="P71" s="6" t="inlineStr">
+      <c r="P71" s="11" t="inlineStr">
         <is>
           <t>1)NV VBIOS 驗證時間6周
 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
@@ -5939,7 +5949,7 @@
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WF</t>
+          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
         </is>
       </c>
       <c r="D72" s="18" t="inlineStr">
@@ -5954,7 +5964,7 @@
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G72" s="9" t="inlineStr">
@@ -6009,84 +6019,83 @@
         </is>
       </c>
     </row>
-    <row r="73" hidden="1" outlineLevel="1">
-      <c r="A73" s="7" t="n">
+    <row r="73">
+      <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="C73" s="9" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
-        </is>
-      </c>
-      <c r="D73" s="18" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>2654</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Raider 16 Max HX B4WH</t>
+        </is>
+      </c>
+      <c r="D73" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F73" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>賴雪鳳</t>
-        </is>
-      </c>
-      <c r="H73" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="J73" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K73" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L73" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/27</t>
-        </is>
-      </c>
-      <c r="M73" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N73" s="9" t="inlineStr">
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>吳美芳</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O73" s="11" t="inlineStr">
-        <is>
-          <t>0A layout start 6/8-7/17</t>
-        </is>
-      </c>
-      <c r="P73" s="11" t="inlineStr">
-        <is>
-          <t>1)NV VBIOS 驗證時間6周
-2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M73" s="4" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O73" s="6" t="inlineStr">
+        <is>
+          <t>0M layout中，预计6/29 gerber out</t>
+        </is>
+      </c>
+      <c r="P73" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6105,12 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
+          <t>Raider 16 Max HX B4WI</t>
         </is>
       </c>
       <c r="D74" s="18" t="inlineStr">
@@ -6111,141 +6120,140 @@
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>NVL-H 45W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
-          <t>2026/05/22</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="I74" s="9" t="inlineStr">
         <is>
-          <t>2026/08/07</t>
+          <t>2026/07/27</t>
         </is>
       </c>
       <c r="J74" s="9" t="inlineStr">
         <is>
-          <t>2026/09/16</t>
+          <t>2026/09/29</t>
         </is>
       </c>
       <c r="K74" s="9" t="inlineStr">
         <is>
-          <t>2026/11/11</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="L74" s="9" t="inlineStr">
         <is>
-          <t>2026/11/27</t>
+          <t>2027/02/02</t>
         </is>
       </c>
       <c r="M74" s="9" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2027/03/08</t>
         </is>
       </c>
       <c r="N74" s="9" t="inlineStr">
         <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O74" s="11" t="inlineStr">
+        <is>
+          <t>0M layout中,预计6/29 gerber out</t>
+        </is>
+      </c>
+      <c r="P74" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" hidden="1" outlineLevel="1">
+      <c r="A75" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>2654</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>Raider 16 Max HX B4WJ</t>
+        </is>
+      </c>
+      <c r="D75" s="18" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5090</t>
+        </is>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>吳美芳</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K75" s="9" t="inlineStr">
+        <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O74" s="11" t="inlineStr">
-        <is>
-          <t>0A layout start 6/8-7/17</t>
-        </is>
-      </c>
-      <c r="P74" s="11" t="inlineStr">
-        <is>
-          <t>1)NV VBIOS 驗證時間6周
-2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>2654</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>Raider 16 Max HX B4WH</t>
-        </is>
-      </c>
-      <c r="D75" s="14" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5070Ti</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>吳美芳</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I75" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K75" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
+      <c r="L75" s="9" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M75" s="4" t="inlineStr">
+      <c r="M75" s="9" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N75" s="4" t="inlineStr">
+      <c r="N75" s="9" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O75" s="6" t="inlineStr">
-        <is>
-          <t>0M layout中，预计6/29 gerber out</t>
-        </is>
-      </c>
-      <c r="P75" s="6" t="inlineStr">
+      <c r="O75" s="11" t="inlineStr">
+        <is>
+          <t>0M layout中,预计6/29 gerber out</t>
+        </is>
+      </c>
+      <c r="P75" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -6262,7 +6270,7 @@
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B4WI</t>
+          <t>Raider 16  HX B4WH</t>
         </is>
       </c>
       <c r="D76" s="18" t="inlineStr">
@@ -6277,7 +6285,7 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="G76" s="9" t="inlineStr">
@@ -6322,7 +6330,7 @@
       </c>
       <c r="O76" s="11" t="inlineStr">
         <is>
-          <t>0M layout中,预计6/29 gerber out</t>
+          <t>0M layout中，预计6/29 gerber out</t>
         </is>
       </c>
       <c r="P76" s="11" t="inlineStr">
@@ -6342,7 +6350,7 @@
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B4WJ</t>
+          <t>Raider 16  HX B4WI</t>
         </is>
       </c>
       <c r="D77" s="18" t="inlineStr">
@@ -6357,7 +6365,7 @@
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="G77" s="9" t="inlineStr">
@@ -6402,7 +6410,7 @@
       </c>
       <c r="O77" s="11" t="inlineStr">
         <is>
-          <t>0M layout中,预计6/29 gerber out</t>
+          <t>0M layout中，预计6/29 gerber out</t>
         </is>
       </c>
       <c r="P77" s="11" t="inlineStr">
@@ -6411,83 +6419,83 @@
         </is>
       </c>
     </row>
-    <row r="78" hidden="1" outlineLevel="1">
-      <c r="A78" s="7" t="n">
+    <row r="78">
+      <c r="A78" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>2654</t>
-        </is>
-      </c>
-      <c r="C78" s="9" t="inlineStr">
-        <is>
-          <t>Raider 16  HX B4WH</t>
-        </is>
-      </c>
-      <c r="D78" s="18" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>2655</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Crosshair 16 Max HX E4WEK</t>
+        </is>
+      </c>
+      <c r="D78" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E78" s="9" t="inlineStr">
+      <c r="E78" s="4" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F78" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070Ti</t>
-        </is>
-      </c>
-      <c r="G78" s="9" t="inlineStr">
-        <is>
-          <t>吳美芳</t>
-        </is>
-      </c>
-      <c r="H78" s="9" t="inlineStr">
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>鮑佩佩</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I78" s="9" t="inlineStr">
+      <c r="I78" s="4" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J78" s="9" t="inlineStr">
+      <c r="J78" s="4" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K78" s="9" t="inlineStr">
+      <c r="K78" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L78" s="9" t="inlineStr">
+      <c r="L78" s="4" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M78" s="9" t="inlineStr">
+      <c r="M78" s="4" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N78" s="9" t="inlineStr">
+      <c r="N78" s="4" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O78" s="11" t="inlineStr">
-        <is>
-          <t>0M layout中，预计6/29 gerber out</t>
-        </is>
-      </c>
-      <c r="P78" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="O78" s="6" t="inlineStr">
+        <is>
+          <t>0A layout中</t>
+        </is>
+      </c>
+      <c r="P78" s="6" t="inlineStr">
+        <is>
+          <t>plan 7/3 gerber out，比預期 delay 4d,對後續schedule無影響</t>
         </is>
       </c>
     </row>
@@ -6497,12 +6505,12 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WI</t>
+          <t>Crosshair 16 Max HX E4WFK</t>
         </is>
       </c>
       <c r="D79" s="18" t="inlineStr">
@@ -6517,12 +6525,12 @@
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>鮑佩佩</t>
         </is>
       </c>
       <c r="H79" s="9" t="inlineStr">
@@ -6562,90 +6570,90 @@
       </c>
       <c r="O79" s="11" t="inlineStr">
         <is>
-          <t>0M layout中，预计6/29 gerber out</t>
+          <t>0A layout中</t>
         </is>
       </c>
       <c r="P79" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
+          <t>plan 7/3 gerber out，比預期 delay 4d,對後續schedule無影響</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" hidden="1" outlineLevel="1">
+      <c r="A80" s="7" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>2655</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WEK</t>
-        </is>
-      </c>
-      <c r="D80" s="14" t="inlineStr">
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>Crosshair 16 Max HX E4WGK</t>
+        </is>
+      </c>
+      <c r="D80" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="E80" s="9" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G80" s="4" t="inlineStr">
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
         <is>
           <t>鮑佩佩</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr">
+      <c r="H80" s="9" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I80" s="4" t="inlineStr">
+      <c r="I80" s="9" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J80" s="4" t="inlineStr">
+      <c r="J80" s="9" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K80" s="4" t="inlineStr">
+      <c r="K80" s="9" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L80" s="4" t="inlineStr">
+      <c r="L80" s="9" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M80" s="4" t="inlineStr">
+      <c r="M80" s="9" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N80" s="4" t="inlineStr">
+      <c r="N80" s="9" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O80" s="6" t="inlineStr">
-        <is>
-          <t>0A layout中</t>
-        </is>
-      </c>
-      <c r="P80" s="6" t="inlineStr">
+      <c r="O80" s="11" t="inlineStr">
+        <is>
+          <t>GN22-X6 8GB SKU,0A layout中</t>
+        </is>
+      </c>
+      <c r="P80" s="11" t="inlineStr">
         <is>
           <t>plan 7/3 gerber out，比預期 delay 4d,對後續schedule無影響</t>
         </is>
@@ -6662,7 +6670,7 @@
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 16 Max HX E4WFK</t>
+          <t>Crosshair 16 Max HX E4WGXK</t>
         </is>
       </c>
       <c r="D81" s="18" t="inlineStr">
@@ -6677,7 +6685,7 @@
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G81" s="9" t="inlineStr">
@@ -6722,7 +6730,7 @@
       </c>
       <c r="O81" s="11" t="inlineStr">
         <is>
-          <t>0A layout中</t>
+          <t>GN22-X6 12GB SKU, 0A layout中</t>
         </is>
       </c>
       <c r="P81" s="11" t="inlineStr">
@@ -6731,168 +6739,8 @@
         </is>
       </c>
     </row>
-    <row r="82" hidden="1" outlineLevel="1">
-      <c r="A82" s="7" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>2655</t>
-        </is>
-      </c>
-      <c r="C82" s="9" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WGK</t>
-        </is>
-      </c>
-      <c r="D82" s="18" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E82" s="9" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G82" s="9" t="inlineStr">
-        <is>
-          <t>鮑佩佩</t>
-        </is>
-      </c>
-      <c r="H82" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I82" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K82" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L82" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M82" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N82" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O82" s="11" t="inlineStr">
-        <is>
-          <t>GN22-X6 8GB SKU,0A layout中</t>
-        </is>
-      </c>
-      <c r="P82" s="11" t="inlineStr">
-        <is>
-          <t>plan 7/3 gerber out，比預期 delay 4d,對後續schedule無影響</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" hidden="1" outlineLevel="1">
-      <c r="A83" s="7" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>2655</t>
-        </is>
-      </c>
-      <c r="C83" s="9" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WGXK</t>
-        </is>
-      </c>
-      <c r="D83" s="18" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E83" s="9" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F83" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G83" s="9" t="inlineStr">
-        <is>
-          <t>鮑佩佩</t>
-        </is>
-      </c>
-      <c r="H83" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I83" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J83" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K83" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L83" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M83" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N83" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O83" s="11" t="inlineStr">
-        <is>
-          <t>GN22-X6 12GB SKU, 0A layout中</t>
-        </is>
-      </c>
-      <c r="P83" s="11" t="inlineStr">
-        <is>
-          <t>plan 7/3 gerber out，比預期 delay 4d,對後續schedule無影響</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P83"/>
+  <autoFilter ref="A1:P81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/npi_dashboard.xlsx
+++ b/npi_dashboard.xlsx
@@ -42,22 +42,22 @@
       <sz val="11"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="00FF4444"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <color rgb="00666666"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FF4444"/>
+      <color rgb="0000B0F0"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="007030A0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0000B0F0"/>
       <sz val="10"/>
     </font>
     <font>
@@ -118,28 +118,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -148,10 +145,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Prestige 14 Flip AI+ Rhône</t>
+          <t>Prestige 14 Flip AI+ Starry Night</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -685,734 +685,737 @@
       </c>
       <c r="O2" s="6" t="inlineStr">
         <is>
-          <t>梵谷特仕版 物料持續追踪，6/23 ATS CR，6/E出貨</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
-          <t>1. ALS sensor NG  HDI 進版 6/27重工， 1.A件成品LOGO不良較高，交料瓶頸 請ID&amp;Buyer持續pull in。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1" outlineLevel="1">
-      <c r="A3" s="7" t="n">
+          <t>1. ALS sensor NG  HDI 進版 6/27重工， 2.A件成品LOGO不良較高，交料瓶頸 請ID&amp;Buyer持續pull in。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>14T2</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Prestige 14 Flip AI+ Starry Night</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>265L</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Crosshair A16 HX MLG Edition E8WFK</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>DRG-HX 55W</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/03</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/10</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>MLG(魔龍姬)ID: ATS @7/3</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/10前完成；
+2) Packing: WW版本設計確認中;</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1" outlineLevel="1">
+      <c r="A4" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>265L</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Crosshair A16 HX MLG Edition E8WEK</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>DRG-HX 55W</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr"/>
+      <c r="J4" s="10" t="inlineStr"/>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/03</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/10</t>
+        </is>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>MLG(魔龍姬)ID:ATS @7/3</t>
+        </is>
+      </c>
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" hidden="1" outlineLevel="1">
+      <c r="A5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>265L</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Crosshair A16 HX MLG Edition E8WGK</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>DRG-HX 55W</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr"/>
+      <c r="J5" s="10" t="inlineStr"/>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/03</t>
+        </is>
+      </c>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/10</t>
+        </is>
+      </c>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>MLG(魔龍姬)ID:  ATS @7/3</t>
+        </is>
+      </c>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" hidden="1" outlineLevel="1">
+      <c r="A6" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>265L</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Crosshair A16 HX MLG Edition E8WGXK</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>DRG-HX 55W</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr"/>
+      <c r="J6" s="10" t="inlineStr"/>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/03</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/10</t>
+        </is>
+      </c>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>MLG(魔龍姬)ID:  ATS @7/3</t>
+        </is>
+      </c>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" hidden="1" outlineLevel="1">
+      <c r="A7" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>265L</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Crosshair A16 HX E9WEK</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>FRG-HX 55W</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr"/>
+      <c r="J7" s="10" t="inlineStr"/>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/16</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="O7" s="12" t="inlineStr">
+        <is>
+          <t>FRG (5/4通知resume）: DQA 測試中</t>
+        </is>
+      </c>
+      <c r="P7" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" hidden="1" outlineLevel="1">
+      <c r="A8" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>265L</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Crosshair A16 HX E9WFK</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>FRG-HX 55W</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr"/>
+      <c r="J8" s="10" t="inlineStr"/>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/16</t>
+        </is>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>FRG (5/4通知resume）: DQA 測試中</t>
+        </is>
+      </c>
+      <c r="P8" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" hidden="1" outlineLevel="1">
+      <c r="A9" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>265L</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Crosshair A16 HX E9WGXK</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>FRG-HX3D 55W</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr"/>
+      <c r="J9" s="10" t="inlineStr"/>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/16</t>
+        </is>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/26</t>
+        </is>
+      </c>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>FRG (5/4通知resume）: DQA 測試中</t>
+        </is>
+      </c>
+      <c r="P9" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>14V2</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Commercial 14 C13M</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>ATS</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>PTL-H 30W</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t>Intel® Arc™ Graphics</t>
-        </is>
-      </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>朱芳芳</t>
-        </is>
-      </c>
-      <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t>2026/04/13</t>
-        </is>
-      </c>
-      <c r="I3" s="9" t="inlineStr"/>
-      <c r="J3" s="9" t="inlineStr"/>
-      <c r="K3" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/10</t>
-        </is>
-      </c>
-      <c r="L3" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="M3" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/23</t>
-        </is>
-      </c>
-      <c r="N3" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/30</t>
-        </is>
-      </c>
-      <c r="O3" s="11" t="inlineStr">
-        <is>
-          <t>梵谷特仕版 物料持續追踪，規劃6/23 ATS CR，6/E出貨</t>
-        </is>
-      </c>
-      <c r="P3" s="11" t="inlineStr">
-        <is>
-          <t>1. ALS sensor NG  HDI 進版 6/27重工， 2.A件成品LOGO不良較高，交料瓶頸 請ID&amp;Buyer持續pull in。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>265L</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Crosshair A16 HX MLG Edition E8WFK</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>DRG-HX 55W</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/26</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/03</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>RPL-U 25W</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Intel® graphics</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>2026/01/04</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>2026/02/05</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>2026/03/16</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>2026/07/10</t>
         </is>
       </c>
-      <c r="O4" s="6" t="inlineStr">
-        <is>
-          <t>MLG(魔龍姬)ID: DQA 測試中</t>
-        </is>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>1) 認證：SRRC認證中, 影響中國區出貨（可清關出貨，但上架售賣有風險）需在7/8前完成；
-2) Packing: WW版本設計確認中;
-3) Schedule: 生管排程, ATS 由7/1更新為7/3. MP @7/10</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" hidden="1" outlineLevel="1">
-      <c r="A5" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>265L</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Crosshair A16 HX MLG Edition E8WEK</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>DRG-HX 55W</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr"/>
-      <c r="J5" s="9" t="inlineStr"/>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/26</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/03</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="inlineStr">
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>因首批安排RPL-U Refresh 優先投產，第二波投產因PCB 最快交期落在6/29,加上微步盤點，預計最快7/10 TTM</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" hidden="1" outlineLevel="1">
+      <c r="A11" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>14V2</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Modern 14 H13M</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>RPL-U 25W</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Intel® graphics</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>2025/11/14</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr"/>
+      <c r="J11" s="10" t="inlineStr"/>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>2026/01/14</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>2026/03/16</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/06</t>
+        </is>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>2026/07/10</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
-        <is>
-          <t>MLG(魔龍姬)ID: DQA 測試中</t>
-        </is>
-      </c>
-      <c r="P5" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" hidden="1" outlineLevel="1">
-      <c r="A6" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>265L</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Crosshair A16 HX MLG Edition E8WGK</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>DRG-HX 55W</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr"/>
-      <c r="J6" s="9" t="inlineStr"/>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/26</t>
-        </is>
-      </c>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/03</t>
-        </is>
-      </c>
-      <c r="N6" s="9" t="inlineStr">
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>因首批安排RPL-U Refresh 優先投產，第二波投產因PCB 最快交期落在6/29,加上微步盤點，預計最快7/10 TTM</t>
+        </is>
+      </c>
+      <c r="P11" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>24VL</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Modern A14 LE J1M</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>RMB 100 35W</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>杜晨光</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>2026/03/30</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/17</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/15</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/01</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>2026/07/10</t>
         </is>
       </c>
-      <c r="O6" s="11" t="inlineStr">
-        <is>
-          <t>MLG(魔龍姬)ID:  DQA 測試中</t>
-        </is>
-      </c>
-      <c r="P6" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" hidden="1" outlineLevel="1">
-      <c r="A7" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>265L</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Crosshair A16 HX MLG Edition E8WGXK</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>DRG-HX 55W</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr"/>
-      <c r="J7" s="9" t="inlineStr"/>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
-      </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/26</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/03</t>
-        </is>
-      </c>
-      <c r="N7" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/10</t>
-        </is>
-      </c>
-      <c r="O7" s="11" t="inlineStr">
-        <is>
-          <t>MLG(魔龍姬)ID:  DQA 測試中</t>
-        </is>
-      </c>
-      <c r="P7" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" hidden="1" outlineLevel="1">
-      <c r="A8" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>265L</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Crosshair A16 HX E9WEK</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>FRG-HX 55W</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="I8" s="9" t="inlineStr"/>
-      <c r="J8" s="9" t="inlineStr"/>
-      <c r="K8" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/18</t>
-        </is>
-      </c>
-      <c r="L8" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/16</t>
-        </is>
-      </c>
-      <c r="M8" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/16</t>
-        </is>
-      </c>
-      <c r="N8" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
-      <c r="O8" s="11" t="inlineStr">
-        <is>
-          <t>FRG (5/4通知resume）: DQA 測試中</t>
-        </is>
-      </c>
-      <c r="P8" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" hidden="1" outlineLevel="1">
-      <c r="A9" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>265L</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Crosshair A16 HX E9WFK</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>FRG-HX 55W</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr"/>
-      <c r="J9" s="9" t="inlineStr"/>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/18</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/16</t>
-        </is>
-      </c>
-      <c r="M9" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/16</t>
-        </is>
-      </c>
-      <c r="N9" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
-      <c r="O9" s="11" t="inlineStr">
-        <is>
-          <t>FRG (5/4通知resume）: DQA 測試中</t>
-        </is>
-      </c>
-      <c r="P9" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" hidden="1" outlineLevel="1">
-      <c r="A10" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>265L</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>Crosshair A16 HX E9WGXK</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>FRG-HX3D 55W</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="I10" s="9" t="inlineStr"/>
-      <c r="J10" s="9" t="inlineStr"/>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/18</t>
-        </is>
-      </c>
-      <c r="L10" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/16</t>
-        </is>
-      </c>
-      <c r="M10" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/16</t>
-        </is>
-      </c>
-      <c r="N10" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
-      <c r="O10" s="11" t="inlineStr">
-        <is>
-          <t>FRG (5/4通知resume）: DQA 測試中</t>
-        </is>
-      </c>
-      <c r="P10" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>14V2</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Commercial 14 C13M</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>ATS</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>RPL-U 25W</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Intel® graphics</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>杜晨光</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>2026/01/04</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr"/>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>2026/02/05</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>2026/03/16</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/06</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/10</t>
-        </is>
-      </c>
-      <c r="O11" s="6" t="inlineStr">
-        <is>
-          <t>因首批安排RPL-U Refresh 優先投產，第二波投產因PCB 最快交期落在6/29,加上微步盤點，預計最快7/10 TTM</t>
-        </is>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" hidden="1" outlineLevel="1">
-      <c r="A12" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>14V2</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Modern 14 H13M</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>ATS</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>RPL-U 25W</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>Intel® graphics</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>杜晨光</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="inlineStr"/>
-      <c r="J12" s="9" t="inlineStr"/>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>2026/01/14</t>
-        </is>
-      </c>
-      <c r="L12" s="9" t="inlineStr">
-        <is>
-          <t>2026/03/16</t>
-        </is>
-      </c>
-      <c r="M12" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/06</t>
-        </is>
-      </c>
-      <c r="N12" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/10</t>
-        </is>
-      </c>
-      <c r="O12" s="11" t="inlineStr">
-        <is>
-          <t>因首批安排RPL-U Refresh 優先投產，第二波投產因PCB 最快交期落在6/29,加上微步盤點，預計最快7/10 TTM</t>
-        </is>
-      </c>
-      <c r="P12" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>ATS 預計7/1 ASSY，客驗安排7/4 ，7/10 機台入庫</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>1)	MVT Issue，Free DOS下，secure boor enable,不能從U盤啟動&amp;UCSI功能未導入 需微步協調人力加速，確保在7/8前導入對策，</t>
         </is>
       </c>
     </row>
@@ -1422,17 +1425,17 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>24VL</t>
+          <t>26VL</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Modern A14 LE J1M</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>MVT</t>
+          <t>Modern A16 LE J1M</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>ATS</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1473,22 +1476,22 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>2026/07/01</t>
+          <t>2026/07/04</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026/07/10</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>預計7/1 ATS ASSY，DQA 測試Issue 需微步協助在6/29前釐清&amp; 導入對策，</t>
+          <t>因26VL 機構物料7/3 ready，預計7/4 ATS ASSY ，7/13 機台入庫</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>1)	Schedule：MVT Issue，需微步協調人力加速，確保在6/29前釐清Issue及導入對策，AMD  VGA WHQL  driver需在6/26 提供，滿足7/1 ATS start,</t>
+          <t>1)	MVT Issue，Free DOS下，secure boor enable,不能從U盤啟動&amp;UCSI功能未導入 需微步協調人力加速，確保在7/8前導入對策，</t>
         </is>
       </c>
     </row>
@@ -1498,143 +1501,135 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>15Q1</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
+          <t>Cyborg 15 B2VE</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>ARL-H 45W</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 4050 (35W+10W)/ GDDR6 6GB</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>李文欽</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>2026/03/30</t>
-        </is>
-      </c>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
       <c r="J14" s="4" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/06/29</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>2026/05/15</t>
+          <t>2026/06/29</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>2026/07/04</t>
+          <t>2026/07/20</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>因26VL 機構物料7/3 ready，預計7/3 ATS ASSY ，</t>
+          <t>（清白光鍵盤庫存）測試HDI預計7/3完成DQA開始驗證,測試預計２周時間</t>
         </is>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>1)	Schedule：MVT Issue，需微步協調人力加速，確保在6/29前釐清Issue及導入對策，AMD  VGA WHQL  driver需在6/26 提供，滿足7/3 ATS start,</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" hidden="1" outlineLevel="1">
+      <c r="A15" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>15Q1</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Cyborg 15 B2VE</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Cyborg 15 B2VEK</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>ARL-H 45W</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>RTX 4050 (35W+10W)/ GDDR6 6GB</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>李文欽</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>2026/06/24</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr"/>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/20</t>
-        </is>
-      </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr"/>
+      <c r="J15" s="10" t="inlineStr"/>
+      <c r="K15" s="10" t="inlineStr"/>
+      <c r="L15" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>2026/07/31</t>
         </is>
       </c>
-      <c r="O15" s="6" t="inlineStr">
-        <is>
-          <t>（清白光鍵盤庫存）預計下周提供樣機給DQA驗證,測試預計２周時間</t>
-        </is>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
+      <c r="O15" s="12" t="inlineStr">
+        <is>
+          <t>（清日文4區RGB鍵盤庫存）預計7/6 試組機台, DQA預計測試2周時間</t>
+        </is>
+      </c>
+      <c r="P15" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1654,7 +1649,7 @@
           <t>Prestige N16 Spark</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
@@ -1723,80 +1718,80 @@
       </c>
     </row>
     <row r="17" hidden="1" outlineLevel="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>Prestige N16 Flip Spark</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>N1x 80W</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>林晉弘</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>2024/11/25</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>2025/01/20</t>
         </is>
       </c>
-      <c r="J17" s="9" t="inlineStr">
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t>2025/06/25</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K17" s="10" t="inlineStr">
         <is>
           <t>2026/03/12</t>
         </is>
       </c>
-      <c r="L17" s="9" t="inlineStr">
+      <c r="L17" s="10" t="inlineStr">
         <is>
           <t>2026/06/30</t>
         </is>
       </c>
-      <c r="M17" s="9" t="inlineStr">
+      <c r="M17" s="10" t="inlineStr">
         <is>
           <t>2026/07/31</t>
         </is>
       </c>
-      <c r="N17" s="9" t="inlineStr">
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>2026/08/14</t>
         </is>
       </c>
-      <c r="O17" s="11" t="inlineStr">
+      <c r="O17" s="12" t="inlineStr">
         <is>
           <t>MVT測試中</t>
         </is>
       </c>
-      <c r="P17" s="11" t="inlineStr">
+      <c r="P17" s="12" t="inlineStr">
         <is>
           <t>1)MSFT 6/24 release power report，report中power consumption數據與battery life跟廠內DQA及RD有落差，待與MSFT比對測試環境差異，釐清測試結果。
 2)DQA/RD/工廠切換到BSP FD Rev.B與BIOS 049測試中。NV 6/23 release BSP FD ver.C，待BIOS與preload更新後，會再切換新版測試。
@@ -1818,7 +1813,7 @@
           <t>Venture 15 AI+ B3M</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -1871,12 +1866,12 @@
       </c>
       <c r="O18" s="6" t="inlineStr">
         <is>
-          <t>DVT Debug &amp; 測試中</t>
+          <t>MVT備料中</t>
         </is>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>1) 10 gerberout@6/26,schedule暫不影響</t>
+          <t>1) 組裝正式上線時間延後2天, MP時間暫不影響</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1889,7 @@
           <t>Katana 15 HX C14WEK</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -1957,380 +1952,380 @@
       </c>
     </row>
     <row r="20" hidden="1" outlineLevel="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>15T3</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>Katana 15 HX C14WFK</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>RTX 5060</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>2026/04/20</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>2026/06/01</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr"/>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="J20" s="10" t="inlineStr"/>
+      <c r="K20" s="10" t="inlineStr">
         <is>
           <t>2026/07/14</t>
         </is>
       </c>
-      <c r="L20" s="9" t="inlineStr">
+      <c r="L20" s="10" t="inlineStr">
         <is>
           <t>2026/07/30</t>
         </is>
       </c>
-      <c r="M20" s="9" t="inlineStr">
+      <c r="M20" s="10" t="inlineStr">
         <is>
           <t>2026/08/20</t>
         </is>
       </c>
-      <c r="N20" s="9" t="inlineStr">
+      <c r="N20" s="10" t="inlineStr">
         <is>
           <t>2026/08/30</t>
         </is>
       </c>
-      <c r="O20" s="11" t="inlineStr">
+      <c r="O20" s="12" t="inlineStr">
         <is>
           <t>DDR5 sku, DVT測試中,預計7/2 PCB 10 gerberout</t>
         </is>
       </c>
-      <c r="P20" s="11" t="inlineStr">
+      <c r="P20" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="21" hidden="1" outlineLevel="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>15T3</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>Katana 15 HX C14WGK</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>2026/04/20</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>2026/06/01</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr"/>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="J21" s="10" t="inlineStr"/>
+      <c r="K21" s="10" t="inlineStr">
         <is>
           <t>2026/07/14</t>
         </is>
       </c>
-      <c r="L21" s="9" t="inlineStr">
+      <c r="L21" s="10" t="inlineStr">
         <is>
           <t>2026/07/30</t>
         </is>
       </c>
-      <c r="M21" s="9" t="inlineStr">
+      <c r="M21" s="10" t="inlineStr">
         <is>
           <t>2026/08/20</t>
         </is>
       </c>
-      <c r="N21" s="9" t="inlineStr">
+      <c r="N21" s="10" t="inlineStr">
         <is>
           <t>2026/08/30</t>
         </is>
       </c>
-      <c r="O21" s="11" t="inlineStr">
+      <c r="O21" s="12" t="inlineStr">
         <is>
           <t>DDR5 sku, DVT測試中,預計7/2 PCB 10 gerberout</t>
         </is>
       </c>
-      <c r="P21" s="11" t="inlineStr">
+      <c r="P21" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="22" hidden="1" outlineLevel="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>15T3</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>Katana 15 HX C14WEOK</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>2026/05/15</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="J22" s="9" t="inlineStr"/>
-      <c r="K22" s="9" t="inlineStr">
+      <c r="J22" s="10" t="inlineStr"/>
+      <c r="K22" s="10" t="inlineStr">
         <is>
           <t>2026/07/24</t>
         </is>
       </c>
-      <c r="L22" s="9" t="inlineStr">
+      <c r="L22" s="10" t="inlineStr">
         <is>
           <t>2026/08/07</t>
         </is>
       </c>
-      <c r="M22" s="9" t="inlineStr">
+      <c r="M22" s="10" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="N22" s="9" t="inlineStr">
+      <c r="N22" s="10" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O22" s="11" t="inlineStr">
+      <c r="O22" s="12" t="inlineStr">
         <is>
           <t>DDR4 sku, DVT測試中</t>
         </is>
       </c>
-      <c r="P22" s="11" t="inlineStr">
+      <c r="P22" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="23" hidden="1" outlineLevel="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>15T3</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>Katana 15 HX C14WFOK</t>
         </is>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>RTX 5060</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>2026/05/15</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="J23" s="9" t="inlineStr"/>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="J23" s="10" t="inlineStr"/>
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>2026/07/24</t>
         </is>
       </c>
-      <c r="L23" s="9" t="inlineStr">
+      <c r="L23" s="10" t="inlineStr">
         <is>
           <t>2026/08/07</t>
         </is>
       </c>
-      <c r="M23" s="9" t="inlineStr">
+      <c r="M23" s="10" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="N23" s="9" t="inlineStr">
+      <c r="N23" s="10" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O23" s="11" t="inlineStr">
+      <c r="O23" s="12" t="inlineStr">
         <is>
           <t>DDR4 sku, DVT測試中</t>
         </is>
       </c>
-      <c r="P23" s="11" t="inlineStr">
+      <c r="P23" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="24" hidden="1" outlineLevel="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>15T3</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>Katana 15 HX C14WGOK</t>
         </is>
       </c>
-      <c r="D24" s="15" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H24" s="9" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>2026/05/15</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="J24" s="9" t="inlineStr"/>
-      <c r="K24" s="9" t="inlineStr">
+      <c r="J24" s="10" t="inlineStr"/>
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>2026/07/24</t>
         </is>
       </c>
-      <c r="L24" s="9" t="inlineStr">
+      <c r="L24" s="10" t="inlineStr">
         <is>
           <t>2026/08/07</t>
         </is>
       </c>
-      <c r="M24" s="9" t="inlineStr">
+      <c r="M24" s="10" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="N24" s="9" t="inlineStr">
+      <c r="N24" s="10" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O24" s="11" t="inlineStr">
+      <c r="O24" s="12" t="inlineStr">
         <is>
           <t>DDR4 sku, DVT測試中</t>
         </is>
       </c>
-      <c r="P24" s="11" t="inlineStr">
+      <c r="P24" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2350,7 +2345,7 @@
           <t>Cyborg A15 Max C1PWE</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D25" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2403,7 +2398,7 @@
       </c>
       <c r="O25" s="6" t="inlineStr">
         <is>
-          <t>HPT sku:RD已重工3台成APU 180,AMI release PI 1200i RC3@6/29,BIOS RD需儘速提供MSI版本BIOSi進行測試</t>
+          <t>請BIOS RD儘速release PI 1200i RC3給EE/SW進行測試</t>
         </is>
       </c>
       <c r="P25" s="6" t="inlineStr">
@@ -2414,76 +2409,76 @@
       </c>
     </row>
     <row r="26" hidden="1" outlineLevel="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>15TK</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>Cyborg A15 Max C1PWF</t>
         </is>
       </c>
-      <c r="D26" s="15" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>HWK 45W</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>RTX 5060</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>2026/05/28</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>2026/06/26</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr"/>
-      <c r="K26" s="9" t="inlineStr">
+      <c r="J26" s="10" t="inlineStr"/>
+      <c r="K26" s="10" t="inlineStr">
         <is>
           <t>2026/07/17</t>
         </is>
       </c>
-      <c r="L26" s="9" t="inlineStr">
+      <c r="L26" s="10" t="inlineStr">
         <is>
           <t>2026/07/31</t>
         </is>
       </c>
-      <c r="M26" s="9" t="inlineStr">
+      <c r="M26" s="10" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="N26" s="9" t="inlineStr">
+      <c r="N26" s="10" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O26" s="11" t="inlineStr">
-        <is>
-          <t>HPT sku:RD已重工3台成APU 180,AMI release PI 1200i RC3@6/29,BIOS RD需儘速提供MSI版本BIOSi進行測試</t>
-        </is>
-      </c>
-      <c r="P26" s="11" t="inlineStr">
+      <c r="O26" s="12" t="inlineStr">
+        <is>
+          <t>請BIOS RD儘速release PI 1200i RC3給EE/SW進行測試</t>
+        </is>
+      </c>
+      <c r="P26" s="12" t="inlineStr">
         <is>
           <t>1).Schedule:APU 155優先ATS,採購已下單6.5k,以 8 月底 MP為目標,其餘APU sku在9月進行ATS C/R,但AMD PI 1200i NDA release延至6/30與APU 155 PR樣品ETD 延至7/11,已影響 MP 時程,待收到PI code與PR樣品後將依實際測試情況確認是否調整MP時程
 2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
@@ -2491,76 +2486,76 @@
       </c>
     </row>
     <row r="27" hidden="1" outlineLevel="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>15TK</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>Cyborg A15 Max C1PWG</t>
         </is>
       </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>HWK 45W</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G27" s="10" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>2026/05/28</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>2026/06/26</t>
         </is>
       </c>
-      <c r="J27" s="9" t="inlineStr"/>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="J27" s="10" t="inlineStr"/>
+      <c r="K27" s="10" t="inlineStr">
         <is>
           <t>2026/07/17</t>
         </is>
       </c>
-      <c r="L27" s="9" t="inlineStr">
+      <c r="L27" s="10" t="inlineStr">
         <is>
           <t>2026/07/31</t>
         </is>
       </c>
-      <c r="M27" s="9" t="inlineStr">
+      <c r="M27" s="10" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="N27" s="9" t="inlineStr">
+      <c r="N27" s="10" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O27" s="11" t="inlineStr">
-        <is>
-          <t>HPT sku:RD已重工3台成APU 180,AMI release PI 1200i RC3@6/29,BIOS RD需儘速提供MSI版本BIOSi進行測試</t>
-        </is>
-      </c>
-      <c r="P27" s="11" t="inlineStr">
+      <c r="O27" s="12" t="inlineStr">
+        <is>
+          <t>請BIOS RD儘速release PI 1200i RC3給EE/SW進行測試</t>
+        </is>
+      </c>
+      <c r="P27" s="12" t="inlineStr">
         <is>
           <t>1).Schedule:APU 155優先ATS,採購已下單6.5k,以 8 月底 MP為目標,其餘APU sku在9月進行ATS C/R,但AMD PI 1200i NDA release延至6/30與APU 155 PR樣品ETD 延至7/11,已影響 MP 時程,待收到PI code與PR樣品後將依實際測試情況確認是否調整MP時程
 2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
@@ -2568,76 +2563,76 @@
       </c>
     </row>
     <row r="28" hidden="1" outlineLevel="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>15TK</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>Cyborg A15 C1PWE</t>
         </is>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>HWK 45W</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>2026/05/28</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>2026/06/26</t>
         </is>
       </c>
-      <c r="J28" s="9" t="inlineStr"/>
-      <c r="K28" s="9" t="inlineStr">
+      <c r="J28" s="10" t="inlineStr"/>
+      <c r="K28" s="10" t="inlineStr">
         <is>
           <t>2026/07/17</t>
         </is>
       </c>
-      <c r="L28" s="9" t="inlineStr">
+      <c r="L28" s="10" t="inlineStr">
         <is>
           <t>2026/07/31</t>
         </is>
       </c>
-      <c r="M28" s="9" t="inlineStr">
+      <c r="M28" s="10" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="N28" s="9" t="inlineStr">
+      <c r="N28" s="10" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O28" s="11" t="inlineStr">
+      <c r="O28" s="12" t="inlineStr">
         <is>
           <t>HPT sku:RD已重工3台成APU 180,AMI release PI 1200i RC3@6/29,BIOS RD需儘速提供MSI版本BIOSi進行測試</t>
         </is>
       </c>
-      <c r="P28" s="11" t="inlineStr">
+      <c r="P28" s="12" t="inlineStr">
         <is>
           <t>1).Schedule:APU 155優先ATS,採購已下單6.5k,以 8 月底 MP為目標,其餘APU sku在9月進行ATS C/R,但AMD PI 1200i NDA release延至6/30與APU 155 PR樣品ETD 延至7/11,已影響 MP 時程,待收到PI code與PR樣品後將依實際測試情況確認是否調整MP時程
 2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
@@ -2658,7 +2653,7 @@
           <t>Modern 14 LE J3M</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -2711,7 +2706,7 @@
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>Weibu plan 6/29 DVT SMT, 7/1 ASSY--熱管&amp;D件重新開模, 交期7/1</t>
+          <t>Weibu update 7/6 ASSY--受新料交期和盤點影響</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
@@ -2735,7 +2730,7 @@
           <t>Modern 16 LE J3M</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -2788,7 +2783,7 @@
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
-          <t>Weibu plan 6/29 DVT SMT, 7/1 ASSY --熱管重新開模, 交期6/30</t>
+          <t>Weibu update 7/6 ASSY--受新料交期和盤點影響</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
@@ -2804,22 +2799,22 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>14T3</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Prestige N16 Spark C1M</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>EVT</t>
+          <t>Prestige N14 AI+ D1M</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>MVT</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>N1 45W</t>
+          <t>N1 35W</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -2829,7 +2824,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>倪嬌嬌</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2869,13 +2864,13 @@
       </c>
       <c r="O31" s="6" t="inlineStr">
         <is>
-          <t>1)EVT 更新BSP6.1.2  持續驗證中, 對應NV schedule 更新 MVT延到7/20.
-2) NV 更新BSP 時間 Factory Drop Final ETA 10/6 ,需要1周時間完成 HDI+BIOS 更新ATS strat 10/13</t>
+          <t>MVT SMT@7/20--depend on Material ready date作調整</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
+          <t>1) Color plan change: a. 顏色變更至炭黑色 b. D件改噴漆製程
+2)備料：量產交料HQ23, 十一月份交料(MSI wish 10/B交料, 待Samsung確認回復）Leading customers量產交料時間 具體九月份ETD日期還在追蹤中. b. Others order: 需轉型號至HQxx, 十一月份交料</t>
         </is>
       </c>
     </row>
@@ -2885,22 +2880,22 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>14T3</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Prestige N14 Spark D1M</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>MVT</t>
+          <t>Prestige N16 C1M</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>EVT</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>N1 35W</t>
+          <t>N1 45W</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -2910,7 +2905,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>倪嬌嬌</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2950,12 +2945,13 @@
       </c>
       <c r="O32" s="6" t="inlineStr">
         <is>
-          <t>MVT SMT@7/20--depend on Material ready date</t>
+          <t>1)EVT 更新BSP6.2.1  持續驗證中, 對應NV schedule 更新 MVT延到7/20.
+2) NV 更新BSP 時間 Factory Drop Final ETA 10/6 ,需要1周時間完成 HDI+BIOS 更新ATS strat 10/13</t>
         </is>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>1)備料：MP focus on 2.8K panel, for MVT@7/M, 待廠商確認中; for MP: a, 1st lot 1K 數量, 型號HQ15, 九月份交料(同步Leading customers量產交料時間 具體九月份ETD日期還在追蹤中. b. Others order: 需轉型號至HQxx, 十一月份交料</t>
+          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2969,7 @@
           <t>Katana 18 HX A14WEK</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="D33" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3030,7 +3026,7 @@
       </c>
       <c r="O33" s="6" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT PCBA快遞3pcs 6/24到,目前已開機,調撥部分6/25到料供RD測試</t>
+          <t>RPL-HX R + DDR5: DVT 測試中</t>
         </is>
       </c>
       <c r="P33" s="6" t="inlineStr">
@@ -3040,2032 +3036,2032 @@
       </c>
     </row>
     <row r="34" hidden="1" outlineLevel="1">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C34" s="10" t="inlineStr">
         <is>
           <t>Katana 18 HX A14WFK</t>
         </is>
       </c>
-      <c r="D34" s="15" t="inlineStr">
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>RTX 5060</t>
         </is>
       </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="J34" s="9" t="inlineStr">
+      <c r="J34" s="10" t="inlineStr">
         <is>
           <t>2026/08/24</t>
         </is>
       </c>
-      <c r="K34" s="9" t="inlineStr">
+      <c r="K34" s="10" t="inlineStr">
         <is>
           <t>2026/10/12</t>
         </is>
       </c>
-      <c r="L34" s="9" t="inlineStr">
+      <c r="L34" s="10" t="inlineStr">
         <is>
           <t>2026/11/02</t>
         </is>
       </c>
-      <c r="M34" s="9" t="inlineStr">
+      <c r="M34" s="10" t="inlineStr">
         <is>
           <t>2026/11/21</t>
         </is>
       </c>
-      <c r="N34" s="9" t="inlineStr">
+      <c r="N34" s="10" t="inlineStr">
         <is>
           <t>2026/11/30</t>
         </is>
       </c>
-      <c r="O34" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR5: DVT PCBA快遞3pcs 6/24到,目前已開機,調撥部分6/25到料供RD測試</t>
-        </is>
-      </c>
-      <c r="P34" s="11" t="inlineStr">
+      <c r="O34" s="12" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR5: DVT 測試中</t>
+        </is>
+      </c>
+      <c r="P34" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="35" hidden="1" outlineLevel="1">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>Katana 18 HX A14WGK</t>
         </is>
       </c>
-      <c r="D35" s="15" t="inlineStr">
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G35" s="9" t="inlineStr">
+      <c r="G35" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="J35" s="9" t="inlineStr">
+      <c r="J35" s="10" t="inlineStr">
         <is>
           <t>2026/08/24</t>
         </is>
       </c>
-      <c r="K35" s="9" t="inlineStr">
+      <c r="K35" s="10" t="inlineStr">
         <is>
           <t>2026/10/12</t>
         </is>
       </c>
-      <c r="L35" s="9" t="inlineStr">
+      <c r="L35" s="10" t="inlineStr">
         <is>
           <t>2026/11/02</t>
         </is>
       </c>
-      <c r="M35" s="9" t="inlineStr">
+      <c r="M35" s="10" t="inlineStr">
         <is>
           <t>2026/11/21</t>
         </is>
       </c>
-      <c r="N35" s="9" t="inlineStr">
+      <c r="N35" s="10" t="inlineStr">
         <is>
           <t>2026/11/30</t>
         </is>
       </c>
-      <c r="O35" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR5: DVT PCBA快遞3pcs 6/24到,目前已開機,調撥部分6/25到料供RD測試</t>
-        </is>
-      </c>
-      <c r="P35" s="11" t="inlineStr">
+      <c r="O35" s="12" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR5: DVT 測試中</t>
+        </is>
+      </c>
+      <c r="P35" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="36" hidden="1" outlineLevel="1">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>Katana 18 HX A14WEOK</t>
         </is>
       </c>
-      <c r="D36" s="15" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G36" s="9" t="inlineStr">
+      <c r="G36" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H36" s="9" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="I36" s="9" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>2026/06/27</t>
         </is>
       </c>
-      <c r="J36" s="9" t="inlineStr"/>
-      <c r="K36" s="9" t="inlineStr">
+      <c r="J36" s="10" t="inlineStr"/>
+      <c r="K36" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
         </is>
       </c>
-      <c r="L36" s="9" t="inlineStr">
+      <c r="L36" s="10" t="inlineStr">
         <is>
           <t>2026/11/02</t>
         </is>
       </c>
-      <c r="M36" s="9" t="inlineStr">
+      <c r="M36" s="10" t="inlineStr">
         <is>
           <t>2026/11/23</t>
         </is>
       </c>
-      <c r="N36" s="9" t="inlineStr">
+      <c r="N36" s="10" t="inlineStr">
         <is>
           <t>2026/12/02</t>
         </is>
       </c>
-      <c r="O36" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR4: DVT SMT @ 6/30</t>
-        </is>
-      </c>
-      <c r="P36" s="11" t="inlineStr">
+      <c r="O36" s="12" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR4: DVT PCBA 7/2 調撥，預計7/6 RD領取測試</t>
+        </is>
+      </c>
+      <c r="P36" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="37" hidden="1" outlineLevel="1">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="8" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>Katana 18 HX A14WFOK</t>
         </is>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="D37" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>RTX 5060</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="G37" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>2026/06/27</t>
         </is>
       </c>
-      <c r="J37" s="9" t="inlineStr"/>
-      <c r="K37" s="9" t="inlineStr">
+      <c r="J37" s="10" t="inlineStr"/>
+      <c r="K37" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
         </is>
       </c>
-      <c r="L37" s="9" t="inlineStr">
+      <c r="L37" s="10" t="inlineStr">
         <is>
           <t>2026/11/02</t>
         </is>
       </c>
-      <c r="M37" s="9" t="inlineStr">
+      <c r="M37" s="10" t="inlineStr">
         <is>
           <t>2026/11/23</t>
         </is>
       </c>
-      <c r="N37" s="9" t="inlineStr">
+      <c r="N37" s="10" t="inlineStr">
         <is>
           <t>2026/12/02</t>
         </is>
       </c>
-      <c r="O37" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR4: DVT SMT @ 6/30</t>
-        </is>
-      </c>
-      <c r="P37" s="11" t="inlineStr">
+      <c r="O37" s="12" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR4: DVT PCBA 7/2 調撥，預計7/6 RD領取測試</t>
+        </is>
+      </c>
+      <c r="P37" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="38" hidden="1" outlineLevel="1">
-      <c r="A38" s="7" t="n">
+      <c r="A38" s="8" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>Katana 18 HX A14WGOK</t>
         </is>
       </c>
-      <c r="D38" s="15" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G38" s="9" t="inlineStr">
+      <c r="G38" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H38" s="9" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="I38" s="9" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>2026/06/27</t>
         </is>
       </c>
-      <c r="J38" s="9" t="inlineStr"/>
-      <c r="K38" s="9" t="inlineStr">
+      <c r="J38" s="10" t="inlineStr"/>
+      <c r="K38" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
         </is>
       </c>
-      <c r="L38" s="9" t="inlineStr">
+      <c r="L38" s="10" t="inlineStr">
         <is>
           <t>2026/11/02</t>
         </is>
       </c>
-      <c r="M38" s="9" t="inlineStr">
+      <c r="M38" s="10" t="inlineStr">
         <is>
           <t>2026/11/23</t>
         </is>
       </c>
-      <c r="N38" s="9" t="inlineStr">
+      <c r="N38" s="10" t="inlineStr">
         <is>
           <t>2026/12/02</t>
         </is>
       </c>
-      <c r="O38" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR4: DVT SMT @ 6/30</t>
-        </is>
-      </c>
-      <c r="P38" s="11" t="inlineStr">
+      <c r="O38" s="12" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR4: DVT PCBA 7/2 調撥，預計7/6 RD領取測試</t>
+        </is>
+      </c>
+      <c r="P38" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="39" hidden="1" outlineLevel="1">
-      <c r="A39" s="7" t="n">
+      <c r="A39" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>Crosshair 18 Max HX B14WEO</t>
         </is>
       </c>
-      <c r="D39" s="15" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G39" s="9" t="inlineStr">
+      <c r="G39" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H39" s="9" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="I39" s="9" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>2026/06/27</t>
         </is>
       </c>
-      <c r="J39" s="9" t="inlineStr"/>
-      <c r="K39" s="9" t="inlineStr">
+      <c r="J39" s="10" t="inlineStr"/>
+      <c r="K39" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
         </is>
       </c>
-      <c r="L39" s="9" t="inlineStr">
+      <c r="L39" s="10" t="inlineStr">
         <is>
           <t>2026/11/02</t>
         </is>
       </c>
-      <c r="M39" s="9" t="inlineStr">
+      <c r="M39" s="10" t="inlineStr">
         <is>
           <t>2026/11/28</t>
         </is>
       </c>
-      <c r="N39" s="9" t="inlineStr">
+      <c r="N39" s="10" t="inlineStr">
         <is>
           <t>2026/12/07</t>
         </is>
       </c>
-      <c r="O39" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR4: DVT SMT @ 6/30</t>
-        </is>
-      </c>
-      <c r="P39" s="11" t="inlineStr">
+      <c r="O39" s="12" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR4: DVT PCBA 7/2 調撥，預計7/6 RD領取測試</t>
+        </is>
+      </c>
+      <c r="P39" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="40" hidden="1" outlineLevel="1">
-      <c r="A40" s="7" t="n">
+      <c r="A40" s="8" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C40" s="10" t="inlineStr">
         <is>
           <t>Crosshair 18 Max HX B14WFO</t>
         </is>
       </c>
-      <c r="D40" s="15" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>RTX 5060</t>
         </is>
       </c>
-      <c r="G40" s="9" t="inlineStr">
+      <c r="G40" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H40" s="9" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>2026/06/27</t>
         </is>
       </c>
-      <c r="J40" s="9" t="inlineStr"/>
-      <c r="K40" s="9" t="inlineStr">
+      <c r="J40" s="10" t="inlineStr"/>
+      <c r="K40" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
         </is>
       </c>
-      <c r="L40" s="9" t="inlineStr">
+      <c r="L40" s="10" t="inlineStr">
         <is>
           <t>2026/11/02</t>
         </is>
       </c>
-      <c r="M40" s="9" t="inlineStr">
+      <c r="M40" s="10" t="inlineStr">
         <is>
           <t>2026/11/28</t>
         </is>
       </c>
-      <c r="N40" s="9" t="inlineStr">
+      <c r="N40" s="10" t="inlineStr">
         <is>
           <t>2026/12/07</t>
         </is>
       </c>
-      <c r="O40" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR4: DVT SMT @ 6/30</t>
-        </is>
-      </c>
-      <c r="P40" s="11" t="inlineStr">
+      <c r="O40" s="12" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR4: DVT PCBA 7/2 調撥，預計7/6 RD領取測試</t>
+        </is>
+      </c>
+      <c r="P40" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="41" hidden="1" outlineLevel="1">
-      <c r="A41" s="7" t="n">
+      <c r="A41" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C41" s="10" t="inlineStr">
         <is>
           <t>Crosshair 18 Max HX B14WGO</t>
         </is>
       </c>
-      <c r="D41" s="15" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G41" s="9" t="inlineStr">
+      <c r="G41" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H41" s="9" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>2026/06/27</t>
         </is>
       </c>
-      <c r="J41" s="9" t="inlineStr"/>
-      <c r="K41" s="9" t="inlineStr">
+      <c r="J41" s="10" t="inlineStr"/>
+      <c r="K41" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
         </is>
       </c>
-      <c r="L41" s="9" t="inlineStr">
+      <c r="L41" s="10" t="inlineStr">
         <is>
           <t>2026/11/02</t>
         </is>
       </c>
-      <c r="M41" s="9" t="inlineStr">
+      <c r="M41" s="10" t="inlineStr">
         <is>
           <t>2026/11/28</t>
         </is>
       </c>
-      <c r="N41" s="9" t="inlineStr">
+      <c r="N41" s="10" t="inlineStr">
         <is>
           <t>2026/12/07</t>
         </is>
       </c>
-      <c r="O41" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR4: DVT SMT @ 6/30</t>
-        </is>
-      </c>
-      <c r="P41" s="11" t="inlineStr">
+      <c r="O41" s="12" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR4: DVT PCBA 7/2 調撥，預計7/6 RD領取測試</t>
+        </is>
+      </c>
+      <c r="P41" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="42" hidden="1" outlineLevel="1">
-      <c r="A42" s="7" t="n">
+      <c r="A42" s="8" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>Crosshair 18 Max HX B14WGXO</t>
         </is>
       </c>
-      <c r="D42" s="15" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr">
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G42" s="9" t="inlineStr">
+      <c r="G42" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H42" s="9" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="I42" s="9" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>2026/06/27</t>
         </is>
       </c>
-      <c r="J42" s="9" t="inlineStr"/>
-      <c r="K42" s="9" t="inlineStr">
+      <c r="J42" s="10" t="inlineStr"/>
+      <c r="K42" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
         </is>
       </c>
-      <c r="L42" s="9" t="inlineStr">
+      <c r="L42" s="10" t="inlineStr">
         <is>
           <t>2026/11/02</t>
         </is>
       </c>
-      <c r="M42" s="9" t="inlineStr">
+      <c r="M42" s="10" t="inlineStr">
         <is>
           <t>2026/11/28</t>
         </is>
       </c>
-      <c r="N42" s="9" t="inlineStr">
+      <c r="N42" s="10" t="inlineStr">
         <is>
           <t>2026/12/07</t>
         </is>
       </c>
-      <c r="O42" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR4: DVT SMT @ 6/30</t>
-        </is>
-      </c>
-      <c r="P42" s="11" t="inlineStr">
+      <c r="O42" s="12" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR4: DVT PCBA 7/2 調撥，預計7/6 RD領取測試</t>
+        </is>
+      </c>
+      <c r="P42" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="43" hidden="1" outlineLevel="1">
-      <c r="A43" s="7" t="n">
+      <c r="A43" s="8" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>Crosshair 18 Max HX B14WE</t>
         </is>
       </c>
-      <c r="D43" s="15" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
+      <c r="E43" s="10" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G43" s="9" t="inlineStr">
+      <c r="G43" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I43" s="9" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="J43" s="9" t="inlineStr">
+      <c r="J43" s="10" t="inlineStr">
         <is>
           <t>2026/08/24</t>
         </is>
       </c>
-      <c r="K43" s="9" t="inlineStr">
+      <c r="K43" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
         </is>
       </c>
-      <c r="L43" s="9" t="inlineStr">
+      <c r="L43" s="10" t="inlineStr">
         <is>
           <t>2026/11/02</t>
         </is>
       </c>
-      <c r="M43" s="9" t="inlineStr">
+      <c r="M43" s="10" t="inlineStr">
         <is>
           <t>2026/11/28</t>
         </is>
       </c>
-      <c r="N43" s="9" t="inlineStr">
+      <c r="N43" s="10" t="inlineStr">
         <is>
           <t>2026/12/07</t>
         </is>
       </c>
-      <c r="O43" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR5: DVT PCBA快遞3pcs 6/24到,目前已開機,調撥部分6/25到料供RD測試</t>
-        </is>
-      </c>
-      <c r="P43" s="11" t="inlineStr">
+      <c r="O43" s="12" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR5: DVT 測試中</t>
+        </is>
+      </c>
+      <c r="P43" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="44" hidden="1" outlineLevel="1">
-      <c r="A44" s="7" t="n">
+      <c r="A44" s="8" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>Crosshair 18 Max HX B14WF</t>
         </is>
       </c>
-      <c r="D44" s="15" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E44" s="9" t="inlineStr">
+      <c r="E44" s="10" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F44" s="9" t="inlineStr">
+      <c r="F44" s="10" t="inlineStr">
         <is>
           <t>RTX 5060</t>
         </is>
       </c>
-      <c r="G44" s="9" t="inlineStr">
+      <c r="G44" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H44" s="9" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I44" s="9" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="J44" s="9" t="inlineStr">
+      <c r="J44" s="10" t="inlineStr">
         <is>
           <t>2026/08/24</t>
         </is>
       </c>
-      <c r="K44" s="9" t="inlineStr">
+      <c r="K44" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
         </is>
       </c>
-      <c r="L44" s="9" t="inlineStr">
+      <c r="L44" s="10" t="inlineStr">
         <is>
           <t>2026/11/02</t>
         </is>
       </c>
-      <c r="M44" s="9" t="inlineStr">
+      <c r="M44" s="10" t="inlineStr">
         <is>
           <t>2026/11/28</t>
         </is>
       </c>
-      <c r="N44" s="9" t="inlineStr">
+      <c r="N44" s="10" t="inlineStr">
         <is>
           <t>2026/12/07</t>
         </is>
       </c>
-      <c r="O44" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR5: DVT PCBA快遞3pcs 6/24到,目前已開機,調撥部分6/25到料供RD測試</t>
-        </is>
-      </c>
-      <c r="P44" s="11" t="inlineStr">
+      <c r="O44" s="12" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR5: DVT 測試中</t>
+        </is>
+      </c>
+      <c r="P44" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="45" hidden="1" outlineLevel="1">
-      <c r="A45" s="7" t="n">
+      <c r="A45" s="8" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>Crosshair 18 Max HX B14WG</t>
         </is>
       </c>
-      <c r="D45" s="15" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G45" s="9" t="inlineStr">
+      <c r="G45" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H45" s="9" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I45" s="9" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="J45" s="9" t="inlineStr">
+      <c r="J45" s="10" t="inlineStr">
         <is>
           <t>2026/08/24</t>
         </is>
       </c>
-      <c r="K45" s="9" t="inlineStr">
+      <c r="K45" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
         </is>
       </c>
-      <c r="L45" s="9" t="inlineStr">
+      <c r="L45" s="10" t="inlineStr">
         <is>
           <t>2026/11/02</t>
         </is>
       </c>
-      <c r="M45" s="9" t="inlineStr">
+      <c r="M45" s="10" t="inlineStr">
         <is>
           <t>2026/11/28</t>
         </is>
       </c>
-      <c r="N45" s="9" t="inlineStr">
+      <c r="N45" s="10" t="inlineStr">
         <is>
           <t>2026/12/07</t>
         </is>
       </c>
-      <c r="O45" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR5: DVT PCBA快遞3pcs 6/24到,目前已開機,調撥部分6/25到料供RD測試</t>
-        </is>
-      </c>
-      <c r="P45" s="11" t="inlineStr">
+      <c r="O45" s="12" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR5: DVT 測試中</t>
+        </is>
+      </c>
+      <c r="P45" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="46" hidden="1" outlineLevel="1">
-      <c r="A46" s="7" t="n">
+      <c r="A46" s="8" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>Crosshair 18 Max HX B14WGX</t>
         </is>
       </c>
-      <c r="D46" s="15" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E46" s="9" t="inlineStr">
+      <c r="E46" s="10" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F46" s="9" t="inlineStr">
+      <c r="F46" s="10" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G46" s="9" t="inlineStr">
+      <c r="G46" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H46" s="9" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I46" s="9" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="J46" s="9" t="inlineStr">
+      <c r="J46" s="10" t="inlineStr">
         <is>
           <t>2026/08/24</t>
         </is>
       </c>
-      <c r="K46" s="9" t="inlineStr">
+      <c r="K46" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
         </is>
       </c>
-      <c r="L46" s="9" t="inlineStr">
+      <c r="L46" s="10" t="inlineStr">
         <is>
           <t>2026/11/02</t>
         </is>
       </c>
-      <c r="M46" s="9" t="inlineStr">
+      <c r="M46" s="10" t="inlineStr">
         <is>
           <t>2026/11/28</t>
         </is>
       </c>
-      <c r="N46" s="9" t="inlineStr">
+      <c r="N46" s="10" t="inlineStr">
         <is>
           <t>2026/12/07</t>
         </is>
       </c>
-      <c r="O46" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR5: DVT PCBA快遞3pcs 6/24到,目前已開機,調撥部分6/25到料供RD測試</t>
-        </is>
-      </c>
-      <c r="P46" s="11" t="inlineStr">
+      <c r="O46" s="12" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR5: DVT 測試中</t>
+        </is>
+      </c>
+      <c r="P46" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="47" hidden="1" outlineLevel="1">
-      <c r="A47" s="7" t="n">
+      <c r="A47" s="8" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C47" s="10" t="inlineStr">
         <is>
           <t>Crosshair 18 Max HX B2WE</t>
         </is>
       </c>
-      <c r="D47" s="18" t="inlineStr">
+      <c r="D47" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr">
+      <c r="E47" s="10" t="inlineStr">
         <is>
           <t>RPL-HX Next 55W</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
+      <c r="F47" s="10" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G47" s="9" t="inlineStr">
+      <c r="G47" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H47" s="9" t="inlineStr">
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr"/>
-      <c r="J47" s="9" t="inlineStr"/>
-      <c r="K47" s="9" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr"/>
+      <c r="J47" s="10" t="inlineStr"/>
+      <c r="K47" s="10" t="inlineStr">
         <is>
           <t>2026/12/08</t>
         </is>
       </c>
-      <c r="L47" s="9" t="inlineStr">
+      <c r="L47" s="10" t="inlineStr">
         <is>
           <t>2026/12/30</t>
         </is>
       </c>
-      <c r="M47" s="9" t="inlineStr">
+      <c r="M47" s="10" t="inlineStr">
         <is>
           <t>2027/01/19</t>
         </is>
       </c>
-      <c r="N47" s="9" t="inlineStr">
+      <c r="N47" s="10" t="inlineStr">
         <is>
           <t>2027/01/30</t>
         </is>
       </c>
-      <c r="O47" s="11" t="inlineStr">
+      <c r="O47" s="12" t="inlineStr">
         <is>
           <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
-      <c r="P47" s="11" t="inlineStr">
+      <c r="P47" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="48" hidden="1" outlineLevel="1">
-      <c r="A48" s="7" t="n">
+      <c r="A48" s="8" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>Crosshair 18 Max HX B2WEO</t>
         </is>
       </c>
-      <c r="D48" s="18" t="inlineStr">
+      <c r="D48" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E48" s="9" t="inlineStr">
+      <c r="E48" s="10" t="inlineStr">
         <is>
           <t>RPL-HX Next 55W</t>
         </is>
       </c>
-      <c r="F48" s="9" t="inlineStr">
+      <c r="F48" s="10" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G48" s="9" t="inlineStr">
+      <c r="G48" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H48" s="9" t="inlineStr">
+      <c r="H48" s="10" t="inlineStr">
         <is>
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="I48" s="9" t="inlineStr"/>
-      <c r="J48" s="9" t="inlineStr"/>
-      <c r="K48" s="9" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr"/>
+      <c r="J48" s="10" t="inlineStr"/>
+      <c r="K48" s="10" t="inlineStr">
         <is>
           <t>2026/12/08</t>
         </is>
       </c>
-      <c r="L48" s="9" t="inlineStr">
+      <c r="L48" s="10" t="inlineStr">
         <is>
           <t>2026/12/30</t>
         </is>
       </c>
-      <c r="M48" s="9" t="inlineStr">
+      <c r="M48" s="10" t="inlineStr">
         <is>
           <t>2027/01/19</t>
         </is>
       </c>
-      <c r="N48" s="9" t="inlineStr">
+      <c r="N48" s="10" t="inlineStr">
         <is>
           <t>2027/01/30</t>
         </is>
       </c>
-      <c r="O48" s="11" t="inlineStr">
+      <c r="O48" s="12" t="inlineStr">
         <is>
           <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
-      <c r="P48" s="11" t="inlineStr">
+      <c r="P48" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="49" hidden="1" outlineLevel="1">
-      <c r="A49" s="7" t="n">
+      <c r="A49" s="8" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C49" s="10" t="inlineStr">
         <is>
           <t>Crosshair 18 Max HX B2WF</t>
         </is>
       </c>
-      <c r="D49" s="18" t="inlineStr">
+      <c r="D49" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr">
+      <c r="E49" s="10" t="inlineStr">
         <is>
           <t>RPL-HX Next 55W</t>
         </is>
       </c>
-      <c r="F49" s="9" t="inlineStr">
+      <c r="F49" s="10" t="inlineStr">
         <is>
           <t>RTX 5060</t>
         </is>
       </c>
-      <c r="G49" s="9" t="inlineStr">
+      <c r="G49" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H49" s="9" t="inlineStr">
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr"/>
-      <c r="J49" s="9" t="inlineStr"/>
-      <c r="K49" s="9" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr"/>
+      <c r="J49" s="10" t="inlineStr"/>
+      <c r="K49" s="10" t="inlineStr">
         <is>
           <t>2026/12/08</t>
         </is>
       </c>
-      <c r="L49" s="9" t="inlineStr">
+      <c r="L49" s="10" t="inlineStr">
         <is>
           <t>2026/12/30</t>
         </is>
       </c>
-      <c r="M49" s="9" t="inlineStr">
+      <c r="M49" s="10" t="inlineStr">
         <is>
           <t>2027/01/19</t>
         </is>
       </c>
-      <c r="N49" s="9" t="inlineStr">
+      <c r="N49" s="10" t="inlineStr">
         <is>
           <t>2027/01/30</t>
         </is>
       </c>
-      <c r="O49" s="11" t="inlineStr">
+      <c r="O49" s="12" t="inlineStr">
         <is>
           <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
-      <c r="P49" s="11" t="inlineStr">
+      <c r="P49" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="50" hidden="1" outlineLevel="1">
-      <c r="A50" s="7" t="n">
+      <c r="A50" s="8" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C50" s="10" t="inlineStr">
         <is>
           <t>Crosshair 18 Max HX B2WFO</t>
         </is>
       </c>
-      <c r="D50" s="18" t="inlineStr">
+      <c r="D50" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr">
+      <c r="E50" s="10" t="inlineStr">
         <is>
           <t>RPL-HX Next 55W</t>
         </is>
       </c>
-      <c r="F50" s="9" t="inlineStr">
+      <c r="F50" s="10" t="inlineStr">
         <is>
           <t>RTX 5060</t>
         </is>
       </c>
-      <c r="G50" s="9" t="inlineStr">
+      <c r="G50" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H50" s="9" t="inlineStr">
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr"/>
-      <c r="J50" s="9" t="inlineStr"/>
-      <c r="K50" s="9" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr"/>
+      <c r="J50" s="10" t="inlineStr"/>
+      <c r="K50" s="10" t="inlineStr">
         <is>
           <t>2026/12/08</t>
         </is>
       </c>
-      <c r="L50" s="9" t="inlineStr">
+      <c r="L50" s="10" t="inlineStr">
         <is>
           <t>2026/12/30</t>
         </is>
       </c>
-      <c r="M50" s="9" t="inlineStr">
+      <c r="M50" s="10" t="inlineStr">
         <is>
           <t>2027/01/19</t>
         </is>
       </c>
-      <c r="N50" s="9" t="inlineStr">
+      <c r="N50" s="10" t="inlineStr">
         <is>
           <t>2027/01/30</t>
         </is>
       </c>
-      <c r="O50" s="11" t="inlineStr">
+      <c r="O50" s="12" t="inlineStr">
         <is>
           <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
-      <c r="P50" s="11" t="inlineStr">
+      <c r="P50" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="51" hidden="1" outlineLevel="1">
-      <c r="A51" s="7" t="n">
+      <c r="A51" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>Crosshair 18 Max HX B2WG</t>
         </is>
       </c>
-      <c r="D51" s="18" t="inlineStr">
+      <c r="D51" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr">
+      <c r="E51" s="10" t="inlineStr">
         <is>
           <t>RPL-HX Next 55W</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G51" s="9" t="inlineStr">
+      <c r="G51" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H51" s="9" t="inlineStr">
+      <c r="H51" s="10" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I51" s="9" t="inlineStr"/>
-      <c r="J51" s="9" t="inlineStr"/>
-      <c r="K51" s="9" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr"/>
+      <c r="J51" s="10" t="inlineStr"/>
+      <c r="K51" s="10" t="inlineStr">
         <is>
           <t>2026/12/08</t>
         </is>
       </c>
-      <c r="L51" s="9" t="inlineStr">
+      <c r="L51" s="10" t="inlineStr">
         <is>
           <t>2026/12/30</t>
         </is>
       </c>
-      <c r="M51" s="9" t="inlineStr">
+      <c r="M51" s="10" t="inlineStr">
         <is>
           <t>2027/01/19</t>
         </is>
       </c>
-      <c r="N51" s="9" t="inlineStr">
+      <c r="N51" s="10" t="inlineStr">
         <is>
           <t>2027/01/30</t>
         </is>
       </c>
-      <c r="O51" s="11" t="inlineStr">
+      <c r="O51" s="12" t="inlineStr">
         <is>
           <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
-      <c r="P51" s="11" t="inlineStr">
+      <c r="P51" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="52" hidden="1" outlineLevel="1">
-      <c r="A52" s="7" t="n">
+      <c r="A52" s="8" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr">
+      <c r="C52" s="10" t="inlineStr">
         <is>
           <t>Crosshair 18 Max HX B2WGO</t>
         </is>
       </c>
-      <c r="D52" s="18" t="inlineStr">
+      <c r="D52" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E52" s="9" t="inlineStr">
+      <c r="E52" s="10" t="inlineStr">
         <is>
           <t>RPL-HX Next 55W</t>
         </is>
       </c>
-      <c r="F52" s="9" t="inlineStr">
+      <c r="F52" s="10" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G52" s="9" t="inlineStr">
+      <c r="G52" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H52" s="9" t="inlineStr">
+      <c r="H52" s="10" t="inlineStr">
         <is>
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="I52" s="9" t="inlineStr"/>
-      <c r="J52" s="9" t="inlineStr"/>
-      <c r="K52" s="9" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr"/>
+      <c r="J52" s="10" t="inlineStr"/>
+      <c r="K52" s="10" t="inlineStr">
         <is>
           <t>2026/12/08</t>
         </is>
       </c>
-      <c r="L52" s="9" t="inlineStr">
+      <c r="L52" s="10" t="inlineStr">
         <is>
           <t>2026/12/30</t>
         </is>
       </c>
-      <c r="M52" s="9" t="inlineStr">
+      <c r="M52" s="10" t="inlineStr">
         <is>
           <t>2027/01/19</t>
         </is>
       </c>
-      <c r="N52" s="9" t="inlineStr">
+      <c r="N52" s="10" t="inlineStr">
         <is>
           <t>2027/01/30</t>
         </is>
       </c>
-      <c r="O52" s="11" t="inlineStr">
+      <c r="O52" s="12" t="inlineStr">
         <is>
           <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
-      <c r="P52" s="11" t="inlineStr">
+      <c r="P52" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="53" hidden="1" outlineLevel="1">
-      <c r="A53" s="7" t="n">
+      <c r="A53" s="8" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t>Crosshair 18 Max HX B2WGX</t>
         </is>
       </c>
-      <c r="D53" s="18" t="inlineStr">
+      <c r="D53" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E53" s="9" t="inlineStr">
+      <c r="E53" s="10" t="inlineStr">
         <is>
           <t>RPL-HX Next 55W</t>
         </is>
       </c>
-      <c r="F53" s="9" t="inlineStr">
+      <c r="F53" s="10" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G53" s="9" t="inlineStr">
+      <c r="G53" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H53" s="9" t="inlineStr">
+      <c r="H53" s="10" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I53" s="9" t="inlineStr"/>
-      <c r="J53" s="9" t="inlineStr"/>
-      <c r="K53" s="9" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr"/>
+      <c r="J53" s="10" t="inlineStr"/>
+      <c r="K53" s="10" t="inlineStr">
         <is>
           <t>2026/12/08</t>
         </is>
       </c>
-      <c r="L53" s="9" t="inlineStr">
+      <c r="L53" s="10" t="inlineStr">
         <is>
           <t>2026/12/30</t>
         </is>
       </c>
-      <c r="M53" s="9" t="inlineStr">
+      <c r="M53" s="10" t="inlineStr">
         <is>
           <t>2027/01/19</t>
         </is>
       </c>
-      <c r="N53" s="9" t="inlineStr">
+      <c r="N53" s="10" t="inlineStr">
         <is>
           <t>2027/01/30</t>
         </is>
       </c>
-      <c r="O53" s="11" t="inlineStr">
+      <c r="O53" s="12" t="inlineStr">
         <is>
           <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
-      <c r="P53" s="11" t="inlineStr">
+      <c r="P53" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="54" hidden="1" outlineLevel="1">
-      <c r="A54" s="7" t="n">
+      <c r="A54" s="8" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C54" s="9" t="inlineStr">
+      <c r="C54" s="10" t="inlineStr">
         <is>
           <t>Crosshair 18 Max HX B2WGXO</t>
         </is>
       </c>
-      <c r="D54" s="18" t="inlineStr">
+      <c r="D54" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E54" s="9" t="inlineStr">
+      <c r="E54" s="10" t="inlineStr">
         <is>
           <t>RPL-HX Next 55W</t>
         </is>
       </c>
-      <c r="F54" s="9" t="inlineStr">
+      <c r="F54" s="10" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G54" s="9" t="inlineStr">
+      <c r="G54" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H54" s="9" t="inlineStr">
+      <c r="H54" s="10" t="inlineStr">
         <is>
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="I54" s="9" t="inlineStr"/>
-      <c r="J54" s="9" t="inlineStr"/>
-      <c r="K54" s="9" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr"/>
+      <c r="J54" s="10" t="inlineStr"/>
+      <c r="K54" s="10" t="inlineStr">
         <is>
           <t>2026/12/08</t>
         </is>
       </c>
-      <c r="L54" s="9" t="inlineStr">
+      <c r="L54" s="10" t="inlineStr">
         <is>
           <t>2026/12/30</t>
         </is>
       </c>
-      <c r="M54" s="9" t="inlineStr">
+      <c r="M54" s="10" t="inlineStr">
         <is>
           <t>2027/01/19</t>
         </is>
       </c>
-      <c r="N54" s="9" t="inlineStr">
+      <c r="N54" s="10" t="inlineStr">
         <is>
           <t>2027/01/30</t>
         </is>
       </c>
-      <c r="O54" s="11" t="inlineStr">
+      <c r="O54" s="12" t="inlineStr">
         <is>
           <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
-      <c r="P54" s="11" t="inlineStr">
+      <c r="P54" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="55" hidden="1" outlineLevel="1">
-      <c r="A55" s="7" t="n">
+      <c r="A55" s="8" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>Katana 18 HX A2WEK</t>
         </is>
       </c>
-      <c r="D55" s="18" t="inlineStr">
+      <c r="D55" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E55" s="9" t="inlineStr">
+      <c r="E55" s="10" t="inlineStr">
         <is>
           <t>RPL-HX Next 55W</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr">
+      <c r="F55" s="10" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G55" s="9" t="inlineStr">
+      <c r="G55" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H55" s="9" t="inlineStr">
+      <c r="H55" s="10" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I55" s="9" t="inlineStr"/>
-      <c r="J55" s="9" t="inlineStr"/>
-      <c r="K55" s="9" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr"/>
+      <c r="J55" s="10" t="inlineStr"/>
+      <c r="K55" s="10" t="inlineStr">
         <is>
           <t>2026/12/08</t>
         </is>
       </c>
-      <c r="L55" s="9" t="inlineStr">
+      <c r="L55" s="10" t="inlineStr">
         <is>
           <t>2026/12/30</t>
         </is>
       </c>
-      <c r="M55" s="9" t="inlineStr">
+      <c r="M55" s="10" t="inlineStr">
         <is>
           <t>2027/01/19</t>
         </is>
       </c>
-      <c r="N55" s="9" t="inlineStr">
+      <c r="N55" s="10" t="inlineStr">
         <is>
           <t>2027/01/30</t>
         </is>
       </c>
-      <c r="O55" s="11" t="inlineStr">
+      <c r="O55" s="12" t="inlineStr">
         <is>
           <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
-      <c r="P55" s="11" t="inlineStr">
+      <c r="P55" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="56" hidden="1" outlineLevel="1">
-      <c r="A56" s="7" t="n">
+      <c r="A56" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="C56" s="10" t="inlineStr">
         <is>
           <t>Katana 18 HX A2WEOK</t>
         </is>
       </c>
-      <c r="D56" s="18" t="inlineStr">
+      <c r="D56" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E56" s="9" t="inlineStr">
+      <c r="E56" s="10" t="inlineStr">
         <is>
           <t>RPL-HX Next 55W</t>
         </is>
       </c>
-      <c r="F56" s="9" t="inlineStr">
+      <c r="F56" s="10" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G56" s="9" t="inlineStr">
+      <c r="G56" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H56" s="9" t="inlineStr">
+      <c r="H56" s="10" t="inlineStr">
         <is>
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="I56" s="9" t="inlineStr">
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <t>2026/06/27</t>
         </is>
       </c>
-      <c r="J56" s="9" t="inlineStr"/>
-      <c r="K56" s="9" t="inlineStr">
+      <c r="J56" s="10" t="inlineStr"/>
+      <c r="K56" s="10" t="inlineStr">
         <is>
           <t>2026/12/08</t>
         </is>
       </c>
-      <c r="L56" s="9" t="inlineStr">
+      <c r="L56" s="10" t="inlineStr">
         <is>
           <t>2026/12/30</t>
         </is>
       </c>
-      <c r="M56" s="9" t="inlineStr">
+      <c r="M56" s="10" t="inlineStr">
         <is>
           <t>2027/01/19</t>
         </is>
       </c>
-      <c r="N56" s="9" t="inlineStr">
+      <c r="N56" s="10" t="inlineStr">
         <is>
           <t>2027/01/30</t>
         </is>
       </c>
-      <c r="O56" s="11" t="inlineStr">
+      <c r="O56" s="12" t="inlineStr">
         <is>
           <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
-      <c r="P56" s="11" t="inlineStr">
+      <c r="P56" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="57" hidden="1" outlineLevel="1">
-      <c r="A57" s="7" t="n">
+      <c r="A57" s="8" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>Katana 18 HX A2WFK</t>
         </is>
       </c>
-      <c r="D57" s="18" t="inlineStr">
+      <c r="D57" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E57" s="9" t="inlineStr">
+      <c r="E57" s="10" t="inlineStr">
         <is>
           <t>RPL-HX Next 55W</t>
         </is>
       </c>
-      <c r="F57" s="9" t="inlineStr">
+      <c r="F57" s="10" t="inlineStr">
         <is>
           <t>RTX 5060</t>
         </is>
       </c>
-      <c r="G57" s="9" t="inlineStr">
+      <c r="G57" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H57" s="9" t="inlineStr">
+      <c r="H57" s="10" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I57" s="9" t="inlineStr"/>
-      <c r="J57" s="9" t="inlineStr"/>
-      <c r="K57" s="9" t="inlineStr">
+      <c r="I57" s="10" t="inlineStr"/>
+      <c r="J57" s="10" t="inlineStr"/>
+      <c r="K57" s="10" t="inlineStr">
         <is>
           <t>2026/12/08</t>
         </is>
       </c>
-      <c r="L57" s="9" t="inlineStr">
+      <c r="L57" s="10" t="inlineStr">
         <is>
           <t>2026/12/30</t>
         </is>
       </c>
-      <c r="M57" s="9" t="inlineStr">
+      <c r="M57" s="10" t="inlineStr">
         <is>
           <t>2027/01/19</t>
         </is>
       </c>
-      <c r="N57" s="9" t="inlineStr">
+      <c r="N57" s="10" t="inlineStr">
         <is>
           <t>2027/01/30</t>
         </is>
       </c>
-      <c r="O57" s="11" t="inlineStr">
+      <c r="O57" s="12" t="inlineStr">
         <is>
           <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
-      <c r="P57" s="11" t="inlineStr">
+      <c r="P57" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="58" hidden="1" outlineLevel="1">
-      <c r="A58" s="7" t="n">
+      <c r="A58" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B58" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C58" s="10" t="inlineStr">
         <is>
           <t>Katana 18 HX A2WFOK</t>
         </is>
       </c>
-      <c r="D58" s="18" t="inlineStr">
+      <c r="D58" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E58" s="9" t="inlineStr">
+      <c r="E58" s="10" t="inlineStr">
         <is>
           <t>RPL-HX Next 55W</t>
         </is>
       </c>
-      <c r="F58" s="9" t="inlineStr">
+      <c r="F58" s="10" t="inlineStr">
         <is>
           <t>RTX 5060</t>
         </is>
       </c>
-      <c r="G58" s="9" t="inlineStr">
+      <c r="G58" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H58" s="9" t="inlineStr">
+      <c r="H58" s="10" t="inlineStr">
         <is>
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="I58" s="9" t="inlineStr">
+      <c r="I58" s="10" t="inlineStr">
         <is>
           <t>2026/06/27</t>
         </is>
       </c>
-      <c r="J58" s="9" t="inlineStr"/>
-      <c r="K58" s="9" t="inlineStr">
+      <c r="J58" s="10" t="inlineStr"/>
+      <c r="K58" s="10" t="inlineStr">
         <is>
           <t>2026/12/08</t>
         </is>
       </c>
-      <c r="L58" s="9" t="inlineStr">
+      <c r="L58" s="10" t="inlineStr">
         <is>
           <t>2026/12/30</t>
         </is>
       </c>
-      <c r="M58" s="9" t="inlineStr">
+      <c r="M58" s="10" t="inlineStr">
         <is>
           <t>2027/01/19</t>
         </is>
       </c>
-      <c r="N58" s="9" t="inlineStr">
+      <c r="N58" s="10" t="inlineStr">
         <is>
           <t>2027/01/30</t>
         </is>
       </c>
-      <c r="O58" s="11" t="inlineStr">
+      <c r="O58" s="12" t="inlineStr">
         <is>
           <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
-      <c r="P58" s="11" t="inlineStr">
+      <c r="P58" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="59" hidden="1" outlineLevel="1">
-      <c r="A59" s="7" t="n">
+      <c r="A59" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B59" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>Katana 18 HX A2WGK</t>
         </is>
       </c>
-      <c r="D59" s="18" t="inlineStr">
+      <c r="D59" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E59" s="9" t="inlineStr">
+      <c r="E59" s="10" t="inlineStr">
         <is>
           <t>RPL-HX Next 55W</t>
         </is>
       </c>
-      <c r="F59" s="9" t="inlineStr">
+      <c r="F59" s="10" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G59" s="9" t="inlineStr">
+      <c r="G59" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H59" s="9" t="inlineStr">
+      <c r="H59" s="10" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I59" s="9" t="inlineStr"/>
-      <c r="J59" s="9" t="inlineStr"/>
-      <c r="K59" s="9" t="inlineStr">
+      <c r="I59" s="10" t="inlineStr"/>
+      <c r="J59" s="10" t="inlineStr"/>
+      <c r="K59" s="10" t="inlineStr">
         <is>
           <t>2026/12/08</t>
         </is>
       </c>
-      <c r="L59" s="9" t="inlineStr">
+      <c r="L59" s="10" t="inlineStr">
         <is>
           <t>2026/12/30</t>
         </is>
       </c>
-      <c r="M59" s="9" t="inlineStr">
+      <c r="M59" s="10" t="inlineStr">
         <is>
           <t>2027/01/19</t>
         </is>
       </c>
-      <c r="N59" s="9" t="inlineStr">
+      <c r="N59" s="10" t="inlineStr">
         <is>
           <t>2027/01/30</t>
         </is>
       </c>
-      <c r="O59" s="11" t="inlineStr">
+      <c r="O59" s="12" t="inlineStr">
         <is>
           <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
-      <c r="P59" s="11" t="inlineStr">
+      <c r="P59" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="60" hidden="1" outlineLevel="1">
-      <c r="A60" s="7" t="n">
+      <c r="A60" s="8" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B60" s="9" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C60" s="10" t="inlineStr">
         <is>
           <t>Katana 18 HX A2WGOK</t>
         </is>
       </c>
-      <c r="D60" s="18" t="inlineStr">
+      <c r="D60" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E60" s="9" t="inlineStr">
+      <c r="E60" s="10" t="inlineStr">
         <is>
           <t>RPL-HX Next 55W</t>
         </is>
       </c>
-      <c r="F60" s="9" t="inlineStr">
+      <c r="F60" s="10" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G60" s="9" t="inlineStr">
+      <c r="G60" s="10" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H60" s="9" t="inlineStr">
+      <c r="H60" s="10" t="inlineStr">
         <is>
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="I60" s="9" t="inlineStr">
+      <c r="I60" s="10" t="inlineStr">
         <is>
           <t>2026/06/27</t>
         </is>
       </c>
-      <c r="J60" s="9" t="inlineStr"/>
-      <c r="K60" s="9" t="inlineStr">
+      <c r="J60" s="10" t="inlineStr"/>
+      <c r="K60" s="10" t="inlineStr">
         <is>
           <t>2026/12/08</t>
         </is>
       </c>
-      <c r="L60" s="9" t="inlineStr">
+      <c r="L60" s="10" t="inlineStr">
         <is>
           <t>2026/12/30</t>
         </is>
       </c>
-      <c r="M60" s="9" t="inlineStr">
+      <c r="M60" s="10" t="inlineStr">
         <is>
           <t>2027/01/19</t>
         </is>
       </c>
-      <c r="N60" s="9" t="inlineStr">
+      <c r="N60" s="10" t="inlineStr">
         <is>
           <t>2027/01/30</t>
         </is>
       </c>
-      <c r="O60" s="11" t="inlineStr">
+      <c r="O60" s="12" t="inlineStr">
         <is>
           <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
-      <c r="P60" s="11" t="inlineStr">
+      <c r="P60" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5085,9 +5081,9 @@
           <t>Prestige 14 AI</t>
         </is>
       </c>
-      <c r="D61" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
+      <c r="D61" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -5142,7 +5138,7 @@
       </c>
       <c r="O61" s="6" t="inlineStr">
         <is>
-          <t>0A gerberout ：6/26,DVT SMT@7/22</t>
+          <t>DVT SMT@7/22</t>
         </is>
       </c>
       <c r="P61" s="6" t="inlineStr">
@@ -5152,80 +5148,80 @@
       </c>
     </row>
     <row r="62" hidden="1" outlineLevel="1">
-      <c r="A62" s="7" t="n">
+      <c r="A62" s="8" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B62" s="9" t="inlineStr">
         <is>
           <t>14T4</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C62" s="10" t="inlineStr">
         <is>
           <t>Prestige 14 AI+ Flip</t>
         </is>
       </c>
-      <c r="D62" s="18" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E62" s="9" t="inlineStr">
+      <c r="D62" s="16" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
         <is>
           <t>NVL-H 30W</t>
         </is>
       </c>
-      <c r="F62" s="9" t="inlineStr">
+      <c r="F62" s="10" t="inlineStr">
         <is>
           <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
-      <c r="G62" s="9" t="inlineStr">
+      <c r="G62" s="10" t="inlineStr">
         <is>
           <t>朱芳芳</t>
         </is>
       </c>
-      <c r="H62" s="9" t="inlineStr">
+      <c r="H62" s="10" t="inlineStr">
         <is>
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="I62" s="9" t="inlineStr">
+      <c r="I62" s="10" t="inlineStr">
         <is>
           <t>2026/07/22</t>
         </is>
       </c>
-      <c r="J62" s="9" t="inlineStr">
+      <c r="J62" s="10" t="inlineStr">
         <is>
           <t>2026/09/15</t>
         </is>
       </c>
-      <c r="K62" s="9" t="inlineStr">
+      <c r="K62" s="10" t="inlineStr">
         <is>
           <t>2026/11/04</t>
         </is>
       </c>
-      <c r="L62" s="9" t="inlineStr">
+      <c r="L62" s="10" t="inlineStr">
         <is>
           <t>2026/11/20</t>
         </is>
       </c>
-      <c r="M62" s="9" t="inlineStr">
+      <c r="M62" s="10" t="inlineStr">
         <is>
           <t>2026/12/15</t>
         </is>
       </c>
-      <c r="N62" s="9" t="inlineStr">
+      <c r="N62" s="10" t="inlineStr">
         <is>
           <t>2026/12/25</t>
         </is>
       </c>
-      <c r="O62" s="11" t="inlineStr">
-        <is>
-          <t>0A gerberout ：6/26,DVT SMT@7/22</t>
-        </is>
-      </c>
-      <c r="P62" s="11" t="inlineStr">
+      <c r="O62" s="12" t="inlineStr">
+        <is>
+          <t>DVT SMT@7/22</t>
+        </is>
+      </c>
+      <c r="P62" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -5245,9 +5241,9 @@
           <t>Prestige 16 AI+</t>
         </is>
       </c>
-      <c r="D63" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
+      <c r="D63" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -5298,86 +5294,86 @@
       </c>
       <c r="O63" s="6" t="inlineStr">
         <is>
+          <t>DVT SMT@7/22</t>
+        </is>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" hidden="1" outlineLevel="1">
+      <c r="A64" s="8" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>2624</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>Prestige 16 Flip AI+</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>NVL-H 30W</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>朱芳芳</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="I64" s="10" t="inlineStr"/>
+      <c r="J64" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="K64" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/04</t>
+        </is>
+      </c>
+      <c r="L64" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/20</t>
+        </is>
+      </c>
+      <c r="M64" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/15</t>
+        </is>
+      </c>
+      <c r="N64" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/25</t>
+        </is>
+      </c>
+      <c r="O64" s="12" t="inlineStr">
+        <is>
           <t>0A gerberout ：6/26,DVT SMT@7/22</t>
         </is>
       </c>
-      <c r="P63" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" hidden="1" outlineLevel="1">
-      <c r="A64" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>2624</t>
-        </is>
-      </c>
-      <c r="C64" s="9" t="inlineStr">
-        <is>
-          <t>Prestige 16 Flip AI+</t>
-        </is>
-      </c>
-      <c r="D64" s="18" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E64" s="9" t="inlineStr">
-        <is>
-          <t>NVL-H 30W</t>
-        </is>
-      </c>
-      <c r="F64" s="9" t="inlineStr">
-        <is>
-          <t>Intel® Arc™ Graphics</t>
-        </is>
-      </c>
-      <c r="G64" s="9" t="inlineStr">
-        <is>
-          <t>朱芳芳</t>
-        </is>
-      </c>
-      <c r="H64" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/14</t>
-        </is>
-      </c>
-      <c r="I64" s="9" t="inlineStr"/>
-      <c r="J64" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/15</t>
-        </is>
-      </c>
-      <c r="K64" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/04</t>
-        </is>
-      </c>
-      <c r="L64" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/20</t>
-        </is>
-      </c>
-      <c r="M64" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/15</t>
-        </is>
-      </c>
-      <c r="N64" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/25</t>
-        </is>
-      </c>
-      <c r="O64" s="11" t="inlineStr">
-        <is>
-          <t>0A gerberout ：6/26,DVT SMT@7/22</t>
-        </is>
-      </c>
-      <c r="P64" s="11" t="inlineStr">
+      <c r="P64" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -5397,7 +5393,7 @@
           <t>Prestige 13 AI+ A4M</t>
         </is>
       </c>
-      <c r="D65" s="16" t="inlineStr">
+      <c r="D65" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5469,7 +5465,7 @@
           <t>Stealth 16 AI+ B4WI</t>
         </is>
       </c>
-      <c r="D66" s="16" t="inlineStr">
+      <c r="D66" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5526,7 +5522,7 @@
       </c>
       <c r="O66" s="6" t="inlineStr">
         <is>
-          <t>0M layout中，预计6/30 gerber out</t>
+          <t>0M gerber out@ 6/30</t>
         </is>
       </c>
       <c r="P66" s="6" t="inlineStr">
@@ -5536,160 +5532,160 @@
       </c>
     </row>
     <row r="67" hidden="1" outlineLevel="1">
-      <c r="A67" s="7" t="n">
+      <c r="A67" s="8" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B67" s="9" t="inlineStr">
         <is>
           <t>2633</t>
         </is>
       </c>
-      <c r="C67" s="9" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t>Stealth 16 AI+ B4WH</t>
         </is>
       </c>
-      <c r="D67" s="18" t="inlineStr">
+      <c r="D67" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E67" s="9" t="inlineStr">
+      <c r="E67" s="10" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F67" s="9" t="inlineStr">
+      <c r="F67" s="10" t="inlineStr">
         <is>
           <t>RTX 5070Ti</t>
         </is>
       </c>
-      <c r="G67" s="9" t="inlineStr">
+      <c r="G67" s="10" t="inlineStr">
         <is>
           <t>朱欣怡</t>
         </is>
       </c>
-      <c r="H67" s="9" t="inlineStr">
+      <c r="H67" s="10" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I67" s="9" t="inlineStr">
+      <c r="I67" s="10" t="inlineStr">
         <is>
           <t>2026/07/22</t>
         </is>
       </c>
-      <c r="J67" s="9" t="inlineStr">
+      <c r="J67" s="10" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K67" s="9" t="inlineStr">
+      <c r="K67" s="10" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L67" s="9" t="inlineStr">
+      <c r="L67" s="10" t="inlineStr">
         <is>
           <t>2026/11/30</t>
         </is>
       </c>
-      <c r="M67" s="9" t="inlineStr">
+      <c r="M67" s="10" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N67" s="9" t="inlineStr">
+      <c r="N67" s="10" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O67" s="11" t="inlineStr">
-        <is>
-          <t>0M layout中，预计6/30 gerber out</t>
-        </is>
-      </c>
-      <c r="P67" s="11" t="inlineStr">
+      <c r="O67" s="12" t="inlineStr">
+        <is>
+          <t>0M gerber out@ 6/30</t>
+        </is>
+      </c>
+      <c r="P67" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="68" hidden="1" outlineLevel="1">
-      <c r="A68" s="7" t="n">
+      <c r="A68" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B68" s="9" t="inlineStr">
         <is>
           <t>2633</t>
         </is>
       </c>
-      <c r="C68" s="9" t="inlineStr">
+      <c r="C68" s="10" t="inlineStr">
         <is>
           <t>Stealth 16 AI+ B4WJ</t>
         </is>
       </c>
-      <c r="D68" s="18" t="inlineStr">
+      <c r="D68" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E68" s="9" t="inlineStr">
+      <c r="E68" s="10" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F68" s="9" t="inlineStr">
+      <c r="F68" s="10" t="inlineStr">
         <is>
           <t>RTX 5090</t>
         </is>
       </c>
-      <c r="G68" s="9" t="inlineStr">
+      <c r="G68" s="10" t="inlineStr">
         <is>
           <t>朱欣怡</t>
         </is>
       </c>
-      <c r="H68" s="9" t="inlineStr">
+      <c r="H68" s="10" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I68" s="9" t="inlineStr">
+      <c r="I68" s="10" t="inlineStr">
         <is>
           <t>2026/07/22</t>
         </is>
       </c>
-      <c r="J68" s="9" t="inlineStr">
+      <c r="J68" s="10" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K68" s="9" t="inlineStr">
+      <c r="K68" s="10" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L68" s="9" t="inlineStr">
+      <c r="L68" s="10" t="inlineStr">
         <is>
           <t>2026/11/30</t>
         </is>
       </c>
-      <c r="M68" s="9" t="inlineStr">
+      <c r="M68" s="10" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N68" s="9" t="inlineStr">
+      <c r="N68" s="10" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O68" s="11" t="inlineStr">
-        <is>
-          <t>0M layout中，预计6/30 gerber out</t>
-        </is>
-      </c>
-      <c r="P68" s="11" t="inlineStr">
+      <c r="O68" s="12" t="inlineStr">
+        <is>
+          <t>0M gerber out@ 6/30</t>
+        </is>
+      </c>
+      <c r="P68" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -5709,7 +5705,7 @@
           <t>Stealth 16 AI+ B4WE</t>
         </is>
       </c>
-      <c r="D69" s="16" t="inlineStr">
+      <c r="D69" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5777,80 +5773,80 @@
       </c>
     </row>
     <row r="70" hidden="1" outlineLevel="1">
-      <c r="A70" s="7" t="n">
+      <c r="A70" s="8" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B70" s="9" t="inlineStr">
         <is>
           <t>2634</t>
         </is>
       </c>
-      <c r="C70" s="9" t="inlineStr">
+      <c r="C70" s="10" t="inlineStr">
         <is>
           <t>Stealth 16 AI+ B4WF</t>
         </is>
       </c>
-      <c r="D70" s="18" t="inlineStr">
+      <c r="D70" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E70" s="9" t="inlineStr">
+      <c r="E70" s="10" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F70" s="9" t="inlineStr">
+      <c r="F70" s="10" t="inlineStr">
         <is>
           <t>RTX 5060</t>
         </is>
       </c>
-      <c r="G70" s="9" t="inlineStr">
+      <c r="G70" s="10" t="inlineStr">
         <is>
           <t>賴雪鳳</t>
         </is>
       </c>
-      <c r="H70" s="9" t="inlineStr">
+      <c r="H70" s="10" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I70" s="9" t="inlineStr">
+      <c r="I70" s="10" t="inlineStr">
         <is>
           <t>2026/08/07</t>
         </is>
       </c>
-      <c r="J70" s="9" t="inlineStr">
+      <c r="J70" s="10" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K70" s="9" t="inlineStr">
+      <c r="K70" s="10" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L70" s="9" t="inlineStr">
+      <c r="L70" s="10" t="inlineStr">
         <is>
           <t>2026/11/27</t>
         </is>
       </c>
-      <c r="M70" s="9" t="inlineStr">
+      <c r="M70" s="10" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N70" s="9" t="inlineStr">
+      <c r="N70" s="10" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O70" s="11" t="inlineStr">
+      <c r="O70" s="12" t="inlineStr">
         <is>
           <t>0A layout start 6/8-7/17</t>
         </is>
       </c>
-      <c r="P70" s="11" t="inlineStr">
+      <c r="P70" s="12" t="inlineStr">
         <is>
           <t>1)NV VBIOS 驗證時間6周
 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
@@ -5858,80 +5854,80 @@
       </c>
     </row>
     <row r="71" hidden="1" outlineLevel="1">
-      <c r="A71" s="7" t="n">
+      <c r="A71" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B71" s="9" t="inlineStr">
         <is>
           <t>2634</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="C71" s="10" t="inlineStr">
         <is>
           <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
         </is>
       </c>
-      <c r="D71" s="18" t="inlineStr">
+      <c r="D71" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E71" s="9" t="inlineStr">
+      <c r="E71" s="10" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F71" s="9" t="inlineStr">
+      <c r="F71" s="10" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G71" s="9" t="inlineStr">
+      <c r="G71" s="10" t="inlineStr">
         <is>
           <t>賴雪鳳</t>
         </is>
       </c>
-      <c r="H71" s="9" t="inlineStr">
+      <c r="H71" s="10" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I71" s="9" t="inlineStr">
+      <c r="I71" s="10" t="inlineStr">
         <is>
           <t>2026/08/07</t>
         </is>
       </c>
-      <c r="J71" s="9" t="inlineStr">
+      <c r="J71" s="10" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K71" s="9" t="inlineStr">
+      <c r="K71" s="10" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L71" s="9" t="inlineStr">
+      <c r="L71" s="10" t="inlineStr">
         <is>
           <t>2026/11/27</t>
         </is>
       </c>
-      <c r="M71" s="9" t="inlineStr">
+      <c r="M71" s="10" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N71" s="9" t="inlineStr">
+      <c r="N71" s="10" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O71" s="11" t="inlineStr">
+      <c r="O71" s="12" t="inlineStr">
         <is>
           <t>0A layout start 6/8-7/17</t>
         </is>
       </c>
-      <c r="P71" s="11" t="inlineStr">
+      <c r="P71" s="12" t="inlineStr">
         <is>
           <t>1)NV VBIOS 驗證時間6周
 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
@@ -5939,80 +5935,80 @@
       </c>
     </row>
     <row r="72" hidden="1" outlineLevel="1">
-      <c r="A72" s="7" t="n">
+      <c r="A72" s="8" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B72" s="9" t="inlineStr">
         <is>
           <t>2634</t>
         </is>
       </c>
-      <c r="C72" s="9" t="inlineStr">
+      <c r="C72" s="10" t="inlineStr">
         <is>
           <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
         </is>
       </c>
-      <c r="D72" s="18" t="inlineStr">
+      <c r="D72" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E72" s="9" t="inlineStr">
+      <c r="E72" s="10" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F72" s="9" t="inlineStr">
+      <c r="F72" s="10" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G72" s="9" t="inlineStr">
+      <c r="G72" s="10" t="inlineStr">
         <is>
           <t>賴雪鳳</t>
         </is>
       </c>
-      <c r="H72" s="9" t="inlineStr">
+      <c r="H72" s="10" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I72" s="9" t="inlineStr">
+      <c r="I72" s="10" t="inlineStr">
         <is>
           <t>2026/08/07</t>
         </is>
       </c>
-      <c r="J72" s="9" t="inlineStr">
+      <c r="J72" s="10" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K72" s="9" t="inlineStr">
+      <c r="K72" s="10" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L72" s="9" t="inlineStr">
+      <c r="L72" s="10" t="inlineStr">
         <is>
           <t>2026/11/27</t>
         </is>
       </c>
-      <c r="M72" s="9" t="inlineStr">
+      <c r="M72" s="10" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N72" s="9" t="inlineStr">
+      <c r="N72" s="10" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O72" s="11" t="inlineStr">
+      <c r="O72" s="12" t="inlineStr">
         <is>
           <t>0A layout start 6/8-7/17</t>
         </is>
       </c>
-      <c r="P72" s="11" t="inlineStr">
+      <c r="P72" s="12" t="inlineStr">
         <is>
           <t>1)NV VBIOS 驗證時間6周
 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
@@ -6033,9 +6029,9 @@
           <t>Raider 16 Max HX B4WH</t>
         </is>
       </c>
-      <c r="D73" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
+      <c r="D73" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -6090,7 +6086,7 @@
       </c>
       <c r="O73" s="6" t="inlineStr">
         <is>
-          <t>0M layout中，预计6/29 gerber out</t>
+          <t>6/29 gerber out，预计7/27 DVT打板</t>
         </is>
       </c>
       <c r="P73" s="6" t="inlineStr">
@@ -6100,320 +6096,320 @@
       </c>
     </row>
     <row r="74" hidden="1" outlineLevel="1">
-      <c r="A74" s="7" t="n">
+      <c r="A74" s="8" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B74" s="9" t="inlineStr">
         <is>
           <t>2654</t>
         </is>
       </c>
-      <c r="C74" s="9" t="inlineStr">
+      <c r="C74" s="10" t="inlineStr">
         <is>
           <t>Raider 16 Max HX B4WI</t>
         </is>
       </c>
-      <c r="D74" s="18" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E74" s="9" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F74" s="9" t="inlineStr">
+      <c r="F74" s="10" t="inlineStr">
         <is>
           <t>RTX 5080</t>
         </is>
       </c>
-      <c r="G74" s="9" t="inlineStr">
+      <c r="G74" s="10" t="inlineStr">
         <is>
           <t>吳美芳</t>
         </is>
       </c>
-      <c r="H74" s="9" t="inlineStr">
+      <c r="H74" s="10" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I74" s="9" t="inlineStr">
+      <c r="I74" s="10" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J74" s="9" t="inlineStr">
+      <c r="J74" s="10" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K74" s="9" t="inlineStr">
+      <c r="K74" s="10" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L74" s="9" t="inlineStr">
+      <c r="L74" s="10" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M74" s="9" t="inlineStr">
+      <c r="M74" s="10" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N74" s="9" t="inlineStr">
+      <c r="N74" s="10" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O74" s="11" t="inlineStr">
-        <is>
-          <t>0M layout中,预计6/29 gerber out</t>
-        </is>
-      </c>
-      <c r="P74" s="11" t="inlineStr">
+      <c r="O74" s="12" t="inlineStr">
+        <is>
+          <t>6/29 gerber out，预计7/27 DVT打板</t>
+        </is>
+      </c>
+      <c r="P74" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="75" hidden="1" outlineLevel="1">
-      <c r="A75" s="7" t="n">
+      <c r="A75" s="8" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B75" s="9" t="inlineStr">
         <is>
           <t>2654</t>
         </is>
       </c>
-      <c r="C75" s="9" t="inlineStr">
+      <c r="C75" s="10" t="inlineStr">
         <is>
           <t>Raider 16 Max HX B4WJ</t>
         </is>
       </c>
-      <c r="D75" s="18" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E75" s="9" t="inlineStr">
+      <c r="D75" s="16" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F75" s="9" t="inlineStr">
+      <c r="F75" s="10" t="inlineStr">
         <is>
           <t>RTX 5090</t>
         </is>
       </c>
-      <c r="G75" s="9" t="inlineStr">
+      <c r="G75" s="10" t="inlineStr">
         <is>
           <t>吳美芳</t>
         </is>
       </c>
-      <c r="H75" s="9" t="inlineStr">
+      <c r="H75" s="10" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I75" s="9" t="inlineStr">
+      <c r="I75" s="10" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J75" s="9" t="inlineStr">
+      <c r="J75" s="10" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K75" s="9" t="inlineStr">
+      <c r="K75" s="10" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L75" s="9" t="inlineStr">
+      <c r="L75" s="10" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M75" s="9" t="inlineStr">
+      <c r="M75" s="10" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N75" s="9" t="inlineStr">
+      <c r="N75" s="10" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O75" s="11" t="inlineStr">
-        <is>
-          <t>0M layout中,预计6/29 gerber out</t>
-        </is>
-      </c>
-      <c r="P75" s="11" t="inlineStr">
+      <c r="O75" s="12" t="inlineStr">
+        <is>
+          <t>6/29 gerber out，预计7/27 DVT打板</t>
+        </is>
+      </c>
+      <c r="P75" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="76" hidden="1" outlineLevel="1">
-      <c r="A76" s="7" t="n">
+      <c r="A76" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B76" s="9" t="inlineStr">
         <is>
           <t>2654</t>
         </is>
       </c>
-      <c r="C76" s="9" t="inlineStr">
+      <c r="C76" s="10" t="inlineStr">
         <is>
           <t>Raider 16  HX B4WH</t>
         </is>
       </c>
-      <c r="D76" s="18" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E76" s="9" t="inlineStr">
+      <c r="D76" s="16" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F76" s="9" t="inlineStr">
+      <c r="F76" s="10" t="inlineStr">
         <is>
           <t>RTX 5070Ti</t>
         </is>
       </c>
-      <c r="G76" s="9" t="inlineStr">
+      <c r="G76" s="10" t="inlineStr">
         <is>
           <t>吳美芳</t>
         </is>
       </c>
-      <c r="H76" s="9" t="inlineStr">
+      <c r="H76" s="10" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I76" s="9" t="inlineStr">
+      <c r="I76" s="10" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J76" s="9" t="inlineStr">
+      <c r="J76" s="10" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K76" s="9" t="inlineStr">
+      <c r="K76" s="10" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L76" s="9" t="inlineStr">
+      <c r="L76" s="10" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M76" s="9" t="inlineStr">
+      <c r="M76" s="10" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N76" s="9" t="inlineStr">
+      <c r="N76" s="10" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O76" s="11" t="inlineStr">
-        <is>
-          <t>0M layout中，预计6/29 gerber out</t>
-        </is>
-      </c>
-      <c r="P76" s="11" t="inlineStr">
+      <c r="O76" s="12" t="inlineStr">
+        <is>
+          <t>6/29 gerber out，预计7/27 DVT打板</t>
+        </is>
+      </c>
+      <c r="P76" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
     <row r="77" hidden="1" outlineLevel="1">
-      <c r="A77" s="7" t="n">
+      <c r="A77" s="8" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B77" s="9" t="inlineStr">
         <is>
           <t>2654</t>
         </is>
       </c>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="C77" s="10" t="inlineStr">
         <is>
           <t>Raider 16  HX B4WI</t>
         </is>
       </c>
-      <c r="D77" s="18" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E77" s="9" t="inlineStr">
+      <c r="D77" s="16" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F77" s="9" t="inlineStr">
+      <c r="F77" s="10" t="inlineStr">
         <is>
           <t>RTX 5080</t>
         </is>
       </c>
-      <c r="G77" s="9" t="inlineStr">
+      <c r="G77" s="10" t="inlineStr">
         <is>
           <t>吳美芳</t>
         </is>
       </c>
-      <c r="H77" s="9" t="inlineStr">
+      <c r="H77" s="10" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I77" s="9" t="inlineStr">
+      <c r="I77" s="10" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J77" s="9" t="inlineStr">
+      <c r="J77" s="10" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K77" s="9" t="inlineStr">
+      <c r="K77" s="10" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L77" s="9" t="inlineStr">
+      <c r="L77" s="10" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M77" s="9" t="inlineStr">
+      <c r="M77" s="10" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N77" s="9" t="inlineStr">
+      <c r="N77" s="10" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O77" s="11" t="inlineStr">
-        <is>
-          <t>0M layout中，预计6/29 gerber out</t>
-        </is>
-      </c>
-      <c r="P77" s="11" t="inlineStr">
+      <c r="O77" s="12" t="inlineStr">
+        <is>
+          <t>6/29 gerber out，预计7/27 DVT打板</t>
+        </is>
+      </c>
+      <c r="P77" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -6433,7 +6429,7 @@
           <t>Crosshair 16 Max HX E4WEK</t>
         </is>
       </c>
-      <c r="D78" s="16" t="inlineStr">
+      <c r="D78" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6490,252 +6486,252 @@
       </c>
       <c r="O78" s="6" t="inlineStr">
         <is>
-          <t>0A layout中</t>
+          <t>0A 7/3 gerber out</t>
         </is>
       </c>
       <c r="P78" s="6" t="inlineStr">
         <is>
-          <t>plan 7/3 gerber out，比預期 delay 4d,對後續schedule無影響</t>
+          <t>na</t>
         </is>
       </c>
     </row>
     <row r="79" hidden="1" outlineLevel="1">
-      <c r="A79" s="7" t="n">
+      <c r="A79" s="8" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B79" s="9" t="inlineStr">
         <is>
           <t>2655</t>
         </is>
       </c>
-      <c r="C79" s="9" t="inlineStr">
+      <c r="C79" s="10" t="inlineStr">
         <is>
           <t>Crosshair 16 Max HX E4WFK</t>
         </is>
       </c>
-      <c r="D79" s="18" t="inlineStr">
+      <c r="D79" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E79" s="9" t="inlineStr">
+      <c r="E79" s="10" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F79" s="9" t="inlineStr">
+      <c r="F79" s="10" t="inlineStr">
         <is>
           <t>RTX 5060</t>
         </is>
       </c>
-      <c r="G79" s="9" t="inlineStr">
+      <c r="G79" s="10" t="inlineStr">
         <is>
           <t>鮑佩佩</t>
         </is>
       </c>
-      <c r="H79" s="9" t="inlineStr">
+      <c r="H79" s="10" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I79" s="9" t="inlineStr">
+      <c r="I79" s="10" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J79" s="9" t="inlineStr">
+      <c r="J79" s="10" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K79" s="9" t="inlineStr">
+      <c r="K79" s="10" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L79" s="9" t="inlineStr">
+      <c r="L79" s="10" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M79" s="9" t="inlineStr">
+      <c r="M79" s="10" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N79" s="9" t="inlineStr">
+      <c r="N79" s="10" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O79" s="11" t="inlineStr">
-        <is>
-          <t>0A layout中</t>
-        </is>
-      </c>
-      <c r="P79" s="11" t="inlineStr">
-        <is>
-          <t>plan 7/3 gerber out，比預期 delay 4d,對後續schedule無影響</t>
+      <c r="O79" s="12" t="inlineStr">
+        <is>
+          <t>0A 7/3 gerber out</t>
+        </is>
+      </c>
+      <c r="P79" s="12" t="inlineStr">
+        <is>
+          <t>na</t>
         </is>
       </c>
     </row>
     <row r="80" hidden="1" outlineLevel="1">
-      <c r="A80" s="7" t="n">
+      <c r="A80" s="8" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B80" s="9" t="inlineStr">
         <is>
           <t>2655</t>
         </is>
       </c>
-      <c r="C80" s="9" t="inlineStr">
+      <c r="C80" s="10" t="inlineStr">
         <is>
           <t>Crosshair 16 Max HX E4WGK</t>
         </is>
       </c>
-      <c r="D80" s="18" t="inlineStr">
+      <c r="D80" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E80" s="9" t="inlineStr">
+      <c r="E80" s="10" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F80" s="9" t="inlineStr">
+      <c r="F80" s="10" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G80" s="9" t="inlineStr">
+      <c r="G80" s="10" t="inlineStr">
         <is>
           <t>鮑佩佩</t>
         </is>
       </c>
-      <c r="H80" s="9" t="inlineStr">
+      <c r="H80" s="10" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I80" s="9" t="inlineStr">
+      <c r="I80" s="10" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J80" s="9" t="inlineStr">
+      <c r="J80" s="10" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K80" s="9" t="inlineStr">
+      <c r="K80" s="10" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L80" s="9" t="inlineStr">
+      <c r="L80" s="10" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M80" s="9" t="inlineStr">
+      <c r="M80" s="10" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N80" s="9" t="inlineStr">
+      <c r="N80" s="10" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O80" s="11" t="inlineStr">
-        <is>
-          <t>GN22-X6 8GB SKU,0A layout中</t>
-        </is>
-      </c>
-      <c r="P80" s="11" t="inlineStr">
-        <is>
-          <t>plan 7/3 gerber out，比預期 delay 4d,對後續schedule無影響</t>
+      <c r="O80" s="12" t="inlineStr">
+        <is>
+          <t>GN22-X6 8GB SKU,0A 7/3 gerber out</t>
+        </is>
+      </c>
+      <c r="P80" s="12" t="inlineStr">
+        <is>
+          <t>na</t>
         </is>
       </c>
     </row>
     <row r="81" hidden="1" outlineLevel="1">
-      <c r="A81" s="7" t="n">
+      <c r="A81" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B81" s="9" t="inlineStr">
         <is>
           <t>2655</t>
         </is>
       </c>
-      <c r="C81" s="9" t="inlineStr">
+      <c r="C81" s="10" t="inlineStr">
         <is>
           <t>Crosshair 16 Max HX E4WGXK</t>
         </is>
       </c>
-      <c r="D81" s="18" t="inlineStr">
+      <c r="D81" s="14" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E81" s="9" t="inlineStr">
+      <c r="E81" s="10" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F81" s="9" t="inlineStr">
+      <c r="F81" s="10" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G81" s="9" t="inlineStr">
+      <c r="G81" s="10" t="inlineStr">
         <is>
           <t>鮑佩佩</t>
         </is>
       </c>
-      <c r="H81" s="9" t="inlineStr">
+      <c r="H81" s="10" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I81" s="9" t="inlineStr">
+      <c r="I81" s="10" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J81" s="9" t="inlineStr">
+      <c r="J81" s="10" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K81" s="9" t="inlineStr">
+      <c r="K81" s="10" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L81" s="9" t="inlineStr">
+      <c r="L81" s="10" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M81" s="9" t="inlineStr">
+      <c r="M81" s="10" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N81" s="9" t="inlineStr">
+      <c r="N81" s="10" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O81" s="11" t="inlineStr">
-        <is>
-          <t>GN22-X6 12GB SKU, 0A layout中</t>
-        </is>
-      </c>
-      <c r="P81" s="11" t="inlineStr">
-        <is>
-          <t>plan 7/3 gerber out，比預期 delay 4d,對後續schedule無影響</t>
+      <c r="O81" s="12" t="inlineStr">
+        <is>
+          <t>GN22-X6 12GB SKU,0A 7/3 gerber out</t>
+        </is>
+      </c>
+      <c r="P81" s="12" t="inlineStr">
+        <is>
+          <t>na</t>
         </is>
       </c>
     </row>

--- a/npi_dashboard.xlsx
+++ b/npi_dashboard.xlsx
@@ -52,12 +52,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000B0F0"/>
+      <color rgb="007030A0"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="007030A0"/>
+      <color rgb="0000B0F0"/>
       <sz val="10"/>
     </font>
     <font>
@@ -139,19 +139,19 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1509,9 +1509,9 @@
           <t>Cyborg 15 B2VEK</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>Design</t>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>MVT</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -1743,7 +1743,7 @@
           <t>Venture 15 AI+ B3M</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -1819,7 +1819,7 @@
           <t>Katana 15 HX C14WEK</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -1895,7 +1895,7 @@
           <t>Katana 15 HX C14WFK</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -1971,7 +1971,7 @@
           <t>Katana 15 HX C14WGK</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2047,7 +2047,7 @@
           <t>Katana 15 HX C14WEOK</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2123,7 +2123,7 @@
           <t>Katana 15 HX C14WFOK</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2199,7 +2199,7 @@
           <t>Katana 15 HX C14WGOK</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2275,7 +2275,7 @@
           <t>Modern 14 LE J3M</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -2352,7 +2352,7 @@
           <t>Modern 16 LE J3M</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -2429,7 +2429,7 @@
           <t>Cyborg A15 Max C1PWE</t>
         </is>
       </c>
-      <c r="D26" s="15" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="O26" s="6" t="inlineStr">
         <is>
-          <t>HPT sku: 目前測試有AMD Graphics驅動無法安裝/TP沒功能/LAN 設備丢失等問題, 麻煩RD盡快釐清</t>
+          <t>HPT sku: 目前AMD Graphics驅動無法安裝/TP沒功能, 請RD儘速釐清</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
@@ -2507,7 +2507,7 @@
           <t>Cyborg A15 Max C1PWF</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D27" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>HPT sku: 目前測試有AMD Graphics驅動無法安裝/TP沒功能/LAN 設備丢失等問題, 麻煩RD盡快釐清</t>
+          <t>HPT sku: 目前AMD Graphics驅動無法安裝/TP沒功能, 請RD儘速釐清</t>
         </is>
       </c>
       <c r="P27" s="11" t="inlineStr">
@@ -2585,7 +2585,7 @@
           <t>Cyborg A15 Max C1PWG</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="O28" s="11" t="inlineStr">
         <is>
-          <t>HPT sku: 目前測試有AMD Graphics驅動無法安裝/TP沒功能/LAN 設備丢失等問題, 麻煩RD盡快釐清</t>
+          <t>HPT sku: 目前AMD Graphics驅動無法安裝/TP沒功能, 請RD儘速釐清</t>
         </is>
       </c>
       <c r="P28" s="11" t="inlineStr">
@@ -2663,7 +2663,7 @@
           <t>Cyborg A15 C1PWE</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D29" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>HPT sku: 目前測試有AMD Graphics驅動無法安裝/TP沒功能/LAN 設備丢失等問題, 麻煩RD盡快釐清</t>
+          <t>HPT sku: 目前AMD Graphics驅動無法安裝/TP沒功能, 請RD儘速釐清</t>
         </is>
       </c>
       <c r="P29" s="11" t="inlineStr">
@@ -2823,7 +2823,7 @@
           <t>Prestige N16 C1M</t>
         </is>
       </c>
-      <c r="D31" s="18" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>EVT</t>
         </is>
@@ -2904,7 +2904,7 @@
           <t>Katana 18 HX A14WEK</t>
         </is>
       </c>
-      <c r="D32" s="15" t="inlineStr">
+      <c r="D32" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2984,7 +2984,7 @@
           <t>Katana 18 HX A14WFK</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D33" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3064,7 +3064,7 @@
           <t>Katana 18 HX A14WGK</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D34" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3144,7 +3144,7 @@
           <t>Katana 18 HX A14WEOK</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D35" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3220,7 +3220,7 @@
           <t>Katana 18 HX A14WFOK</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D36" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3296,7 +3296,7 @@
           <t>Katana 18 HX A14WGOK</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D37" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3372,7 +3372,7 @@
           <t>Crosshair 18 Max HX B14WEO</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D38" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3448,7 +3448,7 @@
           <t>Crosshair 18 Max HX B14WFO</t>
         </is>
       </c>
-      <c r="D39" s="16" t="inlineStr">
+      <c r="D39" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3524,7 +3524,7 @@
           <t>Crosshair 18 Max HX B14WGO</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D40" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3600,7 +3600,7 @@
           <t>Crosshair 18 Max HX B14WGXO</t>
         </is>
       </c>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D41" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3676,7 +3676,7 @@
           <t>Crosshair 18 Max HX B14WE</t>
         </is>
       </c>
-      <c r="D42" s="16" t="inlineStr">
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3756,7 +3756,7 @@
           <t>Crosshair 18 Max HX B14WF</t>
         </is>
       </c>
-      <c r="D43" s="16" t="inlineStr">
+      <c r="D43" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3836,7 +3836,7 @@
           <t>Crosshair 18 Max HX B14WG</t>
         </is>
       </c>
-      <c r="D44" s="16" t="inlineStr">
+      <c r="D44" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3916,7 +3916,7 @@
           <t>Crosshair 18 Max HX B14WGX</t>
         </is>
       </c>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="D45" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3996,7 +3996,7 @@
           <t>Crosshair 18 Max HX B2WE</t>
         </is>
       </c>
-      <c r="D46" s="14" t="inlineStr">
+      <c r="D46" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4068,7 +4068,7 @@
           <t>Crosshair 18 Max HX B2WEO</t>
         </is>
       </c>
-      <c r="D47" s="14" t="inlineStr">
+      <c r="D47" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4140,7 +4140,7 @@
           <t>Crosshair 18 Max HX B2WF</t>
         </is>
       </c>
-      <c r="D48" s="14" t="inlineStr">
+      <c r="D48" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4212,7 +4212,7 @@
           <t>Crosshair 18 Max HX B2WFO</t>
         </is>
       </c>
-      <c r="D49" s="14" t="inlineStr">
+      <c r="D49" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4284,7 +4284,7 @@
           <t>Crosshair 18 Max HX B2WG</t>
         </is>
       </c>
-      <c r="D50" s="14" t="inlineStr">
+      <c r="D50" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4356,7 +4356,7 @@
           <t>Crosshair 18 Max HX B2WGO</t>
         </is>
       </c>
-      <c r="D51" s="14" t="inlineStr">
+      <c r="D51" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4428,7 +4428,7 @@
           <t>Crosshair 18 Max HX B2WGX</t>
         </is>
       </c>
-      <c r="D52" s="14" t="inlineStr">
+      <c r="D52" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4500,7 +4500,7 @@
           <t>Crosshair 18 Max HX B2WGXO</t>
         </is>
       </c>
-      <c r="D53" s="14" t="inlineStr">
+      <c r="D53" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4572,7 +4572,7 @@
           <t>Katana 18 HX A2WEK</t>
         </is>
       </c>
-      <c r="D54" s="14" t="inlineStr">
+      <c r="D54" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4644,7 +4644,7 @@
           <t>Katana 18 HX A2WEOK</t>
         </is>
       </c>
-      <c r="D55" s="14" t="inlineStr">
+      <c r="D55" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4720,7 +4720,7 @@
           <t>Katana 18 HX A2WFK</t>
         </is>
       </c>
-      <c r="D56" s="14" t="inlineStr">
+      <c r="D56" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4792,7 +4792,7 @@
           <t>Katana 18 HX A2WFOK</t>
         </is>
       </c>
-      <c r="D57" s="14" t="inlineStr">
+      <c r="D57" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4868,7 +4868,7 @@
           <t>Katana 18 HX A2WGK</t>
         </is>
       </c>
-      <c r="D58" s="14" t="inlineStr">
+      <c r="D58" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4940,7 +4940,7 @@
           <t>Katana 18 HX A2WGOK</t>
         </is>
       </c>
-      <c r="D59" s="14" t="inlineStr">
+      <c r="D59" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5016,7 +5016,7 @@
           <t>Prestige 14 AI</t>
         </is>
       </c>
-      <c r="D60" s="15" t="inlineStr">
+      <c r="D60" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -5096,7 +5096,7 @@
           <t>Prestige 14 AI+ Flip</t>
         </is>
       </c>
-      <c r="D61" s="16" t="inlineStr">
+      <c r="D61" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -5176,7 +5176,7 @@
           <t>Prestige 16 AI+</t>
         </is>
       </c>
-      <c r="D62" s="15" t="inlineStr">
+      <c r="D62" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -5252,9 +5252,9 @@
           <t>Prestige 16 Flip AI+</t>
         </is>
       </c>
-      <c r="D63" s="14" t="inlineStr">
-        <is>
-          <t>Design</t>
+      <c r="D63" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="O63" s="11" t="inlineStr">
         <is>
-          <t>0A gerberout ：6/26,DVT SMT@7/22</t>
+          <t>DVT SMT@7/22</t>
         </is>
       </c>
       <c r="P63" s="11" t="inlineStr">
@@ -5328,7 +5328,7 @@
           <t>Prestige 13 AI+ A4M</t>
         </is>
       </c>
-      <c r="D64" s="17" t="inlineStr">
+      <c r="D64" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5408,7 +5408,7 @@
           <t>Stealth 16 AI+ B4WI</t>
         </is>
       </c>
-      <c r="D65" s="17" t="inlineStr">
+      <c r="D65" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5488,7 +5488,7 @@
           <t>Stealth 16 AI+ B4WH</t>
         </is>
       </c>
-      <c r="D66" s="14" t="inlineStr">
+      <c r="D66" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5568,7 +5568,7 @@
           <t>Stealth 16 AI+ B4WJ</t>
         </is>
       </c>
-      <c r="D67" s="14" t="inlineStr">
+      <c r="D67" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5648,7 +5648,7 @@
           <t>Stealth 16 AI+ B4WE</t>
         </is>
       </c>
-      <c r="D68" s="17" t="inlineStr">
+      <c r="D68" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5729,7 +5729,7 @@
           <t>Stealth 16 AI+ B4WF</t>
         </is>
       </c>
-      <c r="D69" s="14" t="inlineStr">
+      <c r="D69" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5810,7 +5810,7 @@
           <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
         </is>
       </c>
-      <c r="D70" s="14" t="inlineStr">
+      <c r="D70" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5891,7 +5891,7 @@
           <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
         </is>
       </c>
-      <c r="D71" s="14" t="inlineStr">
+      <c r="D71" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5972,7 +5972,7 @@
           <t>Raider 16 Max HX B4WH</t>
         </is>
       </c>
-      <c r="D72" s="15" t="inlineStr">
+      <c r="D72" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -6052,7 +6052,7 @@
           <t>Raider 16 Max HX B4WI</t>
         </is>
       </c>
-      <c r="D73" s="16" t="inlineStr">
+      <c r="D73" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -6132,7 +6132,7 @@
           <t>Raider 16 Max HX B4WJ</t>
         </is>
       </c>
-      <c r="D74" s="16" t="inlineStr">
+      <c r="D74" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -6212,7 +6212,7 @@
           <t>Raider 16  HX B4WH</t>
         </is>
       </c>
-      <c r="D75" s="16" t="inlineStr">
+      <c r="D75" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -6292,7 +6292,7 @@
           <t>Raider 16  HX B4WI</t>
         </is>
       </c>
-      <c r="D76" s="16" t="inlineStr">
+      <c r="D76" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -6372,9 +6372,9 @@
           <t>Crosshair 16 Max HX E4WEK</t>
         </is>
       </c>
-      <c r="D77" s="17" t="inlineStr">
-        <is>
-          <t>Design</t>
+      <c r="D77" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -6452,9 +6452,9 @@
           <t>Crosshair 16 Max HX E4WFK</t>
         </is>
       </c>
-      <c r="D78" s="14" t="inlineStr">
-        <is>
-          <t>Design</t>
+      <c r="D78" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
@@ -6532,9 +6532,9 @@
           <t>Crosshair 16 Max HX E4WGK</t>
         </is>
       </c>
-      <c r="D79" s="14" t="inlineStr">
-        <is>
-          <t>Design</t>
+      <c r="D79" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
@@ -6612,9 +6612,9 @@
           <t>Crosshair 16 Max HX E4WGXK</t>
         </is>
       </c>
-      <c r="D80" s="14" t="inlineStr">
-        <is>
-          <t>Design</t>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">

--- a/npi_dashboard.xlsx
+++ b/npi_dashboard.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPI Dashboard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -57,12 +57,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000B0F0"/>
+      <color rgb="00ED7D31"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00ED7D31"/>
+      <color rgb="0000B0F0"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -148,10 +148,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -519,7 +519,7 @@
     <outlinePr summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P80"/>
+  <dimension ref="A1:P86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>RMB 100 25W</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1333,17 +1333,18 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>2026/07/10</t>
+          <t>2026/07/13</t>
         </is>
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
-          <t>ATS 預計7/1 ASSY，客驗安排7/4 ，7/10 機台入庫</t>
+          <t>因D件缺料，ASSY 由7/1 推遲到7/5，機台入庫時間預計從7/10延後到7/13</t>
         </is>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>1)	MVT Issue，Free DOS下，secure boor enable,不能從U盤啟動&amp;UCSI功能未導入 需微步協調人力加速，確保在7/8前導入對策，</t>
+          <t>1).Schedule delay 3天
+2).ATS  Issue 進版EC·QA客驗機台最快7/10提供·需QA協助Support三天驗完同步需要微步確保在7/10一早提供客驗機台</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1369,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>RMB 100 35W</t>
+          <t>RMB 100 28W</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1409,17 +1410,17 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/15</t>
         </is>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>因26VL 機構物料7/3 ready，預計7/4 ATS ASSY ，7/13 機台入庫</t>
+          <t>ATS Issue需進版EC，預計7/9 提供DQA客驗機台，</t>
         </is>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>1)	MVT Issue，Free DOS下，secure boor enable,不能從U盤啟動&amp;UCSI功能未導入 需微步協調人力加速，確保在7/8前導入對策，</t>
+          <t>SChedule delay 2d：電池來料電池FW錯誤(規格要求1C·來料0.5C)需退料返工處理·機台入庫時間預計從7/13延後到7/15</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1487,7 @@
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>（清白光鍵盤庫存）測試HDI預計7/3完成DQA開始驗證,測試預計２周時間</t>
+          <t>（清白光鍵盤庫存）DQA測試中,預計7/20完成</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
@@ -1554,7 +1555,7 @@
       </c>
       <c r="O14" s="11" t="inlineStr">
         <is>
-          <t>（清日文4區RGB鍵盤庫存）預計7/6 試組機台, DQA預計測試2周時間</t>
+          <t>（清日文4區RGB鍵盤庫存）DQA測試中,預計7/21完成</t>
         </is>
       </c>
       <c r="P14" s="11" t="inlineStr">
@@ -1796,12 +1797,12 @@
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
-          <t>MVT備料中</t>
+          <t>MVT1 正式組裝@7/13</t>
         </is>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>1) 組裝正式上線時間延後2天, MP時間暫不影響</t>
+          <t>1) w/FP的Touchpad 試產物料,需要採購協助Pull in</t>
         </is>
       </c>
     </row>
@@ -2275,9 +2276,9 @@
           <t>Modern 14 LE J3M</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -2302,7 +2303,7 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
+          <t>2026/07/07</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr"/>
@@ -2318,7 +2319,7 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>2026/08/17</t>
+          <t>2026/08/18</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2328,13 +2329,12 @@
       </c>
       <c r="O24" s="6" t="inlineStr">
         <is>
-          <t>Weibu update 7/6 ASSY--受新料交期和盤點影響</t>
+          <t>Weibu 7/7 ASSY, 7/10安排機器出貨for MSIK &amp; MSIT</t>
         </is>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>1)Schedule: 考量新料備料時程, 調整試產和ATS時間@8/17 start
-2)認證: 參考Weibu認證Schedule, 有四個國家無法同步於8/E TTM, 持續追蹤中 MX: 11/28 ready；AR:10/3 ready；CO: 9/5 ready；RU: 9/12 ready</t>
+          <t>1)認證: 參考Weibu認證Schedule, a. 美洲US FCC 9/8 b.歐洲CE NB &amp;澳洲RCM 8/28 ready, 認證時間有風險, 已經highlight給微步team作認證評估</t>
         </is>
       </c>
     </row>
@@ -2352,9 +2352,9 @@
           <t>Modern 16 LE J3M</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
+          <t>2026/07/07</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr"/>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>2026/08/17</t>
+          <t>2026/08/18</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2405,13 +2405,12 @@
       </c>
       <c r="O25" s="6" t="inlineStr">
         <is>
-          <t>Weibu update 7/6 ASSY--受新料交期和盤點影響</t>
+          <t>Weibu 7/7ASSY, 7/11安排機器出貨for MSIK&amp;MSIT</t>
         </is>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>1)Schedule: 考量新料備料時程, 調整試產和ATS時間@8/17 start
-2)認證: 參考Weibu認證Schedule, 有四個國家無法同步於8/E TTM, 持續追蹤中 MX: 11/28 ready；AR:10/3 ready；CO: 9/5 ready；RU: 9/12 ready</t>
+          <t>1)認證: 參考Weibu認證Schedule, a. 美洲US FCC 9/8 b.歐洲CE NB &amp;澳洲RCM 8/28 ready, 認證時間有風險, 已經highlight給微步team作認證評估</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2777,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>2026/07/20</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2798,12 +2797,12 @@
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
-          <t>MVT SMT@7/20--depend on Material ready date作調整</t>
+          <t>MVT SMT@8/3--depend on Material ready date作調整</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>1) Schedule: 因color plan變更, MVT機構件備料ready日期還待ID&amp;ME確認中, 待評估完成更新MVT ASSY date
+          <t>1) Schedule: MVT機構件備料ready日期預計8/7完成備料
 2）Color plan change: a. 顏色變更至炭黑色 b. D件改噴漆製程
 3)備料：量產交料HQ23, 十一月份交料(MSI wish 10/B交料, 待Samsung確認回復）</t>
         </is>
@@ -2823,7 +2822,7 @@
           <t>Prestige N16 C1M</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>EVT</t>
         </is>
@@ -2860,7 +2859,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>2026/07/20</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2880,8 +2879,7 @@
       </c>
       <c r="O31" s="6" t="inlineStr">
         <is>
-          <t>1)EVT 更新BSP6.2.1  持續驗證中, 對應NV schedule 更新 MVT延到7/20.
-2) NV 更新BSP 時間 Factory Drop Final ETA 10/6 ,需要1周時間完成 HDI+BIOS 更新ATS strat 10/13</t>
+          <t>1)EVT 更新BSP6.2.1  持續驗證中, 因ID 顏色修改+機構修模 MVT 預計延後2周到8/3</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
@@ -2961,7 +2959,7 @@
       </c>
       <c r="O32" s="6" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT 測試中</t>
+          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
         </is>
       </c>
       <c r="P32" s="6" t="inlineStr">
@@ -3041,7 +3039,7 @@
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT 測試中</t>
+          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
         </is>
       </c>
       <c r="P33" s="11" t="inlineStr">
@@ -3121,7 +3119,7 @@
       </c>
       <c r="O34" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT 測試中</t>
+          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
         </is>
       </c>
       <c r="P34" s="11" t="inlineStr">
@@ -3197,7 +3195,7 @@
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT PCBA 7/2 調撥，預計7/6 RD領取測試</t>
+          <t>RPL-HX R + DDR4: DVT 7/6 RD領取測試</t>
         </is>
       </c>
       <c r="P35" s="11" t="inlineStr">
@@ -3273,7 +3271,7 @@
       </c>
       <c r="O36" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT PCBA 7/2 調撥，預計7/6 RD領取測試</t>
+          <t>RPL-HX R + DDR4: DVT 7/6 RD領取測試</t>
         </is>
       </c>
       <c r="P36" s="11" t="inlineStr">
@@ -3349,7 +3347,7 @@
       </c>
       <c r="O37" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT PCBA 7/2 調撥，預計7/6 RD領取測試</t>
+          <t>RPL-HX R + DDR4: DVT 7/6 RD領取測試</t>
         </is>
       </c>
       <c r="P37" s="11" t="inlineStr">
@@ -3425,7 +3423,7 @@
       </c>
       <c r="O38" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT PCBA 7/2 調撥，預計7/6 RD領取測試</t>
+          <t>RPL-HX R + DDR4: DVT 7/6 RD領取測試</t>
         </is>
       </c>
       <c r="P38" s="11" t="inlineStr">
@@ -3501,7 +3499,7 @@
       </c>
       <c r="O39" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT PCBA 7/2 調撥，預計7/6 RD領取測試</t>
+          <t>RPL-HX R + DDR4: DVT 7/6 RD領取測試</t>
         </is>
       </c>
       <c r="P39" s="11" t="inlineStr">
@@ -3577,7 +3575,7 @@
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT PCBA 7/2 調撥，預計7/6 RD領取測試</t>
+          <t>RPL-HX R + DDR4: DVT 7/6 RD領取測試</t>
         </is>
       </c>
       <c r="P40" s="11" t="inlineStr">
@@ -3653,7 +3651,7 @@
       </c>
       <c r="O41" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT PCBA 7/2 調撥，預計7/6 RD領取測試</t>
+          <t>RPL-HX R + DDR4: DVT 7/6 RD領取測試</t>
         </is>
       </c>
       <c r="P41" s="11" t="inlineStr">
@@ -3733,7 +3731,7 @@
       </c>
       <c r="O42" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT 測試中</t>
+          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
         </is>
       </c>
       <c r="P42" s="11" t="inlineStr">
@@ -3813,7 +3811,7 @@
       </c>
       <c r="O43" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT 測試中</t>
+          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
         </is>
       </c>
       <c r="P43" s="11" t="inlineStr">
@@ -3893,7 +3891,7 @@
       </c>
       <c r="O44" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT 測試中</t>
+          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
         </is>
       </c>
       <c r="P44" s="11" t="inlineStr">
@@ -3973,7 +3971,7 @@
       </c>
       <c r="O45" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT 測試中</t>
+          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
         </is>
       </c>
       <c r="P45" s="11" t="inlineStr">
@@ -3996,7 +3994,7 @@
           <t>Crosshair 18 Max HX B2WE</t>
         </is>
       </c>
-      <c r="D46" s="18" t="inlineStr">
+      <c r="D46" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4068,7 +4066,7 @@
           <t>Crosshair 18 Max HX B2WEO</t>
         </is>
       </c>
-      <c r="D47" s="18" t="inlineStr">
+      <c r="D47" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4140,7 +4138,7 @@
           <t>Crosshair 18 Max HX B2WF</t>
         </is>
       </c>
-      <c r="D48" s="18" t="inlineStr">
+      <c r="D48" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4212,7 +4210,7 @@
           <t>Crosshair 18 Max HX B2WFO</t>
         </is>
       </c>
-      <c r="D49" s="18" t="inlineStr">
+      <c r="D49" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4284,7 +4282,7 @@
           <t>Crosshair 18 Max HX B2WG</t>
         </is>
       </c>
-      <c r="D50" s="18" t="inlineStr">
+      <c r="D50" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4356,7 +4354,7 @@
           <t>Crosshair 18 Max HX B2WGO</t>
         </is>
       </c>
-      <c r="D51" s="18" t="inlineStr">
+      <c r="D51" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4428,7 +4426,7 @@
           <t>Crosshair 18 Max HX B2WGX</t>
         </is>
       </c>
-      <c r="D52" s="18" t="inlineStr">
+      <c r="D52" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4500,7 +4498,7 @@
           <t>Crosshair 18 Max HX B2WGXO</t>
         </is>
       </c>
-      <c r="D53" s="18" t="inlineStr">
+      <c r="D53" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4572,7 +4570,7 @@
           <t>Katana 18 HX A2WEK</t>
         </is>
       </c>
-      <c r="D54" s="18" t="inlineStr">
+      <c r="D54" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4644,7 +4642,7 @@
           <t>Katana 18 HX A2WEOK</t>
         </is>
       </c>
-      <c r="D55" s="18" t="inlineStr">
+      <c r="D55" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4720,7 +4718,7 @@
           <t>Katana 18 HX A2WFK</t>
         </is>
       </c>
-      <c r="D56" s="18" t="inlineStr">
+      <c r="D56" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4792,7 +4790,7 @@
           <t>Katana 18 HX A2WFOK</t>
         </is>
       </c>
-      <c r="D57" s="18" t="inlineStr">
+      <c r="D57" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4868,7 +4866,7 @@
           <t>Katana 18 HX A2WGK</t>
         </is>
       </c>
-      <c r="D58" s="18" t="inlineStr">
+      <c r="D58" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4940,7 +4938,7 @@
           <t>Katana 18 HX A2WGOK</t>
         </is>
       </c>
-      <c r="D59" s="18" t="inlineStr">
+      <c r="D59" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5328,7 +5326,7 @@
           <t>Prestige 13 AI+ A4M</t>
         </is>
       </c>
-      <c r="D64" s="16" t="inlineStr">
+      <c r="D64" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5408,7 +5406,7 @@
           <t>Stealth 16 AI+ B4WI</t>
         </is>
       </c>
-      <c r="D65" s="16" t="inlineStr">
+      <c r="D65" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5488,7 +5486,7 @@
           <t>Stealth 16 AI+ B4WH</t>
         </is>
       </c>
-      <c r="D66" s="18" t="inlineStr">
+      <c r="D66" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5568,7 +5566,7 @@
           <t>Stealth 16 AI+ B4WJ</t>
         </is>
       </c>
-      <c r="D67" s="18" t="inlineStr">
+      <c r="D67" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5648,7 +5646,7 @@
           <t>Stealth 16 AI+ B4WE</t>
         </is>
       </c>
-      <c r="D68" s="16" t="inlineStr">
+      <c r="D68" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5665,7 +5663,7 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -5729,7 +5727,7 @@
           <t>Stealth 16 AI+ B4WF</t>
         </is>
       </c>
-      <c r="D69" s="18" t="inlineStr">
+      <c r="D69" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5746,7 +5744,7 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="H69" s="9" t="inlineStr">
@@ -5810,7 +5808,7 @@
           <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
         </is>
       </c>
-      <c r="D70" s="18" t="inlineStr">
+      <c r="D70" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5827,7 +5825,7 @@
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="H70" s="9" t="inlineStr">
@@ -5891,7 +5889,7 @@
           <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
         </is>
       </c>
-      <c r="D71" s="18" t="inlineStr">
+      <c r="D71" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5908,7 +5906,7 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="H71" s="9" t="inlineStr">
@@ -6364,17 +6362,17 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Crosshair 16 Max HX E4WEK</t>
-        </is>
-      </c>
-      <c r="D77" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Titan 18 HX B4WH</t>
+        </is>
+      </c>
+      <c r="D77" s="18" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -6384,37 +6382,37 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>鮑佩佩</t>
+          <t>高宇奇</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/06/29</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/08/14</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>2026/09/29</t>
+          <t>2026/10/23</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>2027/02/02</t>
+          <t>2027/02/01</t>
         </is>
       </c>
       <c r="M77" s="4" t="inlineStr">
@@ -6429,14 +6427,10 @@
       </c>
       <c r="O77" s="6" t="inlineStr">
         <is>
-          <t>0A 7/3 gerber out</t>
-        </is>
-      </c>
-      <c r="P77" s="6" t="inlineStr">
-        <is>
-          <t>na</t>
-        </is>
-      </c>
+          <t>0M layout進行中,預計7/27 0M gerber out.</t>
+        </is>
+      </c>
+      <c r="P77" s="6" t="inlineStr"/>
     </row>
     <row r="78" hidden="1" outlineLevel="1">
       <c r="A78" s="7" t="n">
@@ -6444,17 +6438,17 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 16 Max HX E4WFK</t>
-        </is>
-      </c>
-      <c r="D78" s="15" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Titan 18 HX B4WI</t>
+        </is>
+      </c>
+      <c r="D78" s="17" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
@@ -6464,37 +6458,37 @@
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>鮑佩佩</t>
+          <t>高宇奇</t>
         </is>
       </c>
       <c r="H78" s="9" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/06/29</t>
         </is>
       </c>
       <c r="I78" s="9" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/08/14</t>
         </is>
       </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>2026/09/29</t>
+          <t>2026/10/23</t>
         </is>
       </c>
       <c r="K78" s="9" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="L78" s="9" t="inlineStr">
         <is>
-          <t>2027/02/02</t>
+          <t>2027/02/01</t>
         </is>
       </c>
       <c r="M78" s="9" t="inlineStr">
@@ -6509,14 +6503,10 @@
       </c>
       <c r="O78" s="11" t="inlineStr">
         <is>
-          <t>0A 7/3 gerber out</t>
-        </is>
-      </c>
-      <c r="P78" s="11" t="inlineStr">
-        <is>
-          <t>na</t>
-        </is>
-      </c>
+          <t>0M layout進行中,預計7/27 0M gerber out.</t>
+        </is>
+      </c>
+      <c r="P78" s="11" t="inlineStr"/>
     </row>
     <row r="79" hidden="1" outlineLevel="1">
       <c r="A79" s="7" t="n">
@@ -6524,17 +6514,17 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 16 Max HX E4WGK</t>
-        </is>
-      </c>
-      <c r="D79" s="15" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Titan 18 HX B4WJ</t>
+        </is>
+      </c>
+      <c r="D79" s="17" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
@@ -6544,37 +6534,37 @@
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>鮑佩佩</t>
+          <t>高宇奇</t>
         </is>
       </c>
       <c r="H79" s="9" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/06/29</t>
         </is>
       </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/08/14</t>
         </is>
       </c>
       <c r="J79" s="9" t="inlineStr">
         <is>
-          <t>2026/09/29</t>
+          <t>2026/10/23</t>
         </is>
       </c>
       <c r="K79" s="9" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="L79" s="9" t="inlineStr">
         <is>
-          <t>2027/02/02</t>
+          <t>2027/02/01</t>
         </is>
       </c>
       <c r="M79" s="9" t="inlineStr">
@@ -6589,14 +6579,10 @@
       </c>
       <c r="O79" s="11" t="inlineStr">
         <is>
-          <t>GN22-X6 8GB SKU,0A 7/3 gerber out</t>
-        </is>
-      </c>
-      <c r="P79" s="11" t="inlineStr">
-        <is>
-          <t>na</t>
-        </is>
-      </c>
+          <t>0M layout進行中,預計7/27 0M gerber out.</t>
+        </is>
+      </c>
+      <c r="P79" s="11" t="inlineStr"/>
     </row>
     <row r="80" hidden="1" outlineLevel="1">
       <c r="A80" s="7" t="n">
@@ -6604,82 +6590,550 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>Raider 18 Max HX B4WH</t>
+        </is>
+      </c>
+      <c r="D80" s="17" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>NVL-HX 65W</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>高宇奇</t>
+        </is>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/23</t>
+        </is>
+      </c>
+      <c r="K80" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/08</t>
+        </is>
+      </c>
+      <c r="L80" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/01</t>
+        </is>
+      </c>
+      <c r="M80" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N80" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O80" s="11" t="inlineStr">
+        <is>
+          <t>0M layout進行中,預計7/27 0M gerber out.</t>
+        </is>
+      </c>
+      <c r="P80" s="11" t="inlineStr"/>
+    </row>
+    <row r="81" hidden="1" outlineLevel="1">
+      <c r="A81" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>Raider 18 Max HX B4WI</t>
+        </is>
+      </c>
+      <c r="D81" s="17" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>NVL-HX 65W</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5080</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>高宇奇</t>
+        </is>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/23</t>
+        </is>
+      </c>
+      <c r="K81" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/08</t>
+        </is>
+      </c>
+      <c r="L81" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/01</t>
+        </is>
+      </c>
+      <c r="M81" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N81" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O81" s="11" t="inlineStr">
+        <is>
+          <t>0M layout進行中,預計7/27 0M gerber out.</t>
+        </is>
+      </c>
+      <c r="P81" s="11" t="inlineStr"/>
+    </row>
+    <row r="82" hidden="1" outlineLevel="1">
+      <c r="A82" s="7" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>Raider 18 Max HX B4WJ</t>
+        </is>
+      </c>
+      <c r="D82" s="17" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>NVL-HX 65W</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5090</t>
+        </is>
+      </c>
+      <c r="G82" s="9" t="inlineStr">
+        <is>
+          <t>高宇奇</t>
+        </is>
+      </c>
+      <c r="H82" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/23</t>
+        </is>
+      </c>
+      <c r="K82" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/08</t>
+        </is>
+      </c>
+      <c r="L82" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/01</t>
+        </is>
+      </c>
+      <c r="M82" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N82" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O82" s="11" t="inlineStr">
+        <is>
+          <t>0M layout進行中,預計7/27 0M gerber out.</t>
+        </is>
+      </c>
+      <c r="P82" s="11" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
           <t>2655</t>
         </is>
       </c>
-      <c r="C80" s="9" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Crosshair 16 Max HX E4WEK</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>鮑佩佩</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="L83" s="4" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M83" s="4" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N83" s="4" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O83" s="6" t="inlineStr">
+        <is>
+          <t>0A 7/3 gerber out.plan 7/27 DVT SMT1</t>
+        </is>
+      </c>
+      <c r="P83" s="6" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" hidden="1" outlineLevel="1">
+      <c r="A84" s="7" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>2655</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>Crosshair 16 Max HX E4WFK</t>
+        </is>
+      </c>
+      <c r="D84" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
+        <is>
+          <t>鮑佩佩</t>
+        </is>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K84" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="L84" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M84" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N84" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O84" s="11" t="inlineStr">
+        <is>
+          <t>0A 7/3 gerber out.plan 7/27 DVT SMT1</t>
+        </is>
+      </c>
+      <c r="P84" s="11" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" hidden="1" outlineLevel="1">
+      <c r="A85" s="7" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>2655</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>Crosshair 16 Max HX E4WGK</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F85" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>鮑佩佩</t>
+        </is>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K85" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="L85" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M85" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N85" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O85" s="11" t="inlineStr">
+        <is>
+          <t>0A 7/3 gerber out.plan 7/27 DVT SMT1</t>
+        </is>
+      </c>
+      <c r="P85" s="11" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" hidden="1" outlineLevel="1">
+      <c r="A86" s="7" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>2655</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
         <is>
           <t>Crosshair 16 Max HX E4WGXK</t>
         </is>
       </c>
-      <c r="D80" s="15" t="inlineStr">
+      <c r="D86" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E80" s="9" t="inlineStr">
+      <c r="E86" s="9" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F80" s="9" t="inlineStr">
+      <c r="F86" s="9" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G80" s="9" t="inlineStr">
+      <c r="G86" s="9" t="inlineStr">
         <is>
           <t>鮑佩佩</t>
         </is>
       </c>
-      <c r="H80" s="9" t="inlineStr">
+      <c r="H86" s="9" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I80" s="9" t="inlineStr">
+      <c r="I86" s="9" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J80" s="9" t="inlineStr">
+      <c r="J86" s="9" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K80" s="9" t="inlineStr">
+      <c r="K86" s="9" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L80" s="9" t="inlineStr">
+      <c r="L86" s="9" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M80" s="9" t="inlineStr">
+      <c r="M86" s="9" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N80" s="9" t="inlineStr">
+      <c r="N86" s="9" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O80" s="11" t="inlineStr">
-        <is>
-          <t>GN22-X6 12GB SKU,0A 7/3 gerber out</t>
-        </is>
-      </c>
-      <c r="P80" s="11" t="inlineStr">
+      <c r="O86" s="11" t="inlineStr">
+        <is>
+          <t>0A 7/3 gerber out.plan 7/27 DVT SMT1</t>
+        </is>
+      </c>
+      <c r="P86" s="11" t="inlineStr">
         <is>
           <t>na</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P80"/>
+  <autoFilter ref="A1:P86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/npi_dashboard.xlsx
+++ b/npi_dashboard.xlsx
@@ -682,12 +682,12 @@
       </c>
       <c r="O2" s="6" t="inlineStr">
         <is>
-          <t>因首批安排RPL-U Refresh 優先投產，第二波投產因PCB 最快交期落在6/29,加上微步盤點，預計最快7/10 TTM</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>因首批安排RPL-U Refresh 優先投產，第二波投產因PCB 最快交期落在6/29,加上微步盤點，機台7/9 入庫</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E9WGXK</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -865,12 +865,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1）暫無業務報價，BTO 未開</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WFK</t>
+          <t>Crosshair A16 HX E9WEK</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WGXK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>FRG-HX 55W</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
@@ -2438,9 +2438,9 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>1) Schedule: MVT機構件備料ready日期預計8/7完成備料
-2）Color plan change: a. 顏色變更至炭黑色 b. D件改噴漆製程
-3)備料：量產交料HQ23, 十一月份交料(MSI wish 10/B交料, 待Samsung確認回復）</t>
+          <t>1) Schedule: MVT D件備料ready日期待採購/ME確認中
+2）Color plan: 維持開案版本
+3)備料：量產交料HQ23, 十月份交料, 待Samsung確認具體日期</t>
         </is>
       </c>
     </row>

--- a/npi_dashboard.xlsx
+++ b/npi_dashboard.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPI Dashboard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -516,7 +516,7 @@
     <outlinePr summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P81"/>
+  <dimension ref="A1:P83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -753,18 +753,17 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026/07/13</t>
+          <t>2026/07/18</t>
         </is>
       </c>
       <c r="O3" s="6" t="inlineStr">
         <is>
-          <t>因D件缺料，ASSY 由7/1 推遲到7/5，機台入庫時間預計從7/10延後到7/13</t>
+          <t>ATS客驗：DQA 客驗Pass, QA 機台7/16 提供，待確認客驗結果</t>
         </is>
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>1).Schedule delay 3天
-2).ATS  Issue 進版EC·QA客驗機台最快7/10提供·需QA協助Support三天驗完同步需要微步確保在7/10一早提供客驗機台</t>
+          <t>1).Schedule ：因Camera 丟失問題，安排重工Camera，機台入庫時間預抓從7/13 延後到7/18，delay5天</t>
         </is>
       </c>
     </row>
@@ -830,17 +829,18 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>2026/07/15</t>
+          <t>2026/07/20</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>ATS Issue需進版EC，預計7/9 提供DQA客驗機台，</t>
+          <t>因Camera 丟失ISSUE，待確認執行方案</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>SChedule delay 2d：電池來料電池FW錯誤(規格要求1C·來料0.5C)需退料返工處理·機台入庫時間預計從7/13延後到7/15</t>
+          <t>Schedule  ：（TTM原計劃7/15 先預抓延後到7/
+20）：7/16 會議請微步放量200台驗證以及全掃功能，待微步提供具體數據，請示執行方案後，追蹤最快機台入庫時間</t>
         </is>
       </c>
     </row>
@@ -1206,299 +1206,295 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>15T2</t>
+          <t>15Q3</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Venture 15 AI+ B3M</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Cyborg 15 Black Edition B13WE</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>MVT</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>PTL-H 80W</t>
+          <t>RPL-H 45W</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Intel® Arc™ Graphics</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>李文欽</t>
+          <t>楊淑賢</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/26</t>
-        </is>
-      </c>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
       <c r="J10" s="4" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr">
         <is>
+          <t>2026/07/01</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/14</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>DQA test中,
+1) ME: 搖擺測試pass
+2）Function：待新版MSI Center AP release( 包入MKT name支援AI Noise Cancellation Pro), 安排HDI製作</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>1) Cyborg Black Edition SKU: Cyborg A+Venture B/C/D機構件+白光鍵盤</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" hidden="1" outlineLevel="1">
+      <c r="A11" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>15Q3</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Cyborg 15 Black Edition B13WF</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>RPL-H 45W</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>楊淑賢</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr"/>
+      <c r="J11" s="10" t="inlineStr"/>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/01</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/14</t>
+        </is>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>DQA test中,
+1) ME: 搖擺測試pass
+2）Function：待新版MSI Center AP release( 包入MKT name支援AI Noise Cancellation Pro), 安排HDI製作</t>
+        </is>
+      </c>
+      <c r="P11" s="12" t="inlineStr">
+        <is>
+          <t>1) Cyborg Black Edition SKU: Cyborg A+Venture B/C/D機構件+白光鍵盤</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>15T2</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Venture 15 AI+ B3M</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>PTL-H 80W</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>李文欽</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/20</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
           <t>2026/07/08</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>2026/07/20</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>2026/08/17</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>2026/08/27</t>
         </is>
       </c>
-      <c r="O10" s="6" t="inlineStr">
+      <c r="O12" s="6" t="inlineStr">
         <is>
           <t>MVT1 正式組裝@7/13</t>
         </is>
       </c>
-      <c r="P10" s="6" t="inlineStr">
+      <c r="P12" s="6" t="inlineStr">
         <is>
           <t>1) w/FP的Touchpad 試產物料,需要採購協助Pull in</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>15T3</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Katana 15 HX C14WEK</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>2026/04/20</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>2026/06/01</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>2026/07/14</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>2026/07/30</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>2026/08/20</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>2026/08/30</t>
         </is>
       </c>
-      <c r="O11" s="6" t="inlineStr">
-        <is>
-          <t>DDR5 sku, MVT備料中,預計7/14 MVT SMT</t>
-        </is>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" hidden="1" outlineLevel="1">
-      <c r="A12" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>15T3</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Katana 15 HX C14WFK</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>2026/04/20</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
-      </c>
-      <c r="J12" s="10" t="inlineStr"/>
-      <c r="K12" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/14</t>
-        </is>
-      </c>
-      <c r="L12" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/30</t>
-        </is>
-      </c>
-      <c r="M12" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/20</t>
-        </is>
-      </c>
-      <c r="N12" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/30</t>
-        </is>
-      </c>
-      <c r="O12" s="12" t="inlineStr">
-        <is>
-          <t>DDR5 sku, MVT備料中,預計7/14 MVT SMT</t>
-        </is>
-      </c>
-      <c r="P12" s="12" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" hidden="1" outlineLevel="1">
-      <c r="A13" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>15T3</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>Katana 15 HX C14WGK</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>2026/04/20</t>
-        </is>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
-      </c>
-      <c r="J13" s="10" t="inlineStr"/>
-      <c r="K13" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/14</t>
-        </is>
-      </c>
-      <c r="L13" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/30</t>
-        </is>
-      </c>
-      <c r="M13" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/20</t>
-        </is>
-      </c>
-      <c r="N13" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/30</t>
-        </is>
-      </c>
-      <c r="O13" s="12" t="inlineStr">
-        <is>
-          <t>DDR5 sku, MVT備料中,預計7/14 MVT SMT</t>
-        </is>
-      </c>
-      <c r="P13" s="12" t="inlineStr">
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>DDR5 sku, 預計7/17 MVT Assy</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1515,12 +1511,12 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WEOK</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Katana 15 HX C14WFK</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>MVT</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -1530,7 +1526,7 @@
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
@@ -1540,38 +1536,38 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>2026/05/15</t>
+          <t>2026/04/20</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
+          <t>2026/06/01</t>
         </is>
       </c>
       <c r="J14" s="10" t="inlineStr"/>
       <c r="K14" s="10" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>2026/08/07</t>
+          <t>2026/07/30</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>2026/08/21</t>
+          <t>2026/08/20</t>
         </is>
       </c>
       <c r="N14" s="10" t="inlineStr">
         <is>
-          <t>2026/08/31</t>
+          <t>2026/08/30</t>
         </is>
       </c>
       <c r="O14" s="12" t="inlineStr">
         <is>
-          <t>DDR4 sku, DVT測試中,預計7/14 gerberout PCB 3.1</t>
+          <t>DDR5 sku, 預計7/17 MVT Assy</t>
         </is>
       </c>
       <c r="P14" s="12" t="inlineStr">
@@ -1591,12 +1587,12 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WFOK</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Katana 15 HX C14WGK</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>MVT</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
@@ -1606,7 +1602,7 @@
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
@@ -1616,38 +1612,38 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>2026/05/15</t>
+          <t>2026/04/20</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
+          <t>2026/06/01</t>
         </is>
       </c>
       <c r="J15" s="10" t="inlineStr"/>
       <c r="K15" s="10" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>2026/08/07</t>
+          <t>2026/07/30</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>2026/08/21</t>
+          <t>2026/08/20</t>
         </is>
       </c>
       <c r="N15" s="10" t="inlineStr">
         <is>
-          <t>2026/08/31</t>
+          <t>2026/08/30</t>
         </is>
       </c>
       <c r="O15" s="12" t="inlineStr">
         <is>
-          <t>DDR4 sku, DVT測試中,預計7/14 gerberout PCB 3.1</t>
+          <t>DDR5 sku, 預計7/17 MVT Assy</t>
         </is>
       </c>
       <c r="P15" s="12" t="inlineStr">
@@ -1667,12 +1663,12 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WGOK</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Katana 15 HX C14WEOK</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>MVT</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -1682,7 +1678,7 @@
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -1723,7 +1719,7 @@
       </c>
       <c r="O16" s="12" t="inlineStr">
         <is>
-          <t>DDR4 sku, DVT測試中,預計7/14 gerberout PCB 3.1</t>
+          <t>DDR4 sku, MVT備料中,預計7/24 MVT SMT</t>
         </is>
       </c>
       <c r="P16" s="12" t="inlineStr">
@@ -1732,81 +1728,233 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
+    <row r="17" hidden="1" outlineLevel="1">
+      <c r="A17" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>15T3</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Katana 15 HX C14WFOK</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>蔡東宏</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/15</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr"/>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/24</t>
+        </is>
+      </c>
+      <c r="L17" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="O17" s="12" t="inlineStr">
+        <is>
+          <t>DDR4 sku, MVT備料中,預計7/24 MVT SMT</t>
+        </is>
+      </c>
+      <c r="P17" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" hidden="1" outlineLevel="1">
+      <c r="A18" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>15T3</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Katana 15 HX C14WGOK</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>蔡東宏</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/15</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="inlineStr"/>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/24</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t>DDR4 sku, MVT備料中,預計7/24 MVT SMT</t>
+        </is>
+      </c>
+      <c r="P18" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Prestige N16 Spark</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Prestige N16 AI+ C1XMT</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>N1x 80W</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>林晉弘</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>2024/11/25</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>2025/01/20</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>2025/06/25</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>2026/03/12</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>2026/06/30</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>2026/08/17</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O17" s="6" t="inlineStr">
+      <c r="O19" s="6" t="inlineStr">
         <is>
           <t>MVT測試中</t>
         </is>
       </c>
-      <c r="P17" s="6" t="inlineStr">
+      <c r="P19" s="6" t="inlineStr">
         <is>
           <t>1)battery life測試條件的定義，NV與MSFT討論中，根據7/9會議，DQA會基於BSP Day0 rev.B + balance mode測試，確認是否合乎MSFT要求。
 2)NV Abnormal shut down 的solution，預計會於7/17 BSP Day0 rev.B導入，待SW release後，DQA會驗證確認。
@@ -1815,81 +1963,81 @@
         </is>
       </c>
     </row>
-    <row r="18" hidden="1" outlineLevel="1">
-      <c r="A18" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
+    <row r="20" hidden="1" outlineLevel="1">
+      <c r="A20" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Prestige N16 Flip Spark</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Prestige N16 Flip AI+ C1XMT</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>N1x 80W</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>林晉弘</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>2024/11/25</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>2025/01/20</t>
         </is>
       </c>
-      <c r="J18" s="10" t="inlineStr">
+      <c r="J20" s="10" t="inlineStr">
         <is>
           <t>2025/06/25</t>
         </is>
       </c>
-      <c r="K18" s="10" t="inlineStr">
+      <c r="K20" s="10" t="inlineStr">
         <is>
           <t>2026/03/12</t>
         </is>
       </c>
-      <c r="L18" s="10" t="inlineStr">
+      <c r="L20" s="10" t="inlineStr">
         <is>
           <t>2026/06/30</t>
         </is>
       </c>
-      <c r="M18" s="10" t="inlineStr">
+      <c r="M20" s="10" t="inlineStr">
         <is>
           <t>2026/08/17</t>
         </is>
       </c>
-      <c r="N18" s="10" t="inlineStr">
+      <c r="N20" s="10" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O18" s="12" t="inlineStr">
+      <c r="O20" s="12" t="inlineStr">
         <is>
           <t>MVT測試中</t>
         </is>
       </c>
-      <c r="P18" s="12" t="inlineStr">
+      <c r="P20" s="12" t="inlineStr">
         <is>
           <t>1)battery life測試條件的定義，NV與MSFT討論中，根據7/9會議，DQA會基於BSP Day0 rev.B + balance mode測試，確認是否合乎MSFT要求。
 2)NV Abnormal shut down 的solution，預計會於7/17 BSP Day0 rev.B導入，待SW release後，DQA會驗證確認。
@@ -1898,170 +2046,18 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>24V1</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Modern 14 LE J3M</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>WCL 25W</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Intel® graphics</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>倪嬌嬌</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/07</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/29</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/08</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/18</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/31</t>
-        </is>
-      </c>
-      <c r="O19" s="6" t="inlineStr">
-        <is>
-          <t>Weibu 7/7 ASSY, 7/10安排機器出貨for MSIK &amp; MSIT</t>
-        </is>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>1)認證: 參考Weibu認證Schedule, a. 美洲US FCC 9/8 b.歐洲CE NB &amp;澳洲RCM 8/28 ready, 認證時間有風險, 已經highlight給微步team作認證評估</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>26V1</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Modern 16 LE J3M</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>WCL 25W</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Intel® graphics</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>倪嬌嬌</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/07</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr"/>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/29</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/08</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/18</t>
-        </is>
-      </c>
-      <c r="N20" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/31</t>
-        </is>
-      </c>
-      <c r="O20" s="6" t="inlineStr">
-        <is>
-          <t>Weibu 7/7ASSY, 7/11安排機器出貨for MSIK&amp;MSIT</t>
-        </is>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>1)認證: 參考Weibu認證Schedule, a. 美洲US FCC 9/8 b.歐洲CE NB &amp;澳洲RCM 8/28 ready, 認證時間有風險, 已經highlight給微步team作認證評估</t>
-        </is>
-      </c>
-    </row>
     <row r="21">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>15TK</t>
+          <t>24V1</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Cyborg A15 Max C1PWE</t>
+          <t>Modern 14 LE J3M</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
@@ -2071,27 +2067,27 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>HWK 45W</t>
+          <t>WCL 25W</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>Intel® graphics</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>蔡東宏</t>
+          <t>倪嬌嬌</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>2026/05/28</t>
+          <t>2026/06/02</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>2026/06/26</t>
+          <t>2026/07/07</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr"/>
@@ -2102,25 +2098,177 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="O21" s="6" t="inlineStr">
+        <is>
+          <t>MSIK: 7/14 DQA test start MSIT: 7/16收到機器</t>
+        </is>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>1)認證: 參考Weibu認證Schedule, a. 美洲US FCC 9/8 b.歐洲CE NB &amp;澳洲RCM 8/28 ready, 認證時間有風險, 已經highlight給微步team作認證評估</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>26V1</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Modern 16 LE J3M</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>WCL 25W</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Intel® graphics</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>倪嬌嬌</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/07</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/29</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>MSIK: 7/14 DQA test start MSIT: 7/16收到機器</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>1)認證: 參考Weibu認證Schedule, a. 美洲US FCC 9/8 b.歐洲CE NB &amp;澳洲RCM 8/28 ready, 認證時間有風險, 已經highlight給微步team作認證評估</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>15TK</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Cyborg A15 Max C1PWE</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>HWK 45W</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>蔡東宏</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/29</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
           <t>2026/08/14</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>2026/09/04</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>2026/09/14</t>
         </is>
       </c>
-      <c r="O21" s="6" t="inlineStr">
+      <c r="O23" s="6" t="inlineStr">
         <is>
           <t>HPT sku: MODS無法測試,請BIOS RD儘速釐清</t>
         </is>
       </c>
-      <c r="P21" s="6" t="inlineStr">
+      <c r="P23" s="6" t="inlineStr">
         <is>
           <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/17(Delay 4W),因專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP 預計延後 2週至 9/14 (先前已由9 月底提前至8/31,現又延至9/
 14),後續將依實際測試結果滾動式調整時程。
@@ -2128,77 +2276,77 @@
         </is>
       </c>
     </row>
-    <row r="22" hidden="1" outlineLevel="1">
-      <c r="A22" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
+    <row r="24" hidden="1" outlineLevel="1">
+      <c r="A24" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>15TK</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>Cyborg A15 Max C1PWF</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>HWK 45W</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>RTX 5060</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>2026/05/28</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>2026/06/26</t>
         </is>
       </c>
-      <c r="J22" s="10" t="inlineStr"/>
-      <c r="K22" s="10" t="inlineStr">
+      <c r="J24" s="10" t="inlineStr"/>
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>2026/07/29</t>
         </is>
       </c>
-      <c r="L22" s="10" t="inlineStr">
+      <c r="L24" s="10" t="inlineStr">
         <is>
           <t>2026/08/14</t>
         </is>
       </c>
-      <c r="M22" s="10" t="inlineStr">
+      <c r="M24" s="10" t="inlineStr">
         <is>
           <t>2026/09/04</t>
         </is>
       </c>
-      <c r="N22" s="10" t="inlineStr">
+      <c r="N24" s="10" t="inlineStr">
         <is>
           <t>2026/09/14</t>
         </is>
       </c>
-      <c r="O22" s="12" t="inlineStr">
+      <c r="O24" s="12" t="inlineStr">
         <is>
           <t>HPT sku: MODS無法測試,請BIOS RD儘速釐清</t>
         </is>
       </c>
-      <c r="P22" s="12" t="inlineStr">
+      <c r="P24" s="12" t="inlineStr">
         <is>
           <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/17(Delay 4W),因專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP 預計延後 2週至 9/14 (先前已由9 月底提前至8/31,現又延至9/
 14),後續將依實際測試結果滾動式調整時程。
@@ -2206,77 +2354,77 @@
         </is>
       </c>
     </row>
-    <row r="23" hidden="1" outlineLevel="1">
-      <c r="A23" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
+    <row r="25" hidden="1" outlineLevel="1">
+      <c r="A25" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>15TK</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>Cyborg A15 Max C1PWG</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>HWK 45W</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>2026/05/28</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>2026/06/26</t>
         </is>
       </c>
-      <c r="J23" s="10" t="inlineStr"/>
-      <c r="K23" s="10" t="inlineStr">
+      <c r="J25" s="10" t="inlineStr"/>
+      <c r="K25" s="10" t="inlineStr">
         <is>
           <t>2026/07/29</t>
         </is>
       </c>
-      <c r="L23" s="10" t="inlineStr">
+      <c r="L25" s="10" t="inlineStr">
         <is>
           <t>2026/08/14</t>
         </is>
       </c>
-      <c r="M23" s="10" t="inlineStr">
+      <c r="M25" s="10" t="inlineStr">
         <is>
           <t>2026/09/04</t>
         </is>
       </c>
-      <c r="N23" s="10" t="inlineStr">
+      <c r="N25" s="10" t="inlineStr">
         <is>
           <t>2026/09/14</t>
         </is>
       </c>
-      <c r="O23" s="12" t="inlineStr">
+      <c r="O25" s="12" t="inlineStr">
         <is>
           <t>HPT sku: MODS無法測試,請BIOS RD儘速釐清</t>
         </is>
       </c>
-      <c r="P23" s="12" t="inlineStr">
+      <c r="P25" s="12" t="inlineStr">
         <is>
           <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/17(Delay 4W),因專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP 預計延後 2週至 9/14 (先前已由9 月底提前至8/31,現又延至9/
 14),後續將依實際測試結果滾動式調整時程。
@@ -2284,77 +2432,77 @@
         </is>
       </c>
     </row>
-    <row r="24" hidden="1" outlineLevel="1">
-      <c r="A24" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
+    <row r="26" hidden="1" outlineLevel="1">
+      <c r="A26" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>15TK</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>Cyborg A15 C1PWE</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>HWK 45W</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>2026/05/28</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>2026/06/26</t>
         </is>
       </c>
-      <c r="J24" s="10" t="inlineStr"/>
-      <c r="K24" s="10" t="inlineStr">
+      <c r="J26" s="10" t="inlineStr"/>
+      <c r="K26" s="10" t="inlineStr">
         <is>
           <t>2026/07/29</t>
         </is>
       </c>
-      <c r="L24" s="10" t="inlineStr">
+      <c r="L26" s="10" t="inlineStr">
         <is>
           <t>2026/08/14</t>
         </is>
       </c>
-      <c r="M24" s="10" t="inlineStr">
+      <c r="M26" s="10" t="inlineStr">
         <is>
           <t>2026/09/04</t>
         </is>
       </c>
-      <c r="N24" s="10" t="inlineStr">
+      <c r="N26" s="10" t="inlineStr">
         <is>
           <t>2026/09/14</t>
         </is>
       </c>
-      <c r="O24" s="12" t="inlineStr">
+      <c r="O26" s="12" t="inlineStr">
         <is>
           <t>HPT sku: MODS無法測試,請BIOS RD儘速釐清</t>
         </is>
       </c>
-      <c r="P24" s="12" t="inlineStr">
+      <c r="P26" s="12" t="inlineStr">
         <is>
           <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/17(Delay 4W),因專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP 預計延後 2週至 9/14 (先前已由9 月底提前至8/31,現又延至9/
 14),後續將依實際測試結果滾動式調整時程。
@@ -2362,405 +2510,246 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>14T3</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Prestige N14 AI+ D1M</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>N1 35W</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>倪嬌嬌</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>2025/04/30</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>2025/09/01</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/15</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/03</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/14</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>2026/10/13</t>
-        </is>
-      </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>2026/10/26</t>
-        </is>
-      </c>
-      <c r="O25" s="6" t="inlineStr">
-        <is>
-          <t>MVT SMT@8/3--depend on Material ready date作調整</t>
-        </is>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>1) Schedule: MVT D件備料ready日期待採購/ME確認中
-2）Color plan: 維持開案版本
-3)備料：量產交料HQ23, 十月份交料, 待Samsung確認具體日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>2623</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Prestige N16 C1M</t>
-        </is>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>EVT</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>N1 45W</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>賴雪鳳</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>2025/04/30</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>2025/09/01</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/15</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/03</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/14</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
-          <t>2026/10/13</t>
-        </is>
-      </c>
-      <c r="N26" s="4" t="inlineStr">
-        <is>
-          <t>2026/10/26</t>
-        </is>
-      </c>
-      <c r="O26" s="6" t="inlineStr">
-        <is>
-          <t>1)EVT 更新BSP6.2.1  持續驗證中, 因ID 顏色修改+機構修模 MVT 預計延後2周到8/3</t>
-        </is>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
+          <t>14T3</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Prestige N14 AI+ D1M</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>N1 35W</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>倪嬌嬌</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/30</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>2025/09/01</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/13</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/26</t>
+        </is>
+      </c>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
+          <t>MVT SMT@8/3--depend on Material ready date作調整</t>
+        </is>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>1) Schedule: a.MVT D件備料ready日期@7/29 b. CPU交期還未放行, 先預估8/B交期
+3)備料：量產交料HQ23, 11/M交料, 還在持續追蹤中</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>2623</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Prestige N16 C1M</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>EVT</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>N1 45W</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>賴雪鳳</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/30</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>2025/09/01</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/13</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/26</t>
+        </is>
+      </c>
+      <c r="O28" s="6" t="inlineStr">
+        <is>
+          <t>1)EVT 更新BSP6.2.1  持續驗證中,ID定案 顏色keep 淺灰+ D side 咬花
+3) N1 SoC 出貨延遲 MVT 預計延到8/3 SMT, 8/4 Pre-Assy ,8/6 Assy</t>
+        </is>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Katana 18 HX A14WEK</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
         <is>
           <t>2026/08/24</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>2026/10/12</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="L29" s="4" t="inlineStr">
         <is>
           <t>2026/11/02</t>
         </is>
       </c>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>2026/11/21</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>2026/11/30</t>
         </is>
       </c>
-      <c r="O27" s="6" t="inlineStr">
+      <c r="O29" s="6" t="inlineStr">
         <is>
           <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
         </is>
       </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" hidden="1" outlineLevel="1">
-      <c r="A28" s="8" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>Katana 18 HX A14WFK</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>顧曉琴</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J28" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
-      <c r="K28" s="10" t="inlineStr">
-        <is>
-          <t>2026/10/12</t>
-        </is>
-      </c>
-      <c r="L28" s="10" t="inlineStr">
-        <is>
-          <t>2026/11/02</t>
-        </is>
-      </c>
-      <c r="M28" s="10" t="inlineStr">
-        <is>
-          <t>2026/11/21</t>
-        </is>
-      </c>
-      <c r="N28" s="10" t="inlineStr">
-        <is>
-          <t>2026/11/30</t>
-        </is>
-      </c>
-      <c r="O28" s="12" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
-        </is>
-      </c>
-      <c r="P28" s="12" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" hidden="1" outlineLevel="1">
-      <c r="A29" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>Katana 18 HX A14WGK</t>
-        </is>
-      </c>
-      <c r="D29" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G29" s="10" t="inlineStr">
-        <is>
-          <t>顧曉琴</t>
-        </is>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J29" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
-      <c r="K29" s="10" t="inlineStr">
-        <is>
-          <t>2026/10/12</t>
-        </is>
-      </c>
-      <c r="L29" s="10" t="inlineStr">
-        <is>
-          <t>2026/11/02</t>
-        </is>
-      </c>
-      <c r="M29" s="10" t="inlineStr">
-        <is>
-          <t>2026/11/21</t>
-        </is>
-      </c>
-      <c r="N29" s="10" t="inlineStr">
-        <is>
-          <t>2026/11/30</t>
-        </is>
-      </c>
-      <c r="O29" s="12" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
-        </is>
-      </c>
-      <c r="P29" s="12" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
+2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2764,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WEOK</t>
+          <t>Katana 18 HX A14WFK</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
@@ -2790,7 +2779,7 @@
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
@@ -2800,18 +2789,22 @@
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J30" s="10" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
       <c r="K30" s="10" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/10/12</t>
         </is>
       </c>
       <c r="L30" s="10" t="inlineStr">
@@ -2821,22 +2814,23 @@
       </c>
       <c r="M30" s="10" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2026/11/21</t>
         </is>
       </c>
       <c r="N30" s="10" t="inlineStr">
         <is>
-          <t>2026/12/02</t>
+          <t>2026/11/30</t>
         </is>
       </c>
       <c r="O30" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT 7/6 RD領取測試</t>
+          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
         </is>
       </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
+2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2845,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WFOK</t>
+          <t>Katana 18 HX A14WGK</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
@@ -2866,7 +2860,7 @@
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -2876,18 +2870,22 @@
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J31" s="10" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
       <c r="K31" s="10" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/10/12</t>
         </is>
       </c>
       <c r="L31" s="10" t="inlineStr">
@@ -2897,22 +2895,23 @@
       </c>
       <c r="M31" s="10" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2026/11/21</t>
         </is>
       </c>
       <c r="N31" s="10" t="inlineStr">
         <is>
-          <t>2026/12/02</t>
+          <t>2026/11/30</t>
         </is>
       </c>
       <c r="O31" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT 7/6 RD領取測試</t>
+          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
         </is>
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
+2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
         </is>
       </c>
     </row>
@@ -2927,7 +2926,7 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGOK</t>
+          <t>Katana 18 HX A14WEOK</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
@@ -2942,7 +2941,7 @@
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
@@ -2983,7 +2982,7 @@
       </c>
       <c r="O32" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT 7/6 RD領取測試</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P32" s="12" t="inlineStr">
@@ -3003,7 +3002,7 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WEO</t>
+          <t>Katana 18 HX A14WFOK</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
@@ -3018,7 +3017,7 @@
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
@@ -3049,17 +3048,17 @@
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2026/11/23</t>
         </is>
       </c>
       <c r="N33" s="10" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2026/12/02</t>
         </is>
       </c>
       <c r="O33" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT 7/6 RD領取測試</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P33" s="12" t="inlineStr">
@@ -3079,7 +3078,7 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WFO</t>
+          <t>Katana 18 HX A14WGOK</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
@@ -3094,7 +3093,7 @@
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
@@ -3125,17 +3124,17 @@
       </c>
       <c r="M34" s="10" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2026/11/23</t>
         </is>
       </c>
       <c r="N34" s="10" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2026/12/02</t>
         </is>
       </c>
       <c r="O34" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT 7/6 RD領取測試</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P34" s="12" t="inlineStr">
@@ -3155,7 +3154,7 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WGO</t>
+          <t>Crosshair 18 Max HX B14WE</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
@@ -3170,7 +3169,7 @@
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
@@ -3180,15 +3179,19 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J35" s="10" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
       <c r="K35" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3211,12 +3214,13 @@
       </c>
       <c r="O35" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT 7/6 RD領取測試</t>
+          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
         </is>
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
+2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3235,7 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WGXO</t>
+          <t>Crosshair 18 Max HX B14WF</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
@@ -3246,7 +3250,7 @@
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
@@ -3256,15 +3260,19 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J36" s="10" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
       <c r="K36" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3287,12 +3295,13 @@
       </c>
       <c r="O36" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT 7/6 RD領取測試</t>
+          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
         </is>
       </c>
       <c r="P36" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
+2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3316,7 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WE</t>
+          <t>Crosshair 18 Max HX B14WG</t>
         </is>
       </c>
       <c r="D37" s="14" t="inlineStr">
@@ -3322,7 +3331,7 @@
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
@@ -3372,7 +3381,8 @@
       </c>
       <c r="P37" s="12" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
+2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3397,7 @@
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WF</t>
+          <t>Crosshair 18 Max HX B14WGX</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
@@ -3402,7 +3412,7 @@
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
@@ -3452,7 +3462,8 @@
       </c>
       <c r="P38" s="12" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
+2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3478,7 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WG</t>
+          <t>Crosshair 18 Max HX B14WEO</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
@@ -3482,7 +3493,7 @@
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
@@ -3492,19 +3503,15 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J39" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J39" s="10" t="inlineStr"/>
       <c r="K39" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3527,12 +3534,12 @@
       </c>
       <c r="O39" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3554,7 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WGX</t>
+          <t>Crosshair 18 Max HX B14WFO</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
@@ -3562,7 +3569,7 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
@@ -3572,19 +3579,15 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J40" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J40" s="10" t="inlineStr"/>
       <c r="K40" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3607,12 +3610,12 @@
       </c>
       <c r="O40" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P40" s="12" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3627,22 +3630,22 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WE</t>
-        </is>
-      </c>
-      <c r="D41" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
+          <t>Crosshair 18 Max HX B14WGO</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>RPL-HX Next 55W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
@@ -3652,34 +3655,38 @@
       </c>
       <c r="H41" s="10" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I41" s="10" t="inlineStr"/>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
       <c r="J41" s="10" t="inlineStr"/>
       <c r="K41" s="10" t="inlineStr">
         <is>
-          <t>2026/12/08</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="L41" s="10" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/11/02</t>
         </is>
       </c>
       <c r="M41" s="10" t="inlineStr">
         <is>
-          <t>2027/01/19</t>
+          <t>2026/11/28</t>
         </is>
       </c>
       <c r="N41" s="10" t="inlineStr">
         <is>
-          <t>2027/01/30</t>
+          <t>2026/12/07</t>
         </is>
       </c>
       <c r="O41" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P41" s="12" t="inlineStr">
@@ -3699,22 +3706,22 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WEO</t>
-        </is>
-      </c>
-      <c r="D42" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
+          <t>Crosshair 18 Max HX B14WGXO</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>RPL-HX Next 55W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
@@ -3727,31 +3734,35 @@
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr"/>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
       <c r="J42" s="10" t="inlineStr"/>
       <c r="K42" s="10" t="inlineStr">
         <is>
-          <t>2026/12/08</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="L42" s="10" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/11/02</t>
         </is>
       </c>
       <c r="M42" s="10" t="inlineStr">
         <is>
-          <t>2027/01/19</t>
+          <t>2026/11/28</t>
         </is>
       </c>
       <c r="N42" s="10" t="inlineStr">
         <is>
-          <t>2027/01/30</t>
+          <t>2026/12/07</t>
         </is>
       </c>
       <c r="O42" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P42" s="12" t="inlineStr">
@@ -3771,7 +3782,7 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WF</t>
+          <t>Crosshair 18 Max HX B2WE</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr">
@@ -3786,7 +3797,7 @@
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
@@ -3843,7 +3854,7 @@
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WFO</t>
+          <t>Crosshair 18 Max HX B2WEO</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
@@ -3858,7 +3869,7 @@
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
@@ -3915,7 +3926,7 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WG</t>
+          <t>Crosshair 18 Max HX B2WF</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
@@ -3930,7 +3941,7 @@
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
@@ -3987,7 +3998,7 @@
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WGO</t>
+          <t>Crosshair 18 Max HX B2WFO</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
@@ -4002,7 +4013,7 @@
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
@@ -4059,7 +4070,7 @@
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WGX</t>
+          <t>Crosshair 18 Max HX B2WG</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
@@ -4131,7 +4142,7 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WGXO</t>
+          <t>Crosshair 18 Max HX B2WGO</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
@@ -4203,7 +4214,7 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WEK</t>
+          <t>Crosshair 18 Max HX B2WGX</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
@@ -4218,7 +4229,7 @@
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G49" s="10" t="inlineStr">
@@ -4275,7 +4286,7 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WEOK</t>
+          <t>Crosshair 18 Max HX B2WGXO</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
@@ -4290,7 +4301,7 @@
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
@@ -4303,11 +4314,7 @@
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
+      <c r="I50" s="10" t="inlineStr"/>
       <c r="J50" s="10" t="inlineStr"/>
       <c r="K50" s="10" t="inlineStr">
         <is>
@@ -4331,7 +4338,7 @@
       </c>
       <c r="O50" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P50" s="12" t="inlineStr">
@@ -4351,7 +4358,7 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WFK</t>
+          <t>Katana 18 HX A2WEK</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
@@ -4366,7 +4373,7 @@
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
@@ -4423,7 +4430,7 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WFOK</t>
+          <t>Katana 18 HX A2WEOK</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
@@ -4438,7 +4445,7 @@
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
@@ -4499,7 +4506,7 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WGK</t>
+          <t>Katana 18 HX A2WFK</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
@@ -4514,7 +4521,7 @@
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
@@ -4571,7 +4578,7 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WGOK</t>
+          <t>Katana 18 HX A2WFOK</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
@@ -4586,7 +4593,7 @@
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
@@ -4636,83 +4643,75 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
+    <row r="55" hidden="1" outlineLevel="1">
+      <c r="A55" s="8" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>14T4</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>Prestige 14 AI</t>
-        </is>
-      </c>
-      <c r="D55" s="13" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>NVL-H 30W</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>Intel® Arc™ Graphics</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>朱芳芳</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/14</t>
-        </is>
-      </c>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/22</t>
-        </is>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/15</t>
-        </is>
-      </c>
-      <c r="K55" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/04</t>
-        </is>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/20</t>
-        </is>
-      </c>
-      <c r="M55" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/15</t>
-        </is>
-      </c>
-      <c r="N55" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/25</t>
-        </is>
-      </c>
-      <c r="O55" s="6" t="inlineStr">
-        <is>
-          <t>DVT SMT@7/22</t>
-        </is>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>Katana 18 HX A2WGK</t>
+        </is>
+      </c>
+      <c r="D55" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>RPL-HX Next 55W</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>顧曉琴</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I55" s="10" t="inlineStr"/>
+      <c r="J55" s="10" t="inlineStr"/>
+      <c r="K55" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/08</t>
+        </is>
+      </c>
+      <c r="L55" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/30</t>
+        </is>
+      </c>
+      <c r="M55" s="10" t="inlineStr">
+        <is>
+          <t>2027/01/19</t>
+        </is>
+      </c>
+      <c r="N55" s="10" t="inlineStr">
+        <is>
+          <t>2027/01/30</t>
+        </is>
+      </c>
+      <c r="O55" s="12" t="inlineStr">
+        <is>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+        </is>
+      </c>
+      <c r="P55" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -4722,77 +4721,73 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>14T4</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Prestige 14 AI+ Flip</t>
-        </is>
-      </c>
-      <c r="D56" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Katana 18 HX A2WGOK</t>
+        </is>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>NVL-H 30W</t>
+          <t>RPL-HX Next 55W</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>Intel® Arc™ Graphics</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>朱芳芳</t>
+          <t>顧曉琴</t>
         </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>2026/05/14</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
-          <t>2026/07/22</t>
-        </is>
-      </c>
-      <c r="J56" s="10" t="inlineStr">
-        <is>
-          <t>2026/09/15</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J56" s="10" t="inlineStr"/>
       <c r="K56" s="10" t="inlineStr">
         <is>
-          <t>2026/11/04</t>
+          <t>2026/12/08</t>
         </is>
       </c>
       <c r="L56" s="10" t="inlineStr">
         <is>
-          <t>2026/11/20</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="M56" s="10" t="inlineStr">
         <is>
-          <t>2026/12/15</t>
+          <t>2027/01/19</t>
         </is>
       </c>
       <c r="N56" s="10" t="inlineStr">
         <is>
-          <t>2026/12/25</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="O56" s="12" t="inlineStr">
         <is>
-          <t>DVT SMT@7/22</t>
+          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P56" s="12" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -4802,12 +4797,12 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>14T4</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Prestige 16 AI+</t>
+          <t>Prestige 14 AI</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
@@ -4835,7 +4830,11 @@
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="I57" s="4" t="inlineStr"/>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
           <t>2026/09/15</t>
@@ -4878,12 +4877,12 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>14T4</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Prestige 16 Flip AI+</t>
+          <t>Prestige 14 AI+ Flip</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
@@ -4911,7 +4910,11 @@
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="I58" s="10" t="inlineStr"/>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
       <c r="J58" s="10" t="inlineStr">
         <is>
           <t>2026/09/15</t>
@@ -4954,398 +4957,389 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
+          <t>2624</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Prestige 16 AI+</t>
+        </is>
+      </c>
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>NVL-H 30W</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>朱芳芳</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr"/>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/04</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/20</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/15</t>
+        </is>
+      </c>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/25</t>
+        </is>
+      </c>
+      <c r="O59" s="6" t="inlineStr">
+        <is>
+          <t>DVT SMT@7/22</t>
+        </is>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" hidden="1" outlineLevel="1">
+      <c r="A60" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>2624</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>Prestige 16 Flip AI+</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>NVL-H 30W</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G60" s="10" t="inlineStr">
+        <is>
+          <t>朱芳芳</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="I60" s="10" t="inlineStr"/>
+      <c r="J60" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="K60" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/04</t>
+        </is>
+      </c>
+      <c r="L60" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/20</t>
+        </is>
+      </c>
+      <c r="M60" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/15</t>
+        </is>
+      </c>
+      <c r="N60" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/25</t>
+        </is>
+      </c>
+      <c r="O60" s="12" t="inlineStr">
+        <is>
+          <t>DVT SMT@7/22</t>
+        </is>
+      </c>
+      <c r="P60" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
           <t>13Q5</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>Prestige 13 AI+ A4M</t>
         </is>
       </c>
-      <c r="D59" s="17" t="inlineStr">
+      <c r="D61" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>NVL-H 28W</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>顏春梅</t>
         </is>
       </c>
-      <c r="H59" s="4" t="inlineStr">
+      <c r="H61" s="4" t="inlineStr">
         <is>
           <t>2026/06/29</t>
         </is>
       </c>
-      <c r="I59" s="4" t="inlineStr">
+      <c r="I61" s="4" t="inlineStr">
         <is>
           <t>2026/08/18</t>
         </is>
       </c>
-      <c r="J59" s="4" t="inlineStr">
+      <c r="J61" s="4" t="inlineStr">
         <is>
           <t>2026/10/08</t>
         </is>
       </c>
-      <c r="K59" s="4" t="inlineStr">
+      <c r="K61" s="4" t="inlineStr">
         <is>
           <t>2026/11/21</t>
         </is>
       </c>
-      <c r="L59" s="4" t="inlineStr">
+      <c r="L61" s="4" t="inlineStr">
         <is>
           <t>2026/11/22</t>
         </is>
       </c>
-      <c r="M59" s="4" t="inlineStr">
+      <c r="M61" s="4" t="inlineStr">
         <is>
           <t>2026/12/22</t>
         </is>
       </c>
-      <c r="N59" s="4" t="inlineStr">
+      <c r="N61" s="4" t="inlineStr">
         <is>
           <t>2026/12/31</t>
         </is>
       </c>
-      <c r="O59" s="6" t="inlineStr">
+      <c r="O61" s="6" t="inlineStr">
         <is>
           <t>0A layout 中 0A G/O@8/7</t>
         </is>
       </c>
-      <c r="P59" s="6" t="inlineStr">
+      <c r="P61" s="6" t="inlineStr">
         <is>
           <t>Audio Codec由原來的Reltek更換為TI，線路設計，placement變更</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>2633</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>Stealth 16 AI+ B4WI</t>
         </is>
       </c>
-      <c r="D60" s="17" t="inlineStr">
+      <c r="D62" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>RTX 5080</t>
         </is>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G62" s="4" t="inlineStr">
         <is>
           <t>朱欣怡</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
+      <c r="H62" s="4" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I60" s="4" t="inlineStr">
+      <c r="I62" s="4" t="inlineStr">
         <is>
           <t>2026/07/22</t>
         </is>
       </c>
-      <c r="J60" s="4" t="inlineStr">
+      <c r="J62" s="4" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K60" s="4" t="inlineStr">
+      <c r="K62" s="4" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L60" s="4" t="inlineStr">
+      <c r="L62" s="4" t="inlineStr">
         <is>
           <t>2026/11/30</t>
         </is>
       </c>
-      <c r="M60" s="4" t="inlineStr">
+      <c r="M62" s="4" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N60" s="4" t="inlineStr">
+      <c r="N62" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O60" s="6" t="inlineStr">
-        <is>
-          <t>0M gerber out@ 6/30</t>
-        </is>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
+      <c r="O62" s="6" t="inlineStr">
+        <is>
+          <t>產線排程 DVT SMT@7/23</t>
+        </is>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
         <is>
           <t>1) Schedule:NV VBIOS @1/6, gating 8天,預計12/E 拿到WHQL，可能影響到最終TTM 時間</t>
         </is>
       </c>
     </row>
-    <row r="61" hidden="1" outlineLevel="1">
-      <c r="A61" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="9" t="inlineStr">
+    <row r="63" hidden="1" outlineLevel="1">
+      <c r="A63" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>2633</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>Stealth 16 AI+ B4WH</t>
         </is>
       </c>
-      <c r="D61" s="16" t="inlineStr">
+      <c r="D63" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E61" s="10" t="inlineStr">
+      <c r="E63" s="10" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F61" s="10" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>RTX 5070Ti</t>
         </is>
       </c>
-      <c r="G61" s="10" t="inlineStr">
+      <c r="G63" s="10" t="inlineStr">
         <is>
           <t>朱欣怡</t>
         </is>
       </c>
-      <c r="H61" s="10" t="inlineStr">
+      <c r="H63" s="10" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I61" s="10" t="inlineStr">
+      <c r="I63" s="10" t="inlineStr">
         <is>
           <t>2026/07/22</t>
         </is>
       </c>
-      <c r="J61" s="10" t="inlineStr">
+      <c r="J63" s="10" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K61" s="10" t="inlineStr">
+      <c r="K63" s="10" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L61" s="10" t="inlineStr">
+      <c r="L63" s="10" t="inlineStr">
         <is>
           <t>2026/11/30</t>
         </is>
       </c>
-      <c r="M61" s="10" t="inlineStr">
+      <c r="M63" s="10" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N61" s="10" t="inlineStr">
+      <c r="N63" s="10" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O61" s="12" t="inlineStr">
-        <is>
-          <t>0M gerber out@ 6/30</t>
-        </is>
-      </c>
-      <c r="P61" s="12" t="inlineStr">
+      <c r="O63" s="12" t="inlineStr">
+        <is>
+          <t>產線排程 DVT SMT@7/23</t>
+        </is>
+      </c>
+      <c r="P63" s="12" t="inlineStr">
         <is>
           <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" hidden="1" outlineLevel="1">
-      <c r="A62" s="8" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="C62" s="10" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WJ</t>
-        </is>
-      </c>
-      <c r="D62" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E62" s="10" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F62" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5090</t>
-        </is>
-      </c>
-      <c r="G62" s="10" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H62" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I62" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/22</t>
-        </is>
-      </c>
-      <c r="J62" s="10" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K62" s="10" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L62" s="10" t="inlineStr">
-        <is>
-          <t>2026/11/30</t>
-        </is>
-      </c>
-      <c r="M62" s="10" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N62" s="10" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="O62" s="12" t="inlineStr">
-        <is>
-          <t>0M gerber out@ 6/30</t>
-        </is>
-      </c>
-      <c r="P62" s="12" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WE</t>
-        </is>
-      </c>
-      <c r="D63" s="17" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I63" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K63" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L63" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/27</t>
-        </is>
-      </c>
-      <c r="M63" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N63" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="O63" s="6" t="inlineStr">
-        <is>
-          <t>0A layout start 6/8-7/17</t>
-        </is>
-      </c>
-      <c r="P63" s="6" t="inlineStr">
-        <is>
-          <t>1)NV VBIOS 驗證時間6周
-2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
     </row>
@@ -5355,156 +5349,155 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
+          <t>2633</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WJ</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5090</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
+      <c r="J64" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K64" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L64" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="M64" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N64" s="10" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="O64" s="12" t="inlineStr">
+        <is>
+          <t>產線排程 DVT SMT@7/23</t>
+        </is>
+      </c>
+      <c r="P64" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
           <t>2634</t>
         </is>
       </c>
-      <c r="C64" s="10" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WF</t>
-        </is>
-      </c>
-      <c r="D64" s="16" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WE</t>
+        </is>
+      </c>
+      <c r="D65" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E64" s="10" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F64" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G64" s="10" t="inlineStr">
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
         <is>
           <t>朱欣怡</t>
         </is>
       </c>
-      <c r="H64" s="10" t="inlineStr">
+      <c r="H65" s="4" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I64" s="10" t="inlineStr">
+      <c r="I65" s="4" t="inlineStr">
         <is>
           <t>2026/08/07</t>
         </is>
       </c>
-      <c r="J64" s="10" t="inlineStr">
+      <c r="J65" s="4" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K64" s="10" t="inlineStr">
+      <c r="K65" s="4" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L64" s="10" t="inlineStr">
+      <c r="L65" s="4" t="inlineStr">
         <is>
           <t>2026/11/27</t>
         </is>
       </c>
-      <c r="M64" s="10" t="inlineStr">
+      <c r="M65" s="4" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N64" s="10" t="inlineStr">
+      <c r="N65" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O64" s="12" t="inlineStr">
+      <c r="O65" s="6" t="inlineStr">
         <is>
           <t>0A layout start 6/8-7/17</t>
         </is>
       </c>
-      <c r="P64" s="12" t="inlineStr">
-        <is>
-          <t>1)NV VBIOS 驗證時間6周
-2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" hidden="1" outlineLevel="1">
-      <c r="A65" s="8" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="9" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="C65" s="10" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
-        </is>
-      </c>
-      <c r="D65" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E65" s="10" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F65" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G65" s="10" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H65" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I65" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="J65" s="10" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K65" s="10" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L65" s="10" t="inlineStr">
-        <is>
-          <t>2026/11/27</t>
-        </is>
-      </c>
-      <c r="M65" s="10" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N65" s="10" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="O65" s="12" t="inlineStr">
-        <is>
-          <t>0A layout start 6/8-7/17</t>
-        </is>
-      </c>
-      <c r="P65" s="12" t="inlineStr">
+      <c r="P65" s="6" t="inlineStr">
         <is>
           <t>1)NV VBIOS 驗證時間6周
 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
@@ -5522,7 +5515,7 @@
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
+          <t>Stealth 16 AI+ B4WF</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
@@ -5537,7 +5530,7 @@
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
@@ -5592,83 +5585,84 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
+    <row r="67" hidden="1" outlineLevel="1">
+      <c r="A67" s="8" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>2654</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>Raider 16 Max HX B4WH</t>
-        </is>
-      </c>
-      <c r="D67" s="13" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5070Ti</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>吳美芳</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I67" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K67" s="4" t="inlineStr">
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
+        </is>
+      </c>
+      <c r="D67" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G67" s="10" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="J67" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K67" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L67" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/27</t>
+        </is>
+      </c>
+      <c r="M67" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N67" s="10" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M67" s="4" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N67" s="4" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O67" s="6" t="inlineStr">
-        <is>
-          <t>6/29 gerber out，预计7/27 DVT打板</t>
-        </is>
-      </c>
-      <c r="P67" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="O67" s="12" t="inlineStr">
+        <is>
+          <t>0A layout start 6/8-7/17</t>
+        </is>
+      </c>
+      <c r="P67" s="12" t="inlineStr">
+        <is>
+          <t>1)NV VBIOS 驗證時間6周
+2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
     </row>
@@ -5678,155 +5672,156 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
+        </is>
+      </c>
+      <c r="D68" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G68" s="10" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="J68" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K68" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L68" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/27</t>
+        </is>
+      </c>
+      <c r="M68" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N68" s="10" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="O68" s="12" t="inlineStr">
+        <is>
+          <t>0A layout start 6/8-7/17</t>
+        </is>
+      </c>
+      <c r="P68" s="12" t="inlineStr">
+        <is>
+          <t>1)NV VBIOS 驗證時間6周
+2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
           <t>2654</t>
         </is>
       </c>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
-          <t>Raider 16 Max HX B4WI</t>
-        </is>
-      </c>
-      <c r="D68" s="14" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Raider 16 Max HX B4WH</t>
+        </is>
+      </c>
+      <c r="D69" s="13" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E68" s="10" t="inlineStr">
+      <c r="E69" s="4" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F68" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5080</t>
-        </is>
-      </c>
-      <c r="G68" s="10" t="inlineStr">
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
         <is>
           <t>吳美芳</t>
         </is>
       </c>
-      <c r="H68" s="10" t="inlineStr">
+      <c r="H69" s="4" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I68" s="10" t="inlineStr">
+      <c r="I69" s="4" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J68" s="10" t="inlineStr">
+      <c r="J69" s="4" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K68" s="10" t="inlineStr">
+      <c r="K69" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L68" s="10" t="inlineStr">
+      <c r="L69" s="4" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M68" s="10" t="inlineStr">
+      <c r="M69" s="4" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N68" s="10" t="inlineStr">
+      <c r="N69" s="4" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O68" s="12" t="inlineStr">
+      <c r="O69" s="6" t="inlineStr">
         <is>
           <t>6/29 gerber out，预计7/27 DVT打板</t>
         </is>
       </c>
-      <c r="P68" s="12" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" hidden="1" outlineLevel="1">
-      <c r="A69" s="8" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="9" t="inlineStr">
-        <is>
-          <t>2654</t>
-        </is>
-      </c>
-      <c r="C69" s="10" t="inlineStr">
-        <is>
-          <t>Raider 16 Max HX B4WJ</t>
-        </is>
-      </c>
-      <c r="D69" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E69" s="10" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F69" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5090</t>
-        </is>
-      </c>
-      <c r="G69" s="10" t="inlineStr">
-        <is>
-          <t>吳美芳</t>
-        </is>
-      </c>
-      <c r="H69" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I69" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J69" s="10" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K69" s="10" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L69" s="10" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M69" s="10" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N69" s="10" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O69" s="12" t="inlineStr">
-        <is>
-          <t>6/29 gerber out，预计7/27 DVT打板</t>
-        </is>
-      </c>
-      <c r="P69" s="12" t="inlineStr">
+      <c r="P69" s="6" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -5843,7 +5838,7 @@
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WH</t>
+          <t>Raider 16 Max HX B4WI</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
@@ -5858,7 +5853,7 @@
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
@@ -5923,7 +5918,7 @@
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WI</t>
+          <t>Raider 16 Max HX B4WJ</t>
         </is>
       </c>
       <c r="D71" s="14" t="inlineStr">
@@ -5938,7 +5933,7 @@
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
@@ -5992,81 +5987,85 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="n">
+    <row r="72" hidden="1" outlineLevel="1">
+      <c r="A72" s="8" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>1851</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>Titan 18 HX B4WH</t>
-        </is>
-      </c>
-      <c r="D72" s="17" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>2654</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>Raider 16  HX B4WH</t>
+        </is>
+      </c>
+      <c r="D72" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr">
+      <c r="F72" s="10" t="inlineStr">
         <is>
           <t>RTX 5070Ti</t>
         </is>
       </c>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>高宇奇</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="I72" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/14</t>
-        </is>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>2026/10/23</t>
-        </is>
-      </c>
-      <c r="K72" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/08</t>
-        </is>
-      </c>
-      <c r="L72" s="4" t="inlineStr">
-        <is>
-          <t>2027/02/01</t>
-        </is>
-      </c>
-      <c r="M72" s="4" t="inlineStr">
+      <c r="G72" s="10" t="inlineStr">
+        <is>
+          <t>吳美芳</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I72" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J72" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K72" s="10" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="L72" s="10" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M72" s="10" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N72" s="4" t="inlineStr">
+      <c r="N72" s="10" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O72" s="6" t="inlineStr">
-        <is>
-          <t>0M layout進行中,預計7/27 0M gerber out.</t>
-        </is>
-      </c>
-      <c r="P72" s="6" t="inlineStr"/>
+      <c r="O72" s="12" t="inlineStr">
+        <is>
+          <t>6/29 gerber out，预计7/27 DVT打板</t>
+        </is>
+      </c>
+      <c r="P72" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="73" hidden="1" outlineLevel="1">
       <c r="A73" s="8" t="n">
@@ -6074,151 +6073,155 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
+          <t>2654</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>Raider 16  HX B4WI</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5080</t>
+        </is>
+      </c>
+      <c r="G73" s="10" t="inlineStr">
+        <is>
+          <t>吳美芳</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J73" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K73" s="10" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="L73" s="10" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M73" s="10" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N73" s="10" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O73" s="12" t="inlineStr">
+        <is>
+          <t>6/29 gerber out，预计7/27 DVT打板</t>
+        </is>
+      </c>
+      <c r="P73" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
           <t>1851</t>
         </is>
       </c>
-      <c r="C73" s="10" t="inlineStr">
-        <is>
-          <t>Titan 18 HX B4WI</t>
-        </is>
-      </c>
-      <c r="D73" s="16" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Titan 18 HX B4WH</t>
+        </is>
+      </c>
+      <c r="D74" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E73" s="10" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F73" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5080</t>
-        </is>
-      </c>
-      <c r="G73" s="10" t="inlineStr">
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
         <is>
           <t>高宇奇</t>
         </is>
       </c>
-      <c r="H73" s="10" t="inlineStr">
+      <c r="H74" s="4" t="inlineStr">
         <is>
           <t>2026/06/29</t>
         </is>
       </c>
-      <c r="I73" s="10" t="inlineStr">
+      <c r="I74" s="4" t="inlineStr">
         <is>
           <t>2026/08/14</t>
         </is>
       </c>
-      <c r="J73" s="10" t="inlineStr">
+      <c r="J74" s="4" t="inlineStr">
         <is>
           <t>2026/10/23</t>
         </is>
       </c>
-      <c r="K73" s="10" t="inlineStr">
+      <c r="K74" s="4" t="inlineStr">
         <is>
           <t>2027/01/08</t>
         </is>
       </c>
-      <c r="L73" s="10" t="inlineStr">
+      <c r="L74" s="4" t="inlineStr">
         <is>
           <t>2027/02/01</t>
         </is>
       </c>
-      <c r="M73" s="10" t="inlineStr">
+      <c r="M74" s="4" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N73" s="10" t="inlineStr">
+      <c r="N74" s="4" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O73" s="12" t="inlineStr">
+      <c r="O74" s="6" t="inlineStr">
         <is>
           <t>0M layout進行中,預計7/27 0M gerber out.</t>
         </is>
       </c>
-      <c r="P73" s="12" t="inlineStr"/>
-    </row>
-    <row r="74" hidden="1" outlineLevel="1">
-      <c r="A74" s="8" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="9" t="inlineStr">
-        <is>
-          <t>1851</t>
-        </is>
-      </c>
-      <c r="C74" s="10" t="inlineStr">
-        <is>
-          <t>Titan 18 HX B4WJ</t>
-        </is>
-      </c>
-      <c r="D74" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E74" s="10" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F74" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5090</t>
-        </is>
-      </c>
-      <c r="G74" s="10" t="inlineStr">
-        <is>
-          <t>高宇奇</t>
-        </is>
-      </c>
-      <c r="H74" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="I74" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/14</t>
-        </is>
-      </c>
-      <c r="J74" s="10" t="inlineStr">
-        <is>
-          <t>2026/10/23</t>
-        </is>
-      </c>
-      <c r="K74" s="10" t="inlineStr">
-        <is>
-          <t>2027/01/08</t>
-        </is>
-      </c>
-      <c r="L74" s="10" t="inlineStr">
-        <is>
-          <t>2027/02/01</t>
-        </is>
-      </c>
-      <c r="M74" s="10" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N74" s="10" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O74" s="12" t="inlineStr">
-        <is>
-          <t>0M layout進行中,預計7/27 0M gerber out.</t>
-        </is>
-      </c>
-      <c r="P74" s="12" t="inlineStr"/>
+      <c r="P74" s="6" t="inlineStr"/>
     </row>
     <row r="75" hidden="1" outlineLevel="1">
       <c r="A75" s="8" t="n">
@@ -6231,7 +6234,7 @@
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Raider 18 Max HX B4WH</t>
+          <t>Titan 18 HX B4WI</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
@@ -6241,12 +6244,12 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>NVL-HX 65W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="G75" s="10" t="inlineStr">
@@ -6307,7 +6310,7 @@
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>Raider 18 Max HX B4WI</t>
+          <t>Titan 18 HX B4WJ</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
@@ -6317,12 +6320,12 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>NVL-HX 65W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
@@ -6383,7 +6386,7 @@
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>Raider 18 Max HX B4WJ</t>
+          <t>Raider 18 Max HX B4WH</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
@@ -6398,7 +6401,7 @@
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr">
@@ -6448,85 +6451,81 @@
       </c>
       <c r="P77" s="12" t="inlineStr"/>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="n">
+    <row r="78" hidden="1" outlineLevel="1">
+      <c r="A78" s="8" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>2655</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WEK</t>
-        </is>
-      </c>
-      <c r="D78" s="13" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>鮑佩佩</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I78" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K78" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M78" s="4" t="inlineStr">
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>Raider 18 Max HX B4WI</t>
+        </is>
+      </c>
+      <c r="D78" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>NVL-HX 65W</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5080</t>
+        </is>
+      </c>
+      <c r="G78" s="10" t="inlineStr">
+        <is>
+          <t>高宇奇</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="J78" s="10" t="inlineStr">
+        <is>
+          <t>2026/10/23</t>
+        </is>
+      </c>
+      <c r="K78" s="10" t="inlineStr">
+        <is>
+          <t>2027/01/08</t>
+        </is>
+      </c>
+      <c r="L78" s="10" t="inlineStr">
+        <is>
+          <t>2027/02/01</t>
+        </is>
+      </c>
+      <c r="M78" s="10" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N78" s="4" t="inlineStr">
+      <c r="N78" s="10" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O78" s="6" t="inlineStr">
-        <is>
-          <t>0A 7/3 gerber out.plan 7/27 DVT SMT1</t>
-        </is>
-      </c>
-      <c r="P78" s="6" t="inlineStr">
-        <is>
-          <t>na</t>
-        </is>
-      </c>
+      <c r="O78" s="12" t="inlineStr">
+        <is>
+          <t>0M layout進行中,預計7/27 0M gerber out.</t>
+        </is>
+      </c>
+      <c r="P78" s="12" t="inlineStr"/>
     </row>
     <row r="79" hidden="1" outlineLevel="1">
       <c r="A79" s="8" t="n">
@@ -6534,157 +6533,153 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>Raider 18 Max HX B4WJ</t>
+        </is>
+      </c>
+      <c r="D79" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>NVL-HX 65W</t>
+        </is>
+      </c>
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5090</t>
+        </is>
+      </c>
+      <c r="G79" s="10" t="inlineStr">
+        <is>
+          <t>高宇奇</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="J79" s="10" t="inlineStr">
+        <is>
+          <t>2026/10/23</t>
+        </is>
+      </c>
+      <c r="K79" s="10" t="inlineStr">
+        <is>
+          <t>2027/01/08</t>
+        </is>
+      </c>
+      <c r="L79" s="10" t="inlineStr">
+        <is>
+          <t>2027/02/01</t>
+        </is>
+      </c>
+      <c r="M79" s="10" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N79" s="10" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O79" s="12" t="inlineStr">
+        <is>
+          <t>0M layout進行中,預計7/27 0M gerber out.</t>
+        </is>
+      </c>
+      <c r="P79" s="12" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
           <t>2655</t>
         </is>
       </c>
-      <c r="C79" s="10" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WFK</t>
-        </is>
-      </c>
-      <c r="D79" s="14" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Crosshair 16 Max HX E4WEK</t>
+        </is>
+      </c>
+      <c r="D80" s="13" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E79" s="10" t="inlineStr">
+      <c r="E80" s="4" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F79" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G79" s="10" t="inlineStr">
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
         <is>
           <t>鮑佩佩</t>
         </is>
       </c>
-      <c r="H79" s="10" t="inlineStr">
+      <c r="H80" s="4" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I79" s="10" t="inlineStr">
+      <c r="I80" s="4" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J79" s="10" t="inlineStr">
+      <c r="J80" s="4" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K79" s="10" t="inlineStr">
+      <c r="K80" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L79" s="10" t="inlineStr">
+      <c r="L80" s="4" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M79" s="10" t="inlineStr">
+      <c r="M80" s="4" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N79" s="10" t="inlineStr">
+      <c r="N80" s="4" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O79" s="12" t="inlineStr">
+      <c r="O80" s="6" t="inlineStr">
         <is>
           <t>0A 7/3 gerber out.plan 7/27 DVT SMT1</t>
         </is>
       </c>
-      <c r="P79" s="12" t="inlineStr">
-        <is>
-          <t>na</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" hidden="1" outlineLevel="1">
-      <c r="A80" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>2655</t>
-        </is>
-      </c>
-      <c r="C80" s="10" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WGK</t>
-        </is>
-      </c>
-      <c r="D80" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E80" s="10" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F80" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G80" s="10" t="inlineStr">
-        <is>
-          <t>鮑佩佩</t>
-        </is>
-      </c>
-      <c r="H80" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I80" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J80" s="10" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K80" s="10" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L80" s="10" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M80" s="10" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N80" s="10" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O80" s="12" t="inlineStr">
-        <is>
-          <t>0A 7/3 gerber out.plan 7/27 DVT SMT1</t>
-        </is>
-      </c>
-      <c r="P80" s="12" t="inlineStr">
-        <is>
-          <t>na</t>
+      <c r="P80" s="6" t="inlineStr">
+        <is>
+          <t>產品策略調整,2655 計畫提升為Raider 16,RD 評估中</t>
         </is>
       </c>
     </row>
@@ -6699,77 +6694,237 @@
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
+          <t>Crosshair 16 Max HX E4WFK</t>
+        </is>
+      </c>
+      <c r="D81" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G81" s="10" t="inlineStr">
+        <is>
+          <t>鮑佩佩</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J81" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K81" s="10" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="L81" s="10" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M81" s="10" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N81" s="10" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O81" s="12" t="inlineStr">
+        <is>
+          <t>0A 7/3 gerber out.plan 7/27 DVT SMT1</t>
+        </is>
+      </c>
+      <c r="P81" s="12" t="inlineStr">
+        <is>
+          <t>產品策略調整,2655 計畫提升為Raider 16,RD 評估中</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" hidden="1" outlineLevel="1">
+      <c r="A82" s="8" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>2655</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>Crosshair 16 Max HX E4WGK</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G82" s="10" t="inlineStr">
+        <is>
+          <t>鮑佩佩</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I82" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J82" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K82" s="10" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="L82" s="10" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M82" s="10" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N82" s="10" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O82" s="12" t="inlineStr">
+        <is>
+          <t>0A 7/3 gerber out.plan 7/27 DVT SMT1</t>
+        </is>
+      </c>
+      <c r="P82" s="12" t="inlineStr">
+        <is>
+          <t>產品策略調整,2655 計畫提升為Raider 16,RD 評估中</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" hidden="1" outlineLevel="1">
+      <c r="A83" s="8" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>2655</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
           <t>Crosshair 16 Max HX E4WGXK</t>
         </is>
       </c>
-      <c r="D81" s="14" t="inlineStr">
+      <c r="D83" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E81" s="10" t="inlineStr">
+      <c r="E83" s="10" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr">
+      <c r="F83" s="10" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G81" s="10" t="inlineStr">
+      <c r="G83" s="10" t="inlineStr">
         <is>
           <t>鮑佩佩</t>
         </is>
       </c>
-      <c r="H81" s="10" t="inlineStr">
+      <c r="H83" s="10" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I81" s="10" t="inlineStr">
+      <c r="I83" s="10" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J81" s="10" t="inlineStr">
+      <c r="J83" s="10" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K81" s="10" t="inlineStr">
+      <c r="K83" s="10" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L81" s="10" t="inlineStr">
+      <c r="L83" s="10" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M81" s="10" t="inlineStr">
+      <c r="M83" s="10" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N81" s="10" t="inlineStr">
+      <c r="N83" s="10" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O81" s="12" t="inlineStr">
+      <c r="O83" s="12" t="inlineStr">
         <is>
           <t>0A 7/3 gerber out.plan 7/27 DVT SMT1</t>
         </is>
       </c>
-      <c r="P81" s="12" t="inlineStr">
-        <is>
-          <t>na</t>
+      <c r="P83" s="12" t="inlineStr">
+        <is>
+          <t>產品策略調整,2655 計畫提升為Raider 16,RD 評估中</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P81"/>
+  <autoFilter ref="A1:P83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/npi_dashboard.xlsx
+++ b/npi_dashboard.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPI Dashboard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -516,7 +516,7 @@
     <outlinePr summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P83"/>
+  <dimension ref="A1:P85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -625,12 +625,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>14V2</t>
+          <t>24VL</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Modern 14 H13M</t>
+          <t>Modern A14 LE J1M</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -640,12 +640,12 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>RPL-U 25W</t>
+          <t>RMB 100 25W</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Intel® graphics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -655,39 +655,43 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>2025/11/14</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
+          <t>2026/01/05</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>2026/03/30</t>
+        </is>
+      </c>
       <c r="J2" s="4" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>2026/01/14</t>
+          <t>2026/04/17</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>2026/03/16</t>
+          <t>2026/05/15</t>
         </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>2026/07/06</t>
+          <t>2026/07/01</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>2026/07/10</t>
+          <t>2026/07/18</t>
         </is>
       </c>
       <c r="O2" s="6" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>ATS客驗：DQA 客驗Pass, QA 機台7/16 提供，待確認客驗結果</t>
         </is>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
-          <t>因首批安排RPL-U Refresh 優先投產，第二波投產因PCB 最快交期落在6/29,加上微步盤點，機台7/9 入庫</t>
+          <t>1).Schedule ：因Camera 丟失問題，安排重工Camera，機台入庫時間預抓從7/13 延後到7/18，delay5天</t>
         </is>
       </c>
     </row>
@@ -697,12 +701,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>24VL</t>
+          <t>26VL</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Modern A14 LE J1M</t>
+          <t>Modern A16 LE J1M</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -712,7 +716,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>RMB 100 25W</t>
+          <t>RMB 100 28W</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -748,22 +752,23 @@
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>2026/07/01</t>
+          <t>2026/07/04</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>2026/07/18</t>
+          <t>2026/07/20</t>
         </is>
       </c>
       <c r="O3" s="6" t="inlineStr">
         <is>
-          <t>ATS客驗：DQA 客驗Pass, QA 機台7/16 提供，待確認客驗結果</t>
+          <t>因Camera 丟失ISSUE，待確認執行方案</t>
         </is>
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>1).Schedule ：因Camera 丟失問題，安排重工Camera，機台入庫時間預抓從7/13 延後到7/18，delay5天</t>
+          <t>Schedule  ：（TTM原計劃7/15 先預抓延後到7/
+20）：7/16 會議請微步放量200台驗證以及全掃功能，待微步提供具體數據，請示執行方案後，追蹤最快機台入庫時間</t>
         </is>
       </c>
     </row>
@@ -773,146 +778,141 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>26VL</t>
+          <t>265L</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Modern A16 LE J1M</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>ATS</t>
+          <t>Crosshair A16 HX E9WGXK</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>MVT</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>RMB 100 28W</t>
+          <t>FRG-HX3D 55W</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>杜晨光</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>2026/03/30</t>
-        </is>
-      </c>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
       <c r="J4" s="4" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/05/18</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>2026/05/15</t>
+          <t>2026/06/16</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>2026/07/04</t>
+          <t>2026/07/16</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>2026/07/20</t>
+          <t>2026/07/26</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>因Camera 丟失ISSUE，待確認執行方案</t>
+          <t>FRG (5/4通知resume）: DQA 測試中</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>Schedule  ：（TTM原計劃7/15 先預抓延後到7/
-20）：7/16 會議請微步放量200台驗證以及全掃功能，待微步提供具體數據，請示執行方案後，追蹤最快機台入庫時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
+          <t>1）暫無業務報價，BTO 未開</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" hidden="1" outlineLevel="1">
+      <c r="A5" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>265L</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Crosshair A16 HX E9WGXK</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Crosshair A16 HX E9WEK</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>FRG-HX3D 55W</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>FRG-HX 55W</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>朱欣怡</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>2025/10/22</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr"/>
+      <c r="J5" s="10" t="inlineStr"/>
+      <c r="K5" s="10" t="inlineStr">
         <is>
           <t>2026/05/18</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="L5" s="10" t="inlineStr">
         <is>
           <t>2026/06/16</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>2026/07/16</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>2026/07/26</t>
         </is>
       </c>
-      <c r="O5" s="6" t="inlineStr">
+      <c r="O5" s="12" t="inlineStr">
         <is>
           <t>FRG (5/4通知resume）: DQA 測試中</t>
         </is>
       </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>1）暫無業務報價，BTO 未開</t>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Crosshair A16 HX E9WFK</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -988,665 +988,663 @@
         </is>
       </c>
     </row>
-    <row r="7" hidden="1" outlineLevel="1">
-      <c r="A7" s="8" t="n">
+    <row r="7">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>265L</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>Crosshair A16 HX E9WFK</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>15Q1</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Cyborg 15 B2VEK</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>FRG-HX 55W</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="I7" s="10" t="inlineStr"/>
-      <c r="J7" s="10" t="inlineStr"/>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/18</t>
-        </is>
-      </c>
-      <c r="L7" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/16</t>
-        </is>
-      </c>
-      <c r="M7" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/16</t>
-        </is>
-      </c>
-      <c r="N7" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
-      <c r="O7" s="12" t="inlineStr">
-        <is>
-          <t>FRG (5/4通知resume）: DQA 測試中</t>
-        </is>
-      </c>
-      <c r="P7" s="12" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>ARL-H 45W</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>RTX 4050 (35W+10W)/ GDDR6 6GB</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>李文欽</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr"/>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/31</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>（清日文4區RGB鍵盤庫存）DQA測試中,預計7/21完成</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>1)DQA驗證有Audio問題, WHQL驅動預計7/24提供,需要Preload和DQA等單位加班驗證,滿足業務7/30出貨需求</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" hidden="1" outlineLevel="1">
+      <c r="A8" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>15Q1</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Cyborg 15 B2VE</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>ARL-H 45W</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>RTX 4050 (35W+10W)/ GDDR6 6GB</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>李文欽</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>2026/06/24</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr"/>
+      <c r="J8" s="10" t="inlineStr"/>
+      <c r="K8" s="10" t="inlineStr">
         <is>
           <t>2026/06/29</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="L8" s="10" t="inlineStr">
         <is>
           <t>2026/06/29</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="M8" s="10" t="inlineStr">
         <is>
           <t>2026/07/20</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>2026/07/31</t>
         </is>
       </c>
-      <c r="O8" s="6" t="inlineStr">
+      <c r="O8" s="12" t="inlineStr">
         <is>
           <t>（清白光鍵盤庫存）DQA測試中,預計7/20完成</t>
         </is>
       </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" hidden="1" outlineLevel="1">
-      <c r="A9" s="8" t="n">
+      <c r="P8" s="12" t="inlineStr">
+        <is>
+          <t>1)DQA驗證有Audio問題, WHQL驅動預計7/24提供,需要Preload和DQA等單位加班驗證</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>15Q1</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Cyborg 15 B2VEK</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>15Q3</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Cyborg 15 Black Edition B13WE</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>ARL-H 45W</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>RTX 4050 (35W+10W)/ GDDR6 6GB</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>李文欽</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>RPL-H 45W</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>楊淑賢</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>2026/06/24</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr"/>
-      <c r="J9" s="10" t="inlineStr"/>
-      <c r="K9" s="10" t="inlineStr"/>
-      <c r="L9" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/26</t>
-        </is>
-      </c>
-      <c r="M9" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/22</t>
-        </is>
-      </c>
-      <c r="N9" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/31</t>
-        </is>
-      </c>
-      <c r="O9" s="12" t="inlineStr">
-        <is>
-          <t>（清日文4區RGB鍵盤庫存）DQA測試中,預計7/21完成</t>
-        </is>
-      </c>
-      <c r="P9" s="12" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>15Q3</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Cyborg 15 Black Edition B13WE</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>RPL-H 45W</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>楊淑賢</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/24</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
-      <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>2026/07/01</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>2026/07/14</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>2026/08/03</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>2026/08/07</t>
         </is>
       </c>
-      <c r="O10" s="6" t="inlineStr">
+      <c r="O9" s="6" t="inlineStr">
         <is>
           <t>DQA test中,
 1) ME: 搖擺測試pass
 2）Function：待新版MSI Center AP release( 包入MKT name支援AI Noise Cancellation Pro), 安排HDI製作</t>
         </is>
       </c>
-      <c r="P10" s="6" t="inlineStr">
+      <c r="P9" s="6" t="inlineStr">
         <is>
           <t>1) Cyborg Black Edition SKU: Cyborg A+Venture B/C/D機構件+白光鍵盤</t>
         </is>
       </c>
     </row>
-    <row r="11" hidden="1" outlineLevel="1">
-      <c r="A11" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
+    <row r="10" hidden="1" outlineLevel="1">
+      <c r="A10" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>15Q3</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Cyborg 15 Black Edition B13WF</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>RPL-H 45W</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>RTX 5060</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>楊淑賢</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>2026/06/24</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr"/>
-      <c r="J11" s="10" t="inlineStr"/>
-      <c r="K11" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr"/>
+      <c r="J10" s="10" t="inlineStr"/>
+      <c r="K10" s="10" t="inlineStr">
         <is>
           <t>2026/07/01</t>
         </is>
       </c>
-      <c r="L11" s="10" t="inlineStr">
+      <c r="L10" s="10" t="inlineStr">
         <is>
           <t>2026/07/14</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M10" s="10" t="inlineStr">
         <is>
           <t>2026/08/03</t>
         </is>
       </c>
-      <c r="N11" s="10" t="inlineStr">
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>2026/08/07</t>
         </is>
       </c>
-      <c r="O11" s="12" t="inlineStr">
+      <c r="O10" s="12" t="inlineStr">
         <is>
           <t>DQA test中,
 1) ME: 搖擺測試pass
 2）Function：待新版MSI Center AP release( 包入MKT name支援AI Noise Cancellation Pro), 安排HDI製作</t>
         </is>
       </c>
-      <c r="P11" s="12" t="inlineStr">
+      <c r="P10" s="12" t="inlineStr">
         <is>
           <t>1) Cyborg Black Edition SKU: Cyborg A+Venture B/C/D機構件+白光鍵盤</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>17U3</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Cyborg 17 Black Edition B13WE</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>RPL-H 45W</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>楊淑賢</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/01</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/14</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t>DQA test中,
+1) ME: 搖擺測試pass
+2）Function：待新版MSI Center AP release( 包入MKT name支援AI Noise Cancellation Pro), 安排HDI製作</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>1) Cyborg Black Edition SKU: Cyborg A+Venture B/C/D機構件+白光鍵盤</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" hidden="1" outlineLevel="1">
+      <c r="A12" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>17U3</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Cyborg 17 Black Edition B13WF</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>RPL-H 45W</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>楊淑賢</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr"/>
+      <c r="J12" s="10" t="inlineStr"/>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/01</t>
+        </is>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/14</t>
+        </is>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>DQA test中,
+1) ME: 搖擺測試pass
+2）Function：待新版MSI Center AP release( 包入MKT name支援AI Noise Cancellation Pro), 安排HDI製作</t>
+        </is>
+      </c>
+      <c r="P12" s="12" t="inlineStr">
+        <is>
+          <t>1) Cyborg Black Edition SKU: Cyborg A+Venture B/C/D機構件+白光鍵盤</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" hidden="1" outlineLevel="1">
+      <c r="A13" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>17U3</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Cyborg 17 Black Edition B2RWF</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>RPL-H refresh 45W</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>楊淑賢</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr"/>
+      <c r="J13" s="10" t="inlineStr"/>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/01</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/14</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>DQA test中,
+1) ME: 搖擺測試pass
+2）Function：待新版MSI Center AP release( 包入MKT name支援AI Noise Cancellation Pro), 安排HDI製作</t>
+        </is>
+      </c>
+      <c r="P13" s="12" t="inlineStr">
+        <is>
+          <t>1) Cyborg Black Edition SKU: Cyborg A+Venture B/C/D機構件+白光鍵盤</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>15T2</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Venture 15 AI+ B3M</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>PTL-H 80W</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>李文欽</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>2026/04/20</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>2026/05/26</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr"/>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>2026/07/08</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>2026/07/20</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>2026/08/17</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>2026/08/27</t>
         </is>
       </c>
-      <c r="O12" s="6" t="inlineStr">
+      <c r="O14" s="6" t="inlineStr">
         <is>
           <t>MVT1 正式組裝@7/13</t>
         </is>
       </c>
-      <c r="P12" s="6" t="inlineStr">
+      <c r="P14" s="6" t="inlineStr">
         <is>
           <t>1) w/FP的Touchpad 試產物料,需要採購協助Pull in</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>15T3</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Katana 15 HX C14WEK</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>2026/04/20</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>2026/06/01</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>2026/07/14</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>2026/07/30</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>2026/08/20</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>2026/08/30</t>
         </is>
       </c>
-      <c r="O13" s="6" t="inlineStr">
+      <c r="O15" s="6" t="inlineStr">
         <is>
           <t>DDR5 sku, 預計7/17 MVT Assy</t>
         </is>
       </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" hidden="1" outlineLevel="1">
-      <c r="A14" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>15T3</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Katana 15 HX C14WFK</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>2026/04/20</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
-      </c>
-      <c r="J14" s="10" t="inlineStr"/>
-      <c r="K14" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/14</t>
-        </is>
-      </c>
-      <c r="L14" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/30</t>
-        </is>
-      </c>
-      <c r="M14" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/20</t>
-        </is>
-      </c>
-      <c r="N14" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/30</t>
-        </is>
-      </c>
-      <c r="O14" s="12" t="inlineStr">
-        <is>
-          <t>DDR5 sku, 預計7/17 MVT Assy</t>
-        </is>
-      </c>
-      <c r="P14" s="12" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" hidden="1" outlineLevel="1">
-      <c r="A15" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>15T3</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>Katana 15 HX C14WGK</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>2026/04/20</t>
-        </is>
-      </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
-      </c>
-      <c r="J15" s="10" t="inlineStr"/>
-      <c r="K15" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/14</t>
-        </is>
-      </c>
-      <c r="L15" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/30</t>
-        </is>
-      </c>
-      <c r="M15" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/20</t>
-        </is>
-      </c>
-      <c r="N15" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/30</t>
-        </is>
-      </c>
-      <c r="O15" s="12" t="inlineStr">
-        <is>
-          <t>DDR5 sku, 預計7/17 MVT Assy</t>
-        </is>
-      </c>
-      <c r="P15" s="12" t="inlineStr">
+      <c r="P15" s="6" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1663,7 +1661,7 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WEOK</t>
+          <t>Katana 15 HX C14WFK</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1678,7 +1676,7 @@
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -1688,38 +1686,38 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>2026/05/15</t>
+          <t>2026/04/20</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
+          <t>2026/06/01</t>
         </is>
       </c>
       <c r="J16" s="10" t="inlineStr"/>
       <c r="K16" s="10" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>2026/08/07</t>
+          <t>2026/07/30</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
-          <t>2026/08/21</t>
+          <t>2026/08/20</t>
         </is>
       </c>
       <c r="N16" s="10" t="inlineStr">
         <is>
-          <t>2026/08/31</t>
+          <t>2026/08/30</t>
         </is>
       </c>
       <c r="O16" s="12" t="inlineStr">
         <is>
-          <t>DDR4 sku, MVT備料中,預計7/24 MVT SMT</t>
+          <t>DDR5 sku, 預計7/17 MVT Assy</t>
         </is>
       </c>
       <c r="P16" s="12" t="inlineStr">
@@ -1739,7 +1737,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WFOK</t>
+          <t>Katana 15 HX C14WGK</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1754,7 +1752,7 @@
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
@@ -1764,38 +1762,38 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>2026/05/15</t>
+          <t>2026/04/20</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
+          <t>2026/06/01</t>
         </is>
       </c>
       <c r="J17" s="10" t="inlineStr"/>
       <c r="K17" s="10" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>2026/08/07</t>
+          <t>2026/07/30</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>2026/08/21</t>
+          <t>2026/08/20</t>
         </is>
       </c>
       <c r="N17" s="10" t="inlineStr">
         <is>
-          <t>2026/08/31</t>
+          <t>2026/08/30</t>
         </is>
       </c>
       <c r="O17" s="12" t="inlineStr">
         <is>
-          <t>DDR4 sku, MVT備料中,預計7/24 MVT SMT</t>
+          <t>DDR5 sku, 預計7/17 MVT Assy</t>
         </is>
       </c>
       <c r="P17" s="12" t="inlineStr">
@@ -1815,7 +1813,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WGOK</t>
+          <t>Katana 15 HX C14WEOK</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1830,7 +1828,7 @@
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
@@ -1880,86 +1878,79 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
+    <row r="19" hidden="1" outlineLevel="1">
+      <c r="A19" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>2621</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Prestige N16 AI+ C1XMT</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>15T3</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Katana 15 HX C14WFOK</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>N1x 80W</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>林晉弘</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>2024/11/25</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>2025/01/20</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>2025/06/25</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>2026/03/12</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/30</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/17</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>蔡東宏</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/15</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="inlineStr"/>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/24</t>
+        </is>
+      </c>
+      <c r="L19" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="N19" s="10" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O19" s="6" t="inlineStr">
-        <is>
-          <t>MVT測試中</t>
-        </is>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>1)battery life測試條件的定義，NV與MSFT討論中，根據7/9會議，DQA會基於BSP Day0 rev.B + balance mode測試，確認是否合乎MSFT要求。
-2)NV Abnormal shut down 的solution，預計會於7/17 BSP Day0 rev.B導入，待SW release後，DQA會驗證確認。
-3)NV 7/7 release新版BSP schedule，軟體預計改版new branch for後續驗證出貨。依據此schedule，在軟體驗證皆無重大issue影響量產的狀況下，ATS預計延後到8/17，入庫時間要到8/31。 a)7/10 Day0 rev.A，DQA基於此版本進行full test驗證 b)7/17 Day0 rev.B，導入ABS solution，DQA會驗證battery life c)7/24 Day0 rev.C，BSP lock down可製作for工廠驗證image，計畫依此版本進行ATS。 d)8/21 Day0 rev.F，可供出貨GPU driver release，請工廠/DQA置換image中 GPU driver驗證
-4)三星 3.8K panel因leading customer改版無法準時出貨，除廠內161pcs外，後續物料到10月中才能到，已先通知業務，確認是否以2.8K panel先上ATS。</t>
+      <c r="O19" s="12" t="inlineStr">
+        <is>
+          <t>DDR4 sku, MVT備料中,預計7/24 MVT SMT</t>
+        </is>
+      </c>
+      <c r="P19" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1969,12 +1960,12 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>15T3</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Prestige N16 Flip AI+ C1XMT</t>
+          <t>Katana 15 HX C14WGOK</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1984,47 +1975,43 @@
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>N1x 80W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>林晉弘</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>2024/11/25</t>
+          <t>2026/05/15</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr">
         <is>
-          <t>2025/01/20</t>
-        </is>
-      </c>
-      <c r="J20" s="10" t="inlineStr">
-        <is>
-          <t>2025/06/25</t>
-        </is>
-      </c>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J20" s="10" t="inlineStr"/>
       <c r="K20" s="10" t="inlineStr">
         <is>
-          <t>2026/03/12</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>2026/06/30</t>
+          <t>2026/08/07</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
-          <t>2026/08/17</t>
+          <t>2026/08/21</t>
         </is>
       </c>
       <c r="N20" s="10" t="inlineStr">
@@ -2034,15 +2021,12 @@
       </c>
       <c r="O20" s="12" t="inlineStr">
         <is>
-          <t>MVT測試中</t>
+          <t>DDR4 sku, MVT備料中,預計7/24 MVT SMT</t>
         </is>
       </c>
       <c r="P20" s="12" t="inlineStr">
         <is>
-          <t>1)battery life測試條件的定義，NV與MSFT討論中，根據7/9會議，DQA會基於BSP Day0 rev.B + balance mode測試，確認是否合乎MSFT要求。
-2)NV Abnormal shut down 的solution，預計會於7/17 BSP Day0 rev.B導入，待SW release後，DQA會驗證確認。
-3)NV 7/7 release新版BSP schedule，軟體預計改版new branch for後續驗證出貨。依據此schedule，在軟體驗證皆無重大issue影響量產的狀況下，ATS預計延後到8/17，入庫時間要到8/31。 a)7/10 Day0 rev.A，DQA基於此版本進行full test驗證 b)7/17 Day0 rev.B，導入ABS solution，DQA會驗證battery life c)7/24 Day0 rev.C，BSP lock down可製作for工廠驗證image，計畫依此版本進行ATS。 d)8/21 Day0 rev.F，可供出貨GPU driver release，請工廠/DQA置換image中 GPU driver驗證
-4)三星 3.8K panel因leading customer改版無法準時出貨，除廠內161pcs外，後續物料到10月中才能到，已先通知業務，確認是否以2.8K panel先上ATS。</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2052,58 +2036,62 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>24V1</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Modern 14 LE J3M</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Prestige N16 AI+ C1XMT</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>MVT</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>WCL 25W</t>
+          <t>N1x 80W</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Intel® graphics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>倪嬌嬌</t>
+          <t>林晉弘</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>2026/06/02</t>
+          <t>2024/11/25</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>2026/07/07</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr"/>
+          <t>2025/01/20</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>2025/06/25</t>
+        </is>
+      </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/03/12</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/06/30</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2113,88 +2101,98 @@
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
-          <t>MSIK: 7/14 DQA test start MSIT: 7/16收到機器</t>
+          <t>MVT測試中</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>1)認證: 參考Weibu認證Schedule, a. 美洲US FCC 9/8 b.歐洲CE NB &amp;澳洲RCM 8/28 ready, 認證時間有風險, 已經highlight給微步team作認證評估</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
+          <t>1)battery life評估標準，是否可只用2.8 panel的測試結果為準，MSFT內部確認中。DQA會根據 NV/MSFT要求MSI進行如下測試 a)2.8K panel+day0 rev.A測試balance mode下 web browersing/ Modern standby b)3.8K panel + day0 rev.A測試BPE mode下web browersing/ Procyon
+2)NV Abnormal shut down 的solution，NV本周更新可於BSP Day0 rev.A驗證，待本周SW ready後，DQA/工廠會同時驗證確認。
+3)NV 7/11 release Day0 rev.A，預計7/17會提供BIOS/image for DQA驗證
+4)for NV/MSFT 113pcs樣品預計7/17 SMT，7/22 ASS'Y，會通知業務下單轉單出貨</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" hidden="1" outlineLevel="1">
+      <c r="A22" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>26V1</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Modern 16 LE J3M</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>WCL 25W</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Intel® graphics</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>倪嬌嬌</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/07</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr"/>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/29</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/08</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/18</t>
-        </is>
-      </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>2621</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Prestige N16 Flip AI+ C1XMT</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>N1x 80W</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>林晉弘</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>2024/11/25</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>2025/01/20</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>2025/06/25</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>2026/03/12</t>
+        </is>
+      </c>
+      <c r="L22" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="N22" s="10" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O22" s="6" t="inlineStr">
-        <is>
-          <t>MSIK: 7/14 DQA test start MSIT: 7/16收到機器</t>
-        </is>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>1)認證: 參考Weibu認證Schedule, a. 美洲US FCC 9/8 b.歐洲CE NB &amp;澳洲RCM 8/28 ready, 認證時間有風險, 已經highlight給微步team作認證評估</t>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t>MVT測試中</t>
+        </is>
+      </c>
+      <c r="P22" s="12" t="inlineStr">
+        <is>
+          <t>1)battery life評估標準，是否可只用2.8 panel的測試結果為準，MSFT內部確認中。DQA會根據 NV/MSFT要求MSI進行如下測試 a)2.8K panel+day0 rev.A測試balance mode下 web browersing/ Modern standby b)3.8K panel + day0 rev.A測試BPE mode下web browersing/ Procyon
+2)NV Abnormal shut down 的solution，NV本周更新可於BSP Day0 rev.A驗證，待本周SW ready後，DQA/工廠會同時驗證確認。
+3)NV 7/11 release Day0 rev.A，預計7/17會提供BIOS/image for DQA驗證
+4)for NV/MSFT 113pcs樣品預計7/17 SMT，7/22 ASS'Y，會通知業務下單轉單出貨</t>
         </is>
       </c>
     </row>
@@ -2204,12 +2202,12 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>15TK</t>
+          <t>24V1</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Cyborg A15 Max C1PWE</t>
+          <t>Modern 14 LE J3M</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
@@ -2219,27 +2217,27 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>HWK 45W</t>
+          <t>WCL 25W</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>Intel® graphics</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>蔡東宏</t>
+          <t>倪嬌嬌</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>2026/05/28</t>
+          <t>2026/06/02</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>2026/06/26</t>
+          <t>2026/07/07</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr"/>
@@ -2250,184 +2248,180 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>2026/08/14</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>2026/09/04</t>
+          <t>2026/08/18</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>2026/09/14</t>
+          <t>2026/08/31</t>
         </is>
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
-          <t>HPT sku: MODS無法測試,請BIOS RD儘速釐清</t>
+          <t>MSIK: 7/14 DQA test start MSIT: 7/16收到機器</t>
         </is>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/17(Delay 4W),因專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP 預計延後 2週至 9/14 (先前已由9 月底提前至8/31,現又延至9/
-14),後續將依實際測試結果滾動式調整時程。
-2).Material: Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" hidden="1" outlineLevel="1">
-      <c r="A24" s="8" t="n">
+          <t>1)認證: 參考Weibu認證Schedule, a. 美洲US FCC 9/8 b.歐洲CE NB &amp;澳洲RCM 8/28 ready, 認證時間有風險, 已經highlight給微步team作認證評估</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>26V1</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Modern 16 LE J3M</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>WCL 25W</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Intel® graphics</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>倪嬌嬌</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/07</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/29</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>MSIK: 7/14 DQA test start MSIT: 7/16收到機器</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>1)認證: 參考Weibu認證Schedule, a. 美洲US FCC 9/8 b.歐洲CE NB &amp;澳洲RCM 8/28 ready, 認證時間有風險, 已經highlight給微步team作認證評估</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>15TK</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>Cyborg A15 Max C1PWF</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Cyborg A15 Max C1PWE</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>HWK 45W</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>2026/05/28</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>2026/06/26</t>
         </is>
       </c>
-      <c r="J24" s="10" t="inlineStr"/>
-      <c r="K24" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/29</t>
-        </is>
-      </c>
-      <c r="L24" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/14</t>
-        </is>
-      </c>
-      <c r="M24" s="10" t="inlineStr">
-        <is>
-          <t>2026/09/04</t>
-        </is>
-      </c>
-      <c r="N24" s="10" t="inlineStr">
-        <is>
-          <t>2026/09/14</t>
-        </is>
-      </c>
-      <c r="O24" s="12" t="inlineStr">
-        <is>
-          <t>HPT sku: MODS無法測試,請BIOS RD儘速釐清</t>
-        </is>
-      </c>
-      <c r="P24" s="12" t="inlineStr">
-        <is>
-          <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/17(Delay 4W),因專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP 預計延後 2週至 9/14 (先前已由9 月底提前至8/31,現又延至9/
-14),後續將依實際測試結果滾動式調整時程。
-2).Material: Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" hidden="1" outlineLevel="1">
-      <c r="A25" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>15TK</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>Cyborg A15 Max C1PWG</t>
-        </is>
-      </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>HWK 45W</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="I25" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/26</t>
-        </is>
-      </c>
-      <c r="J25" s="10" t="inlineStr"/>
-      <c r="K25" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/29</t>
-        </is>
-      </c>
-      <c r="L25" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/14</t>
-        </is>
-      </c>
-      <c r="M25" s="10" t="inlineStr">
-        <is>
-          <t>2026/09/04</t>
-        </is>
-      </c>
-      <c r="N25" s="10" t="inlineStr">
-        <is>
-          <t>2026/09/14</t>
-        </is>
-      </c>
-      <c r="O25" s="12" t="inlineStr">
-        <is>
-          <t>HPT sku: MODS無法測試,請BIOS RD儘速釐清</t>
-        </is>
-      </c>
-      <c r="P25" s="12" t="inlineStr">
-        <is>
-          <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/17(Delay 4W),因專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP 預計延後 2週至 9/14 (先前已由9 月底提前至8/31,現又延至9/
-14),後續將依實際測試結果滾動式調整時程。
+      <c r="J25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/04</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/09</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/19</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>HPT sku: HPT1測試MODS fail, HPT1/HPT2 都無法進入 Modern Standby,請RD持續與AMD co-work釐清問題.</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/22(較原時程delay 33天),因需搭配新的PI code &amp; driver且專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP預計延後至9/19 (先前已由 9 月底提前至 8/31, 現又延至9/
+19),後續將依實際測試結果滾動式調整專案時程。
 2).Material: Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
@@ -2443,7 +2437,7 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Cyborg A15 C1PWE</t>
+          <t>Cyborg A15 Max C1PWF</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
@@ -2458,7 +2452,7 @@
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -2479,196 +2473,190 @@
       <c r="J26" s="10" t="inlineStr"/>
       <c r="K26" s="10" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/08/04</t>
         </is>
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
-          <t>2026/08/14</t>
+          <t>2026/08/18</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
-          <t>2026/09/04</t>
+          <t>2026/09/09</t>
         </is>
       </c>
       <c r="N26" s="10" t="inlineStr">
         <is>
-          <t>2026/09/14</t>
+          <t>2026/09/19</t>
         </is>
       </c>
       <c r="O26" s="12" t="inlineStr">
         <is>
-          <t>HPT sku: MODS無法測試,請BIOS RD儘速釐清</t>
+          <t>HPT sku: HPT1測試MODS fail, HPT1/HPT2 都無法進入 Modern Standby,請RD持續與AMD co-work釐清問題.</t>
         </is>
       </c>
       <c r="P26" s="12" t="inlineStr">
         <is>
-          <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/17(Delay 4W),因專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP 預計延後 2週至 9/14 (先前已由9 月底提前至8/31,現又延至9/
-14),後續將依實際測試結果滾動式調整時程。
+          <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/22(較原時程delay 33天),因需搭配新的PI code &amp; driver且專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP預計延後至9/19 (先前已由 9 月底提前至 8/31, 現又延至9/
+19),後續將依實際測試結果滾動式調整專案時程。
 2).Material: Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
+    <row r="27" hidden="1" outlineLevel="1">
+      <c r="A27" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>14T3</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Prestige N14 AI+ D1M</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>N1 35W</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>倪嬌嬌</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>2025/04/30</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>2025/09/01</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/15</t>
-        </is>
-      </c>
-      <c r="K27" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/03</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/14</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>2026/10/13</t>
-        </is>
-      </c>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>2026/10/26</t>
-        </is>
-      </c>
-      <c r="O27" s="6" t="inlineStr">
-        <is>
-          <t>MVT SMT@8/3--depend on Material ready date作調整</t>
-        </is>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>1) Schedule: a.MVT D件備料ready日期@7/29 b. CPU交期還未放行, 先預估8/B交期
-3)備料：量產交料HQ23, 11/M交料, 還在持續追蹤中</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>15TK</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Cyborg A15 Max C1PWG</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>HWK 45W</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>蔡東宏</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr"/>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/04</t>
+        </is>
+      </c>
+      <c r="L27" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/09</t>
+        </is>
+      </c>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/19</t>
+        </is>
+      </c>
+      <c r="O27" s="12" t="inlineStr">
+        <is>
+          <t>HPT sku: HPT1測試MODS fail, HPT1/HPT2 都無法進入 Modern Standby,請RD持續與AMD co-work釐清問題.</t>
+        </is>
+      </c>
+      <c r="P27" s="12" t="inlineStr">
+        <is>
+          <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/22(較原時程delay 33天),因需搭配新的PI code &amp; driver且專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP預計延後至9/19 (先前已由 9 月底提前至 8/31, 現又延至9/
+19),後續將依實際測試結果滾動式調整專案時程。
+2).Material: Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" hidden="1" outlineLevel="1">
+      <c r="A28" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>2623</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Prestige N16 C1M</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="inlineStr">
-        <is>
-          <t>EVT</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>N1 45W</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>賴雪鳳</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>2025/04/30</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>2025/09/01</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/15</t>
-        </is>
-      </c>
-      <c r="K28" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/03</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/14</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>2026/10/13</t>
-        </is>
-      </c>
-      <c r="N28" s="4" t="inlineStr">
-        <is>
-          <t>2026/10/26</t>
-        </is>
-      </c>
-      <c r="O28" s="6" t="inlineStr">
-        <is>
-          <t>1)EVT 更新BSP6.2.1  持續驗證中,ID定案 顏色keep 淺灰+ D side 咬花
-3) N1 SoC 出貨延遲 MVT 預計延到8/3 SMT, 8/4 Pre-Assy ,8/6 Assy</t>
-        </is>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>15TK</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Cyborg A15 C1PWE</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>HWK 45W</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>蔡東宏</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="J28" s="10" t="inlineStr"/>
+      <c r="K28" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/04</t>
+        </is>
+      </c>
+      <c r="L28" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/09</t>
+        </is>
+      </c>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/19</t>
+        </is>
+      </c>
+      <c r="O28" s="12" t="inlineStr">
+        <is>
+          <t>HPT sku: HPT1測試MODS fail, HPT1/HPT2 都無法進入 Modern Standby,請RD持續與AMD co-work釐清問題.</t>
+        </is>
+      </c>
+      <c r="P28" s="12" t="inlineStr">
+        <is>
+          <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/22(較原時程delay 33天),因需搭配新的PI code &amp; driver且專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP預計延後至9/19 (先前已由 9 月底提前至 8/31, 現又延至9/
+19),後續將依實際測試結果滾動式調整專案時程。
+2).Material: Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS, 若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
     </row>
@@ -2678,237 +2666,237 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
+          <t>14T3</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Prestige N14 AI+ D1M</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>N1 35W</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>倪嬌嬌</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/30</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>2025/09/01</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/13</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/26</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>MVT SMT@8/3--depend on Material ready date作調整</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>1) Schedule: a.MVT D件備料ready日期@7/29 b. CPU交期還未放行, 先預估8/B交期
+3)備料：量產交料HQ23, 11/M交料, 還在持續追蹤中</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>2623</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Prestige N16 C1M</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>EVT</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>N1 45W</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>賴雪鳳</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/30</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>2025/09/01</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/13</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/26</t>
+        </is>
+      </c>
+      <c r="O30" s="6" t="inlineStr">
+        <is>
+          <t>1)EVT 更新BSP6.2.1  持續驗證中,ID定案 顏色keep 淺灰+ D side 咬花
+3) N1 SoC 出貨延遲 MVT 預計延到8/3 SMT, 8/4 Pre-Assy ,8/6 Assy</t>
+        </is>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Katana 18 HX A14WEK</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>2026/08/24</t>
         </is>
       </c>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>2026/10/12</t>
         </is>
       </c>
-      <c r="L29" s="4" t="inlineStr">
+      <c r="L31" s="4" t="inlineStr">
         <is>
           <t>2026/11/02</t>
         </is>
       </c>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>2026/11/21</t>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>2026/11/30</t>
         </is>
       </c>
-      <c r="O29" s="6" t="inlineStr">
+      <c r="O31" s="6" t="inlineStr">
         <is>
           <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
         </is>
       </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
-2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" hidden="1" outlineLevel="1">
-      <c r="A30" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Katana 18 HX A14WFK</t>
-        </is>
-      </c>
-      <c r="D30" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>顧曉琴</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J30" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
-      <c r="K30" s="10" t="inlineStr">
-        <is>
-          <t>2026/10/12</t>
-        </is>
-      </c>
-      <c r="L30" s="10" t="inlineStr">
-        <is>
-          <t>2026/11/02</t>
-        </is>
-      </c>
-      <c r="M30" s="10" t="inlineStr">
-        <is>
-          <t>2026/11/21</t>
-        </is>
-      </c>
-      <c r="N30" s="10" t="inlineStr">
-        <is>
-          <t>2026/11/30</t>
-        </is>
-      </c>
-      <c r="O30" s="12" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
-        </is>
-      </c>
-      <c r="P30" s="12" t="inlineStr">
-        <is>
-          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
-2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" hidden="1" outlineLevel="1">
-      <c r="A31" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>Katana 18 HX A14WGK</t>
-        </is>
-      </c>
-      <c r="D31" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G31" s="10" t="inlineStr">
-        <is>
-          <t>顧曉琴</t>
-        </is>
-      </c>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I31" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J31" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
-      <c r="K31" s="10" t="inlineStr">
-        <is>
-          <t>2026/10/12</t>
-        </is>
-      </c>
-      <c r="L31" s="10" t="inlineStr">
-        <is>
-          <t>2026/11/02</t>
-        </is>
-      </c>
-      <c r="M31" s="10" t="inlineStr">
-        <is>
-          <t>2026/11/21</t>
-        </is>
-      </c>
-      <c r="N31" s="10" t="inlineStr">
-        <is>
-          <t>2026/11/30</t>
-        </is>
-      </c>
-      <c r="O31" s="12" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
-        </is>
-      </c>
-      <c r="P31" s="12" t="inlineStr">
+      <c r="P31" s="6" t="inlineStr">
         <is>
           <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
 2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
@@ -2926,7 +2914,7 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WEOK</t>
+          <t>Katana 18 HX A14WFK</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
@@ -2941,7 +2929,7 @@
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
@@ -2951,18 +2939,22 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J32" s="10" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
       <c r="K32" s="10" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/10/12</t>
         </is>
       </c>
       <c r="L32" s="10" t="inlineStr">
@@ -2972,22 +2964,23 @@
       </c>
       <c r="M32" s="10" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2026/11/21</t>
         </is>
       </c>
       <c r="N32" s="10" t="inlineStr">
         <is>
-          <t>2026/12/02</t>
+          <t>2026/11/30</t>
         </is>
       </c>
       <c r="O32" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
         </is>
       </c>
       <c r="P32" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
+2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
         </is>
       </c>
     </row>
@@ -3002,7 +2995,7 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WFOK</t>
+          <t>Katana 18 HX A14WGK</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
@@ -3017,7 +3010,7 @@
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G33" s="10" t="inlineStr">
@@ -3027,18 +3020,22 @@
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J33" s="10" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J33" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
       <c r="K33" s="10" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/10/12</t>
         </is>
       </c>
       <c r="L33" s="10" t="inlineStr">
@@ -3048,22 +3045,23 @@
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2026/11/21</t>
         </is>
       </c>
       <c r="N33" s="10" t="inlineStr">
         <is>
-          <t>2026/12/02</t>
+          <t>2026/11/30</t>
         </is>
       </c>
       <c r="O33" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
         </is>
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
+2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
         </is>
       </c>
     </row>
@@ -3078,7 +3076,7 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGOK</t>
+          <t>Katana 18 HX A14WEOK</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
@@ -3093,7 +3091,7 @@
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
@@ -3154,7 +3152,7 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WE</t>
+          <t>Katana 18 HX A14WFOK</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
@@ -3169,7 +3167,7 @@
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G35" s="10" t="inlineStr">
@@ -3179,19 +3177,15 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J35" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J35" s="10" t="inlineStr"/>
       <c r="K35" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3204,23 +3198,22 @@
       </c>
       <c r="M35" s="10" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2026/11/23</t>
         </is>
       </c>
       <c r="N35" s="10" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2026/12/02</t>
         </is>
       </c>
       <c r="O35" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
-2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3228,7 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WF</t>
+          <t>Katana 18 HX A14WGOK</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
@@ -3250,7 +3243,7 @@
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
@@ -3260,19 +3253,15 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J36" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="inlineStr"/>
       <c r="K36" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3285,23 +3274,22 @@
       </c>
       <c r="M36" s="10" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2026/11/23</t>
         </is>
       </c>
       <c r="N36" s="10" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2026/12/02</t>
         </is>
       </c>
       <c r="O36" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P36" s="12" t="inlineStr">
         <is>
-          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
-2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3304,7 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WG</t>
+          <t>Crosshair 18 Max HX B14WE</t>
         </is>
       </c>
       <c r="D37" s="14" t="inlineStr">
@@ -3331,7 +3319,7 @@
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
@@ -3397,7 +3385,7 @@
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WGX</t>
+          <t>Crosshair 18 Max HX B14WF</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
@@ -3412,7 +3400,7 @@
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
@@ -3478,7 +3466,7 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WEO</t>
+          <t>Crosshair 18 Max HX B14WG</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
@@ -3493,7 +3481,7 @@
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
@@ -3503,15 +3491,19 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J39" s="10" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
       <c r="K39" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3534,12 +3526,13 @@
       </c>
       <c r="O39" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
         </is>
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
+2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3547,7 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WFO</t>
+          <t>Crosshair 18 Max HX B14WGX</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
@@ -3569,7 +3562,7 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
@@ -3579,15 +3572,19 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J40" s="10" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
       <c r="K40" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3610,12 +3607,13 @@
       </c>
       <c r="O40" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
         </is>
       </c>
       <c r="P40" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
+2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3628,7 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WGO</t>
+          <t>Crosshair 18 Max HX B14WEO</t>
         </is>
       </c>
       <c r="D41" s="14" t="inlineStr">
@@ -3645,7 +3643,7 @@
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
@@ -3706,7 +3704,7 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WGXO</t>
+          <t>Crosshair 18 Max HX B14WFO</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
@@ -3721,7 +3719,7 @@
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
@@ -3782,22 +3780,22 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WE</t>
-        </is>
-      </c>
-      <c r="D43" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
+          <t>Crosshair 18 Max HX B14WGO</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>RPL-HX Next 55W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
@@ -3807,34 +3805,38 @@
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I43" s="10" t="inlineStr"/>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
       <c r="J43" s="10" t="inlineStr"/>
       <c r="K43" s="10" t="inlineStr">
         <is>
-          <t>2026/12/08</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="L43" s="10" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/11/02</t>
         </is>
       </c>
       <c r="M43" s="10" t="inlineStr">
         <is>
-          <t>2027/01/19</t>
+          <t>2026/11/28</t>
         </is>
       </c>
       <c r="N43" s="10" t="inlineStr">
         <is>
-          <t>2027/01/30</t>
+          <t>2026/12/07</t>
         </is>
       </c>
       <c r="O43" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P43" s="12" t="inlineStr">
@@ -3854,22 +3856,22 @@
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WEO</t>
-        </is>
-      </c>
-      <c r="D44" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
+          <t>Crosshair 18 Max HX B14WGXO</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>RPL-HX Next 55W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
@@ -3882,31 +3884,35 @@
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr"/>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
       <c r="J44" s="10" t="inlineStr"/>
       <c r="K44" s="10" t="inlineStr">
         <is>
-          <t>2026/12/08</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="L44" s="10" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/11/02</t>
         </is>
       </c>
       <c r="M44" s="10" t="inlineStr">
         <is>
-          <t>2027/01/19</t>
+          <t>2026/11/28</t>
         </is>
       </c>
       <c r="N44" s="10" t="inlineStr">
         <is>
-          <t>2027/01/30</t>
+          <t>2026/12/07</t>
         </is>
       </c>
       <c r="O44" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P44" s="12" t="inlineStr">
@@ -3926,7 +3932,7 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WF</t>
+          <t>Crosshair 18 Max HX B2WE</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
@@ -3941,7 +3947,7 @@
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
@@ -3998,7 +4004,7 @@
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WFO</t>
+          <t>Crosshair 18 Max HX B2WEO</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
@@ -4013,7 +4019,7 @@
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
@@ -4070,7 +4076,7 @@
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WG</t>
+          <t>Crosshair 18 Max HX B2WF</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
@@ -4085,7 +4091,7 @@
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
@@ -4142,7 +4148,7 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WGO</t>
+          <t>Crosshair 18 Max HX B2WFO</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
@@ -4157,7 +4163,7 @@
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
@@ -4214,7 +4220,7 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WGX</t>
+          <t>Crosshair 18 Max HX B2WG</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
@@ -4286,7 +4292,7 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WGXO</t>
+          <t>Crosshair 18 Max HX B2WGO</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
@@ -4358,7 +4364,7 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WEK</t>
+          <t>Crosshair 18 Max HX B2WGX</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
@@ -4373,7 +4379,7 @@
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
@@ -4430,7 +4436,7 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WEOK</t>
+          <t>Crosshair 18 Max HX B2WGXO</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
@@ -4445,7 +4451,7 @@
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
@@ -4458,11 +4464,7 @@
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="I52" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
+      <c r="I52" s="10" t="inlineStr"/>
       <c r="J52" s="10" t="inlineStr"/>
       <c r="K52" s="10" t="inlineStr">
         <is>
@@ -4486,7 +4488,7 @@
       </c>
       <c r="O52" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P52" s="12" t="inlineStr">
@@ -4506,7 +4508,7 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WFK</t>
+          <t>Katana 18 HX A2WEK</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
@@ -4521,7 +4523,7 @@
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
@@ -4578,7 +4580,7 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WFOK</t>
+          <t>Katana 18 HX A2WEOK</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
@@ -4593,7 +4595,7 @@
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
@@ -4654,7 +4656,7 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WGK</t>
+          <t>Katana 18 HX A2WFK</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
@@ -4669,7 +4671,7 @@
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
@@ -4726,7 +4728,7 @@
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WGOK</t>
+          <t>Katana 18 HX A2WFOK</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
@@ -4741,7 +4743,7 @@
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
@@ -4791,83 +4793,75 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
+    <row r="57" hidden="1" outlineLevel="1">
+      <c r="A57" s="8" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>14T4</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>Prestige 14 AI</t>
-        </is>
-      </c>
-      <c r="D57" s="13" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>NVL-H 30W</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>Intel® Arc™ Graphics</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>朱芳芳</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/14</t>
-        </is>
-      </c>
-      <c r="I57" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/22</t>
-        </is>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/15</t>
-        </is>
-      </c>
-      <c r="K57" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/04</t>
-        </is>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/20</t>
-        </is>
-      </c>
-      <c r="M57" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/15</t>
-        </is>
-      </c>
-      <c r="N57" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/25</t>
-        </is>
-      </c>
-      <c r="O57" s="6" t="inlineStr">
-        <is>
-          <t>DVT SMT@7/22</t>
-        </is>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>Katana 18 HX A2WGK</t>
+        </is>
+      </c>
+      <c r="D57" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>RPL-HX Next 55W</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>顧曉琴</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I57" s="10" t="inlineStr"/>
+      <c r="J57" s="10" t="inlineStr"/>
+      <c r="K57" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/08</t>
+        </is>
+      </c>
+      <c r="L57" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/30</t>
+        </is>
+      </c>
+      <c r="M57" s="10" t="inlineStr">
+        <is>
+          <t>2027/01/19</t>
+        </is>
+      </c>
+      <c r="N57" s="10" t="inlineStr">
+        <is>
+          <t>2027/01/30</t>
+        </is>
+      </c>
+      <c r="O57" s="12" t="inlineStr">
+        <is>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+        </is>
+      </c>
+      <c r="P57" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -4877,77 +4871,73 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>14T4</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Prestige 14 AI+ Flip</t>
-        </is>
-      </c>
-      <c r="D58" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Katana 18 HX A2WGOK</t>
+        </is>
+      </c>
+      <c r="D58" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>NVL-H 30W</t>
+          <t>RPL-HX Next 55W</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>Intel® Arc™ Graphics</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>朱芳芳</t>
+          <t>顧曉琴</t>
         </is>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>2026/05/14</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr">
         <is>
-          <t>2026/07/22</t>
-        </is>
-      </c>
-      <c r="J58" s="10" t="inlineStr">
-        <is>
-          <t>2026/09/15</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J58" s="10" t="inlineStr"/>
       <c r="K58" s="10" t="inlineStr">
         <is>
-          <t>2026/11/04</t>
+          <t>2026/12/08</t>
         </is>
       </c>
       <c r="L58" s="10" t="inlineStr">
         <is>
-          <t>2026/11/20</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="M58" s="10" t="inlineStr">
         <is>
-          <t>2026/12/15</t>
+          <t>2027/01/19</t>
         </is>
       </c>
       <c r="N58" s="10" t="inlineStr">
         <is>
-          <t>2026/12/25</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="O58" s="12" t="inlineStr">
         <is>
-          <t>DVT SMT@7/22</t>
+          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P58" s="12" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -4957,12 +4947,12 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>14T4</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Prestige 16 AI+</t>
+          <t>Prestige 14 AI</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr">
@@ -4990,7 +4980,11 @@
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="I59" s="4" t="inlineStr"/>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
           <t>2026/09/15</t>
@@ -5033,12 +5027,12 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>14T4</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Prestige 16 Flip AI+</t>
+          <t>Prestige 14 AI+ Flip</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
@@ -5066,7 +5060,11 @@
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="I60" s="10" t="inlineStr"/>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
       <c r="J60" s="10" t="inlineStr">
         <is>
           <t>2026/09/15</t>
@@ -5109,398 +5107,390 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
+          <t>2624</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Prestige 16 AI+</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>NVL-H 30W</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>朱芳芳</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr"/>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/04</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/20</t>
+        </is>
+      </c>
+      <c r="M61" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/15</t>
+        </is>
+      </c>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/25</t>
+        </is>
+      </c>
+      <c r="O61" s="6" t="inlineStr">
+        <is>
+          <t>DVT SMT@7/22</t>
+        </is>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" hidden="1" outlineLevel="1">
+      <c r="A62" s="8" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>2624</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>Prestige 16 Flip AI+</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>NVL-H 30W</t>
+        </is>
+      </c>
+      <c r="F62" s="10" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="inlineStr">
+        <is>
+          <t>朱芳芳</t>
+        </is>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="I62" s="10" t="inlineStr"/>
+      <c r="J62" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="K62" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/04</t>
+        </is>
+      </c>
+      <c r="L62" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/20</t>
+        </is>
+      </c>
+      <c r="M62" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/15</t>
+        </is>
+      </c>
+      <c r="N62" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/25</t>
+        </is>
+      </c>
+      <c r="O62" s="12" t="inlineStr">
+        <is>
+          <t>DVT SMT@7/22</t>
+        </is>
+      </c>
+      <c r="P62" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
           <t>13Q5</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>Prestige 13 AI+ A4M</t>
         </is>
       </c>
-      <c r="D61" s="17" t="inlineStr">
+      <c r="D63" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="E63" s="4" t="inlineStr">
         <is>
           <t>NVL-H 28W</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="F63" s="4" t="inlineStr">
         <is>
           <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G63" s="4" t="inlineStr">
         <is>
           <t>顏春梅</t>
         </is>
       </c>
-      <c r="H61" s="4" t="inlineStr">
+      <c r="H63" s="4" t="inlineStr">
         <is>
           <t>2026/06/29</t>
         </is>
       </c>
-      <c r="I61" s="4" t="inlineStr">
+      <c r="I63" s="4" t="inlineStr">
         <is>
           <t>2026/08/18</t>
         </is>
       </c>
-      <c r="J61" s="4" t="inlineStr">
+      <c r="J63" s="4" t="inlineStr">
         <is>
           <t>2026/10/08</t>
         </is>
       </c>
-      <c r="K61" s="4" t="inlineStr">
+      <c r="K63" s="4" t="inlineStr">
         <is>
           <t>2026/11/21</t>
         </is>
       </c>
-      <c r="L61" s="4" t="inlineStr">
+      <c r="L63" s="4" t="inlineStr">
         <is>
           <t>2026/11/22</t>
         </is>
       </c>
-      <c r="M61" s="4" t="inlineStr">
+      <c r="M63" s="4" t="inlineStr">
         <is>
           <t>2026/12/22</t>
         </is>
       </c>
-      <c r="N61" s="4" t="inlineStr">
+      <c r="N63" s="4" t="inlineStr">
         <is>
           <t>2026/12/31</t>
         </is>
       </c>
-      <c r="O61" s="6" t="inlineStr">
+      <c r="O63" s="6" t="inlineStr">
         <is>
           <t>0A layout 中 0A G/O@8/7</t>
         </is>
       </c>
-      <c r="P61" s="6" t="inlineStr">
+      <c r="P63" s="6" t="inlineStr">
         <is>
           <t>Audio Codec由原來的Reltek更換為TI，線路設計，placement變更</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>2633</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>Stealth 16 AI+ B4WI</t>
         </is>
       </c>
-      <c r="D62" s="17" t="inlineStr">
+      <c r="D64" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>RTX 5080</t>
         </is>
       </c>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t>朱欣怡</t>
         </is>
       </c>
-      <c r="H62" s="4" t="inlineStr">
+      <c r="H64" s="4" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I62" s="4" t="inlineStr">
+      <c r="I64" s="4" t="inlineStr">
         <is>
           <t>2026/07/22</t>
         </is>
       </c>
-      <c r="J62" s="4" t="inlineStr">
+      <c r="J64" s="4" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K62" s="4" t="inlineStr">
+      <c r="K64" s="4" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L62" s="4" t="inlineStr">
+      <c r="L64" s="4" t="inlineStr">
         <is>
           <t>2026/11/30</t>
         </is>
       </c>
-      <c r="M62" s="4" t="inlineStr">
+      <c r="M64" s="4" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N62" s="4" t="inlineStr">
+      <c r="N64" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O62" s="6" t="inlineStr">
+      <c r="O64" s="6" t="inlineStr">
         <is>
           <t>產線排程 DVT SMT@7/23</t>
         </is>
       </c>
-      <c r="P62" s="6" t="inlineStr">
-        <is>
-          <t>1) Schedule:NV VBIOS @1/6, gating 8天,預計12/E 拿到WHQL，可能影響到最終TTM 時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" hidden="1" outlineLevel="1">
-      <c r="A63" s="8" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="9" t="inlineStr">
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>1) DVT 試產缺料I9B-221100C-T07，交期待定;
+2) Schedule:NV VBIOS @1/6, gating 8天,預計12/E 拿到WHQL，可能影響到最終TTM 時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" hidden="1" outlineLevel="1">
+      <c r="A65" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>2633</t>
         </is>
       </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="C65" s="10" t="inlineStr">
         <is>
           <t>Stealth 16 AI+ B4WH</t>
         </is>
       </c>
-      <c r="D63" s="16" t="inlineStr">
+      <c r="D65" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E63" s="10" t="inlineStr">
+      <c r="E65" s="10" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="F65" s="10" t="inlineStr">
         <is>
           <t>RTX 5070Ti</t>
         </is>
       </c>
-      <c r="G63" s="10" t="inlineStr">
+      <c r="G65" s="10" t="inlineStr">
         <is>
           <t>朱欣怡</t>
         </is>
       </c>
-      <c r="H63" s="10" t="inlineStr">
+      <c r="H65" s="10" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I63" s="10" t="inlineStr">
+      <c r="I65" s="10" t="inlineStr">
         <is>
           <t>2026/07/22</t>
         </is>
       </c>
-      <c r="J63" s="10" t="inlineStr">
+      <c r="J65" s="10" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K63" s="10" t="inlineStr">
+      <c r="K65" s="10" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L63" s="10" t="inlineStr">
+      <c r="L65" s="10" t="inlineStr">
         <is>
           <t>2026/11/30</t>
         </is>
       </c>
-      <c r="M63" s="10" t="inlineStr">
+      <c r="M65" s="10" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N63" s="10" t="inlineStr">
+      <c r="N65" s="10" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O63" s="12" t="inlineStr">
+      <c r="O65" s="12" t="inlineStr">
         <is>
           <t>產線排程 DVT SMT@7/23</t>
         </is>
       </c>
-      <c r="P63" s="12" t="inlineStr">
+      <c r="P65" s="12" t="inlineStr">
         <is>
           <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" hidden="1" outlineLevel="1">
-      <c r="A64" s="8" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="C64" s="10" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WJ</t>
-        </is>
-      </c>
-      <c r="D64" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E64" s="10" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F64" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5090</t>
-        </is>
-      </c>
-      <c r="G64" s="10" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H64" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I64" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/22</t>
-        </is>
-      </c>
-      <c r="J64" s="10" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K64" s="10" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L64" s="10" t="inlineStr">
-        <is>
-          <t>2026/11/30</t>
-        </is>
-      </c>
-      <c r="M64" s="10" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N64" s="10" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="O64" s="12" t="inlineStr">
-        <is>
-          <t>產線排程 DVT SMT@7/23</t>
-        </is>
-      </c>
-      <c r="P64" s="12" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WE</t>
-        </is>
-      </c>
-      <c r="D65" s="17" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K65" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/27</t>
-        </is>
-      </c>
-      <c r="M65" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N65" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="O65" s="6" t="inlineStr">
-        <is>
-          <t>0A layout start 6/8-7/17</t>
-        </is>
-      </c>
-      <c r="P65" s="6" t="inlineStr">
-        <is>
-          <t>1)NV VBIOS 驗證時間6周
-2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
     </row>
@@ -5510,156 +5500,155 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
+          <t>2633</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WJ</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5090</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
+      <c r="J66" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K66" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L66" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="M66" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N66" s="10" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="O66" s="12" t="inlineStr">
+        <is>
+          <t>產線排程 DVT SMT@7/23</t>
+        </is>
+      </c>
+      <c r="P66" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
           <t>2634</t>
         </is>
       </c>
-      <c r="C66" s="10" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WF</t>
-        </is>
-      </c>
-      <c r="D66" s="16" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WE</t>
+        </is>
+      </c>
+      <c r="D67" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E66" s="10" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F66" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G66" s="10" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H66" s="10" t="inlineStr">
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>賴雪鳳</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I66" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="J66" s="10" t="inlineStr">
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K66" s="10" t="inlineStr">
+      <c r="K67" s="4" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L66" s="10" t="inlineStr">
+      <c r="L67" s="4" t="inlineStr">
         <is>
           <t>2026/11/27</t>
         </is>
       </c>
-      <c r="M66" s="10" t="inlineStr">
+      <c r="M67" s="4" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N66" s="10" t="inlineStr">
+      <c r="N67" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O66" s="12" t="inlineStr">
-        <is>
-          <t>0A layout start 6/8-7/17</t>
-        </is>
-      </c>
-      <c r="P66" s="12" t="inlineStr">
-        <is>
-          <t>1)NV VBIOS 驗證時間6周
-2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" hidden="1" outlineLevel="1">
-      <c r="A67" s="8" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="9" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="C67" s="10" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
-        </is>
-      </c>
-      <c r="D67" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E67" s="10" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F67" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G67" s="10" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H67" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I67" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="J67" s="10" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K67" s="10" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L67" s="10" t="inlineStr">
-        <is>
-          <t>2026/11/27</t>
-        </is>
-      </c>
-      <c r="M67" s="10" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N67" s="10" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="O67" s="12" t="inlineStr">
-        <is>
-          <t>0A layout start 6/8-7/17</t>
-        </is>
-      </c>
-      <c r="P67" s="12" t="inlineStr">
+      <c r="O67" s="6" t="inlineStr">
+        <is>
+          <t>0A 7/15 gerber out</t>
+        </is>
+      </c>
+      <c r="P67" s="6" t="inlineStr">
         <is>
           <t>1)NV VBIOS 驗證時間6周
 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
@@ -5677,7 +5666,7 @@
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
+          <t>Stealth 16 AI+ B4WF</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
@@ -5692,12 +5681,12 @@
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
@@ -5707,7 +5696,7 @@
       </c>
       <c r="I68" s="10" t="inlineStr">
         <is>
-          <t>2026/08/07</t>
+          <t>2026/07/30</t>
         </is>
       </c>
       <c r="J68" s="10" t="inlineStr">
@@ -5737,7 +5726,7 @@
       </c>
       <c r="O68" s="12" t="inlineStr">
         <is>
-          <t>0A layout start 6/8-7/17</t>
+          <t>0A 7/15 gerber out</t>
         </is>
       </c>
       <c r="P68" s="12" t="inlineStr">
@@ -5747,83 +5736,84 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="n">
+    <row r="69" hidden="1" outlineLevel="1">
+      <c r="A69" s="8" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>2654</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>Raider 16 Max HX B4WH</t>
-        </is>
-      </c>
-      <c r="D69" s="13" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5070Ti</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>吳美芳</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I69" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K69" s="4" t="inlineStr">
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
+        </is>
+      </c>
+      <c r="D69" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G69" s="10" t="inlineStr">
+        <is>
+          <t>賴雪鳳</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="J69" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K69" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L69" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/27</t>
+        </is>
+      </c>
+      <c r="M69" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N69" s="10" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M69" s="4" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N69" s="4" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O69" s="6" t="inlineStr">
-        <is>
-          <t>6/29 gerber out，预计7/27 DVT打板</t>
-        </is>
-      </c>
-      <c r="P69" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="O69" s="12" t="inlineStr">
+        <is>
+          <t>0A 7/15 gerber out</t>
+        </is>
+      </c>
+      <c r="P69" s="12" t="inlineStr">
+        <is>
+          <t>1)NV VBIOS 驗證時間6周
+2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
     </row>
@@ -5833,155 +5823,156 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
+        </is>
+      </c>
+      <c r="D70" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G70" s="10" t="inlineStr">
+        <is>
+          <t>賴雪鳳</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="J70" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K70" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L70" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/27</t>
+        </is>
+      </c>
+      <c r="M70" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N70" s="10" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="O70" s="12" t="inlineStr">
+        <is>
+          <t>0A 7/15 gerber out</t>
+        </is>
+      </c>
+      <c r="P70" s="12" t="inlineStr">
+        <is>
+          <t>1)NV VBIOS 驗證時間6周
+2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
           <t>2654</t>
         </is>
       </c>
-      <c r="C70" s="10" t="inlineStr">
-        <is>
-          <t>Raider 16 Max HX B4WI</t>
-        </is>
-      </c>
-      <c r="D70" s="14" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Raider 16 Max HX B4WH</t>
+        </is>
+      </c>
+      <c r="D71" s="13" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E70" s="10" t="inlineStr">
+      <c r="E71" s="4" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F70" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5080</t>
-        </is>
-      </c>
-      <c r="G70" s="10" t="inlineStr">
-        <is>
-          <t>吳美芳</t>
-        </is>
-      </c>
-      <c r="H70" s="10" t="inlineStr">
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>鮑佩佩</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I70" s="10" t="inlineStr">
+      <c r="I71" s="4" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J70" s="10" t="inlineStr">
+      <c r="J71" s="4" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K70" s="10" t="inlineStr">
+      <c r="K71" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L70" s="10" t="inlineStr">
+      <c r="L71" s="4" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M70" s="10" t="inlineStr">
+      <c r="M71" s="4" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N70" s="10" t="inlineStr">
+      <c r="N71" s="4" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O70" s="12" t="inlineStr">
+      <c r="O71" s="6" t="inlineStr">
         <is>
           <t>6/29 gerber out，预计7/27 DVT打板</t>
         </is>
       </c>
-      <c r="P70" s="12" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" hidden="1" outlineLevel="1">
-      <c r="A71" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" s="9" t="inlineStr">
-        <is>
-          <t>2654</t>
-        </is>
-      </c>
-      <c r="C71" s="10" t="inlineStr">
-        <is>
-          <t>Raider 16 Max HX B4WJ</t>
-        </is>
-      </c>
-      <c r="D71" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E71" s="10" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F71" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5090</t>
-        </is>
-      </c>
-      <c r="G71" s="10" t="inlineStr">
-        <is>
-          <t>吳美芳</t>
-        </is>
-      </c>
-      <c r="H71" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I71" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J71" s="10" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K71" s="10" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L71" s="10" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M71" s="10" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N71" s="10" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O71" s="12" t="inlineStr">
-        <is>
-          <t>6/29 gerber out，预计7/27 DVT打板</t>
-        </is>
-      </c>
-      <c r="P71" s="12" t="inlineStr">
+      <c r="P71" s="6" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -5998,7 +5989,7 @@
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WH</t>
+          <t>Raider 16 Max HX B4WI</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
@@ -6013,12 +6004,12 @@
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>鮑佩佩</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
@@ -6078,7 +6069,7 @@
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WI</t>
+          <t>Raider 16 Max HX B4WJ</t>
         </is>
       </c>
       <c r="D73" s="14" t="inlineStr">
@@ -6093,135 +6084,139 @@
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="G73" s="10" t="inlineStr">
         <is>
+          <t>鮑佩佩</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J73" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K73" s="10" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="L73" s="10" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M73" s="10" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N73" s="10" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O73" s="12" t="inlineStr">
+        <is>
+          <t>6/29 gerber out，预计7/27 DVT打板</t>
+        </is>
+      </c>
+      <c r="P73" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" hidden="1" outlineLevel="1">
+      <c r="A74" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>2654</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>Raider 16  HX B4WH</t>
+        </is>
+      </c>
+      <c r="D74" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G74" s="10" t="inlineStr">
+        <is>
           <t>吳美芳</t>
         </is>
       </c>
-      <c r="H73" s="10" t="inlineStr">
+      <c r="H74" s="10" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I73" s="10" t="inlineStr">
+      <c r="I74" s="10" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J73" s="10" t="inlineStr">
+      <c r="J74" s="10" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K73" s="10" t="inlineStr">
+      <c r="K74" s="10" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L73" s="10" t="inlineStr">
+      <c r="L74" s="10" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M73" s="10" t="inlineStr">
+      <c r="M74" s="10" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N73" s="10" t="inlineStr">
+      <c r="N74" s="10" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O73" s="12" t="inlineStr">
+      <c r="O74" s="12" t="inlineStr">
         <is>
           <t>6/29 gerber out，预计7/27 DVT打板</t>
         </is>
       </c>
-      <c r="P73" s="12" t="inlineStr">
+      <c r="P74" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>1851</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>Titan 18 HX B4WH</t>
-        </is>
-      </c>
-      <c r="D74" s="17" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5070Ti</t>
-        </is>
-      </c>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>高宇奇</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="I74" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/14</t>
-        </is>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>2026/10/23</t>
-        </is>
-      </c>
-      <c r="K74" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/08</t>
-        </is>
-      </c>
-      <c r="L74" s="4" t="inlineStr">
-        <is>
-          <t>2027/02/01</t>
-        </is>
-      </c>
-      <c r="M74" s="4" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N74" s="4" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O74" s="6" t="inlineStr">
-        <is>
-          <t>0M layout進行中,預計7/27 0M gerber out.</t>
-        </is>
-      </c>
-      <c r="P74" s="6" t="inlineStr"/>
     </row>
     <row r="75" hidden="1" outlineLevel="1">
       <c r="A75" s="8" t="n">
@@ -6229,151 +6224,155 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
+          <t>2654</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>Raider 16  HX B4WI</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5080</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>吳美芳</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J75" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K75" s="10" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="L75" s="10" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M75" s="10" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N75" s="10" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O75" s="12" t="inlineStr">
+        <is>
+          <t>6/29 gerber out，预计7/27 DVT打板</t>
+        </is>
+      </c>
+      <c r="P75" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
           <t>1851</t>
         </is>
       </c>
-      <c r="C75" s="10" t="inlineStr">
-        <is>
-          <t>Titan 18 HX B4WI</t>
-        </is>
-      </c>
-      <c r="D75" s="16" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Titan 18 HX B4WH</t>
+        </is>
+      </c>
+      <c r="D76" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E75" s="10" t="inlineStr">
+      <c r="E76" s="4" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F75" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5080</t>
-        </is>
-      </c>
-      <c r="G75" s="10" t="inlineStr">
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
         <is>
           <t>高宇奇</t>
         </is>
       </c>
-      <c r="H75" s="10" t="inlineStr">
+      <c r="H76" s="4" t="inlineStr">
         <is>
           <t>2026/06/29</t>
         </is>
       </c>
-      <c r="I75" s="10" t="inlineStr">
+      <c r="I76" s="4" t="inlineStr">
         <is>
           <t>2026/08/14</t>
         </is>
       </c>
-      <c r="J75" s="10" t="inlineStr">
+      <c r="J76" s="4" t="inlineStr">
         <is>
           <t>2026/10/23</t>
         </is>
       </c>
-      <c r="K75" s="10" t="inlineStr">
+      <c r="K76" s="4" t="inlineStr">
         <is>
           <t>2027/01/08</t>
         </is>
       </c>
-      <c r="L75" s="10" t="inlineStr">
+      <c r="L76" s="4" t="inlineStr">
         <is>
           <t>2027/02/01</t>
         </is>
       </c>
-      <c r="M75" s="10" t="inlineStr">
+      <c r="M76" s="4" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N75" s="10" t="inlineStr">
+      <c r="N76" s="4" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O75" s="12" t="inlineStr">
+      <c r="O76" s="6" t="inlineStr">
         <is>
           <t>0M layout進行中,預計7/27 0M gerber out.</t>
         </is>
       </c>
-      <c r="P75" s="12" t="inlineStr"/>
-    </row>
-    <row r="76" hidden="1" outlineLevel="1">
-      <c r="A76" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="9" t="inlineStr">
-        <is>
-          <t>1851</t>
-        </is>
-      </c>
-      <c r="C76" s="10" t="inlineStr">
-        <is>
-          <t>Titan 18 HX B4WJ</t>
-        </is>
-      </c>
-      <c r="D76" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E76" s="10" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F76" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5090</t>
-        </is>
-      </c>
-      <c r="G76" s="10" t="inlineStr">
-        <is>
-          <t>高宇奇</t>
-        </is>
-      </c>
-      <c r="H76" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="I76" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/14</t>
-        </is>
-      </c>
-      <c r="J76" s="10" t="inlineStr">
-        <is>
-          <t>2026/10/23</t>
-        </is>
-      </c>
-      <c r="K76" s="10" t="inlineStr">
-        <is>
-          <t>2027/01/08</t>
-        </is>
-      </c>
-      <c r="L76" s="10" t="inlineStr">
-        <is>
-          <t>2027/02/01</t>
-        </is>
-      </c>
-      <c r="M76" s="10" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N76" s="10" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O76" s="12" t="inlineStr">
-        <is>
-          <t>0M layout進行中,預計7/27 0M gerber out.</t>
-        </is>
-      </c>
-      <c r="P76" s="12" t="inlineStr"/>
+      <c r="P76" s="6" t="inlineStr"/>
     </row>
     <row r="77" hidden="1" outlineLevel="1">
       <c r="A77" s="8" t="n">
@@ -6386,7 +6385,7 @@
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>Raider 18 Max HX B4WH</t>
+          <t>Titan 18 HX B4WI</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
@@ -6396,12 +6395,12 @@
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>NVL-HX 65W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr">
@@ -6462,7 +6461,7 @@
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Raider 18 Max HX B4WI</t>
+          <t>Titan 18 HX B4WJ</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
@@ -6472,12 +6471,12 @@
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>NVL-HX 65W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
@@ -6538,7 +6537,7 @@
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Raider 18 Max HX B4WJ</t>
+          <t>Raider 18 Max HX B4WH</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
@@ -6553,7 +6552,7 @@
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
@@ -6603,85 +6602,81 @@
       </c>
       <c r="P79" s="12" t="inlineStr"/>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
+    <row r="80" hidden="1" outlineLevel="1">
+      <c r="A80" s="8" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>2655</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WEK</t>
-        </is>
-      </c>
-      <c r="D80" s="13" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>鮑佩佩</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I80" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K80" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M80" s="4" t="inlineStr">
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>Raider 18 Max HX B4WI</t>
+        </is>
+      </c>
+      <c r="D80" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>NVL-HX 65W</t>
+        </is>
+      </c>
+      <c r="F80" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5080</t>
+        </is>
+      </c>
+      <c r="G80" s="10" t="inlineStr">
+        <is>
+          <t>高宇奇</t>
+        </is>
+      </c>
+      <c r="H80" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I80" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="J80" s="10" t="inlineStr">
+        <is>
+          <t>2026/10/23</t>
+        </is>
+      </c>
+      <c r="K80" s="10" t="inlineStr">
+        <is>
+          <t>2027/01/08</t>
+        </is>
+      </c>
+      <c r="L80" s="10" t="inlineStr">
+        <is>
+          <t>2027/02/01</t>
+        </is>
+      </c>
+      <c r="M80" s="10" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N80" s="4" t="inlineStr">
+      <c r="N80" s="10" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O80" s="6" t="inlineStr">
-        <is>
-          <t>0A 7/3 gerber out.plan 7/27 DVT SMT1</t>
-        </is>
-      </c>
-      <c r="P80" s="6" t="inlineStr">
-        <is>
-          <t>產品策略調整,2655 計畫提升為Raider 16,RD 評估中</t>
-        </is>
-      </c>
+      <c r="O80" s="12" t="inlineStr">
+        <is>
+          <t>0M layout進行中,預計7/27 0M gerber out.</t>
+        </is>
+      </c>
+      <c r="P80" s="12" t="inlineStr"/>
     </row>
     <row r="81" hidden="1" outlineLevel="1">
       <c r="A81" s="8" t="n">
@@ -6689,157 +6684,153 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>Raider 18 Max HX B4WJ</t>
+        </is>
+      </c>
+      <c r="D81" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>NVL-HX 65W</t>
+        </is>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5090</t>
+        </is>
+      </c>
+      <c r="G81" s="10" t="inlineStr">
+        <is>
+          <t>高宇奇</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="J81" s="10" t="inlineStr">
+        <is>
+          <t>2026/10/23</t>
+        </is>
+      </c>
+      <c r="K81" s="10" t="inlineStr">
+        <is>
+          <t>2027/01/08</t>
+        </is>
+      </c>
+      <c r="L81" s="10" t="inlineStr">
+        <is>
+          <t>2027/02/01</t>
+        </is>
+      </c>
+      <c r="M81" s="10" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N81" s="10" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O81" s="12" t="inlineStr">
+        <is>
+          <t>0M layout進行中,預計7/27 0M gerber out.</t>
+        </is>
+      </c>
+      <c r="P81" s="12" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
           <t>2655</t>
         </is>
       </c>
-      <c r="C81" s="10" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WFK</t>
-        </is>
-      </c>
-      <c r="D81" s="14" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Crosshair 16 Max HX E4WEK</t>
+        </is>
+      </c>
+      <c r="D82" s="13" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E81" s="10" t="inlineStr">
+      <c r="E82" s="4" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F81" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G81" s="10" t="inlineStr">
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
         <is>
           <t>鮑佩佩</t>
         </is>
       </c>
-      <c r="H81" s="10" t="inlineStr">
+      <c r="H82" s="4" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I81" s="10" t="inlineStr">
+      <c r="I82" s="4" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J81" s="10" t="inlineStr">
+      <c r="J82" s="4" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K81" s="10" t="inlineStr">
+      <c r="K82" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L81" s="10" t="inlineStr">
+      <c r="L82" s="4" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M81" s="10" t="inlineStr">
+      <c r="M82" s="4" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N81" s="10" t="inlineStr">
+      <c r="N82" s="4" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O81" s="12" t="inlineStr">
-        <is>
-          <t>0A 7/3 gerber out.plan 7/27 DVT SMT1</t>
-        </is>
-      </c>
-      <c r="P81" s="12" t="inlineStr">
-        <is>
-          <t>產品策略調整,2655 計畫提升為Raider 16,RD 評估中</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" hidden="1" outlineLevel="1">
-      <c r="A82" s="8" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="9" t="inlineStr">
-        <is>
-          <t>2655</t>
-        </is>
-      </c>
-      <c r="C82" s="10" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WGK</t>
-        </is>
-      </c>
-      <c r="D82" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E82" s="10" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F82" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G82" s="10" t="inlineStr">
-        <is>
-          <t>鮑佩佩</t>
-        </is>
-      </c>
-      <c r="H82" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I82" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J82" s="10" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K82" s="10" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L82" s="10" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M82" s="10" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N82" s="10" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O82" s="12" t="inlineStr">
-        <is>
-          <t>0A 7/3 gerber out.plan 7/27 DVT SMT1</t>
-        </is>
-      </c>
-      <c r="P82" s="12" t="inlineStr">
-        <is>
-          <t>產品策略調整,2655 計畫提升為Raider 16,RD 評估中</t>
+      <c r="O82" s="6" t="inlineStr">
+        <is>
+          <t>0A 7/3 gerber out.plan 7/27 DVT SMT1，Ti usb repeater BW9871缺料待pull in 交期</t>
+        </is>
+      </c>
+      <c r="P82" s="6" t="inlineStr">
+        <is>
+          <t>1)Spec變更,2655 計畫升規為Raider 16,RD 評估中,為了達到 Raider 等級的效能，由雙風扇升級為三風扇(3F5P)，現有的 DVT 樣品（8mm 風扇）無法用於驗證 230W/200W 的效能目標，必須重新製作手工樣品（10mm 散熱模組），影響Schedule TBD,預計下週會更新，同步重新 review 板端空間及高度干涉問題</t>
         </is>
       </c>
     </row>
@@ -6854,77 +6845,237 @@
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
+          <t>Crosshair 16 Max HX E4WFK</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="inlineStr">
+        <is>
+          <t>鮑佩佩</t>
+        </is>
+      </c>
+      <c r="H83" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I83" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J83" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K83" s="10" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="L83" s="10" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M83" s="10" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N83" s="10" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O83" s="12" t="inlineStr">
+        <is>
+          <t>0A 7/3 gerber out.plan 7/27 DVT SMT1，Ti usb repeater BW9871缺料待pull in 交期</t>
+        </is>
+      </c>
+      <c r="P83" s="12" t="inlineStr">
+        <is>
+          <t>1)Spec變更,2655 計畫升規為Raider 16,RD 評估中,為了達到 Raider 等級的效能，由雙風扇升級為三風扇(3F5P)，現有的 DVT 樣品（8mm 風扇）無法用於驗證 230W/200W 的效能目標，必須重新製作手工樣品（10mm 散熱模組），影響Schedule TBD,預計下週會更新，同步重新 review 板端空間及高度干涉問題</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" hidden="1" outlineLevel="1">
+      <c r="A84" s="8" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>2655</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>Crosshair 16 Max HX E4WGK</t>
+        </is>
+      </c>
+      <c r="D84" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F84" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G84" s="10" t="inlineStr">
+        <is>
+          <t>鮑佩佩</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J84" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K84" s="10" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="L84" s="10" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M84" s="10" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N84" s="10" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O84" s="12" t="inlineStr">
+        <is>
+          <t>0A 7/3 gerber out.plan 7/27 DVT SMT1，Ti usb repeater BW9871缺料待pull in 交期</t>
+        </is>
+      </c>
+      <c r="P84" s="12" t="inlineStr">
+        <is>
+          <t>1)Spec變更,2655 計畫升規為Raider 16,RD 評估中,為了達到 Raider 等級的效能，由雙風扇升級為三風扇(3F5P)，現有的 DVT 樣品（8mm 風扇）無法用於驗證 230W/200W 的效能目標，必須重新製作手工樣品（10mm 散熱模組），影響Schedule TBD,預計下週會更新，同步重新 review 板端空間及高度干涉問題</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" hidden="1" outlineLevel="1">
+      <c r="A85" s="8" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>2655</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
           <t>Crosshair 16 Max HX E4WGXK</t>
         </is>
       </c>
-      <c r="D83" s="14" t="inlineStr">
+      <c r="D85" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E83" s="10" t="inlineStr">
+      <c r="E85" s="10" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F83" s="10" t="inlineStr">
+      <c r="F85" s="10" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G83" s="10" t="inlineStr">
+      <c r="G85" s="10" t="inlineStr">
         <is>
           <t>鮑佩佩</t>
         </is>
       </c>
-      <c r="H83" s="10" t="inlineStr">
+      <c r="H85" s="10" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I83" s="10" t="inlineStr">
+      <c r="I85" s="10" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J83" s="10" t="inlineStr">
+      <c r="J85" s="10" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K83" s="10" t="inlineStr">
+      <c r="K85" s="10" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L83" s="10" t="inlineStr">
+      <c r="L85" s="10" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M83" s="10" t="inlineStr">
+      <c r="M85" s="10" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N83" s="10" t="inlineStr">
+      <c r="N85" s="10" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O83" s="12" t="inlineStr">
-        <is>
-          <t>0A 7/3 gerber out.plan 7/27 DVT SMT1</t>
-        </is>
-      </c>
-      <c r="P83" s="12" t="inlineStr">
-        <is>
-          <t>產品策略調整,2655 計畫提升為Raider 16,RD 評估中</t>
+      <c r="O85" s="12" t="inlineStr">
+        <is>
+          <t>0A 7/3 gerber out.plan 7/27 DVT SMT1，Ti usb repeater BW9871缺料待pull in 交期</t>
+        </is>
+      </c>
+      <c r="P85" s="12" t="inlineStr">
+        <is>
+          <t>1)Spec變更,2655 計畫升規為Raider 16,RD 評估中,為了達到 Raider 等級的效能，由雙風扇升級為三風扇(3F5P)，現有的 DVT 樣品（8mm 風扇）無法用於驗證 230W/200W 的效能目標，必須重新製作手工樣品（10mm 散熱模組），影響Schedule TBD,預計下週會更新，同步重新 review 板端空間及高度干涉問題</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P83"/>
+  <autoFilter ref="A1:P85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/npi_dashboard.xlsx
+++ b/npi_dashboard.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPI Dashboard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -516,7 +516,7 @@
     <outlinePr summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P85"/>
+  <dimension ref="A1:P82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -762,13 +762,13 @@
       </c>
       <c r="O3" s="6" t="inlineStr">
         <is>
-          <t>因Camera 丟失ISSUE，待確認執行方案</t>
+          <t>因Camera 丟失ISSUE，7/17 確認重工更新BIOS ，待客驗結果確認入庫&amp;出貨</t>
         </is>
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>Schedule  ：（TTM原計劃7/15 先預抓延後到7/
-20）：7/16 會議請微步放量200台驗證以及全掃功能，待微步提供具體數據，請示執行方案後，追蹤最快機台入庫時間</t>
+          <t>1)Schedule  ：Camerr Issue  ,重工BIOS ，TTM原計劃7/15 預計延後到7/20 delay  5天.
+2）2nd MP Gating 瓶頸Adapter物料尾數100pcs 待weibu 廠商回復交期，目標7/27 機台入庫</t>
         </is>
       </c>
     </row>
@@ -778,12 +778,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>265L</t>
+          <t>15Q1</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WGXK</t>
+          <t>Cyborg 15 B2VEK</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -793,54 +793,50 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>FRG-HX3D 55W</t>
+          <t>ARL-H 45W</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 4050 (35W+10W)/ GDDR6 6GB</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>李文欽</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2026/06/24</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr"/>
       <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/18</t>
-        </is>
-      </c>
+      <c r="K4" s="4" t="inlineStr"/>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>2026/06/16</t>
+          <t>2026/06/26</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/22</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>FRG (5/4通知resume）: DQA 測試中</t>
+          <t>（清日文4區RGB鍵盤庫存）DQA測試中,預計7/21完成</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>1）暫無業務報價，BTO 未開</t>
+          <t>1)DQA驗證有Audio問題, WHQL驅動預計7/24提供,需要Preload和DQA等單位加班驗證,滿足業務7/30出貨需求</t>
         </is>
       </c>
     </row>
@@ -850,12 +846,12 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>265L</t>
+          <t>15Q1</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Crosshair A16 HX E9WEK</t>
+          <t>Cyborg 15 B2VE</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -865,338 +861,348 @@
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>FRG-HX 55W</t>
+          <t>ARL-H 45W</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 4050 (35W+10W)/ GDDR6 6GB</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>李文欽</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2026/06/24</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr"/>
       <c r="J5" s="10" t="inlineStr"/>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>2026/05/18</t>
+          <t>2026/06/29</t>
         </is>
       </c>
       <c r="L5" s="10" t="inlineStr">
         <is>
-          <t>2026/06/16</t>
+          <t>2026/06/29</t>
         </is>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
-          <t>2026/07/16</t>
+          <t>2026/07/20</t>
         </is>
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
-          <t>2026/07/26</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="O5" s="12" t="inlineStr">
         <is>
-          <t>FRG (5/4通知resume）: DQA 測試中</t>
+          <t>（清白光鍵盤庫存）DQA測試中,預計7/20完成</t>
         </is>
       </c>
       <c r="P5" s="12" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" hidden="1" outlineLevel="1">
-      <c r="A6" s="8" t="n">
+          <t>1)DQA驗證有Audio問題, WHQL驅動預計7/24提供,需要Preload和DQA等單位加班驗證</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>265L</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Crosshair A16 HX E9WFK</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>15Q3</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Cyborg 15 Black Edition B13WE</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>FRG-HX 55W</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="inlineStr"/>
-      <c r="J6" s="10" t="inlineStr"/>
-      <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/18</t>
-        </is>
-      </c>
-      <c r="L6" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/16</t>
-        </is>
-      </c>
-      <c r="M6" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/16</t>
-        </is>
-      </c>
-      <c r="N6" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/26</t>
-        </is>
-      </c>
-      <c r="O6" s="12" t="inlineStr">
-        <is>
-          <t>FRG (5/4通知resume）: DQA 測試中</t>
-        </is>
-      </c>
-      <c r="P6" s="12" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>15Q1</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Cyborg 15 B2VEK</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>ARL-H 45W</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>RTX 4050 (35W+10W)/ GDDR6 6GB</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>李文欽</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>RPL-H 45W</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>楊淑賢</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>2026/06/24</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/26</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/22</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/31</t>
-        </is>
-      </c>
-      <c r="O7" s="6" t="inlineStr">
-        <is>
-          <t>（清日文4區RGB鍵盤庫存）DQA測試中,預計7/21完成</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>1)DQA驗證有Audio問題, WHQL驅動預計7/24提供,需要Preload和DQA等單位加班驗證,滿足業務7/30出貨需求</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" hidden="1" outlineLevel="1">
-      <c r="A8" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>15Q1</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Cyborg 15 B2VE</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>ARL-H 45W</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>RTX 4050 (35W+10W)/ GDDR6 6GB</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>李文欽</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/24</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr"/>
-      <c r="J8" s="10" t="inlineStr"/>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="L8" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="M8" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/20</t>
-        </is>
-      </c>
-      <c r="N8" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/31</t>
-        </is>
-      </c>
-      <c r="O8" s="12" t="inlineStr">
-        <is>
-          <t>（清白光鍵盤庫存）DQA測試中,預計7/20完成</t>
-        </is>
-      </c>
-      <c r="P8" s="12" t="inlineStr">
-        <is>
-          <t>1)DQA驗證有Audio問題, WHQL驅動預計7/24提供,需要Preload和DQA等單位加班驗證</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>15Q3</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Cyborg 15 Black Edition B13WE</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>RPL-H 45W</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>楊淑賢</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/24</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>2026/07/01</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>2026/07/14</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>2026/08/03</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>2026/08/07</t>
         </is>
       </c>
-      <c r="O9" s="6" t="inlineStr">
+      <c r="O6" s="6" t="inlineStr">
         <is>
           <t>DQA test中,
 1) ME: 搖擺測試pass
 2）Function：待新版MSI Center AP release( 包入MKT name支援AI Noise Cancellation Pro), 安排HDI製作</t>
         </is>
       </c>
-      <c r="P9" s="6" t="inlineStr">
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>1) Cyborg Black Edition SKU: Cyborg A+Venture B/C/D機構件+白光鍵盤</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" hidden="1" outlineLevel="1">
+      <c r="A7" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>15Q3</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Cyborg 15 Black Edition B13WF</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>RPL-H 45W</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>楊淑賢</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr"/>
+      <c r="J7" s="10" t="inlineStr"/>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/01</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/14</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="O7" s="12" t="inlineStr">
+        <is>
+          <t>DQA test中,
+1) ME: 搖擺測試pass
+2）Function：待新版MSI Center AP release( 包入MKT name支援AI Noise Cancellation Pro), 安排HDI製作</t>
+        </is>
+      </c>
+      <c r="P7" s="12" t="inlineStr">
+        <is>
+          <t>1) Cyborg Black Edition SKU: Cyborg A+Venture B/C/D機構件+白光鍵盤</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>17U3</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Cyborg 17 Black Edition B13WE</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>RPL-H 45W</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>楊淑賢</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/01</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/14</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>DQA test中,
+1) ME: 搖擺測試pass
+2）Function：待新版MSI Center AP release( 包入MKT name支援AI Noise Cancellation Pro), 安排HDI製作</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>1) Cyborg Black Edition SKU: Cyborg A+Venture B/C/D機構件+白光鍵盤</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" hidden="1" outlineLevel="1">
+      <c r="A9" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>17U3</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Cyborg 17 Black Edition B13WF</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>RPL-H 45W</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>楊淑賢</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr"/>
+      <c r="J9" s="10" t="inlineStr"/>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/01</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/14</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/03</t>
+        </is>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>DQA test中,
+1) ME: 搖擺測試pass
+2）Function：待新版MSI Center AP release( 包入MKT name支援AI Noise Cancellation Pro), 安排HDI製作</t>
+        </is>
+      </c>
+      <c r="P9" s="12" t="inlineStr">
         <is>
           <t>1) Cyborg Black Edition SKU: Cyborg A+Venture B/C/D機構件+白光鍵盤</t>
         </is>
@@ -1208,12 +1214,12 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>15Q3</t>
+          <t>17U3</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Cyborg 15 Black Edition B13WF</t>
+          <t>Cyborg 17 Black Edition B2RWF</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1223,7 +1229,7 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>RPL-H 45W</t>
+          <t>RPL-H refresh 45W</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
@@ -1282,145 +1288,149 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>17U3</t>
+          <t>15T2</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Cyborg 17 Black Edition B13WE</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>MVT</t>
+          <t>Venture 15 AI+ B3M</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>RPL-H 45W</t>
+          <t>PTL-H 80W</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>楊淑賢</t>
+          <t>李文欽</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>2026/06/24</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr"/>
+          <t>2026/04/20</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
+      </c>
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>2026/07/01</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t>MVT1 正式組裝@7/13</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>1) w/FP的Touchpad 試產物料,需要採購協助Pull in</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>15T3</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Katana 15 HX C14WEK</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>蔡東宏</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/20</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
           <t>2026/07/14</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/03</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="O11" s="6" t="inlineStr">
-        <is>
-          <t>DQA test中,
-1) ME: 搖擺測試pass
-2）Function：待新版MSI Center AP release( 包入MKT name支援AI Noise Cancellation Pro), 安排HDI製作</t>
-        </is>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>1) Cyborg Black Edition SKU: Cyborg A+Venture B/C/D機構件+白光鍵盤</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" hidden="1" outlineLevel="1">
-      <c r="A12" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>17U3</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Cyborg 17 Black Edition B13WF</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>RPL-H 45W</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>楊淑賢</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/24</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="inlineStr"/>
-      <c r="J12" s="10" t="inlineStr"/>
-      <c r="K12" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/01</t>
-        </is>
-      </c>
-      <c r="L12" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/14</t>
-        </is>
-      </c>
-      <c r="M12" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/03</t>
-        </is>
-      </c>
-      <c r="N12" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="O12" s="12" t="inlineStr">
-        <is>
-          <t>DQA test中,
-1) ME: 搖擺測試pass
-2）Function：待新版MSI Center AP release( 包入MKT name支援AI Noise Cancellation Pro), 安排HDI製作</t>
-        </is>
-      </c>
-      <c r="P12" s="12" t="inlineStr">
-        <is>
-          <t>1) Cyborg Black Edition SKU: Cyborg A+Venture B/C/D機構件+白光鍵盤</t>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/30</t>
+        </is>
+      </c>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>DDR5 sku, 預計7/17 MVT Assy</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1440,12 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>17U3</t>
+          <t>15T3</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Cyborg 17 Black Edition B2RWF</t>
+          <t>Katana 15 HX C14WFK</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1445,7 +1455,7 @@
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>RPL-H refresh 45W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
@@ -1455,196 +1465,198 @@
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>楊淑賢</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>2026/06/24</t>
-        </is>
-      </c>
-      <c r="I13" s="10" t="inlineStr"/>
+          <t>2026/04/20</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
       <c r="J13" s="10" t="inlineStr"/>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>2026/07/01</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="L13" s="10" t="inlineStr">
         <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/30</t>
+        </is>
+      </c>
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>DDR5 sku, 預計7/17 MVT Assy</t>
+        </is>
+      </c>
+      <c r="P13" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" hidden="1" outlineLevel="1">
+      <c r="A14" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>15T3</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Katana 15 HX C14WGK</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>蔡東宏</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>2026/04/20</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr"/>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
           <t>2026/07/14</t>
         </is>
       </c>
-      <c r="M13" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/03</t>
-        </is>
-      </c>
-      <c r="N13" s="10" t="inlineStr">
+      <c r="L14" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/30</t>
+        </is>
+      </c>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>DDR5 sku, 預計7/17 MVT Assy</t>
+        </is>
+      </c>
+      <c r="P14" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" hidden="1" outlineLevel="1">
+      <c r="A15" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>15T3</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Katana 15 HX C14WEOK</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>蔡東宏</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/15</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr"/>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/24</t>
+        </is>
+      </c>
+      <c r="L15" s="10" t="inlineStr">
         <is>
           <t>2026/08/07</t>
         </is>
       </c>
-      <c r="O13" s="12" t="inlineStr">
-        <is>
-          <t>DQA test中,
-1) ME: 搖擺測試pass
-2）Function：待新版MSI Center AP release( 包入MKT name支援AI Noise Cancellation Pro), 安排HDI製作</t>
-        </is>
-      </c>
-      <c r="P13" s="12" t="inlineStr">
-        <is>
-          <t>1) Cyborg Black Edition SKU: Cyborg A+Venture B/C/D機構件+白光鍵盤</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>15T2</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Venture 15 AI+ B3M</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>PTL-H 80W</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Intel® Arc™ Graphics</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>李文欽</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/20</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/26</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/08</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/20</t>
-        </is>
-      </c>
-      <c r="M14" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/17</t>
-        </is>
-      </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/27</t>
-        </is>
-      </c>
-      <c r="O14" s="6" t="inlineStr">
-        <is>
-          <t>MVT1 正式組裝@7/13</t>
-        </is>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>1) w/FP的Touchpad 試產物料,需要採購協助Pull in</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>15T3</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Katana 15 HX C14WEK</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/20</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/14</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/30</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/20</t>
-        </is>
-      </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/30</t>
-        </is>
-      </c>
-      <c r="O15" s="6" t="inlineStr">
-        <is>
-          <t>DDR5 sku, 預計7/17 MVT Assy</t>
-        </is>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="O15" s="12" t="inlineStr">
+        <is>
+          <t>DDR4 sku, MVT備料中,預計7/24 MVT SMT</t>
+        </is>
+      </c>
+      <c r="P15" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1661,7 +1673,7 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WFK</t>
+          <t>Katana 15 HX C14WFOK</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1686,38 +1698,38 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/05/15</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>2026/06/01</t>
+          <t>2026/06/15</t>
         </is>
       </c>
       <c r="J16" s="10" t="inlineStr"/>
       <c r="K16" s="10" t="inlineStr">
         <is>
-          <t>2026/07/14</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>2026/07/30</t>
+          <t>2026/08/07</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
-          <t>2026/08/20</t>
+          <t>2026/08/21</t>
         </is>
       </c>
       <c r="N16" s="10" t="inlineStr">
         <is>
-          <t>2026/08/30</t>
+          <t>2026/08/31</t>
         </is>
       </c>
       <c r="O16" s="12" t="inlineStr">
         <is>
-          <t>DDR5 sku, 預計7/17 MVT Assy</t>
+          <t>DDR4 sku, MVT備料中,預計7/24 MVT SMT</t>
         </is>
       </c>
       <c r="P16" s="12" t="inlineStr">
@@ -1737,7 +1749,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WGK</t>
+          <t>Katana 15 HX C14WGOK</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1762,38 +1774,38 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/05/15</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>2026/06/01</t>
+          <t>2026/06/15</t>
         </is>
       </c>
       <c r="J17" s="10" t="inlineStr"/>
       <c r="K17" s="10" t="inlineStr">
         <is>
-          <t>2026/07/14</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>2026/07/30</t>
+          <t>2026/08/07</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>2026/08/20</t>
+          <t>2026/08/21</t>
         </is>
       </c>
       <c r="N17" s="10" t="inlineStr">
         <is>
-          <t>2026/08/30</t>
+          <t>2026/08/31</t>
         </is>
       </c>
       <c r="O17" s="12" t="inlineStr">
         <is>
-          <t>DDR5 sku, 預計7/17 MVT Assy</t>
+          <t>DDR4 sku, MVT備料中,預計7/24 MVT SMT</t>
         </is>
       </c>
       <c r="P17" s="12" t="inlineStr">
@@ -1802,309 +1814,81 @@
         </is>
       </c>
     </row>
-    <row r="18" hidden="1" outlineLevel="1">
-      <c r="A18" s="8" t="n">
+    <row r="18">
+      <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>15T3</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Katana 15 HX C14WEOK</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>2621</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Prestige N16 AI+ C1XMT</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/15</t>
-        </is>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J18" s="10" t="inlineStr"/>
-      <c r="K18" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/24</t>
-        </is>
-      </c>
-      <c r="L18" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="M18" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="N18" s="10" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>N1x 80W</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>林晉弘</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>2024/11/25</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>2025/01/20</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>2025/06/25</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>2026/03/12</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O18" s="12" t="inlineStr">
-        <is>
-          <t>DDR4 sku, MVT備料中,預計7/24 MVT SMT</t>
-        </is>
-      </c>
-      <c r="P18" s="12" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" hidden="1" outlineLevel="1">
-      <c r="A19" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>15T3</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Katana 15 HX C14WFOK</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/15</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J19" s="10" t="inlineStr"/>
-      <c r="K19" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/24</t>
-        </is>
-      </c>
-      <c r="L19" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="M19" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="N19" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/31</t>
-        </is>
-      </c>
-      <c r="O19" s="12" t="inlineStr">
-        <is>
-          <t>DDR4 sku, MVT備料中,預計7/24 MVT SMT</t>
-        </is>
-      </c>
-      <c r="P19" s="12" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" hidden="1" outlineLevel="1">
-      <c r="A20" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>15T3</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>Katana 15 HX C14WGOK</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/15</t>
-        </is>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J20" s="10" t="inlineStr"/>
-      <c r="K20" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/24</t>
-        </is>
-      </c>
-      <c r="L20" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="M20" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="N20" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/31</t>
-        </is>
-      </c>
-      <c r="O20" s="12" t="inlineStr">
-        <is>
-          <t>DDR4 sku, MVT備料中,預計7/24 MVT SMT</t>
-        </is>
-      </c>
-      <c r="P20" s="12" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>2621</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Prestige N16 AI+ C1XMT</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>N1x 80W</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>林晉弘</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>2024/11/25</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>2025/01/20</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>2025/06/25</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>2026/03/12</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/30</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/17</t>
-        </is>
-      </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/31</t>
-        </is>
-      </c>
-      <c r="O21" s="6" t="inlineStr">
+      <c r="O18" s="6" t="inlineStr">
         <is>
           <t>MVT測試中</t>
         </is>
       </c>
-      <c r="P21" s="6" t="inlineStr">
+      <c r="P18" s="6" t="inlineStr">
         <is>
           <t>1)battery life評估標準，是否可只用2.8 panel的測試結果為準，MSFT內部確認中。DQA會根據 NV/MSFT要求MSI進行如下測試 a)2.8K panel+day0 rev.A測試balance mode下 web browersing/ Modern standby b)3.8K panel + day0 rev.A測試BPE mode下web browersing/ Procyon
 2)NV Abnormal shut down 的solution，NV本周更新可於BSP Day0 rev.A驗證，待本周SW ready後，DQA/工廠會同時驗證確認。
@@ -2113,81 +1897,81 @@
         </is>
       </c>
     </row>
-    <row r="22" hidden="1" outlineLevel="1">
-      <c r="A22" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
+    <row r="19" hidden="1" outlineLevel="1">
+      <c r="A19" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>2621</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>Prestige N16 Flip AI+ C1XMT</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>N1x 80W</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>林晉弘</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>2024/11/25</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>2025/01/20</t>
         </is>
       </c>
-      <c r="J22" s="10" t="inlineStr">
+      <c r="J19" s="10" t="inlineStr">
         <is>
           <t>2025/06/25</t>
         </is>
       </c>
-      <c r="K22" s="10" t="inlineStr">
+      <c r="K19" s="10" t="inlineStr">
         <is>
           <t>2026/03/12</t>
         </is>
       </c>
-      <c r="L22" s="10" t="inlineStr">
+      <c r="L19" s="10" t="inlineStr">
         <is>
           <t>2026/06/30</t>
         </is>
       </c>
-      <c r="M22" s="10" t="inlineStr">
+      <c r="M19" s="10" t="inlineStr">
         <is>
           <t>2026/08/17</t>
         </is>
       </c>
-      <c r="N22" s="10" t="inlineStr">
+      <c r="N19" s="10" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O22" s="12" t="inlineStr">
+      <c r="O19" s="12" t="inlineStr">
         <is>
           <t>MVT測試中</t>
         </is>
       </c>
-      <c r="P22" s="12" t="inlineStr">
+      <c r="P19" s="12" t="inlineStr">
         <is>
           <t>1)battery life評估標準，是否可只用2.8 panel的測試結果為準，MSFT內部確認中。DQA會根據 NV/MSFT要求MSI進行如下測試 a)2.8K panel+day0 rev.A測試balance mode下 web browersing/ Modern standby b)3.8K panel + day0 rev.A測試BPE mode下web browersing/ Procyon
 2)NV Abnormal shut down 的solution，NV本周更新可於BSP Day0 rev.A驗證，待本周SW ready後，DQA/工廠會同時驗證確認。
@@ -2196,229 +1980,231 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>24V1</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Modern 14 LE J3M</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>WCL 25W</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Intel® graphics</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>倪嬌嬌</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>2026/06/02</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>2026/07/07</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr"/>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>2026/07/29</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>2026/07/08</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>2026/08/18</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O23" s="6" t="inlineStr">
+      <c r="O20" s="6" t="inlineStr">
         <is>
           <t>MSIK: 7/14 DQA test start MSIT: 7/16收到機器</t>
         </is>
       </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>1)認證: 參考Weibu認證Schedule, a. 美洲US FCC 9/8 b.歐洲CE NB &amp;澳洲RCM 8/28 ready, 認證時間有風險, 已經highlight給微步team作認證評估</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>1)認證：8/E ready可出貨地區:  DE/UK/TR/BNX/NEU/SEE/FR/ES/PL/CZ/CIS/IT/JP/AU
+2）認證 8/E無法同步ready地區:  9/8 ready: LA/CA/ AR/CL  9/18 ready: UA 10/2 ready: CO/RU 12/18 ready: MX</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>26V1</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Modern 16 LE J3M</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>WCL 25W</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Intel® graphics</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>倪嬌嬌</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>2026/06/02</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>2026/07/07</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr"/>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>2026/07/29</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>2026/07/08</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>2026/08/18</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O24" s="6" t="inlineStr">
+      <c r="O21" s="6" t="inlineStr">
         <is>
           <t>MSIK: 7/14 DQA test start MSIT: 7/16收到機器</t>
         </is>
       </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>1)認證: 參考Weibu認證Schedule, a. 美洲US FCC 9/8 b.歐洲CE NB &amp;澳洲RCM 8/28 ready, 認證時間有風險, 已經highlight給微步team作認證評估</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>1)認證: 1. 8/E ready可出貨地區:  DE/UK/TR/BNX/NEU/SEE/FR/ES/PL/CZ/CIS/IT/JP/AU
+2)認證 8/E無法同步ready地區:  9/8 ready: LA/CA/ AR/CL  9/18 ready: UA 10/2 ready: CO/RU 12/18 ready: MX</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>15TK</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Cyborg A15 Max C1PWE</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>HWK 45W</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>2026/05/28</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>2026/06/26</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr"/>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>2026/08/04</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>2026/08/18</t>
         </is>
       </c>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>2026/09/09</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>2026/09/19</t>
         </is>
       </c>
-      <c r="O25" s="6" t="inlineStr">
+      <c r="O22" s="6" t="inlineStr">
         <is>
           <t>HPT sku: HPT1測試MODS fail, HPT1/HPT2 都無法進入 Modern Standby,請RD持續與AMD co-work釐清問題.</t>
         </is>
       </c>
-      <c r="P25" s="6" t="inlineStr">
+      <c r="P22" s="6" t="inlineStr">
         <is>
           <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/22(較原時程delay 33天),因需搭配新的PI code &amp; driver且專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP預計延後至9/19 (先前已由 9 月底提前至 8/31, 現又延至9/
 19),後續將依實際測試結果滾動式調整專案時程。
@@ -2426,77 +2212,77 @@
         </is>
       </c>
     </row>
-    <row r="26" hidden="1" outlineLevel="1">
-      <c r="A26" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
+    <row r="23" hidden="1" outlineLevel="1">
+      <c r="A23" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>15TK</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>Cyborg A15 Max C1PWF</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>HWK 45W</t>
         </is>
       </c>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>RTX 5060</t>
         </is>
       </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>2026/05/28</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>2026/06/26</t>
         </is>
       </c>
-      <c r="J26" s="10" t="inlineStr"/>
-      <c r="K26" s="10" t="inlineStr">
+      <c r="J23" s="10" t="inlineStr"/>
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>2026/08/04</t>
         </is>
       </c>
-      <c r="L26" s="10" t="inlineStr">
+      <c r="L23" s="10" t="inlineStr">
         <is>
           <t>2026/08/18</t>
         </is>
       </c>
-      <c r="M26" s="10" t="inlineStr">
+      <c r="M23" s="10" t="inlineStr">
         <is>
           <t>2026/09/09</t>
         </is>
       </c>
-      <c r="N26" s="10" t="inlineStr">
+      <c r="N23" s="10" t="inlineStr">
         <is>
           <t>2026/09/19</t>
         </is>
       </c>
-      <c r="O26" s="12" t="inlineStr">
+      <c r="O23" s="12" t="inlineStr">
         <is>
           <t>HPT sku: HPT1測試MODS fail, HPT1/HPT2 都無法進入 Modern Standby,請RD持續與AMD co-work釐清問題.</t>
         </is>
       </c>
-      <c r="P26" s="12" t="inlineStr">
+      <c r="P23" s="12" t="inlineStr">
         <is>
           <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/22(較原時程delay 33天),因需搭配新的PI code &amp; driver且專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP預計延後至9/19 (先前已由 9 月底提前至 8/31, 現又延至9/
 19),後續將依實際測試結果滾動式調整專案時程。
@@ -2504,77 +2290,77 @@
         </is>
       </c>
     </row>
-    <row r="27" hidden="1" outlineLevel="1">
-      <c r="A27" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
+    <row r="24" hidden="1" outlineLevel="1">
+      <c r="A24" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>15TK</t>
         </is>
       </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>Cyborg A15 Max C1PWG</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>HWK 45W</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>2026/05/28</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>2026/06/26</t>
         </is>
       </c>
-      <c r="J27" s="10" t="inlineStr"/>
-      <c r="K27" s="10" t="inlineStr">
+      <c r="J24" s="10" t="inlineStr"/>
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>2026/08/04</t>
         </is>
       </c>
-      <c r="L27" s="10" t="inlineStr">
+      <c r="L24" s="10" t="inlineStr">
         <is>
           <t>2026/08/18</t>
         </is>
       </c>
-      <c r="M27" s="10" t="inlineStr">
+      <c r="M24" s="10" t="inlineStr">
         <is>
           <t>2026/09/09</t>
         </is>
       </c>
-      <c r="N27" s="10" t="inlineStr">
+      <c r="N24" s="10" t="inlineStr">
         <is>
           <t>2026/09/19</t>
         </is>
       </c>
-      <c r="O27" s="12" t="inlineStr">
+      <c r="O24" s="12" t="inlineStr">
         <is>
           <t>HPT sku: HPT1測試MODS fail, HPT1/HPT2 都無法進入 Modern Standby,請RD持續與AMD co-work釐清問題.</t>
         </is>
       </c>
-      <c r="P27" s="12" t="inlineStr">
+      <c r="P24" s="12" t="inlineStr">
         <is>
           <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/22(較原時程delay 33天),因需搭配新的PI code &amp; driver且專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP預計延後至9/19 (先前已由 9 月底提前至 8/31, 現又延至9/
 19),後續將依實際測試結果滾動式調整專案時程。
@@ -2582,77 +2368,77 @@
         </is>
       </c>
     </row>
-    <row r="28" hidden="1" outlineLevel="1">
-      <c r="A28" s="8" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
+    <row r="25" hidden="1" outlineLevel="1">
+      <c r="A25" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>15TK</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>Cyborg A15 C1PWE</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>HWK 45W</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>2026/05/28</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>2026/06/26</t>
         </is>
       </c>
-      <c r="J28" s="10" t="inlineStr"/>
-      <c r="K28" s="10" t="inlineStr">
+      <c r="J25" s="10" t="inlineStr"/>
+      <c r="K25" s="10" t="inlineStr">
         <is>
           <t>2026/08/04</t>
         </is>
       </c>
-      <c r="L28" s="10" t="inlineStr">
+      <c r="L25" s="10" t="inlineStr">
         <is>
           <t>2026/08/18</t>
         </is>
       </c>
-      <c r="M28" s="10" t="inlineStr">
+      <c r="M25" s="10" t="inlineStr">
         <is>
           <t>2026/09/09</t>
         </is>
       </c>
-      <c r="N28" s="10" t="inlineStr">
+      <c r="N25" s="10" t="inlineStr">
         <is>
           <t>2026/09/19</t>
         </is>
       </c>
-      <c r="O28" s="12" t="inlineStr">
+      <c r="O25" s="12" t="inlineStr">
         <is>
           <t>HPT sku: HPT1測試MODS fail, HPT1/HPT2 都無法進入 Modern Standby,請RD持續與AMD co-work釐清問題.</t>
         </is>
       </c>
-      <c r="P28" s="12" t="inlineStr">
+      <c r="P25" s="12" t="inlineStr">
         <is>
           <t>1).Schedule: AMD 將PI 1200I NDA Release 再延至7/22(較原時程delay 33天),因需搭配新的PI code &amp; driver且專案僅有一個MVT stage,工廠&amp; DQA需完整驗證,若測試順利,MP預計延後至9/19 (先前已由 9 月底提前至 8/31, 現又延至9/
 19),後續將依實際測試結果滾動式調整專案時程。
@@ -2660,246 +2446,484 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>14T3</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Prestige N14 AI+ D1M</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>N1 35W</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>倪嬌嬌</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>2025/09/01</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>2026/04/15</t>
         </is>
       </c>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>2026/08/03</t>
         </is>
       </c>
-      <c r="L29" s="4" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>2026/09/14</t>
         </is>
       </c>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>2026/10/13</t>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="N26" s="4" t="inlineStr">
         <is>
           <t>2026/10/26</t>
         </is>
       </c>
-      <c r="O29" s="6" t="inlineStr">
+      <c r="O26" s="6" t="inlineStr">
         <is>
           <t>MVT SMT@8/3--depend on Material ready date作調整</t>
         </is>
       </c>
-      <c r="P29" s="6" t="inlineStr">
+      <c r="P26" s="6" t="inlineStr">
         <is>
           <t>1) Schedule: a.MVT D件備料ready日期@7/29 b. CPU交期還未放行, 先預估8/B交期
 3)備料：量產交料HQ23, 11/M交料, 還在持續追蹤中</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>2623</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Prestige N16 C1M</t>
         </is>
       </c>
-      <c r="D30" s="15" t="inlineStr">
+      <c r="D27" s="15" t="inlineStr">
         <is>
           <t>EVT</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>N1 45W</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>賴雪鳳</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>2025/04/30</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>2025/09/01</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>2026/04/15</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>2026/08/03</t>
         </is>
       </c>
-      <c r="L30" s="4" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>2026/09/14</t>
         </is>
       </c>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>2026/10/13</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="N27" s="4" t="inlineStr">
         <is>
           <t>2026/10/26</t>
         </is>
       </c>
-      <c r="O30" s="6" t="inlineStr">
+      <c r="O27" s="6" t="inlineStr">
         <is>
           <t>1)EVT 更新BSP6.2.1  持續驗證中,ID定案 顏色keep 淺灰+ D side 咬花
 3) N1 SoC 出貨延遲 MVT 預計延到8/3 SMT, 8/4 Pre-Assy ,8/6 Assy</t>
         </is>
       </c>
-      <c r="P30" s="6" t="inlineStr">
+      <c r="P27" s="6" t="inlineStr">
         <is>
           <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Katana 18 HX A14WEK</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>2026/08/24</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>2026/10/12</t>
         </is>
       </c>
-      <c r="L31" s="4" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr">
         <is>
           <t>2026/11/02</t>
         </is>
       </c>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>2026/11/21</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="N28" s="4" t="inlineStr">
         <is>
           <t>2026/11/30</t>
         </is>
       </c>
-      <c r="O31" s="6" t="inlineStr">
+      <c r="O28" s="6" t="inlineStr">
         <is>
           <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
         </is>
       </c>
-      <c r="P31" s="6" t="inlineStr">
+      <c r="P28" s="6" t="inlineStr">
         <is>
           <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
 2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" hidden="1" outlineLevel="1">
+      <c r="A29" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Katana 18 HX A14WFK</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>顧曉琴</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="inlineStr">
+        <is>
+          <t>2026/10/12</t>
+        </is>
+      </c>
+      <c r="L29" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/21</t>
+        </is>
+      </c>
+      <c r="N29" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="O29" s="12" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
+        </is>
+      </c>
+      <c r="P29" s="12" t="inlineStr">
+        <is>
+          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
+2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" hidden="1" outlineLevel="1">
+      <c r="A30" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Katana 18 HX A14WGK</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>顧曉琴</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
+      <c r="K30" s="10" t="inlineStr">
+        <is>
+          <t>2026/10/12</t>
+        </is>
+      </c>
+      <c r="L30" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/21</t>
+        </is>
+      </c>
+      <c r="N30" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="O30" s="12" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
+        </is>
+      </c>
+      <c r="P30" s="12" t="inlineStr">
+        <is>
+          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
+2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" hidden="1" outlineLevel="1">
+      <c r="A31" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Katana 18 HX A14WEOK</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>顧曉琴</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="inlineStr"/>
+      <c r="K31" s="10" t="inlineStr">
+        <is>
+          <t>2026/10/20</t>
+        </is>
+      </c>
+      <c r="L31" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/23</t>
+        </is>
+      </c>
+      <c r="N31" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/02</t>
+        </is>
+      </c>
+      <c r="O31" s="12" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+        </is>
+      </c>
+      <c r="P31" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2938,7 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WFK</t>
+          <t>Katana 18 HX A14WFOK</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
@@ -2939,22 +2963,18 @@
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J32" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr"/>
       <c r="K32" s="10" t="inlineStr">
         <is>
-          <t>2026/10/12</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="L32" s="10" t="inlineStr">
@@ -2964,23 +2984,22 @@
       </c>
       <c r="M32" s="10" t="inlineStr">
         <is>
-          <t>2026/11/21</t>
+          <t>2026/11/23</t>
         </is>
       </c>
       <c r="N32" s="10" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2026/12/02</t>
         </is>
       </c>
       <c r="O32" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P32" s="12" t="inlineStr">
         <is>
-          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
-2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -2995,7 +3014,7 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGK</t>
+          <t>Katana 18 HX A14WGOK</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
@@ -3020,22 +3039,18 @@
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J33" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J33" s="10" t="inlineStr"/>
       <c r="K33" s="10" t="inlineStr">
         <is>
-          <t>2026/10/12</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="L33" s="10" t="inlineStr">
@@ -3045,23 +3060,22 @@
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
-          <t>2026/11/21</t>
+          <t>2026/11/23</t>
         </is>
       </c>
       <c r="N33" s="10" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2026/12/02</t>
         </is>
       </c>
       <c r="O33" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
-2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3090,7 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WEOK</t>
+          <t>Crosshair 18 Max HX B14WE</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
@@ -3101,15 +3115,19 @@
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J34" s="10" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
       <c r="K34" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3122,22 +3140,23 @@
       </c>
       <c r="M34" s="10" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2026/11/28</t>
         </is>
       </c>
       <c r="N34" s="10" t="inlineStr">
         <is>
-          <t>2026/12/02</t>
+          <t>2026/12/07</t>
         </is>
       </c>
       <c r="O34" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
         </is>
       </c>
       <c r="P34" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
+2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3171,7 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WFOK</t>
+          <t>Crosshair 18 Max HX B14WF</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
@@ -3177,15 +3196,19 @@
       </c>
       <c r="H35" s="10" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J35" s="10" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
       <c r="K35" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3198,22 +3221,23 @@
       </c>
       <c r="M35" s="10" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2026/11/28</t>
         </is>
       </c>
       <c r="N35" s="10" t="inlineStr">
         <is>
-          <t>2026/12/02</t>
+          <t>2026/12/07</t>
         </is>
       </c>
       <c r="O35" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
         </is>
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
+2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
         </is>
       </c>
     </row>
@@ -3228,7 +3252,7 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGOK</t>
+          <t>Crosshair 18 Max HX B14WG</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
@@ -3253,15 +3277,19 @@
       </c>
       <c r="H36" s="10" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J36" s="10" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
       <c r="K36" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3274,22 +3302,23 @@
       </c>
       <c r="M36" s="10" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2026/11/28</t>
         </is>
       </c>
       <c r="N36" s="10" t="inlineStr">
         <is>
-          <t>2026/12/02</t>
+          <t>2026/12/07</t>
         </is>
       </c>
       <c r="O36" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
         </is>
       </c>
       <c r="P36" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
+2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3333,7 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WE</t>
+          <t>Crosshair 18 Max HX B14WGX</t>
         </is>
       </c>
       <c r="D37" s="14" t="inlineStr">
@@ -3319,7 +3348,7 @@
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G37" s="10" t="inlineStr">
@@ -3385,7 +3414,7 @@
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WF</t>
+          <t>Crosshair 18 Max HX B14WEO</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
@@ -3400,7 +3429,7 @@
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
@@ -3410,19 +3439,15 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J38" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J38" s="10" t="inlineStr"/>
       <c r="K38" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3445,13 +3470,12 @@
       </c>
       <c r="O38" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P38" s="12" t="inlineStr">
         <is>
-          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
-2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3490,7 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WG</t>
+          <t>Crosshair 18 Max HX B14WFO</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
@@ -3481,7 +3505,7 @@
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G39" s="10" t="inlineStr">
@@ -3491,19 +3515,15 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J39" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J39" s="10" t="inlineStr"/>
       <c r="K39" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3526,13 +3546,12 @@
       </c>
       <c r="O39" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
-2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3566,7 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WGX</t>
+          <t>Crosshair 18 Max HX B14WGO</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
@@ -3572,19 +3591,15 @@
       </c>
       <c r="H40" s="10" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J40" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/24</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J40" s="10" t="inlineStr"/>
       <c r="K40" s="10" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3607,13 +3622,12 @@
       </c>
       <c r="O40" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P40" s="12" t="inlineStr">
         <is>
-          <t>1) SPEC: DDR5 SKU LAN 會改2.5GbE, D4 SKU LAN 維持1GbE 不變
-2) schedule: Lan修改，0B導入，EVT改成兩次打板，8/12打板for SI 重測Lan，8/24打板for EVT組裝, 此修改吃掉此前DVT-&gt; EVT PCB的驗證buffer時間，若0A測試有問題，or 進版0B第一次打板測試有問題，會影響到EVT 組裝及後續schedule</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3642,7 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WEO</t>
+          <t>Crosshair 18 Max HX B14WGXO</t>
         </is>
       </c>
       <c r="D41" s="14" t="inlineStr">
@@ -3643,7 +3657,7 @@
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
@@ -3704,22 +3718,22 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WFO</t>
-        </is>
-      </c>
-      <c r="D42" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Crosshair 18 Max HX B2WE</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>RPL-HX Next 55W</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
@@ -3729,38 +3743,34 @@
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I42" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I42" s="10" t="inlineStr"/>
       <c r="J42" s="10" t="inlineStr"/>
       <c r="K42" s="10" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/12/08</t>
         </is>
       </c>
       <c r="L42" s="10" t="inlineStr">
         <is>
-          <t>2026/11/02</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="M42" s="10" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2027/01/19</t>
         </is>
       </c>
       <c r="N42" s="10" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="O42" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P42" s="12" t="inlineStr">
@@ -3780,22 +3790,22 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WGO</t>
-        </is>
-      </c>
-      <c r="D43" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Crosshair 18 Max HX B2WEO</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>RPL-HX Next 55W</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
@@ -3808,35 +3818,31 @@
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
+      <c r="I43" s="10" t="inlineStr"/>
       <c r="J43" s="10" t="inlineStr"/>
       <c r="K43" s="10" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/12/08</t>
         </is>
       </c>
       <c r="L43" s="10" t="inlineStr">
         <is>
-          <t>2026/11/02</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="M43" s="10" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2027/01/19</t>
         </is>
       </c>
       <c r="N43" s="10" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="O43" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P43" s="12" t="inlineStr">
@@ -3856,22 +3862,22 @@
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WGXO</t>
-        </is>
-      </c>
-      <c r="D44" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Crosshair 18 Max HX B2WF</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>RPL-HX Next 55W</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
@@ -3881,38 +3887,34 @@
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I44" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I44" s="10" t="inlineStr"/>
       <c r="J44" s="10" t="inlineStr"/>
       <c r="K44" s="10" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/12/08</t>
         </is>
       </c>
       <c r="L44" s="10" t="inlineStr">
         <is>
-          <t>2026/11/02</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="M44" s="10" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2027/01/19</t>
         </is>
       </c>
       <c r="N44" s="10" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="O44" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P44" s="12" t="inlineStr">
@@ -3932,7 +3934,7 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WE</t>
+          <t>Crosshair 18 Max HX B2WFO</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
@@ -3947,7 +3949,7 @@
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
@@ -3957,7 +3959,7 @@
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr"/>
@@ -3984,7 +3986,7 @@
       </c>
       <c r="O45" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P45" s="12" t="inlineStr">
@@ -4004,7 +4006,7 @@
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WEO</t>
+          <t>Crosshair 18 Max HX B2WG</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
@@ -4019,7 +4021,7 @@
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
@@ -4029,7 +4031,7 @@
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr"/>
@@ -4056,7 +4058,7 @@
       </c>
       <c r="O46" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P46" s="12" t="inlineStr">
@@ -4076,7 +4078,7 @@
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WF</t>
+          <t>Crosshair 18 Max HX B2WGO</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
@@ -4091,7 +4093,7 @@
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G47" s="10" t="inlineStr">
@@ -4101,7 +4103,7 @@
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr"/>
@@ -4128,7 +4130,7 @@
       </c>
       <c r="O47" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P47" s="12" t="inlineStr">
@@ -4148,7 +4150,7 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WFO</t>
+          <t>Crosshair 18 Max HX B2WGX</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
@@ -4163,7 +4165,7 @@
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
@@ -4173,7 +4175,7 @@
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr"/>
@@ -4200,7 +4202,7 @@
       </c>
       <c r="O48" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P48" s="12" t="inlineStr">
@@ -4220,7 +4222,7 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WG</t>
+          <t>Crosshair 18 Max HX B2WGXO</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
@@ -4245,7 +4247,7 @@
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr"/>
@@ -4272,7 +4274,7 @@
       </c>
       <c r="O49" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P49" s="12" t="inlineStr">
@@ -4292,7 +4294,7 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WGO</t>
+          <t>Katana 18 HX A2WEK</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
@@ -4307,7 +4309,7 @@
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
@@ -4317,7 +4319,7 @@
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr"/>
@@ -4344,7 +4346,7 @@
       </c>
       <c r="O50" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P50" s="12" t="inlineStr">
@@ -4364,7 +4366,7 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WGX</t>
+          <t>Katana 18 HX A2WEOK</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
@@ -4379,7 +4381,7 @@
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
@@ -4389,10 +4391,14 @@
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I51" s="10" t="inlineStr"/>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
       <c r="J51" s="10" t="inlineStr"/>
       <c r="K51" s="10" t="inlineStr">
         <is>
@@ -4416,7 +4422,7 @@
       </c>
       <c r="O51" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P51" s="12" t="inlineStr">
@@ -4436,7 +4442,7 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WGXO</t>
+          <t>Katana 18 HX A2WFK</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
@@ -4451,7 +4457,7 @@
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
@@ -4461,7 +4467,7 @@
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr"/>
@@ -4488,7 +4494,7 @@
       </c>
       <c r="O52" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P52" s="12" t="inlineStr">
@@ -4508,7 +4514,7 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WEK</t>
+          <t>Katana 18 HX A2WFOK</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
@@ -4523,7 +4529,7 @@
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G53" s="10" t="inlineStr">
@@ -4533,10 +4539,14 @@
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I53" s="10" t="inlineStr"/>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
       <c r="J53" s="10" t="inlineStr"/>
       <c r="K53" s="10" t="inlineStr">
         <is>
@@ -4560,7 +4570,7 @@
       </c>
       <c r="O53" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P53" s="12" t="inlineStr">
@@ -4580,7 +4590,7 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WEOK</t>
+          <t>Katana 18 HX A2WGK</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
@@ -4595,7 +4605,7 @@
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
@@ -4605,14 +4615,10 @@
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I54" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I54" s="10" t="inlineStr"/>
       <c r="J54" s="10" t="inlineStr"/>
       <c r="K54" s="10" t="inlineStr">
         <is>
@@ -4636,7 +4642,7 @@
       </c>
       <c r="O54" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P54" s="12" t="inlineStr">
@@ -4656,7 +4662,7 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WFK</t>
+          <t>Katana 18 HX A2WGOK</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
@@ -4671,7 +4677,7 @@
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr">
@@ -4681,10 +4687,14 @@
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I55" s="10" t="inlineStr"/>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
       <c r="J55" s="10" t="inlineStr"/>
       <c r="K55" s="10" t="inlineStr">
         <is>
@@ -4708,7 +4718,7 @@
       </c>
       <c r="O55" s="12" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P55" s="12" t="inlineStr">
@@ -4717,79 +4727,83 @@
         </is>
       </c>
     </row>
-    <row r="56" hidden="1" outlineLevel="1">
-      <c r="A56" s="8" t="n">
+    <row r="56">
+      <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="C56" s="10" t="inlineStr">
-        <is>
-          <t>Katana 18 HX A2WFOK</t>
-        </is>
-      </c>
-      <c r="D56" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E56" s="10" t="inlineStr">
-        <is>
-          <t>RPL-HX Next 55W</t>
-        </is>
-      </c>
-      <c r="F56" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G56" s="10" t="inlineStr">
-        <is>
-          <t>顧曉琴</t>
-        </is>
-      </c>
-      <c r="H56" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I56" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J56" s="10" t="inlineStr"/>
-      <c r="K56" s="10" t="inlineStr">
-        <is>
-          <t>2026/12/08</t>
-        </is>
-      </c>
-      <c r="L56" s="10" t="inlineStr">
-        <is>
-          <t>2026/12/30</t>
-        </is>
-      </c>
-      <c r="M56" s="10" t="inlineStr">
-        <is>
-          <t>2027/01/19</t>
-        </is>
-      </c>
-      <c r="N56" s="10" t="inlineStr">
-        <is>
-          <t>2027/01/30</t>
-        </is>
-      </c>
-      <c r="O56" s="12" t="inlineStr">
-        <is>
-          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
-        </is>
-      </c>
-      <c r="P56" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>14T4</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Prestige 14 AI</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>NVL-H 30W</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>朱芳芳</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/04</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/20</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/15</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/25</t>
+        </is>
+      </c>
+      <c r="O56" s="6" t="inlineStr">
+        <is>
+          <t>DVT SMT@7/22</t>
+        </is>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4799,305 +4813,309 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>14T4</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WGK</t>
-        </is>
-      </c>
-      <c r="D57" s="16" t="inlineStr">
+          <t>Prestige 14 AI+ Flip</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>NVL-H 30W</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>朱芳芳</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
+      <c r="J57" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="K57" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/04</t>
+        </is>
+      </c>
+      <c r="L57" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/20</t>
+        </is>
+      </c>
+      <c r="M57" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/15</t>
+        </is>
+      </c>
+      <c r="N57" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/25</t>
+        </is>
+      </c>
+      <c r="O57" s="12" t="inlineStr">
+        <is>
+          <t>DVT SMT@7/22</t>
+        </is>
+      </c>
+      <c r="P57" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>2624</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Prestige 16 AI+</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>NVL-H 30W</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>朱芳芳</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr"/>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/04</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/20</t>
+        </is>
+      </c>
+      <c r="M58" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/15</t>
+        </is>
+      </c>
+      <c r="N58" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/25</t>
+        </is>
+      </c>
+      <c r="O58" s="6" t="inlineStr">
+        <is>
+          <t>DVT SMT@7/22</t>
+        </is>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" hidden="1" outlineLevel="1">
+      <c r="A59" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>2624</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>Prestige 16 Flip AI+</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>NVL-H 30W</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="inlineStr">
+        <is>
+          <t>朱芳芳</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="I59" s="10" t="inlineStr"/>
+      <c r="J59" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="K59" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/04</t>
+        </is>
+      </c>
+      <c r="L59" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/20</t>
+        </is>
+      </c>
+      <c r="M59" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/15</t>
+        </is>
+      </c>
+      <c r="N59" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/25</t>
+        </is>
+      </c>
+      <c r="O59" s="12" t="inlineStr">
+        <is>
+          <t>DVT SMT@7/22</t>
+        </is>
+      </c>
+      <c r="P59" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>13Q5</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Prestige 13 AI+ A4M</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E57" s="10" t="inlineStr">
-        <is>
-          <t>RPL-HX Next 55W</t>
-        </is>
-      </c>
-      <c r="F57" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G57" s="10" t="inlineStr">
-        <is>
-          <t>顧曉琴</t>
-        </is>
-      </c>
-      <c r="H57" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I57" s="10" t="inlineStr"/>
-      <c r="J57" s="10" t="inlineStr"/>
-      <c r="K57" s="10" t="inlineStr">
-        <is>
-          <t>2026/12/08</t>
-        </is>
-      </c>
-      <c r="L57" s="10" t="inlineStr">
-        <is>
-          <t>2026/12/30</t>
-        </is>
-      </c>
-      <c r="M57" s="10" t="inlineStr">
-        <is>
-          <t>2027/01/19</t>
-        </is>
-      </c>
-      <c r="N57" s="10" t="inlineStr">
-        <is>
-          <t>2027/01/30</t>
-        </is>
-      </c>
-      <c r="O57" s="12" t="inlineStr">
-        <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
-        </is>
-      </c>
-      <c r="P57" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" hidden="1" outlineLevel="1">
-      <c r="A58" s="8" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="C58" s="10" t="inlineStr">
-        <is>
-          <t>Katana 18 HX A2WGOK</t>
-        </is>
-      </c>
-      <c r="D58" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E58" s="10" t="inlineStr">
-        <is>
-          <t>RPL-HX Next 55W</t>
-        </is>
-      </c>
-      <c r="F58" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G58" s="10" t="inlineStr">
-        <is>
-          <t>顧曉琴</t>
-        </is>
-      </c>
-      <c r="H58" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I58" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J58" s="10" t="inlineStr"/>
-      <c r="K58" s="10" t="inlineStr">
-        <is>
-          <t>2026/12/08</t>
-        </is>
-      </c>
-      <c r="L58" s="10" t="inlineStr">
-        <is>
-          <t>2026/12/30</t>
-        </is>
-      </c>
-      <c r="M58" s="10" t="inlineStr">
-        <is>
-          <t>2027/01/19</t>
-        </is>
-      </c>
-      <c r="N58" s="10" t="inlineStr">
-        <is>
-          <t>2027/01/30</t>
-        </is>
-      </c>
-      <c r="O58" s="12" t="inlineStr">
-        <is>
-          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
-        </is>
-      </c>
-      <c r="P58" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>14T4</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>Prestige 14 AI</t>
-        </is>
-      </c>
-      <c r="D59" s="13" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>NVL-H 30W</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>NVL-H 28W</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>朱芳芳</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/14</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/22</t>
-        </is>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/15</t>
-        </is>
-      </c>
-      <c r="K59" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/04</t>
-        </is>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/20</t>
-        </is>
-      </c>
-      <c r="M59" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/15</t>
-        </is>
-      </c>
-      <c r="N59" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/25</t>
-        </is>
-      </c>
-      <c r="O59" s="6" t="inlineStr">
-        <is>
-          <t>DVT SMT@7/22</t>
-        </is>
-      </c>
-      <c r="P59" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" hidden="1" outlineLevel="1">
-      <c r="A60" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>14T4</t>
-        </is>
-      </c>
-      <c r="C60" s="10" t="inlineStr">
-        <is>
-          <t>Prestige 14 AI+ Flip</t>
-        </is>
-      </c>
-      <c r="D60" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E60" s="10" t="inlineStr">
-        <is>
-          <t>NVL-H 30W</t>
-        </is>
-      </c>
-      <c r="F60" s="10" t="inlineStr">
-        <is>
-          <t>Intel® Arc™ Graphics</t>
-        </is>
-      </c>
-      <c r="G60" s="10" t="inlineStr">
-        <is>
-          <t>朱芳芳</t>
-        </is>
-      </c>
-      <c r="H60" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/14</t>
-        </is>
-      </c>
-      <c r="I60" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/22</t>
-        </is>
-      </c>
-      <c r="J60" s="10" t="inlineStr">
-        <is>
-          <t>2026/09/15</t>
-        </is>
-      </c>
-      <c r="K60" s="10" t="inlineStr">
-        <is>
-          <t>2026/11/04</t>
-        </is>
-      </c>
-      <c r="L60" s="10" t="inlineStr">
-        <is>
-          <t>2026/11/20</t>
-        </is>
-      </c>
-      <c r="M60" s="10" t="inlineStr">
-        <is>
-          <t>2026/12/15</t>
-        </is>
-      </c>
-      <c r="N60" s="10" t="inlineStr">
-        <is>
-          <t>2026/12/25</t>
-        </is>
-      </c>
-      <c r="O60" s="12" t="inlineStr">
-        <is>
-          <t>DVT SMT@7/22</t>
-        </is>
-      </c>
-      <c r="P60" s="12" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>顏春梅</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/08</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/21</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/22</t>
+        </is>
+      </c>
+      <c r="M60" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/22</t>
+        </is>
+      </c>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/31</t>
+        </is>
+      </c>
+      <c r="O60" s="6" t="inlineStr">
+        <is>
+          <t>0A layout 中 0A G/O@8/7</t>
+        </is>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>Audio Codec由原來的Reltek更換為TI，線路設計，placement變更</t>
         </is>
       </c>
     </row>
@@ -5107,12 +5125,12 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Prestige 16 AI+</t>
+          <t>Stealth 16 AI+ B4WI</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr">
@@ -5122,58 +5140,63 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>NVL-H 30W</t>
+          <t>NVL-H 45W</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Intel® Arc™ Graphics</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>朱芳芳</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>2026/05/14</t>
-        </is>
-      </c>
-      <c r="I61" s="4" t="inlineStr"/>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>2026/09/15</t>
+          <t>2026/09/16</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>2026/11/04</t>
+          <t>2026/11/11</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>2026/11/20</t>
+          <t>2026/11/30</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>2026/12/15</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>2026/12/25</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="O61" s="6" t="inlineStr">
         <is>
-          <t>DVT SMT@7/22</t>
+          <t>產線排程 DVT SMT@7/23</t>
         </is>
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) DVT 試產缺料I9B-221100C-T07，交期待定;
+2) Schedule:NV VBIOS @1/6, gating 8天,預計12/E 拿到WHQL，可能影響到最終TTM 時間</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5206,12 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Prestige 16 Flip AI+</t>
+          <t>Stealth 16 AI+ B4WH</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
@@ -5198,53 +5221,57 @@
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>NVL-H 30W</t>
+          <t>NVL-H 45W</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>Intel® Arc™ Graphics</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>朱芳芳</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="H62" s="10" t="inlineStr">
         <is>
-          <t>2026/05/14</t>
-        </is>
-      </c>
-      <c r="I62" s="10" t="inlineStr"/>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
       <c r="J62" s="10" t="inlineStr">
         <is>
-          <t>2026/09/15</t>
+          <t>2026/09/16</t>
         </is>
       </c>
       <c r="K62" s="10" t="inlineStr">
         <is>
-          <t>2026/11/04</t>
+          <t>2026/11/11</t>
         </is>
       </c>
       <c r="L62" s="10" t="inlineStr">
         <is>
-          <t>2026/11/20</t>
+          <t>2026/11/30</t>
         </is>
       </c>
       <c r="M62" s="10" t="inlineStr">
         <is>
-          <t>2026/12/15</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="N62" s="10" t="inlineStr">
         <is>
-          <t>2026/12/25</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="O62" s="12" t="inlineStr">
         <is>
-          <t>DVT SMT@7/22</t>
+          <t>產線排程 DVT SMT@7/23</t>
         </is>
       </c>
       <c r="P62" s="12" t="inlineStr">
@@ -5253,83 +5280,83 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
+    <row r="63" hidden="1" outlineLevel="1">
+      <c r="A63" s="8" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>13Q5</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>Prestige 13 AI+ A4M</t>
-        </is>
-      </c>
-      <c r="D63" s="17" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>NVL-H 28W</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>Intel® Arc™ Graphics</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>顏春梅</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="I63" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/18</t>
-        </is>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>2026/10/08</t>
-        </is>
-      </c>
-      <c r="K63" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/21</t>
-        </is>
-      </c>
-      <c r="L63" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/22</t>
-        </is>
-      </c>
-      <c r="M63" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/22</t>
-        </is>
-      </c>
-      <c r="N63" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/31</t>
-        </is>
-      </c>
-      <c r="O63" s="6" t="inlineStr">
-        <is>
-          <t>0A layout 中 0A G/O@8/7</t>
-        </is>
-      </c>
-      <c r="P63" s="6" t="inlineStr">
-        <is>
-          <t>Audio Codec由原來的Reltek更換為TI，線路設計，placement變更</t>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>2633</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WJ</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F63" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5090</t>
+        </is>
+      </c>
+      <c r="G63" s="10" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H63" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/22</t>
+        </is>
+      </c>
+      <c r="J63" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K63" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L63" s="10" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="M63" s="10" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N63" s="10" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="O63" s="12" t="inlineStr">
+        <is>
+          <t>產線排程 DVT SMT@7/23</t>
+        </is>
+      </c>
+      <c r="P63" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -5339,12 +5366,12 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WI</t>
+          <t>Stealth 16 AI+ B4WE</t>
         </is>
       </c>
       <c r="D64" s="17" t="inlineStr">
@@ -5359,12 +5386,12 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -5374,7 +5401,7 @@
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>2026/07/22</t>
+          <t>2026/07/30</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
@@ -5389,7 +5416,7 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2026/11/27</t>
         </is>
       </c>
       <c r="M64" s="4" t="inlineStr">
@@ -5404,13 +5431,13 @@
       </c>
       <c r="O64" s="6" t="inlineStr">
         <is>
-          <t>產線排程 DVT SMT@7/23</t>
+          <t>0A 7/15 gerber out</t>
         </is>
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
-          <t>1) DVT 試產缺料I9B-221100C-T07，交期待定;
-2) Schedule:NV VBIOS @1/6, gating 8天,預計12/E 拿到WHQL，可能影響到最終TTM 時間</t>
+          <t>1)NV VBIOS 驗證時間6周
+2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
     </row>
@@ -5420,12 +5447,12 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WH</t>
+          <t>Stealth 16 AI+ B4WF</t>
         </is>
       </c>
       <c r="D65" s="16" t="inlineStr">
@@ -5440,12 +5467,12 @@
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="H65" s="10" t="inlineStr">
@@ -5455,7 +5482,7 @@
       </c>
       <c r="I65" s="10" t="inlineStr">
         <is>
-          <t>2026/07/22</t>
+          <t>2026/07/30</t>
         </is>
       </c>
       <c r="J65" s="10" t="inlineStr">
@@ -5470,7 +5497,7 @@
       </c>
       <c r="L65" s="10" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2026/11/27</t>
         </is>
       </c>
       <c r="M65" s="10" t="inlineStr">
@@ -5485,12 +5512,13 @@
       </c>
       <c r="O65" s="12" t="inlineStr">
         <is>
-          <t>產線排程 DVT SMT@7/23</t>
+          <t>0A 7/15 gerber out</t>
         </is>
       </c>
       <c r="P65" s="12" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)NV VBIOS 驗證時間6周
+2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5528,12 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WJ</t>
+          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
@@ -5520,12 +5548,12 @@
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="H66" s="10" t="inlineStr">
@@ -5535,7 +5563,7 @@
       </c>
       <c r="I66" s="10" t="inlineStr">
         <is>
-          <t>2026/07/22</t>
+          <t>2026/07/30</t>
         </is>
       </c>
       <c r="J66" s="10" t="inlineStr">
@@ -5550,7 +5578,7 @@
       </c>
       <c r="L66" s="10" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2026/11/27</t>
         </is>
       </c>
       <c r="M66" s="10" t="inlineStr">
@@ -5565,174 +5593,174 @@
       </c>
       <c r="O66" s="12" t="inlineStr">
         <is>
-          <t>產線排程 DVT SMT@7/23</t>
+          <t>0A 7/15 gerber out</t>
         </is>
       </c>
       <c r="P66" s="12" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WE</t>
-        </is>
-      </c>
-      <c r="D67" s="17" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>賴雪鳳</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I67" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/30</t>
-        </is>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K67" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/27</t>
-        </is>
-      </c>
-      <c r="M67" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N67" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="O67" s="6" t="inlineStr">
-        <is>
-          <t>0A 7/15 gerber out</t>
-        </is>
-      </c>
-      <c r="P67" s="6" t="inlineStr">
         <is>
           <t>1)NV VBIOS 驗證時間6周
 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
     </row>
-    <row r="68" hidden="1" outlineLevel="1">
-      <c r="A68" s="8" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="9" t="inlineStr">
+    <row r="67" hidden="1" outlineLevel="1">
+      <c r="A67" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
         <is>
           <t>2634</t>
         </is>
       </c>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WF</t>
-        </is>
-      </c>
-      <c r="D68" s="16" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
+        </is>
+      </c>
+      <c r="D67" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E68" s="10" t="inlineStr">
+      <c r="E67" s="10" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F68" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G68" s="10" t="inlineStr">
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G67" s="10" t="inlineStr">
         <is>
           <t>賴雪鳳</t>
         </is>
       </c>
-      <c r="H68" s="10" t="inlineStr">
+      <c r="H67" s="10" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I68" s="10" t="inlineStr">
+      <c r="I67" s="10" t="inlineStr">
         <is>
           <t>2026/07/30</t>
         </is>
       </c>
-      <c r="J68" s="10" t="inlineStr">
+      <c r="J67" s="10" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K68" s="10" t="inlineStr">
+      <c r="K67" s="10" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L68" s="10" t="inlineStr">
+      <c r="L67" s="10" t="inlineStr">
         <is>
           <t>2026/11/27</t>
         </is>
       </c>
-      <c r="M68" s="10" t="inlineStr">
+      <c r="M67" s="10" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N68" s="10" t="inlineStr">
+      <c r="N67" s="10" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O68" s="12" t="inlineStr">
+      <c r="O67" s="12" t="inlineStr">
         <is>
           <t>0A 7/15 gerber out</t>
         </is>
       </c>
-      <c r="P68" s="12" t="inlineStr">
+      <c r="P67" s="12" t="inlineStr">
         <is>
           <t>1)NV VBIOS 驗證時間6周
 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>2654</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Raider 16 Max HX B4WH</t>
+        </is>
+      </c>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>吳美芳</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M68" s="4" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N68" s="4" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O68" s="6" t="inlineStr">
+        <is>
+          <t>6/29 gerber out，预计7/27 DVT打板</t>
+        </is>
+      </c>
+      <c r="P68" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -5742,78 +5770,77 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
-        </is>
-      </c>
-      <c r="D69" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
+          <t>Raider 16 Max HX B4WI</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>NVL-H 45W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>2026/05/22</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr">
         <is>
-          <t>2026/07/30</t>
+          <t>2026/07/27</t>
         </is>
       </c>
       <c r="J69" s="10" t="inlineStr">
         <is>
-          <t>2026/09/16</t>
+          <t>2026/09/29</t>
         </is>
       </c>
       <c r="K69" s="10" t="inlineStr">
         <is>
-          <t>2026/11/11</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="L69" s="10" t="inlineStr">
         <is>
-          <t>2026/11/27</t>
+          <t>2027/02/02</t>
         </is>
       </c>
       <c r="M69" s="10" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2027/03/08</t>
         </is>
       </c>
       <c r="N69" s="10" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2027/03/18</t>
         </is>
       </c>
       <c r="O69" s="12" t="inlineStr">
         <is>
-          <t>0A 7/15 gerber out</t>
+          <t>6/29 gerber out，预计7/27 DVT打板</t>
         </is>
       </c>
       <c r="P69" s="12" t="inlineStr">
         <is>
-          <t>1)NV VBIOS 驗證時間6周
-2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -5823,156 +5850,155 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
-        </is>
-      </c>
-      <c r="D70" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
+          <t>Raider 16 Max HX B4WJ</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>NVL-H 45W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>2026/05/22</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr">
         <is>
-          <t>2026/07/30</t>
+          <t>2026/07/27</t>
         </is>
       </c>
       <c r="J70" s="10" t="inlineStr">
         <is>
-          <t>2026/09/16</t>
+          <t>2026/09/29</t>
         </is>
       </c>
       <c r="K70" s="10" t="inlineStr">
         <is>
-          <t>2026/11/11</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="L70" s="10" t="inlineStr">
         <is>
-          <t>2026/11/27</t>
+          <t>2027/02/02</t>
         </is>
       </c>
       <c r="M70" s="10" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2027/03/08</t>
         </is>
       </c>
       <c r="N70" s="10" t="inlineStr">
         <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O70" s="12" t="inlineStr">
+        <is>
+          <t>6/29 gerber out，预计7/27 DVT打板</t>
+        </is>
+      </c>
+      <c r="P70" s="12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" hidden="1" outlineLevel="1">
+      <c r="A71" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>2654</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>Raider 16  HX B4WH</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G71" s="10" t="inlineStr">
+        <is>
+          <t>吳美芳</t>
+        </is>
+      </c>
+      <c r="H71" s="10" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J71" s="10" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K71" s="10" t="inlineStr">
+        <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O70" s="12" t="inlineStr">
-        <is>
-          <t>0A 7/15 gerber out</t>
-        </is>
-      </c>
-      <c r="P70" s="12" t="inlineStr">
-        <is>
-          <t>1)NV VBIOS 驗證時間6周
-2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>2654</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>Raider 16 Max HX B4WH</t>
-        </is>
-      </c>
-      <c r="D71" s="13" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5070Ti</t>
-        </is>
-      </c>
-      <c r="G71" s="4" t="inlineStr">
-        <is>
-          <t>鮑佩佩</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I71" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K71" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
+      <c r="L71" s="10" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M71" s="4" t="inlineStr">
+      <c r="M71" s="10" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N71" s="4" t="inlineStr">
+      <c r="N71" s="10" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O71" s="6" t="inlineStr">
-        <is>
-          <t>6/29 gerber out，预计7/27 DVT打板</t>
-        </is>
-      </c>
-      <c r="P71" s="6" t="inlineStr">
+      <c r="O71" s="12" t="inlineStr">
+        <is>
+          <t>原预计7/27 DVT打板，其中一颗D03-636BA0C-N03最快27號進，打板delay一天，不影響后續schedule</t>
+        </is>
+      </c>
+      <c r="P71" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -5989,7 +6015,7 @@
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B4WI</t>
+          <t>Raider 16  HX B4WI</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
@@ -6009,7 +6035,7 @@
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>鮑佩佩</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
@@ -6049,7 +6075,7 @@
       </c>
       <c r="O72" s="12" t="inlineStr">
         <is>
-          <t>6/29 gerber out，预计7/27 DVT打板</t>
+          <t>原预计7/27 DVT打板，其中一颗D03-636BA0C-N03最快27號進，打板delay一天，不影響后續schedule</t>
         </is>
       </c>
       <c r="P72" s="12" t="inlineStr">
@@ -6058,85 +6084,81 @@
         </is>
       </c>
     </row>
-    <row r="73" hidden="1" outlineLevel="1">
-      <c r="A73" s="8" t="n">
+    <row r="73">
+      <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t>2654</t>
-        </is>
-      </c>
-      <c r="C73" s="10" t="inlineStr">
-        <is>
-          <t>Raider 16 Max HX B4WJ</t>
-        </is>
-      </c>
-      <c r="D73" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E73" s="10" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Titan 18 HX B4WH</t>
+        </is>
+      </c>
+      <c r="D73" s="17" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F73" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5090</t>
-        </is>
-      </c>
-      <c r="G73" s="10" t="inlineStr">
-        <is>
-          <t>鮑佩佩</t>
-        </is>
-      </c>
-      <c r="H73" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I73" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J73" s="10" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K73" s="10" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L73" s="10" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M73" s="10" t="inlineStr">
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>高宇奇</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/23</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>2027/01/08</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>2027/02/01</t>
+        </is>
+      </c>
+      <c r="M73" s="4" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N73" s="10" t="inlineStr">
+      <c r="N73" s="4" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O73" s="12" t="inlineStr">
-        <is>
-          <t>6/29 gerber out，预计7/27 DVT打板</t>
-        </is>
-      </c>
-      <c r="P73" s="12" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="O73" s="6" t="inlineStr">
+        <is>
+          <t>0M layout進行中,預計7/27 0M gerber out.</t>
+        </is>
+      </c>
+      <c r="P73" s="6" t="inlineStr"/>
     </row>
     <row r="74" hidden="1" outlineLevel="1">
       <c r="A74" s="8" t="n">
@@ -6144,17 +6166,17 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WH</t>
-        </is>
-      </c>
-      <c r="D74" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Titan 18 HX B4WI</t>
+        </is>
+      </c>
+      <c r="D74" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E74" s="10" t="inlineStr">
@@ -6164,37 +6186,37 @@
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>高宇奇</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/06/29</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/08/14</t>
         </is>
       </c>
       <c r="J74" s="10" t="inlineStr">
         <is>
-          <t>2026/09/29</t>
+          <t>2026/10/23</t>
         </is>
       </c>
       <c r="K74" s="10" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="L74" s="10" t="inlineStr">
         <is>
-          <t>2027/02/02</t>
+          <t>2027/02/01</t>
         </is>
       </c>
       <c r="M74" s="10" t="inlineStr">
@@ -6209,14 +6231,10 @@
       </c>
       <c r="O74" s="12" t="inlineStr">
         <is>
-          <t>6/29 gerber out，预计7/27 DVT打板</t>
-        </is>
-      </c>
-      <c r="P74" s="12" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t>0M layout進行中,預計7/27 0M gerber out.</t>
+        </is>
+      </c>
+      <c r="P74" s="12" t="inlineStr"/>
     </row>
     <row r="75" hidden="1" outlineLevel="1">
       <c r="A75" s="8" t="n">
@@ -6224,17 +6242,17 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Raider 16  HX B4WI</t>
-        </is>
-      </c>
-      <c r="D75" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Titan 18 HX B4WJ</t>
+        </is>
+      </c>
+      <c r="D75" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E75" s="10" t="inlineStr">
@@ -6244,37 +6262,37 @@
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="G75" s="10" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>高宇奇</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/06/29</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/08/14</t>
         </is>
       </c>
       <c r="J75" s="10" t="inlineStr">
         <is>
-          <t>2026/09/29</t>
+          <t>2026/10/23</t>
         </is>
       </c>
       <c r="K75" s="10" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="L75" s="10" t="inlineStr">
         <is>
-          <t>2027/02/02</t>
+          <t>2027/02/01</t>
         </is>
       </c>
       <c r="M75" s="10" t="inlineStr">
@@ -6289,90 +6307,86 @@
       </c>
       <c r="O75" s="12" t="inlineStr">
         <is>
-          <t>6/29 gerber out，预计7/27 DVT打板</t>
-        </is>
-      </c>
-      <c r="P75" s="12" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="n">
+          <t>0M layout進行中,預計7/27 0M gerber out.</t>
+        </is>
+      </c>
+      <c r="P75" s="12" t="inlineStr"/>
+    </row>
+    <row r="76" hidden="1" outlineLevel="1">
+      <c r="A76" s="8" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B76" s="9" t="inlineStr">
         <is>
           <t>1851</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>Titan 18 HX B4WH</t>
-        </is>
-      </c>
-      <c r="D76" s="17" t="inlineStr">
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>Raider 18 Max HX B4WH</t>
+        </is>
+      </c>
+      <c r="D76" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>NVL-HX 65W</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="inlineStr">
         <is>
           <t>RTX 5070Ti</t>
         </is>
       </c>
-      <c r="G76" s="4" t="inlineStr">
+      <c r="G76" s="10" t="inlineStr">
         <is>
           <t>高宇奇</t>
         </is>
       </c>
-      <c r="H76" s="4" t="inlineStr">
+      <c r="H76" s="10" t="inlineStr">
         <is>
           <t>2026/06/29</t>
         </is>
       </c>
-      <c r="I76" s="4" t="inlineStr">
+      <c r="I76" s="10" t="inlineStr">
         <is>
           <t>2026/08/14</t>
         </is>
       </c>
-      <c r="J76" s="4" t="inlineStr">
+      <c r="J76" s="10" t="inlineStr">
         <is>
           <t>2026/10/23</t>
         </is>
       </c>
-      <c r="K76" s="4" t="inlineStr">
+      <c r="K76" s="10" t="inlineStr">
         <is>
           <t>2027/01/08</t>
         </is>
       </c>
-      <c r="L76" s="4" t="inlineStr">
+      <c r="L76" s="10" t="inlineStr">
         <is>
           <t>2027/02/01</t>
         </is>
       </c>
-      <c r="M76" s="4" t="inlineStr">
+      <c r="M76" s="10" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N76" s="4" t="inlineStr">
+      <c r="N76" s="10" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O76" s="6" t="inlineStr">
+      <c r="O76" s="12" t="inlineStr">
         <is>
           <t>0M layout進行中,預計7/27 0M gerber out.</t>
         </is>
       </c>
-      <c r="P76" s="6" t="inlineStr"/>
+      <c r="P76" s="12" t="inlineStr"/>
     </row>
     <row r="77" hidden="1" outlineLevel="1">
       <c r="A77" s="8" t="n">
@@ -6385,7 +6399,7 @@
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>Titan 18 HX B4WI</t>
+          <t>Raider 18 Max HX B4WI</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
@@ -6395,7 +6409,7 @@
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>NVL-HX 55W</t>
+          <t>NVL-HX 65W</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
@@ -6461,7 +6475,7 @@
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Titan 18 HX B4WJ</t>
+          <t>Raider 18 Max HX B4WJ</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
@@ -6471,136 +6485,140 @@
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
+          <t>NVL-HX 65W</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5090</t>
+        </is>
+      </c>
+      <c r="G78" s="10" t="inlineStr">
+        <is>
+          <t>高宇奇</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I78" s="10" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="J78" s="10" t="inlineStr">
+        <is>
+          <t>2026/10/23</t>
+        </is>
+      </c>
+      <c r="K78" s="10" t="inlineStr">
+        <is>
+          <t>2027/01/08</t>
+        </is>
+      </c>
+      <c r="L78" s="10" t="inlineStr">
+        <is>
+          <t>2027/02/01</t>
+        </is>
+      </c>
+      <c r="M78" s="10" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N78" s="10" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O78" s="12" t="inlineStr">
+        <is>
+          <t>0M layout進行中,預計7/27 0M gerber out.</t>
+        </is>
+      </c>
+      <c r="P78" s="12" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>2655</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Crosshair 16 Max HX E4WEK</t>
+        </is>
+      </c>
+      <c r="D79" s="13" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F78" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5090</t>
-        </is>
-      </c>
-      <c r="G78" s="10" t="inlineStr">
-        <is>
-          <t>高宇奇</t>
-        </is>
-      </c>
-      <c r="H78" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="I78" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/14</t>
-        </is>
-      </c>
-      <c r="J78" s="10" t="inlineStr">
-        <is>
-          <t>2026/10/23</t>
-        </is>
-      </c>
-      <c r="K78" s="10" t="inlineStr">
-        <is>
-          <t>2027/01/08</t>
-        </is>
-      </c>
-      <c r="L78" s="10" t="inlineStr">
-        <is>
-          <t>2027/02/01</t>
-        </is>
-      </c>
-      <c r="M78" s="10" t="inlineStr">
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>鮑佩佩</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="L79" s="4" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M79" s="4" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N78" s="10" t="inlineStr">
+      <c r="N79" s="4" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O78" s="12" t="inlineStr">
-        <is>
-          <t>0M layout進行中,預計7/27 0M gerber out.</t>
-        </is>
-      </c>
-      <c r="P78" s="12" t="inlineStr"/>
-    </row>
-    <row r="79" hidden="1" outlineLevel="1">
-      <c r="A79" s="8" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="9" t="inlineStr">
-        <is>
-          <t>1851</t>
-        </is>
-      </c>
-      <c r="C79" s="10" t="inlineStr">
-        <is>
-          <t>Raider 18 Max HX B4WH</t>
-        </is>
-      </c>
-      <c r="D79" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E79" s="10" t="inlineStr">
-        <is>
-          <t>NVL-HX 65W</t>
-        </is>
-      </c>
-      <c r="F79" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5070Ti</t>
-        </is>
-      </c>
-      <c r="G79" s="10" t="inlineStr">
-        <is>
-          <t>高宇奇</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr">
-        <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="I79" s="10" t="inlineStr">
-        <is>
-          <t>2026/08/14</t>
-        </is>
-      </c>
-      <c r="J79" s="10" t="inlineStr">
-        <is>
-          <t>2026/10/23</t>
-        </is>
-      </c>
-      <c r="K79" s="10" t="inlineStr">
-        <is>
-          <t>2027/01/08</t>
-        </is>
-      </c>
-      <c r="L79" s="10" t="inlineStr">
-        <is>
-          <t>2027/02/01</t>
-        </is>
-      </c>
-      <c r="M79" s="10" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N79" s="10" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O79" s="12" t="inlineStr">
-        <is>
-          <t>0M layout進行中,預計7/27 0M gerber out.</t>
-        </is>
-      </c>
-      <c r="P79" s="12" t="inlineStr"/>
+      <c r="O79" s="6" t="inlineStr">
+        <is>
+          <t>原预计7/27 DVT打板，其中一颗D03-636BA0C-N03最快27號進，打板delay一天，不影響后續schedule</t>
+        </is>
+      </c>
+      <c r="P79" s="6" t="inlineStr">
+        <is>
+          <t>1)Spec變更,2655 計畫升規為Raider 16,RD 評估中,為了達到 Raider 等級的效能，由雙風扇升級為三風扇(3F5P)，現有的 DVT 樣品（8mm 風扇）無法用於驗證 230W/200W 的效能目標，必須重新製作手工樣品（10mm 散熱模組），影響Schedule TBD,預計下週會更新，同步重新 review 板端空間及高度干涉問題</t>
+        </is>
+      </c>
     </row>
     <row r="80" hidden="1" outlineLevel="1">
       <c r="A80" s="8" t="n">
@@ -6608,57 +6626,57 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Raider 18 Max HX B4WI</t>
-        </is>
-      </c>
-      <c r="D80" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
+          <t>Crosshair 16 Max HX E4WFK</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>NVL-HX 65W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>高宇奇</t>
+          <t>鮑佩佩</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr">
         <is>
-          <t>2026/08/14</t>
+          <t>2026/07/27</t>
         </is>
       </c>
       <c r="J80" s="10" t="inlineStr">
         <is>
-          <t>2026/10/23</t>
+          <t>2026/09/29</t>
         </is>
       </c>
       <c r="K80" s="10" t="inlineStr">
         <is>
-          <t>2027/01/08</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="L80" s="10" t="inlineStr">
         <is>
-          <t>2027/02/01</t>
+          <t>2027/02/02</t>
         </is>
       </c>
       <c r="M80" s="10" t="inlineStr">
@@ -6673,10 +6691,14 @@
       </c>
       <c r="O80" s="12" t="inlineStr">
         <is>
-          <t>0M layout進行中,預計7/27 0M gerber out.</t>
-        </is>
-      </c>
-      <c r="P80" s="12" t="inlineStr"/>
+          <t>原预计7/27 DVT打板，其中一颗D03-636BA0C-N03最快27號進，打板delay一天，不影響后續schedule</t>
+        </is>
+      </c>
+      <c r="P80" s="12" t="inlineStr">
+        <is>
+          <t>1)Spec變更,2655 計畫升規為Raider 16,RD 評估中,為了達到 Raider 等級的效能，由雙風扇升級為三風扇(3F5P)，現有的 DVT 樣品（8mm 風扇）無法用於驗證 230W/200W 的效能目標，必須重新製作手工樣品（10mm 散熱模組），影響Schedule TBD,預計下週會更新，同步重新 review 板端空間及高度干涉問題</t>
+        </is>
+      </c>
     </row>
     <row r="81" hidden="1" outlineLevel="1">
       <c r="A81" s="8" t="n">
@@ -6684,57 +6706,57 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Raider 18 Max HX B4WJ</t>
-        </is>
-      </c>
-      <c r="D81" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
+          <t>Crosshair 16 Max HX E4WGK</t>
+        </is>
+      </c>
+      <c r="D81" s="14" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E81" s="10" t="inlineStr">
         <is>
-          <t>NVL-HX 65W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>高宇奇</t>
+          <t>鮑佩佩</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="I81" s="10" t="inlineStr">
         <is>
-          <t>2026/08/14</t>
+          <t>2026/07/27</t>
         </is>
       </c>
       <c r="J81" s="10" t="inlineStr">
         <is>
-          <t>2026/10/23</t>
+          <t>2026/09/29</t>
         </is>
       </c>
       <c r="K81" s="10" t="inlineStr">
         <is>
-          <t>2027/01/08</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="L81" s="10" t="inlineStr">
         <is>
-          <t>2027/02/01</t>
+          <t>2027/02/02</t>
         </is>
       </c>
       <c r="M81" s="10" t="inlineStr">
@@ -6749,333 +6771,97 @@
       </c>
       <c r="O81" s="12" t="inlineStr">
         <is>
-          <t>0M layout進行中,預計7/27 0M gerber out.</t>
-        </is>
-      </c>
-      <c r="P81" s="12" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
+          <t>原预计7/27 DVT打板，其中一颗D03-636BA0C-N03最快27號進，打板delay一天，不影響后續schedule</t>
+        </is>
+      </c>
+      <c r="P81" s="12" t="inlineStr">
+        <is>
+          <t>1)Spec變更,2655 計畫升規為Raider 16,RD 評估中,為了達到 Raider 等級的效能，由雙風扇升級為三風扇(3F5P)，現有的 DVT 樣品（8mm 風扇）無法用於驗證 230W/200W 的效能目標，必須重新製作手工樣品（10mm 散熱模組），影響Schedule TBD,預計下週會更新，同步重新 review 板端空間及高度干涉問題</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" hidden="1" outlineLevel="1">
+      <c r="A82" s="8" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B82" s="9" t="inlineStr">
         <is>
           <t>2655</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WEK</t>
-        </is>
-      </c>
-      <c r="D82" s="13" t="inlineStr">
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>Crosshair 16 Max HX E4WGXK</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
+      <c r="E82" s="10" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G82" s="4" t="inlineStr">
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G82" s="10" t="inlineStr">
         <is>
           <t>鮑佩佩</t>
         </is>
       </c>
-      <c r="H82" s="4" t="inlineStr">
+      <c r="H82" s="10" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I82" s="4" t="inlineStr">
+      <c r="I82" s="10" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J82" s="4" t="inlineStr">
+      <c r="J82" s="10" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K82" s="4" t="inlineStr">
+      <c r="K82" s="10" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L82" s="4" t="inlineStr">
+      <c r="L82" s="10" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M82" s="4" t="inlineStr">
+      <c r="M82" s="10" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N82" s="4" t="inlineStr">
+      <c r="N82" s="10" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O82" s="6" t="inlineStr">
-        <is>
-          <t>0A 7/3 gerber out.plan 7/27 DVT SMT1，Ti usb repeater BW9871缺料待pull in 交期</t>
-        </is>
-      </c>
-      <c r="P82" s="6" t="inlineStr">
+      <c r="O82" s="12" t="inlineStr">
+        <is>
+          <t>原预计7/27 DVT打板，其中一颗D03-636BA0C-N03最快27號進，打板delay一天，不影響后續schedule</t>
+        </is>
+      </c>
+      <c r="P82" s="12" t="inlineStr">
         <is>
           <t>1)Spec變更,2655 計畫升規為Raider 16,RD 評估中,為了達到 Raider 等級的效能，由雙風扇升級為三風扇(3F5P)，現有的 DVT 樣品（8mm 風扇）無法用於驗證 230W/200W 的效能目標，必須重新製作手工樣品（10mm 散熱模組），影響Schedule TBD,預計下週會更新，同步重新 review 板端空間及高度干涉問題</t>
         </is>
       </c>
     </row>
-    <row r="83" hidden="1" outlineLevel="1">
-      <c r="A83" s="8" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" s="9" t="inlineStr">
-        <is>
-          <t>2655</t>
-        </is>
-      </c>
-      <c r="C83" s="10" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WFK</t>
-        </is>
-      </c>
-      <c r="D83" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E83" s="10" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F83" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G83" s="10" t="inlineStr">
-        <is>
-          <t>鮑佩佩</t>
-        </is>
-      </c>
-      <c r="H83" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I83" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J83" s="10" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K83" s="10" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L83" s="10" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M83" s="10" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N83" s="10" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O83" s="12" t="inlineStr">
-        <is>
-          <t>0A 7/3 gerber out.plan 7/27 DVT SMT1，Ti usb repeater BW9871缺料待pull in 交期</t>
-        </is>
-      </c>
-      <c r="P83" s="12" t="inlineStr">
-        <is>
-          <t>1)Spec變更,2655 計畫升規為Raider 16,RD 評估中,為了達到 Raider 等級的效能，由雙風扇升級為三風扇(3F5P)，現有的 DVT 樣品（8mm 風扇）無法用於驗證 230W/200W 的效能目標，必須重新製作手工樣品（10mm 散熱模組），影響Schedule TBD,預計下週會更新，同步重新 review 板端空間及高度干涉問題</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" hidden="1" outlineLevel="1">
-      <c r="A84" s="8" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>2655</t>
-        </is>
-      </c>
-      <c r="C84" s="10" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WGK</t>
-        </is>
-      </c>
-      <c r="D84" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E84" s="10" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F84" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G84" s="10" t="inlineStr">
-        <is>
-          <t>鮑佩佩</t>
-        </is>
-      </c>
-      <c r="H84" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I84" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J84" s="10" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K84" s="10" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L84" s="10" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M84" s="10" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N84" s="10" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O84" s="12" t="inlineStr">
-        <is>
-          <t>0A 7/3 gerber out.plan 7/27 DVT SMT1，Ti usb repeater BW9871缺料待pull in 交期</t>
-        </is>
-      </c>
-      <c r="P84" s="12" t="inlineStr">
-        <is>
-          <t>1)Spec變更,2655 計畫升規為Raider 16,RD 評估中,為了達到 Raider 等級的效能，由雙風扇升級為三風扇(3F5P)，現有的 DVT 樣品（8mm 風扇）無法用於驗證 230W/200W 的效能目標，必須重新製作手工樣品（10mm 散熱模組），影響Schedule TBD,預計下週會更新，同步重新 review 板端空間及高度干涉問題</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" hidden="1" outlineLevel="1">
-      <c r="A85" s="8" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" s="9" t="inlineStr">
-        <is>
-          <t>2655</t>
-        </is>
-      </c>
-      <c r="C85" s="10" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WGXK</t>
-        </is>
-      </c>
-      <c r="D85" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E85" s="10" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F85" s="10" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G85" s="10" t="inlineStr">
-        <is>
-          <t>鮑佩佩</t>
-        </is>
-      </c>
-      <c r="H85" s="10" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I85" s="10" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J85" s="10" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K85" s="10" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L85" s="10" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M85" s="10" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N85" s="10" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O85" s="12" t="inlineStr">
-        <is>
-          <t>0A 7/3 gerber out.plan 7/27 DVT SMT1，Ti usb repeater BW9871缺料待pull in 交期</t>
-        </is>
-      </c>
-      <c r="P85" s="12" t="inlineStr">
-        <is>
-          <t>1)Spec變更,2655 計畫升規為Raider 16,RD 評估中,為了達到 Raider 等級的效能，由雙風扇升級為三風扇(3F5P)，現有的 DVT 樣品（8mm 風扇）無法用於驗證 230W/200W 的效能目標，必須重新製作手工樣品（10mm 散熱模組），影響Schedule TBD,預計下週會更新，同步重新 review 板端空間及高度干涉問題</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P85"/>
+  <autoFilter ref="A1:P82"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/npi_dashboard.xlsx
+++ b/npi_dashboard.xlsx
@@ -93,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -135,6 +135,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -670,12 +673,12 @@
       </c>
       <c r="O2" s="6" t="inlineStr">
         <is>
-          <t>（清日文4區RGB鍵盤庫存）DQA測試中,預計7/21完成</t>
+          <t>（清日文4區RGB鍵盤庫存)</t>
         </is>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
-          <t>1)DQA驗證有Audio問題, WHQL驅動預計7/24提供,需要Preload和DQA等單位加班驗證,滿足業務7/30出貨需求</t>
+          <t>1)方向鍵上的快捷鍵無功能, EC和BIOS需要進版, 請DQA協助快掃測試</t>
         </is>
       </c>
     </row>
@@ -742,12 +745,12 @@
       </c>
       <c r="O3" s="11" t="inlineStr">
         <is>
-          <t>（清白光鍵盤庫存）DQA測試中,預計7/20完成</t>
+          <t>（清白光鍵盤庫存）ATS C/R驗證中</t>
         </is>
       </c>
       <c r="P3" s="11" t="inlineStr">
         <is>
-          <t>1)DQA驗證有Audio問題, WHQL驅動預計7/24提供,需要Preload和DQA等單位加班驗證</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -814,9 +817,7 @@
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>DQA test中,
-1) ME: 搖擺測試pass
-2）Function：待新版MSI Center AP release( 包入MKT name支援AI Noise Cancellation Pro), 安排HDI製作</t>
+          <t>DQA MP HDI測試進行中, 暫無量產工單產生</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
@@ -878,19 +879,17 @@
       </c>
       <c r="M5" s="9" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/07</t>
         </is>
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>2026/08/07</t>
+          <t>2026/08/12</t>
         </is>
       </c>
       <c r="O5" s="11" t="inlineStr">
         <is>
-          <t>DQA test中,
-1) ME: 搖擺測試pass
-2）Function：最新版MSI Center AP聯網會支援noise Cancellation Pro, 待安排HDI製作</t>
+          <t>ATS C/R工單： 9S7-15Q373-1258* 50 pcs 預排8/7 ASSY</t>
         </is>
       </c>
       <c r="P5" s="11" t="inlineStr">
@@ -962,9 +961,7 @@
       </c>
       <c r="O6" s="6" t="inlineStr">
         <is>
-          <t>DQA test中,
-1) ME: 搖擺測試pass
-2）Function：待新版MSI Center AP release( 包入MKT name支援AI Noise Cancellation Pro), 安排HDI製作</t>
+          <t>DQA MP HDI測試進行中, 暫無量產工單產生</t>
         </is>
       </c>
       <c r="P6" s="6" t="inlineStr">
@@ -1026,19 +1023,17 @@
       </c>
       <c r="M7" s="9" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/07</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>2026/08/07</t>
+          <t>2026/08/12</t>
         </is>
       </c>
       <c r="O7" s="11" t="inlineStr">
         <is>
-          <t>DQA test中,
-1) ME: 搖擺測試pass
-2）Function：待新版MSI Center AP release( 包入MKT name支援AI Noise Cancellation Pro), 安排HDI製作</t>
+          <t>ATS C/R工單： 9S7-17U344-449 * 50 pcs 預排8/7 ASSY</t>
         </is>
       </c>
       <c r="P7" s="11" t="inlineStr">
@@ -1100,19 +1095,17 @@
       </c>
       <c r="M8" s="9" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/08</t>
         </is>
       </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
-          <t>2026/08/07</t>
+          <t>2026/08/12</t>
         </is>
       </c>
       <c r="O8" s="11" t="inlineStr">
         <is>
-          <t>DQA test中,
-1) ME: 搖擺測試pass
-2）Function：待新版MSI Center AP release( 包入MKT name支援AI Noise Cancellation Pro), 安排HDI製作</t>
+          <t>9S7-17U344-441 * 300pcs ASSY @ 8/8</t>
         </is>
       </c>
       <c r="P8" s="11" t="inlineStr">
@@ -1135,9 +1128,9 @@
           <t>Venture 15 AI+ B3M</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>DVT</t>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>MVT</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1188,12 +1181,13 @@
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>MVT2 組裝@7/27</t>
+          <t>MVT2驗證中</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>1) ATS與MP的物料簽樣與備料,需要RD與採購和物管協助</t>
+          <t>1) ATS與MP的物料簽樣與備料,需要RD與採購和物管協助
+2)A件交期依森田薄膜進料時間,15T2 ATS組裝在8/20, MP在8/30, 會比原時程晚2天,會導致15T2無法meet 8/27 MP的目標,需要RD/採購協助pull in</t>
         </is>
       </c>
     </row>
@@ -1269,8 +1263,7 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>(
-1) ATS與MP的物料簽樣與備料,需要RD與採購和物管協助</t>
+          <t>1).Materiel: #A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/E MP的目標,麻煩RD/採購pull in森田薄膜進料時間. #因7/28需量產備料四區鍵盤,如果還有鍵盤相關問題,請儘速提出</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1339,7 @@
       </c>
       <c r="P11" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1).Materiel: #A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/E MP的目標,麻煩RD/採購pull in森田薄膜進料時間. #因7/28需量產備料四區鍵盤,如果還有鍵盤相關問題,請儘速提出</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1415,7 @@
       </c>
       <c r="P12" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1).Materiel: #A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/E MP的目標,麻煩RD/採購pull in森田薄膜進料時間. #因7/28需量產備料四區鍵盤,如果還有鍵盤相關問題,請儘速提出</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1486,13 @@
       </c>
       <c r="O13" s="11" t="inlineStr">
         <is>
-          <t>DDR4 sku, 7/24 MVT SMT, 預計7/27試組, 7/29組裝</t>
+          <t>DDR4 sku,MVT組裝中,預計8/4拿到機器開始測試,8/7 PCB risk buy</t>
         </is>
       </c>
       <c r="P13" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) ATS與MP的物料簽樣與備料,需要RD與採購和物管協助
+2)A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/30 MP的目標,需要RD/採購協助助pull in</t>
         </is>
       </c>
     </row>
@@ -1569,12 +1563,13 @@
       </c>
       <c r="O14" s="11" t="inlineStr">
         <is>
-          <t>DDR4 sku, 7/24 MVT SMT, 預計7/27試組, 7/29組裝</t>
+          <t>DDR4 sku,MVT組裝中,預計8/4拿到機器開始測試,8/7 PCB risk buy</t>
         </is>
       </c>
       <c r="P14" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) ATS與MP的物料簽樣與備料,需要RD與採購和物管協助
+2)A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/30 MP的目標,需要RD/採購協助助pull in</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1640,12 @@
       </c>
       <c r="O15" s="11" t="inlineStr">
         <is>
-          <t>DDR4 sku, 7/24 MVT SMT, 預計7/27試組, 7/29組裝</t>
+          <t>DDR4 sku,MVT組裝中,預計8/4拿到機器開始測試,8/7 PCB risk buy</t>
         </is>
       </c>
       <c r="P15" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1).Materiel: #A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/E MP的目標,麻煩RD/採購pull in森田薄膜進料時間.</t>
         </is>
       </c>
     </row>
@@ -1729,6 +1724,89 @@
         </is>
       </c>
       <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>1)Battery life: 2.8K panel+day0 rev.B+balance mode測試，Web browersing測試達716min，接近過關。NV更新會導入部分省電作法於Rev. C，待更新SW後驗證。
+2)NV Abnormal shut down 的solution，經DQA於BSP Day0 rev.B驗證後，未發生除error code "0x7E"外的ABS現象，後續會持續觀察。
+3) Day0 rev.C BIOS 7/29 release，測試image預計7/30 release，工廠/DQA將同時切換測試。
+4)工廠用MP樣品測試，反應主要問題，需RD一起分析 1.Long run自動測試 S3/S4/S5/ Reboot/ FSU進系統在login 画面持续转圈宕機，黑屏無顯 ,宕機 2. LCD 花屏（panel 有黑線) 3. camera 開啟錄像后 camera APP 卡住</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" hidden="1" outlineLevel="1">
+      <c r="A17" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>2621</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Prestige N16 Flip AI+ C1XMT</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>N1x 80W</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>林晉弘</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>2024/11/25</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>2025/01/20</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>2025/06/25</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>2026/03/12</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="M17" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="N17" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="O17" s="11" t="inlineStr">
+        <is>
+          <t>MVT測試中</t>
+        </is>
+      </c>
+      <c r="P17" s="11" t="inlineStr">
         <is>
           <t>1)Battery life: 以2.8K panel+day0 rev.A環境用balance mode測試，Modern standby可達標準，Web browersing尚差0.2Hr，將於BSP Day0 rev.B再進行驗證。
 2)NV Abnormal shut down 的solution，確認需於BSP Day0 rev.B驗證，預計7/23 image完成後，DQA/工廠會同時切換驗證確認。
@@ -1737,89 +1815,6 @@
         </is>
       </c>
     </row>
-    <row r="17" hidden="1" outlineLevel="1">
-      <c r="A17" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>2621</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Prestige N16 Flip AI+ C1XMT</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>N1x 80W</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>林晉弘</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>2024/11/25</t>
-        </is>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>2025/01/20</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/25</t>
-        </is>
-      </c>
-      <c r="K17" s="9" t="inlineStr">
-        <is>
-          <t>2026/03/12</t>
-        </is>
-      </c>
-      <c r="L17" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/30</t>
-        </is>
-      </c>
-      <c r="M17" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/17</t>
-        </is>
-      </c>
-      <c r="N17" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/31</t>
-        </is>
-      </c>
-      <c r="O17" s="11" t="inlineStr">
-        <is>
-          <t>MVT測試中</t>
-        </is>
-      </c>
-      <c r="P17" s="11" t="inlineStr">
-        <is>
-          <t>1)Battery life: 以2.8K panel+day0 rev.A環境用balance mode測試，Modern standby可達標準，Web browersing尚差0.2Hr，將於BSP Day0 rev.B再進行驗證。
-2)NV Abnormal shut down 的solution，確認需於BSP Day0 rev.B驗證，預計7/23 image完成後，DQA/工廠會同時切換驗證確認。
-3)NV更新可for出貨的 GPU driver提前於8/3美國時間release，後須計畫以此版本進行測試並出貨，不影響現行Schedule，ATS仍定於8/17開始
-4)for NV/MSFT 113pcs樣品，已於7/17 SMT，7/22 ASS'Y，並通知業務轉單，預計下周可出貨</t>
-        </is>
-      </c>
-    </row>
     <row r="18">
       <c r="A18" s="2" t="n">
         <v>17</v>
@@ -1834,9 +1829,9 @@
           <t>Modern 14 LE J3M</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>DVT</t>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>MVT</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1887,13 +1882,14 @@
       </c>
       <c r="O18" s="6" t="inlineStr">
         <is>
-          <t>MSIK: DQA test中; Weibu: plan MVT 7/29 SMT, 確認料況中</t>
+          <t>Weibu: MVT 7/30 ASSY中</t>
         </is>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
           <t>1)認證：8/E ready可出貨地區:  DE/UK/TR/BNX/NEU/SEE/FR/ES/PL/CZ/CIS/IT/JP/AU
-2）認證 8/E無法同步ready地區:  9/8 ready: LA/CA/ AR/CL  9/18 ready: UA 10/2 ready: CO/RU 12/18 ready: MX</t>
+2）認證 8/E無法同步ready地區:  9/8 ready: LA/CA/ AR/CL  9/18 ready: UA 10/2 ready: CO/RU 12/18 ready: MX
+2）備料: 日文鍵芯開放時程待追蹤</t>
         </is>
       </c>
     </row>
@@ -1911,9 +1907,9 @@
           <t>Modern 16 LE J3M</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>DVT</t>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>MVT</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1964,7 +1960,7 @@
       </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
-          <t>MSIK: DQA test中; Weibu: plan MVT 7/29 SMT, 確認料況中</t>
+          <t>Weibu: 7/30 MVT ASSY</t>
         </is>
       </c>
       <c r="P19" s="6" t="inlineStr">
@@ -2333,7 +2329,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/13</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -2353,13 +2349,13 @@
       </c>
       <c r="O24" s="6" t="inlineStr">
         <is>
-          <t>MVT SMT@8/3--depend on Material ready date作調整</t>
+          <t>MVT SMT@8/13--depend on PS chip &amp; Software時間作調整</t>
         </is>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>1) Schedule: a.MVT D件備料ready日期@7/29 b. CPU交期還未放行, 先預估8/B交期
-3)備料：量產交料HQ23, 最新交期回復在12月份（follow leading customer）交料, 還在持續追蹤中</t>
+          <t>1) Schedule:  本週CPU交期還未放行, 綜合PS software時間, 先預抓8/13 MVT start.
+2)備料：量產交料2.8k HQ23, 最新MP*1K交期回復在12/M（follow leading customer）交料, 與ATS start Gap 2個月, 採購協助push廠商交期中</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2410,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/13</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -2434,8 +2430,7 @@
       </c>
       <c r="O25" s="6" t="inlineStr">
         <is>
-          <t>1)EVT 更新BSP6.2.1  持續驗證中,ID定案 顏色keep 淺灰+ D side 咬花
-3) N1 SoC 出貨延遲 MVT 預計延到8/3 SMT, 8/4 Pre-Assy ,8/6 Assy</t>
+          <t>N1 SoC 出貨延遲 MVT 預計延到8/13 SMT</t>
         </is>
       </c>
       <c r="P25" s="6" t="inlineStr">
@@ -2458,9 +2453,9 @@
           <t>Katana 18 HX A14WEK</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>DVT</t>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>EVT</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -2490,7 +2485,7 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>2026/08/24</t>
+          <t>2026/08/12</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -2515,7 +2510,7 @@
       </c>
       <c r="O26" s="6" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖, SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
+          <t>RPL-HX R + DDR5: 7/28 0B出圖, SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
@@ -2538,9 +2533,9 @@
           <t>Katana 18 HX A14WFK</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>DVT</t>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>EVT</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -2570,7 +2565,7 @@
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>2026/08/24</t>
+          <t>2026/08/12</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr">
@@ -2595,7 +2590,7 @@
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖, SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
+          <t>RPL-HX R + DDR5: 7/28 0B出圖, SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
         </is>
       </c>
       <c r="P27" s="11" t="inlineStr">
@@ -2618,9 +2613,9 @@
           <t>Katana 18 HX A14WGK</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
-          <t>DVT</t>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>EVT</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -2650,7 +2645,7 @@
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>2026/08/24</t>
+          <t>2026/08/12</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr">
@@ -2675,7 +2670,7 @@
       </c>
       <c r="O28" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖, SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
+          <t>RPL-HX R + DDR5: 7/28 0B出圖, SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
         </is>
       </c>
       <c r="P28" s="11" t="inlineStr">
@@ -3230,9 +3225,9 @@
           <t>Crosshair 18 Max HX B14WE</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
-        <is>
-          <t>DVT</t>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>EVT</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -3262,7 +3257,7 @@
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>2026/08/24</t>
+          <t>2026/08/12</t>
         </is>
       </c>
       <c r="K36" s="9" t="inlineStr">
@@ -3287,7 +3282,7 @@
       </c>
       <c r="O36" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖, SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
+          <t>RPL-HX R + DDR5: 7/28 0B出圖, SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
         </is>
       </c>
       <c r="P36" s="11" t="inlineStr">
@@ -3310,9 +3305,9 @@
           <t>Crosshair 18 Max HX B14WF</t>
         </is>
       </c>
-      <c r="D37" s="13" t="inlineStr">
-        <is>
-          <t>DVT</t>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>EVT</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -3342,7 +3337,7 @@
       </c>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>2026/08/24</t>
+          <t>2026/08/12</t>
         </is>
       </c>
       <c r="K37" s="9" t="inlineStr">
@@ -3367,7 +3362,7 @@
       </c>
       <c r="O37" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖, SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
+          <t>RPL-HX R + DDR5: 7/28 0B出圖, SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
         </is>
       </c>
       <c r="P37" s="11" t="inlineStr">
@@ -3390,9 +3385,9 @@
           <t>Crosshair 18 Max HX B14WG</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
-        <is>
-          <t>DVT</t>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>EVT</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -3422,7 +3417,7 @@
       </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>2026/08/24</t>
+          <t>2026/08/12</t>
         </is>
       </c>
       <c r="K38" s="9" t="inlineStr">
@@ -3447,7 +3442,7 @@
       </c>
       <c r="O38" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖, SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
+          <t>RPL-HX R + DDR5: 7/28 0B出圖, SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
         </is>
       </c>
       <c r="P38" s="11" t="inlineStr">
@@ -3470,9 +3465,9 @@
           <t>Crosshair 18 Max HX B14WGX</t>
         </is>
       </c>
-      <c r="D39" s="13" t="inlineStr">
-        <is>
-          <t>DVT</t>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>EVT</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -3502,7 +3497,7 @@
       </c>
       <c r="J39" s="9" t="inlineStr">
         <is>
-          <t>2026/08/24</t>
+          <t>2026/08/12</t>
         </is>
       </c>
       <c r="K39" s="9" t="inlineStr">
@@ -3527,7 +3522,7 @@
       </c>
       <c r="O39" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: DVT 測試中,預計7/28 0B出圖, SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
+          <t>RPL-HX R + DDR5: 7/28 0B出圖, SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
         </is>
       </c>
       <c r="P39" s="11" t="inlineStr">
@@ -3550,7 +3545,7 @@
           <t>Crosshair 18 Max HX B2WE</t>
         </is>
       </c>
-      <c r="D40" s="15" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -3622,7 +3617,7 @@
           <t>Crosshair 18 Max HX B2WEO</t>
         </is>
       </c>
-      <c r="D41" s="15" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -3694,7 +3689,7 @@
           <t>Crosshair 18 Max HX B2WF</t>
         </is>
       </c>
-      <c r="D42" s="15" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -3766,7 +3761,7 @@
           <t>Crosshair 18 Max HX B2WFO</t>
         </is>
       </c>
-      <c r="D43" s="15" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -3838,7 +3833,7 @@
           <t>Crosshair 18 Max HX B2WG</t>
         </is>
       </c>
-      <c r="D44" s="15" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -3910,7 +3905,7 @@
           <t>Crosshair 18 Max HX B2WGO</t>
         </is>
       </c>
-      <c r="D45" s="15" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -3982,7 +3977,7 @@
           <t>Crosshair 18 Max HX B2WGX</t>
         </is>
       </c>
-      <c r="D46" s="15" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4054,7 +4049,7 @@
           <t>Crosshair 18 Max HX B2WGXO</t>
         </is>
       </c>
-      <c r="D47" s="15" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4126,7 +4121,7 @@
           <t>Katana 18 HX A2WEK</t>
         </is>
       </c>
-      <c r="D48" s="15" t="inlineStr">
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4198,7 +4193,7 @@
           <t>Katana 18 HX A2WEOK</t>
         </is>
       </c>
-      <c r="D49" s="15" t="inlineStr">
+      <c r="D49" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4274,7 +4269,7 @@
           <t>Katana 18 HX A2WFK</t>
         </is>
       </c>
-      <c r="D50" s="15" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4346,7 +4341,7 @@
           <t>Katana 18 HX A2WFOK</t>
         </is>
       </c>
-      <c r="D51" s="15" t="inlineStr">
+      <c r="D51" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4422,7 +4417,7 @@
           <t>Katana 18 HX A2WGK</t>
         </is>
       </c>
-      <c r="D52" s="15" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4494,7 +4489,7 @@
           <t>Katana 18 HX A2WGOK</t>
         </is>
       </c>
-      <c r="D53" s="15" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4627,7 +4622,7 @@
       </c>
       <c r="O54" s="6" t="inlineStr">
         <is>
-          <t>DVT SMT@7/27</t>
+          <t>DVT 開機OK， RD test :8/4~8/31</t>
         </is>
       </c>
       <c r="P54" s="6" t="inlineStr">
@@ -4707,7 +4702,7 @@
       </c>
       <c r="O55" s="11" t="inlineStr">
         <is>
-          <t>DVT SMT@7/27</t>
+          <t>DVT 開機OK， RD test :8/4~8/31</t>
         </is>
       </c>
       <c r="P55" s="11" t="inlineStr">
@@ -4783,7 +4778,7 @@
       </c>
       <c r="O56" s="6" t="inlineStr">
         <is>
-          <t>DVT SMT@7/27</t>
+          <t>DVT 開機OK， RD test :8/4~8/31</t>
         </is>
       </c>
       <c r="P56" s="6" t="inlineStr">
@@ -4859,7 +4854,7 @@
       </c>
       <c r="O57" s="11" t="inlineStr">
         <is>
-          <t>DVT SMT@7/27</t>
+          <t>DVT 開機OK， RD test :8/4~8/31</t>
         </is>
       </c>
       <c r="P57" s="11" t="inlineStr">
@@ -4882,7 +4877,7 @@
           <t>Prestige 13 AI+ A4M</t>
         </is>
       </c>
-      <c r="D58" s="16" t="inlineStr">
+      <c r="D58" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4944,7 +4939,7 @@
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
-          <t>Audio Codec由原來的Reltek更換為TI，線路設計，placement變更</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5014,7 @@
       </c>
       <c r="O59" s="6" t="inlineStr">
         <is>
-          <t>產線排程 DVT SMT@7/23</t>
+          <t>DVT SMT@7/23, RD 開機中</t>
         </is>
       </c>
       <c r="P59" s="6" t="inlineStr">
@@ -5100,7 +5095,7 @@
       </c>
       <c r="O60" s="11" t="inlineStr">
         <is>
-          <t>產線排程 DVT SMT@7/23</t>
+          <t>DVT SMT@7/23, RD 開機中</t>
         </is>
       </c>
       <c r="P60" s="11" t="inlineStr">
@@ -5180,7 +5175,7 @@
       </c>
       <c r="O61" s="11" t="inlineStr">
         <is>
-          <t>產線排程 DVT SMT@7/23</t>
+          <t>DVT SMT@7/23, RD 開機中</t>
         </is>
       </c>
       <c r="P61" s="11" t="inlineStr">
@@ -5203,7 +5198,7 @@
           <t>Stealth 16 AI+ B4WE</t>
         </is>
       </c>
-      <c r="D62" s="16" t="inlineStr">
+      <c r="D62" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5230,7 +5225,7 @@
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>2026/07/30</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
@@ -5260,7 +5255,7 @@
       </c>
       <c r="O62" s="6" t="inlineStr">
         <is>
-          <t>0A 7/15 gerber out</t>
+          <t>0A 7/31 SMT</t>
         </is>
       </c>
       <c r="P62" s="6" t="inlineStr">
@@ -5284,7 +5279,7 @@
           <t>Stealth 16 AI+ B4WF</t>
         </is>
       </c>
-      <c r="D63" s="15" t="inlineStr">
+      <c r="D63" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5311,7 +5306,7 @@
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
-          <t>2026/07/30</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="J63" s="9" t="inlineStr">
@@ -5341,7 +5336,7 @@
       </c>
       <c r="O63" s="11" t="inlineStr">
         <is>
-          <t>0A 7/15 gerber out</t>
+          <t>0A 7/31 SMT</t>
         </is>
       </c>
       <c r="P63" s="11" t="inlineStr">
@@ -5365,7 +5360,7 @@
           <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
         </is>
       </c>
-      <c r="D64" s="15" t="inlineStr">
+      <c r="D64" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5392,7 +5387,7 @@
       </c>
       <c r="I64" s="9" t="inlineStr">
         <is>
-          <t>2026/07/30</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="J64" s="9" t="inlineStr">
@@ -5422,7 +5417,7 @@
       </c>
       <c r="O64" s="11" t="inlineStr">
         <is>
-          <t>0A 7/15 gerber out</t>
+          <t>0A 7/31 SMT</t>
         </is>
       </c>
       <c r="P64" s="11" t="inlineStr">
@@ -5446,7 +5441,7 @@
           <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
         </is>
       </c>
-      <c r="D65" s="15" t="inlineStr">
+      <c r="D65" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5473,7 +5468,7 @@
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
-          <t>2026/07/30</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="J65" s="9" t="inlineStr">
@@ -5503,7 +5498,7 @@
       </c>
       <c r="O65" s="11" t="inlineStr">
         <is>
-          <t>0A 7/15 gerber out</t>
+          <t>0A 7/31 SMT</t>
         </is>
       </c>
       <c r="P65" s="11" t="inlineStr">
@@ -5527,7 +5522,7 @@
           <t>Raider 16 HX B14WI</t>
         </is>
       </c>
-      <c r="D66" s="16" t="inlineStr">
+      <c r="D66" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5604,10 +5599,10 @@
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Raider 16 HX B14WH</t>
-        </is>
-      </c>
-      <c r="D67" s="15" t="inlineStr">
+          <t>Raider 16 HX B14WJ</t>
+        </is>
+      </c>
+      <c r="D67" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5619,7 +5614,7 @@
       </c>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="G67" s="9" t="inlineStr">
@@ -5664,10 +5659,14 @@
       </c>
       <c r="O67" s="11" t="inlineStr">
         <is>
-          <t>leverage Raider 16 HX B14WJ</t>
-        </is>
-      </c>
-      <c r="P67" s="11" t="inlineStr"/>
+          <t>7/24 Kick off，預計0M gerberout 8/28</t>
+        </is>
+      </c>
+      <c r="P67" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="68" hidden="1" outlineLevel="1">
       <c r="A68" s="7" t="n">
@@ -5680,10 +5679,10 @@
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Raider 16 HX B14WJ</t>
-        </is>
-      </c>
-      <c r="D68" s="15" t="inlineStr">
+          <t>Raider 16 HX B14WH</t>
+        </is>
+      </c>
+      <c r="D68" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5695,7 +5694,7 @@
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="G68" s="9" t="inlineStr">
@@ -5740,7 +5739,7 @@
       </c>
       <c r="O68" s="11" t="inlineStr">
         <is>
-          <t>7/24 Kick off，預計0A gerberout 8/28</t>
+          <t>leverage Raider 16 HX B14WJ</t>
         </is>
       </c>
       <c r="P68" s="11" t="inlineStr"/>
@@ -5786,7 +5785,7 @@
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -5816,7 +5815,7 @@
       </c>
       <c r="O69" s="6" t="inlineStr">
         <is>
-          <t>预计8/3 DVT打板</t>
+          <t>预计8/5 DVT打板</t>
         </is>
       </c>
       <c r="P69" s="6" t="inlineStr">
@@ -5866,7 +5865,7 @@
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="J70" s="9" t="inlineStr">
@@ -5896,7 +5895,7 @@
       </c>
       <c r="O70" s="11" t="inlineStr">
         <is>
-          <t>预计8/3 DVT打板</t>
+          <t>预计8/5 DVT打板</t>
         </is>
       </c>
       <c r="P70" s="11" t="inlineStr">
@@ -5946,7 +5945,7 @@
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="J71" s="9" t="inlineStr">
@@ -5976,7 +5975,7 @@
       </c>
       <c r="O71" s="11" t="inlineStr">
         <is>
-          <t>预计8/3 DVT打板</t>
+          <t>预计8/5 DVT打板</t>
         </is>
       </c>
       <c r="P71" s="11" t="inlineStr">
@@ -6026,7 +6025,7 @@
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
@@ -6056,12 +6055,12 @@
       </c>
       <c r="O72" s="6" t="inlineStr">
         <is>
-          <t>8/3 DVT SMT(H&amp;HX同步打板驗證)</t>
+          <t>8/6  DVT SMT</t>
         </is>
       </c>
       <c r="P72" s="6" t="inlineStr">
         <is>
-          <t>Spec變更:由crosshair max正式改Raider系列,對應thermal 手工樣品需重新打樣, RD 確認預計8/17收到樣品開始測試，比原計劃delay1周，雖不影響TTM，但期望RD 持續push廠商，keep原schedule不變,否則可能會影響到後續規劃的特仕版送樣時間,持續tracking</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6105,7 @@
       </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="J73" s="9" t="inlineStr">
@@ -6136,12 +6135,12 @@
       </c>
       <c r="O73" s="11" t="inlineStr">
         <is>
-          <t>8/3 DVT SMT(H&amp;HX同步打板驗證)</t>
+          <t>8/6  DVT SMT</t>
         </is>
       </c>
       <c r="P73" s="11" t="inlineStr">
         <is>
-          <t>Spec變更:由crosshair max正式改Raider系列,對應thermal 手工樣品需重新打樣, RD 確認預計8/17收到樣品開始測試，比原計劃delay1周，雖不影響TTM，但期望RD 持續push廠商，keep原schedule不變,否則可能會影響到後續規劃的特仕版送樣時間,持續tracking</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6185,7 @@
       </c>
       <c r="I74" s="9" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="J74" s="9" t="inlineStr">
@@ -6216,12 +6215,12 @@
       </c>
       <c r="O74" s="11" t="inlineStr">
         <is>
-          <t>8/3 DVT SMT(H&amp;HX同步打板驗證)</t>
+          <t>8/6  DVT SMT</t>
         </is>
       </c>
       <c r="P74" s="11" t="inlineStr">
         <is>
-          <t>Spec變更:由crosshair max正式改Raider系列,對應thermal 手工樣品需重新打樣, RD 確認預計8/17收到樣品開始測試，比原計劃delay1周，雖不影響TTM，但期望RD 持續push廠商，keep原schedule不變,否則可能會影響到後續規劃的特仕版送樣時間,持續tracking</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6265,7 @@
       </c>
       <c r="I75" s="9" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="J75" s="9" t="inlineStr">
@@ -6296,12 +6295,12 @@
       </c>
       <c r="O75" s="11" t="inlineStr">
         <is>
-          <t>8/3 DVT SMT(H&amp;HX同步打板驗證)</t>
+          <t>8/6  DVT SMT</t>
         </is>
       </c>
       <c r="P75" s="11" t="inlineStr">
         <is>
-          <t>Spec變更:由crosshair max正式改Raider系列,對應thermal 手工樣品需重新打樣, RD 確認預計8/17收到樣品開始測試，比原計劃delay1周，雖不影響TTM，但期望RD 持續push廠商，keep原schedule不變,否則可能會影響到後續規劃的特仕版送樣時間,持續tracking</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -6319,7 +6318,7 @@
           <t>Titan 18 HX B4WH</t>
         </is>
       </c>
-      <c r="D76" s="16" t="inlineStr">
+      <c r="D76" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6381,7 +6380,8 @@
       </c>
       <c r="P76" s="6" t="inlineStr">
         <is>
-          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study.</t>
+          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.
+2) Seamless Haptic TP待Liteon提供final線路圖/2D3D/Spec for Lockdown確認.</t>
         </is>
       </c>
     </row>
@@ -6399,7 +6399,7 @@
           <t>Titan 18 HX B4WI</t>
         </is>
       </c>
-      <c r="D77" s="15" t="inlineStr">
+      <c r="D77" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6461,7 +6461,8 @@
       </c>
       <c r="P77" s="11" t="inlineStr">
         <is>
-          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study.</t>
+          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.
+2) Seamless Haptic TP待Liteon提供final線路圖/2D3D/Spec for Lockdown確認.</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6480,7 @@
           <t>Titan 18 HX B4WJ</t>
         </is>
       </c>
-      <c r="D78" s="15" t="inlineStr">
+      <c r="D78" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6541,7 +6542,8 @@
       </c>
       <c r="P78" s="11" t="inlineStr">
         <is>
-          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study.</t>
+          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.
+2) Seamless Haptic TP待Liteon提供final線路圖/2D3D/Spec for Lockdown確認.</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6561,7 @@
           <t>Raider 18 Max HX B4WH</t>
         </is>
       </c>
-      <c r="D79" s="15" t="inlineStr">
+      <c r="D79" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6621,7 +6623,7 @@
       </c>
       <c r="P79" s="11" t="inlineStr">
         <is>
-          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study.</t>
+          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6641,7 @@
           <t>Raider 18 Max HX B4WI</t>
         </is>
       </c>
-      <c r="D80" s="15" t="inlineStr">
+      <c r="D80" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6701,7 +6703,7 @@
       </c>
       <c r="P80" s="11" t="inlineStr">
         <is>
-          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study.</t>
+          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6721,7 @@
           <t>Raider 18 Max HX B4WJ</t>
         </is>
       </c>
-      <c r="D81" s="15" t="inlineStr">
+      <c r="D81" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6781,7 +6783,7 @@
       </c>
       <c r="P81" s="11" t="inlineStr">
         <is>
-          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study.</t>
+          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
         </is>
       </c>
     </row>

--- a/npi_dashboard.xlsx
+++ b/npi_dashboard.xlsx
@@ -1258,12 +1258,13 @@
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
-          <t>DDR5 sku, MVT測試中, 7/24調撥,預計7/30 PCB risk buy</t>
+          <t>DDR5 sku, MVT2 組裝中</t>
         </is>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>1).Materiel: #A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/E MP的目標,麻煩RD/採購pull in森田薄膜進料時間. #因7/28需量產備料四區鍵盤,如果還有鍵盤相關問題,請儘速提出</t>
+          <t>1) ATS與MP的物料簽樣與備料,需要RD與採購和物管協助
+2)A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/30 MP的目標,需要RD/採購協助助pull in</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1335,13 @@
       </c>
       <c r="O11" s="11" t="inlineStr">
         <is>
-          <t>DDR5 sku, MVT測試中, 7/24調撥,預計7/30 PCB risk buy</t>
+          <t>DDR5 sku, MVT2組裝中</t>
         </is>
       </c>
       <c r="P11" s="11" t="inlineStr">
         <is>
-          <t>1).Materiel: #A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/E MP的目標,麻煩RD/採購pull in森田薄膜進料時間. #因7/28需量產備料四區鍵盤,如果還有鍵盤相關問題,請儘速提出</t>
+          <t>1) ATS與MP的物料簽樣與備料,需要RD與採購和物管協助
+2)A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/30 MP的目標,需要RD/採購協助助pull in</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1412,13 @@
       </c>
       <c r="O12" s="11" t="inlineStr">
         <is>
-          <t>DDR5 sku, MVT測試中, 7/24調撥,預計7/30 PCB risk buy</t>
+          <t>DDR5 sku, MVT2組裝中</t>
         </is>
       </c>
       <c r="P12" s="11" t="inlineStr">
         <is>
-          <t>1).Materiel: #A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/E MP的目標,麻煩RD/採購pull in森田薄膜進料時間. #因7/28需量產備料四區鍵盤,如果還有鍵盤相關問題,請儘速提出</t>
+          <t>1) ATS與MP的物料簽樣與備料,需要RD與採購和物管協助
+2)A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/30 MP的目標,需要RD/採購協助助pull in</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1648,8 @@
       </c>
       <c r="P15" s="11" t="inlineStr">
         <is>
-          <t>1).Materiel: #A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/E MP的目標,麻煩RD/採購pull in森田薄膜進料時間.</t>
+          <t>1) ATS與MP的物料簽樣與備料,需要RD與採購和物管協助
+2)A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/30 MP的目標,需要RD/採購協助助pull in</t>
         </is>
       </c>
     </row>
@@ -1808,10 +1812,10 @@
       </c>
       <c r="P17" s="11" t="inlineStr">
         <is>
-          <t>1)Battery life: 以2.8K panel+day0 rev.A環境用balance mode測試，Modern standby可達標準，Web browersing尚差0.2Hr，將於BSP Day0 rev.B再進行驗證。
-2)NV Abnormal shut down 的solution，確認需於BSP Day0 rev.B驗證，預計7/23 image完成後，DQA/工廠會同時切換驗證確認。
-3)NV更新可for出貨的 GPU driver提前於8/3美國時間release，後須計畫以此版本進行測試並出貨，不影響現行Schedule，ATS仍定於8/17開始
-4)for NV/MSFT 113pcs樣品，已於7/17 SMT，7/22 ASS'Y，並通知業務轉單，預計下周可出貨</t>
+          <t>1)Battery life: 2.8K panel+day0 rev.B+balance mode測試，Web browersing測試達716min，接近過關。NV更新會導入部分省電作法於Rev. C，待更新SW後驗證。
+2)NV Abnormal shut down 的solution，經DQA於BSP Day0 rev.B驗證後，未發生除error code "0x7E"外的ABS現象，後續會持續觀察。
+3) Day0 rev.C BIOS 7/29 release，測試image預計7/30 release，工廠/DQA將同時切換測試。
+4)工廠用MP樣品測試，反應主要問題，需RD一起分析 1.Long run自動測試 S3/S4/S5/ Reboot/ FSU進系統在login 画面持续转圈宕機，黑屏無顯 ,宕機 2. LCD 花屏（panel 有黑線) 3. camera 開啟錄像后 camera APP 卡住</t>
         </is>
       </c>
     </row>
@@ -5019,8 +5023,9 @@
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
-          <t>1) B07-669945C-T07，FW 燒錄不上，待治具更新軟體;
-2) Schedule:NV VBIOS @1/6, gating 8天,預計12/E 拿到WHQL，可能影響到最終TTM 時間</t>
+          <t>1)目前0M PCBA未開機,0N geberout@8/25;
+2) B07-669945C-T07，FW 燒錄不上，待治具更新軟體;
+3) Schedule:NV VBIOS @1/6, gating 8天,預計12/E 拿到WHQL，可能影響到最終TTM 時間</t>
         </is>
       </c>
     </row>
@@ -5519,7 +5524,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Raider 16 HX B14WI</t>
+          <t>Raider 16 HX B14WH</t>
         </is>
       </c>
       <c r="D66" s="17" t="inlineStr">
@@ -5534,7 +5539,7 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -5579,7 +5584,7 @@
       </c>
       <c r="O66" s="6" t="inlineStr">
         <is>
-          <t>leverage Raider 16 HX B14WJ</t>
+          <t>7/24 Kick off，預計0M gerberout 8/28</t>
         </is>
       </c>
       <c r="P66" s="6" t="inlineStr">
@@ -5599,7 +5604,7 @@
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Raider 16 HX B14WJ</t>
+          <t>Raider 16 HX B14WI</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
@@ -5614,7 +5619,7 @@
       </c>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="G67" s="9" t="inlineStr">
@@ -5679,7 +5684,7 @@
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Raider 16 HX B14WH</t>
+          <t>Raider 16 HX B14WJ</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
@@ -5694,7 +5699,7 @@
       </c>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="G68" s="9" t="inlineStr">
@@ -5739,10 +5744,14 @@
       </c>
       <c r="O68" s="11" t="inlineStr">
         <is>
-          <t>leverage Raider 16 HX B14WJ</t>
-        </is>
-      </c>
-      <c r="P68" s="11" t="inlineStr"/>
+          <t>7/24 Kick off，預計0M gerberout 8/28</t>
+        </is>
+      </c>
+      <c r="P68" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -6060,7 +6069,7 @@
       </c>
       <c r="P72" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>由raider改回crosshair，待確認 final SPEC&amp;ID color plan，對schedule 影響TBD</t>
         </is>
       </c>
     </row>
@@ -6140,7 +6149,7 @@
       </c>
       <c r="P73" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>由raider改回crosshair，待確認 final SPEC&amp;ID color plan，對schedule 影響TBD</t>
         </is>
       </c>
     </row>
@@ -6220,7 +6229,7 @@
       </c>
       <c r="P74" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>由raider改回crosshair，待確認 final SPEC&amp;ID color plan，對schedule 影響TBD</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6309,7 @@
       </c>
       <c r="P75" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>由raider改回crosshair，待確認 final SPEC&amp;ID color plan，對schedule 影響TBD</t>
         </is>
       </c>
     </row>

--- a/npi_dashboard.xlsx
+++ b/npi_dashboard.xlsx
@@ -47,12 +47,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="007030A0"/>
+      <color rgb="00ED7D31"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00ED7D31"/>
+      <color rgb="007030A0"/>
       <sz val="10"/>
     </font>
     <font>
@@ -134,13 +134,13 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1985,12 +1985,12 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Cyborg A15 Max C1PWE</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Cyborg A15 Max C1PWF</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>MVT</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -2021,33 +2021,35 @@
       <c r="J20" s="4" t="inlineStr"/>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>2026/08/04</t>
+          <t>2026/08/07</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/08/21</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>2026/09/09</t>
+          <t>2026/09/12</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>2026/09/19</t>
+          <t>2026/09/22</t>
         </is>
       </c>
       <c r="O20" s="6" t="inlineStr">
         <is>
-          <t>HPT sku:預計8/3 MVT SMT,目前HPT1搭配RC4版本的BIOS測試MODS still fail,請BIOS RD持續與AMD co-work釐清問題</t>
+          <t>HPT sku:預計8/7 MVT SMT,請BIOS RD儘速提供PI 1200i NDA版本的MSI BIOS</t>
         </is>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>1).Schedule:AMD原預計7/22 release PI 1200I NDA,再次延期,待 AMD提供進一步時程後,將更新 MP Schedule.
-2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS,若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
+          <t>"
+1).Schedule:AMD PI 1200i NDA release@7/28 USA time(original 6/19,delay 39天)與工廠將MVT排程延至8/7 (original 8/4,delay 3天),因要和量產工單一起生產,因應上述時程變更,MP預計延至9/22(先前已由 9 /17提前至 8/31, 現又延至9/
+22),後續將依實際測試結果滾動式調整專案時程。
+2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS,若實測結果未達預期,物料需報廢,schedule也可能因此造成影響"</t>
         </is>
       </c>
     </row>
@@ -2062,12 +2064,12 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Cyborg A15 Max C1PWF</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Cyborg A15 Max C1PWG</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>MVT</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -2077,7 +2079,7 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
@@ -2098,33 +2100,35 @@
       <c r="J21" s="9" t="inlineStr"/>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>2026/08/04</t>
+          <t>2026/08/07</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/08/21</t>
         </is>
       </c>
       <c r="M21" s="9" t="inlineStr">
         <is>
-          <t>2026/09/09</t>
+          <t>2026/09/12</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>2026/09/19</t>
+          <t>2026/09/22</t>
         </is>
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>HPT sku:預計8/3 MVT SMT,目前HPT1搭配RC4版本的BIOS測試MODS still fail,請BIOS RD持續與AMD co-work釐清問題</t>
+          <t>HPT sku:預計8/7 MVT SMT,請BIOS RD儘速提供PI 1200i NDA版本的MSI BIOS</t>
         </is>
       </c>
       <c r="P21" s="11" t="inlineStr">
         <is>
-          <t>1).Schedule:AMD原預計7/22 release PI 1200I NDA,再次延期,待 AMD提供進一步時程後,將更新 MP Schedule.
-2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS,若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
+          <t>"
+1).Schedule:AMD PI 1200i NDA release@7/28 USA time(original 6/19,delay 39天)與工廠將MVT排程延至8/7 (original 8/4,delay 3天),因要和量產工單一起生產,因應上述時程變更,MP預計延至9/22(先前已由 9 /17提前至 8/31, 現又延至9/
+22),後續將依實際測試結果滾動式調整專案時程。
+2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS,若實測結果未達預期,物料需報廢,schedule也可能因此造成影響"</t>
         </is>
       </c>
     </row>
@@ -2139,12 +2143,12 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Cyborg A15 Max C1PWG</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Cyborg A15 Max C1PWE</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>MVT</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -2154,7 +2158,7 @@
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -2175,32 +2179,33 @@
       <c r="J22" s="9" t="inlineStr"/>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>2026/08/04</t>
+          <t>2026/08/07</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/08/21</t>
         </is>
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
-          <t>2026/09/09</t>
+          <t>2026/09/12</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
         <is>
-          <t>2026/09/19</t>
+          <t>2026/09/22</t>
         </is>
       </c>
       <c r="O22" s="11" t="inlineStr">
         <is>
-          <t>HPT sku:預計8/3 MVT SMT,目前HPT1搭配RC4版本的BIOS測試MODS still fail,請BIOS RD持續與AMD co-work釐清問題</t>
+          <t>HPT sku:預計8/7 MVT SMT,請BIOS RD儘速提供PI 1200i NDA版本的MSI BIOS</t>
         </is>
       </c>
       <c r="P22" s="11" t="inlineStr">
         <is>
-          <t>1).Schedule:AMD原預計7/22 release PI 1200I NDA,再次延期,待 AMD提供進一步時程後,將更新 MP Schedule.
+          <t>1).Schedule:AMD PI 1200i NDA release@7/28 USA time(original 6/19,delay 39天)與工廠將MVT排程延至8/7 (original 8/4,delay 3天),因要和量產工單一起生產,因應上述時程變更,MP預計延至9/22(先前已由 9 /17提前至 8/31, 現又延至9/
+22),後續將依實際測試結果滾動式調整專案時程。
 2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS,若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
@@ -2219,9 +2224,9 @@
           <t>Cyborg A15 C1PWE</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>DVT</t>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>MVT</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -2252,32 +2257,33 @@
       <c r="J23" s="9" t="inlineStr"/>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>2026/08/04</t>
+          <t>2026/08/07</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/08/21</t>
         </is>
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>2026/09/09</t>
+          <t>2026/09/12</t>
         </is>
       </c>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>2026/09/19</t>
+          <t>2026/09/22</t>
         </is>
       </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
-          <t>HPT sku:預計8/3 MVT SMT,目前HPT1搭配RC4版本的BIOS測試MODS still fail,請BIOS RD持續與AMD co-work釐清問題</t>
+          <t>HPT sku:預計8/7 MVT SMT,請BIOS RD儘速提供PI 1200i NDA版本的MSI BIOS</t>
         </is>
       </c>
       <c r="P23" s="11" t="inlineStr">
         <is>
-          <t>1).Schedule:AMD原預計7/22 release PI 1200I NDA,再次延期,待 AMD提供進一步時程後,將更新 MP Schedule.
+          <t>1).Schedule:AMD PI 1200i NDA release@7/28 USA time(original 6/19,delay 39天)與工廠將MVT排程延至8/7 (original 8/4,delay 3天),因要和量產工單一起生產,因應上述時程變更,MP預計延至9/22(先前已由 9 /17提前至 8/31, 現又延至9/
+22),後續將依實際測試結果滾動式調整專案時程。
 2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS,若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
@@ -2377,7 +2383,7 @@
           <t>Prestige N16 AI+ C1M</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>EVT</t>
         </is>
@@ -2457,7 +2463,7 @@
           <t>Katana 18 HX A14WEK</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>EVT</t>
         </is>
@@ -2537,7 +2543,7 @@
           <t>Katana 18 HX A14WFK</t>
         </is>
       </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>EVT</t>
         </is>
@@ -2617,7 +2623,7 @@
           <t>Katana 18 HX A14WGK</t>
         </is>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>EVT</t>
         </is>
@@ -2697,7 +2703,7 @@
           <t>Katana 18 HX A14WEOK</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D29" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2773,7 +2779,7 @@
           <t>Katana 18 HX A14WFOK</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D30" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2849,7 +2855,7 @@
           <t>Katana 18 HX A14WGOK</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2925,7 +2931,7 @@
           <t>Crosshair 18 Max HX B14WEO</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D32" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3001,7 +3007,7 @@
           <t>Crosshair 18 Max HX B14WFO</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
+      <c r="D33" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3077,7 +3083,7 @@
           <t>Crosshair 18 Max HX B14WGO</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D34" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3153,7 +3159,7 @@
           <t>Crosshair 18 Max HX B14WGXO</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
+      <c r="D35" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3229,7 +3235,7 @@
           <t>Crosshair 18 Max HX B14WE</t>
         </is>
       </c>
-      <c r="D36" s="15" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>EVT</t>
         </is>
@@ -3309,7 +3315,7 @@
           <t>Crosshair 18 Max HX B14WF</t>
         </is>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
         <is>
           <t>EVT</t>
         </is>
@@ -3389,7 +3395,7 @@
           <t>Crosshair 18 Max HX B14WG</t>
         </is>
       </c>
-      <c r="D38" s="15" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>EVT</t>
         </is>
@@ -3469,7 +3475,7 @@
           <t>Crosshair 18 Max HX B14WGX</t>
         </is>
       </c>
-      <c r="D39" s="15" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>EVT</t>
         </is>
@@ -3549,7 +3555,7 @@
           <t>Crosshair 18 Max HX B2WE</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D40" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -3621,7 +3627,7 @@
           <t>Crosshair 18 Max HX B2WEO</t>
         </is>
       </c>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D41" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -3693,7 +3699,7 @@
           <t>Crosshair 18 Max HX B2WF</t>
         </is>
       </c>
-      <c r="D42" s="16" t="inlineStr">
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -3765,7 +3771,7 @@
           <t>Crosshair 18 Max HX B2WFO</t>
         </is>
       </c>
-      <c r="D43" s="16" t="inlineStr">
+      <c r="D43" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -3837,7 +3843,7 @@
           <t>Crosshair 18 Max HX B2WG</t>
         </is>
       </c>
-      <c r="D44" s="16" t="inlineStr">
+      <c r="D44" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -3909,7 +3915,7 @@
           <t>Crosshair 18 Max HX B2WGO</t>
         </is>
       </c>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="D45" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -3981,7 +3987,7 @@
           <t>Crosshair 18 Max HX B2WGX</t>
         </is>
       </c>
-      <c r="D46" s="16" t="inlineStr">
+      <c r="D46" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4053,7 +4059,7 @@
           <t>Crosshair 18 Max HX B2WGXO</t>
         </is>
       </c>
-      <c r="D47" s="16" t="inlineStr">
+      <c r="D47" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4125,7 +4131,7 @@
           <t>Katana 18 HX A2WEK</t>
         </is>
       </c>
-      <c r="D48" s="16" t="inlineStr">
+      <c r="D48" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4197,7 +4203,7 @@
           <t>Katana 18 HX A2WEOK</t>
         </is>
       </c>
-      <c r="D49" s="16" t="inlineStr">
+      <c r="D49" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4273,7 +4279,7 @@
           <t>Katana 18 HX A2WFK</t>
         </is>
       </c>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="D50" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4345,7 +4351,7 @@
           <t>Katana 18 HX A2WFOK</t>
         </is>
       </c>
-      <c r="D51" s="16" t="inlineStr">
+      <c r="D51" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4421,7 +4427,7 @@
           <t>Katana 18 HX A2WGK</t>
         </is>
       </c>
-      <c r="D52" s="16" t="inlineStr">
+      <c r="D52" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4493,7 +4499,7 @@
           <t>Katana 18 HX A2WGOK</t>
         </is>
       </c>
-      <c r="D53" s="16" t="inlineStr">
+      <c r="D53" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4569,7 +4575,7 @@
           <t>Prestige 14 AI</t>
         </is>
       </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -4649,7 +4655,7 @@
           <t>Prestige 14 AI+ Flip</t>
         </is>
       </c>
-      <c r="D55" s="13" t="inlineStr">
+      <c r="D55" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -4729,7 +4735,7 @@
           <t>Prestige 16 AI+</t>
         </is>
       </c>
-      <c r="D56" s="12" t="inlineStr">
+      <c r="D56" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -4805,7 +4811,7 @@
           <t>Prestige 16 Flip AI+</t>
         </is>
       </c>
-      <c r="D57" s="13" t="inlineStr">
+      <c r="D57" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -4961,7 +4967,7 @@
           <t>Stealth 16 AI+ B4WI</t>
         </is>
       </c>
-      <c r="D59" s="12" t="inlineStr">
+      <c r="D59" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -5018,12 +5024,12 @@
       </c>
       <c r="O59" s="6" t="inlineStr">
         <is>
-          <t>DVT SMT@7/23, RD 開機中</t>
+          <t>RD debug中 (PCBA僅HDMI會顯示)</t>
         </is>
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
-          <t>1)目前0M PCBA未開機,0N geberout@8/25;
+          <t>1)目前0M PCBA開機,但目前僅HDMI會顯示，0N geberout@8/25，請RD幫忙盡快debug;
 2) B07-669945C-T07，FW 燒錄不上，待治具更新軟體;
 3) Schedule:NV VBIOS @1/6, gating 8天,預計12/E 拿到WHQL，可能影響到最終TTM 時間</t>
         </is>
@@ -5043,7 +5049,7 @@
           <t>Stealth 16 AI+ B4WH</t>
         </is>
       </c>
-      <c r="D60" s="13" t="inlineStr">
+      <c r="D60" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -5100,7 +5106,7 @@
       </c>
       <c r="O60" s="11" t="inlineStr">
         <is>
-          <t>DVT SMT@7/23, RD 開機中</t>
+          <t>RD debug中 (PCBA僅HDMI會顯示)</t>
         </is>
       </c>
       <c r="P60" s="11" t="inlineStr">
@@ -5123,7 +5129,7 @@
           <t>Stealth 16 AI+ B4WJ</t>
         </is>
       </c>
-      <c r="D61" s="13" t="inlineStr">
+      <c r="D61" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -5180,7 +5186,7 @@
       </c>
       <c r="O61" s="11" t="inlineStr">
         <is>
-          <t>DVT SMT@7/23, RD 開機中</t>
+          <t>RD debug中 (PCBA僅HDMI會顯示)</t>
         </is>
       </c>
       <c r="P61" s="11" t="inlineStr">
@@ -5284,7 +5290,7 @@
           <t>Stealth 16 AI+ B4WF</t>
         </is>
       </c>
-      <c r="D63" s="16" t="inlineStr">
+      <c r="D63" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5365,7 +5371,7 @@
           <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
         </is>
       </c>
-      <c r="D64" s="16" t="inlineStr">
+      <c r="D64" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5446,7 +5452,7 @@
           <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
         </is>
       </c>
-      <c r="D65" s="16" t="inlineStr">
+      <c r="D65" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5607,7 +5613,7 @@
           <t>Raider 16 HX B14WI</t>
         </is>
       </c>
-      <c r="D67" s="16" t="inlineStr">
+      <c r="D67" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5687,7 +5693,7 @@
           <t>Raider 16 HX B14WJ</t>
         </is>
       </c>
-      <c r="D68" s="16" t="inlineStr">
+      <c r="D68" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -5767,7 +5773,7 @@
           <t>Raider 16 Max HX B4WH</t>
         </is>
       </c>
-      <c r="D69" s="12" t="inlineStr">
+      <c r="D69" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -5847,7 +5853,7 @@
           <t>Raider 16 Max HX B4WI</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
+      <c r="D70" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -5927,7 +5933,7 @@
           <t>Raider 16 Max HX B4WJ</t>
         </is>
       </c>
-      <c r="D71" s="13" t="inlineStr">
+      <c r="D71" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -6007,7 +6013,7 @@
           <t>Raider 16 HX B4WE</t>
         </is>
       </c>
-      <c r="D72" s="12" t="inlineStr">
+      <c r="D72" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -6087,7 +6093,7 @@
           <t>Raider 16 HX B4WF</t>
         </is>
       </c>
-      <c r="D73" s="13" t="inlineStr">
+      <c r="D73" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -6167,7 +6173,7 @@
           <t>Raider 16 HX B4WG</t>
         </is>
       </c>
-      <c r="D74" s="13" t="inlineStr">
+      <c r="D74" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -6247,7 +6253,7 @@
           <t>Raider 16 HX B4WGX</t>
         </is>
       </c>
-      <c r="D75" s="13" t="inlineStr">
+      <c r="D75" s="14" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -6384,13 +6390,12 @@
       </c>
       <c r="O76" s="6" t="inlineStr">
         <is>
-          <t>LAN footprint線路修改,0M gerber out變更為8/3,暫不影響後續EVT schedule.</t>
+          <t>製程DFM修改需求,0M gerber out變更為8/4,暫不影響後續EVT schedule.</t>
         </is>
       </c>
       <c r="P76" s="6" t="inlineStr">
         <is>
-          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.
-2) Seamless Haptic TP待Liteon提供final線路圖/2D3D/Spec for Lockdown確認.</t>
+          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6413,7 @@
           <t>Titan 18 HX B4WI</t>
         </is>
       </c>
-      <c r="D77" s="16" t="inlineStr">
+      <c r="D77" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6465,13 +6470,12 @@
       </c>
       <c r="O77" s="11" t="inlineStr">
         <is>
-          <t>LAN footprint線路修改,0M gerber out變更為8/3,暫不影響後續EVT schedule.</t>
+          <t>製程DFM修改需求,0M gerber out變更為8/4,暫不影響後續EVT schedule.</t>
         </is>
       </c>
       <c r="P77" s="11" t="inlineStr">
         <is>
-          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.
-2) Seamless Haptic TP待Liteon提供final線路圖/2D3D/Spec for Lockdown確認.</t>
+          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6493,7 @@
           <t>Titan 18 HX B4WJ</t>
         </is>
       </c>
-      <c r="D78" s="16" t="inlineStr">
+      <c r="D78" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6546,13 +6550,12 @@
       </c>
       <c r="O78" s="11" t="inlineStr">
         <is>
-          <t>LAN footprint線路修改,0M gerber out變更為8/3,暫不影響後續EVT schedule.</t>
+          <t>製程DFM修改需求,0M gerber out變更為8/4,暫不影響後續EVT schedule.</t>
         </is>
       </c>
       <c r="P78" s="11" t="inlineStr">
         <is>
-          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.
-2) Seamless Haptic TP待Liteon提供final線路圖/2D3D/Spec for Lockdown確認.</t>
+          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6573,7 @@
           <t>Raider 18 Max HX B4WH</t>
         </is>
       </c>
-      <c r="D79" s="16" t="inlineStr">
+      <c r="D79" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6627,7 +6630,7 @@
       </c>
       <c r="O79" s="11" t="inlineStr">
         <is>
-          <t>LAN footprint線路修改,0M gerber out變更為8/3,暫不影響後續EVT schedule.</t>
+          <t>製程DFM修改需求,0M gerber out變更為8/4,暫不影響後續EVT schedule.</t>
         </is>
       </c>
       <c r="P79" s="11" t="inlineStr">
@@ -6650,7 +6653,7 @@
           <t>Raider 18 Max HX B4WI</t>
         </is>
       </c>
-      <c r="D80" s="16" t="inlineStr">
+      <c r="D80" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6707,7 +6710,7 @@
       </c>
       <c r="O80" s="11" t="inlineStr">
         <is>
-          <t>LAN footprint線路修改,0M gerber out變更為8/3,暫不影響後續EVT schedule.</t>
+          <t>製程DFM修改需求,0M gerber out變更為8/4,暫不影響後續EVT schedule.</t>
         </is>
       </c>
       <c r="P80" s="11" t="inlineStr">
@@ -6730,7 +6733,7 @@
           <t>Raider 18 Max HX B4WJ</t>
         </is>
       </c>
-      <c r="D81" s="16" t="inlineStr">
+      <c r="D81" s="15" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -6787,7 +6790,7 @@
       </c>
       <c r="O81" s="11" t="inlineStr">
         <is>
-          <t>LAN footprint線路修改,0M gerber out變更為8/3,暫不影響後續EVT schedule.</t>
+          <t>製程DFM修改需求,0M gerber out變更為8/4,暫不影響後續EVT schedule.</t>
         </is>
       </c>
       <c r="P81" s="11" t="inlineStr">

--- a/npi_dashboard.xlsx
+++ b/npi_dashboard.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPI Dashboard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +40,11 @@
     <font>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0070AD47"/>
+      <sz val="10"/>
     </font>
     <font>
       <color rgb="00666666"/>
@@ -93,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -116,22 +121,22 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -140,10 +145,13 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -511,7 +519,7 @@
     <outlinePr summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P81"/>
+  <dimension ref="A1:P79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -620,12 +628,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>15Q1</t>
+          <t>15Q3</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Cyborg 15 B2VEK</t>
+          <t>Cyborg 15 Black Edition B13WE</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -635,17 +643,17 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>ARL-H 45W</t>
+          <t>RPL-H 45W</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>RTX 4050 (35W+10W)/ GDDR6 6GB</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>李文欽</t>
+          <t>楊淑賢</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -655,30 +663,34 @@
       </c>
       <c r="I2" s="4" t="inlineStr"/>
       <c r="J2" s="4" t="inlineStr"/>
-      <c r="K2" s="4" t="inlineStr"/>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/01</t>
+        </is>
+      </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>2026/06/26</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>2026/07/22</t>
+          <t>2026/08/03</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>2026/07/31</t>
+          <t>2026/08/07</t>
         </is>
       </c>
       <c r="O2" s="6" t="inlineStr">
         <is>
-          <t>（清日文4區RGB鍵盤庫存)</t>
+          <t>DQA MP HDI測試進行中, 暫無量產工單產生</t>
         </is>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
-          <t>1)方向鍵上的快捷鍵無功能, EC和BIOS需要進版, 請DQA協助快掃測試</t>
+          <t>1) Cyborg Black Edition SKU: Cyborg A+Venture B/C/D機構件+白光鍵盤</t>
         </is>
       </c>
     </row>
@@ -688,32 +700,32 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>15Q1</t>
+          <t>15Q3</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Cyborg 15 B2VE</t>
+          <t>Cyborg 15 Black Edition B13WF</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>ARL-H 45W</t>
+          <t>RPL-H 45W</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>RTX 4050 (35W+10W)/ GDDR6 6GB</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>李文欽</t>
+          <t>楊淑賢</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
@@ -725,32 +737,32 @@
       <c r="J3" s="9" t="inlineStr"/>
       <c r="K3" s="9" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
+          <t>2026/07/01</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>2026/07/20</t>
+          <t>2026/08/10</t>
         </is>
       </c>
       <c r="N3" s="9" t="inlineStr">
         <is>
-          <t>2026/07/31</t>
+          <t>2026/08/13</t>
         </is>
       </c>
       <c r="O3" s="11" t="inlineStr">
         <is>
-          <t>（清白光鍵盤庫存）ATS C/R驗證中</t>
+          <t>ATS C/R工單： 9S7-15Q373-1258* 50 pcs 預排8/10 ASSY</t>
         </is>
       </c>
       <c r="P3" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) Cyborg Black Edition SKU: Cyborg A+Venture B/C/D機構件+白光鍵盤</t>
         </is>
       </c>
     </row>
@@ -760,12 +772,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>15Q3</t>
+          <t>17U3</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Cyborg 15 Black Edition B13WE</t>
+          <t>Cyborg 17 Black Edition B13WE</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -832,15 +844,15 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>15Q3</t>
+          <t>17U3</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Cyborg 15 Black Edition B13WF</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
+          <t>Cyborg 17 Black Edition B13WF</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
@@ -879,389 +891,400 @@
       </c>
       <c r="M5" s="9" t="inlineStr">
         <is>
-          <t>2026/08/07</t>
+          <t>2026/08/10</t>
         </is>
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="O5" s="11" t="inlineStr">
+        <is>
+          <t>ATS C/R工單： 9S7-17U344-449 * 50 pcs 預排8/10 ASSY</t>
+        </is>
+      </c>
+      <c r="P5" s="11" t="inlineStr">
+        <is>
+          <t>1) Cyborg Black Edition SKU: Cyborg A+Venture B/C/D機構件+白光鍵盤</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" hidden="1" outlineLevel="1">
+      <c r="A6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>17U3</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Cyborg 17 Black Edition B2RWF</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>RPL-H refresh 45W</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>楊淑賢</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr"/>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/01</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/14</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
           <t>2026/08/12</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
-        <is>
-          <t>ATS C/R工單： 9S7-15Q373-1258* 50 pcs 預排8/7 ASSY</t>
-        </is>
-      </c>
-      <c r="P5" s="11" t="inlineStr">
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="O6" s="11" t="inlineStr">
+        <is>
+          <t>9S7-17U344-441 * 300pcs ASSY @ 8/12</t>
+        </is>
+      </c>
+      <c r="P6" s="11" t="inlineStr">
         <is>
           <t>1) Cyborg Black Edition SKU: Cyborg A+Venture B/C/D機構件+白光鍵盤</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>17U3</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Cyborg 17 Black Edition B13WE</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>15T2</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Venture 15 AI+ B3M</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>RPL-H 45W</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>PTL-H 80W</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>李文欽</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/20</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/27</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>MVT2驗證中</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>1) ATS與MP的物料簽樣與備料,需要RD與採購和物管協助
+2)A件交期依森田薄膜進料時間,15T2 ATS組裝在8/20, MP在8/30, 會比原時程晚2天,會導致15T2無法meet 8/27 MP的目標,需要RD/採購協助pull in
+3)PCB預計交期在8/20,需麻煩採購協助Pull in</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>15T3</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Katana 15 HX C14WEK</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>楊淑賢</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/24</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/01</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>蔡東宏</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/20</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>2026/07/14</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/03</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="O6" s="6" t="inlineStr">
-        <is>
-          <t>DQA MP HDI測試進行中, 暫無量產工單產生</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>1) Cyborg Black Edition SKU: Cyborg A+Venture B/C/D機構件+白光鍵盤</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" hidden="1" outlineLevel="1">
-      <c r="A7" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>17U3</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Cyborg 17 Black Edition B13WF</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/30</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>DDR5 sku, MVT 測試中</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>1) ATS與MP的物料簽樣與備料,需要RD與採購和物管協助
+2)A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/30 MP的目標,需要RD/採購協助助pull in</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" hidden="1" outlineLevel="1">
+      <c r="A9" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>15T3</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Katana 15 HX C14WFK</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>RPL-H 45W</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>RTX 5060</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>楊淑賢</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/24</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr"/>
-      <c r="J7" s="9" t="inlineStr"/>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/01</t>
-        </is>
-      </c>
-      <c r="L7" s="9" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>蔡東宏</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>2026/04/20</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr"/>
+      <c r="K9" s="9" t="inlineStr">
         <is>
           <t>2026/07/14</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="N7" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/12</t>
-        </is>
-      </c>
-      <c r="O7" s="11" t="inlineStr">
-        <is>
-          <t>ATS C/R工單： 9S7-17U344-449 * 50 pcs 預排8/7 ASSY</t>
-        </is>
-      </c>
-      <c r="P7" s="11" t="inlineStr">
-        <is>
-          <t>1) Cyborg Black Edition SKU: Cyborg A+Venture B/C/D機構件+白光鍵盤</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" hidden="1" outlineLevel="1">
-      <c r="A8" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>17U3</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Cyborg 17 Black Edition B2RWF</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/30</t>
+        </is>
+      </c>
+      <c r="O9" s="11" t="inlineStr">
+        <is>
+          <t>DDR5 sku, MVT 測試中</t>
+        </is>
+      </c>
+      <c r="P9" s="11" t="inlineStr">
+        <is>
+          <t>1) ATS與MP的物料簽樣與備料,需要RD與採購和物管協助
+2)A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/30 MP的目標,需要RD/採購協助助pull in</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" hidden="1" outlineLevel="1">
+      <c r="A10" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>15T3</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Katana 15 HX C14WGK</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>RPL-H refresh 45W</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>楊淑賢</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/24</t>
-        </is>
-      </c>
-      <c r="I8" s="9" t="inlineStr"/>
-      <c r="J8" s="9" t="inlineStr"/>
-      <c r="K8" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/01</t>
-        </is>
-      </c>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>蔡東宏</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>2026/04/20</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr"/>
+      <c r="K10" s="9" t="inlineStr">
         <is>
           <t>2026/07/14</t>
         </is>
       </c>
-      <c r="M8" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/08</t>
-        </is>
-      </c>
-      <c r="N8" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/12</t>
-        </is>
-      </c>
-      <c r="O8" s="11" t="inlineStr">
-        <is>
-          <t>9S7-17U344-441 * 300pcs ASSY @ 8/8</t>
-        </is>
-      </c>
-      <c r="P8" s="11" t="inlineStr">
-        <is>
-          <t>1) Cyborg Black Edition SKU: Cyborg A+Venture B/C/D機構件+白光鍵盤</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>15T2</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Venture 15 AI+ B3M</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>PTL-H 80W</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Intel® Arc™ Graphics</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>李文欽</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/20</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/26</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/08</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/20</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/17</t>
-        </is>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/27</t>
-        </is>
-      </c>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>MVT2驗證中</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>1) ATS與MP的物料簽樣與備料,需要RD與採購和物管協助
-2)A件交期依森田薄膜進料時間,15T2 ATS組裝在8/20, MP在8/30, 會比原時程晚2天,會導致15T2無法meet 8/27 MP的目標,需要RD/採購協助pull in</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>15T3</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Katana 15 HX C14WEK</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/20</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/14</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L10" s="9" t="inlineStr">
         <is>
           <t>2026/07/30</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="M10" s="9" t="inlineStr">
         <is>
           <t>2026/08/20</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N10" s="9" t="inlineStr">
         <is>
           <t>2026/08/30</t>
         </is>
       </c>
-      <c r="O10" s="6" t="inlineStr">
-        <is>
-          <t>DDR5 sku, MVT2 組裝中</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
+        <is>
+          <t>DDR5 sku, MVT 測試中</t>
+        </is>
+      </c>
+      <c r="P10" s="11" t="inlineStr">
         <is>
           <t>1) ATS與MP的物料簽樣與備料,需要RD與採購和物管協助
 2)A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/30 MP的目標,需要RD/採購協助助pull in</t>
@@ -1279,10 +1302,10 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WFK</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
+          <t>Katana 15 HX C14WEOK</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
@@ -1294,7 +1317,7 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
@@ -1304,38 +1327,38 @@
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/05/15</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>2026/06/01</t>
+          <t>2026/06/15</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr"/>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>2026/07/14</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>2026/07/30</t>
+          <t>2026/08/07</t>
         </is>
       </c>
       <c r="M11" s="9" t="inlineStr">
         <is>
-          <t>2026/08/20</t>
+          <t>2026/08/21</t>
         </is>
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>2026/08/30</t>
+          <t>2026/08/31</t>
         </is>
       </c>
       <c r="O11" s="11" t="inlineStr">
         <is>
-          <t>DDR5 sku, MVT2組裝中</t>
+          <t>DDR4 sku, MVT 測試中,預計8/7 PCB risk buy</t>
         </is>
       </c>
       <c r="P11" s="11" t="inlineStr">
@@ -1356,10 +1379,10 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WGK</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
+          <t>Katana 15 HX C14WFOK</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
@@ -1371,7 +1394,7 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -1381,38 +1404,38 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/05/15</t>
         </is>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>2026/06/01</t>
+          <t>2026/06/15</t>
         </is>
       </c>
       <c r="J12" s="9" t="inlineStr"/>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>2026/07/14</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>2026/07/30</t>
+          <t>2026/08/07</t>
         </is>
       </c>
       <c r="M12" s="9" t="inlineStr">
         <is>
-          <t>2026/08/20</t>
+          <t>2026/08/21</t>
         </is>
       </c>
       <c r="N12" s="9" t="inlineStr">
         <is>
-          <t>2026/08/30</t>
+          <t>2026/08/31</t>
         </is>
       </c>
       <c r="O12" s="11" t="inlineStr">
         <is>
-          <t>DDR5 sku, MVT2組裝中</t>
+          <t>DDR4 sku, MVT 測試中,預計8/7 PCB risk buy</t>
         </is>
       </c>
       <c r="P12" s="11" t="inlineStr">
@@ -1433,10 +1456,10 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WEOK</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
+          <t>Katana 15 HX C14WGOK</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
@@ -1448,7 +1471,7 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -1489,7 +1512,7 @@
       </c>
       <c r="O13" s="11" t="inlineStr">
         <is>
-          <t>DDR4 sku,MVT組裝中,預計8/4拿到機器開始測試,8/7 PCB risk buy</t>
+          <t>DDR4 sku, MVT 測試中,預計8/7 PCB risk buy</t>
         </is>
       </c>
       <c r="P13" s="11" t="inlineStr">
@@ -1499,80 +1522,85 @@
         </is>
       </c>
     </row>
-    <row r="14" hidden="1" outlineLevel="1">
-      <c r="A14" s="7" t="n">
+    <row r="14">
+      <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>15T3</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Katana 15 HX C14WFOK</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>2621</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Prestige N16 AI+ C1XMT</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/15</t>
-        </is>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="inlineStr"/>
-      <c r="K14" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/24</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="M14" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="N14" s="9" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>N1x 80W</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>林晉弘</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>2024/11/25</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>2025/01/20</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>2025/06/25</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>2026/03/12</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O14" s="11" t="inlineStr">
-        <is>
-          <t>DDR4 sku,MVT組裝中,預計8/4拿到機器開始測試,8/7 PCB risk buy</t>
-        </is>
-      </c>
-      <c r="P14" s="11" t="inlineStr">
-        <is>
-          <t>1) ATS與MP的物料簽樣與備料,需要RD與採購和物管協助
-2)A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/30 MP的目標,需要RD/採購協助助pull in</t>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>MVT測試中</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>1)Battery life: 8/6三方會議中，MSFT口頭布達，MSFT用MSI機台測試battery life，結果不如預期，因現象不僅出現在MSI機台上，其他OEM亦同，故會議中MSFT請NV內部先確認，MSFT預計8/7出分析報告。因結果跟MSI自測與NV手上的數據差距頗大，待與MSFT確認測試細節。
+2)NV 8/5 relese Day0 rev.E，預計8/10 release BIOS與 image，工廠/DQA將同時切換測試。
+3)更新到day0 rev.C後測試，工廠/DQA主要問題點如下，仍須RD與廠商協助 a)Camera lost and 錄影當住 b)Audio撥放雜音與耳機孔插拔問題 c)Abnormal shut down and 0x7E BSOD須持續觀察 d)SD卡有機率插壞 e)USB Type A redetect問題 f)Light sensor</t>
         </is>
       </c>
     </row>
@@ -1582,58 +1610,62 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>15T3</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WGOK</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
+          <t>Prestige N16 Flip AI+ C1XMT</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>N1x 80W</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>蔡東宏</t>
+          <t>林晉弘</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>2026/05/15</t>
+          <t>2024/11/25</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr"/>
+          <t>2025/01/20</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>2025/06/25</t>
+        </is>
+      </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/03/12</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>2026/08/07</t>
+          <t>2026/06/30</t>
         </is>
       </c>
       <c r="M15" s="9" t="inlineStr">
         <is>
-          <t>2026/08/21</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="N15" s="9" t="inlineStr">
@@ -1643,13 +1675,14 @@
       </c>
       <c r="O15" s="11" t="inlineStr">
         <is>
-          <t>DDR4 sku,MVT組裝中,預計8/4拿到機器開始測試,8/7 PCB risk buy</t>
+          <t>MVT測試中</t>
         </is>
       </c>
       <c r="P15" s="11" t="inlineStr">
         <is>
-          <t>1) ATS與MP的物料簽樣與備料,需要RD與採購和物管協助
-2)A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/30 MP的目標,需要RD/採購協助助pull in</t>
+          <t>1)Battery life: 8/6三方會議中，MSFT口頭布達，MSFT用MSI機台測試battery life，結果不如預期，因現象不僅出現在MSI機台上，其他OEM亦同，故會議中MSFT請NV內部先確認，MSFT預計8/7出分析報告。因結果跟MSI自測與NV手上的數據差距頗大，待與MSFT確認測試細節。
+2)NV 8/5 relese Day0 rev.E，預計8/10 release BIOS與 image，工廠/DQA將同時切換測試。
+3)更新到day0 rev.C後測試，工廠/DQA主要問題點如下，仍須RD與廠商協助 a)Camera lost and 錄影當住 b)Audio撥放雜音與耳機孔插拔問題 c)Abnormal shut down and 0x7E BSOD須持續觀察 d)SD卡有機率插壞 e)USB Type A redetect問題 f)Light sensor</t>
         </is>
       </c>
     </row>
@@ -1659,12 +1692,12 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>26V1</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Prestige N16 AI+ C1XMT</t>
+          <t>Modern 16 LE J3M</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1674,47 +1707,43 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>N1x 80W</t>
+          <t>WCL 25W</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Intel® graphics</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>林晉弘</t>
+          <t>倪嬌嬌</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>2024/11/25</t>
+          <t>2026/06/02</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>2025/01/20</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>2025/06/25</t>
-        </is>
-      </c>
+          <t>2026/07/07</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr"/>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>2026/03/12</t>
+          <t>2026/07/29</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>2026/06/30</t>
+          <t>2026/07/08</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>2026/08/17</t>
+          <t>2026/08/18</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -1724,98 +1753,94 @@
       </c>
       <c r="O16" s="6" t="inlineStr">
         <is>
-          <t>MVT測試中</t>
+          <t>Weibu: 7/30 MVT ASSY</t>
         </is>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>1)Battery life: 2.8K panel+day0 rev.B+balance mode測試，Web browersing測試達716min，接近過關。NV更新會導入部分省電作法於Rev. C，待更新SW後驗證。
-2)NV Abnormal shut down 的solution，經DQA於BSP Day0 rev.B驗證後，未發生除error code "0x7E"外的ABS現象，後續會持續觀察。
-3) Day0 rev.C BIOS 7/29 release，測試image預計7/30 release，工廠/DQA將同時切換測試。
-4)工廠用MP樣品測試，反應主要問題，需RD一起分析 1.Long run自動測試 S3/S4/S5/ Reboot/ FSU進系統在login 画面持续转圈宕機，黑屏無顯 ,宕機 2. LCD 花屏（panel 有黑線) 3. camera 開啟錄像后 camera APP 卡住</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" hidden="1" outlineLevel="1">
-      <c r="A17" s="7" t="n">
+          <t>1)認證: 1. 8/E ready可出貨地區:  DE/UK/TR/BNX/NEU/SEE/FR/ES/PL/CZ/CIS/IT/JP/AU
+2)認證 8/E無法同步ready地區:  9/8 ready: LA/CA/ AR/CL  9/18 ready: UA 10/2 ready: CO/RU 12/18 ready: MX
+2） 備料: 8/7待業務確認26V1 D件是否需修模改善按壓偏軟問題, 可能會ATS排程有影響 .
+3) 八月訂單: 680台</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>2621</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Prestige N16 Flip AI+ C1XMT</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>24V1</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Modern 14 LE J3M</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>N1x 80W</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>林晉弘</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>2024/11/25</t>
-        </is>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>2025/01/20</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/25</t>
-        </is>
-      </c>
-      <c r="K17" s="9" t="inlineStr">
-        <is>
-          <t>2026/03/12</t>
-        </is>
-      </c>
-      <c r="L17" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/30</t>
-        </is>
-      </c>
-      <c r="M17" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/17</t>
-        </is>
-      </c>
-      <c r="N17" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/31</t>
-        </is>
-      </c>
-      <c r="O17" s="11" t="inlineStr">
-        <is>
-          <t>MVT測試中</t>
-        </is>
-      </c>
-      <c r="P17" s="11" t="inlineStr">
-        <is>
-          <t>1)Battery life: 2.8K panel+day0 rev.B+balance mode測試，Web browersing測試達716min，接近過關。NV更新會導入部分省電作法於Rev. C，待更新SW後驗證。
-2)NV Abnormal shut down 的solution，經DQA於BSP Day0 rev.B驗證後，未發生除error code "0x7E"外的ABS現象，後續會持續觀察。
-3) Day0 rev.C BIOS 7/29 release，測試image預計7/30 release，工廠/DQA將同時切換測試。
-4)工廠用MP樣品測試，反應主要問題，需RD一起分析 1.Long run自動測試 S3/S4/S5/ Reboot/ FSU進系統在login 画面持续转圈宕機，黑屏無顯 ,宕機 2. LCD 花屏（panel 有黑線) 3. camera 開啟錄像后 camera APP 卡住</t>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>WCL 25W</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Intel® graphics</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>倪嬌嬌</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/07</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/29</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/26</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="O17" s="6" t="inlineStr">
+        <is>
+          <t>Weibu: MVT 7/30 ASSY</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>1)認證：8/E ready可出貨地區:  DE/UK/TR/BNX/NEU/SEE/FR/ES/PL/CZ/CIS/IT/JP/AU
+2）認證 8/E無法同步ready地區:  9/8 ready: LA/CA/ AR/CL  9/18 ready: UA 10/2 ready: CO/RU 12/18 ready: MX
+2）備料: a. 日文鍵芯開放時程待追蹤 b. 8/4通知微步D件修模改善按壓偏軟的問題, 評估D件備料8/25 ready.
+3）8月訂單: 132台</t>
         </is>
       </c>
     </row>
@@ -1825,12 +1850,12 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>24V1</t>
+          <t>15TK</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Modern 14 LE J3M</t>
+          <t>Cyborg A15 Max C1PWF</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1840,211 +1865,56 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>WCL 25W</t>
+          <t>HWK 45W</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Intel® graphics</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>倪嬌嬌</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>2026/06/02</t>
+          <t>2026/05/28</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>2026/07/07</t>
+          <t>2026/06/26</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr"/>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/08/07</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/08/21</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/09/12</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>2026/08/31</t>
+          <t>2026/09/22</t>
         </is>
       </c>
       <c r="O18" s="6" t="inlineStr">
         <is>
-          <t>Weibu: MVT 7/30 ASSY中</t>
+          <t>HPT sku:預計8/7 MVT SMT,8/10試組,8/12組裝</t>
         </is>
       </c>
       <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>1)認證：8/E ready可出貨地區:  DE/UK/TR/BNX/NEU/SEE/FR/ES/PL/CZ/CIS/IT/JP/AU
-2）認證 8/E無法同步ready地區:  9/8 ready: LA/CA/ AR/CL  9/18 ready: UA 10/2 ready: CO/RU 12/18 ready: MX
-2）備料: 日文鍵芯開放時程待追蹤</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>26V1</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Modern 16 LE J3M</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>WCL 25W</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Intel® graphics</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>倪嬌嬌</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/07</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/29</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/08</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/18</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/31</t>
-        </is>
-      </c>
-      <c r="O19" s="6" t="inlineStr">
-        <is>
-          <t>Weibu: 7/30 MVT ASSY</t>
-        </is>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>1)認證: 1. 8/E ready可出貨地區:  DE/UK/TR/BNX/NEU/SEE/FR/ES/PL/CZ/CIS/IT/JP/AU
-2)認證 8/E無法同步ready地區:  9/8 ready: LA/CA/ AR/CL  9/18 ready: UA 10/2 ready: CO/RU 12/18 ready: MX</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>15TK</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Cyborg A15 Max C1PWF</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>HWK 45W</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/26</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr"/>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/12</t>
-        </is>
-      </c>
-      <c r="N20" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/22</t>
-        </is>
-      </c>
-      <c r="O20" s="6" t="inlineStr">
-        <is>
-          <t>HPT sku:預計8/7 MVT SMT,請BIOS RD儘速提供PI 1200i NDA版本的MSI BIOS</t>
-        </is>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
         <is>
           <t>"
 1).Schedule:AMD PI 1200i NDA release@7/28 USA time(original 6/19,delay 39天)與工廠將MVT排程延至8/7 (original 8/4,delay 3天),因要和量產工單一起生產,因應上述時程變更,MP預計延至9/22(先前已由 9 /17提前至 8/31, 現又延至9/
@@ -2053,77 +1923,77 @@
         </is>
       </c>
     </row>
-    <row r="21" hidden="1" outlineLevel="1">
-      <c r="A21" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+    <row r="19" hidden="1" outlineLevel="1">
+      <c r="A19" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>15TK</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>Cyborg A15 Max C1PWG</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>HWK 45W</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>2026/05/28</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>2026/06/26</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr"/>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr"/>
+      <c r="K19" s="9" t="inlineStr">
         <is>
           <t>2026/08/07</t>
         </is>
       </c>
-      <c r="L21" s="9" t="inlineStr">
+      <c r="L19" s="9" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="M21" s="9" t="inlineStr">
+      <c r="M19" s="9" t="inlineStr">
         <is>
           <t>2026/09/12</t>
         </is>
       </c>
-      <c r="N21" s="9" t="inlineStr">
+      <c r="N19" s="9" t="inlineStr">
         <is>
           <t>2026/09/22</t>
         </is>
       </c>
-      <c r="O21" s="11" t="inlineStr">
-        <is>
-          <t>HPT sku:預計8/7 MVT SMT,請BIOS RD儘速提供PI 1200i NDA版本的MSI BIOS</t>
-        </is>
-      </c>
-      <c r="P21" s="11" t="inlineStr">
+      <c r="O19" s="11" t="inlineStr">
+        <is>
+          <t>HPT sku:預計8/7 MVT SMT,8/10試組,8/12組裝</t>
+        </is>
+      </c>
+      <c r="P19" s="11" t="inlineStr">
         <is>
           <t>"
 1).Schedule:AMD PI 1200i NDA release@7/28 USA time(original 6/19,delay 39天)與工廠將MVT排程延至8/7 (original 8/4,delay 3天),因要和量產工單一起生產,因應上述時程變更,MP預計延至9/22(先前已由 9 /17提前至 8/31, 現又延至9/
@@ -2132,77 +2002,77 @@
         </is>
       </c>
     </row>
-    <row r="22" hidden="1" outlineLevel="1">
-      <c r="A22" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
+    <row r="20" hidden="1" outlineLevel="1">
+      <c r="A20" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>15TK</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Cyborg A15 Max C1PWE</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>HWK 45W</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="H20" s="9" t="inlineStr">
         <is>
           <t>2026/05/28</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr">
         <is>
           <t>2026/06/26</t>
         </is>
       </c>
-      <c r="J22" s="9" t="inlineStr"/>
-      <c r="K22" s="9" t="inlineStr">
+      <c r="J20" s="9" t="inlineStr"/>
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>2026/08/07</t>
         </is>
       </c>
-      <c r="L22" s="9" t="inlineStr">
+      <c r="L20" s="9" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="M22" s="9" t="inlineStr">
+      <c r="M20" s="9" t="inlineStr">
         <is>
           <t>2026/09/12</t>
         </is>
       </c>
-      <c r="N22" s="9" t="inlineStr">
+      <c r="N20" s="9" t="inlineStr">
         <is>
           <t>2026/09/22</t>
         </is>
       </c>
-      <c r="O22" s="11" t="inlineStr">
-        <is>
-          <t>HPT sku:預計8/7 MVT SMT,請BIOS RD儘速提供PI 1200i NDA版本的MSI BIOS</t>
-        </is>
-      </c>
-      <c r="P22" s="11" t="inlineStr">
+      <c r="O20" s="11" t="inlineStr">
+        <is>
+          <t>HPT sku:預計8/7 MVT SMT,8/10試組,8/12組裝</t>
+        </is>
+      </c>
+      <c r="P20" s="11" t="inlineStr">
         <is>
           <t>1).Schedule:AMD PI 1200i NDA release@7/28 USA time(original 6/19,delay 39天)與工廠將MVT排程延至8/7 (original 8/4,delay 3天),因要和量產工單一起生產,因應上述時程變更,MP預計延至9/22(先前已由 9 /17提前至 8/31, 現又延至9/
 22),後續將依實際測試結果滾動式調整專案時程。
@@ -2210,77 +2080,77 @@
         </is>
       </c>
     </row>
-    <row r="23" hidden="1" outlineLevel="1">
-      <c r="A23" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
+    <row r="21" hidden="1" outlineLevel="1">
+      <c r="A21" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>15TK</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Cyborg A15 C1PWE</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>HWK 45W</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>2026/05/28</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>2026/06/26</t>
         </is>
       </c>
-      <c r="J23" s="9" t="inlineStr"/>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="J21" s="9" t="inlineStr"/>
+      <c r="K21" s="9" t="inlineStr">
         <is>
           <t>2026/08/07</t>
         </is>
       </c>
-      <c r="L23" s="9" t="inlineStr">
+      <c r="L21" s="9" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="M23" s="9" t="inlineStr">
+      <c r="M21" s="9" t="inlineStr">
         <is>
           <t>2026/09/12</t>
         </is>
       </c>
-      <c r="N23" s="9" t="inlineStr">
+      <c r="N21" s="9" t="inlineStr">
         <is>
           <t>2026/09/22</t>
         </is>
       </c>
-      <c r="O23" s="11" t="inlineStr">
-        <is>
-          <t>HPT sku:預計8/7 MVT SMT,請BIOS RD儘速提供PI 1200i NDA版本的MSI BIOS</t>
-        </is>
-      </c>
-      <c r="P23" s="11" t="inlineStr">
+      <c r="O21" s="11" t="inlineStr">
+        <is>
+          <t>HPT sku:預計8/7 MVT SMT,8/10試組,8/12組裝</t>
+        </is>
+      </c>
+      <c r="P21" s="11" t="inlineStr">
         <is>
           <t>1).Schedule:AMD PI 1200i NDA release@7/28 USA time(original 6/19,delay 39天)與工廠將MVT排程延至8/7 (original 8/4,delay 3天),因要和量產工單一起生產,因應上述時程變更,MP預計延至9/22(先前已由 9 /17提前至 8/31, 現又延至9/
 22),後續將依實際測試結果滾動式調整專案時程。
@@ -2288,242 +2158,403 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>14T3</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Prestige N14 AI+ D1M</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>N1 35W</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>倪嬌嬌</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/30</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>2025/09/01</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/09</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/23</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>1)MVT1 SMT@8/13--只先安排少量for TE/BIOS/HW
+2)MVT2 SMT depend on PS Software時間, plan as 8/19</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>1) Schedule:  a. MVT拆分兩次SMT搭配PS software作驗證 b. 量產software更新時間至10/16, update ATS@11/9.
+2)備料：量產交料2.8k HQ23, 最新MP*1K交期回復在12/M（follow leading customer）交料, 與ATS start Gap 2個月, 採購協助push廠商交期中</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>2623</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Prestige N16 AI+ C1M</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>EVT</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>N1 45W</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>賴雪鳳</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/30</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>2025/09/01</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/09</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/23</t>
+        </is>
+      </c>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>N1 SoC 出貨延遲 MVT 預計延到8/13  做 MVT1 for 少數RD 測試, 待PS SW ready 再上線做MVT2 for 全部team member</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>14T3</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Prestige N14 AI+ D1M</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>MVT</t>
+          <t>Katana 18 HX A14WEK</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>EVT</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>N1 35W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>倪嬌嬌</t>
+          <t>顧曉琴</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>2025/04/30</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>2025/09/01</t>
+          <t>2026/06/15</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>2026/04/15</t>
+          <t>2026/08/12</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>2026/08/13</t>
+          <t>2026/10/12</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>2026/09/14</t>
+          <t>2026/11/02</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>2026/10/13</t>
+          <t>2026/11/21</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>2026/10/26</t>
+          <t>2026/11/30</t>
         </is>
       </c>
       <c r="O24" s="6" t="inlineStr">
         <is>
-          <t>MVT SMT@8/13--depend on PS chip &amp; Software時間作調整</t>
+          <t>RPL-HX R + DDR5: EVT SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
         </is>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>1) Schedule:  本週CPU交期還未放行, 綜合PS software時間, 先預抓8/13 MVT start.
-2)備料：量產交料2.8k HQ23, 最新MP*1K交期回復在12/M（follow leading customer）交料, 與ATS start Gap 2個月, 採購協助push廠商交期中</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" hidden="1" outlineLevel="1">
+      <c r="A25" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>2623</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Prestige N16 AI+ C1M</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Katana 18 HX A14WFK</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>EVT</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>N1 45W</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>賴雪鳳</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>2025/04/30</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>2025/09/01</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/15</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/14</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>2026/10/13</t>
-        </is>
-      </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>2026/10/26</t>
-        </is>
-      </c>
-      <c r="O25" s="6" t="inlineStr">
-        <is>
-          <t>N1 SoC 出貨延遲 MVT 預計延到8/13 SMT</t>
-        </is>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>備料: Samsung 2.8K panel 可先出HR14*1K for N1 9月ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>顧曉琴</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/12</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/12</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="M25" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/21</t>
+        </is>
+      </c>
+      <c r="N25" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="O25" s="11" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR5: EVT SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
+        </is>
+      </c>
+      <c r="P25" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" hidden="1" outlineLevel="1">
+      <c r="A26" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Katana 18 HX A14WEK</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Katana 18 HX A14WGK</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>EVT</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>2026/08/12</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>2026/10/12</t>
         </is>
       </c>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="L26" s="9" t="inlineStr">
         <is>
           <t>2026/11/02</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="M26" s="9" t="inlineStr">
         <is>
           <t>2026/11/21</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="N26" s="9" t="inlineStr">
         <is>
           <t>2026/11/30</t>
         </is>
       </c>
-      <c r="O26" s="6" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR5: 7/28 0B出圖, SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
-        </is>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
+      <c r="O26" s="11" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR5: EVT SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
+        </is>
+      </c>
+      <c r="P26" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2540,12 +2571,12 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WFK</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>EVT</t>
+          <t>Katana 18 HX A14WEOK</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -2555,7 +2586,7 @@
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
@@ -2565,22 +2596,18 @@
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J27" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/12</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="inlineStr"/>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>2026/10/12</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="L27" s="9" t="inlineStr">
@@ -2590,22 +2617,22 @@
       </c>
       <c r="M27" s="9" t="inlineStr">
         <is>
-          <t>2026/11/21</t>
+          <t>2026/11/23</t>
         </is>
       </c>
       <c r="N27" s="9" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2026/12/02</t>
         </is>
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: 7/28 0B出圖, SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P27" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -2620,12 +2647,12 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGK</t>
-        </is>
-      </c>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
-          <t>EVT</t>
+          <t>Katana 18 HX A14WFOK</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -2635,7 +2662,7 @@
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
@@ -2645,22 +2672,18 @@
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J28" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/12</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr"/>
       <c r="K28" s="9" t="inlineStr">
         <is>
-          <t>2026/10/12</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="L28" s="9" t="inlineStr">
@@ -2670,22 +2693,22 @@
       </c>
       <c r="M28" s="9" t="inlineStr">
         <is>
-          <t>2026/11/21</t>
+          <t>2026/11/23</t>
         </is>
       </c>
       <c r="N28" s="9" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2026/12/02</t>
         </is>
       </c>
       <c r="O28" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: 7/28 0B出圖, SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P28" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -2700,10 +2723,10 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WEOK</t>
-        </is>
-      </c>
-      <c r="D29" s="14" t="inlineStr">
+          <t>Katana 18 HX A14WGOK</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2715,7 +2738,7 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -2776,12 +2799,12 @@
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WFOK</t>
+          <t>Crosshair 18 Max HX B14WE</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>DVT</t>
+          <t>EVT</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -2791,7 +2814,7 @@
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
@@ -2801,15 +2824,19 @@
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J30" s="9" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/12</t>
+        </is>
+      </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -2822,22 +2849,22 @@
       </c>
       <c r="M30" s="9" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2026/11/28</t>
         </is>
       </c>
       <c r="N30" s="9" t="inlineStr">
         <is>
-          <t>2026/12/02</t>
+          <t>2026/12/07</t>
         </is>
       </c>
       <c r="O30" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+          <t>RPL-HX R + DDR5: EVT SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
         </is>
       </c>
       <c r="P30" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>系列調整，Crosshair max -&gt; Crosshair：改為塑膠A, 移除light module，EVT備料先以Katana來安排</t>
         </is>
       </c>
     </row>
@@ -2852,12 +2879,12 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGOK</t>
+          <t>Crosshair 18 Max HX B14WF</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>DVT</t>
+          <t>EVT</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -2867,7 +2894,7 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
@@ -2877,15 +2904,19 @@
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/12</t>
+        </is>
+      </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -2898,22 +2929,22 @@
       </c>
       <c r="M31" s="9" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2026/11/28</t>
         </is>
       </c>
       <c r="N31" s="9" t="inlineStr">
         <is>
-          <t>2026/12/02</t>
+          <t>2026/12/07</t>
         </is>
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+          <t>RPL-HX R + DDR5: EVT SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
         </is>
       </c>
       <c r="P31" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>系列調整，Crosshair max -&gt; Crosshair：改為塑膠A, 移除light module，EVT備料先以Katana來安排</t>
         </is>
       </c>
     </row>
@@ -2928,12 +2959,12 @@
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WEO</t>
+          <t>Crosshair 18 Max HX B14WG</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>DVT</t>
+          <t>EVT</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -2943,7 +2974,7 @@
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -2953,15 +2984,19 @@
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J32" s="9" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/12</t>
+        </is>
+      </c>
       <c r="K32" s="9" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -2984,12 +3019,12 @@
       </c>
       <c r="O32" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+          <t>RPL-HX R + DDR5: EVT SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
         </is>
       </c>
       <c r="P32" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>系列調整，Crosshair max -&gt; Crosshair：改為塑膠A, 移除light module，EVT備料先以Katana來安排</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3039,12 @@
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WFO</t>
+          <t>Crosshair 18 Max HX B14WGX</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>DVT</t>
+          <t>EVT</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -3019,7 +3054,7 @@
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
@@ -3029,15 +3064,19 @@
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J33" s="9" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/12</t>
+        </is>
+      </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3060,12 +3099,12 @@
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+          <t>RPL-HX R + DDR5: EVT SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
         </is>
       </c>
       <c r="P33" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>系列調整，Crosshair max -&gt; Crosshair：改為塑膠A, 移除light module，EVT備料先以Katana來安排</t>
         </is>
       </c>
     </row>
@@ -3080,10 +3119,10 @@
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WGO</t>
-        </is>
-      </c>
-      <c r="D34" s="14" t="inlineStr">
+          <t>Crosshair 18 Max HX B14WEO</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3095,7 +3134,7 @@
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -3156,10 +3195,10 @@
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WGXO</t>
-        </is>
-      </c>
-      <c r="D35" s="14" t="inlineStr">
+          <t>Crosshair 18 Max HX B14WFO</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3171,7 +3210,7 @@
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
@@ -3232,12 +3271,12 @@
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WE</t>
-        </is>
-      </c>
-      <c r="D36" s="13" t="inlineStr">
-        <is>
-          <t>EVT</t>
+          <t>Crosshair 18 Max HX B14WGO</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -3247,7 +3286,7 @@
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -3257,19 +3296,15 @@
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J36" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/12</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr"/>
       <c r="K36" s="9" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3292,12 +3327,12 @@
       </c>
       <c r="O36" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: 7/28 0B出圖, SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P36" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3312,12 +3347,12 @@
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WF</t>
-        </is>
-      </c>
-      <c r="D37" s="13" t="inlineStr">
-        <is>
-          <t>EVT</t>
+          <t>Crosshair 18 Max HX B14WGXO</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -3327,7 +3362,7 @@
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -3337,19 +3372,15 @@
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/12</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="inlineStr"/>
       <c r="K37" s="9" t="inlineStr">
         <is>
           <t>2026/10/20</t>
@@ -3372,12 +3403,12 @@
       </c>
       <c r="O37" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: 7/28 0B出圖, SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P37" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3392,22 +3423,22 @@
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WG</t>
-        </is>
-      </c>
-      <c r="D38" s="13" t="inlineStr">
-        <is>
-          <t>EVT</t>
+          <t>Crosshair 18 Max HX B2WE</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>RPL-HX Next 55W</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -3420,44 +3451,36 @@
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J38" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/12</t>
-        </is>
-      </c>
+      <c r="I38" s="9" t="inlineStr"/>
+      <c r="J38" s="9" t="inlineStr"/>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/12/08</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr">
         <is>
-          <t>2026/11/02</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="M38" s="9" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2027/01/19</t>
         </is>
       </c>
       <c r="N38" s="9" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="O38" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: 7/28 0B出圖, SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P38" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3472,22 +3495,22 @@
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B14WGX</t>
-        </is>
-      </c>
-      <c r="D39" s="13" t="inlineStr">
-        <is>
-          <t>EVT</t>
+          <t>Crosshair 18 Max HX B2WEO</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>RPL-HX Next 55W</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
@@ -3497,47 +3520,39 @@
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J39" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/12</t>
-        </is>
-      </c>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr"/>
+      <c r="J39" s="9" t="inlineStr"/>
       <c r="K39" s="9" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/12/08</t>
         </is>
       </c>
       <c r="L39" s="9" t="inlineStr">
         <is>
-          <t>2026/11/02</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="M39" s="9" t="inlineStr">
         <is>
-          <t>2026/11/28</t>
+          <t>2027/01/19</t>
         </is>
       </c>
       <c r="N39" s="9" t="inlineStr">
         <is>
-          <t>2026/12/07</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="O39" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: 7/28 0B出圖, SMT1 @ 8/12 SMT2 @ 8/24 for ASSY</t>
+          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P39" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3552,10 +3567,10 @@
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WE</t>
-        </is>
-      </c>
-      <c r="D40" s="15" t="inlineStr">
+          <t>Crosshair 18 Max HX B2WF</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -3567,7 +3582,7 @@
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
@@ -3624,10 +3639,10 @@
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WEO</t>
-        </is>
-      </c>
-      <c r="D41" s="15" t="inlineStr">
+          <t>Crosshair 18 Max HX B2WFO</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -3639,7 +3654,7 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -3696,10 +3711,10 @@
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WF</t>
-        </is>
-      </c>
-      <c r="D42" s="15" t="inlineStr">
+          <t>Crosshair 18 Max HX B2WG</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -3711,7 +3726,7 @@
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -3768,10 +3783,10 @@
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WFO</t>
-        </is>
-      </c>
-      <c r="D43" s="15" t="inlineStr">
+          <t>Crosshair 18 Max HX B2WGO</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -3783,7 +3798,7 @@
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -3840,10 +3855,10 @@
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WG</t>
-        </is>
-      </c>
-      <c r="D44" s="15" t="inlineStr">
+          <t>Crosshair 18 Max HX B2WGX</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -3912,10 +3927,10 @@
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WGO</t>
-        </is>
-      </c>
-      <c r="D45" s="15" t="inlineStr">
+          <t>Crosshair 18 Max HX B2WGXO</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -3984,10 +3999,10 @@
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WGX</t>
-        </is>
-      </c>
-      <c r="D46" s="15" t="inlineStr">
+          <t>Katana 18 HX A2WEK</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -3999,7 +4014,7 @@
       </c>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G46" s="9" t="inlineStr">
@@ -4056,10 +4071,10 @@
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 18 Max HX B2WGXO</t>
-        </is>
-      </c>
-      <c r="D47" s="15" t="inlineStr">
+          <t>Katana 18 HX A2WEOK</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4071,7 +4086,7 @@
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G47" s="9" t="inlineStr">
@@ -4084,7 +4099,11 @@
           <t>2026/05/20</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr"/>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
       <c r="J47" s="9" t="inlineStr"/>
       <c r="K47" s="9" t="inlineStr">
         <is>
@@ -4108,7 +4127,7 @@
       </c>
       <c r="O47" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P47" s="11" t="inlineStr">
@@ -4128,10 +4147,10 @@
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WEK</t>
-        </is>
-      </c>
-      <c r="D48" s="15" t="inlineStr">
+          <t>Katana 18 HX A2WFK</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4143,7 +4162,7 @@
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
@@ -4200,10 +4219,10 @@
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WEOK</t>
-        </is>
-      </c>
-      <c r="D49" s="15" t="inlineStr">
+          <t>Katana 18 HX A2WFOK</t>
+        </is>
+      </c>
+      <c r="D49" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4215,7 +4234,7 @@
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G49" s="9" t="inlineStr">
@@ -4276,10 +4295,10 @@
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WFK</t>
-        </is>
-      </c>
-      <c r="D50" s="15" t="inlineStr">
+          <t>Katana 18 HX A2WGK</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4291,7 +4310,7 @@
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G50" s="9" t="inlineStr">
@@ -4348,10 +4367,10 @@
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WFOK</t>
-        </is>
-      </c>
-      <c r="D51" s="15" t="inlineStr">
+          <t>Katana 18 HX A2WGOK</t>
+        </is>
+      </c>
+      <c r="D51" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4363,7 +4382,7 @@
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G51" s="9" t="inlineStr">
@@ -4413,75 +4432,83 @@
         </is>
       </c>
     </row>
-    <row r="52" hidden="1" outlineLevel="1">
-      <c r="A52" s="7" t="n">
+    <row r="52">
+      <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>Katana 18 HX A2WGK</t>
-        </is>
-      </c>
-      <c r="D52" s="15" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>RPL-HX Next 55W</t>
-        </is>
-      </c>
-      <c r="F52" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G52" s="9" t="inlineStr">
-        <is>
-          <t>顧曉琴</t>
-        </is>
-      </c>
-      <c r="H52" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I52" s="9" t="inlineStr"/>
-      <c r="J52" s="9" t="inlineStr"/>
-      <c r="K52" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/08</t>
-        </is>
-      </c>
-      <c r="L52" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/30</t>
-        </is>
-      </c>
-      <c r="M52" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/19</t>
-        </is>
-      </c>
-      <c r="N52" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/30</t>
-        </is>
-      </c>
-      <c r="O52" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
-        </is>
-      </c>
-      <c r="P52" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>14T4</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Prestige 14 AI+ D4MG</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>NVL-H 30W</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>朱芳芳</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/04</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/20</t>
+        </is>
+      </c>
+      <c r="M52" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/15</t>
+        </is>
+      </c>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/25</t>
+        </is>
+      </c>
+      <c r="O52" s="6" t="inlineStr">
+        <is>
+          <t>DVT 開機OK， RD test :8/4~8/31</t>
+        </is>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4491,73 +4518,77 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>14T4</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WGOK</t>
+          <t>Prestige 14 Flip AI+ D4MTG</t>
         </is>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX Next 55W</t>
+          <t>NVL-H 30W</t>
         </is>
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>顧曉琴</t>
+          <t>朱芳芳</t>
         </is>
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/14</t>
         </is>
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J53" s="9" t="inlineStr"/>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/15</t>
+        </is>
+      </c>
       <c r="K53" s="9" t="inlineStr">
         <is>
-          <t>2026/12/08</t>
+          <t>2026/11/04</t>
         </is>
       </c>
       <c r="L53" s="9" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/11/20</t>
         </is>
       </c>
       <c r="M53" s="9" t="inlineStr">
         <is>
-          <t>2027/01/19</t>
+          <t>2026/12/15</t>
         </is>
       </c>
       <c r="N53" s="9" t="inlineStr">
         <is>
-          <t>2027/01/30</t>
+          <t>2026/12/25</t>
         </is>
       </c>
       <c r="O53" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>DVT 開機OK， RD test :8/4~8/31</t>
         </is>
       </c>
       <c r="P53" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4567,15 +4598,15 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>14T4</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Prestige 14 AI</t>
-        </is>
-      </c>
-      <c r="D54" s="16" t="inlineStr">
+          <t>Prestige 16 AI+</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -4600,11 +4631,7 @@
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="I54" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
+      <c r="I54" s="4" t="inlineStr"/>
       <c r="J54" s="4" t="inlineStr">
         <is>
           <t>2026/09/15</t>
@@ -4647,15 +4674,15 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>14T4</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Prestige 14 AI+ Flip</t>
-        </is>
-      </c>
-      <c r="D55" s="14" t="inlineStr">
+          <t>Prestige 16 Flip AI+</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -4680,11 +4707,7 @@
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="I55" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
+      <c r="I55" s="9" t="inlineStr"/>
       <c r="J55" s="9" t="inlineStr">
         <is>
           <t>2026/09/15</t>
@@ -4727,22 +4750,22 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>13Q5</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Prestige 16 AI+</t>
-        </is>
-      </c>
-      <c r="D56" s="16" t="inlineStr">
+          <t>Prestige 13 AI+ A4M</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>NVL-H 30W</t>
+          <t>NVL-H 28W</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -4752,43 +4775,47 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>朱芳芳</t>
+          <t>顏春梅</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>2026/05/14</t>
-        </is>
-      </c>
-      <c r="I56" s="4" t="inlineStr"/>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>2026/09/15</t>
+          <t>2026/10/08</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>2026/11/04</t>
+          <t>2026/11/21</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>2026/11/20</t>
+          <t>2026/11/22</t>
         </is>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>2026/12/15</t>
+          <t>2026/12/22</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>2026/12/25</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="O56" s="6" t="inlineStr">
         <is>
-          <t>DVT 開機OK， RD test :8/4~8/31</t>
+          <t>0A G/O@8/7，DVT SMT@8/18</t>
         </is>
       </c>
       <c r="P56" s="6" t="inlineStr">
@@ -4797,321 +4824,325 @@
         </is>
       </c>
     </row>
-    <row r="57" hidden="1" outlineLevel="1">
-      <c r="A57" s="7" t="n">
+    <row r="57">
+      <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>2624</t>
-        </is>
-      </c>
-      <c r="C57" s="9" t="inlineStr">
-        <is>
-          <t>Prestige 16 Flip AI+</t>
-        </is>
-      </c>
-      <c r="D57" s="14" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>2633</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WI</t>
+        </is>
+      </c>
+      <c r="D57" s="17" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>NVL-H 30W</t>
-        </is>
-      </c>
-      <c r="F57" s="9" t="inlineStr">
-        <is>
-          <t>Intel® Arc™ Graphics</t>
-        </is>
-      </c>
-      <c r="G57" s="9" t="inlineStr">
-        <is>
-          <t>朱芳芳</t>
-        </is>
-      </c>
-      <c r="H57" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/14</t>
-        </is>
-      </c>
-      <c r="I57" s="9" t="inlineStr"/>
-      <c r="J57" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/15</t>
-        </is>
-      </c>
-      <c r="K57" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/04</t>
-        </is>
-      </c>
-      <c r="L57" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/20</t>
-        </is>
-      </c>
-      <c r="M57" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/15</t>
-        </is>
-      </c>
-      <c r="N57" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/25</t>
-        </is>
-      </c>
-      <c r="O57" s="11" t="inlineStr">
-        <is>
-          <t>DVT 開機OK， RD test :8/4~8/31</t>
-        </is>
-      </c>
-      <c r="P57" s="11" t="inlineStr">
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5080</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/23</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="O57" s="6" t="inlineStr">
+        <is>
+          <t>RD 測試中</t>
+        </is>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>1）B07-669945C-T07，FW 燒錄在2654上驗證;
+2) Schedule:NV VBIOS @1/6, gating 8天,預計12/E 拿到WHQL，可能影響到最終TTM 時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" hidden="1" outlineLevel="1">
+      <c r="A58" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>2633</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WH</t>
+        </is>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/23</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K58" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L58" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="M58" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N58" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="O58" s="11" t="inlineStr">
+        <is>
+          <t>RD 測試中</t>
+        </is>
+      </c>
+      <c r="P58" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>13Q5</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>Prestige 13 AI+ A4M</t>
-        </is>
-      </c>
-      <c r="D58" s="17" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>NVL-H 28W</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>Intel® Arc™ Graphics</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>顏春梅</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="I58" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/18</t>
-        </is>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>2026/10/08</t>
-        </is>
-      </c>
-      <c r="K58" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/21</t>
-        </is>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/22</t>
-        </is>
-      </c>
-      <c r="M58" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/22</t>
-        </is>
-      </c>
-      <c r="N58" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/31</t>
-        </is>
-      </c>
-      <c r="O58" s="6" t="inlineStr">
-        <is>
-          <t>0A layout 中 0A G/O@8/7</t>
-        </is>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
+    <row r="59" hidden="1" outlineLevel="1">
+      <c r="A59" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>2633</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WJ</t>
+        </is>
+      </c>
+      <c r="D59" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5090</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/23</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L59" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="M59" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N59" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="O59" s="11" t="inlineStr">
+        <is>
+          <t>RD 測試中</t>
+        </is>
+      </c>
+      <c r="P59" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WI</t>
-        </is>
-      </c>
-      <c r="D59" s="16" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WE</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5080</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>賴雪鳳</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/23</t>
-        </is>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/31</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K59" s="4" t="inlineStr">
+      <c r="K60" s="4" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/30</t>
-        </is>
-      </c>
-      <c r="M59" s="4" t="inlineStr">
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/27</t>
+        </is>
+      </c>
+      <c r="M60" s="4" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N59" s="4" t="inlineStr">
+      <c r="N60" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O59" s="6" t="inlineStr">
-        <is>
-          <t>RD debug中 (PCBA僅HDMI會顯示)</t>
-        </is>
-      </c>
-      <c r="P59" s="6" t="inlineStr">
-        <is>
-          <t>1)目前0M PCBA開機,但目前僅HDMI會顯示，0N geberout@8/25，請RD幫忙盡快debug;
-2) B07-669945C-T07，FW 燒錄不上，待治具更新軟體;
-3) Schedule:NV VBIOS @1/6, gating 8天,預計12/E 拿到WHQL，可能影響到最終TTM 時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" hidden="1" outlineLevel="1">
-      <c r="A60" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="C60" s="9" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WH</t>
-        </is>
-      </c>
-      <c r="D60" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E60" s="9" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F60" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070Ti</t>
-        </is>
-      </c>
-      <c r="G60" s="9" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H60" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/23</t>
-        </is>
-      </c>
-      <c r="J60" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K60" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L60" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/30</t>
-        </is>
-      </c>
-      <c r="M60" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N60" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="O60" s="11" t="inlineStr">
-        <is>
-          <t>RD debug中 (PCBA僅HDMI會顯示)</t>
-        </is>
-      </c>
-      <c r="P60" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="O60" s="6" t="inlineStr">
+        <is>
+          <t>0A PCBA DVT 驗證中,預計9/2 0B 出圖</t>
+        </is>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>1)NV VBIOS 驗證時間6周
+2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
     </row>
@@ -5121,15 +5152,15 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WJ</t>
-        </is>
-      </c>
-      <c r="D61" s="14" t="inlineStr">
+          <t>Stealth 16 AI+ B4WF</t>
+        </is>
+      </c>
+      <c r="D61" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -5141,12 +5172,12 @@
       </c>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="H61" s="9" t="inlineStr">
@@ -5156,7 +5187,7 @@
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
-          <t>2026/07/23</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="J61" s="9" t="inlineStr">
@@ -5171,7 +5202,7 @@
       </c>
       <c r="L61" s="9" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2026/11/27</t>
         </is>
       </c>
       <c r="M61" s="9" t="inlineStr">
@@ -5186,90 +5217,91 @@
       </c>
       <c r="O61" s="11" t="inlineStr">
         <is>
-          <t>RD debug中 (PCBA僅HDMI會顯示)</t>
+          <t>0A PCBA DVT 驗證中,預計9/2 0B 出圖</t>
         </is>
       </c>
       <c r="P61" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
+          <t>1)NV VBIOS 驗證時間6周
+2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" hidden="1" outlineLevel="1">
+      <c r="A62" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>2634</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WE</t>
-        </is>
-      </c>
-      <c r="D62" s="17" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
+        </is>
+      </c>
+      <c r="D62" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
         <is>
           <t>賴雪鳳</t>
         </is>
       </c>
-      <c r="H62" s="4" t="inlineStr">
+      <c r="H62" s="9" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I62" s="4" t="inlineStr">
+      <c r="I62" s="9" t="inlineStr">
         <is>
           <t>2026/07/31</t>
         </is>
       </c>
-      <c r="J62" s="4" t="inlineStr">
+      <c r="J62" s="9" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K62" s="4" t="inlineStr">
+      <c r="K62" s="9" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L62" s="4" t="inlineStr">
+      <c r="L62" s="9" t="inlineStr">
         <is>
           <t>2026/11/27</t>
         </is>
       </c>
-      <c r="M62" s="4" t="inlineStr">
+      <c r="M62" s="9" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N62" s="4" t="inlineStr">
+      <c r="N62" s="9" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O62" s="6" t="inlineStr">
-        <is>
-          <t>0A 7/31 SMT</t>
-        </is>
-      </c>
-      <c r="P62" s="6" t="inlineStr">
+      <c r="O62" s="11" t="inlineStr">
+        <is>
+          <t>0A PCBA DVT 驗證中,預計9/2 0B 出圖</t>
+        </is>
+      </c>
+      <c r="P62" s="11" t="inlineStr">
         <is>
           <t>1)NV VBIOS 驗證時間6周
 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
@@ -5287,12 +5319,12 @@
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WF</t>
+          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
         </is>
       </c>
       <c r="D63" s="15" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
@@ -5302,7 +5334,7 @@
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G63" s="9" t="inlineStr">
@@ -5347,7 +5379,7 @@
       </c>
       <c r="O63" s="11" t="inlineStr">
         <is>
-          <t>0A 7/31 SMT</t>
+          <t>0A PCBA DVT 驗證中,預計9/2 0B 出圖</t>
         </is>
       </c>
       <c r="P63" s="11" t="inlineStr">
@@ -5357,84 +5389,83 @@
         </is>
       </c>
     </row>
-    <row r="64" hidden="1" outlineLevel="1">
-      <c r="A64" s="7" t="n">
+    <row r="64">
+      <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="C64" s="9" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
-        </is>
-      </c>
-      <c r="D64" s="15" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>2656</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Raider 16 HX B14WH</t>
+        </is>
+      </c>
+      <c r="D64" s="18" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E64" s="9" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F64" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G64" s="9" t="inlineStr">
-        <is>
-          <t>賴雪鳳</t>
-        </is>
-      </c>
-      <c r="H64" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/31</t>
-        </is>
-      </c>
-      <c r="J64" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K64" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L64" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/27</t>
-        </is>
-      </c>
-      <c r="M64" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N64" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="O64" s="11" t="inlineStr">
-        <is>
-          <t>0A 7/31 SMT</t>
-        </is>
-      </c>
-      <c r="P64" s="11" t="inlineStr">
-        <is>
-          <t>1)NV VBIOS 驗證時間6周
-2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>RPL-HX Next 55W</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>吳美芳</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/24</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/21</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/08</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/25</t>
+        </is>
+      </c>
+      <c r="M64" s="4" t="inlineStr">
+        <is>
+          <t>2027/01/25</t>
+        </is>
+      </c>
+      <c r="N64" s="4" t="inlineStr">
+        <is>
+          <t>2027/02/04</t>
+        </is>
+      </c>
+      <c r="O64" s="6" t="inlineStr">
+        <is>
+          <t>7/24 Kick off，預計0M gerberout 8/28</t>
+        </is>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -5444,236 +5475,235 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
-        </is>
-      </c>
-      <c r="D65" s="15" t="inlineStr">
+          <t>Raider 16 HX B14WI</t>
+        </is>
+      </c>
+      <c r="D65" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>NVL-H 45W</t>
+          <t>RPL-HX Next 55W</t>
         </is>
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
-          <t>2026/05/22</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
-          <t>2026/07/31</t>
+          <t>2026/09/08</t>
         </is>
       </c>
       <c r="J65" s="9" t="inlineStr">
         <is>
-          <t>2026/09/16</t>
+          <t>2026/10/21</t>
         </is>
       </c>
       <c r="K65" s="9" t="inlineStr">
         <is>
-          <t>2026/11/11</t>
+          <t>2026/12/08</t>
         </is>
       </c>
       <c r="L65" s="9" t="inlineStr">
         <is>
-          <t>2026/11/27</t>
+          <t>2026/12/25</t>
         </is>
       </c>
       <c r="M65" s="9" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2027/01/25</t>
         </is>
       </c>
       <c r="N65" s="9" t="inlineStr">
         <is>
+          <t>2027/02/04</t>
+        </is>
+      </c>
+      <c r="O65" s="11" t="inlineStr">
+        <is>
+          <t>7/24 Kick off，預計0M gerberout 8/28</t>
+        </is>
+      </c>
+      <c r="P65" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" hidden="1" outlineLevel="1">
+      <c r="A66" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>2656</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>Raider 16 HX B14WJ</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>RPL-HX Next 55W</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5090</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>吳美芳</t>
+        </is>
+      </c>
+      <c r="H66" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/24</t>
+        </is>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/08</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/21</t>
+        </is>
+      </c>
+      <c r="K66" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/08</t>
+        </is>
+      </c>
+      <c r="L66" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/25</t>
+        </is>
+      </c>
+      <c r="M66" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/25</t>
+        </is>
+      </c>
+      <c r="N66" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/04</t>
+        </is>
+      </c>
+      <c r="O66" s="11" t="inlineStr">
+        <is>
+          <t>7/24 Kick off，預計0M gerberout 8/28</t>
+        </is>
+      </c>
+      <c r="P66" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>2654</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Raider 16 Max HX B4WH</t>
+        </is>
+      </c>
+      <c r="D67" s="17" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>吳美芳</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O65" s="11" t="inlineStr">
-        <is>
-          <t>0A 7/31 SMT</t>
-        </is>
-      </c>
-      <c r="P65" s="11" t="inlineStr">
-        <is>
-          <t>1)NV VBIOS 驗證時間6周
-2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>2656</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>Raider 16 HX B14WH</t>
-        </is>
-      </c>
-      <c r="D66" s="17" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>RPL-HX Next 55W</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5070Ti</t>
-        </is>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>吳美芳</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/24</t>
-        </is>
-      </c>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/08</t>
-        </is>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>2026/10/21</t>
-        </is>
-      </c>
-      <c r="K66" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/08</t>
-        </is>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/25</t>
-        </is>
-      </c>
-      <c r="M66" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/25</t>
-        </is>
-      </c>
-      <c r="N66" s="4" t="inlineStr">
-        <is>
-          <t>2027/02/04</t>
-        </is>
-      </c>
-      <c r="O66" s="6" t="inlineStr">
-        <is>
-          <t>7/24 Kick off，預計0M gerberout 8/28</t>
-        </is>
-      </c>
-      <c r="P66" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" hidden="1" outlineLevel="1">
-      <c r="A67" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>2656</t>
-        </is>
-      </c>
-      <c r="C67" s="9" t="inlineStr">
-        <is>
-          <t>Raider 16 HX B14WI</t>
-        </is>
-      </c>
-      <c r="D67" s="15" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E67" s="9" t="inlineStr">
-        <is>
-          <t>RPL-HX Next 55W</t>
-        </is>
-      </c>
-      <c r="F67" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5080</t>
-        </is>
-      </c>
-      <c r="G67" s="9" t="inlineStr">
-        <is>
-          <t>吳美芳</t>
-        </is>
-      </c>
-      <c r="H67" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/24</t>
-        </is>
-      </c>
-      <c r="I67" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/08</t>
-        </is>
-      </c>
-      <c r="J67" s="9" t="inlineStr">
-        <is>
-          <t>2026/10/21</t>
-        </is>
-      </c>
-      <c r="K67" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/08</t>
-        </is>
-      </c>
-      <c r="L67" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/25</t>
-        </is>
-      </c>
-      <c r="M67" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/25</t>
-        </is>
-      </c>
-      <c r="N67" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/04</t>
-        </is>
-      </c>
-      <c r="O67" s="11" t="inlineStr">
-        <is>
-          <t>7/24 Kick off，預計0M gerberout 8/28</t>
-        </is>
-      </c>
-      <c r="P67" s="11" t="inlineStr">
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M67" s="4" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N67" s="4" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O67" s="6" t="inlineStr">
+        <is>
+          <t>8/5 DVT打板已入库, 下周一调拨回台for RD test</t>
+        </is>
+      </c>
+      <c r="P67" s="6" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -5685,237 +5715,237 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>2656</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Raider 16 HX B14WJ</t>
+          <t>Raider 16 Max HX B4WI</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5080</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>吳美芳</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K68" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="L68" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M68" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N68" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O68" s="11" t="inlineStr">
+        <is>
+          <t>8/5 DVT打板已入库, 下周一调拨回台for RD test</t>
+        </is>
+      </c>
+      <c r="P68" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" hidden="1" outlineLevel="1">
+      <c r="A69" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>2654</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>Raider 16 Max HX B4WJ</t>
+        </is>
+      </c>
+      <c r="D69" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5090</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>吳美芳</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K69" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="L69" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M69" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N69" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O69" s="11" t="inlineStr">
+        <is>
+          <t>8/5 DVT打板已入库, 下周一调拨回台for RD test</t>
+        </is>
+      </c>
+      <c r="P69" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Titan 18 HX B4WH</t>
+        </is>
+      </c>
+      <c r="D70" s="18" t="inlineStr">
+        <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E68" s="9" t="inlineStr">
-        <is>
-          <t>RPL-HX Next 55W</t>
-        </is>
-      </c>
-      <c r="F68" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5090</t>
-        </is>
-      </c>
-      <c r="G68" s="9" t="inlineStr">
-        <is>
-          <t>吳美芳</t>
-        </is>
-      </c>
-      <c r="H68" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/24</t>
-        </is>
-      </c>
-      <c r="I68" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/08</t>
-        </is>
-      </c>
-      <c r="J68" s="9" t="inlineStr">
-        <is>
-          <t>2026/10/21</t>
-        </is>
-      </c>
-      <c r="K68" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/08</t>
-        </is>
-      </c>
-      <c r="L68" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/25</t>
-        </is>
-      </c>
-      <c r="M68" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/25</t>
-        </is>
-      </c>
-      <c r="N68" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/04</t>
-        </is>
-      </c>
-      <c r="O68" s="11" t="inlineStr">
-        <is>
-          <t>7/24 Kick off，預計0M gerberout 8/28</t>
-        </is>
-      </c>
-      <c r="P68" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>2654</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>Raider 16 Max HX B4WH</t>
-        </is>
-      </c>
-      <c r="D69" s="16" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="F70" s="4" t="inlineStr">
         <is>
           <t>RTX 5070Ti</t>
         </is>
       </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>吳美芳</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I69" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/05</t>
-        </is>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K69" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M69" s="4" t="inlineStr">
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>高宇奇</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/23</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>2027/01/08</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>2027/02/01</t>
+        </is>
+      </c>
+      <c r="M70" s="4" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N69" s="4" t="inlineStr">
+      <c r="N70" s="4" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O69" s="6" t="inlineStr">
-        <is>
-          <t>预计8/5 DVT打板</t>
-        </is>
-      </c>
-      <c r="P69" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" hidden="1" outlineLevel="1">
-      <c r="A70" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>2654</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="inlineStr">
-        <is>
-          <t>Raider 16 Max HX B4WI</t>
-        </is>
-      </c>
-      <c r="D70" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E70" s="9" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F70" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5080</t>
-        </is>
-      </c>
-      <c r="G70" s="9" t="inlineStr">
-        <is>
-          <t>吳美芳</t>
-        </is>
-      </c>
-      <c r="H70" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I70" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/05</t>
-        </is>
-      </c>
-      <c r="J70" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K70" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L70" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M70" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N70" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O70" s="11" t="inlineStr">
-        <is>
-          <t>预计8/5 DVT打板</t>
-        </is>
-      </c>
-      <c r="P70" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="O70" s="6" t="inlineStr">
+        <is>
+          <t>PCB 0M已於8/4 gerber out,預計8/19 DVT SMT.</t>
+        </is>
+      </c>
+      <c r="P70" s="6" t="inlineStr">
+        <is>
+          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
         </is>
       </c>
     </row>
@@ -5925,17 +5955,17 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B4WJ</t>
-        </is>
-      </c>
-      <c r="D71" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Titan 18 HX B4WI</t>
+        </is>
+      </c>
+      <c r="D71" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
@@ -5945,137 +5975,137 @@
       </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
+          <t>RTX 5080</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>高宇奇</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/23</t>
+        </is>
+      </c>
+      <c r="K71" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/08</t>
+        </is>
+      </c>
+      <c r="L71" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/01</t>
+        </is>
+      </c>
+      <c r="M71" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N71" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O71" s="11" t="inlineStr">
+        <is>
+          <t>PCB 0M已於8/4 gerber out,預計8/19 DVT SMT.</t>
+        </is>
+      </c>
+      <c r="P71" s="11" t="inlineStr">
+        <is>
+          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" hidden="1" outlineLevel="1">
+      <c r="A72" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>Titan 18 HX B4WJ</t>
+        </is>
+      </c>
+      <c r="D72" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
           <t>RTX 5090</t>
         </is>
       </c>
-      <c r="G71" s="9" t="inlineStr">
-        <is>
-          <t>吳美芳</t>
-        </is>
-      </c>
-      <c r="H71" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/05</t>
-        </is>
-      </c>
-      <c r="J71" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K71" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L71" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M71" s="9" t="inlineStr">
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>高宇奇</t>
+        </is>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/23</t>
+        </is>
+      </c>
+      <c r="K72" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/08</t>
+        </is>
+      </c>
+      <c r="L72" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/01</t>
+        </is>
+      </c>
+      <c r="M72" s="9" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N71" s="9" t="inlineStr">
+      <c r="N72" s="9" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O71" s="11" t="inlineStr">
-        <is>
-          <t>预计8/5 DVT打板</t>
-        </is>
-      </c>
-      <c r="P71" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>2655</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>Raider 16 HX B4WE</t>
-        </is>
-      </c>
-      <c r="D72" s="16" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>鮑佩佩</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I72" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/06</t>
-        </is>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K72" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L72" s="4" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M72" s="4" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N72" s="4" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O72" s="6" t="inlineStr">
-        <is>
-          <t>8/6  DVT SMT</t>
-        </is>
-      </c>
-      <c r="P72" s="6" t="inlineStr">
-        <is>
-          <t>由raider改回crosshair，待確認 final SPEC&amp;ID color plan，對schedule 影響TBD</t>
+      <c r="O72" s="11" t="inlineStr">
+        <is>
+          <t>PCB 0M已於8/4 gerber out,預計8/19 DVT SMT.</t>
+        </is>
+      </c>
+      <c r="P72" s="11" t="inlineStr">
+        <is>
+          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
         </is>
       </c>
     </row>
@@ -6085,57 +6115,57 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Raider 16 HX B4WF</t>
-        </is>
-      </c>
-      <c r="D73" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Raider 18 Max HX B4WH</t>
+        </is>
+      </c>
+      <c r="D73" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>NVL-HX 55W</t>
+          <t>NVL-HX 65W</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="G73" s="9" t="inlineStr">
         <is>
-          <t>鮑佩佩</t>
+          <t>高宇奇</t>
         </is>
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/06/29</t>
         </is>
       </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
-          <t>2026/08/06</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="J73" s="9" t="inlineStr">
         <is>
-          <t>2026/09/29</t>
+          <t>2026/10/23</t>
         </is>
       </c>
       <c r="K73" s="9" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="L73" s="9" t="inlineStr">
         <is>
-          <t>2027/02/02</t>
+          <t>2027/02/01</t>
         </is>
       </c>
       <c r="M73" s="9" t="inlineStr">
@@ -6150,12 +6180,12 @@
       </c>
       <c r="O73" s="11" t="inlineStr">
         <is>
-          <t>8/6  DVT SMT</t>
+          <t>PCB 0M已於8/4 gerber out,預計8/19 DVT SMT.</t>
         </is>
       </c>
       <c r="P73" s="11" t="inlineStr">
         <is>
-          <t>由raider改回crosshair，待確認 final SPEC&amp;ID color plan，對schedule 影響TBD</t>
+          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
         </is>
       </c>
     </row>
@@ -6165,57 +6195,57 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Raider 16 HX B4WG</t>
-        </is>
-      </c>
-      <c r="D74" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Raider 18 Max HX B4WI</t>
+        </is>
+      </c>
+      <c r="D74" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>NVL-HX 55W</t>
+          <t>NVL-HX 65W</t>
         </is>
       </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>鮑佩佩</t>
+          <t>高宇奇</t>
         </is>
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/06/29</t>
         </is>
       </c>
       <c r="I74" s="9" t="inlineStr">
         <is>
-          <t>2026/08/06</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="J74" s="9" t="inlineStr">
         <is>
-          <t>2026/09/29</t>
+          <t>2026/10/23</t>
         </is>
       </c>
       <c r="K74" s="9" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="L74" s="9" t="inlineStr">
         <is>
-          <t>2027/02/02</t>
+          <t>2027/02/01</t>
         </is>
       </c>
       <c r="M74" s="9" t="inlineStr">
@@ -6230,12 +6260,12 @@
       </c>
       <c r="O74" s="11" t="inlineStr">
         <is>
-          <t>8/6  DVT SMT</t>
+          <t>PCB 0M已於8/4 gerber out,預計8/19 DVT SMT.</t>
         </is>
       </c>
       <c r="P74" s="11" t="inlineStr">
         <is>
-          <t>由raider改回crosshair，待確認 final SPEC&amp;ID color plan，對schedule 影響TBD</t>
+          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
         </is>
       </c>
     </row>
@@ -6245,57 +6275,57 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Raider 16 HX B4WGX</t>
-        </is>
-      </c>
-      <c r="D75" s="14" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Raider 18 Max HX B4WJ</t>
+        </is>
+      </c>
+      <c r="D75" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>NVL-HX 55W</t>
+          <t>NVL-HX 65W</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="G75" s="9" t="inlineStr">
         <is>
-          <t>鮑佩佩</t>
+          <t>高宇奇</t>
         </is>
       </c>
       <c r="H75" s="9" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/06/29</t>
         </is>
       </c>
       <c r="I75" s="9" t="inlineStr">
         <is>
-          <t>2026/08/06</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="J75" s="9" t="inlineStr">
         <is>
-          <t>2026/09/29</t>
+          <t>2026/10/23</t>
         </is>
       </c>
       <c r="K75" s="9" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="L75" s="9" t="inlineStr">
         <is>
-          <t>2027/02/02</t>
+          <t>2027/02/01</t>
         </is>
       </c>
       <c r="M75" s="9" t="inlineStr">
@@ -6310,12 +6340,12 @@
       </c>
       <c r="O75" s="11" t="inlineStr">
         <is>
-          <t>8/6  DVT SMT</t>
+          <t>PCB 0M已於8/4 gerber out,預計8/19 DVT SMT.</t>
         </is>
       </c>
       <c r="P75" s="11" t="inlineStr">
         <is>
-          <t>由raider改回crosshair，待確認 final SPEC&amp;ID color plan，對schedule 影響TBD</t>
+          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
         </is>
       </c>
     </row>
@@ -6325,17 +6355,17 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Titan 18 HX B4WH</t>
+          <t>Crosshair 16 Max HX E4WEK</t>
         </is>
       </c>
       <c r="D76" s="17" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -6345,37 +6375,37 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>高宇奇</t>
+          <t>鮑佩佩</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>2026/10/23</t>
+          <t>2026/09/29</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>2027/01/08</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>2027/02/01</t>
+          <t>2027/02/02</t>
         </is>
       </c>
       <c r="M76" s="4" t="inlineStr">
@@ -6390,12 +6420,12 @@
       </c>
       <c r="O76" s="6" t="inlineStr">
         <is>
-          <t>製程DFM修改需求,0M gerber out變更為8/4,暫不影響後續EVT schedule.</t>
+          <t>8/6 DVT SMT</t>
         </is>
       </c>
       <c r="P76" s="6" t="inlineStr">
         <is>
-          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
+          <t>由 Raider改回Crosshair Max with D件快拆門</t>
         </is>
       </c>
     </row>
@@ -6405,17 +6435,17 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Titan 18 HX B4WI</t>
+          <t>Crosshair 16 Max HX E4WFK</t>
         </is>
       </c>
       <c r="D77" s="15" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
@@ -6425,37 +6455,37 @@
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
-          <t>高宇奇</t>
+          <t>鮑佩佩</t>
         </is>
       </c>
       <c r="H77" s="9" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="J77" s="9" t="inlineStr">
         <is>
-          <t>2026/10/23</t>
+          <t>2026/09/29</t>
         </is>
       </c>
       <c r="K77" s="9" t="inlineStr">
         <is>
-          <t>2027/01/08</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="L77" s="9" t="inlineStr">
         <is>
-          <t>2027/02/01</t>
+          <t>2027/02/02</t>
         </is>
       </c>
       <c r="M77" s="9" t="inlineStr">
@@ -6470,12 +6500,12 @@
       </c>
       <c r="O77" s="11" t="inlineStr">
         <is>
-          <t>製程DFM修改需求,0M gerber out變更為8/4,暫不影響後續EVT schedule.</t>
+          <t>8/6 DVT SMT</t>
         </is>
       </c>
       <c r="P77" s="11" t="inlineStr">
         <is>
-          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
+          <t>由 Raider改回Crosshair Max with D件快拆門</t>
         </is>
       </c>
     </row>
@@ -6485,17 +6515,17 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Titan 18 HX B4WJ</t>
+          <t>Crosshair 16 Max HX E4WGK</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
@@ -6505,37 +6535,37 @@
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>高宇奇</t>
+          <t>鮑佩佩</t>
         </is>
       </c>
       <c r="H78" s="9" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="I78" s="9" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>2026/10/23</t>
+          <t>2026/09/29</t>
         </is>
       </c>
       <c r="K78" s="9" t="inlineStr">
         <is>
-          <t>2027/01/08</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="L78" s="9" t="inlineStr">
         <is>
-          <t>2027/02/01</t>
+          <t>2027/02/02</t>
         </is>
       </c>
       <c r="M78" s="9" t="inlineStr">
@@ -6550,12 +6580,12 @@
       </c>
       <c r="O78" s="11" t="inlineStr">
         <is>
-          <t>製程DFM修改需求,0M gerber out變更為8/4,暫不影響後續EVT schedule.</t>
+          <t>8/6 DVT SMT</t>
         </is>
       </c>
       <c r="P78" s="11" t="inlineStr">
         <is>
-          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
+          <t>由 Raider改回Crosshair Max with D件快拆門</t>
         </is>
       </c>
     </row>
@@ -6565,57 +6595,57 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Raider 18 Max HX B4WH</t>
+          <t>Crosshair 16 Max HX E4WGXK</t>
         </is>
       </c>
       <c r="D79" s="15" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>NVL-HX 65W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>高宇奇</t>
+          <t>鮑佩佩</t>
         </is>
       </c>
       <c r="H79" s="9" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="J79" s="9" t="inlineStr">
         <is>
-          <t>2026/10/23</t>
+          <t>2026/09/29</t>
         </is>
       </c>
       <c r="K79" s="9" t="inlineStr">
         <is>
-          <t>2027/01/08</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="L79" s="9" t="inlineStr">
         <is>
-          <t>2027/02/01</t>
+          <t>2027/02/02</t>
         </is>
       </c>
       <c r="M79" s="9" t="inlineStr">
@@ -6630,177 +6660,17 @@
       </c>
       <c r="O79" s="11" t="inlineStr">
         <is>
-          <t>製程DFM修改需求,0M gerber out變更為8/4,暫不影響後續EVT schedule.</t>
+          <t>8/6 DVT SMT</t>
         </is>
       </c>
       <c r="P79" s="11" t="inlineStr">
         <is>
-          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" hidden="1" outlineLevel="1">
-      <c r="A80" s="7" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>1851</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>Raider 18 Max HX B4WI</t>
-        </is>
-      </c>
-      <c r="D80" s="15" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E80" s="9" t="inlineStr">
-        <is>
-          <t>NVL-HX 65W</t>
-        </is>
-      </c>
-      <c r="F80" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5080</t>
-        </is>
-      </c>
-      <c r="G80" s="9" t="inlineStr">
-        <is>
-          <t>高宇奇</t>
-        </is>
-      </c>
-      <c r="H80" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="I80" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/18</t>
-        </is>
-      </c>
-      <c r="J80" s="9" t="inlineStr">
-        <is>
-          <t>2026/10/23</t>
-        </is>
-      </c>
-      <c r="K80" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/08</t>
-        </is>
-      </c>
-      <c r="L80" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/01</t>
-        </is>
-      </c>
-      <c r="M80" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N80" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O80" s="11" t="inlineStr">
-        <is>
-          <t>製程DFM修改需求,0M gerber out變更為8/4,暫不影響後續EVT schedule.</t>
-        </is>
-      </c>
-      <c r="P80" s="11" t="inlineStr">
-        <is>
-          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" hidden="1" outlineLevel="1">
-      <c r="A81" s="7" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>1851</t>
-        </is>
-      </c>
-      <c r="C81" s="9" t="inlineStr">
-        <is>
-          <t>Raider 18 Max HX B4WJ</t>
-        </is>
-      </c>
-      <c r="D81" s="15" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E81" s="9" t="inlineStr">
-        <is>
-          <t>NVL-HX 65W</t>
-        </is>
-      </c>
-      <c r="F81" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5090</t>
-        </is>
-      </c>
-      <c r="G81" s="9" t="inlineStr">
-        <is>
-          <t>高宇奇</t>
-        </is>
-      </c>
-      <c r="H81" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/18</t>
-        </is>
-      </c>
-      <c r="J81" s="9" t="inlineStr">
-        <is>
-          <t>2026/10/23</t>
-        </is>
-      </c>
-      <c r="K81" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/08</t>
-        </is>
-      </c>
-      <c r="L81" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/01</t>
-        </is>
-      </c>
-      <c r="M81" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N81" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O81" s="11" t="inlineStr">
-        <is>
-          <t>製程DFM修改需求,0M gerber out變更為8/4,暫不影響後續EVT schedule.</t>
-        </is>
-      </c>
-      <c r="P81" s="11" t="inlineStr">
-        <is>
-          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
+          <t>由 Raider改回Crosshair Max with D件快拆門</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P81"/>
+  <autoFilter ref="A1:P79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/npi_dashboard.xlsx
+++ b/npi_dashboard.xlsx
@@ -1127,7 +1127,7 @@
       </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
-          <t>DDR5 sku, MVT 測試中</t>
+          <t>DDR5 sku, MVT驗證中</t>
         </is>
       </c>
       <c r="P8" s="6" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="O9" s="11" t="inlineStr">
         <is>
-          <t>DDR5 sku, MVT 測試中</t>
+          <t>DDR5 sku, MVT驗證中</t>
         </is>
       </c>
       <c r="P9" s="11" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="O10" s="11" t="inlineStr">
         <is>
-          <t>DDR5 sku, MVT 測試中</t>
+          <t>DDR5 sku, MVT驗證中</t>
         </is>
       </c>
       <c r="P10" s="11" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="O11" s="11" t="inlineStr">
         <is>
-          <t>DDR4 sku, MVT 測試中,預計8/7 PCB risk buy</t>
+          <t>DDR4 sku, MVT驗證中</t>
         </is>
       </c>
       <c r="P11" s="11" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="O12" s="11" t="inlineStr">
         <is>
-          <t>DDR4 sku, MVT 測試中,預計8/7 PCB risk buy</t>
+          <t>DDR4 sku, MVT驗證中</t>
         </is>
       </c>
       <c r="P12" s="11" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="O13" s="11" t="inlineStr">
         <is>
-          <t>DDR4 sku, MVT 測試中,預計8/7 PCB risk buy</t>
+          <t>DDR4 sku, MVT驗證中</t>
         </is>
       </c>
       <c r="P13" s="11" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Cyborg A15 Max C1PWF</t>
+          <t>Cyborg A15 Max C1PWE</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1911,15 +1911,16 @@
       </c>
       <c r="O18" s="6" t="inlineStr">
         <is>
-          <t>HPT sku:預計8/7 MVT SMT,8/10試組,8/12組裝</t>
+          <t>HPT sku:預計8/10 MVT 試組,8/12組裝</t>
         </is>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>"
-1).Schedule:AMD PI 1200i NDA release@7/28 USA time(original 6/19,delay 39天)與工廠將MVT排程延至8/7 (original 8/4,delay 3天),因要和量產工單一起生產,因應上述時程變更,MP預計延至9/22(先前已由 9 /17提前至 8/31, 現又延至9/
-22),後續將依實際測試結果滾動式調整專案時程。
-2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS,若實測結果未達預期,物料需報廢,schedule也可能因此造成影響"</t>
+          <t>1).Schedule:AMD PI 1200I NDA Release delay(6/19→7/
+28)與MVT SMT 排程延後(8/4→8/
+7), 累計delay 42天, 取消 DVT排程改以 APU Rework 驗證追趕時程後, MP還是會delay 22天至9/22(先前已由 9 /17提前至 8/31, 現又延至9/
+22),後續將依實際測試結果滾動式調整專案時程
+2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS,若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1935,7 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Cyborg A15 Max C1PWG</t>
+          <t>Cyborg A15 Max C1PWF</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1949,7 +1950,7 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
@@ -1990,15 +1991,16 @@
       </c>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>HPT sku:預計8/7 MVT SMT,8/10試組,8/12組裝</t>
+          <t>HPT sku:預計8/10 MVT 試組,8/12組裝</t>
         </is>
       </c>
       <c r="P19" s="11" t="inlineStr">
         <is>
-          <t>"
-1).Schedule:AMD PI 1200i NDA release@7/28 USA time(original 6/19,delay 39天)與工廠將MVT排程延至8/7 (original 8/4,delay 3天),因要和量產工單一起生產,因應上述時程變更,MP預計延至9/22(先前已由 9 /17提前至 8/31, 現又延至9/
-22),後續將依實際測試結果滾動式調整專案時程。
-2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS,若實測結果未達預期,物料需報廢,schedule也可能因此造成影響"</t>
+          <t>1).Schedule:AMD PI 1200I NDA Release delay(6/19→7/
+28)與MVT SMT 排程延後(8/4→8/
+7), 累計delay 42天, 取消 DVT排程改以 APU Rework 驗證追趕時程後, MP還是會delay 22天至9/22(先前已由 9 /17提前至 8/31, 現又延至9/
+22),後續將依實際測試結果滾動式調整專案時程
+2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS,若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2015,7 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Cyborg A15 Max C1PWE</t>
+          <t>Cyborg A15 Max C1PWG</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -2028,7 +2030,7 @@
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
@@ -2069,13 +2071,15 @@
       </c>
       <c r="O20" s="11" t="inlineStr">
         <is>
-          <t>HPT sku:預計8/7 MVT SMT,8/10試組,8/12組裝</t>
+          <t>HPT sku:預計8/10 MVT 試組,8/12組裝</t>
         </is>
       </c>
       <c r="P20" s="11" t="inlineStr">
         <is>
-          <t>1).Schedule:AMD PI 1200i NDA release@7/28 USA time(original 6/19,delay 39天)與工廠將MVT排程延至8/7 (original 8/4,delay 3天),因要和量產工單一起生產,因應上述時程變更,MP預計延至9/22(先前已由 9 /17提前至 8/31, 現又延至9/
-22),後續將依實際測試結果滾動式調整專案時程。
+          <t>1).Schedule:AMD PI 1200I NDA Release delay(6/19→7/
+28)與MVT SMT 排程延後(8/4→8/
+7), 累計delay 42天, 取消 DVT排程改以 APU Rework 驗證追趕時程後, MP還是會delay 22天至9/22(先前已由 9 /17提前至 8/31, 現又延至9/
+22),後續將依實際測試結果滾動式調整專案時程
 2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS,若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
@@ -2147,13 +2151,15 @@
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>HPT sku:預計8/7 MVT SMT,8/10試組,8/12組裝</t>
+          <t>HPT sku:預計8/10 MVT 試組,8/12組裝</t>
         </is>
       </c>
       <c r="P21" s="11" t="inlineStr">
         <is>
-          <t>1).Schedule:AMD PI 1200i NDA release@7/28 USA time(original 6/19,delay 39天)與工廠將MVT排程延至8/7 (original 8/4,delay 3天),因要和量產工單一起生產,因應上述時程變更,MP預計延至9/22(先前已由 9 /17提前至 8/31, 現又延至9/
-22),後續將依實際測試結果滾動式調整專案時程。
+          <t>1).Schedule:AMD PI 1200I NDA Release delay(6/19→7/
+28)與MVT SMT 排程延後(8/4→8/
+7), 累計delay 42天, 取消 DVT排程改以 APU Rework 驗證追趕時程後, MP還是會delay 22天至9/22(先前已由 9 /17提前至 8/31, 現又延至9/
+22),後續將依實際測試結果滾動式調整專案時程
 2).Material:Thermal module依現有設計圖面take risk讓廠商去進行修模同時備料MVT &amp; ATS,若實測結果未達預期,物料需報廢,schedule也可能因此造成影響</t>
         </is>
       </c>
@@ -2236,7 +2242,7 @@
       <c r="P22" s="6" t="inlineStr">
         <is>
           <t>1) Schedule:  a. MVT拆分兩次SMT搭配PS software作驗證 b. 量產software更新時間至10/16, update ATS@11/9.
-2)備料：量產交料2.8k HQ23, 最新MP*1K交期回復在12/M（follow leading customer）交料, 與ATS start Gap 2個月, 採購協助push廠商交期中</t>
+2)備料：量產交料2.8k HQ23, 最新MP*1K交期, MSI &amp; Samsung co-work, target 10/M交料for ATS, tracking</t>
         </is>
       </c>
     </row>

--- a/npi_dashboard.xlsx
+++ b/npi_dashboard.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPI Dashboard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -34,7 +34,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FF4444"/>
+      <color rgb="0070AD47"/>
       <sz val="10"/>
     </font>
     <font>
@@ -42,12 +42,12 @@
       <sz val="11"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="0070AD47"/>
+      <color rgb="00666666"/>
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00666666"/>
+      <b val="1"/>
+      <color rgb="00FF4444"/>
       <sz val="10"/>
     </font>
     <font>
@@ -121,19 +121,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -519,7 +519,7 @@
     <outlinePr summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P63"/>
+  <dimension ref="A1:P59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -628,22 +628,22 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>15Q3</t>
+          <t>15T3</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Cyborg 15 Black Edition B13WE</t>
+          <t>Katana 15 HX C14WEK</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>RPL-H 45W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -653,44 +653,48 @@
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>楊淑賢</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>2026/06/24</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr"/>
+          <t>2026/04/20</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
       <c r="J2" s="4" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>2026/07/01</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
-          <t>2026/07/14</t>
+          <t>2026/07/30</t>
         </is>
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>2026/08/03</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>2026/08/07</t>
+          <t>2026/08/30</t>
         </is>
       </c>
       <c r="O2" s="6" t="inlineStr">
         <is>
-          <t>DQA MP HDI測試進行中, 暫無量產工單產生</t>
+          <t>DDR5: RTX5050進行C/R組裝@8/20 26PN078888C*50</t>
         </is>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
-          <t>1) Cyborg Black Edition SKU: Cyborg A+Venture B/C/D機構件+白光鍵盤</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -700,12 +704,12 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>15Q3</t>
+          <t>15T3</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Cyborg 15 Black Edition B13WF</t>
+          <t>Katana 15 HX C14WFK</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -715,7 +719,7 @@
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>RPL-H 45W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
@@ -725,121 +729,124 @@
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>楊淑賢</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>2026/06/24</t>
-        </is>
-      </c>
-      <c r="I3" s="9" t="inlineStr"/>
+          <t>2026/04/20</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
       <c r="J3" s="9" t="inlineStr"/>
       <c r="K3" s="9" t="inlineStr">
         <is>
-          <t>2026/07/01</t>
+          <t>2026/07/14</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
         <is>
+          <t>2026/07/30</t>
+        </is>
+      </c>
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="N3" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/30</t>
+        </is>
+      </c>
+      <c r="O3" s="11" t="inlineStr">
+        <is>
+          <t>DDR5: RTX5060預計C/R組裝@8/28 26PN077951C*50</t>
+        </is>
+      </c>
+      <c r="P3" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" hidden="1" outlineLevel="1">
+      <c r="A4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>15T3</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Katana 15 HX C14WGK</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>蔡東宏</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>2026/04/20</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/01</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr"/>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
           <t>2026/07/14</t>
         </is>
       </c>
-      <c r="M3" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/10</t>
-        </is>
-      </c>
-      <c r="N3" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
-      <c r="O3" s="11" t="inlineStr">
-        <is>
-          <t>ATS C/R工單： 9S7-15Q373-1258* 50 pcs 8/10 ASSY, 測試中</t>
-        </is>
-      </c>
-      <c r="P3" s="11" t="inlineStr">
-        <is>
-          <t>1) Cyborg Black Edition SKU: Cyborg A+Venture B/C/D機構件+白光鍵盤</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>15T3</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Katana 15 HX C14WEK</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/20</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/14</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>2026/07/30</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/20</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="N4" s="9" t="inlineStr">
         <is>
           <t>2026/08/30</t>
         </is>
       </c>
-      <c r="O4" s="6" t="inlineStr">
-        <is>
-          <t>DDR5 sku, MVT驗證中</t>
-        </is>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>1) ATS與MP的物料簽樣與備料,需要RD與採購和物管協助
-2)A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/30 MP的目標,需要RD/採購協助助pull in</t>
+      <c r="O4" s="11" t="inlineStr">
+        <is>
+          <t>DDR5: RTX5070進行ATS 組裝@8/20 26PN077002A*100</t>
+        </is>
+      </c>
+      <c r="P4" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -854,12 +861,12 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WFK</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>MVT</t>
+          <t>Katana 15 HX C14WEOK</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>ATS</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -869,7 +876,7 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
@@ -879,44 +886,43 @@
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/05/15</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>2026/06/01</t>
+          <t>2026/06/15</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr"/>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>2026/07/14</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>2026/07/30</t>
+          <t>2026/08/07</t>
         </is>
       </c>
       <c r="M5" s="9" t="inlineStr">
         <is>
-          <t>2026/08/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>2026/08/30</t>
+          <t>2026/08/31</t>
         </is>
       </c>
       <c r="O5" s="11" t="inlineStr">
         <is>
-          <t>DDR5 sku, MVT驗證中</t>
+          <t>DDR4: RTX5050進行C/R組裝@8/20 26PN078888C*50</t>
         </is>
       </c>
       <c r="P5" s="11" t="inlineStr">
         <is>
-          <t>1) ATS與MP的物料簽樣與備料,需要RD與採購和物管協助
-2)A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/30 MP的目標,需要RD/採購協助助pull in</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -931,12 +937,12 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WGK</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>MVT</t>
+          <t>Katana 15 HX C14WFOK</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>ATS</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -946,7 +952,7 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
@@ -956,44 +962,43 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/05/15</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>2026/06/01</t>
+          <t>2026/06/15</t>
         </is>
       </c>
       <c r="J6" s="9" t="inlineStr"/>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>2026/07/14</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>2026/07/30</t>
+          <t>2026/08/07</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
-          <t>2026/08/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="N6" s="9" t="inlineStr">
         <is>
-          <t>2026/08/30</t>
+          <t>2026/08/31</t>
         </is>
       </c>
       <c r="O6" s="11" t="inlineStr">
         <is>
-          <t>DDR5 sku, MVT驗證中</t>
+          <t>DDR4: RTX5060預計C/R組裝@8/28 26PN077951C*50</t>
         </is>
       </c>
       <c r="P6" s="11" t="inlineStr">
         <is>
-          <t>1) ATS與MP的物料簽樣與備料,需要RD與採購和物管協助
-2)A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/30 MP的目標,需要RD/採購協助助pull in</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1013,12 @@
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WEOK</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>MVT</t>
+          <t>Katana 15 HX C14WGOK</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>ATS</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -1023,7 +1028,7 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
@@ -1054,7 +1059,7 @@
       </c>
       <c r="M7" s="9" t="inlineStr">
         <is>
-          <t>2026/08/21</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="N7" s="9" t="inlineStr">
@@ -1064,90 +1069,92 @@
       </c>
       <c r="O7" s="11" t="inlineStr">
         <is>
-          <t>DDR4 sku, MVT驗證中</t>
+          <t>DDR4: RTX5070進行ATS 組裝@8/20 26PN077002A*100</t>
         </is>
       </c>
       <c r="P7" s="11" t="inlineStr">
         <is>
-          <t>1) ATS與MP的物料簽樣與備料,需要RD與採購和物管協助
-2)A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/30 MP的目標,需要RD/採購協助助pull in</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" hidden="1" outlineLevel="1">
-      <c r="A8" s="7" t="n">
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>15T3</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Katana 15 HX C14WFOK</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/15</t>
-        </is>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="inlineStr"/>
-      <c r="K8" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/24</t>
-        </is>
-      </c>
-      <c r="L8" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="M8" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="N8" s="9" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>2621</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Prestige N16 AI+ C1XMT</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>N1x 80W</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>林晉弘</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>2024/11/25</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>2025/01/20</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>2025/06/25</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>2026/03/12</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/17</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>2026/08/31</t>
         </is>
       </c>
-      <c r="O8" s="11" t="inlineStr">
-        <is>
-          <t>DDR4 sku, MVT驗證中</t>
-        </is>
-      </c>
-      <c r="P8" s="11" t="inlineStr">
-        <is>
-          <t>1) ATS與MP的物料簽樣與備料,需要RD與採購和物管協助
-2)A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/30 MP的目標,需要RD/採購協助助pull in</t>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>ATS測試中</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>1)Battery life: BIOS導入BTP後，DQA測試modern standby battery life可達16.44 days，合乎MSFT標準。NV於Day0 rev.F版本針對功耗有所改善，Web browersing的測試，將後續更新測試BIOS與image後，重新測試。 2.ATS ASS'Y 8/18上線，8/20開始進行IRT測試。IRT測試目前發現問題如下。 a)手動reboot藍屏，DC/AC下各發現一台，error code 0x7E，為已知問題，與NV co-work中 b)平板模式下手動reboot，touch panel失效，測試17台發現1台，重啟現象消失，持續追蹤 c)camera test開始錄像/關閉錄像有延遲，4台發現2台，重開機後，現象消失，持續追蹤 d)手動S4 resume撥放音樂，插入耳機，耳機無聲，發現一台，RD分析中</t>
         </is>
       </c>
     </row>
@@ -1157,58 +1164,62 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>15T3</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WGOK</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>MVT</t>
+          <t>Prestige N16 Flip AI+ C1XMT</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>ATS</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>N1x 80W</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>蔡東宏</t>
+          <t>林晉弘</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>2026/05/15</t>
+          <t>2024/11/25</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr"/>
+          <t>2025/01/20</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>2025/06/25</t>
+        </is>
+      </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/03/12</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>2026/08/07</t>
+          <t>2026/06/30</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
-          <t>2026/08/21</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="N9" s="9" t="inlineStr">
@@ -1218,13 +1229,12 @@
       </c>
       <c r="O9" s="11" t="inlineStr">
         <is>
-          <t>DDR4 sku, MVT驗證中</t>
+          <t>ATS測試中</t>
         </is>
       </c>
       <c r="P9" s="11" t="inlineStr">
         <is>
-          <t>1) ATS與MP的物料簽樣與備料,需要RD與採購和物管協助
-2)A件交期依森田薄膜進料時間,預計15T3組裝在8/25,MP在9/3,會比原時程晚4天,會導致15T3無法meet原8/30 MP的目標,需要RD/採購協助助pull in</t>
+          <t>1)Battery life: BIOS導入BTP後，DQA測試modern standby battery life可達16.44 days，合乎MSFT標準。NV於Day0 rev.F版本針對功耗有所改善，Web browersing的測試，將後續更新測試BIOS與image後，重新測試。 2.ATS ASS'Y 8/18上線，8/20開始進行IRT測試。IRT測試目前發現問題如下。 a)手動reboot藍屏，DC/AC下各發現一台，error code 0x7E，為已知問題，與NV co-work中 b)平板模式下手動reboot，touch panel失效，測試17台發現1台，重啟現象消失，持續追蹤 c)camera test開始錄像/關閉錄像有延遲，4台發現2台，重開機後，現象消失，持續追蹤 d)手動S4 resume撥放音樂，插入耳機，耳機無聲，發現一台，RD分析中</t>
         </is>
       </c>
     </row>
@@ -1234,162 +1244,155 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>15T2</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Prestige N16 Flip AI+ C1XMT</t>
+          <t>Venture 15 AI+ B3M</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>PTL-H 80W</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>李文欽</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/20</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/26</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/20</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>1) ATS 組裝@ 8/20, 工單:26PN072477A / 26PN072950A 各50</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>24V1</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Modern 14 LE J3M</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>N1x 80W</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>林晉弘</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>2024/11/25</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>2025/01/20</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>2025/06/25</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>2026/03/12</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/30</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/17</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/31</t>
-        </is>
-      </c>
-      <c r="O10" s="6" t="inlineStr">
-        <is>
-          <t>MVT測試中</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>1
-1)Battery life: 8/7 MSFT提供battery報告，web browersing與DQA依Day0 rev.E測試結果雷同，目前約11.5Hrs。Modern standby測試結果11.68天，需待EC/BIOS按照MSFT要求導入BTP後重新測試。
-2)8/10 Day0 rev.E BIOS與 image，工廠/DQA已同時切換測試。
-3)SW更新到day0 rev.E，後續會以此版本進行驗證for出貨。因問題點皆與軟體有關，已先更新工廠/DQA主要問題點與寬哥先同意ATS上線，後續仍須RD與廠商協助。 1.USB 抓取不稳定 2.reboot藍屏 3. speaker 在網上播放視頻有noise 4.abnormal shutdown 5.SSD S5丢失 6.Battery life 小於預期 7.camera App 執行camera recording 時候hang 住 8.在執行reboot modern standby 時候出现camera lost or YB 9.audio ：在app 播放music 時候做speaker &amp; headphone 切換出現： a. 切換到另一output 時'候播放器卡顿max 15s b. 切換到耳機状态时候app 暂停 10.SD 卡槽插壞 11.手動lid modern standby  喚醒后panel 無顯</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" hidden="1" outlineLevel="1">
-      <c r="A11" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>2621</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Prestige N16 AI+ C1XMT</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>N1x 80W</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>林晉弘</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>2024/11/25</t>
-        </is>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>2025/01/20</t>
-        </is>
-      </c>
-      <c r="J11" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/25</t>
-        </is>
-      </c>
-      <c r="K11" s="9" t="inlineStr">
-        <is>
-          <t>2026/03/12</t>
-        </is>
-      </c>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/30</t>
-        </is>
-      </c>
-      <c r="M11" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/17</t>
-        </is>
-      </c>
-      <c r="N11" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/31</t>
-        </is>
-      </c>
-      <c r="O11" s="11" t="inlineStr">
-        <is>
-          <t>MVT測試中</t>
-        </is>
-      </c>
-      <c r="P11" s="11" t="inlineStr">
-        <is>
-          <t>1)Battery life: 8/7 MSFT提供battery報告，web browersing與DQA依Day0 rev.E測試結果雷同，目前約11.5Hrs。Modern standby測試結果11.68天，需待EC/BIOS按照MSFT要求導入BTP後重新測試。
-2)8/10 Day0 rev.E BIOS與 image，工廠/DQA已同時切換測試。
-3)SW更新到day0 rev.E，後續會以此版本進行驗證for出貨。因問題點皆與軟體有關，已先更新工廠/DQA主要問題點與寬哥先同意ATS上線，後續仍須RD與廠商協助。 1.USB 抓取不稳定 2.reboot藍屏 3. speaker 在網上播放視頻有noise 4.abnormal shutdown 5.SSD S5丢失 6.Battery life 小於預期 7.camera App 執行camera recording 時候hang 住 8.在執行reboot modern standby 時候出现camera lost or YB 9.audio ：在app 播放music 時候做speaker &amp; headphone 切換出現： a. 切換到另一output 時'候播放器卡顿max 15s b. 切換到耳機状态时候app 暂停 10.SD 卡槽插壞 11.手動lid modern standby  喚醒后panel 無顯</t>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>WCL 25W</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Intel® graphics</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>倪嬌嬌</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/07</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/29</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/08</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/26</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/07</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t>MSI:  MVT DQA test中 微步：ATS ASSY@8/25--會再匯整料況明確組裝時間</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>1) Function issue： a.	HDI: 8/20提供MP HDI申請單, 8/21開始製作 b.	BIOS: 待8/20 微步提供BIOS 100 , 需驗證bug &amp; 測試完整BIOS Function c.	Long run reboot issue, 5台run 500 loops, 3台hang MSI logo, 微步team正在分析中 (
+2) ATS工單： 9S7-24V111-006*38 9S7-24V111-015*56 (
+3)8月&amp;9月業務訂單認證追蹤 a. DE 9S7-24V111-011* 56 CE認證, 取證時間target 8/E, 具體日期待微步確認中 b. NZ* 76 （9S7-24V111-005* 38+ 9S7-24V111-006 *
+38） RCM認證, CE+ 1 week提供RCM報告, 需進口商登記完成後出貨 c.UA* 112（9S7-24V111-017*56+ 9S7-24V111-015*
+56） Ukraine RF CoC+DoC認證, 由MSI負責申請, UA業務確認follow系統時間排單出貨 d.JP*56(9S7-24V111-009*50+ 9S7-24V111-016*
+6) VCCI認證, 8/E之前可 取證完成, 出貨時間需考量JP鍵盤備料ready日期, 9/E之前可出貨. (
+4) JP KB 開模9/10試模, 9/20交料, JP工單可出貨時間@9/24</t>
         </is>
       </c>
     </row>
@@ -1399,73 +1402,75 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>15T2</t>
+          <t>26V1</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Venture 15 AI+ B3M</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
+          <t>Modern 16 LE J3M</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>PTL-H 80W</t>
+          <t>WCL 25W</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Intel® Arc™ Graphics</t>
+          <t>Intel® graphics</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>李文欽</t>
+          <t>倪嬌嬌</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/06/02</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>2026/05/26</t>
+          <t>2026/07/07</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
+          <t>2026/07/29</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
           <t>2026/07/08</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/20</t>
-        </is>
-      </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>2026/08/19</t>
+          <t>2026/08/26</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>2026/08/31</t>
+          <t>2026/09/07</t>
         </is>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>MVT2驗證中</t>
+          <t>MSI: MVT DQA test中 微步：ATS ASSY@8/25--會再匯整料況明確組裝時間</t>
         </is>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>1) Schedule:ATS的PCB預計8/18交料,SMT改為8/19.MP為8/31</t>
+          <t>1) Function issue：同24V1, ME issue: a.Panel Mura: 使用COST panel, 微步回復需增加輔料，預抓8/21寄送機器增加Mura對策for MSI驗證 b.	Shock測試fail, B件攝像頭位置彈開&amp;電池定位柱斷裂：需要新的鍵芯支架 複驗, 同時參考26VL機種, 將力度改160G作複測, 樣品可提供時間待微步確認 c.	Panel Scuff測試屏幕碎晶：參考26VL機種, 使用加背包的方式進行模擬複測 d.	Shock測試屏幕破損: 參考26VL機種, 將力度改160G作測試 (
+2) ATS工單: 9S7-26V111-006*20 9S7-26V111-004*200 9S7-26V111-005*400 (
+2) 8月&amp;9月業務訂單認證追蹤 a.DE* 1650 CE認證, 取證時間target 8/E, 具體日期待微步確認中 b.IT 9S7-26V111-002*300 CE認證, 取證時間target 8/E, 具體日期待微步確認中 c.US 9S7-26V111-001*1020 FCC ID， Target 9/M取證(已經拿到FCC報告在內部確認中)  d.PL 9S7-26V111-003*56 CE認證, 取證時間target 8/E, 具體日期待微步確認中</t>
         </is>
       </c>
     </row>
@@ -1475,75 +1480,77 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>24V1</t>
+          <t>15TK</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Modern 14 LE J3M</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+          <t>Cyborg A15 C1PWE</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>WCL 25W</t>
+          <t>HWK 45W</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Intel® graphics</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>倪嬌嬌</t>
+          <t>蔡東宏</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>2026/06/02</t>
+          <t>2026/05/28</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>2026/07/07</t>
+          <t>2026/06/26</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/08/07</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/08/21</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>2026/08/26</t>
+          <t>2026/09/12</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>2026/09/07</t>
+          <t>2026/09/22</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>MSI: 8/11收到機器, MVT test中</t>
+          <t>HPT sku:MVT測試中</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>1）Schedule: 8/4通知微步修模D件,  TTM Schedule由原定的8/26更新至9/7 ready, Delay 10 days
-2) Function issue: a. HDI: driver package問題反饋微步SW確認中 b.BIOS: 等8/13新的TSA BIOS作驗證, due day: 8/13
-3）認證for 八&amp;九月份訂單（total 300 pcs): a. DE * 56 CE認證, 取證時間target 8/25 b. NZ* 76  RCM認證, CE+ 1 week, 9/1提供RCM報告, 需進口商登記完成後出貨 c.UA* 112 Ukraine RF CoC+DoC, CE轉證+ 8weeks, 10/20取證, 業務確認可先出貨 d.JP*56 VCCI認證, 取證時間target 8/17（但出貨時間需考量JP鍵盤備料ready日期@9/E）</t>
+          <t>1).業務下單要收斂到Cyborg A15 non Max, 因team member已取得Max HPT MVT機台測試中,只會完成MVT測試,Max不開BTO,不做ATS
+2).Schedule:AMD PI 1200I NDA Release delay(6/19→7/
+28)與生管延後MVT SMT 排程(8/4→8/
+7),累計delay 42天,取消 DVT排程改以 APU Rework 驗證追趕時程後,MP還是會delay 22天至9/22(先前已由 9 /17提前至 8/31,現又延至9/
+22),後續將依實際測試結果滾動式調整專案時程</t>
         </is>
       </c>
     </row>
@@ -1553,75 +1560,78 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>26V1</t>
+          <t>1T91</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Modern 16 LE J3M</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+          <t>Claw 8 EX AI+ CG3M</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>WCL 25W</t>
+          <t>PTL-H 25W</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Intel® graphics</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>倪嬌嬌</t>
+          <t>楊淑賢</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>2026/06/02</t>
+          <t>2025/11/06</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>2026/07/07</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr"/>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>2026/01/31</t>
+        </is>
+      </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>2026/07/29</t>
+          <t>2026/08/26</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/08/18</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>2026/08/26</t>
+          <t>2026/09/15</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>2026/09/07</t>
+          <t>2026/09/30</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>MSI: 8/11收到機器, MVT test中</t>
+          <t>1. function: 需補測G3+LPDDR5x-32GB的performance/BAT/thermal test, PCBA預抓8/26 SMT
+2)藍色機構件驗證: 8/21樣品到料, ME RD更換4台機器, 8/24 test start</t>
         </is>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>1)Schedule: 8/7通知微步八月份680台訂單先備舊料, TTM Schedule由原定的8/26更新至9/7 ready, Delay 10 days.
-2) function issue: 同24V1
-3) 八&amp;九月訂單認證追蹤(total 2970 pcs）：a.DE* 1650 CE認證, 取證時間target 8/25 b.IT *300 CE認證, 取證時間target 8/25 c.US *1020 FCC ID， Target 9/M取證(等Intel回簽授權文件)</t>
+          <t>新增藍色SKU G3+ LPDDR5x-32GB需求, 1st MOQ: 3K</t>
         </is>
       </c>
     </row>
@@ -1631,234 +1641,238 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>15TK</t>
+          <t>14T3</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Cyborg A15 Max C1PWE</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
+          <t>Prestige N14 AI+ D1M</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>HWK 45W</t>
+          <t>N1 35W</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>倪嬌嬌</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/30</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>2025/09/01</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/09</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/23</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>MVT2 SMT depend on PS Software時間-- PS software release@8/21, 可排單日期預抓8/27, 需與MPM討論後確認</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>1) Schedule:  a. MVT2 SMT date考量PS software release時間 b. 2.8K panel*286 pcs 8/28 ETD, 廠內庫存不足, 計劃等9/4進料後再作MVT ASSY
+2)備料：量產交料2.8k HQ23, 最新MP*1K交期,  Samsung回復計劃10/E ETD, 可滿足ATS需求, 持續追蹤</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>2623</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Prestige N16 AI+ C1M</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>N1 45W</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>賴雪鳳</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/30</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>2025/09/01</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/09</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/23</t>
+        </is>
+      </c>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>MVT1:8/13 SMT, 8/14 Pre -Assy  for 少數RD 測試, 待PS SW ready 再上線做MVT2 for 全部team member</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>備料: Samsung 2.8K panel 採購備料HR14*2K for N1 ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Katana 18 HX A14WEK</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>EVT</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/26</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/12</t>
-        </is>
-      </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/22</t>
-        </is>
-      </c>
-      <c r="O15" s="6" t="inlineStr">
-        <is>
-          <t>HPT sku:MVT 組裝中,預計8/17入庫,8/18調撥</t>
-        </is>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>1).Schedule:AMD PI 1200I NDA Release delay(6/19→7/
-28)與生管延後MVT SMT排程(8/4→8/
-7), 累計delay 42天, 取消 DVT排程改以 APU Rework 驗證追趕時程後, MP還是會delay 22天至9/22(先前已由 9 /17提前至 8/31, 現又延至9/
-22),後續將依實際測試結果滾動式調整專案時程</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" hidden="1" outlineLevel="1">
-      <c r="A16" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>15TK</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Cyborg A15 Max C1PWF</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>HWK 45W</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/26</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="inlineStr"/>
-      <c r="K16" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="L16" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="M16" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/12</t>
-        </is>
-      </c>
-      <c r="N16" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/22</t>
-        </is>
-      </c>
-      <c r="O16" s="11" t="inlineStr">
-        <is>
-          <t>HPT sku:MVT 組裝中,預計8/17入庫,8/18調撥</t>
-        </is>
-      </c>
-      <c r="P16" s="11" t="inlineStr">
-        <is>
-          <t>1).Schedule:AMD PI 1200I NDA Release delay(6/19→7/
-28)與生管延後MVT SMT排程(8/4→8/
-7), 累計delay 42天, 取消 DVT排程改以 APU Rework 驗證追趕時程後, MP還是會delay 22天至9/22(先前已由 9 /17提前至 8/31, 現又延至9/
-22),後續將依實際測試結果滾動式調整專案時程</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" hidden="1" outlineLevel="1">
-      <c r="A17" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>15TK</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>Cyborg A15 Max C1PWG</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>HWK 45W</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/26</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="inlineStr"/>
-      <c r="K17" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="L17" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="M17" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/12</t>
-        </is>
-      </c>
-      <c r="N17" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/22</t>
-        </is>
-      </c>
-      <c r="O17" s="11" t="inlineStr">
-        <is>
-          <t>HPT sku:MVT 組裝中,預計8/17入庫,8/18調撥</t>
-        </is>
-      </c>
-      <c r="P17" s="11" t="inlineStr">
-        <is>
-          <t>1).Schedule:AMD PI 1200I NDA Release delay(6/19→7/
-28)與生管延後MVT SMT排程(8/4→8/
-7), 累計delay 42天, 取消 DVT排程改以 APU Rework 驗證追趕時程後, MP還是會delay 22天至9/22(先前已由 9 /17提前至 8/31, 現又延至9/
-22),後續將依實際測試結果滾動式調整專案時程</t>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>顧曉琴</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/12</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/21</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="O17" s="6" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR5: EVT SMT1 PCBA預計8/20 到台北供RD測試; SMT2 @ 8/24, Pre-assy @ 8/25, ASSY @ 8/29</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1868,318 +1882,313 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>15TK</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Cyborg A15 C1PWE</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>MVT</t>
+          <t>Katana 18 HX A14WFK</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>EVT</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>HWK 45W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>顧曉琴</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/12</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="M18" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/21</t>
+        </is>
+      </c>
+      <c r="N18" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="O18" s="11" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR5: EVT SMT1 PCBA預計8/20 到台北供RD測試; SMT2 @ 8/24, Pre-assy @ 8/25, ASSY @ 8/29</t>
+        </is>
+      </c>
+      <c r="P18" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" hidden="1" outlineLevel="1">
+      <c r="A19" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Katana 18 HX A14WGK</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>EVT</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>顧曉琴</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/12</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="M19" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/21</t>
+        </is>
+      </c>
+      <c r="N19" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="O19" s="11" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR5: EVT SMT1 PCBA預計8/20 到台北供RD測試; SMT2 @ 8/24, Pre-assy @ 8/25, ASSY @ 8/29</t>
+        </is>
+      </c>
+      <c r="P19" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" hidden="1" outlineLevel="1">
+      <c r="A20" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Katana 18 HX A14WGXK</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>EVT</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>顧曉琴</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/12</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="M20" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/21</t>
+        </is>
+      </c>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="O20" s="11" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR5: EVT SMT1 PCBA預計8/20 到台北供RD測試; SMT2 @ 8/24, Pre-assy @ 8/25, ASSY @ 8/29</t>
+        </is>
+      </c>
+      <c r="P20" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" hidden="1" outlineLevel="1">
+      <c r="A21" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Katana 18 HX A14WEOK</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/28</t>
-        </is>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/26</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="inlineStr"/>
-      <c r="K18" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="L18" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/21</t>
-        </is>
-      </c>
-      <c r="M18" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/12</t>
-        </is>
-      </c>
-      <c r="N18" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/22</t>
-        </is>
-      </c>
-      <c r="O18" s="11" t="inlineStr">
-        <is>
-          <t>HPT sku:MVT 組裝中,預計8/17入庫,8/18調撥</t>
-        </is>
-      </c>
-      <c r="P18" s="11" t="inlineStr">
-        <is>
-          <t>1).Schedule:AMD PI 1200I NDA Release delay(6/19→7/
-28)與生管延後MVT SMT排程(8/4→8/
-7), 累計delay 42天, 取消 DVT排程改以 APU Rework 驗證追趕時程後, MP還是會delay 22天至9/22(先前已由 9 /17提前至 8/31, 現又延至9/
-22),後續將依實際測試結果滾動式調整專案時程</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>14T3</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Prestige N14 AI+ D1M</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>N1 35W</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>顧曉琴</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr"/>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/20</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/23</t>
+        </is>
+      </c>
+      <c r="N21" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/02</t>
+        </is>
+      </c>
+      <c r="O21" s="11" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+        </is>
+      </c>
+      <c r="P21" s="11" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>倪嬌嬌</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>2025/04/30</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>2025/09/01</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/15</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/14</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/09</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/23</t>
-        </is>
-      </c>
-      <c r="O19" s="6" t="inlineStr">
-        <is>
-          <t>1)MVT1 SMT@8/13--只先安排少量for TE/BIOS/HW
-2)MVT2 SMT depend on PS Software時間, plan as 8/19</t>
-        </is>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>1) Schedule:  a. MVT2 SMT date需考量PS software release時間 b. 2.8K panel*286 pcs 8/30 ETD, 廠內庫存不足, 計劃拆分MVT ASSY中 拆分兩次SMT搭配PS software作驗證
-2)備料：量產交料2.8k HQ23, 最新MP*1K交期,  Samsung回復計劃10/E ETD, 可滿足ATS需求, 持續追蹤</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>2623</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Prestige N16 AI+ C1M</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>N1 45W</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>賴雪鳳</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>2025/04/30</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>2025/09/01</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/15</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/14</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/09</t>
-        </is>
-      </c>
-      <c r="N20" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/23</t>
-        </is>
-      </c>
-      <c r="O20" s="6" t="inlineStr">
-        <is>
-          <t>MVT1:8/13 SMT, 8/14 Pre -Assy  for 少數RD 測試, 待PS SW ready 再上線做MVT2 for 全部team member</t>
-        </is>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>備料: Samsung 2.8K panel 採購備料HR14*2K for N1 ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Katana 18 HX A14WEK</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>EVT</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>顧曉琴</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>2026/10/12</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/02</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/21</t>
-        </is>
-      </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/30</t>
-        </is>
-      </c>
-      <c r="O21" s="6" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR5: EVT SMT1 @ 8/13, PCBA預計8/20 到台北供RD測試; SMT2 @ 8/24 for ASSY</t>
-        </is>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2194,12 +2203,12 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WFK</t>
-        </is>
-      </c>
-      <c r="D22" s="14" t="inlineStr">
-        <is>
-          <t>EVT</t>
+          <t>Katana 18 HX A14WFOK</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -2219,22 +2228,18 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr"/>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>2026/10/12</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
@@ -2244,22 +2249,22 @@
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
-          <t>2026/11/21</t>
+          <t>2026/11/23</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2026/12/02</t>
         </is>
       </c>
       <c r="O22" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: EVT SMT1 @ 8/13, PCBA預計8/20 到台北供RD測試; SMT2 @ 8/24 for ASSY</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P22" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -2274,12 +2279,12 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGK</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>EVT</t>
+          <t>Katana 18 HX A14WGOK</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -2299,22 +2304,18 @@
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr"/>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>2026/10/12</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
@@ -2324,22 +2325,22 @@
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>2026/11/21</t>
+          <t>2026/11/23</t>
         </is>
       </c>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2026/12/02</t>
         </is>
       </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: EVT SMT1 @ 8/13, PCBA預計8/20 到台北供RD測試; SMT2 @ 8/24 for ASSY</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P23" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -2354,12 +2355,12 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGXK</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="inlineStr">
-        <is>
-          <t>EVT</t>
+          <t>Katana 18 HX A14WGXOK</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -2379,22 +2380,18 @@
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J24" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr"/>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>2026/10/12</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
@@ -2404,22 +2401,22 @@
       </c>
       <c r="M24" s="9" t="inlineStr">
         <is>
-          <t>2026/11/21</t>
+          <t>2026/11/23</t>
         </is>
       </c>
       <c r="N24" s="9" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2026/12/02</t>
         </is>
       </c>
       <c r="O24" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: EVT SMT1 @ 8/13, PCBA預計8/20 到台北供RD測試; SMT2 @ 8/24 for ASSY</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P24" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -2434,17 +2431,17 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WEOK</t>
-        </is>
-      </c>
-      <c r="D25" s="15" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Katana 18 HX A2WEK</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>RPL-HX Next 55W</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
@@ -2459,38 +2456,34 @@
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr"/>
       <c r="J25" s="9" t="inlineStr"/>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/12/08</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
-          <t>2026/11/02</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="M25" s="9" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2027/01/19</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
         <is>
-          <t>2026/12/02</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P25" s="11" t="inlineStr">
@@ -2510,22 +2503,22 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WFOK</t>
-        </is>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Katana 18 HX A2WEOK</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>RPL-HX Next 55W</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
@@ -2546,27 +2539,27 @@
       <c r="J26" s="9" t="inlineStr"/>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/12/08</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>2026/11/02</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="M26" s="9" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2027/01/19</t>
         </is>
       </c>
       <c r="N26" s="9" t="inlineStr">
         <is>
-          <t>2026/12/02</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="O26" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P26" s="11" t="inlineStr">
@@ -2586,22 +2579,22 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGOK</t>
-        </is>
-      </c>
-      <c r="D27" s="15" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Katana 18 HX A2WFK</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>RPL-HX Next 55W</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
@@ -2611,38 +2604,34 @@
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="inlineStr"/>
       <c r="J27" s="9" t="inlineStr"/>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/12/08</t>
         </is>
       </c>
       <c r="L27" s="9" t="inlineStr">
         <is>
-          <t>2026/11/02</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="M27" s="9" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2027/01/19</t>
         </is>
       </c>
       <c r="N27" s="9" t="inlineStr">
         <is>
-          <t>2026/12/02</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P27" s="11" t="inlineStr">
@@ -2662,22 +2651,22 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGXOK</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Katana 18 HX A2WFOK</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>RPL-HX Next 55W</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
@@ -2698,27 +2687,27 @@
       <c r="J28" s="9" t="inlineStr"/>
       <c r="K28" s="9" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/12/08</t>
         </is>
       </c>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>2026/11/02</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="M28" s="9" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2027/01/19</t>
         </is>
       </c>
       <c r="N28" s="9" t="inlineStr">
         <is>
-          <t>2026/12/02</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="O28" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P28" s="11" t="inlineStr">
@@ -2738,7 +2727,7 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WEK</t>
+          <t>Katana 18 HX A2WGK</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
@@ -2753,7 +2742,7 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -2810,7 +2799,7 @@
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WEOK</t>
+          <t>Katana 18 HX A2WGOK</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
@@ -2825,7 +2814,7 @@
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
@@ -2886,7 +2875,7 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WFK</t>
+          <t>Katana 18 HX A2WGXK</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
@@ -2901,7 +2890,7 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
@@ -2958,7 +2947,7 @@
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WFOK</t>
+          <t>Katana 18 HX A2WGXOK</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
@@ -2973,7 +2962,7 @@
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -3023,151 +3012,163 @@
         </is>
       </c>
     </row>
-    <row r="33" hidden="1" outlineLevel="1">
-      <c r="A33" s="7" t="n">
+    <row r="33">
+      <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Katana 18 HX A2WGK</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>RPL-HX Next 55W</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>顧曉琴</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I33" s="9" t="inlineStr"/>
-      <c r="J33" s="9" t="inlineStr"/>
-      <c r="K33" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/08</t>
-        </is>
-      </c>
-      <c r="L33" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/30</t>
-        </is>
-      </c>
-      <c r="M33" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/19</t>
-        </is>
-      </c>
-      <c r="N33" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/30</t>
-        </is>
-      </c>
-      <c r="O33" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
-        </is>
-      </c>
-      <c r="P33" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" hidden="1" outlineLevel="1">
-      <c r="A34" s="7" t="n">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>13Q5</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Prestige 13 AI+ A4M</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>NVL-H 28W</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>顏春梅</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/08</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/21</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/22</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/22</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/31</t>
+        </is>
+      </c>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>DVT PCBA 調撥回台@8/21</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Katana 18 HX A2WGOK</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>RPL-HX Next 55W</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>顧曉琴</t>
-        </is>
-      </c>
-      <c r="H34" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J34" s="9" t="inlineStr"/>
-      <c r="K34" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/08</t>
-        </is>
-      </c>
-      <c r="L34" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/30</t>
-        </is>
-      </c>
-      <c r="M34" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/19</t>
-        </is>
-      </c>
-      <c r="N34" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/30</t>
-        </is>
-      </c>
-      <c r="O34" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
-        </is>
-      </c>
-      <c r="P34" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>14T4</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Prestige 14 AI+ D4MG</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>NVL-H 30W</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>朱芳芳</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/22</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/12</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/20</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/21</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/31</t>
+        </is>
+      </c>
+      <c r="O34" s="6" t="inlineStr">
+        <is>
+          <t>DVT RD test中 :8/4~9/7</t>
+        </is>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3177,379 +3178,387 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>14T4</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WGXK</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
+          <t>Prestige 14 Flip AI+ D4MTG</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX Next 55W</t>
+          <t>NVL-H 30W</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>顧曉琴</t>
+          <t>朱芳芳</t>
         </is>
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I35" s="9" t="inlineStr"/>
-      <c r="J35" s="9" t="inlineStr"/>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/22</t>
+        </is>
+      </c>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>2026/12/08</t>
+          <t>2026/11/12</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/11/20</t>
         </is>
       </c>
       <c r="M35" s="9" t="inlineStr">
         <is>
-          <t>2027/01/19</t>
+          <t>2026/12/21</t>
         </is>
       </c>
       <c r="N35" s="9" t="inlineStr">
         <is>
-          <t>2027/01/30</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="O35" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>DVT RD test中 :8/4~9/7</t>
         </is>
       </c>
       <c r="P35" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" hidden="1" outlineLevel="1">
-      <c r="A36" s="7" t="n">
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Katana 18 HX A2WGXOK</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>RPL-HX Next 55W</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G36" s="9" t="inlineStr">
-        <is>
-          <t>顧曉琴</t>
-        </is>
-      </c>
-      <c r="H36" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J36" s="9" t="inlineStr"/>
-      <c r="K36" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/08</t>
-        </is>
-      </c>
-      <c r="L36" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/30</t>
-        </is>
-      </c>
-      <c r="M36" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/19</t>
-        </is>
-      </c>
-      <c r="N36" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/30</t>
-        </is>
-      </c>
-      <c r="O36" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
-        </is>
-      </c>
-      <c r="P36" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>2624</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Prestige 16 AI+</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>NVL-H 30W</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>朱芳芳</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr"/>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/22</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/12</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/20</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/21</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/31</t>
+        </is>
+      </c>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>DVT RD test中 :8/4~9/7</t>
+        </is>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" hidden="1" outlineLevel="1">
+      <c r="A37" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>14T4</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Prestige 14 AI+ D4MG</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>2624</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Prestige 16 Flip AI+</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
         <is>
           <t>NVL-H 30W</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F37" s="9" t="inlineStr">
         <is>
           <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr">
         <is>
           <t>朱芳芳</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="H37" s="9" t="inlineStr">
         <is>
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/15</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/04</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
+      <c r="I37" s="9" t="inlineStr"/>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/22</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/12</t>
+        </is>
+      </c>
+      <c r="L37" s="9" t="inlineStr">
         <is>
           <t>2026/11/20</t>
         </is>
       </c>
-      <c r="M37" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/15</t>
-        </is>
-      </c>
-      <c r="N37" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/25</t>
-        </is>
-      </c>
-      <c r="O37" s="6" t="inlineStr">
-        <is>
-          <t>DVT 開機OK， RD test :8/4~8/31</t>
-        </is>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
+      <c r="M37" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/21</t>
+        </is>
+      </c>
+      <c r="N37" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/31</t>
+        </is>
+      </c>
+      <c r="O37" s="11" t="inlineStr">
+        <is>
+          <t>DVT RD test中 :8/4~9/7</t>
+        </is>
+      </c>
+      <c r="P37" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
-    <row r="38" hidden="1" outlineLevel="1">
-      <c r="A38" s="7" t="n">
+    <row r="38">
+      <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>14T4</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Prestige 14 Flip AI+ D4MTG</t>
-        </is>
-      </c>
-      <c r="D38" s="15" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>2633</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WI</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>NVL-H 30W</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>Intel® Arc™ Graphics</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>朱芳芳</t>
-        </is>
-      </c>
-      <c r="H38" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/14</t>
-        </is>
-      </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J38" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/15</t>
-        </is>
-      </c>
-      <c r="K38" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/04</t>
-        </is>
-      </c>
-      <c r="L38" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/20</t>
-        </is>
-      </c>
-      <c r="M38" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/15</t>
-        </is>
-      </c>
-      <c r="N38" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/25</t>
-        </is>
-      </c>
-      <c r="O38" s="11" t="inlineStr">
-        <is>
-          <t>DVT 開機OK， RD test :8/4~8/31</t>
-        </is>
-      </c>
-      <c r="P38" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5080</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/23</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="O38" s="6" t="inlineStr">
+        <is>
+          <t>RD 測試中, 0N gerberout @8/25</t>
+        </is>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>1) Schedule:NV VBIOS @1/6, gating 8天,預計12/E 拿到WHQL，可能影響到最終TTM 時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" hidden="1" outlineLevel="1">
+      <c r="A39" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>2624</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>Prestige 16 AI+</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>2633</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WH</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>NVL-H 30W</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>Intel® Arc™ Graphics</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>朱芳芳</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/14</t>
-        </is>
-      </c>
-      <c r="I39" s="4" t="inlineStr"/>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/15</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/04</t>
-        </is>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/20</t>
-        </is>
-      </c>
-      <c r="M39" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/15</t>
-        </is>
-      </c>
-      <c r="N39" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/25</t>
-        </is>
-      </c>
-      <c r="O39" s="6" t="inlineStr">
-        <is>
-          <t>DVT 開機OK， RD test :8/4~8/31</t>
-        </is>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/23</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="M39" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N39" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="O39" s="11" t="inlineStr">
+        <is>
+          <t>RD 測試中, 0N gerberout @8/25</t>
+        </is>
+      </c>
+      <c r="P39" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -3561,12 +3570,12 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Prestige 16 Flip AI+</t>
+          <t>Stealth 16 AI+ B4WJ</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
@@ -3576,53 +3585,57 @@
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>NVL-H 30W</t>
+          <t>NVL-H 45W</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>Intel® Arc™ Graphics</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
-          <t>朱芳芳</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>2026/05/14</t>
-        </is>
-      </c>
-      <c r="I40" s="9" t="inlineStr"/>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/23</t>
+        </is>
+      </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>2026/09/15</t>
+          <t>2026/09/16</t>
         </is>
       </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>2026/11/04</t>
+          <t>2026/11/11</t>
         </is>
       </c>
       <c r="L40" s="9" t="inlineStr">
         <is>
-          <t>2026/11/20</t>
+          <t>2026/11/30</t>
         </is>
       </c>
       <c r="M40" s="9" t="inlineStr">
         <is>
-          <t>2026/12/15</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="N40" s="9" t="inlineStr">
         <is>
-          <t>2026/12/25</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
-          <t>DVT 開機OK， RD test :8/4~8/31</t>
+          <t>RD 測試中, 0N gerberout @8/25</t>
         </is>
       </c>
       <c r="P40" s="11" t="inlineStr">
@@ -3637,12 +3650,12 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>13Q5</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Prestige 13 AI+ A4M</t>
+          <t>Stealth 16 AI+ B4WE</t>
         </is>
       </c>
       <c r="D41" s="17" t="inlineStr">
@@ -3652,142 +3665,144 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>NVL-H 28W</t>
+          <t>NVL-H 45W</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Intel® Arc™ Graphics</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>顏春梅</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
+          <t>2026/05/22</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>2026/10/08</t>
+          <t>2026/09/16</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>2026/11/21</t>
+          <t>2026/11/11</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>2026/11/22</t>
+          <t>2026/11/27</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>2026/12/22</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="O41" s="6" t="inlineStr">
         <is>
-          <t>DVT SMT@8/18</t>
+          <t>0A PCBA DVT 驗證中,預計9/2 0B 出圖</t>
         </is>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
+          <t>1)NV VBIOS 驗證時間6周
+2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" hidden="1" outlineLevel="1">
+      <c r="A42" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WI</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WF</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E42" s="9" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5080</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>賴雪鳳</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/23</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/31</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K42" s="4" t="inlineStr">
+      <c r="K42" s="9" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/30</t>
-        </is>
-      </c>
-      <c r="M42" s="4" t="inlineStr">
+      <c r="L42" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/27</t>
+        </is>
+      </c>
+      <c r="M42" s="9" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="N42" s="9" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O42" s="6" t="inlineStr">
-        <is>
-          <t>RD 測試中, 0N gerberout @8/25</t>
-        </is>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>1) Schedule:NV VBIOS @1/6, gating 8天,預計12/E 拿到WHQL，可能影響到最終TTM 時間</t>
+      <c r="O42" s="11" t="inlineStr">
+        <is>
+          <t>0A PCBA DVT 驗證中,預計9/2 0B 出圖</t>
+        </is>
+      </c>
+      <c r="P42" s="11" t="inlineStr">
+        <is>
+          <t>1)NV VBIOS 驗證時間6周
+2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3812,12 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WH</t>
+          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
         </is>
       </c>
       <c r="D43" s="15" t="inlineStr">
@@ -3817,12 +3832,12 @@
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr">
@@ -3832,7 +3847,7 @@
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
-          <t>2026/07/23</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="J43" s="9" t="inlineStr">
@@ -3847,7 +3862,7 @@
       </c>
       <c r="L43" s="9" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2026/11/27</t>
         </is>
       </c>
       <c r="M43" s="9" t="inlineStr">
@@ -3862,12 +3877,13 @@
       </c>
       <c r="O43" s="11" t="inlineStr">
         <is>
-          <t>RD 測試中, 0N gerberout @8/25</t>
+          <t>0A PCBA DVT 驗證中,預計9/2 0B 出圖</t>
         </is>
       </c>
       <c r="P43" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)NV VBIOS 驗證時間6周
+2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
     </row>
@@ -3877,12 +3893,12 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WJ</t>
+          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
@@ -3897,12 +3913,12 @@
       </c>
       <c r="F44" s="9" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="H44" s="9" t="inlineStr">
@@ -3912,7 +3928,7 @@
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
-          <t>2026/07/23</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="J44" s="9" t="inlineStr">
@@ -3927,7 +3943,7 @@
       </c>
       <c r="L44" s="9" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2026/11/27</t>
         </is>
       </c>
       <c r="M44" s="9" t="inlineStr">
@@ -3942,12 +3958,13 @@
       </c>
       <c r="O44" s="11" t="inlineStr">
         <is>
-          <t>RD 測試中, 0N gerberout @8/25</t>
+          <t>0A PCBA DVT 驗證中,預計9/2 0B 出圖</t>
         </is>
       </c>
       <c r="P44" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)NV VBIOS 驗證時間6周
+2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
     </row>
@@ -3957,240 +3974,237 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>14W1</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WE</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="inlineStr">
+          <t>Modern 14S H3M</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>WCL 25W</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Intel® graphics</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>許婕</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/28</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/10</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/10</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/15</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>2027/01/12</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>2027/01/22</t>
+        </is>
+      </c>
+      <c r="O45" s="6" t="inlineStr">
+        <is>
+          <t>8/11 已kick off，预计9/14 0A gerberout</t>
+        </is>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>BOE FHD 120Hz panel MP料交期16w-20w，RD回復需等EVT 測試結束視結果備MP料，MP料最快到料時間3/E，機種MP 4/M，與target gap 2.5M</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>2661</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Modern 16S H3M</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>WCL 25W</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Intel® graphics</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>許婕</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/28</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/10</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/10</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/15</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>2027/01/12</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>2027/01/22</t>
+        </is>
+      </c>
+      <c r="O46" s="6" t="inlineStr">
+        <is>
+          <t>leverage Modern 14S H3M</t>
+        </is>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>2654</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Raider 16 Max HX B4WH</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>賴雪鳳</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/31</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/27</t>
-        </is>
-      </c>
-      <c r="M45" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N45" s="4" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>吳美芳</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O45" s="6" t="inlineStr">
-        <is>
-          <t>0A PCBA DVT 驗證中,預計9/2 0B 出圖</t>
-        </is>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>1)NV VBIOS 驗證時間6周
-2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" hidden="1" outlineLevel="1">
-      <c r="A46" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WF</t>
-        </is>
-      </c>
-      <c r="D46" s="15" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E46" s="9" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F46" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G46" s="9" t="inlineStr">
-        <is>
-          <t>賴雪鳳</t>
-        </is>
-      </c>
-      <c r="H46" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/31</t>
-        </is>
-      </c>
-      <c r="J46" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K46" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L46" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/27</t>
-        </is>
-      </c>
-      <c r="M46" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N46" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="O46" s="11" t="inlineStr">
-        <is>
-          <t>0A PCBA DVT 驗證中,預計9/2 0B 出圖</t>
-        </is>
-      </c>
-      <c r="P46" s="11" t="inlineStr">
-        <is>
-          <t>1)NV VBIOS 驗證時間6周
-2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" hidden="1" outlineLevel="1">
-      <c r="A47" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
-        </is>
-      </c>
-      <c r="D47" s="15" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F47" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G47" s="9" t="inlineStr">
-        <is>
-          <t>賴雪鳳</t>
-        </is>
-      </c>
-      <c r="H47" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/31</t>
-        </is>
-      </c>
-      <c r="J47" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K47" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L47" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/27</t>
-        </is>
-      </c>
-      <c r="M47" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N47" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="O47" s="11" t="inlineStr">
-        <is>
-          <t>0A PCBA DVT 驗證中,預計9/2 0B 出圖</t>
-        </is>
-      </c>
-      <c r="P47" s="11" t="inlineStr">
-        <is>
-          <t>1)NV VBIOS 驗證時間6周
-2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O47" s="6" t="inlineStr">
+        <is>
+          <t>DVT RD測試中8/14~9/11，預計9/11 0N出圖</t>
+        </is>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4200,12 +4214,12 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
+          <t>Raider 16 Max HX B4WI</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
@@ -4215,141 +4229,140 @@
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>NVL-H 45W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
-          <t>2026/05/22</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
-          <t>2026/07/31</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>2026/09/16</t>
+          <t>2026/09/29</t>
         </is>
       </c>
       <c r="K48" s="9" t="inlineStr">
         <is>
-          <t>2026/11/11</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="L48" s="9" t="inlineStr">
         <is>
-          <t>2026/11/27</t>
+          <t>2027/02/02</t>
         </is>
       </c>
       <c r="M48" s="9" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2027/03/08</t>
         </is>
       </c>
       <c r="N48" s="9" t="inlineStr">
         <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O48" s="11" t="inlineStr">
+        <is>
+          <t>DVT RD測試中8/14~9/11，預計9/11 0N出圖</t>
+        </is>
+      </c>
+      <c r="P48" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" hidden="1" outlineLevel="1">
+      <c r="A49" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>2654</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>Raider 16 Max HX B4WJ</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5090</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>吳美芳</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K49" s="9" t="inlineStr">
+        <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O48" s="11" t="inlineStr">
-        <is>
-          <t>0A PCBA DVT 驗證中,預計9/2 0B 出圖</t>
-        </is>
-      </c>
-      <c r="P48" s="11" t="inlineStr">
-        <is>
-          <t>1)NV VBIOS 驗證時間6周
-2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>14W1</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Modern 14S H3M</t>
-        </is>
-      </c>
-      <c r="D49" s="18" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>WCL 25W</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>Intel® graphics</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>許婕</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/11</t>
-        </is>
-      </c>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/28</t>
-        </is>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/10</t>
-        </is>
-      </c>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/10</t>
-        </is>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/15</t>
-        </is>
-      </c>
-      <c r="M49" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/12</t>
-        </is>
-      </c>
-      <c r="N49" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/22</t>
-        </is>
-      </c>
-      <c r="O49" s="6" t="inlineStr">
-        <is>
-          <t>8/11 已kick off，预计9/14 0A gerberout</t>
-        </is>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
+      <c r="L49" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M49" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N49" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O49" s="11" t="inlineStr">
+        <is>
+          <t>DVT RD測試中8/14~9/11，預計9/11 0N出圖</t>
+        </is>
+      </c>
+      <c r="P49" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -4361,12 +4374,12 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Modern 16S H3M</t>
+          <t>Titan 18 HX B4WH</t>
         </is>
       </c>
       <c r="D50" s="18" t="inlineStr">
@@ -4376,142 +4389,142 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>WCL 25W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Intel® graphics</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>許婕</t>
+          <t>高宇奇</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>2026/08/11</t>
+          <t>2026/06/29</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>2026/09/28</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>2026/11/10</t>
+          <t>2026/10/23</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>2026/12/10</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>2026/12/15</t>
+          <t>2027/02/01</t>
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>2027/01/12</t>
+          <t>2027/03/08</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>2027/01/22</t>
+          <t>2027/03/18</t>
         </is>
       </c>
       <c r="O50" s="6" t="inlineStr">
         <is>
-          <t>leverage Modern 14S H3M</t>
+          <t>1) 根據料況及排程,已安排8/19 DVT上線SMT,打板後不測試立即入庫調撥,Target 8/24 for台北RD測試開機.</t>
         </is>
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
+          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" hidden="1" outlineLevel="1">
+      <c r="A51" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>2654</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Raider 16 Max HX B4WH</t>
-        </is>
-      </c>
-      <c r="D51" s="17" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>Titan 18 HX B4WI</t>
+        </is>
+      </c>
+      <c r="D51" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5070Ti</t>
-        </is>
-      </c>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>吳美芳</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/05</t>
-        </is>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K51" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M51" s="4" t="inlineStr">
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5080</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>高宇奇</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/23</t>
+        </is>
+      </c>
+      <c r="K51" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/08</t>
+        </is>
+      </c>
+      <c r="L51" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/01</t>
+        </is>
+      </c>
+      <c r="M51" s="9" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N51" s="4" t="inlineStr">
+      <c r="N51" s="9" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O51" s="6" t="inlineStr">
-        <is>
-          <t>DVT板子原計劃8/10調撥，因臺風delay兩天，板子早上已到臺北</t>
-        </is>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="O51" s="11" t="inlineStr">
+        <is>
+          <t>1) 根據料況及排程,已安排8/19 DVT上線SMT,打板後不測試立即入庫調撥,Target 8/24 for台北RD測試開機.</t>
+        </is>
+      </c>
+      <c r="P51" s="11" t="inlineStr">
+        <is>
+          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
         </is>
       </c>
     </row>
@@ -4521,17 +4534,17 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B4WI</t>
-        </is>
-      </c>
-      <c r="D52" s="15" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Titan 18 HX B4WJ</t>
+        </is>
+      </c>
+      <c r="D52" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
@@ -4541,37 +4554,37 @@
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>高宇奇</t>
         </is>
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/06/29</t>
         </is>
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>2026/09/29</t>
+          <t>2026/10/23</t>
         </is>
       </c>
       <c r="K52" s="9" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="L52" s="9" t="inlineStr">
         <is>
-          <t>2027/02/02</t>
+          <t>2027/02/01</t>
         </is>
       </c>
       <c r="M52" s="9" t="inlineStr">
@@ -4586,12 +4599,12 @@
       </c>
       <c r="O52" s="11" t="inlineStr">
         <is>
-          <t>DVT板子原計劃8/10調撥，因臺風delay兩天，板子早上已到臺北</t>
+          <t>1) 根據料況及排程,已安排8/19 DVT上線SMT,打板後不測試立即入庫調撥,Target 8/24 for台北RD測試開機.</t>
         </is>
       </c>
       <c r="P52" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
         </is>
       </c>
     </row>
@@ -4601,57 +4614,57 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B4WJ</t>
-        </is>
-      </c>
-      <c r="D53" s="15" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Raider 18 Max HX B4WH</t>
+        </is>
+      </c>
+      <c r="D53" s="16" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>NVL-HX 55W</t>
+          <t>NVL-HX 65W</t>
         </is>
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>高宇奇</t>
         </is>
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/06/29</t>
         </is>
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
-          <t>2026/09/29</t>
+          <t>2026/10/23</t>
         </is>
       </c>
       <c r="K53" s="9" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="L53" s="9" t="inlineStr">
         <is>
-          <t>2027/02/02</t>
+          <t>2027/02/01</t>
         </is>
       </c>
       <c r="M53" s="9" t="inlineStr">
@@ -4666,92 +4679,92 @@
       </c>
       <c r="O53" s="11" t="inlineStr">
         <is>
-          <t>DVT板子原計劃8/10調撥，因臺風delay兩天，板子早上已到臺北</t>
+          <t>1) 根據料況及排程,已安排8/19 DVT上線SMT,打板後不測試立即入庫調撥,Target 8/24 for台北RD測試開機.</t>
         </is>
       </c>
       <c r="P53" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
+          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" hidden="1" outlineLevel="1">
+      <c r="A54" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>1851</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>Titan 18 HX B4WH</t>
-        </is>
-      </c>
-      <c r="D54" s="18" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Raider 18 Max HX B4WI</t>
+        </is>
+      </c>
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5070Ti</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>NVL-HX 65W</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5080</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
         <is>
           <t>高宇奇</t>
         </is>
       </c>
-      <c r="H54" s="4" t="inlineStr">
+      <c r="H54" s="9" t="inlineStr">
         <is>
           <t>2026/06/29</t>
         </is>
       </c>
-      <c r="I54" s="4" t="inlineStr">
+      <c r="I54" s="9" t="inlineStr">
         <is>
           <t>2026/08/19</t>
         </is>
       </c>
-      <c r="J54" s="4" t="inlineStr">
+      <c r="J54" s="9" t="inlineStr">
         <is>
           <t>2026/10/23</t>
         </is>
       </c>
-      <c r="K54" s="4" t="inlineStr">
+      <c r="K54" s="9" t="inlineStr">
         <is>
           <t>2027/01/08</t>
         </is>
       </c>
-      <c r="L54" s="4" t="inlineStr">
+      <c r="L54" s="9" t="inlineStr">
         <is>
           <t>2027/02/01</t>
         </is>
       </c>
-      <c r="M54" s="4" t="inlineStr">
+      <c r="M54" s="9" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N54" s="4" t="inlineStr">
+      <c r="N54" s="9" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O54" s="6" t="inlineStr">
-        <is>
-          <t>PCB 0M已於8/4 gerber out,預計8/19 DVT SMT.</t>
-        </is>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
+      <c r="O54" s="11" t="inlineStr">
+        <is>
+          <t>1) 根據料況及排程,已安排8/19 DVT上線SMT,打板後不測試立即入庫調撥,Target 8/24 for台北RD測試開機.</t>
+        </is>
+      </c>
+      <c r="P54" s="11" t="inlineStr">
+        <is>
+          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
         </is>
       </c>
     </row>
@@ -4766,7 +4779,7 @@
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Titan 18 HX B4WI</t>
+          <t>Raider 18 Max HX B4WJ</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
@@ -4776,142 +4789,142 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
+          <t>NVL-HX 65W</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5090</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>高宇奇</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/23</t>
+        </is>
+      </c>
+      <c r="K55" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/08</t>
+        </is>
+      </c>
+      <c r="L55" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/01</t>
+        </is>
+      </c>
+      <c r="M55" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N55" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O55" s="11" t="inlineStr">
+        <is>
+          <t>1) 根據料況及排程,已安排8/19 DVT上線SMT,打板後不測試立即入庫調撥,Target 8/24 for台北RD測試開機.</t>
+        </is>
+      </c>
+      <c r="P55" s="11" t="inlineStr">
+        <is>
+          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>2655</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Crosshair 16 Max HX E4WEK</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5080</t>
-        </is>
-      </c>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>高宇奇</t>
-        </is>
-      </c>
-      <c r="H55" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="I55" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/19</t>
-        </is>
-      </c>
-      <c r="J55" s="9" t="inlineStr">
-        <is>
-          <t>2026/10/23</t>
-        </is>
-      </c>
-      <c r="K55" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/08</t>
-        </is>
-      </c>
-      <c r="L55" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/01</t>
-        </is>
-      </c>
-      <c r="M55" s="9" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>鮑佩佩</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N55" s="9" t="inlineStr">
+      <c r="N56" s="4" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O55" s="11" t="inlineStr">
-        <is>
-          <t>PCB 0M已於8/4 gerber out,預計8/19 DVT SMT.</t>
-        </is>
-      </c>
-      <c r="P55" s="11" t="inlineStr">
-        <is>
-          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" hidden="1" outlineLevel="1">
-      <c r="A56" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>1851</t>
-        </is>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>Titan 18 HX B4WJ</t>
-        </is>
-      </c>
-      <c r="D56" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F56" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5090</t>
-        </is>
-      </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>高宇奇</t>
-        </is>
-      </c>
-      <c r="H56" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/19</t>
-        </is>
-      </c>
-      <c r="J56" s="9" t="inlineStr">
-        <is>
-          <t>2026/10/23</t>
-        </is>
-      </c>
-      <c r="K56" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/08</t>
-        </is>
-      </c>
-      <c r="L56" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/01</t>
-        </is>
-      </c>
-      <c r="M56" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N56" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O56" s="11" t="inlineStr">
-        <is>
-          <t>PCB 0M已於8/4 gerber out,預計8/19 DVT SMT.</t>
-        </is>
-      </c>
-      <c r="P56" s="11" t="inlineStr">
-        <is>
-          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
+      <c r="O56" s="6" t="inlineStr">
+        <is>
+          <t>DVT 測試中</t>
+        </is>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4921,57 +4934,57 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Raider 18 Max HX B4WH</t>
-        </is>
-      </c>
-      <c r="D57" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
+          <t>Crosshair 16 Max HX E4WFK</t>
+        </is>
+      </c>
+      <c r="D57" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>NVL-HX 65W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
-          <t>高宇奇</t>
+          <t>鮑佩佩</t>
         </is>
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
-          <t>2026/08/19</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="J57" s="9" t="inlineStr">
         <is>
-          <t>2026/10/23</t>
+          <t>2026/09/29</t>
         </is>
       </c>
       <c r="K57" s="9" t="inlineStr">
         <is>
-          <t>2027/01/08</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="L57" s="9" t="inlineStr">
         <is>
-          <t>2027/02/01</t>
+          <t>2027/02/02</t>
         </is>
       </c>
       <c r="M57" s="9" t="inlineStr">
@@ -4986,12 +4999,12 @@
       </c>
       <c r="O57" s="11" t="inlineStr">
         <is>
-          <t>PCB 0M已於8/4 gerber out,預計8/19 DVT SMT.</t>
+          <t>DVT 測試中</t>
         </is>
       </c>
       <c r="P57" s="11" t="inlineStr">
         <is>
-          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -5001,57 +5014,57 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Raider 18 Max HX B4WI</t>
-        </is>
-      </c>
-      <c r="D58" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
+          <t>Crosshair 16 Max HX E4WGK</t>
+        </is>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>NVL-HX 65W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>高宇奇</t>
+          <t>鮑佩佩</t>
         </is>
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
-          <t>2026/08/19</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>2026/10/23</t>
+          <t>2026/09/29</t>
         </is>
       </c>
       <c r="K58" s="9" t="inlineStr">
         <is>
-          <t>2027/01/08</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="L58" s="9" t="inlineStr">
         <is>
-          <t>2027/02/01</t>
+          <t>2027/02/02</t>
         </is>
       </c>
       <c r="M58" s="9" t="inlineStr">
@@ -5066,12 +5079,12 @@
       </c>
       <c r="O58" s="11" t="inlineStr">
         <is>
-          <t>PCB 0M已於8/4 gerber out,預計8/19 DVT SMT.</t>
+          <t>DVT 測試中</t>
         </is>
       </c>
       <c r="P58" s="11" t="inlineStr">
         <is>
-          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -5081,57 +5094,57 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Raider 18 Max HX B4WJ</t>
-        </is>
-      </c>
-      <c r="D59" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
+          <t>Crosshair 16 Max HX E4WGXK</t>
+        </is>
+      </c>
+      <c r="D59" s="15" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>NVL-HX 65W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>高宇奇</t>
+          <t>鮑佩佩</t>
         </is>
       </c>
       <c r="H59" s="9" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
-          <t>2026/08/19</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="J59" s="9" t="inlineStr">
         <is>
-          <t>2026/10/23</t>
+          <t>2026/09/29</t>
         </is>
       </c>
       <c r="K59" s="9" t="inlineStr">
         <is>
-          <t>2027/01/08</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="L59" s="9" t="inlineStr">
         <is>
-          <t>2027/02/01</t>
+          <t>2027/02/02</t>
         </is>
       </c>
       <c r="M59" s="9" t="inlineStr">
@@ -5146,337 +5159,17 @@
       </c>
       <c r="O59" s="11" t="inlineStr">
         <is>
-          <t>PCB 0M已於8/4 gerber out,預計8/19 DVT SMT.</t>
+          <t>DVT 測試中</t>
         </is>
       </c>
       <c r="P59" s="11" t="inlineStr">
         <is>
-          <t>1) SSE需要進行約4週的POC評估確認1851 aRGB介面Light Bar的技術可行性以及後續FW開發工作,已提供MCU demo board/Light bar for SSE POC study, SSE預計WW33提供評估結果.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>2655</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WEK</t>
-        </is>
-      </c>
-      <c r="D60" s="17" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>鮑佩佩</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I60" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/06</t>
-        </is>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K60" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M60" s="4" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N60" s="4" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O60" s="6" t="inlineStr">
-        <is>
-          <t>DVT 測試中</t>
-        </is>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
-        <is>
           <t>NA</t>
         </is>
       </c>
     </row>
-    <row r="61" hidden="1" outlineLevel="1">
-      <c r="A61" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>2655</t>
-        </is>
-      </c>
-      <c r="C61" s="9" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WFK</t>
-        </is>
-      </c>
-      <c r="D61" s="15" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E61" s="9" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F61" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G61" s="9" t="inlineStr">
-        <is>
-          <t>鮑佩佩</t>
-        </is>
-      </c>
-      <c r="H61" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/06</t>
-        </is>
-      </c>
-      <c r="J61" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K61" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L61" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M61" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N61" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O61" s="11" t="inlineStr">
-        <is>
-          <t>DVT 測試中</t>
-        </is>
-      </c>
-      <c r="P61" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" hidden="1" outlineLevel="1">
-      <c r="A62" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>2655</t>
-        </is>
-      </c>
-      <c r="C62" s="9" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WGK</t>
-        </is>
-      </c>
-      <c r="D62" s="15" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E62" s="9" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F62" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G62" s="9" t="inlineStr">
-        <is>
-          <t>鮑佩佩</t>
-        </is>
-      </c>
-      <c r="H62" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/06</t>
-        </is>
-      </c>
-      <c r="J62" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K62" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L62" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M62" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N62" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O62" s="11" t="inlineStr">
-        <is>
-          <t>DVT 測試中</t>
-        </is>
-      </c>
-      <c r="P62" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" hidden="1" outlineLevel="1">
-      <c r="A63" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>2655</t>
-        </is>
-      </c>
-      <c r="C63" s="9" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WGXK</t>
-        </is>
-      </c>
-      <c r="D63" s="15" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E63" s="9" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F63" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G63" s="9" t="inlineStr">
-        <is>
-          <t>鮑佩佩</t>
-        </is>
-      </c>
-      <c r="H63" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I63" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/06</t>
-        </is>
-      </c>
-      <c r="J63" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K63" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L63" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M63" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N63" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O63" s="11" t="inlineStr">
-        <is>
-          <t>DVT 測試中</t>
-        </is>
-      </c>
-      <c r="P63" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P63"/>
+  <autoFilter ref="A1:P59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/npi_dashboard.xlsx
+++ b/npi_dashboard.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPI Dashboard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -134,6 +134,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -519,7 +522,7 @@
     <outlinePr summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P59"/>
+  <dimension ref="A1:P60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -689,7 +692,7 @@
       </c>
       <c r="O2" s="6" t="inlineStr">
         <is>
-          <t>DDR5: RTX5050進行C/R組裝@8/20 26PN078888C*50</t>
+          <t>DDR5: RTX5050,8/28正式進入MP</t>
         </is>
       </c>
       <c r="P2" s="6" t="inlineStr">
@@ -765,7 +768,7 @@
       </c>
       <c r="O3" s="11" t="inlineStr">
         <is>
-          <t>DDR5: RTX5060預計C/R組裝@8/28 26PN077951C*50</t>
+          <t>DDR5: RTX5060預計C/R組裝@8/29 26PN077951C*50</t>
         </is>
       </c>
       <c r="P3" s="11" t="inlineStr">
@@ -841,7 +844,7 @@
       </c>
       <c r="O4" s="11" t="inlineStr">
         <is>
-          <t>DDR5: RTX5070進行ATS 組裝@8/20 26PN077002A*100</t>
+          <t>DDR5: RTX5070,8/28正式進入MP</t>
         </is>
       </c>
       <c r="P4" s="11" t="inlineStr">
@@ -917,7 +920,7 @@
       </c>
       <c r="O5" s="11" t="inlineStr">
         <is>
-          <t>DDR4: RTX5050進行C/R組裝@8/20 26PN078888C*50</t>
+          <t>DDR4: RTX5050,8/28正式進入MP</t>
         </is>
       </c>
       <c r="P5" s="11" t="inlineStr">
@@ -993,7 +996,7 @@
       </c>
       <c r="O6" s="11" t="inlineStr">
         <is>
-          <t>DDR4: RTX5060預計C/R組裝@8/28 26PN077951C*50</t>
+          <t>DDR4: RTX5060預計C/R組裝@8/29 26PN077951C*50</t>
         </is>
       </c>
       <c r="P6" s="11" t="inlineStr">
@@ -1069,7 +1072,7 @@
       </c>
       <c r="O7" s="11" t="inlineStr">
         <is>
-          <t>DDR4: RTX5070進行ATS 組裝@8/20 26PN077002A*100</t>
+          <t>DDR4: RTX5070,8/28正式進入MP</t>
         </is>
       </c>
       <c r="P7" s="11" t="inlineStr">
@@ -1305,7 +1308,7 @@
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
-          <t>1) ATS 組裝@ 8/20, 工單:26PN072477A / 26PN072950A 各50</t>
+          <t>1) 8/28正式進入MP</t>
         </is>
       </c>
       <c r="P10" s="6" t="inlineStr">
@@ -1381,17 +1384,14 @@
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
-          <t>MSI:  MVT DQA test中 微步：ATS ASSY@8/25--會再匯整料況明確組裝時間</t>
+          <t>微步：ATS ASSY@8/27早進行首件組裝, 客驗機器8/28 ready</t>
         </is>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>1) Function issue： a.	HDI: 8/20提供MP HDI申請單, 8/21開始製作 b.	BIOS: 待8/20 微步提供BIOS 100 , 需驗證bug &amp; 測試完整BIOS Function c.	Long run reboot issue, 5台run 500 loops, 3台hang MSI logo, 微步team正在分析中 (
+          <t>1) Function issue：等8/27 BIOS 102作驗證 a.UCSI充电的OS信息, 驗證在60W的時候, 幾率性不跳OS彈窗 b.	User Password進入BSU, Storage Information &amp; System Information有灰階 c.	AC下无法透过1P15 Docking的LAN唤醒MODS d.	BSU下使用UEFI BIOS update方式有概率更新BIOS fail ME Issue:Drop &amp; Shock(non-OP)測試需使用ATS客驗機器複驗	 (
 2) ATS工單： 9S7-24V111-006*38 9S7-24V111-015*56 (
-3)8月&amp;9月業務訂單認證追蹤 a. DE 9S7-24V111-011* 56 CE認證, 取證時間target 8/E, 具體日期待微步確認中 b. NZ* 76 （9S7-24V111-005* 38+ 9S7-24V111-006 *
-38） RCM認證, CE+ 1 week提供RCM報告, 需進口商登記完成後出貨 c.UA* 112（9S7-24V111-017*56+ 9S7-24V111-015*
-56） Ukraine RF CoC+DoC認證, 由MSI負責申請, UA業務確認follow系統時間排單出貨 d.JP*56(9S7-24V111-009*50+ 9S7-24V111-016*
-6) VCCI認證, 8/E之前可 取證完成, 出貨時間需考量JP鍵盤備料ready日期, 9/E之前可出貨. (
+3)8月&amp;9月業務訂單認證追蹤 a. DE : CE草稿8/27 ready, Review OK後加一周取證 b. NZ: RCM認證, CE+ 1 week提供RCM報告, 需進口商登記完成後出貨 c.UA：Ukraine RF CoC+DoC認證, 由MSI負責申請, UA業務確認follow系統時間排單出貨 d.JP*56: VCCI認證8/26完成, 出貨時間需考量JP鍵盤備料ready日期, 9/E之前可出貨. (
 4) JP KB 開模9/10試模, 9/20交料, JP工單可出貨時間@9/24</t>
         </is>
       </c>
@@ -1468,9 +1468,10 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>1) Function issue：同24V1, ME issue: a.Panel Mura: 使用COST panel, 微步回復需增加輔料，預抓8/21寄送機器增加Mura對策for MSI驗證 b.	Shock測試fail, B件攝像頭位置彈開&amp;電池定位柱斷裂：需要新的鍵芯支架 複驗, 同時參考26VL機種, 將力度改160G作複測, 樣品可提供時間待微步確認 c.	Panel Scuff測試屏幕碎晶：參考26VL機種, 使用加背包的方式進行模擬複測 d.	Shock測試屏幕破損: 參考26VL機種, 將力度改160G作測試 (
-2) ATS工單: 9S7-26V111-006*20 9S7-26V111-004*200 9S7-26V111-005*400 (
-2) 8月&amp;9月業務訂單認證追蹤 a.DE* 1650 CE認證, 取證時間target 8/E, 具體日期待微步確認中 b.IT 9S7-26V111-002*300 CE認證, 取證時間target 8/E, 具體日期待微步確認中 c.US 9S7-26V111-001*1020 FCC ID， Target 9/M取證(已經拿到FCC報告在內部確認中)  d.PL 9S7-26V111-003*56 CE認證, 取證時間target 8/E, 具體日期待微步確認中</t>
+          <t>1) Function issue：同24V1 (
+2) ATS工單:  9S7-26V111-005*400 (
+2) 8月&amp;9月業務訂單認證追蹤：a. DE&amp;IT&amp;PL : CE草稿8/27 ready, Review OK後加一周取證 b.US: FCC: 報告確認天線位置需修改   ETL認證: 待微步更新進度  ，9/B control number, ETL認證logo圖樣 9/M取證, (
+4) 新增: JP KB開模備料時間待確認, 日本業務期望11月份的訂單</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1486,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Cyborg A15 C1PWE</t>
+          <t>Cyborg A15 Max C1PWF</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -1500,7 +1501,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -1541,12 +1542,12 @@
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>HPT sku:MVT測試中</t>
+          <t>HPT:MVT測試中</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>1).業務下單要收斂到Cyborg A15 non Max, 因team member已取得Max HPT MVT機台測試中,只會完成MVT測試,Max不開BTO,不做ATS
+          <t>1).8/25 業務通知需專案開BTO,滿足業務已接訂單
 2).Schedule:AMD PI 1200I NDA Release delay(6/19→7/
 28)與生管延後MVT SMT 排程(8/4→8/
 7),累計delay 42天,取消 DVT排程改以 APU Rework 驗證追趕時程後,MP還是會delay 22天至9/22(先前已由 9 /17提前至 8/31,現又延至9/
@@ -1554,84 +1555,82 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
+    <row r="14" hidden="1" outlineLevel="1">
+      <c r="A14" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>1T91</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Claw 8 EX AI+ CG3M</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>15TK</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Cyborg A15 C1PWE</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>PTL-H 25W</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>楊淑賢</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>2026/01/31</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/26</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/18</t>
-        </is>
-      </c>
-      <c r="M14" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/15</t>
-        </is>
-      </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/30</t>
-        </is>
-      </c>
-      <c r="O14" s="6" t="inlineStr">
-        <is>
-          <t>1. function: 需補測G3+LPDDR5x-32GB的performance/BAT/thermal test, PCBA預抓8/26 SMT
-2)藍色機構件驗證: 8/21樣品到料, ME RD更換4台機器, 8/24 test start</t>
-        </is>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>新增藍色SKU G3+ LPDDR5x-32GB需求, 1st MOQ: 3K</t>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>HWK 45W</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>蔡東宏</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/28</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr"/>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/07</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/12</t>
+        </is>
+      </c>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/22</t>
+        </is>
+      </c>
+      <c r="O14" s="11" t="inlineStr">
+        <is>
+          <t>HPT:MVT測試中</t>
+        </is>
+      </c>
+      <c r="P14" s="11" t="inlineStr">
+        <is>
+          <t>1).Schedule:AMD PI 1200I NDA Release delay(6/19→7/
+28)與生管延後MVT SMT 排程(8/4→8/
+7),累計delay 42天,取消 DVT排程改以 APU Rework 驗證追趕時程後,MP還是會delay 22天至9/22(先前已由 9 /17提前至 8/31,現又延至9/
+22),後續將依實際測試結果滾動式調整專案時程</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1640,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>14T3</t>
+          <t>1T91</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Prestige N14 AI+ D1M</t>
+          <t>Claw 8 EX AI+ CG3M</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -1656,7 +1655,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>N1 35W</t>
+          <t>PTL-H 25W</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1666,53 +1665,52 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>倪嬌嬌</t>
+          <t>楊淑賢</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>2025/04/30</t>
+          <t>2025/11/06</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>2025/09/01</t>
+          <t>2025/12/16</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>2026/04/15</t>
+          <t>2026/01/31</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>2026/08/13</t>
+          <t>2026/08/26</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>2026/09/14</t>
+          <t>2026/08/18</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>2026/11/09</t>
+          <t>2026/09/21</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2026/09/30</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>MVT2 SMT depend on PS Software時間-- PS software release@8/21, 可排單日期預抓8/27, 需與MPM討論後確認</t>
+          <t>MVT DQA test中, 8/26-9/11</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>1) Schedule:  a. MVT2 SMT date考量PS software release時間 b. 2.8K panel*286 pcs 8/28 ETD, 廠內庫存不足, 計劃等9/4進料後再作MVT ASSY
-2)備料：量產交料2.8k HQ23, 最新MP*1K交期,  Samsung回復計劃10/E ETD, 可滿足ATS需求, 持續追蹤</t>
+          <t>1）備料: 藍色機構件9/18, update ATS start@9/21</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1720,12 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>14T3</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Prestige N16 AI+ C1M</t>
+          <t>Prestige N14 AI+ D1M</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -1737,7 +1735,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>N1 45W</t>
+          <t>N1 35W</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1747,7 +1745,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>倪嬌嬌</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1787,12 +1785,12 @@
       </c>
       <c r="O16" s="6" t="inlineStr">
         <is>
-          <t>MVT1:8/13 SMT, 8/14 Pre -Assy  for 少數RD 測試, 待PS SW ready 再上線做MVT2 for 全部team member</t>
+          <t>MVT2 SMT@8/28, MVT ASSY@9/4-- depend on panel交期</t>
         </is>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>備料: Samsung 2.8K panel 採購備料HR14*2K for N1 ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
+          <t>1)備料：a. 2.8K panel: MP*1K交期, 計劃10/E ETD, 可滿足ATS需求, 但需持續追蹤DR set測試狀況 b. PCB原材: 1st MOQ1K,目前只先留300 pcs PCB原材for ATS use, 剩餘PCB原材料預估需11/E才能ready, PCB備料L/T 8weeks, PCB交料預估到一月份, 採購持續pull in中</t>
         </is>
       </c>
     </row>
@@ -1802,155 +1800,155 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
+          <t>2623</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Prestige N16 AI+ C1M</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>N1 45W</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>賴雪鳳</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/30</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>2025/09/01</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/09</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/23</t>
+        </is>
+      </c>
+      <c r="O17" s="6" t="inlineStr">
+        <is>
+          <t>MVT1:8/13 SMT, 8/14 Pre -Assy  for 少數RD 測試, 待PS SW ready 再上線做MVT2 for 全部team member</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>備料: Samsung 2.8K panel 採購備料HR14*2K for N1 ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
           <t>1861</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Katana 18 HX A14WEK</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>EVT</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>RPL-HX refresh 55W</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>顧曉琴</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>2026/06/15</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>2026/08/13</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>2026/10/12</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>2026/11/02</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>2026/11/21</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>2026/11/30</t>
         </is>
       </c>
-      <c r="O17" s="6" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR5: EVT SMT1 PCBA預計8/20 到台北供RD測試; SMT2 @ 8/24, Pre-assy @ 8/25, ASSY @ 8/29</t>
-        </is>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" hidden="1" outlineLevel="1">
-      <c r="A18" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Katana 18 HX A14WFK</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>EVT</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>顧曉琴</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
-      <c r="K18" s="9" t="inlineStr">
-        <is>
-          <t>2026/10/12</t>
-        </is>
-      </c>
-      <c r="L18" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/02</t>
-        </is>
-      </c>
-      <c r="M18" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/21</t>
-        </is>
-      </c>
-      <c r="N18" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/30</t>
-        </is>
-      </c>
-      <c r="O18" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR5: EVT SMT1 PCBA預計8/20 到台北供RD測試; SMT2 @ 8/24, Pre-assy @ 8/25, ASSY @ 8/29</t>
-        </is>
-      </c>
-      <c r="P18" s="11" t="inlineStr">
+      <c r="O18" s="6" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR5: EVT Pre-assy @ 8/25, ASSY @ 8/29, 預抓9/2提供給DQA測試</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1967,10 +1965,10 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGK</t>
-        </is>
-      </c>
-      <c r="D19" s="14" t="inlineStr">
+          <t>Katana 18 HX A14WFK</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>EVT</t>
         </is>
@@ -1982,7 +1980,7 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
@@ -2027,7 +2025,7 @@
       </c>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: EVT SMT1 PCBA預計8/20 到台北供RD測試; SMT2 @ 8/24, Pre-assy @ 8/25, ASSY @ 8/29</t>
+          <t>RPL-HX R + DDR5: EVT Pre-assy @ 8/25, ASSY @ 8/29, 預抓9/2提供給DQA測試</t>
         </is>
       </c>
       <c r="P19" s="11" t="inlineStr">
@@ -2047,10 +2045,10 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGXK</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="inlineStr">
+          <t>Katana 18 HX A14WGK</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>EVT</t>
         </is>
@@ -2107,7 +2105,7 @@
       </c>
       <c r="O20" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: EVT SMT1 PCBA預計8/20 到台北供RD測試; SMT2 @ 8/24, Pre-assy @ 8/25, ASSY @ 8/29</t>
+          <t>RPL-HX R + DDR5: EVT Pre-assy @ 8/25, ASSY @ 8/29, 預抓9/2提供給DQA測試</t>
         </is>
       </c>
       <c r="P20" s="11" t="inlineStr">
@@ -2127,12 +2125,12 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WEOK</t>
+          <t>Katana 18 HX A14WGXK</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>DVT</t>
+          <t>EVT</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -2142,7 +2140,7 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
@@ -2152,18 +2150,22 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/08</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J21" s="9" t="inlineStr"/>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/10/12</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
@@ -2173,22 +2175,22 @@
       </c>
       <c r="M21" s="9" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2026/11/21</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>2026/12/02</t>
+          <t>2026/11/30</t>
         </is>
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+          <t>RPL-HX R + DDR5: EVT Pre-assy @ 8/25, ASSY @ 8/29, 預抓9/2提供給DQA測試</t>
         </is>
       </c>
       <c r="P21" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2203,10 +2205,10 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WFOK</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
+          <t>Katana 18 HX A14WEOK</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2218,7 +2220,7 @@
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -2279,10 +2281,10 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGOK</t>
-        </is>
-      </c>
-      <c r="D23" s="15" t="inlineStr">
+          <t>Katana 18 HX A14WFOK</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2294,7 +2296,7 @@
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
@@ -2355,10 +2357,10 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGXOK</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
+          <t>Katana 18 HX A14WGOK</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -2431,22 +2433,22 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WEK</t>
+          <t>Katana 18 HX A14WGXOK</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX Next 55W</t>
+          <t>RPL-HX refresh 55W</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
@@ -2456,34 +2458,38 @@
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I25" s="9" t="inlineStr"/>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
       <c r="J25" s="9" t="inlineStr"/>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>2026/12/08</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/11/02</t>
         </is>
       </c>
       <c r="M25" s="9" t="inlineStr">
         <is>
-          <t>2027/01/19</t>
+          <t>2026/11/23</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
         <is>
-          <t>2027/01/30</t>
+          <t>2026/12/02</t>
         </is>
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P25" s="11" t="inlineStr">
@@ -2503,10 +2509,10 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WEOK</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
+          <t>Katana 18 HX A2WEK</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -2528,14 +2534,10 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr"/>
       <c r="J26" s="9" t="inlineStr"/>
       <c r="K26" s="9" t="inlineStr">
         <is>
@@ -2559,7 +2561,7 @@
       </c>
       <c r="O26" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P26" s="11" t="inlineStr">
@@ -2579,10 +2581,10 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WFK</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
+          <t>Katana 18 HX A2WEOK</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -2594,7 +2596,7 @@
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
@@ -2604,10 +2606,14 @@
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I27" s="9" t="inlineStr"/>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
       <c r="J27" s="9" t="inlineStr"/>
       <c r="K27" s="9" t="inlineStr">
         <is>
@@ -2631,7 +2637,7 @@
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P27" s="11" t="inlineStr">
@@ -2651,10 +2657,10 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WFOK</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
+          <t>Katana 18 HX A2WFK</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -2676,14 +2682,10 @@
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr"/>
       <c r="J28" s="9" t="inlineStr"/>
       <c r="K28" s="9" t="inlineStr">
         <is>
@@ -2707,7 +2709,7 @@
       </c>
       <c r="O28" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P28" s="11" t="inlineStr">
@@ -2727,10 +2729,10 @@
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WGK</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
+          <t>Katana 18 HX A2WFOK</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -2742,7 +2744,7 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -2752,10 +2754,14 @@
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I29" s="9" t="inlineStr"/>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
       <c r="J29" s="9" t="inlineStr"/>
       <c r="K29" s="9" t="inlineStr">
         <is>
@@ -2779,7 +2785,7 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P29" s="11" t="inlineStr">
@@ -2799,10 +2805,10 @@
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WGOK</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
+          <t>Katana 18 HX A2WGK</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -2824,14 +2830,10 @@
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr"/>
       <c r="J30" s="9" t="inlineStr"/>
       <c r="K30" s="9" t="inlineStr">
         <is>
@@ -2855,7 +2857,7 @@
       </c>
       <c r="O30" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P30" s="11" t="inlineStr">
@@ -2875,10 +2877,10 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WGXK</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
+          <t>Katana 18 HX A2WGOK</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -2900,10 +2902,14 @@
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I31" s="9" t="inlineStr"/>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
       <c r="J31" s="9" t="inlineStr"/>
       <c r="K31" s="9" t="inlineStr">
         <is>
@@ -2927,7 +2933,7 @@
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P31" s="11" t="inlineStr">
@@ -2947,10 +2953,10 @@
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WGXOK</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
+          <t>Katana 18 HX A2WGXK</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -2972,14 +2978,10 @@
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr"/>
       <c r="J32" s="9" t="inlineStr"/>
       <c r="K32" s="9" t="inlineStr">
         <is>
@@ -3003,92 +3005,88 @@
       </c>
       <c r="O32" s="11" t="inlineStr">
         <is>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+        </is>
+      </c>
+      <c r="P32" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" hidden="1" outlineLevel="1">
+      <c r="A33" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Katana 18 HX A2WGXOK</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>RPL-HX Next 55W</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>顧曉琴</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr"/>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/08</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/30</t>
+        </is>
+      </c>
+      <c r="M33" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/19</t>
+        </is>
+      </c>
+      <c r="N33" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/30</t>
+        </is>
+      </c>
+      <c r="O33" s="11" t="inlineStr">
+        <is>
           <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
-      <c r="P32" s="11" t="inlineStr">
+      <c r="P33" s="11" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>13Q5</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Prestige 13 AI+ A4M</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>NVL-H 28W</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Intel® Arc™ Graphics</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>顏春梅</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/18</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>2026/10/08</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/21</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/22</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/22</t>
-        </is>
-      </c>
-      <c r="N33" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/31</t>
-        </is>
-      </c>
-      <c r="O33" s="6" t="inlineStr">
-        <is>
-          <t>DVT PCBA 調撥回台@8/21</t>
-        </is>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3098,469 +3096,469 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
+          <t>13Q5</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Prestige 13 AI+ A4M</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>NVL-H 28W</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>顏春梅</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/08</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/21</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/22</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/22</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/31</t>
+        </is>
+      </c>
+      <c r="O34" s="6" t="inlineStr">
+        <is>
+          <t>DVT RD 測試中</t>
+        </is>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
           <t>14T4</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Prestige 14 AI+ D4MG</t>
         </is>
       </c>
-      <c r="D34" s="17" t="inlineStr">
+      <c r="D35" s="18" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>NVL-H 30W</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>朱芳芳</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>2026/09/22</t>
         </is>
       </c>
-      <c r="K34" s="4" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>2026/11/12</t>
         </is>
       </c>
-      <c r="L34" s="4" t="inlineStr">
+      <c r="L35" s="4" t="inlineStr">
         <is>
           <t>2026/11/20</t>
         </is>
       </c>
-      <c r="M34" s="4" t="inlineStr">
+      <c r="M35" s="4" t="inlineStr">
         <is>
           <t>2026/12/21</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>2026/12/31</t>
         </is>
       </c>
-      <c r="O34" s="6" t="inlineStr">
-        <is>
-          <t>DVT RD test中 :8/4~9/7</t>
-        </is>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>DVT RD test中 :8/4~9/7，9/7 0B gerberout</t>
+        </is>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
-    <row r="35" hidden="1" outlineLevel="1">
-      <c r="A35" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
+    <row r="36" hidden="1" outlineLevel="1">
+      <c r="A36" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>14T4</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>Prestige 14 Flip AI+ D4MTG</t>
         </is>
       </c>
-      <c r="D35" s="15" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>NVL-H 30W</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F36" s="9" t="inlineStr">
         <is>
           <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
-      <c r="G35" s="9" t="inlineStr">
+      <c r="G36" s="9" t="inlineStr">
         <is>
           <t>朱芳芳</t>
         </is>
       </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="H36" s="9" t="inlineStr">
         <is>
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
+      <c r="I36" s="9" t="inlineStr">
         <is>
           <t>2026/07/27</t>
         </is>
       </c>
-      <c r="J35" s="9" t="inlineStr">
+      <c r="J36" s="9" t="inlineStr">
         <is>
           <t>2026/09/22</t>
         </is>
       </c>
-      <c r="K35" s="9" t="inlineStr">
+      <c r="K36" s="9" t="inlineStr">
         <is>
           <t>2026/11/12</t>
         </is>
       </c>
-      <c r="L35" s="9" t="inlineStr">
+      <c r="L36" s="9" t="inlineStr">
         <is>
           <t>2026/11/20</t>
         </is>
       </c>
-      <c r="M35" s="9" t="inlineStr">
+      <c r="M36" s="9" t="inlineStr">
         <is>
           <t>2026/12/21</t>
         </is>
       </c>
-      <c r="N35" s="9" t="inlineStr">
+      <c r="N36" s="9" t="inlineStr">
         <is>
           <t>2026/12/31</t>
         </is>
       </c>
-      <c r="O35" s="11" t="inlineStr">
-        <is>
-          <t>DVT RD test中 :8/4~9/7</t>
-        </is>
-      </c>
-      <c r="P35" s="11" t="inlineStr">
+      <c r="O36" s="11" t="inlineStr">
+        <is>
+          <t>DVT RD test中 :8/4~9/7，9/7 0B gerberout</t>
+        </is>
+      </c>
+      <c r="P36" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>Prestige 16 AI+</t>
         </is>
       </c>
-      <c r="D36" s="17" t="inlineStr">
+      <c r="D37" s="18" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>NVL-H 30W</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>朱芳芳</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="I36" s="4" t="inlineStr"/>
-      <c r="J36" s="4" t="inlineStr">
+      <c r="I37" s="4" t="inlineStr"/>
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>2026/09/22</t>
         </is>
       </c>
-      <c r="K36" s="4" t="inlineStr">
+      <c r="K37" s="4" t="inlineStr">
         <is>
           <t>2026/11/12</t>
         </is>
       </c>
-      <c r="L36" s="4" t="inlineStr">
+      <c r="L37" s="4" t="inlineStr">
         <is>
           <t>2026/11/20</t>
         </is>
       </c>
-      <c r="M36" s="4" t="inlineStr">
+      <c r="M37" s="4" t="inlineStr">
         <is>
           <t>2026/12/21</t>
         </is>
       </c>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="N37" s="4" t="inlineStr">
         <is>
           <t>2026/12/31</t>
         </is>
       </c>
-      <c r="O36" s="6" t="inlineStr">
-        <is>
-          <t>DVT RD test中 :8/4~9/7</t>
-        </is>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
+      <c r="O37" s="6" t="inlineStr">
+        <is>
+          <t>DVT RD test中 :8/4~9/7，9/7 0B gerberout</t>
+        </is>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
-    <row r="37" hidden="1" outlineLevel="1">
-      <c r="A37" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
+    <row r="38" hidden="1" outlineLevel="1">
+      <c r="A38" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>2624</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>Prestige 16 Flip AI+</t>
         </is>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>NVL-H 30W</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F38" s="9" t="inlineStr">
         <is>
           <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="G38" s="9" t="inlineStr">
         <is>
           <t>朱芳芳</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="H38" s="9" t="inlineStr">
         <is>
           <t>2026/05/14</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr"/>
-      <c r="J37" s="9" t="inlineStr">
+      <c r="I38" s="9" t="inlineStr"/>
+      <c r="J38" s="9" t="inlineStr">
         <is>
           <t>2026/09/22</t>
         </is>
       </c>
-      <c r="K37" s="9" t="inlineStr">
+      <c r="K38" s="9" t="inlineStr">
         <is>
           <t>2026/11/12</t>
         </is>
       </c>
-      <c r="L37" s="9" t="inlineStr">
+      <c r="L38" s="9" t="inlineStr">
         <is>
           <t>2026/11/20</t>
         </is>
       </c>
-      <c r="M37" s="9" t="inlineStr">
+      <c r="M38" s="9" t="inlineStr">
         <is>
           <t>2026/12/21</t>
         </is>
       </c>
-      <c r="N37" s="9" t="inlineStr">
+      <c r="N38" s="9" t="inlineStr">
         <is>
           <t>2026/12/31</t>
         </is>
       </c>
-      <c r="O37" s="11" t="inlineStr">
-        <is>
-          <t>DVT RD test中 :8/4~9/7</t>
-        </is>
-      </c>
-      <c r="P37" s="11" t="inlineStr">
+      <c r="O38" s="11" t="inlineStr">
+        <is>
+          <t>DVT RD test中 :8/4~9/7，9/7 0B gerberout</t>
+        </is>
+      </c>
+      <c r="P38" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>2633</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Stealth 16 AI+ B4WI</t>
         </is>
       </c>
-      <c r="D38" s="17" t="inlineStr">
+      <c r="D39" s="18" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>RTX 5080</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>朱欣怡</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I38" s="4" t="inlineStr">
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>2026/07/23</t>
         </is>
       </c>
-      <c r="J38" s="4" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K38" s="4" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L38" s="4" t="inlineStr">
+      <c r="L39" s="4" t="inlineStr">
         <is>
           <t>2026/11/30</t>
         </is>
       </c>
-      <c r="M38" s="4" t="inlineStr">
+      <c r="M39" s="4" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="N39" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O38" s="6" t="inlineStr">
+      <c r="O39" s="6" t="inlineStr">
         <is>
           <t>RD 測試中, 0N gerberout @8/25</t>
         </is>
       </c>
-      <c r="P38" s="6" t="inlineStr">
+      <c r="P39" s="6" t="inlineStr">
         <is>
           <t>1) Schedule:NV VBIOS @1/6, gating 8天,預計12/E 拿到WHQL，可能影響到最終TTM 時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" hidden="1" outlineLevel="1">
-      <c r="A39" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WH</t>
-        </is>
-      </c>
-      <c r="D39" s="15" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070Ti</t>
-        </is>
-      </c>
-      <c r="G39" s="9" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H39" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/23</t>
-        </is>
-      </c>
-      <c r="J39" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K39" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L39" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/30</t>
-        </is>
-      </c>
-      <c r="M39" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N39" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="O39" s="11" t="inlineStr">
-        <is>
-          <t>RD 測試中, 0N gerberout @8/25</t>
-        </is>
-      </c>
-      <c r="P39" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3575,231 +3573,230 @@
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
+          <t>Stealth 16 AI+ B4WH</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/23</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K40" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L40" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="M40" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N40" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="O40" s="11" t="inlineStr">
+        <is>
+          <t>RD 測試中, 0N gerberout @8/25</t>
+        </is>
+      </c>
+      <c r="P40" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" hidden="1" outlineLevel="1">
+      <c r="A41" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>2633</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
           <t>Stealth 16 AI+ B4WJ</t>
         </is>
       </c>
-      <c r="D40" s="15" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="F41" s="9" t="inlineStr">
         <is>
           <t>RTX 5090</t>
         </is>
       </c>
-      <c r="G40" s="9" t="inlineStr">
+      <c r="G41" s="9" t="inlineStr">
         <is>
           <t>朱欣怡</t>
         </is>
       </c>
-      <c r="H40" s="9" t="inlineStr">
+      <c r="H41" s="9" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
+      <c r="I41" s="9" t="inlineStr">
         <is>
           <t>2026/07/23</t>
         </is>
       </c>
-      <c r="J40" s="9" t="inlineStr">
+      <c r="J41" s="9" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K40" s="9" t="inlineStr">
+      <c r="K41" s="9" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L40" s="9" t="inlineStr">
+      <c r="L41" s="9" t="inlineStr">
         <is>
           <t>2026/11/30</t>
         </is>
       </c>
-      <c r="M40" s="9" t="inlineStr">
+      <c r="M41" s="9" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N40" s="9" t="inlineStr">
+      <c r="N41" s="9" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O40" s="11" t="inlineStr">
+      <c r="O41" s="11" t="inlineStr">
         <is>
           <t>RD 測試中, 0N gerberout @8/25</t>
         </is>
       </c>
-      <c r="P40" s="11" t="inlineStr">
+      <c r="P41" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>2634</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>Stealth 16 AI+ B4WE</t>
         </is>
       </c>
-      <c r="D41" s="17" t="inlineStr">
+      <c r="D42" s="18" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>賴雪鳳</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr">
+      <c r="I42" s="4" t="inlineStr">
         <is>
           <t>2026/07/31</t>
         </is>
       </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="J42" s="4" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K41" s="4" t="inlineStr">
+      <c r="K42" s="4" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L41" s="4" t="inlineStr">
+      <c r="L42" s="4" t="inlineStr">
         <is>
           <t>2026/11/27</t>
         </is>
       </c>
-      <c r="M41" s="4" t="inlineStr">
+      <c r="M42" s="4" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N41" s="4" t="inlineStr">
+      <c r="N42" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O41" s="6" t="inlineStr">
+      <c r="O42" s="6" t="inlineStr">
         <is>
           <t>0A PCBA DVT 驗證中,預計9/2 0B 出圖</t>
         </is>
       </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>1)NV VBIOS 驗證時間6周
-2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" hidden="1" outlineLevel="1">
-      <c r="A42" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WF</t>
-        </is>
-      </c>
-      <c r="D42" s="15" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G42" s="9" t="inlineStr">
-        <is>
-          <t>賴雪鳳</t>
-        </is>
-      </c>
-      <c r="H42" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/31</t>
-        </is>
-      </c>
-      <c r="J42" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K42" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L42" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/27</t>
-        </is>
-      </c>
-      <c r="M42" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N42" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="O42" s="11" t="inlineStr">
-        <is>
-          <t>0A PCBA DVT 驗證中,預計9/2 0B 出圖</t>
-        </is>
-      </c>
-      <c r="P42" s="11" t="inlineStr">
+      <c r="P42" s="6" t="inlineStr">
         <is>
           <t>1)NV VBIOS 驗證時間6周
 2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
@@ -3817,10 +3814,10 @@
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
-        </is>
-      </c>
-      <c r="D43" s="15" t="inlineStr">
+          <t>Stealth 16 AI+ B4WF</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3832,7 +3829,7 @@
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -3898,10 +3895,10 @@
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
-        </is>
-      </c>
-      <c r="D44" s="15" t="inlineStr">
+          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -3968,83 +3965,84 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
+    <row r="45" hidden="1" outlineLevel="1">
+      <c r="A45" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>14W1</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>Modern 14S H3M</t>
-        </is>
-      </c>
-      <c r="D45" s="18" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>WCL 25W</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>Intel® graphics</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>許婕</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/11</t>
-        </is>
-      </c>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/28</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/10</t>
-        </is>
-      </c>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/10</t>
-        </is>
-      </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/15</t>
-        </is>
-      </c>
-      <c r="M45" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/12</t>
-        </is>
-      </c>
-      <c r="N45" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/22</t>
-        </is>
-      </c>
-      <c r="O45" s="6" t="inlineStr">
-        <is>
-          <t>8/11 已kick off，预计9/14 0A gerberout</t>
-        </is>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>BOE FHD 120Hz panel MP料交期16w-20w，RD回復需等EVT 測試結束視結果備MP料，MP料最快到料時間3/E，機種MP 4/M，與target gap 2.5M</t>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>賴雪鳳</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/31</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K45" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/27</t>
+        </is>
+      </c>
+      <c r="M45" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N45" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="O45" s="11" t="inlineStr">
+        <is>
+          <t>0A PCBA DVT 驗證中,預計9/2 0B 出圖</t>
+        </is>
+      </c>
+      <c r="P45" s="11" t="inlineStr">
+        <is>
+          <t>1)NV VBIOS 驗證時間6周
+2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
     </row>
@@ -4054,15 +4052,15 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>14W1</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Modern 16S H3M</t>
-        </is>
-      </c>
-      <c r="D46" s="18" t="inlineStr">
+          <t>Modern 14S H3M</t>
+        </is>
+      </c>
+      <c r="D46" s="19" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
@@ -4119,12 +4117,12 @@
       </c>
       <c r="O46" s="6" t="inlineStr">
         <is>
-          <t>leverage Modern 14S H3M</t>
+          <t>8/11 已kick off，预计9/14 0A gerberout</t>
         </is>
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>BOE FHD 120Hz panel MP料交期16w-20w，RD回復需等EVT 測試結束視結果備MP料，MP料最快到料時間3/E，機種MP 4/M，與target gap 2.5M</t>
         </is>
       </c>
     </row>
@@ -4134,155 +4132,155 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
+          <t>2661</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Modern 16S H3M</t>
+        </is>
+      </c>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>WCL 25W</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Intel® graphics</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>許婕</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/28</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/10</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/10</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/15</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>2027/01/12</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>2027/01/22</t>
+        </is>
+      </c>
+      <c r="O47" s="6" t="inlineStr">
+        <is>
+          <t>leverage Modern 14S H3M</t>
+        </is>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
           <t>2654</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>Raider 16 Max HX B4WH</t>
         </is>
       </c>
-      <c r="D47" s="17" t="inlineStr">
+      <c r="D48" s="18" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>RTX 5070Ti</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>吳美芳</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I47" s="4" t="inlineStr">
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>2026/08/05</t>
         </is>
       </c>
-      <c r="J47" s="4" t="inlineStr">
+      <c r="J48" s="4" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K47" s="4" t="inlineStr">
+      <c r="K48" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L47" s="4" t="inlineStr">
+      <c r="L48" s="4" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M47" s="4" t="inlineStr">
+      <c r="M48" s="4" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N47" s="4" t="inlineStr">
+      <c r="N48" s="4" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O47" s="6" t="inlineStr">
+      <c r="O48" s="6" t="inlineStr">
         <is>
           <t>DVT RD測試中8/14~9/11，預計9/11 0N出圖</t>
         </is>
       </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" hidden="1" outlineLevel="1">
-      <c r="A48" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>2654</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>Raider 16 Max HX B4WI</t>
-        </is>
-      </c>
-      <c r="D48" s="15" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E48" s="9" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F48" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5080</t>
-        </is>
-      </c>
-      <c r="G48" s="9" t="inlineStr">
-        <is>
-          <t>吳美芳</t>
-        </is>
-      </c>
-      <c r="H48" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/05</t>
-        </is>
-      </c>
-      <c r="J48" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K48" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L48" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M48" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N48" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O48" s="11" t="inlineStr">
-        <is>
-          <t>DVT RD測試中8/14~9/11，預計9/11 0N出圖</t>
-        </is>
-      </c>
-      <c r="P48" s="11" t="inlineStr">
+      <c r="P48" s="6" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -4299,230 +4297,230 @@
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
+          <t>Raider 16 Max HX B4WI</t>
+        </is>
+      </c>
+      <c r="D49" s="16" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5080</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>吳美芳</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K49" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="L49" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M49" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N49" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O49" s="11" t="inlineStr">
+        <is>
+          <t>DVT RD測試中8/14~9/11，預計9/11 0N出圖</t>
+        </is>
+      </c>
+      <c r="P49" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" hidden="1" outlineLevel="1">
+      <c r="A50" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>2654</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
           <t>Raider 16 Max HX B4WJ</t>
         </is>
       </c>
-      <c r="D49" s="15" t="inlineStr">
+      <c r="D50" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr">
+      <c r="E50" s="9" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F49" s="9" t="inlineStr">
+      <c r="F50" s="9" t="inlineStr">
         <is>
           <t>RTX 5090</t>
         </is>
       </c>
-      <c r="G49" s="9" t="inlineStr">
+      <c r="G50" s="9" t="inlineStr">
         <is>
           <t>吳美芳</t>
         </is>
       </c>
-      <c r="H49" s="9" t="inlineStr">
+      <c r="H50" s="9" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr">
+      <c r="I50" s="9" t="inlineStr">
         <is>
           <t>2026/08/05</t>
         </is>
       </c>
-      <c r="J49" s="9" t="inlineStr">
+      <c r="J50" s="9" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K49" s="9" t="inlineStr">
+      <c r="K50" s="9" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L49" s="9" t="inlineStr">
+      <c r="L50" s="9" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M49" s="9" t="inlineStr">
+      <c r="M50" s="9" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N49" s="9" t="inlineStr">
+      <c r="N50" s="9" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O49" s="11" t="inlineStr">
+      <c r="O50" s="11" t="inlineStr">
         <is>
           <t>DVT RD測試中8/14~9/11，預計9/11 0N出圖</t>
         </is>
       </c>
-      <c r="P49" s="11" t="inlineStr">
+      <c r="P50" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>1851</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>Titan 18 HX B4WH</t>
         </is>
       </c>
-      <c r="D50" s="18" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="D51" s="18" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>RTX 5070Ti</t>
         </is>
       </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="G51" s="4" t="inlineStr">
         <is>
           <t>高宇奇</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr">
+      <c r="H51" s="4" t="inlineStr">
         <is>
           <t>2026/06/29</t>
         </is>
       </c>
-      <c r="I50" s="4" t="inlineStr">
+      <c r="I51" s="4" t="inlineStr">
         <is>
           <t>2026/08/19</t>
         </is>
       </c>
-      <c r="J50" s="4" t="inlineStr">
+      <c r="J51" s="4" t="inlineStr">
         <is>
           <t>2026/10/23</t>
         </is>
       </c>
-      <c r="K50" s="4" t="inlineStr">
+      <c r="K51" s="4" t="inlineStr">
         <is>
           <t>2027/01/08</t>
         </is>
       </c>
-      <c r="L50" s="4" t="inlineStr">
+      <c r="L51" s="4" t="inlineStr">
         <is>
           <t>2027/02/01</t>
         </is>
       </c>
-      <c r="M50" s="4" t="inlineStr">
+      <c r="M51" s="4" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N50" s="4" t="inlineStr">
+      <c r="N51" s="4" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O50" s="6" t="inlineStr">
-        <is>
-          <t>1) 根據料況及排程,已安排8/19 DVT上線SMT,打板後不測試立即入庫調撥,Target 8/24 for台北RD測試開機.</t>
-        </is>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" hidden="1" outlineLevel="1">
-      <c r="A51" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>1851</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>Titan 18 HX B4WI</t>
-        </is>
-      </c>
-      <c r="D51" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5080</t>
-        </is>
-      </c>
-      <c r="G51" s="9" t="inlineStr">
-        <is>
-          <t>高宇奇</t>
-        </is>
-      </c>
-      <c r="H51" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/19</t>
-        </is>
-      </c>
-      <c r="J51" s="9" t="inlineStr">
-        <is>
-          <t>2026/10/23</t>
-        </is>
-      </c>
-      <c r="K51" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/08</t>
-        </is>
-      </c>
-      <c r="L51" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/01</t>
-        </is>
-      </c>
-      <c r="M51" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N51" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O51" s="11" t="inlineStr">
-        <is>
-          <t>1) 根據料況及排程,已安排8/19 DVT上線SMT,打板後不測試立即入庫調撥,Target 8/24 for台北RD測試開機.</t>
-        </is>
-      </c>
-      <c r="P51" s="11" t="inlineStr">
+      <c r="O51" s="6" t="inlineStr">
+        <is>
+          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
+        </is>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
         <is>
           <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
         </is>
@@ -4539,12 +4537,12 @@
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Titan 18 HX B4WJ</t>
+          <t>Titan 18 HX B4WI</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
@@ -4554,7 +4552,7 @@
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="G52" s="9" t="inlineStr">
@@ -4599,7 +4597,7 @@
       </c>
       <c r="O52" s="11" t="inlineStr">
         <is>
-          <t>1) 根據料況及排程,已安排8/19 DVT上線SMT,打板後不測試立即入庫調撥,Target 8/24 for台北RD測試開機.</t>
+          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
         </is>
       </c>
       <c r="P52" s="11" t="inlineStr">
@@ -4619,22 +4617,22 @@
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Raider 18 Max HX B4WH</t>
+          <t>Titan 18 HX B4WJ</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>NVL-HX 65W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
@@ -4679,7 +4677,7 @@
       </c>
       <c r="O53" s="11" t="inlineStr">
         <is>
-          <t>1) 根據料況及排程,已安排8/19 DVT上線SMT,打板後不測試立即入庫調撥,Target 8/24 for台北RD測試開機.</t>
+          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
         </is>
       </c>
       <c r="P53" s="11" t="inlineStr">
@@ -4699,12 +4697,12 @@
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Raider 18 Max HX B4WI</t>
+          <t>Raider 18 Max HX B4WH</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
@@ -4714,7 +4712,7 @@
       </c>
       <c r="F54" s="9" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr">
@@ -4759,7 +4757,7 @@
       </c>
       <c r="O54" s="11" t="inlineStr">
         <is>
-          <t>1) 根據料況及排程,已安排8/19 DVT上線SMT,打板後不測試立即入庫調撥,Target 8/24 for台北RD測試開機.</t>
+          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
         </is>
       </c>
       <c r="P54" s="11" t="inlineStr">
@@ -4779,230 +4777,230 @@
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
+          <t>Raider 18 Max HX B4WI</t>
+        </is>
+      </c>
+      <c r="D55" s="16" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>NVL-HX 65W</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5080</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>高宇奇</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/23</t>
+        </is>
+      </c>
+      <c r="K55" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/08</t>
+        </is>
+      </c>
+      <c r="L55" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/01</t>
+        </is>
+      </c>
+      <c r="M55" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N55" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O55" s="11" t="inlineStr">
+        <is>
+          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
+        </is>
+      </c>
+      <c r="P55" s="11" t="inlineStr">
+        <is>
+          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" hidden="1" outlineLevel="1">
+      <c r="A56" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
           <t>Raider 18 Max HX B4WJ</t>
         </is>
       </c>
-      <c r="D55" s="16" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
         <is>
           <t>NVL-HX 65W</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr">
+      <c r="F56" s="9" t="inlineStr">
         <is>
           <t>RTX 5090</t>
         </is>
       </c>
-      <c r="G55" s="9" t="inlineStr">
+      <c r="G56" s="9" t="inlineStr">
         <is>
           <t>高宇奇</t>
         </is>
       </c>
-      <c r="H55" s="9" t="inlineStr">
+      <c r="H56" s="9" t="inlineStr">
         <is>
           <t>2026/06/29</t>
         </is>
       </c>
-      <c r="I55" s="9" t="inlineStr">
+      <c r="I56" s="9" t="inlineStr">
         <is>
           <t>2026/08/19</t>
         </is>
       </c>
-      <c r="J55" s="9" t="inlineStr">
+      <c r="J56" s="9" t="inlineStr">
         <is>
           <t>2026/10/23</t>
         </is>
       </c>
-      <c r="K55" s="9" t="inlineStr">
+      <c r="K56" s="9" t="inlineStr">
         <is>
           <t>2027/01/08</t>
         </is>
       </c>
-      <c r="L55" s="9" t="inlineStr">
+      <c r="L56" s="9" t="inlineStr">
         <is>
           <t>2027/02/01</t>
         </is>
       </c>
-      <c r="M55" s="9" t="inlineStr">
+      <c r="M56" s="9" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N55" s="9" t="inlineStr">
+      <c r="N56" s="9" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O55" s="11" t="inlineStr">
-        <is>
-          <t>1) 根據料況及排程,已安排8/19 DVT上線SMT,打板後不測試立即入庫調撥,Target 8/24 for台北RD測試開機.</t>
-        </is>
-      </c>
-      <c r="P55" s="11" t="inlineStr">
+      <c r="O56" s="11" t="inlineStr">
+        <is>
+          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
+        </is>
+      </c>
+      <c r="P56" s="11" t="inlineStr">
         <is>
           <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>2655</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>Crosshair 16 Max HX E4WEK</t>
         </is>
       </c>
-      <c r="D56" s="17" t="inlineStr">
+      <c r="D57" s="18" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="F57" s="4" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G56" s="4" t="inlineStr">
+      <c r="G57" s="4" t="inlineStr">
         <is>
           <t>鮑佩佩</t>
         </is>
       </c>
-      <c r="H56" s="4" t="inlineStr">
+      <c r="H57" s="4" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I56" s="4" t="inlineStr">
+      <c r="I57" s="4" t="inlineStr">
         <is>
           <t>2026/08/06</t>
         </is>
       </c>
-      <c r="J56" s="4" t="inlineStr">
+      <c r="J57" s="4" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K56" s="4" t="inlineStr">
+      <c r="K57" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L56" s="4" t="inlineStr">
+      <c r="L57" s="4" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M56" s="4" t="inlineStr">
+      <c r="M57" s="4" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N56" s="4" t="inlineStr">
+      <c r="N57" s="4" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O56" s="6" t="inlineStr">
+      <c r="O57" s="6" t="inlineStr">
         <is>
           <t>DVT 測試中</t>
         </is>
       </c>
-      <c r="P56" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" hidden="1" outlineLevel="1">
-      <c r="A57" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>2655</t>
-        </is>
-      </c>
-      <c r="C57" s="9" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WFK</t>
-        </is>
-      </c>
-      <c r="D57" s="15" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F57" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G57" s="9" t="inlineStr">
-        <is>
-          <t>鮑佩佩</t>
-        </is>
-      </c>
-      <c r="H57" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I57" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/06</t>
-        </is>
-      </c>
-      <c r="J57" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K57" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L57" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M57" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N57" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O57" s="11" t="inlineStr">
-        <is>
-          <t>DVT 測試中</t>
-        </is>
-      </c>
-      <c r="P57" s="11" t="inlineStr">
+      <c r="P57" s="6" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -5019,10 +5017,10 @@
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 16 Max HX E4WGK</t>
-        </is>
-      </c>
-      <c r="D58" s="15" t="inlineStr">
+          <t>Crosshair 16 Max HX E4WFK</t>
+        </is>
+      </c>
+      <c r="D58" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
@@ -5034,7 +5032,7 @@
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr">
@@ -5099,77 +5097,157 @@
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
+          <t>Crosshair 16 Max HX E4WGK</t>
+        </is>
+      </c>
+      <c r="D59" s="16" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>鮑佩佩</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="L59" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M59" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N59" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O59" s="11" t="inlineStr">
+        <is>
+          <t>DVT 測試中</t>
+        </is>
+      </c>
+      <c r="P59" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" hidden="1" outlineLevel="1">
+      <c r="A60" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>2655</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
           <t>Crosshair 16 Max HX E4WGXK</t>
         </is>
       </c>
-      <c r="D59" s="15" t="inlineStr">
+      <c r="D60" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E59" s="9" t="inlineStr">
+      <c r="E60" s="9" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F59" s="9" t="inlineStr">
+      <c r="F60" s="9" t="inlineStr">
         <is>
           <t>RTX 5070</t>
         </is>
       </c>
-      <c r="G59" s="9" t="inlineStr">
+      <c r="G60" s="9" t="inlineStr">
         <is>
           <t>鮑佩佩</t>
         </is>
       </c>
-      <c r="H59" s="9" t="inlineStr">
+      <c r="H60" s="9" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I59" s="9" t="inlineStr">
+      <c r="I60" s="9" t="inlineStr">
         <is>
           <t>2026/08/06</t>
         </is>
       </c>
-      <c r="J59" s="9" t="inlineStr">
+      <c r="J60" s="9" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K59" s="9" t="inlineStr">
+      <c r="K60" s="9" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L59" s="9" t="inlineStr">
+      <c r="L60" s="9" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M59" s="9" t="inlineStr">
+      <c r="M60" s="9" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N59" s="9" t="inlineStr">
+      <c r="N60" s="9" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O59" s="11" t="inlineStr">
+      <c r="O60" s="11" t="inlineStr">
         <is>
           <t>DVT 測試中</t>
         </is>
       </c>
-      <c r="P59" s="11" t="inlineStr">
+      <c r="P60" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P59"/>
+  <autoFilter ref="A1:P60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/npi_dashboard.xlsx
+++ b/npi_dashboard.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPI Dashboard" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NPI Dashboard'!$A$1:$P$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -522,7 +522,7 @@
     <outlinePr summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P60"/>
+  <dimension ref="A1:P58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -636,7 +636,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WEK</t>
+          <t>Katana 15 HX C14WFK</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="O2" s="6" t="inlineStr">
         <is>
-          <t>DDR5: RTX5050,8/28正式進入MP</t>
+          <t>DDR5: RTX5060預計C/R組裝@8/29 26PN077951C*50</t>
         </is>
       </c>
       <c r="P2" s="6" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WFK</t>
+          <t>Katana 15 HX C14WFOK</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -737,23 +737,23 @@
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/05/15</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>2026/06/01</t>
+          <t>2026/06/15</t>
         </is>
       </c>
       <c r="J3" s="9" t="inlineStr"/>
       <c r="K3" s="9" t="inlineStr">
         <is>
-          <t>2026/07/14</t>
+          <t>2026/07/24</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
         <is>
-          <t>2026/07/30</t>
+          <t>2026/08/07</t>
         </is>
       </c>
       <c r="M3" s="9" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="N3" s="9" t="inlineStr">
         <is>
-          <t>2026/08/30</t>
+          <t>2026/08/31</t>
         </is>
       </c>
       <c r="O3" s="11" t="inlineStr">
         <is>
-          <t>DDR5: RTX5060預計C/R組裝@8/29 26PN077951C*50</t>
+          <t>DDR4: RTX5060預計C/R組裝@8/29 26PN077951C*50</t>
         </is>
       </c>
       <c r="P3" s="11" t="inlineStr">
@@ -777,79 +777,83 @@
         </is>
       </c>
     </row>
-    <row r="4" hidden="1" outlineLevel="1">
-      <c r="A4" s="7" t="n">
+    <row r="4">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>15T3</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>Katana 15 HX C14WGK</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>2621</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Prestige N16 AI+ C1XMT</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>ATS</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>2026/04/20</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/01</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr"/>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/14</t>
-        </is>
-      </c>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/30</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>N1x 80W</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>林晉弘</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>2024/11/25</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>2025/01/20</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>2025/06/25</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>2026/03/12</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>2026/08/17</t>
         </is>
       </c>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/30</t>
-        </is>
-      </c>
-      <c r="O4" s="11" t="inlineStr">
-        <is>
-          <t>DDR5: RTX5070,8/28正式進入MP</t>
-        </is>
-      </c>
-      <c r="P4" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/31</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>ATS測試中</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>1)Battery life: BIOS導入BTP後，DQA測試modern standby battery life可達16.44 days，合乎MSFT標準。NV於Day0 rev.F版本針對功耗有所改善，Web browersing的測試，將後續更新測試BIOS與image後，重新測試。 2.ATS ASS'Y 8/18上線，8/20開始進行IRT測試。IRT測試目前發現問題如下。 a)手動reboot藍屏，DC/AC下各發現一台，error code 0x7E，為已知問題，與NV co-work中 b)平板模式下手動reboot，touch panel失效，測試17台發現1台，重啟現象消失，持續追蹤 c)camera test開始錄像/關閉錄像有延遲，4台發現2台，重開機後，現象消失，持續追蹤 d)手動S4 resume撥放音樂，插入耳機，耳機無聲，發現一台，RD分析中</t>
         </is>
       </c>
     </row>
@@ -859,12 +863,12 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>15T3</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Katana 15 HX C14WEOK</t>
+          <t>Prestige N16 Flip AI+ C1XMT</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
@@ -874,38 +878,42 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>N1x 80W</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>蔡東宏</t>
+          <t>林晉弘</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>2026/05/15</t>
+          <t>2024/11/25</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="inlineStr"/>
+          <t>2025/01/20</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>2025/06/25</t>
+        </is>
+      </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/03/12</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>2026/08/07</t>
+          <t>2026/06/30</t>
         </is>
       </c>
       <c r="M5" s="9" t="inlineStr">
@@ -920,474 +928,86 @@
       </c>
       <c r="O5" s="11" t="inlineStr">
         <is>
-          <t>DDR4: RTX5050,8/28正式進入MP</t>
+          <t>ATS測試中</t>
         </is>
       </c>
       <c r="P5" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" hidden="1" outlineLevel="1">
-      <c r="A6" s="7" t="n">
+          <t>1)Battery life: BIOS導入BTP後，DQA測試modern standby battery life可達16.44 days，合乎MSFT標準。NV於Day0 rev.F版本針對功耗有所改善，Web browersing的測試，將後續更新測試BIOS與image後，重新測試。 2.ATS ASS'Y 8/18上線，8/20開始進行IRT測試。IRT測試目前發現問題如下。 a)手動reboot藍屏，DC/AC下各發現一台，error code 0x7E，為已知問題，與NV co-work中 b)平板模式下手動reboot，touch panel失效，測試17台發現1台，重啟現象消失，持續追蹤 c)camera test開始錄像/關閉錄像有延遲，4台發現2台，重開機後，現象消失，持續追蹤 d)手動S4 resume撥放音樂，插入耳機，耳機無聲，發現一台，RD分析中</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>15T3</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Katana 15 HX C14WFOK</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>ATS</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/15</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="inlineStr"/>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/24</t>
-        </is>
-      </c>
-      <c r="L6" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="M6" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/17</t>
-        </is>
-      </c>
-      <c r="N6" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/31</t>
-        </is>
-      </c>
-      <c r="O6" s="11" t="inlineStr">
-        <is>
-          <t>DDR4: RTX5060預計C/R組裝@8/29 26PN077951C*50</t>
-        </is>
-      </c>
-      <c r="P6" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" hidden="1" outlineLevel="1">
-      <c r="A7" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>15T3</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Katana 15 HX C14WGOK</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>ATS</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>蔡東宏</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/15</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="inlineStr"/>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/24</t>
-        </is>
-      </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/07</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/17</t>
-        </is>
-      </c>
-      <c r="N7" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/31</t>
-        </is>
-      </c>
-      <c r="O7" s="11" t="inlineStr">
-        <is>
-          <t>DDR4: RTX5070,8/28正式進入MP</t>
-        </is>
-      </c>
-      <c r="P7" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>2621</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Prestige N16 AI+ C1XMT</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>ATS</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>N1x 80W</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>林晉弘</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>2024/11/25</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>2025/01/20</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>2025/06/25</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>2026/03/12</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/30</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/17</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/31</t>
-        </is>
-      </c>
-      <c r="O8" s="6" t="inlineStr">
-        <is>
-          <t>ATS測試中</t>
-        </is>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>1)Battery life: BIOS導入BTP後，DQA測試modern standby battery life可達16.44 days，合乎MSFT標準。NV於Day0 rev.F版本針對功耗有所改善，Web browersing的測試，將後續更新測試BIOS與image後，重新測試。 2.ATS ASS'Y 8/18上線，8/20開始進行IRT測試。IRT測試目前發現問題如下。 a)手動reboot藍屏，DC/AC下各發現一台，error code 0x7E，為已知問題，與NV co-work中 b)平板模式下手動reboot，touch panel失效，測試17台發現1台，重啟現象消失，持續追蹤 c)camera test開始錄像/關閉錄像有延遲，4台發現2台，重開機後，現象消失，持續追蹤 d)手動S4 resume撥放音樂，插入耳機，耳機無聲，發現一台，RD分析中</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" hidden="1" outlineLevel="1">
-      <c r="A9" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>2621</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Prestige N16 Flip AI+ C1XMT</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>ATS</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>N1x 80W</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>林晉弘</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>2024/11/25</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>2025/01/20</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t>2025/06/25</t>
-        </is>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>2026/03/12</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/30</t>
-        </is>
-      </c>
-      <c r="M9" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/17</t>
-        </is>
-      </c>
-      <c r="N9" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/31</t>
-        </is>
-      </c>
-      <c r="O9" s="11" t="inlineStr">
-        <is>
-          <t>ATS測試中</t>
-        </is>
-      </c>
-      <c r="P9" s="11" t="inlineStr">
-        <is>
-          <t>1)Battery life: BIOS導入BTP後，DQA測試modern standby battery life可達16.44 days，合乎MSFT標準。NV於Day0 rev.F版本針對功耗有所改善，Web browersing的測試，將後續更新測試BIOS與image後，重新測試。 2.ATS ASS'Y 8/18上線，8/20開始進行IRT測試。IRT測試目前發現問題如下。 a)手動reboot藍屏，DC/AC下各發現一台，error code 0x7E，為已知問題，與NV co-work中 b)平板模式下手動reboot，touch panel失效，測試17台發現1台，重啟現象消失，持續追蹤 c)camera test開始錄像/關閉錄像有延遲，4台發現2台，重開機後，現象消失，持續追蹤 d)手動S4 resume撥放音樂，插入耳機，耳機無聲，發現一台，RD分析中</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>15T2</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Venture 15 AI+ B3M</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>ATS</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>PTL-H 80W</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Intel® Arc™ Graphics</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>李文欽</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/20</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/26</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>24V1</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Modern 14 LE J3M</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>WCL 25W</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Intel® graphics</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>倪嬌嬌</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/02</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/07</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/29</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>2026/07/08</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/20</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/19</t>
-        </is>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/31</t>
-        </is>
-      </c>
-      <c r="O10" s="6" t="inlineStr">
-        <is>
-          <t>1) 8/28正式進入MP</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>24V1</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Modern 14 LE J3M</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>WCL 25W</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Intel® graphics</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>倪嬌嬌</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/02</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/07</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/29</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/08</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>2026/08/26</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>2026/09/07</t>
         </is>
       </c>
-      <c r="O11" s="6" t="inlineStr">
+      <c r="O6" s="6" t="inlineStr">
         <is>
           <t>微步：ATS ASSY@8/27早進行首件組裝, 客驗機器8/28 ready</t>
         </is>
       </c>
-      <c r="P11" s="6" t="inlineStr">
+      <c r="P6" s="6" t="inlineStr">
         <is>
           <t>1) Function issue：等8/27 BIOS 102作驗證 a.UCSI充电的OS信息, 驗證在60W的時候, 幾率性不跳OS彈窗 b.	User Password進入BSU, Storage Information &amp; System Information有灰階 c.	AC下无法透过1P15 Docking的LAN唤醒MODS d.	BSU下使用UEFI BIOS update方式有概率更新BIOS fail ME Issue:Drop &amp; Shock(non-OP)測試需使用ATS客驗機器複驗	 (
 2) ATS工單： 9S7-24V111-006*38 9S7-24V111-015*56 (
@@ -1396,77 +1016,77 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>26V1</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Modern 16 LE J3M</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>WCL 25W</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Intel® graphics</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>倪嬌嬌</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>2026/06/02</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>2026/07/07</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr"/>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>2026/07/29</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>2026/07/08</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>2026/08/26</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>2026/09/07</t>
         </is>
       </c>
-      <c r="O12" s="6" t="inlineStr">
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>MSI: MVT DQA test中 微步：ATS ASSY@8/25--會再匯整料況明確組裝時間</t>
         </is>
       </c>
-      <c r="P12" s="6" t="inlineStr">
+      <c r="P7" s="6" t="inlineStr">
         <is>
           <t>1) Function issue：同24V1 (
 2) ATS工單:  9S7-26V111-005*400 (
@@ -1475,77 +1095,77 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>15TK</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Cyborg A15 Max C1PWF</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>HWK 45W</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>RTX 5060</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>2026/05/28</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>2026/06/26</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>2026/08/07</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>2026/09/12</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>2026/09/22</t>
         </is>
       </c>
-      <c r="O13" s="6" t="inlineStr">
+      <c r="O8" s="6" t="inlineStr">
         <is>
           <t>HPT:MVT測試中</t>
         </is>
       </c>
-      <c r="P13" s="6" t="inlineStr">
+      <c r="P8" s="6" t="inlineStr">
         <is>
           <t>1).8/25 業務通知需專案開BTO,滿足業務已接訂單
 2).Schedule:AMD PI 1200I NDA Release delay(6/19→7/
@@ -1555,77 +1175,77 @@
         </is>
       </c>
     </row>
-    <row r="14" hidden="1" outlineLevel="1">
-      <c r="A14" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
+    <row r="9" hidden="1" outlineLevel="1">
+      <c r="A9" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>15TK</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Cyborg A15 C1PWE</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>MVT</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>HWK 45W</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>RTX 5050</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>蔡東宏</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>2026/05/28</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>2026/06/26</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr"/>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="J9" s="9" t="inlineStr"/>
+      <c r="K9" s="9" t="inlineStr">
         <is>
           <t>2026/08/07</t>
         </is>
       </c>
-      <c r="L14" s="9" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>2026/08/21</t>
         </is>
       </c>
-      <c r="M14" s="9" t="inlineStr">
+      <c r="M9" s="9" t="inlineStr">
         <is>
           <t>2026/09/12</t>
         </is>
       </c>
-      <c r="N14" s="9" t="inlineStr">
+      <c r="N9" s="9" t="inlineStr">
         <is>
           <t>2026/09/22</t>
         </is>
       </c>
-      <c r="O14" s="11" t="inlineStr">
+      <c r="O9" s="11" t="inlineStr">
         <is>
           <t>HPT:MVT測試中</t>
         </is>
       </c>
-      <c r="P14" s="11" t="inlineStr">
+      <c r="P9" s="11" t="inlineStr">
         <is>
           <t>1).Schedule:AMD PI 1200I NDA Release delay(6/19→7/
 28)與生管延後MVT SMT 排程(8/4→8/
@@ -1634,323 +1254,715 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>1T91</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Claw 8 EX AI+ CG3M</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>PTL-H 25W</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>楊淑賢</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>2025/12/16</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>2026/01/31</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/26</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/21</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/30</t>
+        </is>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>MVT DQA test中, 8/26-9/11</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>1）備料: 藍色機構件9/18, update ATS start@9/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>14T3</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Prestige N14 AI+ D1M</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>N1 35W</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>倪嬌嬌</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/30</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>2025/09/01</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/09</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/23</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t>MVT2 SMT@8/28, MVT ASSY@9/4-- depend on panel交期</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>1)備料：a. 2.8K panel: MP*1K交期, 計劃10/E ETD, 可滿足ATS需求, 但需持續追蹤DR set測試狀況 b. PCB原材: 1st MOQ1K,目前只先留300 pcs PCB原材for ATS use, 剩餘PCB原材料預估需11/E才能ready, PCB備料L/T 8weeks, PCB交料預估到一月份, 採購持續pull in中</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>2623</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Prestige N16 AI+ C1M</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>N1 45W</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>賴雪鳳</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>2025/04/30</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>2025/09/01</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>2026/04/15</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/14</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/09</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/23</t>
+        </is>
+      </c>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>MVT2 8/28 SMT , 9/2 Assy for 全部team member</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>備料: Samsung 2.8K panel 採購備料HR14*2K for N1 ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Katana 18 HX A14WEK</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>EVT</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>顧曉琴</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/12</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/21</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR5: EVT Pre-assy @ 8/25, ASSY @ 8/29, 預抓9/2提供給DQA測試</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" hidden="1" outlineLevel="1">
+      <c r="A14" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Katana 18 HX A14WFK</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>EVT</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>顧曉琴</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/12</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/21</t>
+        </is>
+      </c>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="O14" s="11" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR5: EVT Pre-assy @ 8/25, ASSY @ 8/29, 預抓9/2提供給DQA測試</t>
+        </is>
+      </c>
+      <c r="P14" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" hidden="1" outlineLevel="1">
+      <c r="A15" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>1T91</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Claw 8 EX AI+ CG3M</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>PTL-H 25W</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Katana 18 HX A14WGK</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>EVT</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>顧曉琴</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/12</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/21</t>
+        </is>
+      </c>
+      <c r="N15" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="O15" s="11" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR5: EVT Pre-assy @ 8/25, ASSY @ 8/29, 預抓9/2提供給DQA測試</t>
+        </is>
+      </c>
+      <c r="P15" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" hidden="1" outlineLevel="1">
+      <c r="A16" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Katana 18 HX A14WGXK</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>EVT</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>顧曉琴</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/15</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/13</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/12</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="M16" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/21</t>
+        </is>
+      </c>
+      <c r="N16" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="O16" s="11" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR5: EVT Pre-assy @ 8/25, ASSY @ 8/29, 預抓9/2提供給DQA測試</t>
+        </is>
+      </c>
+      <c r="P16" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" hidden="1" outlineLevel="1">
+      <c r="A17" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Katana 18 HX A14WEOK</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>顧曉琴</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr"/>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/20</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="M17" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/23</t>
+        </is>
+      </c>
+      <c r="N17" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/02</t>
+        </is>
+      </c>
+      <c r="O17" s="11" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+        </is>
+      </c>
+      <c r="P17" s="11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>楊淑賢</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>2025/11/06</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>2025/12/16</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>2026/01/31</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/26</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/18</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/21</t>
-        </is>
-      </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/30</t>
-        </is>
-      </c>
-      <c r="O15" s="6" t="inlineStr">
-        <is>
-          <t>MVT DQA test中, 8/26-9/11</t>
-        </is>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>1）備料: 藍色機構件9/18, update ATS start@9/21</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>14T3</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Prestige N14 AI+ D1M</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>N1 35W</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
+    </row>
+    <row r="18" hidden="1" outlineLevel="1">
+      <c r="A18" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Katana 18 HX A14WFOK</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>RPL-HX refresh 55W</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>顧曉琴</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr"/>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/20</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/02</t>
+        </is>
+      </c>
+      <c r="M18" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/23</t>
+        </is>
+      </c>
+      <c r="N18" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/02</t>
+        </is>
+      </c>
+      <c r="O18" s="11" t="inlineStr">
+        <is>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+        </is>
+      </c>
+      <c r="P18" s="11" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>倪嬌嬌</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>2025/04/30</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>2025/09/01</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/15</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/14</t>
-        </is>
-      </c>
-      <c r="M16" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/09</t>
-        </is>
-      </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/23</t>
-        </is>
-      </c>
-      <c r="O16" s="6" t="inlineStr">
-        <is>
-          <t>MVT2 SMT@8/28, MVT ASSY@9/4-- depend on panel交期</t>
-        </is>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>1)備料：a. 2.8K panel: MP*1K交期, 計劃10/E ETD, 可滿足ATS需求, 但需持續追蹤DR set測試狀況 b. PCB原材: 1st MOQ1K,目前只先留300 pcs PCB原材for ATS use, 剩餘PCB原材料預估需11/E才能ready, PCB備料L/T 8weeks, PCB交料預估到一月份, 採購持續pull in中</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>2623</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Prestige N16 AI+ C1M</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>MVT</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>N1 45W</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>賴雪鳳</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>2025/04/30</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>2025/09/01</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>2026/04/15</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/14</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/09</t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/23</t>
-        </is>
-      </c>
-      <c r="O17" s="6" t="inlineStr">
-        <is>
-          <t>MVT1:8/13 SMT, 8/14 Pre -Assy  for 少數RD 測試, 待PS SW ready 再上線做MVT2 for 全部team member</t>
-        </is>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>備料: Samsung 2.8K panel 採購備料HR14*2K for N1 ATS 用, 另外要再驗證HR16 for後續出貨需求</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Katana 18 HX A14WEK</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>EVT</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>RPL-HX refresh 55W</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>顧曉琴</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>2026/10/12</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/02</t>
-        </is>
-      </c>
-      <c r="M18" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/21</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/30</t>
-        </is>
-      </c>
-      <c r="O18" s="6" t="inlineStr">
-        <is>
-          <t>RPL-HX R + DDR5: EVT Pre-assy @ 8/25, ASSY @ 8/29, 預抓9/2提供給DQA測試</t>
-        </is>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1965,12 +1977,12 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WFK</t>
-        </is>
-      </c>
-      <c r="D19" s="15" t="inlineStr">
-        <is>
-          <t>EVT</t>
+          <t>Katana 18 HX A14WGOK</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -1980,7 +1992,7 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
@@ -1990,22 +2002,18 @@
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J19" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr"/>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>2026/10/12</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
@@ -2015,22 +2023,22 @@
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
-          <t>2026/11/21</t>
+          <t>2026/11/23</t>
         </is>
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2026/12/02</t>
         </is>
       </c>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: EVT Pre-assy @ 8/25, ASSY @ 8/29, 預抓9/2提供給DQA測試</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P19" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -2045,12 +2053,12 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGK</t>
-        </is>
-      </c>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>EVT</t>
+          <t>Katana 18 HX A14WGXOK</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -2070,22 +2078,18 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
+          <t>2026/05/20</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
+          <t>2026/06/27</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr"/>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>2026/10/12</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
@@ -2095,22 +2099,22 @@
       </c>
       <c r="M20" s="9" t="inlineStr">
         <is>
-          <t>2026/11/21</t>
+          <t>2026/11/23</t>
         </is>
       </c>
       <c r="N20" s="9" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2026/12/02</t>
         </is>
       </c>
       <c r="O20" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: EVT Pre-assy @ 8/25, ASSY @ 8/29, 預抓9/2提供給DQA測試</t>
+          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
         </is>
       </c>
       <c r="P20" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -2125,22 +2129,22 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGXK</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>EVT</t>
+          <t>Katana 18 HX A2WEK</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>RPL-HX Next 55W</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
@@ -2153,44 +2157,36 @@
           <t>2026/05/08</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/15</t>
-        </is>
-      </c>
-      <c r="J21" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/13</t>
-        </is>
-      </c>
+      <c r="I21" s="9" t="inlineStr"/>
+      <c r="J21" s="9" t="inlineStr"/>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>2026/10/12</t>
+          <t>2026/12/08</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>2026/11/02</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="M21" s="9" t="inlineStr">
         <is>
-          <t>2026/11/21</t>
+          <t>2027/01/19</t>
         </is>
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="O21" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR5: EVT Pre-assy @ 8/25, ASSY @ 8/29, 預抓9/2提供給DQA測試</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P21" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -2205,17 +2201,17 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WEOK</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Katana 18 HX A2WEOK</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>RPL-HX Next 55W</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
@@ -2241,27 +2237,27 @@
       <c r="J22" s="9" t="inlineStr"/>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/12/08</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>2026/11/02</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2027/01/19</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
         <is>
-          <t>2026/12/02</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="O22" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P22" s="11" t="inlineStr">
@@ -2281,17 +2277,17 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WFOK</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Katana 18 HX A2WFK</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>RPL-HX Next 55W</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
@@ -2306,38 +2302,34 @@
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr"/>
       <c r="J23" s="9" t="inlineStr"/>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/12/08</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>2026/11/02</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="M23" s="9" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2027/01/19</t>
         </is>
       </c>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>2026/12/02</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="O23" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P23" s="11" t="inlineStr">
@@ -2357,22 +2349,22 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGOK</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Katana 18 HX A2WFOK</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>RPL-HX Next 55W</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
@@ -2393,27 +2385,27 @@
       <c r="J24" s="9" t="inlineStr"/>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/12/08</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>2026/11/02</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="M24" s="9" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2027/01/19</t>
         </is>
       </c>
       <c r="N24" s="9" t="inlineStr">
         <is>
-          <t>2026/12/02</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="O24" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P24" s="11" t="inlineStr">
@@ -2433,17 +2425,17 @@
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A14WGXOK</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Katana 18 HX A2WGK</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX refresh 55W</t>
+          <t>RPL-HX Next 55W</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
@@ -2458,38 +2450,34 @@
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I25" s="9" t="inlineStr"/>
       <c r="J25" s="9" t="inlineStr"/>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>2026/10/20</t>
+          <t>2026/12/08</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
-          <t>2026/11/02</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="M25" s="9" t="inlineStr">
         <is>
-          <t>2026/11/23</t>
+          <t>2027/01/19</t>
         </is>
       </c>
       <c r="N25" s="9" t="inlineStr">
         <is>
-          <t>2026/12/02</t>
+          <t>2027/01/30</t>
         </is>
       </c>
       <c r="O25" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX R + DDR4: DVT test start @ 7/6, 待9/E進版3.1 go MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P25" s="11" t="inlineStr">
@@ -2509,7 +2497,7 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WEK</t>
+          <t>Katana 18 HX A2WGOK</t>
         </is>
       </c>
       <c r="D26" s="17" t="inlineStr">
@@ -2524,7 +2512,7 @@
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
@@ -2534,10 +2522,14 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I26" s="9" t="inlineStr"/>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
       <c r="J26" s="9" t="inlineStr"/>
       <c r="K26" s="9" t="inlineStr">
         <is>
@@ -2561,7 +2553,7 @@
       </c>
       <c r="O26" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P26" s="11" t="inlineStr">
@@ -2581,7 +2573,7 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WEOK</t>
+          <t>Katana 18 HX A2WGXK</t>
         </is>
       </c>
       <c r="D27" s="17" t="inlineStr">
@@ -2596,7 +2588,7 @@
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>RTX 5050</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
@@ -2606,14 +2598,10 @@
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
+          <t>2026/05/08</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="inlineStr"/>
       <c r="J27" s="9" t="inlineStr"/>
       <c r="K27" s="9" t="inlineStr">
         <is>
@@ -2637,7 +2625,7 @@
       </c>
       <c r="O27" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P27" s="11" t="inlineStr">
@@ -2657,7 +2645,7 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WFK</t>
+          <t>Katana 18 HX A2WGXOK</t>
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr">
@@ -2672,7 +2660,7 @@
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
@@ -2682,10 +2670,14 @@
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I28" s="9" t="inlineStr"/>
+          <t>2026/05/20</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/27</t>
+        </is>
+      </c>
       <c r="J28" s="9" t="inlineStr"/>
       <c r="K28" s="9" t="inlineStr">
         <is>
@@ -2709,7 +2701,7 @@
       </c>
       <c r="O28" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
         </is>
       </c>
       <c r="P28" s="11" t="inlineStr">
@@ -2718,151 +2710,163 @@
         </is>
       </c>
     </row>
-    <row r="29" hidden="1" outlineLevel="1">
-      <c r="A29" s="7" t="n">
+    <row r="29">
+      <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Katana 18 HX A2WFOK</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>RPL-HX Next 55W</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>顧曉琴</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="inlineStr"/>
-      <c r="K29" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/08</t>
-        </is>
-      </c>
-      <c r="L29" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/30</t>
-        </is>
-      </c>
-      <c r="M29" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/19</t>
-        </is>
-      </c>
-      <c r="N29" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/30</t>
-        </is>
-      </c>
-      <c r="O29" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
-        </is>
-      </c>
-      <c r="P29" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" hidden="1" outlineLevel="1">
-      <c r="A30" s="7" t="n">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>13Q5</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Prestige 13 AI+ A4M</t>
+        </is>
+      </c>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>NVL-H 28W</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>顏春梅</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>2026/10/08</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/21</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/22</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/22</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/31</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>DVT RD 測試中</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Katana 18 HX A2WGK</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>RPL-HX Next 55W</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>顧曉琴</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I30" s="9" t="inlineStr"/>
-      <c r="J30" s="9" t="inlineStr"/>
-      <c r="K30" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/08</t>
-        </is>
-      </c>
-      <c r="L30" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/30</t>
-        </is>
-      </c>
-      <c r="M30" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/19</t>
-        </is>
-      </c>
-      <c r="N30" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/30</t>
-        </is>
-      </c>
-      <c r="O30" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
-        </is>
-      </c>
-      <c r="P30" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>14T4</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Prestige 14 AI+ D4MG</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>NVL-H 30W</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>朱芳芳</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/22</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/12</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/20</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/21</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/31</t>
+        </is>
+      </c>
+      <c r="O30" s="6" t="inlineStr">
+        <is>
+          <t>DVT RD test中 :8/4~9/7，9/7 0B gerberout</t>
+        </is>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2872,145 +2876,153 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>14T4</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WGOK</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>Design</t>
+          <t>Prestige 14 Flip AI+ D4MTG</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX Next 55W</t>
+          <t>NVL-H 30W</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>顧曉琴</t>
+          <t>朱芳芳</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/14</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="inlineStr"/>
+          <t>2026/07/27</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/22</t>
+        </is>
+      </c>
       <c r="K31" s="9" t="inlineStr">
         <is>
-          <t>2026/12/08</t>
+          <t>2026/11/12</t>
         </is>
       </c>
       <c r="L31" s="9" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/11/20</t>
         </is>
       </c>
       <c r="M31" s="9" t="inlineStr">
         <is>
-          <t>2027/01/19</t>
+          <t>2026/12/21</t>
         </is>
       </c>
       <c r="N31" s="9" t="inlineStr">
         <is>
-          <t>2027/01/30</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="O31" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>DVT RD test中 :8/4~9/7，9/7 0B gerberout</t>
         </is>
       </c>
       <c r="P31" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" hidden="1" outlineLevel="1">
-      <c r="A32" s="7" t="n">
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Katana 18 HX A2WGXK</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>RPL-HX Next 55W</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>顧曉琴</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/08</t>
-        </is>
-      </c>
-      <c r="I32" s="9" t="inlineStr"/>
-      <c r="J32" s="9" t="inlineStr"/>
-      <c r="K32" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/08</t>
-        </is>
-      </c>
-      <c r="L32" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/30</t>
-        </is>
-      </c>
-      <c r="M32" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/19</t>
-        </is>
-      </c>
-      <c r="N32" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/30</t>
-        </is>
-      </c>
-      <c r="O32" s="11" t="inlineStr">
-        <is>
-          <t>RPL-HX Next + DDR5: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
-        </is>
-      </c>
-      <c r="P32" s="11" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>2624</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Prestige 16 AI+</t>
+        </is>
+      </c>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>NVL-H 30W</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Intel® Arc™ Graphics</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>朱芳芳</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr"/>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/22</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/12</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/20</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/21</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/31</t>
+        </is>
+      </c>
+      <c r="O32" s="6" t="inlineStr">
+        <is>
+          <t>DVT RD test中 :8/4~9/7，9/7 0B gerberout</t>
+        </is>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3020,73 +3032,73 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Katana 18 HX A2WGXOK</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr">
-        <is>
-          <t>Design</t>
+          <t>Prestige 16 Flip AI+</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>RPL-HX Next 55W</t>
+          <t>NVL-H 30W</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>Intel® Arc™ Graphics</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>顧曉琴</t>
+          <t>朱芳芳</t>
         </is>
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
-        </is>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/27</t>
-        </is>
-      </c>
-      <c r="J33" s="9" t="inlineStr"/>
+          <t>2026/05/14</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr"/>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/22</t>
+        </is>
+      </c>
       <c r="K33" s="9" t="inlineStr">
         <is>
-          <t>2026/12/08</t>
+          <t>2026/11/12</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/11/20</t>
         </is>
       </c>
       <c r="M33" s="9" t="inlineStr">
         <is>
-          <t>2027/01/19</t>
+          <t>2026/12/21</t>
         </is>
       </c>
       <c r="N33" s="9" t="inlineStr">
         <is>
-          <t>2027/01/30</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="O33" s="11" t="inlineStr">
         <is>
-          <t>RPL-HX Next+ DDR4: follow RPL HX Refresh, 待RPL HX Next QS sample WW49到料後安排MVT</t>
+          <t>DVT RD test中 :8/4~9/7，9/7 0B gerberout</t>
         </is>
       </c>
       <c r="P33" s="11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3096,12 +3108,12 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>13Q5</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Prestige 13 AI+ A4M</t>
+          <t>Stealth 16 AI+ B4WI</t>
         </is>
       </c>
       <c r="D34" s="18" t="inlineStr">
@@ -3111,140 +3123,140 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>NVL-H 28W</t>
+          <t>NVL-H 45W</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Intel® Arc™ Graphics</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>顏春梅</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
+          <t>2026/05/22</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>2026/08/18</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>2026/10/08</t>
+          <t>2026/09/16</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>2026/11/21</t>
+          <t>2026/11/11</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>2026/11/22</t>
+          <t>2026/11/30</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>2026/12/22</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="O34" s="6" t="inlineStr">
         <is>
-          <t>DVT RD 測試中</t>
+          <t>RD 測試中, 0N gerberout @8/25</t>
         </is>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
+          <t>1) Schedule:NV VBIOS @1/6, gating 8天,預計12/E 拿到WHQL，可能影響到最終TTM 時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" hidden="1" outlineLevel="1">
+      <c r="A35" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>14T4</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Prestige 14 AI+ D4MG</t>
-        </is>
-      </c>
-      <c r="D35" s="18" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>2633</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WH</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>NVL-H 30W</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>Intel® Arc™ Graphics</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>朱芳芳</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/14</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/27</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/22</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/12</t>
-        </is>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/20</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/21</t>
-        </is>
-      </c>
-      <c r="N35" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/31</t>
-        </is>
-      </c>
-      <c r="O35" s="6" t="inlineStr">
-        <is>
-          <t>DVT RD test中 :8/4~9/7，9/7 0B gerberout</t>
-        </is>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>NVL-H 45W</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>朱欣怡</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/23</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/16</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/11</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/30</t>
+        </is>
+      </c>
+      <c r="M35" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/29</t>
+        </is>
+      </c>
+      <c r="N35" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/11</t>
+        </is>
+      </c>
+      <c r="O35" s="11" t="inlineStr">
+        <is>
+          <t>RD 測試中, 0N gerberout @8/25</t>
+        </is>
+      </c>
+      <c r="P35" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -3256,12 +3268,12 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>14T4</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Prestige 14 Flip AI+ D4MTG</t>
+          <t>Stealth 16 AI+ B4WJ</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr">
@@ -3271,57 +3283,57 @@
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>NVL-H 30W</t>
+          <t>NVL-H 45W</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>Intel® Arc™ Graphics</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>朱芳芳</t>
+          <t>朱欣怡</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>2026/05/14</t>
+          <t>2026/05/22</t>
         </is>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>2026/07/27</t>
+          <t>2026/07/23</t>
         </is>
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>2026/09/22</t>
+          <t>2026/09/16</t>
         </is>
       </c>
       <c r="K36" s="9" t="inlineStr">
         <is>
-          <t>2026/11/12</t>
+          <t>2026/11/11</t>
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>2026/11/20</t>
+          <t>2026/11/30</t>
         </is>
       </c>
       <c r="M36" s="9" t="inlineStr">
         <is>
-          <t>2026/12/21</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="N36" s="9" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="O36" s="11" t="inlineStr">
         <is>
-          <t>DVT RD test中 :8/4~9/7，9/7 0B gerberout</t>
+          <t>RD 測試中, 0N gerberout @8/25</t>
         </is>
       </c>
       <c r="P36" s="11" t="inlineStr">
@@ -3336,12 +3348,12 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Prestige 16 AI+</t>
+          <t>Stealth 16 AI+ B4WE</t>
         </is>
       </c>
       <c r="D37" s="18" t="inlineStr">
@@ -3351,58 +3363,63 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>NVL-H 30W</t>
+          <t>NVL-H 45W</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Intel® Arc™ Graphics</t>
+          <t>RTX 5050</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>朱芳芳</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>2026/05/14</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr"/>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>2026/07/31</t>
+        </is>
+      </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>2026/09/22</t>
+          <t>2026/09/16</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>2026/11/12</t>
+          <t>2026/11/11</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>2026/11/20</t>
+          <t>2026/11/27</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>2026/12/21</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="O37" s="6" t="inlineStr">
         <is>
-          <t>DVT RD test中 :8/4~9/7，9/7 0B gerberout</t>
+          <t>0A PCBA DVT 驗證中,預計9/2 0B 出圖</t>
         </is>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)NV VBIOS 驗證時間6周
+2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
     </row>
@@ -3412,12 +3429,12 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Prestige 16 Flip AI+</t>
+          <t>Stealth 16 AI+ B4WF</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
@@ -3427,138 +3444,144 @@
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>NVL-H 30W</t>
+          <t>NVL-H 45W</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>Intel® Arc™ Graphics</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
-          <t>朱芳芳</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>2026/05/14</t>
-        </is>
-      </c>
-      <c r="I38" s="9" t="inlineStr"/>
+          <t>2026/05/22</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/31</t>
+        </is>
+      </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>2026/09/22</t>
+          <t>2026/09/16</t>
         </is>
       </c>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>2026/11/12</t>
+          <t>2026/11/11</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr">
         <is>
-          <t>2026/11/20</t>
+          <t>2026/11/27</t>
         </is>
       </c>
       <c r="M38" s="9" t="inlineStr">
         <is>
-          <t>2026/12/21</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="N38" s="9" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="O38" s="11" t="inlineStr">
         <is>
-          <t>DVT RD test中 :8/4~9/7，9/7 0B gerberout</t>
+          <t>0A PCBA DVT 驗證中,預計9/2 0B 出圖</t>
         </is>
       </c>
       <c r="P38" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
+          <t>1)NV VBIOS 驗證時間6周
+2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" hidden="1" outlineLevel="1">
+      <c r="A39" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WI</t>
-        </is>
-      </c>
-      <c r="D39" s="18" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>NVL-H 45W</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5080</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5070</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>賴雪鳳</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
         <is>
           <t>2026/05/22</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/23</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>2026/07/31</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="inlineStr">
         <is>
           <t>2026/09/16</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr">
+      <c r="K39" s="9" t="inlineStr">
         <is>
           <t>2026/11/11</t>
         </is>
       </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/30</t>
-        </is>
-      </c>
-      <c r="M39" s="4" t="inlineStr">
+      <c r="L39" s="9" t="inlineStr">
+        <is>
+          <t>2026/11/27</t>
+        </is>
+      </c>
+      <c r="M39" s="9" t="inlineStr">
         <is>
           <t>2026/12/29</t>
         </is>
       </c>
-      <c r="N39" s="4" t="inlineStr">
+      <c r="N39" s="9" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O39" s="6" t="inlineStr">
-        <is>
-          <t>RD 測試中, 0N gerberout @8/25</t>
-        </is>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>1) Schedule:NV VBIOS @1/6, gating 8天,預計12/E 拿到WHQL，可能影響到最終TTM 時間</t>
+      <c r="O39" s="11" t="inlineStr">
+        <is>
+          <t>0A PCBA DVT 驗證中,預計9/2 0B 出圖</t>
+        </is>
+      </c>
+      <c r="P39" s="11" t="inlineStr">
+        <is>
+          <t>1)NV VBIOS 驗證時間6周
+2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
         </is>
       </c>
     </row>
@@ -3568,12 +3591,12 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WH</t>
+          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
         </is>
       </c>
       <c r="D40" s="16" t="inlineStr">
@@ -3588,12 +3611,12 @@
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
-          <t>朱欣怡</t>
+          <t>賴雪鳳</t>
         </is>
       </c>
       <c r="H40" s="9" t="inlineStr">
@@ -3603,7 +3626,7 @@
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>2026/07/23</t>
+          <t>2026/07/31</t>
         </is>
       </c>
       <c r="J40" s="9" t="inlineStr">
@@ -3618,7 +3641,7 @@
       </c>
       <c r="L40" s="9" t="inlineStr">
         <is>
-          <t>2026/11/30</t>
+          <t>2026/11/27</t>
         </is>
       </c>
       <c r="M40" s="9" t="inlineStr">
@@ -3633,92 +3656,93 @@
       </c>
       <c r="O40" s="11" t="inlineStr">
         <is>
-          <t>RD 測試中, 0N gerberout @8/25</t>
+          <t>0A PCBA DVT 驗證中,預計9/2 0B 出圖</t>
         </is>
       </c>
       <c r="P40" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" hidden="1" outlineLevel="1">
-      <c r="A41" s="7" t="n">
+          <t>1)NV VBIOS 驗證時間6周
+2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WJ</t>
-        </is>
-      </c>
-      <c r="D41" s="16" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5090</t>
-        </is>
-      </c>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>朱欣怡</t>
-        </is>
-      </c>
-      <c r="H41" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/23</t>
-        </is>
-      </c>
-      <c r="J41" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K41" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L41" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/30</t>
-        </is>
-      </c>
-      <c r="M41" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N41" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="O41" s="11" t="inlineStr">
-        <is>
-          <t>RD 測試中, 0N gerberout @8/25</t>
-        </is>
-      </c>
-      <c r="P41" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>14W1</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Modern 14S H3M</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>WCL 25W</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Intel® graphics</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>許婕</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/28</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/10</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/10</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/15</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>2027/01/12</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>2027/01/22</t>
+        </is>
+      </c>
+      <c r="O41" s="6" t="inlineStr">
+        <is>
+          <t>8/11 已kick off，预计9/14 0A gerberout</t>
+        </is>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>BOE FHD 120Hz panel MP料交期16w-20w，RD回復需等EVT 測試結束視結果備MP料，MP料最快到料時間3/E，機種MP 4/M，與target gap 2.5M</t>
         </is>
       </c>
     </row>
@@ -3728,159 +3752,157 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WE</t>
-        </is>
-      </c>
-      <c r="D42" s="18" t="inlineStr">
+          <t>Modern 16S H3M</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>WCL 25W</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>Intel® graphics</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>許婕</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/11</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/28</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>2026/11/10</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/10</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/15</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>2027/01/12</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>2027/01/22</t>
+        </is>
+      </c>
+      <c r="O42" s="6" t="inlineStr">
+        <is>
+          <t>leverage Modern 14S H3M</t>
+        </is>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>2654</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Raider 16 Max HX B4WH</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>賴雪鳳</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>2026/07/31</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/27</t>
-        </is>
-      </c>
-      <c r="M42" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5070Ti</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>吳美芳</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/05</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="O42" s="6" t="inlineStr">
-        <is>
-          <t>0A PCBA DVT 驗證中,預計9/2 0B 出圖</t>
-        </is>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>1)NV VBIOS 驗證時間6周
-2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" hidden="1" outlineLevel="1">
-      <c r="A43" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>Stealth 16 AI+ B4WF</t>
-        </is>
-      </c>
-      <c r="D43" s="16" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>NVL-H 45W</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5060</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
-        <is>
-          <t>賴雪鳳</t>
-        </is>
-      </c>
-      <c r="H43" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/22</t>
-        </is>
-      </c>
-      <c r="I43" s="9" t="inlineStr">
-        <is>
-          <t>2026/07/31</t>
-        </is>
-      </c>
-      <c r="J43" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/16</t>
-        </is>
-      </c>
-      <c r="K43" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/11</t>
-        </is>
-      </c>
-      <c r="L43" s="9" t="inlineStr">
-        <is>
-          <t>2026/11/27</t>
-        </is>
-      </c>
-      <c r="M43" s="9" t="inlineStr">
-        <is>
-          <t>2026/12/29</t>
-        </is>
-      </c>
-      <c r="N43" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="O43" s="11" t="inlineStr">
-        <is>
-          <t>0A PCBA DVT 驗證中,預計9/2 0B 出圖</t>
-        </is>
-      </c>
-      <c r="P43" s="11" t="inlineStr">
-        <is>
-          <t>1)NV VBIOS 驗證時間6周
-2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>2027/02/02</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O43" s="6" t="inlineStr">
+        <is>
+          <t>DVT RD測試中8/14~9/11，預計9/11 0N出圖</t>
+        </is>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3890,12 +3912,12 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WG/GD7 8GB</t>
+          <t>Raider 16 Max HX B4WI</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
@@ -3905,63 +3927,62 @@
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>NVL-H 45W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="F44" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5080</t>
         </is>
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="H44" s="9" t="inlineStr">
         <is>
-          <t>2026/05/22</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
-          <t>2026/07/31</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>2026/09/16</t>
+          <t>2026/09/29</t>
         </is>
       </c>
       <c r="K44" s="9" t="inlineStr">
         <is>
-          <t>2026/11/11</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="L44" s="9" t="inlineStr">
         <is>
-          <t>2026/11/27</t>
+          <t>2027/02/02</t>
         </is>
       </c>
       <c r="M44" s="9" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2027/03/08</t>
         </is>
       </c>
       <c r="N44" s="9" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2027/03/18</t>
         </is>
       </c>
       <c r="O44" s="11" t="inlineStr">
         <is>
-          <t>0A PCBA DVT 驗證中,預計9/2 0B 出圖</t>
+          <t>DVT RD測試中8/14~9/11，預計9/11 0N出圖</t>
         </is>
       </c>
       <c r="P44" s="11" t="inlineStr">
         <is>
-          <t>1)NV VBIOS 驗證時間6周
-2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3971,12 +3992,12 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Stealth 16 AI+ B4WGX/GD7 12GB</t>
+          <t>Raider 16 Max HX B4WJ</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
@@ -3986,63 +4007,62 @@
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>NVL-H 45W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070</t>
+          <t>RTX 5090</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>賴雪鳳</t>
+          <t>吳美芳</t>
         </is>
       </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
-          <t>2026/05/22</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>2026/07/31</t>
+          <t>2026/08/05</t>
         </is>
       </c>
       <c r="J45" s="9" t="inlineStr">
         <is>
-          <t>2026/09/16</t>
+          <t>2026/09/29</t>
         </is>
       </c>
       <c r="K45" s="9" t="inlineStr">
         <is>
-          <t>2026/11/11</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="L45" s="9" t="inlineStr">
         <is>
-          <t>2026/11/27</t>
+          <t>2027/02/02</t>
         </is>
       </c>
       <c r="M45" s="9" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2027/03/08</t>
         </is>
       </c>
       <c r="N45" s="9" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2027/03/18</t>
         </is>
       </c>
       <c r="O45" s="11" t="inlineStr">
         <is>
-          <t>0A PCBA DVT 驗證中,預計9/2 0B 出圖</t>
+          <t>DVT RD測試中8/14~9/11，預計9/11 0N出圖</t>
         </is>
       </c>
       <c r="P45" s="11" t="inlineStr">
         <is>
-          <t>1)NV VBIOS 驗證時間6周
-2)Intel WHQL :12/E 拿到 可能影響到最終TTM 時間</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4052,237 +4072,237 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>14W1</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Modern 14S H3M</t>
-        </is>
-      </c>
-      <c r="D46" s="19" t="inlineStr">
-        <is>
-          <t>Design</t>
+          <t>Titan 18 HX B4WH</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>DVT</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>WCL 25W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Intel® graphics</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>許婕</t>
+          <t>高宇奇</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>2026/08/11</t>
+          <t>2026/06/29</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>2026/09/28</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>2026/11/10</t>
+          <t>2026/10/23</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>2026/12/10</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>2026/12/15</t>
+          <t>2027/02/01</t>
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>2027/01/12</t>
+          <t>2027/03/08</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>2027/01/22</t>
+          <t>2027/03/18</t>
         </is>
       </c>
       <c r="O46" s="6" t="inlineStr">
         <is>
-          <t>8/11 已kick off，预计9/14 0A gerberout</t>
+          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
         </is>
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
-          <t>BOE FHD 120Hz panel MP料交期16w-20w，RD回復需等EVT 測試結束視結果備MP料，MP料最快到料時間3/E，機種MP 4/M，與target gap 2.5M</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
+          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" hidden="1" outlineLevel="1">
+      <c r="A47" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>2661</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>Modern 16S H3M</t>
-        </is>
-      </c>
-      <c r="D47" s="19" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>WCL 25W</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>Intel® graphics</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>許婕</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/11</t>
-        </is>
-      </c>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/28</t>
-        </is>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>2026/11/10</t>
-        </is>
-      </c>
-      <c r="K47" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/10</t>
-        </is>
-      </c>
-      <c r="L47" s="4" t="inlineStr">
-        <is>
-          <t>2026/12/15</t>
-        </is>
-      </c>
-      <c r="M47" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/12</t>
-        </is>
-      </c>
-      <c r="N47" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/22</t>
-        </is>
-      </c>
-      <c r="O47" s="6" t="inlineStr">
-        <is>
-          <t>leverage Modern 14S H3M</t>
-        </is>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Titan 18 HX B4WI</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5080</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>高宇奇</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/23</t>
+        </is>
+      </c>
+      <c r="K47" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/08</t>
+        </is>
+      </c>
+      <c r="L47" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/01</t>
+        </is>
+      </c>
+      <c r="M47" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N47" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O47" s="11" t="inlineStr">
+        <is>
+          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
+        </is>
+      </c>
+      <c r="P47" s="11" t="inlineStr">
+        <is>
+          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" hidden="1" outlineLevel="1">
+      <c r="A48" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>2654</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>Raider 16 Max HX B4WH</t>
-        </is>
-      </c>
-      <c r="D48" s="18" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Titan 18 HX B4WJ</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
         <is>
           <t>DVT</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E48" s="9" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5070Ti</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>吳美芳</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/05</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K48" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M48" s="4" t="inlineStr">
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5090</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>高宇奇</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/23</t>
+        </is>
+      </c>
+      <c r="K48" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/08</t>
+        </is>
+      </c>
+      <c r="L48" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/01</t>
+        </is>
+      </c>
+      <c r="M48" s="9" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N48" s="4" t="inlineStr">
+      <c r="N48" s="9" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O48" s="6" t="inlineStr">
-        <is>
-          <t>DVT RD測試中8/14~9/11，預計9/11 0N出圖</t>
-        </is>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>NA</t>
+      <c r="O48" s="11" t="inlineStr">
+        <is>
+          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
+        </is>
+      </c>
+      <c r="P48" s="11" t="inlineStr">
+        <is>
+          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
         </is>
       </c>
     </row>
@@ -4292,12 +4312,12 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B4WI</t>
+          <t>Raider 18 Max HX B4WH</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
@@ -4307,42 +4327,42 @@
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>NVL-HX 55W</t>
+          <t>NVL-HX 65W</t>
         </is>
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070Ti</t>
         </is>
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
-          <t>吳美芳</t>
+          <t>高宇奇</t>
         </is>
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/06/29</t>
         </is>
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
-          <t>2026/08/05</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>2026/09/29</t>
+          <t>2026/10/23</t>
         </is>
       </c>
       <c r="K49" s="9" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2027/01/08</t>
         </is>
       </c>
       <c r="L49" s="9" t="inlineStr">
         <is>
-          <t>2027/02/02</t>
+          <t>2027/02/01</t>
         </is>
       </c>
       <c r="M49" s="9" t="inlineStr">
@@ -4357,12 +4377,12 @@
       </c>
       <c r="O49" s="11" t="inlineStr">
         <is>
-          <t>DVT RD測試中8/14~9/11，預計9/11 0N出圖</t>
+          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
         </is>
       </c>
       <c r="P49" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4392,12 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Raider 16 Max HX B4WJ</t>
+          <t>Raider 18 Max HX B4WI</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
@@ -4387,222 +4407,222 @@
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
+          <t>NVL-HX 65W</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5080</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>高宇奇</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/23</t>
+        </is>
+      </c>
+      <c r="K50" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/08</t>
+        </is>
+      </c>
+      <c r="L50" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/01</t>
+        </is>
+      </c>
+      <c r="M50" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N50" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O50" s="11" t="inlineStr">
+        <is>
+          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
+        </is>
+      </c>
+      <c r="P50" s="11" t="inlineStr">
+        <is>
+          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" hidden="1" outlineLevel="1">
+      <c r="A51" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>Raider 18 Max HX B4WJ</t>
+        </is>
+      </c>
+      <c r="D51" s="16" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>NVL-HX 65W</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5090</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>高宇奇</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/23</t>
+        </is>
+      </c>
+      <c r="K51" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/08</t>
+        </is>
+      </c>
+      <c r="L51" s="9" t="inlineStr">
+        <is>
+          <t>2027/02/01</t>
+        </is>
+      </c>
+      <c r="M51" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/08</t>
+        </is>
+      </c>
+      <c r="N51" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/18</t>
+        </is>
+      </c>
+      <c r="O51" s="11" t="inlineStr">
+        <is>
+          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
+        </is>
+      </c>
+      <c r="P51" s="11" t="inlineStr">
+        <is>
+          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>2655</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Crosshair 16 Max HX E4WEK</t>
+        </is>
+      </c>
+      <c r="D52" s="18" t="inlineStr">
+        <is>
+          <t>DVT</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F50" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5090</t>
-        </is>
-      </c>
-      <c r="G50" s="9" t="inlineStr">
-        <is>
-          <t>吳美芳</t>
-        </is>
-      </c>
-      <c r="H50" s="9" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>鮑佩佩</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/05</t>
-        </is>
-      </c>
-      <c r="J50" s="9" t="inlineStr">
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/06</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
         <is>
           <t>2026/09/29</t>
         </is>
       </c>
-      <c r="K50" s="9" t="inlineStr">
+      <c r="K52" s="4" t="inlineStr">
         <is>
           <t>2027/01/11</t>
         </is>
       </c>
-      <c r="L50" s="9" t="inlineStr">
+      <c r="L52" s="4" t="inlineStr">
         <is>
           <t>2027/02/02</t>
         </is>
       </c>
-      <c r="M50" s="9" t="inlineStr">
+      <c r="M52" s="4" t="inlineStr">
         <is>
           <t>2027/03/08</t>
         </is>
       </c>
-      <c r="N50" s="9" t="inlineStr">
+      <c r="N52" s="4" t="inlineStr">
         <is>
           <t>2027/03/18</t>
         </is>
       </c>
-      <c r="O50" s="11" t="inlineStr">
-        <is>
-          <t>DVT RD測試中8/14~9/11，預計9/11 0N出圖</t>
-        </is>
-      </c>
-      <c r="P50" s="11" t="inlineStr">
+      <c r="O52" s="6" t="inlineStr">
+        <is>
+          <t>DVT 測試中</t>
+        </is>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
         <is>
           <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>1851</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Titan 18 HX B4WH</t>
-        </is>
-      </c>
-      <c r="D51" s="18" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5070Ti</t>
-        </is>
-      </c>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>高宇奇</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/19</t>
-        </is>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>2026/10/23</t>
-        </is>
-      </c>
-      <c r="K51" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/08</t>
-        </is>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>2027/02/01</t>
-        </is>
-      </c>
-      <c r="M51" s="4" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N51" s="4" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O51" s="6" t="inlineStr">
-        <is>
-          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
-        </is>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" hidden="1" outlineLevel="1">
-      <c r="A52" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>1851</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>Titan 18 HX B4WI</t>
-        </is>
-      </c>
-      <c r="D52" s="16" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F52" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5080</t>
-        </is>
-      </c>
-      <c r="G52" s="9" t="inlineStr">
-        <is>
-          <t>高宇奇</t>
-        </is>
-      </c>
-      <c r="H52" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/19</t>
-        </is>
-      </c>
-      <c r="J52" s="9" t="inlineStr">
-        <is>
-          <t>2026/10/23</t>
-        </is>
-      </c>
-      <c r="K52" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/08</t>
-        </is>
-      </c>
-      <c r="L52" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/01</t>
-        </is>
-      </c>
-      <c r="M52" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N52" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O52" s="11" t="inlineStr">
-        <is>
-          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
-        </is>
-      </c>
-      <c r="P52" s="11" t="inlineStr">
-        <is>
-          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4632,12 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Titan 18 HX B4WJ</t>
+          <t>Crosshair 16 Max HX E4WFK</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
@@ -4632,37 +4652,37 @@
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>RTX 5090</t>
+          <t>RTX 5060</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>高宇奇</t>
+          <t>鮑佩佩</t>
         </is>
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
-          <t>2026/08/19</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
-          <t>2026/10/23</t>
+          <t>2026/09/29</t>
         </is>
       </c>
       <c r="K53" s="9" t="inlineStr">
         <is>
-          <t>2027/01/08</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="L53" s="9" t="inlineStr">
         <is>
-          <t>2027/02/01</t>
+          <t>2027/02/02</t>
         </is>
       </c>
       <c r="M53" s="9" t="inlineStr">
@@ -4677,12 +4697,12 @@
       </c>
       <c r="O53" s="11" t="inlineStr">
         <is>
-          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
+          <t>DVT 測試中</t>
         </is>
       </c>
       <c r="P53" s="11" t="inlineStr">
         <is>
-          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4692,12 +4712,12 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Raider 18 Max HX B4WH</t>
+          <t>Crosshair 16 Max HX E4WGK</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
@@ -4707,42 +4727,42 @@
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>NVL-HX 65W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="F54" s="9" t="inlineStr">
         <is>
-          <t>RTX 5070Ti</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
-          <t>高宇奇</t>
+          <t>鮑佩佩</t>
         </is>
       </c>
       <c r="H54" s="9" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="I54" s="9" t="inlineStr">
         <is>
-          <t>2026/08/19</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>2026/10/23</t>
+          <t>2026/09/29</t>
         </is>
       </c>
       <c r="K54" s="9" t="inlineStr">
         <is>
-          <t>2027/01/08</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="L54" s="9" t="inlineStr">
         <is>
-          <t>2027/02/01</t>
+          <t>2027/02/02</t>
         </is>
       </c>
       <c r="M54" s="9" t="inlineStr">
@@ -4757,12 +4777,12 @@
       </c>
       <c r="O54" s="11" t="inlineStr">
         <is>
-          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
+          <t>DVT 測試中</t>
         </is>
       </c>
       <c r="P54" s="11" t="inlineStr">
         <is>
-          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4772,12 +4792,12 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Raider 18 Max HX B4WI</t>
+          <t>Crosshair 16 Max HX E4WGXK</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
@@ -4787,42 +4807,42 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>NVL-HX 65W</t>
+          <t>NVL-HX 55W</t>
         </is>
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>RTX 5080</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
-          <t>高宇奇</t>
+          <t>鮑佩佩</t>
         </is>
       </c>
       <c r="H55" s="9" t="inlineStr">
         <is>
-          <t>2026/06/29</t>
+          <t>2026/05/19</t>
         </is>
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
-          <t>2026/08/19</t>
+          <t>2026/08/06</t>
         </is>
       </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
-          <t>2026/10/23</t>
+          <t>2026/09/29</t>
         </is>
       </c>
       <c r="K55" s="9" t="inlineStr">
         <is>
-          <t>2027/01/08</t>
+          <t>2027/01/11</t>
         </is>
       </c>
       <c r="L55" s="9" t="inlineStr">
         <is>
-          <t>2027/02/01</t>
+          <t>2027/02/02</t>
         </is>
       </c>
       <c r="M55" s="9" t="inlineStr">
@@ -4837,170 +4857,166 @@
       </c>
       <c r="O55" s="11" t="inlineStr">
         <is>
-          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
+          <t>DVT 測試中</t>
         </is>
       </c>
       <c r="P55" s="11" t="inlineStr">
         <is>
-          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" hidden="1" outlineLevel="1">
-      <c r="A56" s="7" t="n">
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>1851</t>
-        </is>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>Raider 18 Max HX B4WJ</t>
-        </is>
-      </c>
-      <c r="D56" s="16" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>NVL-HX 65W</t>
-        </is>
-      </c>
-      <c r="F56" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5090</t>
-        </is>
-      </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>高宇奇</t>
-        </is>
-      </c>
-      <c r="H56" s="9" t="inlineStr">
-        <is>
-          <t>2026/06/29</t>
-        </is>
-      </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/19</t>
-        </is>
-      </c>
-      <c r="J56" s="9" t="inlineStr">
-        <is>
-          <t>2026/10/23</t>
-        </is>
-      </c>
-      <c r="K56" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/08</t>
-        </is>
-      </c>
-      <c r="L56" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/01</t>
-        </is>
-      </c>
-      <c r="M56" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N56" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O56" s="11" t="inlineStr">
-        <is>
-          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
-        </is>
-      </c>
-      <c r="P56" s="11" t="inlineStr">
-        <is>
-          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>1862</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Crosshair 18 Max HX B4WE</t>
+        </is>
+      </c>
+      <c r="D56" s="19" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>NVL-HX 55W</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>RTX 5050</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>劉芬</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>2026/09/28</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>2026/12/07</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>2027/01/22</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>2027/03/03</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="inlineStr">
+        <is>
+          <t>2027/03/31</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>2027/04/14</t>
+        </is>
+      </c>
+      <c r="O56" s="6" t="inlineStr">
+        <is>
+          <t>0A layout進行中</t>
+        </is>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" hidden="1" outlineLevel="1">
+      <c r="A57" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>2655</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WEK</t>
-        </is>
-      </c>
-      <c r="D57" s="18" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>1862</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>Crosshair 18 Max HX B4WF</t>
+        </is>
+      </c>
+      <c r="D57" s="17" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
         <is>
           <t>NVL-HX 55W</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>RTX 5050</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>鮑佩佩</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I57" s="4" t="inlineStr">
-        <is>
-          <t>2026/08/06</t>
-        </is>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K57" s="4" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M57" s="4" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N57" s="4" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O57" s="6" t="inlineStr">
-        <is>
-          <t>DVT 測試中</t>
-        </is>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>RTX 5060</t>
+        </is>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>劉芬</t>
+        </is>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>2026/09/28</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="inlineStr">
+        <is>
+          <t>2026/12/07</t>
+        </is>
+      </c>
+      <c r="K57" s="9" t="inlineStr">
+        <is>
+          <t>2027/01/22</t>
+        </is>
+      </c>
+      <c r="L57" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/03</t>
+        </is>
+      </c>
+      <c r="M57" s="9" t="inlineStr">
+        <is>
+          <t>2027/03/31</t>
+        </is>
+      </c>
+      <c r="N57" s="9" t="inlineStr">
+        <is>
+          <t>2027/04/14</t>
+        </is>
+      </c>
+      <c r="O57" s="11" t="inlineStr"/>
+      <c r="P57" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -5012,17 +5028,17 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Crosshair 16 Max HX E4WFK</t>
-        </is>
-      </c>
-      <c r="D58" s="16" t="inlineStr">
-        <is>
-          <t>DVT</t>
+          <t>Crosshair 18 Max HX B4WG</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="inlineStr">
+        <is>
+          <t>Design</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
@@ -5032,222 +5048,58 @@
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>RTX 5060</t>
+          <t>RTX 5070</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>鮑佩佩</t>
+          <t>劉芬</t>
         </is>
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/08/21</t>
         </is>
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
-          <t>2026/08/06</t>
+          <t>2026/09/28</t>
         </is>
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>2026/09/29</t>
+          <t>2026/12/07</t>
         </is>
       </c>
       <c r="K58" s="9" t="inlineStr">
         <is>
-          <t>2027/01/11</t>
+          <t>2027/01/22</t>
         </is>
       </c>
       <c r="L58" s="9" t="inlineStr">
         <is>
-          <t>2027/02/02</t>
+          <t>2027/03/03</t>
         </is>
       </c>
       <c r="M58" s="9" t="inlineStr">
         <is>
-          <t>2027/03/08</t>
+          <t>2027/03/31</t>
         </is>
       </c>
       <c r="N58" s="9" t="inlineStr">
         <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O58" s="11" t="inlineStr">
-        <is>
-          <t>DVT 測試中</t>
-        </is>
-      </c>
+          <t>2027/04/14</t>
+        </is>
+      </c>
+      <c r="O58" s="11" t="inlineStr"/>
       <c r="P58" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
     </row>
-    <row r="59" hidden="1" outlineLevel="1">
-      <c r="A59" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>2655</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WGK</t>
-        </is>
-      </c>
-      <c r="D59" s="16" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E59" s="9" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F59" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>鮑佩佩</t>
-        </is>
-      </c>
-      <c r="H59" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/06</t>
-        </is>
-      </c>
-      <c r="J59" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K59" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L59" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M59" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N59" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O59" s="11" t="inlineStr">
-        <is>
-          <t>DVT 測試中</t>
-        </is>
-      </c>
-      <c r="P59" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" hidden="1" outlineLevel="1">
-      <c r="A60" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>2655</t>
-        </is>
-      </c>
-      <c r="C60" s="9" t="inlineStr">
-        <is>
-          <t>Crosshair 16 Max HX E4WGXK</t>
-        </is>
-      </c>
-      <c r="D60" s="16" t="inlineStr">
-        <is>
-          <t>DVT</t>
-        </is>
-      </c>
-      <c r="E60" s="9" t="inlineStr">
-        <is>
-          <t>NVL-HX 55W</t>
-        </is>
-      </c>
-      <c r="F60" s="9" t="inlineStr">
-        <is>
-          <t>RTX 5070</t>
-        </is>
-      </c>
-      <c r="G60" s="9" t="inlineStr">
-        <is>
-          <t>鮑佩佩</t>
-        </is>
-      </c>
-      <c r="H60" s="9" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
-        </is>
-      </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>2026/08/06</t>
-        </is>
-      </c>
-      <c r="J60" s="9" t="inlineStr">
-        <is>
-          <t>2026/09/29</t>
-        </is>
-      </c>
-      <c r="K60" s="9" t="inlineStr">
-        <is>
-          <t>2027/01/11</t>
-        </is>
-      </c>
-      <c r="L60" s="9" t="inlineStr">
-        <is>
-          <t>2027/02/02</t>
-        </is>
-      </c>
-      <c r="M60" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/08</t>
-        </is>
-      </c>
-      <c r="N60" s="9" t="inlineStr">
-        <is>
-          <t>2027/03/18</t>
-        </is>
-      </c>
-      <c r="O60" s="11" t="inlineStr">
-        <is>
-          <t>DVT 測試中</t>
-        </is>
-      </c>
-      <c r="P60" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P60"/>
+  <autoFilter ref="A1:P58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/npi_dashboard.xlsx
+++ b/npi_dashboard.xlsx
@@ -847,16 +847,16 @@
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>HPT:MVT進行中, APU R7 155 ETD@9/21, 暫定9/24進行C/R@26PN081119C*50</t>
+          <t>HPT:MVT進行中, 預計9/11 ATS@26PN083486A*100</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>1).8/31 業務通知決定收斂到Max, non Max 還有最後2.9K 套料, 接完就收斂.現在開始的新報價往Max
+          <t>1).9/3 業務通知:R7 155 報價單會改回在non-Max sku,優先消化non-Max thermal庫存
 2).Schedule:AMD PI 1200I NDA Release delay(6/19→7/
-28)與生管延後MVT SMT 排程(8/4→8/
-7),累計delay 42天,取消 DVT排程改以 APU Rework 驗證追趕時程後,MP還是會delay 22天至9/22(先前已由 9 /17提前至 8/31,現又延至9/
-22),後續將依實際測試結果滾動式調整專案時程</t>
+28)與生管延後MVT SMT (8/4→8/
+7),累計delay 42天,取消 DVT排程改以 APU Rework 驗證追趕進度後,MP還是會delay 22天至9/22(先前已由 9 /17提前至 8/31,現又延至9/
+22)</t>
         </is>
       </c>
     </row>
@@ -927,16 +927,16 @@
       </c>
       <c r="O5" s="12" t="inlineStr">
         <is>
-          <t>HPT:MVT進行中, 預計9/11 ATS@26PN083486A*100</t>
+          <t>HPT:MVT進行中, APU R7 155 ETD@9/21, 暫定9/24進行C/R@26PN081119C*50</t>
         </is>
       </c>
       <c r="P5" s="12" t="inlineStr">
         <is>
-          <t>1).8/31 業務通知決定收斂到Max, non Max 還有最後2.9K 套料, 接完就收斂.現在開始的新報價往Max
+          <t>1).9/3 業務通知:R7 155 報價單會改回在non-Max sku,優先消化non-Max thermal庫存
 2).Schedule:AMD PI 1200I NDA Release delay(6/19→7/
-28)與生管延後MVT SMT 排程(8/4→8/
-7),累計delay 42天,取消 DVT排程改以 APU Rework 驗證追趕時程後,MP還是會delay 22天至9/22(先前已由 9 /17提前至 8/31,現又延至9/
-22),後續將依實際測試結果滾動式調整專案時程</t>
+28)與生管延後MVT SMT (8/4→8/
+7),累計delay 42天,取消 DVT排程改以 APU Rework 驗證追趕進度後,MP還是會delay 22天至9/22(先前已由 9 /17提前至 8/31,現又延至9/
+22)</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)備料: 業務尚未提供1st lot需求, 塑膠顆粒先按MOQ備料</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="P10" s="12" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)備料: 業務尚未提供1st lot需求, 塑膠顆粒先按MOQ備料</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)備料: 業務尚未提供1st lot需求, 塑膠顆粒先按MOQ備料</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>1)備料: 業務尚未提供1st lot需求, 塑膠顆粒先按MOQ備料</t>
         </is>
       </c>
     </row>
@@ -3828,12 +3828,12 @@
       </c>
       <c r="O42" s="6" t="inlineStr">
         <is>
-          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
+          <t>DVT板子測試中</t>
         </is>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
-          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
+          <t>1851目前上4支memory才能開機,RD正在跟Intel debug/study此問題.</t>
         </is>
       </c>
     </row>
@@ -3908,12 +3908,12 @@
       </c>
       <c r="O43" s="12" t="inlineStr">
         <is>
-          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
+          <t>DVT板子測試中</t>
         </is>
       </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
-          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
+          <t>1851目前上4支memory才能開機,RD正在跟Intel debug/study此問題.</t>
         </is>
       </c>
     </row>
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O44" s="12" t="inlineStr">
         <is>
-          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
+          <t>DVT板子測試中</t>
         </is>
       </c>
       <c r="P44" s="12" t="inlineStr">
         <is>
-          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
+          <t>1851目前上4支memory才能開機,RD正在跟Intel debug/study此問題.</t>
         </is>
       </c>
     </row>
@@ -4068,12 +4068,12 @@
       </c>
       <c r="O45" s="12" t="inlineStr">
         <is>
-          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
+          <t>DVT板子測試中</t>
         </is>
       </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
+          <t>1851目前上4支memory才能開機,RD正在跟Intel debug/study此問題.</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="O46" s="12" t="inlineStr">
         <is>
-          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
+          <t>DVT板子測試中</t>
         </is>
       </c>
       <c r="P46" s="12" t="inlineStr">
         <is>
-          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
+          <t>1851目前上4支memory才能開機,RD正在跟Intel debug/study此問題.</t>
         </is>
       </c>
     </row>
@@ -4228,12 +4228,12 @@
       </c>
       <c r="O47" s="12" t="inlineStr">
         <is>
-          <t>1) DVT板子已於8/24到台北,目前板子已開機並分發給各team member開始進行測試.</t>
+          <t>DVT板子測試中</t>
         </is>
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>1) 根據SSE POC會議討論共識,1851最後採用2顆MCU架構for所有的發光device,並且根據SSE提出的建議,第1顆MCU控制Per key KB,另1顆MCU控制其餘所有發光device,預計9月初提供1台1851 mockup系統for SSE FW implement.</t>
+          <t>1851目前上4支memory才能開機,RD正在跟Intel debug/study此問題.</t>
         </is>
       </c>
     </row>

--- a/npi_dashboard.xlsx
+++ b/npi_dashboard.xlsx
@@ -847,7 +847,7 @@
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>HPT:MVT進行中, 預計9/11 ATS@26PN083486A*100</t>
+          <t>HPT: 預計9/11 ATS@26PN083486A*100</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="O5" s="12" t="inlineStr">
         <is>
-          <t>HPT:MVT進行中, APU R7 155 ETD@9/21, 暫定9/24進行C/R@26PN081119C*50</t>
+          <t>HPT: APU R7 155 ETD@9/21, 暫定9/24進行C/R@26PN081119C*50</t>
         </is>
       </c>
       <c r="P5" s="12" t="inlineStr">
